--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F24"/>
+  <dimension ref="B2:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C12" s="52">
-        <f>-'02_Parametres'!$D$22*'06_Structure'!D18</f>
+        <f>-'02_Parametres'!$D$24*'06_Structure'!D18</f>
         <v/>
       </c>
       <c r="D12" s="39">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="C13" s="61">
-        <f>'06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$22*'06_Structure'!D18</f>
+        <f>'06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$24*'06_Structure'!D18</f>
         <v/>
       </c>
       <c r="D13" s="61">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C14" s="64">
-        <f>IFERROR(('06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$22*'06_Structure'!D18)/'06_Structure'!D18,0)</f>
+        <f>IFERROR(('06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$24*'06_Structure'!D18)/'06_Structure'!D18,0)</f>
         <v/>
       </c>
       <c r="D14" s="65">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C16" s="61">
-        <f>'06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$22*'06_Structure'!D18-'06_Structure'!I18</f>
+        <f>'06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$24*'06_Structure'!D18-'06_Structure'!I18</f>
         <v/>
       </c>
       <c r="D16" s="61">
@@ -1426,43 +1426,54 @@
     <row r="21">
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  + Effet Volume (Δ effectif × tarif N-1)</t>
+          <t xml:space="preserve">  + Effet Volume (Δ effectif)</t>
         </is>
       </c>
       <c r="C21" s="39">
-        <f>SUMPRODUCT(('07_Moteur'!$R$3:$R$60-'07_Moteur'!$F$3:$F$60)*'07_Moteur'!$J$3:$J$60)</f>
+        <f>SUMPRODUCT(('07_Moteur'!$R$3:$R$60-'07_Moteur'!$F$3:$F$60)*'07_Moteur'!$J$3:$J$60*'07_Moteur'!$AB$3:$AB$60)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  + Effet Prix (effectif Bud × Δ tarif)</t>
+          <t xml:space="preserve">  + Effet Tarif (hausse prix)</t>
         </is>
       </c>
       <c r="C22" s="39">
-        <f>SUMPRODUCT('07_Moteur'!$R$3:$R$60*('07_Moteur'!$S$3:$S$60-'07_Moteur'!$J$3:$J$60))</f>
+        <f>SUMPRODUCT('07_Moteur'!$R$3:$R$60*('07_Moteur'!$S$3:$S$60-'07_Moteur'!$J$3:$J$60)*'07_Moteur'!$AB$3:$AB$60)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  + Effet Signature (financement OPCO)</t>
+        </is>
+      </c>
+      <c r="C23" s="39">
+        <f>SUMPRODUCT('07_Moteur'!$R$3:$R$60*'07_Moteur'!$S$3:$S$60*('07_Moteur'!$AC$3:$AC$60-'07_Moteur'!$AB$3:$AB$60))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  + Effet Frais de dossier</t>
         </is>
       </c>
-      <c r="C23" s="39">
-        <f>SUMPRODUCT('07_Moteur'!$P$3:$P$60)*'02_Parametres'!$D$20-SUMPRODUCT('07_Moteur'!$G$3:$G$60)*'02_Parametres'!$D$20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="40" t="inlineStr">
+      <c r="C24" s="39">
+        <f>SUMPRODUCT('07_Moteur'!$P$3:$P$60)*'02_Parametres'!$D$22-SUMPRODUCT('07_Moteur'!$G$3:$G$60)*'02_Parametres'!$D$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>CA Budget N+1</t>
         </is>
       </c>
-      <c r="C24" s="42">
+      <c r="C25" s="42">
         <f>SUM('07_Moteur'!$T$3:$T$60)</f>
         <v/>
       </c>
@@ -1631,7 +1642,7 @@
         <v/>
       </c>
       <c r="J4" s="39">
-        <f>(F4-G4)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F4-G4)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K4" s="16">
@@ -1643,7 +1654,7 @@
         <v/>
       </c>
       <c r="M4" s="46">
-        <f>IFERROR(G4*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S3-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G4*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S3*'07_Moteur'!AC3-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N4" s="46">
@@ -1693,7 +1704,7 @@
         <v/>
       </c>
       <c r="J5" s="39">
-        <f>(F5-G5)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F5-G5)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K5" s="16">
@@ -1705,7 +1716,7 @@
         <v/>
       </c>
       <c r="M5" s="46">
-        <f>IFERROR(G5*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S4-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G5*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S4*'07_Moteur'!AC4-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N5" s="46">
@@ -1755,7 +1766,7 @@
         <v/>
       </c>
       <c r="J6" s="39">
-        <f>(F6-G6)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F6-G6)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K6" s="16">
@@ -1767,7 +1778,7 @@
         <v/>
       </c>
       <c r="M6" s="46">
-        <f>IFERROR(G6*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S5-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G6*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S5*'07_Moteur'!AC5-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N6" s="46">
@@ -1817,7 +1828,7 @@
         <v/>
       </c>
       <c r="J7" s="39">
-        <f>(F7-G7)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F7-G7)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K7" s="16">
@@ -1829,7 +1840,7 @@
         <v/>
       </c>
       <c r="M7" s="46">
-        <f>IFERROR(G7*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S6-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G7*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S6*'07_Moteur'!AC6-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N7" s="46">
@@ -1879,7 +1890,7 @@
         <v/>
       </c>
       <c r="J8" s="39">
-        <f>(F8-G8)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F8-G8)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K8" s="16">
@@ -1891,7 +1902,7 @@
         <v/>
       </c>
       <c r="M8" s="46">
-        <f>IFERROR(G8*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S7-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G8*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S7*'07_Moteur'!AC7-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N8" s="46">
@@ -1941,7 +1952,7 @@
         <v/>
       </c>
       <c r="J9" s="39">
-        <f>(F9-G9)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F9-G9)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K9" s="16">
@@ -1953,7 +1964,7 @@
         <v/>
       </c>
       <c r="M9" s="46">
-        <f>IFERROR(G9*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S8-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G9*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S8*'07_Moteur'!AC8-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N9" s="46">
@@ -2003,7 +2014,7 @@
         <v/>
       </c>
       <c r="J10" s="39">
-        <f>(F10-G10)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F10-G10)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K10" s="16">
@@ -2015,7 +2026,7 @@
         <v/>
       </c>
       <c r="M10" s="46">
-        <f>IFERROR(G10*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S9-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G10*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S9*'07_Moteur'!AC9-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N10" s="46">
@@ -2065,7 +2076,7 @@
         <v/>
       </c>
       <c r="J11" s="39">
-        <f>(F11-G11)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F11-G11)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K11" s="16">
@@ -2077,7 +2088,7 @@
         <v/>
       </c>
       <c r="M11" s="46">
-        <f>IFERROR(G11*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S10-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G11*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S10*'07_Moteur'!AC10-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N11" s="46">
@@ -2127,7 +2138,7 @@
         <v/>
       </c>
       <c r="J12" s="39">
-        <f>(F12-G12)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F12-G12)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K12" s="16">
@@ -2139,7 +2150,7 @@
         <v/>
       </c>
       <c r="M12" s="46">
-        <f>IFERROR(G12*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S11-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G12*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S11*'07_Moteur'!AC11-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N12" s="46">
@@ -2189,7 +2200,7 @@
         <v/>
       </c>
       <c r="J13" s="39">
-        <f>(F13-G13)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F13-G13)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K13" s="16">
@@ -2201,7 +2212,7 @@
         <v/>
       </c>
       <c r="M13" s="46">
-        <f>IFERROR(G13*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S12-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G13*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S12*'07_Moteur'!AC12-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N13" s="46">
@@ -2251,7 +2262,7 @@
         <v/>
       </c>
       <c r="J14" s="39">
-        <f>(F14-G14)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F14-G14)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K14" s="16">
@@ -2263,7 +2274,7 @@
         <v/>
       </c>
       <c r="M14" s="46">
-        <f>IFERROR(G14*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S13-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G14*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S13*'07_Moteur'!AC13-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N14" s="46">
@@ -2313,7 +2324,7 @@
         <v/>
       </c>
       <c r="J15" s="39">
-        <f>(F15-G15)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F15-G15)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K15" s="16">
@@ -2325,7 +2336,7 @@
         <v/>
       </c>
       <c r="M15" s="46">
-        <f>IFERROR(G15*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S14-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G15*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S14*'07_Moteur'!AC14-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N15" s="46">
@@ -2375,7 +2386,7 @@
         <v/>
       </c>
       <c r="J16" s="39">
-        <f>(F16-G16)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F16-G16)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K16" s="16">
@@ -2387,7 +2398,7 @@
         <v/>
       </c>
       <c r="M16" s="46">
-        <f>IFERROR(G16*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S15-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G16*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S15*'07_Moteur'!AC15-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N16" s="46">
@@ -2437,7 +2448,7 @@
         <v/>
       </c>
       <c r="J17" s="39">
-        <f>(F17-G17)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F17-G17)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K17" s="16">
@@ -2449,7 +2460,7 @@
         <v/>
       </c>
       <c r="M17" s="46">
-        <f>IFERROR(G17*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S16-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G17*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S16*'07_Moteur'!AC16-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N17" s="46">
@@ -2499,7 +2510,7 @@
         <v/>
       </c>
       <c r="J18" s="39">
-        <f>(F18-G18)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F18-G18)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K18" s="16">
@@ -2511,7 +2522,7 @@
         <v/>
       </c>
       <c r="M18" s="46">
-        <f>IFERROR(G18*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S17-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G18*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S17*'07_Moteur'!AC17-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N18" s="46">
@@ -2561,7 +2572,7 @@
         <v/>
       </c>
       <c r="J19" s="39">
-        <f>(F19-G19)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F19-G19)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K19" s="16">
@@ -2573,7 +2584,7 @@
         <v/>
       </c>
       <c r="M19" s="46">
-        <f>IFERROR(G19*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S18-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G19*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S18*'07_Moteur'!AC18-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N19" s="46">
@@ -2623,7 +2634,7 @@
         <v/>
       </c>
       <c r="J20" s="39">
-        <f>(F20-G20)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F20-G20)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K20" s="16">
@@ -2635,7 +2646,7 @@
         <v/>
       </c>
       <c r="M20" s="46">
-        <f>IFERROR(G20*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S19-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G20*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S19*'07_Moteur'!AC19-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N20" s="46">
@@ -2685,7 +2696,7 @@
         <v/>
       </c>
       <c r="J21" s="39">
-        <f>(F21-G21)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F21-G21)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K21" s="16">
@@ -2697,7 +2708,7 @@
         <v/>
       </c>
       <c r="M21" s="46">
-        <f>IFERROR(G21*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S20-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G21*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S20*'07_Moteur'!AC20-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N21" s="46">
@@ -2747,7 +2758,7 @@
         <v/>
       </c>
       <c r="J22" s="39">
-        <f>(F22-G22)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F22-G22)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K22" s="16">
@@ -2759,7 +2770,7 @@
         <v/>
       </c>
       <c r="M22" s="46">
-        <f>IFERROR(G22*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S21-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G22*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S21*'07_Moteur'!AC21-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N22" s="46">
@@ -2809,7 +2820,7 @@
         <v/>
       </c>
       <c r="J23" s="39">
-        <f>(F23-G23)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F23-G23)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K23" s="16">
@@ -2821,7 +2832,7 @@
         <v/>
       </c>
       <c r="M23" s="46">
-        <f>IFERROR(G23*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S22-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G23*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S22*'07_Moteur'!AC22-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N23" s="46">
@@ -2871,7 +2882,7 @@
         <v/>
       </c>
       <c r="J24" s="39">
-        <f>(F24-G24)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F24-G24)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K24" s="16">
@@ -2883,7 +2894,7 @@
         <v/>
       </c>
       <c r="M24" s="46">
-        <f>IFERROR(G24*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S23-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G24*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S23*'07_Moteur'!AC23-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N24" s="46">
@@ -2933,7 +2944,7 @@
         <v/>
       </c>
       <c r="J25" s="39">
-        <f>(F25-G25)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F25-G25)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K25" s="16">
@@ -2945,7 +2956,7 @@
         <v/>
       </c>
       <c r="M25" s="46">
-        <f>IFERROR(G25*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S24-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G25*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S24*'07_Moteur'!AC24-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N25" s="46">
@@ -2995,7 +3006,7 @@
         <v/>
       </c>
       <c r="J26" s="39">
-        <f>(F26-G26)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F26-G26)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K26" s="16">
@@ -3007,7 +3018,7 @@
         <v/>
       </c>
       <c r="M26" s="46">
-        <f>IFERROR(G26*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S25-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G26*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S25*'07_Moteur'!AC25-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N26" s="46">
@@ -3057,7 +3068,7 @@
         <v/>
       </c>
       <c r="J27" s="39">
-        <f>(F27-G27)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F27-G27)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K27" s="16">
@@ -3069,7 +3080,7 @@
         <v/>
       </c>
       <c r="M27" s="46">
-        <f>IFERROR(G27*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S26-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G27*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S26*'07_Moteur'!AC26-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N27" s="46">
@@ -3119,7 +3130,7 @@
         <v/>
       </c>
       <c r="J28" s="39">
-        <f>(F28-G28)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F28-G28)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K28" s="16">
@@ -3131,7 +3142,7 @@
         <v/>
       </c>
       <c r="M28" s="46">
-        <f>IFERROR(G28*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S27-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G28*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S27*'07_Moteur'!AC27-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N28" s="46">
@@ -3181,7 +3192,7 @@
         <v/>
       </c>
       <c r="J29" s="39">
-        <f>(F29-G29)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F29-G29)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K29" s="16">
@@ -3193,7 +3204,7 @@
         <v/>
       </c>
       <c r="M29" s="46">
-        <f>IFERROR(G29*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S28-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G29*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S28*'07_Moteur'!AC28-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N29" s="46">
@@ -3243,7 +3254,7 @@
         <v/>
       </c>
       <c r="J30" s="39">
-        <f>(F30-G30)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F30-G30)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K30" s="16">
@@ -3255,7 +3266,7 @@
         <v/>
       </c>
       <c r="M30" s="46">
-        <f>IFERROR(G30*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S29-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G30*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S29*'07_Moteur'!AC29-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N30" s="46">
@@ -3305,7 +3316,7 @@
         <v/>
       </c>
       <c r="J31" s="39">
-        <f>(F31-G31)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F31-G31)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K31" s="16">
@@ -3317,7 +3328,7 @@
         <v/>
       </c>
       <c r="M31" s="46">
-        <f>IFERROR(G31*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S30-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G31*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S30*'07_Moteur'!AC30-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N31" s="46">
@@ -3367,7 +3378,7 @@
         <v/>
       </c>
       <c r="J32" s="39">
-        <f>(F32-G32)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F32-G32)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K32" s="16">
@@ -3379,7 +3390,7 @@
         <v/>
       </c>
       <c r="M32" s="46">
-        <f>IFERROR(G32*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S31-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G32*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S31*'07_Moteur'!AC31-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N32" s="46">
@@ -3429,7 +3440,7 @@
         <v/>
       </c>
       <c r="J33" s="39">
-        <f>(F33-G33)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F33-G33)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K33" s="16">
@@ -3441,7 +3452,7 @@
         <v/>
       </c>
       <c r="M33" s="46">
-        <f>IFERROR(G33*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S32-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G33*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S32*'07_Moteur'!AC32-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N33" s="46">
@@ -3491,7 +3502,7 @@
         <v/>
       </c>
       <c r="J34" s="39">
-        <f>(F34-G34)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F34-G34)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K34" s="16">
@@ -3503,7 +3514,7 @@
         <v/>
       </c>
       <c r="M34" s="46">
-        <f>IFERROR(G34*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S33-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G34*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S33*'07_Moteur'!AC33-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N34" s="46">
@@ -3553,7 +3564,7 @@
         <v/>
       </c>
       <c r="J35" s="39">
-        <f>(F35-G35)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F35-G35)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K35" s="16">
@@ -3565,7 +3576,7 @@
         <v/>
       </c>
       <c r="M35" s="46">
-        <f>IFERROR(G35*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S34-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G35*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S34*'07_Moteur'!AC34-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N35" s="46">
@@ -3615,7 +3626,7 @@
         <v/>
       </c>
       <c r="J36" s="39">
-        <f>(F36-G36)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F36-G36)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K36" s="16">
@@ -3627,7 +3638,7 @@
         <v/>
       </c>
       <c r="M36" s="46">
-        <f>IFERROR(G36*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S35-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G36*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S35*'07_Moteur'!AC35-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N36" s="46">
@@ -3677,7 +3688,7 @@
         <v/>
       </c>
       <c r="J37" s="39">
-        <f>(F37-G37)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F37-G37)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K37" s="16">
@@ -3689,7 +3700,7 @@
         <v/>
       </c>
       <c r="M37" s="46">
-        <f>IFERROR(G37*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S36-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G37*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S36*'07_Moteur'!AC36-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N37" s="46">
@@ -3739,7 +3750,7 @@
         <v/>
       </c>
       <c r="J38" s="39">
-        <f>(F38-G38)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F38-G38)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K38" s="16">
@@ -3751,7 +3762,7 @@
         <v/>
       </c>
       <c r="M38" s="46">
-        <f>IFERROR(G38*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S37-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G38*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S37*'07_Moteur'!AC37-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N38" s="46">
@@ -3801,7 +3812,7 @@
         <v/>
       </c>
       <c r="J39" s="39">
-        <f>(F39-G39)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F39-G39)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K39" s="16">
@@ -3813,7 +3824,7 @@
         <v/>
       </c>
       <c r="M39" s="46">
-        <f>IFERROR(G39*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S38-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G39*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S38*'07_Moteur'!AC38-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N39" s="46">
@@ -3863,7 +3874,7 @@
         <v/>
       </c>
       <c r="J40" s="39">
-        <f>(F40-G40)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F40-G40)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K40" s="16">
@@ -3875,7 +3886,7 @@
         <v/>
       </c>
       <c r="M40" s="46">
-        <f>IFERROR(G40*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S39-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G40*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S39*'07_Moteur'!AC39-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N40" s="46">
@@ -3925,7 +3936,7 @@
         <v/>
       </c>
       <c r="J41" s="39">
-        <f>(F41-G41)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F41-G41)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K41" s="16">
@@ -3937,7 +3948,7 @@
         <v/>
       </c>
       <c r="M41" s="46">
-        <f>IFERROR(G41*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S40-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G41*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S40*'07_Moteur'!AC40-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N41" s="46">
@@ -3987,7 +3998,7 @@
         <v/>
       </c>
       <c r="J42" s="39">
-        <f>(F42-G42)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F42-G42)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K42" s="16">
@@ -3999,7 +4010,7 @@
         <v/>
       </c>
       <c r="M42" s="46">
-        <f>IFERROR(G42*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S41-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G42*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S41*'07_Moteur'!AC41-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N42" s="46">
@@ -4049,7 +4060,7 @@
         <v/>
       </c>
       <c r="J43" s="39">
-        <f>(F43-G43)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F43-G43)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K43" s="16">
@@ -4061,7 +4072,7 @@
         <v/>
       </c>
       <c r="M43" s="46">
-        <f>IFERROR(G43*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S42-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G43*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S42*'07_Moteur'!AC42-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N43" s="46">
@@ -4111,7 +4122,7 @@
         <v/>
       </c>
       <c r="J44" s="39">
-        <f>(F44-G44)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F44-G44)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K44" s="16">
@@ -4123,7 +4134,7 @@
         <v/>
       </c>
       <c r="M44" s="46">
-        <f>IFERROR(G44*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S43-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G44*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S43*'07_Moteur'!AC43-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N44" s="46">
@@ -4173,7 +4184,7 @@
         <v/>
       </c>
       <c r="J45" s="39">
-        <f>(F45-G45)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F45-G45)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K45" s="16">
@@ -4185,7 +4196,7 @@
         <v/>
       </c>
       <c r="M45" s="46">
-        <f>IFERROR(G45*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S44-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G45*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S44*'07_Moteur'!AC44-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N45" s="46">
@@ -4235,7 +4246,7 @@
         <v/>
       </c>
       <c r="J46" s="39">
-        <f>(F46-G46)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F46-G46)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K46" s="16">
@@ -4247,7 +4258,7 @@
         <v/>
       </c>
       <c r="M46" s="46">
-        <f>IFERROR(G46*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S45-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G46*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S45*'07_Moteur'!AC45-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N46" s="46">
@@ -4297,7 +4308,7 @@
         <v/>
       </c>
       <c r="J47" s="39">
-        <f>(F47-G47)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F47-G47)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K47" s="16">
@@ -4309,7 +4320,7 @@
         <v/>
       </c>
       <c r="M47" s="46">
-        <f>IFERROR(G47*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S46-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G47*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S46*'07_Moteur'!AC46-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N47" s="46">
@@ -4359,7 +4370,7 @@
         <v/>
       </c>
       <c r="J48" s="39">
-        <f>(F48-G48)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F48-G48)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K48" s="16">
@@ -4371,7 +4382,7 @@
         <v/>
       </c>
       <c r="M48" s="46">
-        <f>IFERROR(G48*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S47-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G48*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S47*'07_Moteur'!AC47-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N48" s="46">
@@ -4421,7 +4432,7 @@
         <v/>
       </c>
       <c r="J49" s="39">
-        <f>(F49-G49)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F49-G49)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K49" s="16">
@@ -4433,7 +4444,7 @@
         <v/>
       </c>
       <c r="M49" s="46">
-        <f>IFERROR(G49*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S48-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G49*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S48*'07_Moteur'!AC48-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N49" s="46">
@@ -4483,7 +4494,7 @@
         <v/>
       </c>
       <c r="J50" s="39">
-        <f>(F50-G50)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F50-G50)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K50" s="16">
@@ -4495,7 +4506,7 @@
         <v/>
       </c>
       <c r="M50" s="46">
-        <f>IFERROR(G50*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S49-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G50*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S49*'07_Moteur'!AC49-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N50" s="46">
@@ -4545,7 +4556,7 @@
         <v/>
       </c>
       <c r="J51" s="39">
-        <f>(F51-G51)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F51-G51)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K51" s="16">
@@ -4557,7 +4568,7 @@
         <v/>
       </c>
       <c r="M51" s="46">
-        <f>IFERROR(G51*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S50-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G51*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S50*'07_Moteur'!AC50-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N51" s="46">
@@ -4607,7 +4618,7 @@
         <v/>
       </c>
       <c r="J52" s="39">
-        <f>(F52-G52)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F52-G52)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K52" s="16">
@@ -4619,7 +4630,7 @@
         <v/>
       </c>
       <c r="M52" s="46">
-        <f>IFERROR(G52*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S51-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G52*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S51*'07_Moteur'!AC51-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N52" s="46">
@@ -4669,7 +4680,7 @@
         <v/>
       </c>
       <c r="J53" s="39">
-        <f>(F53-G53)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F53-G53)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K53" s="16">
@@ -4681,7 +4692,7 @@
         <v/>
       </c>
       <c r="M53" s="46">
-        <f>IFERROR(G53*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S52-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G53*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S52*'07_Moteur'!AC52-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N53" s="46">
@@ -4731,7 +4742,7 @@
         <v/>
       </c>
       <c r="J54" s="39">
-        <f>(F54-G54)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F54-G54)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K54" s="16">
@@ -4743,7 +4754,7 @@
         <v/>
       </c>
       <c r="M54" s="46">
-        <f>IFERROR(G54*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S53-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G54*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S53*'07_Moteur'!AC53-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N54" s="46">
@@ -4793,7 +4804,7 @@
         <v/>
       </c>
       <c r="J55" s="39">
-        <f>(F55-G55)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F55-G55)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K55" s="16">
@@ -4805,7 +4816,7 @@
         <v/>
       </c>
       <c r="M55" s="46">
-        <f>IFERROR(G55*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S54-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G55*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S54*'07_Moteur'!AC54-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N55" s="46">
@@ -4855,7 +4866,7 @@
         <v/>
       </c>
       <c r="J56" s="39">
-        <f>(F56-G56)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F56-G56)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K56" s="16">
@@ -4867,7 +4878,7 @@
         <v/>
       </c>
       <c r="M56" s="46">
-        <f>IFERROR(G56*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S55-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G56*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S55*'07_Moteur'!AC55-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N56" s="46">
@@ -4917,7 +4928,7 @@
         <v/>
       </c>
       <c r="J57" s="39">
-        <f>(F57-G57)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F57-G57)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K57" s="16">
@@ -4929,7 +4940,7 @@
         <v/>
       </c>
       <c r="M57" s="46">
-        <f>IFERROR(G57*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S56-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G57*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S56*'07_Moteur'!AC56-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N57" s="46">
@@ -4979,7 +4990,7 @@
         <v/>
       </c>
       <c r="J58" s="39">
-        <f>(F58-G58)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F58-G58)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K58" s="16">
@@ -4991,7 +5002,7 @@
         <v/>
       </c>
       <c r="M58" s="46">
-        <f>IFERROR(G58*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S57-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G58*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S57*'07_Moteur'!AC57-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N58" s="46">
@@ -5041,7 +5052,7 @@
         <v/>
       </c>
       <c r="J59" s="39">
-        <f>(F59-G59)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F59-G59)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K59" s="16">
@@ -5053,7 +5064,7 @@
         <v/>
       </c>
       <c r="M59" s="46">
-        <f>IFERROR(G59*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S58-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G59*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S58*'07_Moteur'!AC58-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N59" s="46">
@@ -5103,7 +5114,7 @@
         <v/>
       </c>
       <c r="J60" s="39">
-        <f>(F60-G60)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F60-G60)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K60" s="16">
@@ -5115,7 +5126,7 @@
         <v/>
       </c>
       <c r="M60" s="46">
-        <f>IFERROR(G60*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S59-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G60*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S59*'07_Moteur'!AC59-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N60" s="46">
@@ -5165,7 +5176,7 @@
         <v/>
       </c>
       <c r="J61" s="39">
-        <f>(F61-G61)*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>(F61-G61)*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="K61" s="16">
@@ -5177,7 +5188,7 @@
         <v/>
       </c>
       <c r="M61" s="46">
-        <f>IFERROR(G61*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)/('07_Moteur'!S60-'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)),0)</f>
+        <f>IFERROR(G61*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)/('07_Moteur'!S60*'07_Moteur'!AC60-'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)),0)</f>
         <v/>
       </c>
       <c r="N61" s="46">
@@ -5276,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5413,7 +5424,7 @@
         <v/>
       </c>
       <c r="D11" s="48">
-        <f>'06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$22*'06_Structure'!D18</f>
+        <f>'06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$24*'06_Structure'!D18</f>
         <v/>
       </c>
       <c r="E11" s="32">
@@ -5432,7 +5443,7 @@
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>IFERROR(('06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$22*'06_Structure'!D18)/'06_Structure'!D18,0)</f>
+        <f>IFERROR(('06_Structure'!E18-'06_Structure'!F18-'06_Structure'!H18-'02_Parametres'!$D$24*'06_Structure'!D18)/'06_Structure'!D18,0)</f>
         <v/>
       </c>
       <c r="E12" s="32">
@@ -5478,208 +5489,269 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>Taux d'alternance</t>
+        </is>
+      </c>
+      <c r="C15" s="32">
+        <f>IFERROR(SUMIF('07_Moteur'!$E$3:$E$60,"ALT",'07_Moteur'!$R$3:$R$60)/SUM('07_Moteur'!$R$3:$R$60),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="32">
+        <f>IFERROR(SUMIF('07_Moteur'!$E$3:$E$60,"ALT",'07_Moteur'!$F$3:$F$60)/SUM('07_Moteur'!$F$3:$F$60),0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>D15-C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t>Taux de signature contrat</t>
+        </is>
+      </c>
+      <c r="C16" s="32">
+        <f>'02_Parametres'!$G$9</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>'02_Parametres'!$D$26</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>D16-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Comparatif des scénarios (leviers)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Levier</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Cadrage</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Optimiste</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Prudent</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>Actif</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Croissance recrutement</t>
-        </is>
-      </c>
-      <c r="C18" s="16">
-        <f>'02_Parametres'!D6</f>
-        <v/>
-      </c>
-      <c r="D18" s="16">
-        <f>'02_Parametres'!E6</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>'02_Parametres'!F6</f>
-        <v/>
-      </c>
-      <c r="F18" s="68">
-        <f>'02_Parametres'!G6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Hausse tarifaire</t>
-        </is>
-      </c>
-      <c r="C19" s="16">
-        <f>'02_Parametres'!D7</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>'02_Parametres'!E7</f>
-        <v/>
-      </c>
-      <c r="E19" s="16">
-        <f>'02_Parametres'!F7</f>
-        <v/>
-      </c>
-      <c r="F19" s="68">
-        <f>'02_Parametres'!G7</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Gain conversion</t>
+          <t>Croissance recrutement</t>
         </is>
       </c>
       <c r="C20" s="16">
-        <f>'02_Parametres'!D8</f>
+        <f>'02_Parametres'!D6</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>'02_Parametres'!E8</f>
+        <f>'02_Parametres'!E6</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>'02_Parametres'!F8</f>
+        <f>'02_Parametres'!F6</f>
         <v/>
       </c>
       <c r="F20" s="68">
-        <f>'02_Parametres'!G8</f>
+        <f>'02_Parametres'!G6</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Taux réinscription</t>
+          <t>Hausse tarifaire</t>
         </is>
       </c>
       <c r="C21" s="16">
-        <f>'02_Parametres'!D9</f>
+        <f>'02_Parametres'!D7</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>'02_Parametres'!E9</f>
+        <f>'02_Parametres'!E7</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>'02_Parametres'!F9</f>
+        <f>'02_Parametres'!F7</f>
         <v/>
       </c>
       <c r="F21" s="68">
-        <f>'02_Parametres'!G9</f>
+        <f>'02_Parametres'!G7</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Inflation charges</t>
+          <t>Gain conversion</t>
         </is>
       </c>
       <c r="C22" s="16">
-        <f>'02_Parametres'!D10</f>
+        <f>'02_Parametres'!D8</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>'02_Parametres'!E10</f>
+        <f>'02_Parametres'!E8</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>'02_Parametres'!F10</f>
+        <f>'02_Parametres'!F8</f>
         <v/>
       </c>
       <c r="F22" s="68">
-        <f>'02_Parametres'!G10</f>
+        <f>'02_Parametres'!G8</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Politique salariale</t>
+          <t>Taux signature contrat</t>
         </is>
       </c>
       <c r="C23" s="16">
-        <f>'02_Parametres'!D11</f>
+        <f>'02_Parametres'!D9</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>'02_Parametres'!E11</f>
+        <f>'02_Parametres'!E9</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>'02_Parametres'!F11</f>
+        <f>'02_Parametres'!F9</f>
         <v/>
       </c>
       <c r="F23" s="68">
-        <f>'02_Parametres'!G11</f>
+        <f>'02_Parametres'!G9</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
+          <t>Taux réinscription</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>'02_Parametres'!D10</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>'02_Parametres'!E10</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>'02_Parametres'!F10</f>
+        <v/>
+      </c>
+      <c r="F24" s="68">
+        <f>'02_Parametres'!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Inflation charges</t>
+        </is>
+      </c>
+      <c r="C25" s="16">
+        <f>'02_Parametres'!D11</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>'02_Parametres'!E11</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>'02_Parametres'!F11</f>
+        <v/>
+      </c>
+      <c r="F25" s="68">
+        <f>'02_Parametres'!G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Politique salariale</t>
+        </is>
+      </c>
+      <c r="C26" s="16">
+        <f>'02_Parametres'!D12</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f>'02_Parametres'!E12</f>
+        <v/>
+      </c>
+      <c r="E26" s="16">
+        <f>'02_Parametres'!F12</f>
+        <v/>
+      </c>
+      <c r="F26" s="68">
+        <f>'02_Parametres'!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="C24" s="18">
-        <f>'02_Parametres'!D12</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>'02_Parametres'!E12</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>'02_Parametres'!F12</f>
-        <v/>
-      </c>
-      <c r="F24" s="69">
-        <f>'02_Parametres'!G12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="13" t="inlineStr">
+      <c r="C27" s="18">
+        <f>'02_Parametres'!D13</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
+        <f>'02_Parametres'!E13</f>
+        <v/>
+      </c>
+      <c r="E27" s="18">
+        <f>'02_Parametres'!F13</f>
+        <v/>
+      </c>
+      <c r="F27" s="69">
+        <f>'02_Parametres'!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Astuce démo : un gain de conversion admissions (levier « Gain conversion ») augmente les inscrits SANS hausse tarifaire ni dépense volume — souvent le levier le plus rentable.</t>
         </is>
@@ -5689,9 +5761,9 @@
   <mergeCells count="5">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B16:G16"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5988,7 +6060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D25"/>
+  <dimension ref="B2:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6118,7 +6190,7 @@
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Taux de réinscription</t>
+          <t>Taux de signature contrat (alternance)</t>
         </is>
       </c>
       <c r="C15" s="16">
@@ -6127,14 +6199,14 @@
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Progression des étudiants d'une année sur l'autre.</t>
+          <t>Part des alternants avec contrat signé → financés OPCO/NPEC. Levier de REVENU.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Inflation des charges</t>
+          <t>Taux de réinscription</t>
         </is>
       </c>
       <c r="C16" s="16">
@@ -6143,14 +6215,14 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>Loyers, pédagogie, autres charges.</t>
+          <t>Progression des étudiants d'une année sur l'autre.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Politique salariale</t>
+          <t>Inflation des charges</t>
         </is>
       </c>
       <c r="C17" s="16">
@@ -6159,65 +6231,81 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Revalorisation des rémunérations chargées.</t>
+          <t>Loyers, pédagogie, autres charges.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="9" t="inlineStr">
         <is>
+          <t>Politique salariale</t>
+        </is>
+      </c>
+      <c r="C18" s="16">
+        <f>'02_Parametres'!D12</f>
+        <v/>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Revalorisation des rémunérations chargées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
           <t>Coût d'acquisition (CAC)</t>
         </is>
       </c>
-      <c r="C18" s="18">
-        <f>'02_Parametres'!D12</f>
-        <v/>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C19" s="18">
+        <f>'02_Parametres'!D13</f>
+        <v/>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Dépense marketing par nouvel inscrit.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Règles de gestion</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Nouveaux inscrits = candidatures × (1+croissance×coef marque) × (conversion N-1 + gain conversion).</t>
-        </is>
-      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Réinscrits = réinscrits N-1 × (taux réinscription / référence).  Effectif = réinscrits + nouveaux.</t>
+          <t>Nouveaux inscrits = candidatures × (1+croissance×coef marque) × (conversion N-1 + gain conversion).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Tarif budget = tarif N-1 × (1 + hausse prix × coef marque).</t>
+          <t>Réinscrits = réinscrits N-1 × (taux réinscription / référence).  Effectif = réinscrits + nouveaux.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Nombre de classes = arrondi supérieur (effectif / capacité cible).  Coût enseignement = classes × heures × taux.</t>
+          <t>Tarif budget = tarif N-1 × (1 + hausse prix × coef marque).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Nombre de classes = arrondi supérieur (effectif / capacité cible).  Coût enseignement = classes × heures × taux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Contribution = CA − enseignement − pédagogie variable − marketing.  EBITDA = Σ contributions − loyers − permanents − structure.</t>
         </is>
@@ -6231,13 +6319,13 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6249,7 +6337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G24"/>
+  <dimension ref="B2:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6395,7 +6483,7 @@
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Taux de réinscription</t>
+          <t>Taux de signature contrat (alternance)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6404,13 +6492,13 @@
         </is>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="24">
         <f>INDEX(D9:F9,MATCH($C$3,$D$5:$F$5,0))</f>
@@ -6420,7 +6508,7 @@
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Inflation des charges</t>
+          <t>Taux de réinscription</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6429,13 +6517,13 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>0.015</v>
+        <v>0.87</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="G10" s="24">
         <f>INDEX(D10:F10,MATCH($C$3,$D$5:$F$5,0))</f>
@@ -6445,7 +6533,7 @@
     <row r="11">
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Politique salariale</t>
+          <t>Inflation des charges</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6454,10 +6542,10 @@
         </is>
       </c>
       <c r="D11" s="23" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="F11" s="23" t="n">
         <v>0.03</v>
@@ -6470,131 +6558,98 @@
     <row r="12">
       <c r="B12" s="9" t="inlineStr">
         <is>
+          <t>Politique salariale</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G12" s="24">
+        <f>INDEX(D12:F12,MATCH($C$3,$D$5:$F$5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
           <t>Coût d'acquisition (CAC)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D13" s="25" t="n">
         <v>1300</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E13" s="25" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F13" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="G12" s="26">
-        <f>INDEX(D12:F12,MATCH($C$3,$D$5:$F$5,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="G13" s="26">
+        <f>INDEX(D13:F13,MATCH($C$3,$D$5:$F$5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Constantes (calibrées, sourcées)</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="G13" s="27" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Capacité cible / classe</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>nb</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F14" s="29" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G14" s="30">
-        <f>D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Seuil d'ouverture / classe</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>nb</t>
-        </is>
-      </c>
-      <c r="D15" s="28" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G15" s="30">
-        <f>D15</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Heures d'enseignement / classe / an</t>
+          <t>Capacité cible / classe</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>nb</t>
         </is>
       </c>
       <c r="D16" s="28" t="n">
-        <v>550</v>
+        <v>30</v>
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
@@ -6614,16 +6669,16 @@
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Taux horaire chargé enseignement</t>
+          <t>Seuil d'ouverture / classe</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>€</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="n">
-        <v>60</v>
+          <t>nb</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>15</v>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
@@ -6635,7 +6690,7 @@
           <t> </t>
         </is>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="30">
         <f>D17</f>
         <v/>
       </c>
@@ -6643,16 +6698,16 @@
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Coût pédagogique variable / étudiant</t>
+          <t>Heures d'enseignement / classe / an</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>€</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="n">
-        <v>400</v>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>550</v>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
@@ -6664,7 +6719,7 @@
           <t> </t>
         </is>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="30">
         <f>D18</f>
         <v/>
       </c>
@@ -6672,7 +6727,7 @@
     <row r="19">
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Coût chargé / ETP permanent</t>
+          <t>Taux horaire chargé enseignement</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -6681,7 +6736,7 @@
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>48000</v>
+        <v>60</v>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
@@ -6701,7 +6756,7 @@
     <row r="20">
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Frais de dossier / nouvel inscrit</t>
+          <t>Coût pédagogique variable / étudiant</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -6710,7 +6765,7 @@
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
@@ -6730,16 +6785,16 @@
     <row r="21">
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Réf. taux de réinscription</t>
+          <t>Coût chargé / ETP permanent</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="n">
-        <v>0.84</v>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="n">
+        <v>48000</v>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
@@ -6751,7 +6806,7 @@
           <t> </t>
         </is>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="26">
         <f>D21</f>
         <v/>
       </c>
@@ -6759,44 +6814,160 @@
     <row r="22">
       <c r="B22" s="9" t="inlineStr">
         <is>
+          <t>Frais de dossier / nouvel inscrit</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G22" s="26">
+        <f>D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Réf. taux de réinscription</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G23" s="24">
+        <f>D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
           <t>Frais de structure groupe (% CA)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.08</v>
       </c>
-      <c r="E22" s="29" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="G22" s="24">
-        <f>D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="19" t="inlineStr">
+      <c r="G24" s="24">
+        <f>D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Revenu net d'un alternant NON signé (% NPEC)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G25" s="24">
+        <f>D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Réf. taux de signature contrat N-1</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G26" s="24">
+        <f>D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Driver d'allocation des frais de structure :</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Effectifs</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>◄ change la clé de répartition (feuille 08)</t>
         </is>
@@ -6805,15 +6976,15 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E28:G28"/>
     <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Cadrage,Optimiste,Prudent"</formula1>
     </dataValidation>
-    <dataValidation sqref="D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Effectifs,Chiffre d'affaires,Surface m2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8036,7 +8207,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G5" s="28" t="n">
@@ -8055,7 +8226,7 @@
         <v>66</v>
       </c>
       <c r="L5" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M5" s="28" t="n">
         <v>3</v>
@@ -8321,7 +8492,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G10" s="28" t="n">
@@ -8340,7 +8511,7 @@
         <v>56</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M10" s="28" t="n">
         <v>2</v>
@@ -8606,7 +8777,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G15" s="28" t="n">
@@ -8625,7 +8796,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M15" s="28" t="n">
         <v>2</v>
@@ -8891,7 +9062,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G20" s="28" t="n">
@@ -8910,7 +9081,7 @@
         <v>43</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M20" s="28" t="n">
         <v>2</v>
@@ -9176,7 +9347,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G25" s="28" t="n">
@@ -9195,7 +9366,7 @@
         <v>61</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M25" s="28" t="n">
         <v>3</v>
@@ -9461,7 +9632,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G30" s="28" t="n">
@@ -9480,7 +9651,7 @@
         <v>42</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M30" s="28" t="n">
         <v>2</v>
@@ -9746,7 +9917,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G35" s="28" t="n">
@@ -9765,7 +9936,7 @@
         <v>40</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M35" s="28" t="n">
         <v>2</v>
@@ -9974,7 +10145,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G39" s="28" t="n">
@@ -9993,7 +10164,7 @@
         <v>50</v>
       </c>
       <c r="L39" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M39" s="28" t="n">
         <v>2</v>
@@ -10031,7 +10202,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G40" s="28" t="n">
@@ -10050,7 +10221,7 @@
         <v>42</v>
       </c>
       <c r="L40" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M40" s="28" t="n">
         <v>2</v>
@@ -10145,7 +10316,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G42" s="28" t="n">
@@ -10164,7 +10335,7 @@
         <v>40</v>
       </c>
       <c r="L42" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M42" s="28" t="n">
         <v>2</v>
@@ -10202,7 +10373,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G43" s="28" t="n">
@@ -10221,7 +10392,7 @@
         <v>34</v>
       </c>
       <c r="L43" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M43" s="28" t="n">
         <v>2</v>
@@ -10316,7 +10487,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G45" s="28" t="n">
@@ -10335,7 +10506,7 @@
         <v>40</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M45" s="28" t="n">
         <v>2</v>
@@ -10373,7 +10544,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G46" s="28" t="n">
@@ -10392,7 +10563,7 @@
         <v>34</v>
       </c>
       <c r="L46" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M46" s="28" t="n">
         <v>2</v>
@@ -10601,7 +10772,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G50" s="28" t="n">
@@ -10620,7 +10791,7 @@
         <v>46</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M50" s="28" t="n">
         <v>2</v>
@@ -10829,7 +11000,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G54" s="28" t="n">
@@ -10848,7 +11019,7 @@
         <v>36</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M54" s="28" t="n">
         <v>2</v>
@@ -10943,7 +11114,7 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G56" s="28" t="n">
@@ -10962,7 +11133,7 @@
         <v>47</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M56" s="28" t="n">
         <v>2</v>
@@ -11000,7 +11171,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G57" s="28" t="n">
@@ -11019,7 +11190,7 @@
         <v>40</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M57" s="28" t="n">
         <v>2</v>
@@ -11114,7 +11285,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G59" s="28" t="n">
@@ -11133,7 +11304,7 @@
         <v>40</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M59" s="28" t="n">
         <v>2</v>
@@ -11171,7 +11342,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>INIT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="G60" s="28" t="n">
@@ -11190,7 +11361,7 @@
         <v>34</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="M60" s="28" t="n">
         <v>2</v>
@@ -11374,23 +11545,23 @@
         <v>291</v>
       </c>
       <c r="D4" s="38" t="n">
-        <v>2501510</v>
+        <v>2339414</v>
       </c>
       <c r="E4" s="38" t="n">
-        <v>1857060</v>
+        <v>1694964</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>275000</v>
+        <v>257000</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="39">
-        <f>G4*'02_Parametres'!$D$19</f>
+        <f>G4*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I4" s="38" t="n">
-        <v>75000</v>
+        <v>70000</v>
       </c>
       <c r="J4" s="28" t="n">
         <v>2328</v>
@@ -11415,23 +11586,23 @@
         <v>248</v>
       </c>
       <c r="D5" s="38" t="n">
-        <v>2131620</v>
+        <v>1993316</v>
       </c>
       <c r="E5" s="38" t="n">
-        <v>1557320</v>
+        <v>1419016</v>
       </c>
       <c r="F5" s="38" t="n">
-        <v>234000</v>
+        <v>219000</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" s="39">
-        <f>G5*'02_Parametres'!$D$19</f>
+        <f>G5*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I5" s="38" t="n">
-        <v>64000</v>
+        <v>60000</v>
       </c>
       <c r="J5" s="28" t="n">
         <v>1984</v>
@@ -11456,23 +11627,23 @@
         <v>224</v>
       </c>
       <c r="D6" s="38" t="n">
-        <v>1925130</v>
+        <v>1800270</v>
       </c>
       <c r="E6" s="38" t="n">
-        <v>1403880</v>
+        <v>1279020</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>212000</v>
+        <v>198000</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" s="39">
-        <f>G6*'02_Parametres'!$D$19</f>
+        <f>G6*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I6" s="38" t="n">
-        <v>58000</v>
+        <v>54000</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>1792</v>
@@ -11497,23 +11668,23 @@
         <v>191</v>
       </c>
       <c r="D7" s="38" t="n">
-        <v>1642100</v>
+        <v>1535712</v>
       </c>
       <c r="E7" s="38" t="n">
-        <v>1183200</v>
+        <v>1076812</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>181000</v>
+        <v>169000</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" s="39">
-        <f>G7*'02_Parametres'!$D$19</f>
+        <f>G7*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I7" s="38" t="n">
-        <v>49000</v>
+        <v>46000</v>
       </c>
       <c r="J7" s="28" t="n">
         <v>1528</v>
@@ -11538,23 +11709,23 @@
         <v>269</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>2311930</v>
+        <v>2162054</v>
       </c>
       <c r="E8" s="38" t="n">
-        <v>1687680</v>
+        <v>1537804</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>254000</v>
+        <v>238000</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" s="39">
-        <f>G8*'02_Parametres'!$D$19</f>
+        <f>G8*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I8" s="38" t="n">
-        <v>69000</v>
+        <v>65000</v>
       </c>
       <c r="J8" s="28" t="n">
         <v>2152</v>
@@ -11579,23 +11750,23 @@
         <v>187</v>
       </c>
       <c r="D9" s="38" t="n">
-        <v>1606920</v>
+        <v>1502904</v>
       </c>
       <c r="E9" s="38" t="n">
-        <v>1184520</v>
+        <v>1080504</v>
       </c>
       <c r="F9" s="38" t="n">
-        <v>177000</v>
+        <v>165000</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="39">
-        <f>G9*'02_Parametres'!$D$19</f>
+        <f>G9*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I9" s="38" t="n">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="J9" s="28" t="n">
         <v>1496</v>
@@ -11620,23 +11791,23 @@
         <v>175</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>1503970</v>
+        <v>1406426</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>1091120</v>
+        <v>993576</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>165000</v>
+        <v>155000</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H10" s="39">
-        <f>G10*'02_Parametres'!$D$19</f>
+        <f>G10*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I10" s="38" t="n">
-        <v>45000</v>
+        <v>42000</v>
       </c>
       <c r="J10" s="28" t="n">
         <v>1400</v>
@@ -11661,23 +11832,23 @@
         <v>130</v>
       </c>
       <c r="D11" s="38" t="n">
-        <v>1091130</v>
+        <v>970250</v>
       </c>
       <c r="E11" s="38" t="n">
-        <v>786980</v>
+        <v>666100</v>
       </c>
       <c r="F11" s="38" t="n">
-        <v>120000</v>
+        <v>107000</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" s="39">
-        <f>G11*'02_Parametres'!$D$19</f>
+        <f>G11*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I11" s="38" t="n">
-        <v>33000</v>
+        <v>29000</v>
       </c>
       <c r="J11" s="28" t="n">
         <v>1040</v>
@@ -11702,23 +11873,23 @@
         <v>104</v>
       </c>
       <c r="D12" s="38" t="n">
-        <v>873050</v>
+        <v>776146</v>
       </c>
       <c r="E12" s="38" t="n">
-        <v>623700</v>
+        <v>526796</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>96000</v>
+        <v>85000</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="39">
-        <f>G12*'02_Parametres'!$D$19</f>
+        <f>G12*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I12" s="38" t="n">
-        <v>26000</v>
+        <v>23000</v>
       </c>
       <c r="J12" s="28" t="n">
         <v>832</v>
@@ -11743,23 +11914,23 @@
         <v>104</v>
       </c>
       <c r="D13" s="38" t="n">
-        <v>873050</v>
+        <v>776146</v>
       </c>
       <c r="E13" s="38" t="n">
-        <v>623700</v>
+        <v>526796</v>
       </c>
       <c r="F13" s="38" t="n">
-        <v>96000</v>
+        <v>85000</v>
       </c>
       <c r="G13" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="39">
-        <f>G13*'02_Parametres'!$D$19</f>
+        <f>G13*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I13" s="38" t="n">
-        <v>26000</v>
+        <v>23000</v>
       </c>
       <c r="J13" s="28" t="n">
         <v>832</v>
@@ -11784,23 +11955,23 @@
         <v>149</v>
       </c>
       <c r="D14" s="38" t="n">
-        <v>1153920</v>
+        <v>1050064</v>
       </c>
       <c r="E14" s="38" t="n">
-        <v>746720</v>
+        <v>642864</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>127000</v>
+        <v>116000</v>
       </c>
       <c r="G14" s="28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" s="39">
-        <f>G14*'02_Parametres'!$D$19</f>
+        <f>G14*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I14" s="38" t="n">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="J14" s="28" t="n">
         <v>1192</v>
@@ -11825,23 +11996,23 @@
         <v>117</v>
       </c>
       <c r="D15" s="38" t="n">
-        <v>906120</v>
+        <v>824616</v>
       </c>
       <c r="E15" s="38" t="n">
-        <v>629720</v>
+        <v>548216</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>100000</v>
+        <v>91000</v>
       </c>
       <c r="G15" s="28" t="n">
         <v>7</v>
       </c>
       <c r="H15" s="39">
-        <f>G15*'02_Parametres'!$D$19</f>
+        <f>G15*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I15" s="38" t="n">
-        <v>27000</v>
+        <v>25000</v>
       </c>
       <c r="J15" s="28" t="n">
         <v>936</v>
@@ -11866,23 +12037,23 @@
         <v>122</v>
       </c>
       <c r="D16" s="38" t="n">
-        <v>1024360</v>
+        <v>910588</v>
       </c>
       <c r="E16" s="38" t="n">
-        <v>726260</v>
+        <v>612488</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>113000</v>
+        <v>100000</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="39">
-        <f>G16*'02_Parametres'!$D$19</f>
+        <f>G16*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I16" s="38" t="n">
-        <v>31000</v>
+        <v>27000</v>
       </c>
       <c r="J16" s="28" t="n">
         <v>976</v>
@@ -11907,23 +12078,23 @@
         <v>104</v>
       </c>
       <c r="D17" s="38" t="n">
-        <v>873050</v>
+        <v>776146</v>
       </c>
       <c r="E17" s="38" t="n">
-        <v>623700</v>
+        <v>526796</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>96000</v>
+        <v>85000</v>
       </c>
       <c r="G17" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="39">
-        <f>G17*'02_Parametres'!$D$19</f>
+        <f>G17*'02_Parametres'!$D$21</f>
         <v/>
       </c>
       <c r="I17" s="38" t="n">
-        <v>26000</v>
+        <v>23000</v>
       </c>
       <c r="J17" s="28" t="n">
         <v>832</v>
@@ -11996,7 +12167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA61"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12026,6 +12197,8 @@
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -12171,6 +12344,16 @@
           <t>Contr/étu</t>
         </is>
       </c>
+      <c r="AB2" s="15" t="inlineStr">
+        <is>
+          <t>Sig N-1</t>
+        </is>
+      </c>
+      <c r="AC2" s="15" t="inlineStr">
+        <is>
+          <t>Sig Bud</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="43">
@@ -12238,7 +12421,7 @@
         <v/>
       </c>
       <c r="Q3" s="46">
-        <f>H3*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H3*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R3" s="47">
@@ -12250,23 +12433,23 @@
         <v/>
       </c>
       <c r="T3" s="39">
-        <f>R3*S3+P3*'02_Parametres'!$D$20</f>
+        <f>R3*S3*AC3+P3*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U3" s="46">
-        <f>IF(R3&lt;=0,0,MAX(1,ROUNDUP(R3/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R3&lt;=0,0,MAX(1,ROUNDUP(R3/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V3" s="39">
-        <f>U3*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U3*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W3" s="39">
-        <f>R3*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R3*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X3" s="39">
-        <f>P3*'02_Parametres'!$G$12</f>
+        <f>P3*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y3" s="49">
@@ -12274,11 +12457,19 @@
         <v/>
       </c>
       <c r="Z3" s="32">
-        <f>IFERROR(R3/(U3*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R3/(U3*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA3" s="48">
         <f>IFERROR(Y3/R3,0)</f>
+        <v/>
+      </c>
+      <c r="AB3" s="45">
+        <f>IF(E3="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC3" s="45">
+        <f>IF(E3="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -12348,7 +12539,7 @@
         <v/>
       </c>
       <c r="Q4" s="46">
-        <f>H4*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H4*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R4" s="47">
@@ -12360,23 +12551,23 @@
         <v/>
       </c>
       <c r="T4" s="39">
-        <f>R4*S4+P4*'02_Parametres'!$D$20</f>
+        <f>R4*S4*AC4+P4*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U4" s="46">
-        <f>IF(R4&lt;=0,0,MAX(1,ROUNDUP(R4/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R4&lt;=0,0,MAX(1,ROUNDUP(R4/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V4" s="39">
-        <f>U4*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U4*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W4" s="39">
-        <f>R4*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R4*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X4" s="39">
-        <f>P4*'02_Parametres'!$G$12</f>
+        <f>P4*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y4" s="49">
@@ -12384,11 +12575,19 @@
         <v/>
       </c>
       <c r="Z4" s="32">
-        <f>IFERROR(R4/(U4*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R4/(U4*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA4" s="48">
         <f>IFERROR(Y4/R4,0)</f>
+        <v/>
+      </c>
+      <c r="AB4" s="45">
+        <f>IF(E4="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC4" s="45">
+        <f>IF(E4="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -12458,7 +12657,7 @@
         <v/>
       </c>
       <c r="Q5" s="46">
-        <f>H5*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H5*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R5" s="47">
@@ -12470,23 +12669,23 @@
         <v/>
       </c>
       <c r="T5" s="39">
-        <f>R5*S5+P5*'02_Parametres'!$D$20</f>
+        <f>R5*S5*AC5+P5*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U5" s="46">
-        <f>IF(R5&lt;=0,0,MAX(1,ROUNDUP(R5/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R5&lt;=0,0,MAX(1,ROUNDUP(R5/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V5" s="39">
-        <f>U5*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U5*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W5" s="39">
-        <f>R5*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R5*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X5" s="39">
-        <f>P5*'02_Parametres'!$G$12</f>
+        <f>P5*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y5" s="49">
@@ -12494,11 +12693,19 @@
         <v/>
       </c>
       <c r="Z5" s="32">
-        <f>IFERROR(R5/(U5*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R5/(U5*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA5" s="48">
         <f>IFERROR(Y5/R5,0)</f>
+        <v/>
+      </c>
+      <c r="AB5" s="45">
+        <f>IF(E5="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC5" s="45">
+        <f>IF(E5="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -12568,7 +12775,7 @@
         <v/>
       </c>
       <c r="Q6" s="46">
-        <f>H6*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H6*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R6" s="47">
@@ -12580,23 +12787,23 @@
         <v/>
       </c>
       <c r="T6" s="39">
-        <f>R6*S6+P6*'02_Parametres'!$D$20</f>
+        <f>R6*S6*AC6+P6*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U6" s="46">
-        <f>IF(R6&lt;=0,0,MAX(1,ROUNDUP(R6/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R6&lt;=0,0,MAX(1,ROUNDUP(R6/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V6" s="39">
-        <f>U6*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U6*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W6" s="39">
-        <f>R6*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R6*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X6" s="39">
-        <f>P6*'02_Parametres'!$G$12</f>
+        <f>P6*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y6" s="49">
@@ -12604,11 +12811,19 @@
         <v/>
       </c>
       <c r="Z6" s="32">
-        <f>IFERROR(R6/(U6*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R6/(U6*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA6" s="48">
         <f>IFERROR(Y6/R6,0)</f>
+        <v/>
+      </c>
+      <c r="AB6" s="45">
+        <f>IF(E6="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC6" s="45">
+        <f>IF(E6="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -12678,7 +12893,7 @@
         <v/>
       </c>
       <c r="Q7" s="46">
-        <f>H7*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H7*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R7" s="47">
@@ -12690,23 +12905,23 @@
         <v/>
       </c>
       <c r="T7" s="39">
-        <f>R7*S7+P7*'02_Parametres'!$D$20</f>
+        <f>R7*S7*AC7+P7*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U7" s="46">
-        <f>IF(R7&lt;=0,0,MAX(1,ROUNDUP(R7/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R7&lt;=0,0,MAX(1,ROUNDUP(R7/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V7" s="39">
-        <f>U7*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U7*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W7" s="39">
-        <f>R7*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R7*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X7" s="39">
-        <f>P7*'02_Parametres'!$G$12</f>
+        <f>P7*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y7" s="49">
@@ -12714,11 +12929,19 @@
         <v/>
       </c>
       <c r="Z7" s="32">
-        <f>IFERROR(R7/(U7*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R7/(U7*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA7" s="48">
         <f>IFERROR(Y7/R7,0)</f>
+        <v/>
+      </c>
+      <c r="AB7" s="45">
+        <f>IF(E7="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC7" s="45">
+        <f>IF(E7="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -12788,7 +13011,7 @@
         <v/>
       </c>
       <c r="Q8" s="46">
-        <f>H8*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H8*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R8" s="47">
@@ -12800,23 +13023,23 @@
         <v/>
       </c>
       <c r="T8" s="39">
-        <f>R8*S8+P8*'02_Parametres'!$D$20</f>
+        <f>R8*S8*AC8+P8*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U8" s="46">
-        <f>IF(R8&lt;=0,0,MAX(1,ROUNDUP(R8/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R8&lt;=0,0,MAX(1,ROUNDUP(R8/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V8" s="39">
-        <f>U8*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U8*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W8" s="39">
-        <f>R8*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R8*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X8" s="39">
-        <f>P8*'02_Parametres'!$G$12</f>
+        <f>P8*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y8" s="49">
@@ -12824,11 +13047,19 @@
         <v/>
       </c>
       <c r="Z8" s="32">
-        <f>IFERROR(R8/(U8*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R8/(U8*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA8" s="48">
         <f>IFERROR(Y8/R8,0)</f>
+        <v/>
+      </c>
+      <c r="AB8" s="45">
+        <f>IF(E8="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC8" s="45">
+        <f>IF(E8="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -12898,7 +13129,7 @@
         <v/>
       </c>
       <c r="Q9" s="46">
-        <f>H9*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H9*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R9" s="47">
@@ -12910,23 +13141,23 @@
         <v/>
       </c>
       <c r="T9" s="39">
-        <f>R9*S9+P9*'02_Parametres'!$D$20</f>
+        <f>R9*S9*AC9+P9*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U9" s="46">
-        <f>IF(R9&lt;=0,0,MAX(1,ROUNDUP(R9/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R9&lt;=0,0,MAX(1,ROUNDUP(R9/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V9" s="39">
-        <f>U9*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U9*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W9" s="39">
-        <f>R9*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R9*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X9" s="39">
-        <f>P9*'02_Parametres'!$G$12</f>
+        <f>P9*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y9" s="49">
@@ -12934,11 +13165,19 @@
         <v/>
       </c>
       <c r="Z9" s="32">
-        <f>IFERROR(R9/(U9*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R9/(U9*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA9" s="48">
         <f>IFERROR(Y9/R9,0)</f>
+        <v/>
+      </c>
+      <c r="AB9" s="45">
+        <f>IF(E9="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC9" s="45">
+        <f>IF(E9="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13008,7 +13247,7 @@
         <v/>
       </c>
       <c r="Q10" s="46">
-        <f>H10*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H10*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R10" s="47">
@@ -13020,23 +13259,23 @@
         <v/>
       </c>
       <c r="T10" s="39">
-        <f>R10*S10+P10*'02_Parametres'!$D$20</f>
+        <f>R10*S10*AC10+P10*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U10" s="46">
-        <f>IF(R10&lt;=0,0,MAX(1,ROUNDUP(R10/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R10&lt;=0,0,MAX(1,ROUNDUP(R10/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V10" s="39">
-        <f>U10*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U10*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W10" s="39">
-        <f>R10*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R10*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X10" s="39">
-        <f>P10*'02_Parametres'!$G$12</f>
+        <f>P10*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y10" s="49">
@@ -13044,11 +13283,19 @@
         <v/>
       </c>
       <c r="Z10" s="32">
-        <f>IFERROR(R10/(U10*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R10/(U10*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA10" s="48">
         <f>IFERROR(Y10/R10,0)</f>
+        <v/>
+      </c>
+      <c r="AB10" s="45">
+        <f>IF(E10="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC10" s="45">
+        <f>IF(E10="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13118,7 +13365,7 @@
         <v/>
       </c>
       <c r="Q11" s="46">
-        <f>H11*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H11*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R11" s="47">
@@ -13130,23 +13377,23 @@
         <v/>
       </c>
       <c r="T11" s="39">
-        <f>R11*S11+P11*'02_Parametres'!$D$20</f>
+        <f>R11*S11*AC11+P11*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U11" s="46">
-        <f>IF(R11&lt;=0,0,MAX(1,ROUNDUP(R11/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R11&lt;=0,0,MAX(1,ROUNDUP(R11/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V11" s="39">
-        <f>U11*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U11*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W11" s="39">
-        <f>R11*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R11*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X11" s="39">
-        <f>P11*'02_Parametres'!$G$12</f>
+        <f>P11*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y11" s="49">
@@ -13154,11 +13401,19 @@
         <v/>
       </c>
       <c r="Z11" s="32">
-        <f>IFERROR(R11/(U11*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R11/(U11*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA11" s="48">
         <f>IFERROR(Y11/R11,0)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="45">
+        <f>IF(E11="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC11" s="45">
+        <f>IF(E11="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13228,7 +13483,7 @@
         <v/>
       </c>
       <c r="Q12" s="46">
-        <f>H12*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H12*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R12" s="47">
@@ -13240,23 +13495,23 @@
         <v/>
       </c>
       <c r="T12" s="39">
-        <f>R12*S12+P12*'02_Parametres'!$D$20</f>
+        <f>R12*S12*AC12+P12*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U12" s="46">
-        <f>IF(R12&lt;=0,0,MAX(1,ROUNDUP(R12/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R12&lt;=0,0,MAX(1,ROUNDUP(R12/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V12" s="39">
-        <f>U12*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U12*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W12" s="39">
-        <f>R12*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R12*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X12" s="39">
-        <f>P12*'02_Parametres'!$G$12</f>
+        <f>P12*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y12" s="49">
@@ -13264,11 +13519,19 @@
         <v/>
       </c>
       <c r="Z12" s="32">
-        <f>IFERROR(R12/(U12*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R12/(U12*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA12" s="48">
         <f>IFERROR(Y12/R12,0)</f>
+        <v/>
+      </c>
+      <c r="AB12" s="45">
+        <f>IF(E12="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC12" s="45">
+        <f>IF(E12="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13338,7 +13601,7 @@
         <v/>
       </c>
       <c r="Q13" s="46">
-        <f>H13*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H13*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R13" s="47">
@@ -13350,23 +13613,23 @@
         <v/>
       </c>
       <c r="T13" s="39">
-        <f>R13*S13+P13*'02_Parametres'!$D$20</f>
+        <f>R13*S13*AC13+P13*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U13" s="46">
-        <f>IF(R13&lt;=0,0,MAX(1,ROUNDUP(R13/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R13&lt;=0,0,MAX(1,ROUNDUP(R13/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V13" s="39">
-        <f>U13*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U13*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W13" s="39">
-        <f>R13*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R13*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X13" s="39">
-        <f>P13*'02_Parametres'!$G$12</f>
+        <f>P13*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y13" s="49">
@@ -13374,11 +13637,19 @@
         <v/>
       </c>
       <c r="Z13" s="32">
-        <f>IFERROR(R13/(U13*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R13/(U13*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA13" s="48">
         <f>IFERROR(Y13/R13,0)</f>
+        <v/>
+      </c>
+      <c r="AB13" s="45">
+        <f>IF(E13="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC13" s="45">
+        <f>IF(E13="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13448,7 +13719,7 @@
         <v/>
       </c>
       <c r="Q14" s="46">
-        <f>H14*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H14*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R14" s="47">
@@ -13460,23 +13731,23 @@
         <v/>
       </c>
       <c r="T14" s="39">
-        <f>R14*S14+P14*'02_Parametres'!$D$20</f>
+        <f>R14*S14*AC14+P14*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U14" s="46">
-        <f>IF(R14&lt;=0,0,MAX(1,ROUNDUP(R14/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R14&lt;=0,0,MAX(1,ROUNDUP(R14/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V14" s="39">
-        <f>U14*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U14*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W14" s="39">
-        <f>R14*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R14*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X14" s="39">
-        <f>P14*'02_Parametres'!$G$12</f>
+        <f>P14*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y14" s="49">
@@ -13484,11 +13755,19 @@
         <v/>
       </c>
       <c r="Z14" s="32">
-        <f>IFERROR(R14/(U14*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R14/(U14*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA14" s="48">
         <f>IFERROR(Y14/R14,0)</f>
+        <v/>
+      </c>
+      <c r="AB14" s="45">
+        <f>IF(E14="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC14" s="45">
+        <f>IF(E14="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13558,7 +13837,7 @@
         <v/>
       </c>
       <c r="Q15" s="46">
-        <f>H15*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H15*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R15" s="47">
@@ -13570,23 +13849,23 @@
         <v/>
       </c>
       <c r="T15" s="39">
-        <f>R15*S15+P15*'02_Parametres'!$D$20</f>
+        <f>R15*S15*AC15+P15*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U15" s="46">
-        <f>IF(R15&lt;=0,0,MAX(1,ROUNDUP(R15/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R15&lt;=0,0,MAX(1,ROUNDUP(R15/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V15" s="39">
-        <f>U15*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U15*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W15" s="39">
-        <f>R15*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R15*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X15" s="39">
-        <f>P15*'02_Parametres'!$G$12</f>
+        <f>P15*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y15" s="49">
@@ -13594,11 +13873,19 @@
         <v/>
       </c>
       <c r="Z15" s="32">
-        <f>IFERROR(R15/(U15*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R15/(U15*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA15" s="48">
         <f>IFERROR(Y15/R15,0)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="45">
+        <f>IF(E15="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC15" s="45">
+        <f>IF(E15="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13668,7 +13955,7 @@
         <v/>
       </c>
       <c r="Q16" s="46">
-        <f>H16*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H16*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R16" s="47">
@@ -13680,23 +13967,23 @@
         <v/>
       </c>
       <c r="T16" s="39">
-        <f>R16*S16+P16*'02_Parametres'!$D$20</f>
+        <f>R16*S16*AC16+P16*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U16" s="46">
-        <f>IF(R16&lt;=0,0,MAX(1,ROUNDUP(R16/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R16&lt;=0,0,MAX(1,ROUNDUP(R16/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V16" s="39">
-        <f>U16*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U16*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W16" s="39">
-        <f>R16*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R16*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X16" s="39">
-        <f>P16*'02_Parametres'!$G$12</f>
+        <f>P16*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y16" s="49">
@@ -13704,11 +13991,19 @@
         <v/>
       </c>
       <c r="Z16" s="32">
-        <f>IFERROR(R16/(U16*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R16/(U16*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA16" s="48">
         <f>IFERROR(Y16/R16,0)</f>
+        <v/>
+      </c>
+      <c r="AB16" s="45">
+        <f>IF(E16="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC16" s="45">
+        <f>IF(E16="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13778,7 +14073,7 @@
         <v/>
       </c>
       <c r="Q17" s="46">
-        <f>H17*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H17*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R17" s="47">
@@ -13790,23 +14085,23 @@
         <v/>
       </c>
       <c r="T17" s="39">
-        <f>R17*S17+P17*'02_Parametres'!$D$20</f>
+        <f>R17*S17*AC17+P17*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U17" s="46">
-        <f>IF(R17&lt;=0,0,MAX(1,ROUNDUP(R17/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R17&lt;=0,0,MAX(1,ROUNDUP(R17/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V17" s="39">
-        <f>U17*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U17*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W17" s="39">
-        <f>R17*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R17*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X17" s="39">
-        <f>P17*'02_Parametres'!$G$12</f>
+        <f>P17*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y17" s="49">
@@ -13814,11 +14109,19 @@
         <v/>
       </c>
       <c r="Z17" s="32">
-        <f>IFERROR(R17/(U17*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R17/(U17*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA17" s="48">
         <f>IFERROR(Y17/R17,0)</f>
+        <v/>
+      </c>
+      <c r="AB17" s="45">
+        <f>IF(E17="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC17" s="45">
+        <f>IF(E17="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13888,7 +14191,7 @@
         <v/>
       </c>
       <c r="Q18" s="46">
-        <f>H18*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H18*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R18" s="47">
@@ -13900,23 +14203,23 @@
         <v/>
       </c>
       <c r="T18" s="39">
-        <f>R18*S18+P18*'02_Parametres'!$D$20</f>
+        <f>R18*S18*AC18+P18*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U18" s="46">
-        <f>IF(R18&lt;=0,0,MAX(1,ROUNDUP(R18/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R18&lt;=0,0,MAX(1,ROUNDUP(R18/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V18" s="39">
-        <f>U18*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U18*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W18" s="39">
-        <f>R18*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R18*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X18" s="39">
-        <f>P18*'02_Parametres'!$G$12</f>
+        <f>P18*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y18" s="49">
@@ -13924,11 +14227,19 @@
         <v/>
       </c>
       <c r="Z18" s="32">
-        <f>IFERROR(R18/(U18*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R18/(U18*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA18" s="48">
         <f>IFERROR(Y18/R18,0)</f>
+        <v/>
+      </c>
+      <c r="AB18" s="45">
+        <f>IF(E18="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC18" s="45">
+        <f>IF(E18="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -13998,7 +14309,7 @@
         <v/>
       </c>
       <c r="Q19" s="46">
-        <f>H19*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H19*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R19" s="47">
@@ -14010,23 +14321,23 @@
         <v/>
       </c>
       <c r="T19" s="39">
-        <f>R19*S19+P19*'02_Parametres'!$D$20</f>
+        <f>R19*S19*AC19+P19*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U19" s="46">
-        <f>IF(R19&lt;=0,0,MAX(1,ROUNDUP(R19/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R19&lt;=0,0,MAX(1,ROUNDUP(R19/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V19" s="39">
-        <f>U19*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U19*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W19" s="39">
-        <f>R19*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R19*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X19" s="39">
-        <f>P19*'02_Parametres'!$G$12</f>
+        <f>P19*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y19" s="49">
@@ -14034,11 +14345,19 @@
         <v/>
       </c>
       <c r="Z19" s="32">
-        <f>IFERROR(R19/(U19*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R19/(U19*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA19" s="48">
         <f>IFERROR(Y19/R19,0)</f>
+        <v/>
+      </c>
+      <c r="AB19" s="45">
+        <f>IF(E19="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC19" s="45">
+        <f>IF(E19="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14108,7 +14427,7 @@
         <v/>
       </c>
       <c r="Q20" s="46">
-        <f>H20*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H20*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R20" s="47">
@@ -14120,23 +14439,23 @@
         <v/>
       </c>
       <c r="T20" s="39">
-        <f>R20*S20+P20*'02_Parametres'!$D$20</f>
+        <f>R20*S20*AC20+P20*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U20" s="46">
-        <f>IF(R20&lt;=0,0,MAX(1,ROUNDUP(R20/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R20&lt;=0,0,MAX(1,ROUNDUP(R20/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V20" s="39">
-        <f>U20*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U20*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W20" s="39">
-        <f>R20*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R20*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X20" s="39">
-        <f>P20*'02_Parametres'!$G$12</f>
+        <f>P20*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y20" s="49">
@@ -14144,11 +14463,19 @@
         <v/>
       </c>
       <c r="Z20" s="32">
-        <f>IFERROR(R20/(U20*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R20/(U20*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA20" s="48">
         <f>IFERROR(Y20/R20,0)</f>
+        <v/>
+      </c>
+      <c r="AB20" s="45">
+        <f>IF(E20="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC20" s="45">
+        <f>IF(E20="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14218,7 +14545,7 @@
         <v/>
       </c>
       <c r="Q21" s="46">
-        <f>H21*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H21*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R21" s="47">
@@ -14230,23 +14557,23 @@
         <v/>
       </c>
       <c r="T21" s="39">
-        <f>R21*S21+P21*'02_Parametres'!$D$20</f>
+        <f>R21*S21*AC21+P21*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U21" s="46">
-        <f>IF(R21&lt;=0,0,MAX(1,ROUNDUP(R21/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R21&lt;=0,0,MAX(1,ROUNDUP(R21/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V21" s="39">
-        <f>U21*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U21*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W21" s="39">
-        <f>R21*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R21*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X21" s="39">
-        <f>P21*'02_Parametres'!$G$12</f>
+        <f>P21*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y21" s="49">
@@ -14254,11 +14581,19 @@
         <v/>
       </c>
       <c r="Z21" s="32">
-        <f>IFERROR(R21/(U21*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R21/(U21*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA21" s="48">
         <f>IFERROR(Y21/R21,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="45">
+        <f>IF(E21="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="45">
+        <f>IF(E21="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14328,7 +14663,7 @@
         <v/>
       </c>
       <c r="Q22" s="46">
-        <f>H22*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H22*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R22" s="47">
@@ -14340,23 +14675,23 @@
         <v/>
       </c>
       <c r="T22" s="39">
-        <f>R22*S22+P22*'02_Parametres'!$D$20</f>
+        <f>R22*S22*AC22+P22*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U22" s="46">
-        <f>IF(R22&lt;=0,0,MAX(1,ROUNDUP(R22/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R22&lt;=0,0,MAX(1,ROUNDUP(R22/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V22" s="39">
-        <f>U22*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U22*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W22" s="39">
-        <f>R22*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R22*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X22" s="39">
-        <f>P22*'02_Parametres'!$G$12</f>
+        <f>P22*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y22" s="49">
@@ -14364,11 +14699,19 @@
         <v/>
       </c>
       <c r="Z22" s="32">
-        <f>IFERROR(R22/(U22*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R22/(U22*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA22" s="48">
         <f>IFERROR(Y22/R22,0)</f>
+        <v/>
+      </c>
+      <c r="AB22" s="45">
+        <f>IF(E22="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC22" s="45">
+        <f>IF(E22="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14438,7 +14781,7 @@
         <v/>
       </c>
       <c r="Q23" s="46">
-        <f>H23*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H23*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R23" s="47">
@@ -14450,23 +14793,23 @@
         <v/>
       </c>
       <c r="T23" s="39">
-        <f>R23*S23+P23*'02_Parametres'!$D$20</f>
+        <f>R23*S23*AC23+P23*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U23" s="46">
-        <f>IF(R23&lt;=0,0,MAX(1,ROUNDUP(R23/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R23&lt;=0,0,MAX(1,ROUNDUP(R23/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V23" s="39">
-        <f>U23*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U23*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W23" s="39">
-        <f>R23*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R23*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X23" s="39">
-        <f>P23*'02_Parametres'!$G$12</f>
+        <f>P23*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y23" s="49">
@@ -14474,11 +14817,19 @@
         <v/>
       </c>
       <c r="Z23" s="32">
-        <f>IFERROR(R23/(U23*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R23/(U23*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA23" s="48">
         <f>IFERROR(Y23/R23,0)</f>
+        <v/>
+      </c>
+      <c r="AB23" s="45">
+        <f>IF(E23="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC23" s="45">
+        <f>IF(E23="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14548,7 +14899,7 @@
         <v/>
       </c>
       <c r="Q24" s="46">
-        <f>H24*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H24*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R24" s="47">
@@ -14560,23 +14911,23 @@
         <v/>
       </c>
       <c r="T24" s="39">
-        <f>R24*S24+P24*'02_Parametres'!$D$20</f>
+        <f>R24*S24*AC24+P24*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U24" s="46">
-        <f>IF(R24&lt;=0,0,MAX(1,ROUNDUP(R24/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R24&lt;=0,0,MAX(1,ROUNDUP(R24/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V24" s="39">
-        <f>U24*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U24*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W24" s="39">
-        <f>R24*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R24*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X24" s="39">
-        <f>P24*'02_Parametres'!$G$12</f>
+        <f>P24*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y24" s="49">
@@ -14584,11 +14935,19 @@
         <v/>
       </c>
       <c r="Z24" s="32">
-        <f>IFERROR(R24/(U24*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R24/(U24*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA24" s="48">
         <f>IFERROR(Y24/R24,0)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="45">
+        <f>IF(E24="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="45">
+        <f>IF(E24="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14658,7 +15017,7 @@
         <v/>
       </c>
       <c r="Q25" s="46">
-        <f>H25*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H25*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R25" s="47">
@@ -14670,23 +15029,23 @@
         <v/>
       </c>
       <c r="T25" s="39">
-        <f>R25*S25+P25*'02_Parametres'!$D$20</f>
+        <f>R25*S25*AC25+P25*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U25" s="46">
-        <f>IF(R25&lt;=0,0,MAX(1,ROUNDUP(R25/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R25&lt;=0,0,MAX(1,ROUNDUP(R25/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V25" s="39">
-        <f>U25*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U25*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W25" s="39">
-        <f>R25*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R25*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X25" s="39">
-        <f>P25*'02_Parametres'!$G$12</f>
+        <f>P25*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y25" s="49">
@@ -14694,11 +15053,19 @@
         <v/>
       </c>
       <c r="Z25" s="32">
-        <f>IFERROR(R25/(U25*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R25/(U25*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA25" s="48">
         <f>IFERROR(Y25/R25,0)</f>
+        <v/>
+      </c>
+      <c r="AB25" s="45">
+        <f>IF(E25="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="45">
+        <f>IF(E25="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14768,7 +15135,7 @@
         <v/>
       </c>
       <c r="Q26" s="46">
-        <f>H26*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H26*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R26" s="47">
@@ -14780,23 +15147,23 @@
         <v/>
       </c>
       <c r="T26" s="39">
-        <f>R26*S26+P26*'02_Parametres'!$D$20</f>
+        <f>R26*S26*AC26+P26*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U26" s="46">
-        <f>IF(R26&lt;=0,0,MAX(1,ROUNDUP(R26/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R26&lt;=0,0,MAX(1,ROUNDUP(R26/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V26" s="39">
-        <f>U26*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U26*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W26" s="39">
-        <f>R26*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R26*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X26" s="39">
-        <f>P26*'02_Parametres'!$G$12</f>
+        <f>P26*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y26" s="49">
@@ -14804,11 +15171,19 @@
         <v/>
       </c>
       <c r="Z26" s="32">
-        <f>IFERROR(R26/(U26*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R26/(U26*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA26" s="48">
         <f>IFERROR(Y26/R26,0)</f>
+        <v/>
+      </c>
+      <c r="AB26" s="45">
+        <f>IF(E26="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC26" s="45">
+        <f>IF(E26="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14878,7 +15253,7 @@
         <v/>
       </c>
       <c r="Q27" s="46">
-        <f>H27*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H27*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R27" s="47">
@@ -14890,23 +15265,23 @@
         <v/>
       </c>
       <c r="T27" s="39">
-        <f>R27*S27+P27*'02_Parametres'!$D$20</f>
+        <f>R27*S27*AC27+P27*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U27" s="46">
-        <f>IF(R27&lt;=0,0,MAX(1,ROUNDUP(R27/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R27&lt;=0,0,MAX(1,ROUNDUP(R27/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V27" s="39">
-        <f>U27*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U27*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W27" s="39">
-        <f>R27*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R27*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X27" s="39">
-        <f>P27*'02_Parametres'!$G$12</f>
+        <f>P27*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y27" s="49">
@@ -14914,11 +15289,19 @@
         <v/>
       </c>
       <c r="Z27" s="32">
-        <f>IFERROR(R27/(U27*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R27/(U27*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA27" s="48">
         <f>IFERROR(Y27/R27,0)</f>
+        <v/>
+      </c>
+      <c r="AB27" s="45">
+        <f>IF(E27="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC27" s="45">
+        <f>IF(E27="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -14988,7 +15371,7 @@
         <v/>
       </c>
       <c r="Q28" s="46">
-        <f>H28*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H28*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R28" s="47">
@@ -15000,23 +15383,23 @@
         <v/>
       </c>
       <c r="T28" s="39">
-        <f>R28*S28+P28*'02_Parametres'!$D$20</f>
+        <f>R28*S28*AC28+P28*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U28" s="46">
-        <f>IF(R28&lt;=0,0,MAX(1,ROUNDUP(R28/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R28&lt;=0,0,MAX(1,ROUNDUP(R28/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V28" s="39">
-        <f>U28*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U28*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W28" s="39">
-        <f>R28*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R28*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X28" s="39">
-        <f>P28*'02_Parametres'!$G$12</f>
+        <f>P28*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y28" s="49">
@@ -15024,11 +15407,19 @@
         <v/>
       </c>
       <c r="Z28" s="32">
-        <f>IFERROR(R28/(U28*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R28/(U28*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA28" s="48">
         <f>IFERROR(Y28/R28,0)</f>
+        <v/>
+      </c>
+      <c r="AB28" s="45">
+        <f>IF(E28="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC28" s="45">
+        <f>IF(E28="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15098,7 +15489,7 @@
         <v/>
       </c>
       <c r="Q29" s="46">
-        <f>H29*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H29*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R29" s="47">
@@ -15110,23 +15501,23 @@
         <v/>
       </c>
       <c r="T29" s="39">
-        <f>R29*S29+P29*'02_Parametres'!$D$20</f>
+        <f>R29*S29*AC29+P29*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U29" s="46">
-        <f>IF(R29&lt;=0,0,MAX(1,ROUNDUP(R29/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R29&lt;=0,0,MAX(1,ROUNDUP(R29/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V29" s="39">
-        <f>U29*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U29*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W29" s="39">
-        <f>R29*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R29*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X29" s="39">
-        <f>P29*'02_Parametres'!$G$12</f>
+        <f>P29*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y29" s="49">
@@ -15134,11 +15525,19 @@
         <v/>
       </c>
       <c r="Z29" s="32">
-        <f>IFERROR(R29/(U29*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R29/(U29*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA29" s="48">
         <f>IFERROR(Y29/R29,0)</f>
+        <v/>
+      </c>
+      <c r="AB29" s="45">
+        <f>IF(E29="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC29" s="45">
+        <f>IF(E29="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15208,7 +15607,7 @@
         <v/>
       </c>
       <c r="Q30" s="46">
-        <f>H30*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H30*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R30" s="47">
@@ -15220,23 +15619,23 @@
         <v/>
       </c>
       <c r="T30" s="39">
-        <f>R30*S30+P30*'02_Parametres'!$D$20</f>
+        <f>R30*S30*AC30+P30*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U30" s="46">
-        <f>IF(R30&lt;=0,0,MAX(1,ROUNDUP(R30/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R30&lt;=0,0,MAX(1,ROUNDUP(R30/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V30" s="39">
-        <f>U30*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U30*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W30" s="39">
-        <f>R30*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R30*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X30" s="39">
-        <f>P30*'02_Parametres'!$G$12</f>
+        <f>P30*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y30" s="49">
@@ -15244,11 +15643,19 @@
         <v/>
       </c>
       <c r="Z30" s="32">
-        <f>IFERROR(R30/(U30*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R30/(U30*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA30" s="48">
         <f>IFERROR(Y30/R30,0)</f>
+        <v/>
+      </c>
+      <c r="AB30" s="45">
+        <f>IF(E30="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC30" s="45">
+        <f>IF(E30="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15318,7 +15725,7 @@
         <v/>
       </c>
       <c r="Q31" s="46">
-        <f>H31*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H31*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R31" s="47">
@@ -15330,23 +15737,23 @@
         <v/>
       </c>
       <c r="T31" s="39">
-        <f>R31*S31+P31*'02_Parametres'!$D$20</f>
+        <f>R31*S31*AC31+P31*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U31" s="46">
-        <f>IF(R31&lt;=0,0,MAX(1,ROUNDUP(R31/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R31&lt;=0,0,MAX(1,ROUNDUP(R31/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V31" s="39">
-        <f>U31*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U31*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W31" s="39">
-        <f>R31*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R31*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X31" s="39">
-        <f>P31*'02_Parametres'!$G$12</f>
+        <f>P31*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y31" s="49">
@@ -15354,11 +15761,19 @@
         <v/>
       </c>
       <c r="Z31" s="32">
-        <f>IFERROR(R31/(U31*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R31/(U31*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA31" s="48">
         <f>IFERROR(Y31/R31,0)</f>
+        <v/>
+      </c>
+      <c r="AB31" s="45">
+        <f>IF(E31="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC31" s="45">
+        <f>IF(E31="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15428,7 +15843,7 @@
         <v/>
       </c>
       <c r="Q32" s="46">
-        <f>H32*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H32*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R32" s="47">
@@ -15440,23 +15855,23 @@
         <v/>
       </c>
       <c r="T32" s="39">
-        <f>R32*S32+P32*'02_Parametres'!$D$20</f>
+        <f>R32*S32*AC32+P32*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U32" s="46">
-        <f>IF(R32&lt;=0,0,MAX(1,ROUNDUP(R32/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R32&lt;=0,0,MAX(1,ROUNDUP(R32/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V32" s="39">
-        <f>U32*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U32*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W32" s="39">
-        <f>R32*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R32*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X32" s="39">
-        <f>P32*'02_Parametres'!$G$12</f>
+        <f>P32*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y32" s="49">
@@ -15464,11 +15879,19 @@
         <v/>
       </c>
       <c r="Z32" s="32">
-        <f>IFERROR(R32/(U32*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R32/(U32*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA32" s="48">
         <f>IFERROR(Y32/R32,0)</f>
+        <v/>
+      </c>
+      <c r="AB32" s="45">
+        <f>IF(E32="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC32" s="45">
+        <f>IF(E32="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15538,7 +15961,7 @@
         <v/>
       </c>
       <c r="Q33" s="46">
-        <f>H33*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H33*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R33" s="47">
@@ -15550,23 +15973,23 @@
         <v/>
       </c>
       <c r="T33" s="39">
-        <f>R33*S33+P33*'02_Parametres'!$D$20</f>
+        <f>R33*S33*AC33+P33*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U33" s="46">
-        <f>IF(R33&lt;=0,0,MAX(1,ROUNDUP(R33/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R33&lt;=0,0,MAX(1,ROUNDUP(R33/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V33" s="39">
-        <f>U33*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U33*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W33" s="39">
-        <f>R33*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R33*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X33" s="39">
-        <f>P33*'02_Parametres'!$G$12</f>
+        <f>P33*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y33" s="49">
@@ -15574,11 +15997,19 @@
         <v/>
       </c>
       <c r="Z33" s="32">
-        <f>IFERROR(R33/(U33*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R33/(U33*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA33" s="48">
         <f>IFERROR(Y33/R33,0)</f>
+        <v/>
+      </c>
+      <c r="AB33" s="45">
+        <f>IF(E33="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC33" s="45">
+        <f>IF(E33="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15648,7 +16079,7 @@
         <v/>
       </c>
       <c r="Q34" s="46">
-        <f>H34*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H34*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R34" s="47">
@@ -15660,23 +16091,23 @@
         <v/>
       </c>
       <c r="T34" s="39">
-        <f>R34*S34+P34*'02_Parametres'!$D$20</f>
+        <f>R34*S34*AC34+P34*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U34" s="46">
-        <f>IF(R34&lt;=0,0,MAX(1,ROUNDUP(R34/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R34&lt;=0,0,MAX(1,ROUNDUP(R34/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V34" s="39">
-        <f>U34*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U34*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W34" s="39">
-        <f>R34*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R34*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X34" s="39">
-        <f>P34*'02_Parametres'!$G$12</f>
+        <f>P34*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y34" s="49">
@@ -15684,11 +16115,19 @@
         <v/>
       </c>
       <c r="Z34" s="32">
-        <f>IFERROR(R34/(U34*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R34/(U34*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA34" s="48">
         <f>IFERROR(Y34/R34,0)</f>
+        <v/>
+      </c>
+      <c r="AB34" s="45">
+        <f>IF(E34="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC34" s="45">
+        <f>IF(E34="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15758,7 +16197,7 @@
         <v/>
       </c>
       <c r="Q35" s="46">
-        <f>H35*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H35*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R35" s="47">
@@ -15770,23 +16209,23 @@
         <v/>
       </c>
       <c r="T35" s="39">
-        <f>R35*S35+P35*'02_Parametres'!$D$20</f>
+        <f>R35*S35*AC35+P35*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U35" s="46">
-        <f>IF(R35&lt;=0,0,MAX(1,ROUNDUP(R35/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R35&lt;=0,0,MAX(1,ROUNDUP(R35/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V35" s="39">
-        <f>U35*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U35*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W35" s="39">
-        <f>R35*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R35*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X35" s="39">
-        <f>P35*'02_Parametres'!$G$12</f>
+        <f>P35*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y35" s="49">
@@ -15794,11 +16233,19 @@
         <v/>
       </c>
       <c r="Z35" s="32">
-        <f>IFERROR(R35/(U35*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R35/(U35*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA35" s="48">
         <f>IFERROR(Y35/R35,0)</f>
+        <v/>
+      </c>
+      <c r="AB35" s="45">
+        <f>IF(E35="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC35" s="45">
+        <f>IF(E35="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15868,7 +16315,7 @@
         <v/>
       </c>
       <c r="Q36" s="46">
-        <f>H36*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H36*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R36" s="47">
@@ -15880,23 +16327,23 @@
         <v/>
       </c>
       <c r="T36" s="39">
-        <f>R36*S36+P36*'02_Parametres'!$D$20</f>
+        <f>R36*S36*AC36+P36*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U36" s="46">
-        <f>IF(R36&lt;=0,0,MAX(1,ROUNDUP(R36/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R36&lt;=0,0,MAX(1,ROUNDUP(R36/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V36" s="39">
-        <f>U36*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U36*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W36" s="39">
-        <f>R36*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R36*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X36" s="39">
-        <f>P36*'02_Parametres'!$G$12</f>
+        <f>P36*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y36" s="49">
@@ -15904,11 +16351,19 @@
         <v/>
       </c>
       <c r="Z36" s="32">
-        <f>IFERROR(R36/(U36*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R36/(U36*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA36" s="48">
         <f>IFERROR(Y36/R36,0)</f>
+        <v/>
+      </c>
+      <c r="AB36" s="45">
+        <f>IF(E36="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC36" s="45">
+        <f>IF(E36="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -15978,7 +16433,7 @@
         <v/>
       </c>
       <c r="Q37" s="46">
-        <f>H37*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H37*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R37" s="47">
@@ -15990,23 +16445,23 @@
         <v/>
       </c>
       <c r="T37" s="39">
-        <f>R37*S37+P37*'02_Parametres'!$D$20</f>
+        <f>R37*S37*AC37+P37*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U37" s="46">
-        <f>IF(R37&lt;=0,0,MAX(1,ROUNDUP(R37/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R37&lt;=0,0,MAX(1,ROUNDUP(R37/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V37" s="39">
-        <f>U37*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U37*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W37" s="39">
-        <f>R37*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R37*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X37" s="39">
-        <f>P37*'02_Parametres'!$G$12</f>
+        <f>P37*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y37" s="49">
@@ -16014,11 +16469,19 @@
         <v/>
       </c>
       <c r="Z37" s="32">
-        <f>IFERROR(R37/(U37*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R37/(U37*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA37" s="48">
         <f>IFERROR(Y37/R37,0)</f>
+        <v/>
+      </c>
+      <c r="AB37" s="45">
+        <f>IF(E37="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC37" s="45">
+        <f>IF(E37="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16088,7 +16551,7 @@
         <v/>
       </c>
       <c r="Q38" s="46">
-        <f>H38*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H38*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R38" s="47">
@@ -16100,23 +16563,23 @@
         <v/>
       </c>
       <c r="T38" s="39">
-        <f>R38*S38+P38*'02_Parametres'!$D$20</f>
+        <f>R38*S38*AC38+P38*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U38" s="46">
-        <f>IF(R38&lt;=0,0,MAX(1,ROUNDUP(R38/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R38&lt;=0,0,MAX(1,ROUNDUP(R38/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V38" s="39">
-        <f>U38*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U38*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W38" s="39">
-        <f>R38*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R38*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X38" s="39">
-        <f>P38*'02_Parametres'!$G$12</f>
+        <f>P38*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y38" s="49">
@@ -16124,11 +16587,19 @@
         <v/>
       </c>
       <c r="Z38" s="32">
-        <f>IFERROR(R38/(U38*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R38/(U38*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA38" s="48">
         <f>IFERROR(Y38/R38,0)</f>
+        <v/>
+      </c>
+      <c r="AB38" s="45">
+        <f>IF(E38="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC38" s="45">
+        <f>IF(E38="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16198,7 +16669,7 @@
         <v/>
       </c>
       <c r="Q39" s="46">
-        <f>H39*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H39*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R39" s="47">
@@ -16210,23 +16681,23 @@
         <v/>
       </c>
       <c r="T39" s="39">
-        <f>R39*S39+P39*'02_Parametres'!$D$20</f>
+        <f>R39*S39*AC39+P39*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U39" s="46">
-        <f>IF(R39&lt;=0,0,MAX(1,ROUNDUP(R39/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R39&lt;=0,0,MAX(1,ROUNDUP(R39/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V39" s="39">
-        <f>U39*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U39*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W39" s="39">
-        <f>R39*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R39*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X39" s="39">
-        <f>P39*'02_Parametres'!$G$12</f>
+        <f>P39*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y39" s="49">
@@ -16234,11 +16705,19 @@
         <v/>
       </c>
       <c r="Z39" s="32">
-        <f>IFERROR(R39/(U39*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R39/(U39*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA39" s="48">
         <f>IFERROR(Y39/R39,0)</f>
+        <v/>
+      </c>
+      <c r="AB39" s="45">
+        <f>IF(E39="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC39" s="45">
+        <f>IF(E39="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16308,7 +16787,7 @@
         <v/>
       </c>
       <c r="Q40" s="46">
-        <f>H40*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H40*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R40" s="47">
@@ -16320,23 +16799,23 @@
         <v/>
       </c>
       <c r="T40" s="39">
-        <f>R40*S40+P40*'02_Parametres'!$D$20</f>
+        <f>R40*S40*AC40+P40*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U40" s="46">
-        <f>IF(R40&lt;=0,0,MAX(1,ROUNDUP(R40/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R40&lt;=0,0,MAX(1,ROUNDUP(R40/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V40" s="39">
-        <f>U40*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U40*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W40" s="39">
-        <f>R40*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R40*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X40" s="39">
-        <f>P40*'02_Parametres'!$G$12</f>
+        <f>P40*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y40" s="49">
@@ -16344,11 +16823,19 @@
         <v/>
       </c>
       <c r="Z40" s="32">
-        <f>IFERROR(R40/(U40*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R40/(U40*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA40" s="48">
         <f>IFERROR(Y40/R40,0)</f>
+        <v/>
+      </c>
+      <c r="AB40" s="45">
+        <f>IF(E40="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC40" s="45">
+        <f>IF(E40="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16418,7 +16905,7 @@
         <v/>
       </c>
       <c r="Q41" s="46">
-        <f>H41*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H41*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R41" s="47">
@@ -16430,23 +16917,23 @@
         <v/>
       </c>
       <c r="T41" s="39">
-        <f>R41*S41+P41*'02_Parametres'!$D$20</f>
+        <f>R41*S41*AC41+P41*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U41" s="46">
-        <f>IF(R41&lt;=0,0,MAX(1,ROUNDUP(R41/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R41&lt;=0,0,MAX(1,ROUNDUP(R41/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V41" s="39">
-        <f>U41*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U41*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W41" s="39">
-        <f>R41*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R41*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X41" s="39">
-        <f>P41*'02_Parametres'!$G$12</f>
+        <f>P41*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y41" s="49">
@@ -16454,11 +16941,19 @@
         <v/>
       </c>
       <c r="Z41" s="32">
-        <f>IFERROR(R41/(U41*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R41/(U41*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA41" s="48">
         <f>IFERROR(Y41/R41,0)</f>
+        <v/>
+      </c>
+      <c r="AB41" s="45">
+        <f>IF(E41="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC41" s="45">
+        <f>IF(E41="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16528,7 +17023,7 @@
         <v/>
       </c>
       <c r="Q42" s="46">
-        <f>H42*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H42*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R42" s="47">
@@ -16540,23 +17035,23 @@
         <v/>
       </c>
       <c r="T42" s="39">
-        <f>R42*S42+P42*'02_Parametres'!$D$20</f>
+        <f>R42*S42*AC42+P42*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U42" s="46">
-        <f>IF(R42&lt;=0,0,MAX(1,ROUNDUP(R42/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R42&lt;=0,0,MAX(1,ROUNDUP(R42/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V42" s="39">
-        <f>U42*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U42*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W42" s="39">
-        <f>R42*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R42*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X42" s="39">
-        <f>P42*'02_Parametres'!$G$12</f>
+        <f>P42*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y42" s="49">
@@ -16564,11 +17059,19 @@
         <v/>
       </c>
       <c r="Z42" s="32">
-        <f>IFERROR(R42/(U42*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R42/(U42*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA42" s="48">
         <f>IFERROR(Y42/R42,0)</f>
+        <v/>
+      </c>
+      <c r="AB42" s="45">
+        <f>IF(E42="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC42" s="45">
+        <f>IF(E42="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16638,7 +17141,7 @@
         <v/>
       </c>
       <c r="Q43" s="46">
-        <f>H43*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H43*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R43" s="47">
@@ -16650,23 +17153,23 @@
         <v/>
       </c>
       <c r="T43" s="39">
-        <f>R43*S43+P43*'02_Parametres'!$D$20</f>
+        <f>R43*S43*AC43+P43*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U43" s="46">
-        <f>IF(R43&lt;=0,0,MAX(1,ROUNDUP(R43/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R43&lt;=0,0,MAX(1,ROUNDUP(R43/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V43" s="39">
-        <f>U43*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U43*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W43" s="39">
-        <f>R43*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R43*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X43" s="39">
-        <f>P43*'02_Parametres'!$G$12</f>
+        <f>P43*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y43" s="49">
@@ -16674,11 +17177,19 @@
         <v/>
       </c>
       <c r="Z43" s="32">
-        <f>IFERROR(R43/(U43*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R43/(U43*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA43" s="48">
         <f>IFERROR(Y43/R43,0)</f>
+        <v/>
+      </c>
+      <c r="AB43" s="45">
+        <f>IF(E43="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC43" s="45">
+        <f>IF(E43="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16748,7 +17259,7 @@
         <v/>
       </c>
       <c r="Q44" s="46">
-        <f>H44*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H44*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R44" s="47">
@@ -16760,23 +17271,23 @@
         <v/>
       </c>
       <c r="T44" s="39">
-        <f>R44*S44+P44*'02_Parametres'!$D$20</f>
+        <f>R44*S44*AC44+P44*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U44" s="46">
-        <f>IF(R44&lt;=0,0,MAX(1,ROUNDUP(R44/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R44&lt;=0,0,MAX(1,ROUNDUP(R44/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V44" s="39">
-        <f>U44*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U44*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W44" s="39">
-        <f>R44*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R44*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X44" s="39">
-        <f>P44*'02_Parametres'!$G$12</f>
+        <f>P44*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y44" s="49">
@@ -16784,11 +17295,19 @@
         <v/>
       </c>
       <c r="Z44" s="32">
-        <f>IFERROR(R44/(U44*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R44/(U44*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA44" s="48">
         <f>IFERROR(Y44/R44,0)</f>
+        <v/>
+      </c>
+      <c r="AB44" s="45">
+        <f>IF(E44="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC44" s="45">
+        <f>IF(E44="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16858,7 +17377,7 @@
         <v/>
       </c>
       <c r="Q45" s="46">
-        <f>H45*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H45*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R45" s="47">
@@ -16870,23 +17389,23 @@
         <v/>
       </c>
       <c r="T45" s="39">
-        <f>R45*S45+P45*'02_Parametres'!$D$20</f>
+        <f>R45*S45*AC45+P45*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U45" s="46">
-        <f>IF(R45&lt;=0,0,MAX(1,ROUNDUP(R45/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R45&lt;=0,0,MAX(1,ROUNDUP(R45/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V45" s="39">
-        <f>U45*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U45*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W45" s="39">
-        <f>R45*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R45*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X45" s="39">
-        <f>P45*'02_Parametres'!$G$12</f>
+        <f>P45*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y45" s="49">
@@ -16894,11 +17413,19 @@
         <v/>
       </c>
       <c r="Z45" s="32">
-        <f>IFERROR(R45/(U45*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R45/(U45*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA45" s="48">
         <f>IFERROR(Y45/R45,0)</f>
+        <v/>
+      </c>
+      <c r="AB45" s="45">
+        <f>IF(E45="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC45" s="45">
+        <f>IF(E45="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -16968,7 +17495,7 @@
         <v/>
       </c>
       <c r="Q46" s="46">
-        <f>H46*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H46*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R46" s="47">
@@ -16980,23 +17507,23 @@
         <v/>
       </c>
       <c r="T46" s="39">
-        <f>R46*S46+P46*'02_Parametres'!$D$20</f>
+        <f>R46*S46*AC46+P46*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U46" s="46">
-        <f>IF(R46&lt;=0,0,MAX(1,ROUNDUP(R46/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R46&lt;=0,0,MAX(1,ROUNDUP(R46/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V46" s="39">
-        <f>U46*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U46*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W46" s="39">
-        <f>R46*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R46*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X46" s="39">
-        <f>P46*'02_Parametres'!$G$12</f>
+        <f>P46*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y46" s="49">
@@ -17004,11 +17531,19 @@
         <v/>
       </c>
       <c r="Z46" s="32">
-        <f>IFERROR(R46/(U46*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R46/(U46*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA46" s="48">
         <f>IFERROR(Y46/R46,0)</f>
+        <v/>
+      </c>
+      <c r="AB46" s="45">
+        <f>IF(E46="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC46" s="45">
+        <f>IF(E46="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17078,7 +17613,7 @@
         <v/>
       </c>
       <c r="Q47" s="46">
-        <f>H47*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H47*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R47" s="47">
@@ -17090,23 +17625,23 @@
         <v/>
       </c>
       <c r="T47" s="39">
-        <f>R47*S47+P47*'02_Parametres'!$D$20</f>
+        <f>R47*S47*AC47+P47*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U47" s="46">
-        <f>IF(R47&lt;=0,0,MAX(1,ROUNDUP(R47/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R47&lt;=0,0,MAX(1,ROUNDUP(R47/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V47" s="39">
-        <f>U47*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U47*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W47" s="39">
-        <f>R47*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R47*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X47" s="39">
-        <f>P47*'02_Parametres'!$G$12</f>
+        <f>P47*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y47" s="49">
@@ -17114,11 +17649,19 @@
         <v/>
       </c>
       <c r="Z47" s="32">
-        <f>IFERROR(R47/(U47*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R47/(U47*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA47" s="48">
         <f>IFERROR(Y47/R47,0)</f>
+        <v/>
+      </c>
+      <c r="AB47" s="45">
+        <f>IF(E47="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC47" s="45">
+        <f>IF(E47="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17188,7 +17731,7 @@
         <v/>
       </c>
       <c r="Q48" s="46">
-        <f>H48*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H48*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R48" s="47">
@@ -17200,23 +17743,23 @@
         <v/>
       </c>
       <c r="T48" s="39">
-        <f>R48*S48+P48*'02_Parametres'!$D$20</f>
+        <f>R48*S48*AC48+P48*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U48" s="46">
-        <f>IF(R48&lt;=0,0,MAX(1,ROUNDUP(R48/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R48&lt;=0,0,MAX(1,ROUNDUP(R48/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V48" s="39">
-        <f>U48*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U48*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W48" s="39">
-        <f>R48*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R48*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X48" s="39">
-        <f>P48*'02_Parametres'!$G$12</f>
+        <f>P48*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y48" s="49">
@@ -17224,11 +17767,19 @@
         <v/>
       </c>
       <c r="Z48" s="32">
-        <f>IFERROR(R48/(U48*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R48/(U48*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA48" s="48">
         <f>IFERROR(Y48/R48,0)</f>
+        <v/>
+      </c>
+      <c r="AB48" s="45">
+        <f>IF(E48="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC48" s="45">
+        <f>IF(E48="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17298,7 +17849,7 @@
         <v/>
       </c>
       <c r="Q49" s="46">
-        <f>H49*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H49*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R49" s="47">
@@ -17310,23 +17861,23 @@
         <v/>
       </c>
       <c r="T49" s="39">
-        <f>R49*S49+P49*'02_Parametres'!$D$20</f>
+        <f>R49*S49*AC49+P49*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U49" s="46">
-        <f>IF(R49&lt;=0,0,MAX(1,ROUNDUP(R49/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R49&lt;=0,0,MAX(1,ROUNDUP(R49/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V49" s="39">
-        <f>U49*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U49*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W49" s="39">
-        <f>R49*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R49*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X49" s="39">
-        <f>P49*'02_Parametres'!$G$12</f>
+        <f>P49*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y49" s="49">
@@ -17334,11 +17885,19 @@
         <v/>
       </c>
       <c r="Z49" s="32">
-        <f>IFERROR(R49/(U49*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R49/(U49*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA49" s="48">
         <f>IFERROR(Y49/R49,0)</f>
+        <v/>
+      </c>
+      <c r="AB49" s="45">
+        <f>IF(E49="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC49" s="45">
+        <f>IF(E49="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17408,7 +17967,7 @@
         <v/>
       </c>
       <c r="Q50" s="46">
-        <f>H50*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H50*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R50" s="47">
@@ -17420,23 +17979,23 @@
         <v/>
       </c>
       <c r="T50" s="39">
-        <f>R50*S50+P50*'02_Parametres'!$D$20</f>
+        <f>R50*S50*AC50+P50*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U50" s="46">
-        <f>IF(R50&lt;=0,0,MAX(1,ROUNDUP(R50/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R50&lt;=0,0,MAX(1,ROUNDUP(R50/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V50" s="39">
-        <f>U50*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U50*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W50" s="39">
-        <f>R50*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R50*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X50" s="39">
-        <f>P50*'02_Parametres'!$G$12</f>
+        <f>P50*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y50" s="49">
@@ -17444,11 +18003,19 @@
         <v/>
       </c>
       <c r="Z50" s="32">
-        <f>IFERROR(R50/(U50*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R50/(U50*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA50" s="48">
         <f>IFERROR(Y50/R50,0)</f>
+        <v/>
+      </c>
+      <c r="AB50" s="45">
+        <f>IF(E50="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC50" s="45">
+        <f>IF(E50="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17518,7 +18085,7 @@
         <v/>
       </c>
       <c r="Q51" s="46">
-        <f>H51*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H51*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R51" s="47">
@@ -17530,23 +18097,23 @@
         <v/>
       </c>
       <c r="T51" s="39">
-        <f>R51*S51+P51*'02_Parametres'!$D$20</f>
+        <f>R51*S51*AC51+P51*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U51" s="46">
-        <f>IF(R51&lt;=0,0,MAX(1,ROUNDUP(R51/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R51&lt;=0,0,MAX(1,ROUNDUP(R51/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V51" s="39">
-        <f>U51*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U51*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W51" s="39">
-        <f>R51*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R51*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X51" s="39">
-        <f>P51*'02_Parametres'!$G$12</f>
+        <f>P51*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y51" s="49">
@@ -17554,11 +18121,19 @@
         <v/>
       </c>
       <c r="Z51" s="32">
-        <f>IFERROR(R51/(U51*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R51/(U51*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA51" s="48">
         <f>IFERROR(Y51/R51,0)</f>
+        <v/>
+      </c>
+      <c r="AB51" s="45">
+        <f>IF(E51="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC51" s="45">
+        <f>IF(E51="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17628,7 +18203,7 @@
         <v/>
       </c>
       <c r="Q52" s="46">
-        <f>H52*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H52*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R52" s="47">
@@ -17640,23 +18215,23 @@
         <v/>
       </c>
       <c r="T52" s="39">
-        <f>R52*S52+P52*'02_Parametres'!$D$20</f>
+        <f>R52*S52*AC52+P52*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U52" s="46">
-        <f>IF(R52&lt;=0,0,MAX(1,ROUNDUP(R52/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R52&lt;=0,0,MAX(1,ROUNDUP(R52/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V52" s="39">
-        <f>U52*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U52*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W52" s="39">
-        <f>R52*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R52*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X52" s="39">
-        <f>P52*'02_Parametres'!$G$12</f>
+        <f>P52*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y52" s="49">
@@ -17664,11 +18239,19 @@
         <v/>
       </c>
       <c r="Z52" s="32">
-        <f>IFERROR(R52/(U52*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R52/(U52*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA52" s="48">
         <f>IFERROR(Y52/R52,0)</f>
+        <v/>
+      </c>
+      <c r="AB52" s="45">
+        <f>IF(E52="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC52" s="45">
+        <f>IF(E52="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17738,7 +18321,7 @@
         <v/>
       </c>
       <c r="Q53" s="46">
-        <f>H53*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H53*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R53" s="47">
@@ -17750,23 +18333,23 @@
         <v/>
       </c>
       <c r="T53" s="39">
-        <f>R53*S53+P53*'02_Parametres'!$D$20</f>
+        <f>R53*S53*AC53+P53*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U53" s="46">
-        <f>IF(R53&lt;=0,0,MAX(1,ROUNDUP(R53/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R53&lt;=0,0,MAX(1,ROUNDUP(R53/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V53" s="39">
-        <f>U53*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U53*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W53" s="39">
-        <f>R53*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R53*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X53" s="39">
-        <f>P53*'02_Parametres'!$G$12</f>
+        <f>P53*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y53" s="49">
@@ -17774,11 +18357,19 @@
         <v/>
       </c>
       <c r="Z53" s="32">
-        <f>IFERROR(R53/(U53*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R53/(U53*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA53" s="48">
         <f>IFERROR(Y53/R53,0)</f>
+        <v/>
+      </c>
+      <c r="AB53" s="45">
+        <f>IF(E53="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC53" s="45">
+        <f>IF(E53="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17848,7 +18439,7 @@
         <v/>
       </c>
       <c r="Q54" s="46">
-        <f>H54*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H54*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R54" s="47">
@@ -17860,23 +18451,23 @@
         <v/>
       </c>
       <c r="T54" s="39">
-        <f>R54*S54+P54*'02_Parametres'!$D$20</f>
+        <f>R54*S54*AC54+P54*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U54" s="46">
-        <f>IF(R54&lt;=0,0,MAX(1,ROUNDUP(R54/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R54&lt;=0,0,MAX(1,ROUNDUP(R54/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V54" s="39">
-        <f>U54*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U54*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W54" s="39">
-        <f>R54*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R54*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X54" s="39">
-        <f>P54*'02_Parametres'!$G$12</f>
+        <f>P54*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y54" s="49">
@@ -17884,11 +18475,19 @@
         <v/>
       </c>
       <c r="Z54" s="32">
-        <f>IFERROR(R54/(U54*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R54/(U54*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA54" s="48">
         <f>IFERROR(Y54/R54,0)</f>
+        <v/>
+      </c>
+      <c r="AB54" s="45">
+        <f>IF(E54="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC54" s="45">
+        <f>IF(E54="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -17958,7 +18557,7 @@
         <v/>
       </c>
       <c r="Q55" s="46">
-        <f>H55*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H55*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R55" s="47">
@@ -17970,23 +18569,23 @@
         <v/>
       </c>
       <c r="T55" s="39">
-        <f>R55*S55+P55*'02_Parametres'!$D$20</f>
+        <f>R55*S55*AC55+P55*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U55" s="46">
-        <f>IF(R55&lt;=0,0,MAX(1,ROUNDUP(R55/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R55&lt;=0,0,MAX(1,ROUNDUP(R55/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V55" s="39">
-        <f>U55*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U55*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W55" s="39">
-        <f>R55*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R55*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X55" s="39">
-        <f>P55*'02_Parametres'!$G$12</f>
+        <f>P55*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y55" s="49">
@@ -17994,11 +18593,19 @@
         <v/>
       </c>
       <c r="Z55" s="32">
-        <f>IFERROR(R55/(U55*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R55/(U55*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA55" s="48">
         <f>IFERROR(Y55/R55,0)</f>
+        <v/>
+      </c>
+      <c r="AB55" s="45">
+        <f>IF(E55="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC55" s="45">
+        <f>IF(E55="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -18068,7 +18675,7 @@
         <v/>
       </c>
       <c r="Q56" s="46">
-        <f>H56*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H56*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R56" s="47">
@@ -18080,23 +18687,23 @@
         <v/>
       </c>
       <c r="T56" s="39">
-        <f>R56*S56+P56*'02_Parametres'!$D$20</f>
+        <f>R56*S56*AC56+P56*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U56" s="46">
-        <f>IF(R56&lt;=0,0,MAX(1,ROUNDUP(R56/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R56&lt;=0,0,MAX(1,ROUNDUP(R56/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V56" s="39">
-        <f>U56*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U56*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W56" s="39">
-        <f>R56*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R56*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X56" s="39">
-        <f>P56*'02_Parametres'!$G$12</f>
+        <f>P56*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y56" s="49">
@@ -18104,11 +18711,19 @@
         <v/>
       </c>
       <c r="Z56" s="32">
-        <f>IFERROR(R56/(U56*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R56/(U56*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA56" s="48">
         <f>IFERROR(Y56/R56,0)</f>
+        <v/>
+      </c>
+      <c r="AB56" s="45">
+        <f>IF(E56="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC56" s="45">
+        <f>IF(E56="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -18178,7 +18793,7 @@
         <v/>
       </c>
       <c r="Q57" s="46">
-        <f>H57*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H57*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R57" s="47">
@@ -18190,23 +18805,23 @@
         <v/>
       </c>
       <c r="T57" s="39">
-        <f>R57*S57+P57*'02_Parametres'!$D$20</f>
+        <f>R57*S57*AC57+P57*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U57" s="46">
-        <f>IF(R57&lt;=0,0,MAX(1,ROUNDUP(R57/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R57&lt;=0,0,MAX(1,ROUNDUP(R57/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V57" s="39">
-        <f>U57*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U57*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W57" s="39">
-        <f>R57*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R57*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X57" s="39">
-        <f>P57*'02_Parametres'!$G$12</f>
+        <f>P57*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y57" s="49">
@@ -18214,11 +18829,19 @@
         <v/>
       </c>
       <c r="Z57" s="32">
-        <f>IFERROR(R57/(U57*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R57/(U57*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA57" s="48">
         <f>IFERROR(Y57/R57,0)</f>
+        <v/>
+      </c>
+      <c r="AB57" s="45">
+        <f>IF(E57="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC57" s="45">
+        <f>IF(E57="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -18288,7 +18911,7 @@
         <v/>
       </c>
       <c r="Q58" s="46">
-        <f>H58*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H58*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R58" s="47">
@@ -18300,23 +18923,23 @@
         <v/>
       </c>
       <c r="T58" s="39">
-        <f>R58*S58+P58*'02_Parametres'!$D$20</f>
+        <f>R58*S58*AC58+P58*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U58" s="46">
-        <f>IF(R58&lt;=0,0,MAX(1,ROUNDUP(R58/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R58&lt;=0,0,MAX(1,ROUNDUP(R58/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V58" s="39">
-        <f>U58*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U58*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W58" s="39">
-        <f>R58*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R58*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X58" s="39">
-        <f>P58*'02_Parametres'!$G$12</f>
+        <f>P58*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y58" s="49">
@@ -18324,11 +18947,19 @@
         <v/>
       </c>
       <c r="Z58" s="32">
-        <f>IFERROR(R58/(U58*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R58/(U58*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA58" s="48">
         <f>IFERROR(Y58/R58,0)</f>
+        <v/>
+      </c>
+      <c r="AB58" s="45">
+        <f>IF(E58="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC58" s="45">
+        <f>IF(E58="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -18398,7 +19029,7 @@
         <v/>
       </c>
       <c r="Q59" s="46">
-        <f>H59*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H59*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R59" s="47">
@@ -18410,23 +19041,23 @@
         <v/>
       </c>
       <c r="T59" s="39">
-        <f>R59*S59+P59*'02_Parametres'!$D$20</f>
+        <f>R59*S59*AC59+P59*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U59" s="46">
-        <f>IF(R59&lt;=0,0,MAX(1,ROUNDUP(R59/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R59&lt;=0,0,MAX(1,ROUNDUP(R59/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V59" s="39">
-        <f>U59*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U59*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W59" s="39">
-        <f>R59*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R59*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X59" s="39">
-        <f>P59*'02_Parametres'!$G$12</f>
+        <f>P59*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y59" s="49">
@@ -18434,11 +19065,19 @@
         <v/>
       </c>
       <c r="Z59" s="32">
-        <f>IFERROR(R59/(U59*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R59/(U59*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA59" s="48">
         <f>IFERROR(Y59/R59,0)</f>
+        <v/>
+      </c>
+      <c r="AB59" s="45">
+        <f>IF(E59="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC59" s="45">
+        <f>IF(E59="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
         <v/>
       </c>
     </row>
@@ -18508,7 +19147,7 @@
         <v/>
       </c>
       <c r="Q60" s="46">
-        <f>H60*('02_Parametres'!$G$9/'02_Parametres'!$D$21)</f>
+        <f>H60*('02_Parametres'!$G$10/'02_Parametres'!$D$23)</f>
         <v/>
       </c>
       <c r="R60" s="47">
@@ -18520,23 +19159,23 @@
         <v/>
       </c>
       <c r="T60" s="39">
-        <f>R60*S60+P60*'02_Parametres'!$D$20</f>
+        <f>R60*S60*AC60+P60*'02_Parametres'!$D$22</f>
         <v/>
       </c>
       <c r="U60" s="46">
-        <f>IF(R60&lt;=0,0,MAX(1,ROUNDUP(R60/'02_Parametres'!$D$14,0)))</f>
+        <f>IF(R60&lt;=0,0,MAX(1,ROUNDUP(R60/'02_Parametres'!$D$16,0)))</f>
         <v/>
       </c>
       <c r="V60" s="39">
-        <f>U60*'02_Parametres'!$D$16*'02_Parametres'!$D$17*(1+'02_Parametres'!$G$11)</f>
+        <f>U60*'02_Parametres'!$D$18*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="W60" s="39">
-        <f>R60*'02_Parametres'!$D$18*(1+'02_Parametres'!$G$10)</f>
+        <f>R60*'02_Parametres'!$D$20*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="X60" s="39">
-        <f>P60*'02_Parametres'!$G$12</f>
+        <f>P60*'02_Parametres'!$G$13</f>
         <v/>
       </c>
       <c r="Y60" s="49">
@@ -18544,13 +19183,21 @@
         <v/>
       </c>
       <c r="Z60" s="32">
-        <f>IFERROR(R60/(U60*'02_Parametres'!$D$14),0)</f>
+        <f>IFERROR(R60/(U60*'02_Parametres'!$D$16),0)</f>
         <v/>
       </c>
       <c r="AA60" s="48">
         <f>IFERROR(Y60/R60,0)</f>
         <v/>
       </c>
+      <c r="AB60" s="45">
+        <f>IF(E60="ALT",'02_Parametres'!$D$26+(1-'02_Parametres'!$D$26)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
+      <c r="AC60" s="45">
+        <f>IF(E60="ALT",'02_Parametres'!$G$9+(1-'02_Parametres'!$G$9)*'02_Parametres'!$D$25,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="40" t="inlineStr">
@@ -18676,10 +19323,20 @@
           <t> </t>
         </is>
       </c>
+      <c r="AB61" s="36" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="AC61" s="36" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A1:AC1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18722,7 +19379,7 @@
         </is>
       </c>
       <c r="C3" s="50">
-        <f>'02_Parametres'!D24</f>
+        <f>'02_Parametres'!D28</f>
         <v/>
       </c>
       <c r="E3" s="19" t="inlineStr">
@@ -18731,7 +19388,7 @@
         </is>
       </c>
       <c r="I3" s="49">
-        <f>'02_Parametres'!$D$22*SUM('07_Moteur'!$T$3:$T$60)</f>
+        <f>'02_Parametres'!$D$24*SUM('07_Moteur'!$T$3:$T$60)</f>
         <v/>
       </c>
       <c r="J3" s="51" t="n"/>
@@ -18809,11 +19466,11 @@
         <v/>
       </c>
       <c r="E6" s="52">
-        <f>'06_Structure'!F4*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F4*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F6" s="52">
-        <f>'06_Structure'!G4*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G4*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G6" s="53">
@@ -18857,11 +19514,11 @@
         <v/>
       </c>
       <c r="E7" s="52">
-        <f>'06_Structure'!F5*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F5*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F7" s="52">
-        <f>'06_Structure'!G5*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G5*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G7" s="53">
@@ -18905,11 +19562,11 @@
         <v/>
       </c>
       <c r="E8" s="52">
-        <f>'06_Structure'!F6*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F6*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F8" s="52">
-        <f>'06_Structure'!G6*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G6*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G8" s="53">
@@ -18953,11 +19610,11 @@
         <v/>
       </c>
       <c r="E9" s="52">
-        <f>'06_Structure'!F7*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F7*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F9" s="52">
-        <f>'06_Structure'!G7*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G7*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G9" s="53">
@@ -19001,11 +19658,11 @@
         <v/>
       </c>
       <c r="E10" s="52">
-        <f>'06_Structure'!F8*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F8*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F10" s="52">
-        <f>'06_Structure'!G8*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G8*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G10" s="53">
@@ -19049,11 +19706,11 @@
         <v/>
       </c>
       <c r="E11" s="52">
-        <f>'06_Structure'!F9*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F9*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F11" s="52">
-        <f>'06_Structure'!G9*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G9*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G11" s="53">
@@ -19097,11 +19754,11 @@
         <v/>
       </c>
       <c r="E12" s="52">
-        <f>'06_Structure'!F10*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F10*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F12" s="52">
-        <f>'06_Structure'!G10*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G10*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G12" s="53">
@@ -19145,11 +19802,11 @@
         <v/>
       </c>
       <c r="E13" s="52">
-        <f>'06_Structure'!F11*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F11*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F13" s="52">
-        <f>'06_Structure'!G11*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G11*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G13" s="53">
@@ -19193,11 +19850,11 @@
         <v/>
       </c>
       <c r="E14" s="52">
-        <f>'06_Structure'!F12*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F12*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F14" s="52">
-        <f>'06_Structure'!G12*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G12*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G14" s="53">
@@ -19241,11 +19898,11 @@
         <v/>
       </c>
       <c r="E15" s="52">
-        <f>'06_Structure'!F13*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F13*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F15" s="52">
-        <f>'06_Structure'!G13*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G13*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G15" s="53">
@@ -19289,11 +19946,11 @@
         <v/>
       </c>
       <c r="E16" s="52">
-        <f>'06_Structure'!F14*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F14*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F16" s="52">
-        <f>'06_Structure'!G14*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G14*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G16" s="53">
@@ -19337,11 +19994,11 @@
         <v/>
       </c>
       <c r="E17" s="52">
-        <f>'06_Structure'!F15*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F15*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F17" s="52">
-        <f>'06_Structure'!G15*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G15*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G17" s="53">
@@ -19385,11 +20042,11 @@
         <v/>
       </c>
       <c r="E18" s="52">
-        <f>'06_Structure'!F16*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F16*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F18" s="52">
-        <f>'06_Structure'!G16*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G16*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G18" s="53">
@@ -19433,11 +20090,11 @@
         <v/>
       </c>
       <c r="E19" s="52">
-        <f>'06_Structure'!F17*(1+'02_Parametres'!$G$10)</f>
+        <f>'06_Structure'!F17*(1+'02_Parametres'!$G$11)</f>
         <v/>
       </c>
       <c r="F19" s="52">
-        <f>'06_Structure'!G17*'02_Parametres'!$D$19*(1+'02_Parametres'!$G$11)</f>
+        <f>'06_Structure'!G17*'02_Parametres'!$D$21*(1+'02_Parametres'!$G$12)</f>
         <v/>
       </c>
       <c r="G19" s="53">

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -381,8 +381,17 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1099,16 +1108,16 @@
         </is>
       </c>
       <c r="C3" s="56">
-        <f>'02_Leviers'!$D$24</f>
+        <f>'02_Leviers'!$D$23</f>
         <v/>
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>Frais de structure à allouer :</t>
+          <t>Frais de structure (fixe) à allouer :</t>
         </is>
       </c>
       <c r="H3" s="55">
-        <f>'02_Leviers'!$D$18*SUM('08_Moteur'!$AH$3:$AH$60)</f>
+        <f>'02_Leviers'!$D$17*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="I3" s="30" t="n"/>
@@ -1190,7 +1199,7 @@
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>'07_Structure'!G4*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G4*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G6" s="57">
@@ -1238,7 +1247,7 @@
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>'07_Structure'!G5*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G5*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G7" s="57">
@@ -1286,7 +1295,7 @@
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>'07_Structure'!G6*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G6*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G8" s="57">
@@ -1334,7 +1343,7 @@
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>'07_Structure'!G7*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G7*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G9" s="57">
@@ -1382,7 +1391,7 @@
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>'07_Structure'!G8*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G8*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G10" s="57">
@@ -1430,7 +1439,7 @@
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>'07_Structure'!G9*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G9*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G11" s="57">
@@ -1478,7 +1487,7 @@
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>'07_Structure'!G10*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G10*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G12" s="57">
@@ -1526,7 +1535,7 @@
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>'07_Structure'!G11*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G11*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G13" s="57">
@@ -1574,7 +1583,7 @@
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>'07_Structure'!G12*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G12*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G14" s="57">
@@ -1622,7 +1631,7 @@
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>'07_Structure'!G13*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G13*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G15" s="57">
@@ -1670,7 +1679,7 @@
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>'07_Structure'!G14*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G14*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G16" s="57">
@@ -1718,7 +1727,7 @@
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>'07_Structure'!G15*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G15*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G17" s="57">
@@ -1766,7 +1775,7 @@
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>'07_Structure'!G16*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G16*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G18" s="57">
@@ -1814,7 +1823,7 @@
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>'07_Structure'!G17*'02_Leviers'!$D$16*(1+'02_Leviers'!$G$12)</f>
+        <f>'07_Structure'!G17*'02_Leviers'!$D$15*(1+'02_Leviers'!$G$12)</f>
         <v/>
       </c>
       <c r="G19" s="57">
@@ -2108,7 +2117,7 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>-'02_Leviers'!$D$18*'07_Structure'!D18</f>
+        <f>-2000000</f>
         <v/>
       </c>
       <c r="D12" s="17">
@@ -2131,7 +2140,7 @@
         </is>
       </c>
       <c r="C13" s="64">
-        <f>'07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-'02_Leviers'!$D$18*'07_Structure'!D18</f>
+        <f>'07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-2000000</f>
         <v/>
       </c>
       <c r="D13" s="64">
@@ -2154,7 +2163,7 @@
         </is>
       </c>
       <c r="C14" s="67">
-        <f>IFERROR(('07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-'02_Leviers'!$D$18*'07_Structure'!D18)/'07_Structure'!D18,0)</f>
+        <f>IFERROR(('07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-2000000)/'07_Structure'!D18,0)</f>
         <v/>
       </c>
       <c r="D14" s="18">
@@ -2201,7 +2210,7 @@
         </is>
       </c>
       <c r="C16" s="64">
-        <f>'07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-'02_Leviers'!$D$18*'07_Structure'!D18-'07_Structure'!I18</f>
+        <f>'07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-2000000-'07_Structure'!I18</f>
         <v/>
       </c>
       <c r="D16" s="64">
@@ -2291,7 +2300,7 @@
         </is>
       </c>
       <c r="C24" s="17">
-        <f>SUMPRODUCT('08_Moteur'!$AB$3:$AB$60)*'02_Leviers'!$D$17-SUMPRODUCT('08_Moteur'!$H$3:$H$60)*'02_Leviers'!$D$17</f>
+        <f>SUMPRODUCT('08_Moteur'!$AB$3:$AB$60)*'02_Leviers'!$D$16-SUMPRODUCT('08_Moteur'!$H$3:$H$60)*'02_Leviers'!$D$16</f>
         <v/>
       </c>
     </row>
@@ -2321,28 +2330,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Simulateur de décisions (planification rentrée) — impact AVANT → APRÈS</t>
+          <t>Simulateur &amp; conseil de décisions (planification rentrée) — impact AVANT → APRÈS</t>
         </is>
       </c>
     </row>
@@ -2361,20 +2373,34 @@
           <t>Somme Δ décisions :</t>
         </is>
       </c>
-      <c r="H2" s="55">
-        <f>SUM(M4:M61)</f>
-        <v/>
-      </c>
+      <c r="G2" s="55">
+        <f>SUM(P4:P61)</f>
+        <v/>
+      </c>
+      <c r="H2" s="30" t="n"/>
       <c r="I2" s="19" t="inlineStr">
         <is>
           <t>EBITDA après :</t>
         </is>
       </c>
       <c r="J2" s="47">
-        <f>D2+H2</f>
-        <v/>
-      </c>
-      <c r="K2" s="30" t="n"/>
+        <f>D2+G2</f>
+        <v/>
+      </c>
+      <c r="K2" s="19" t="inlineStr">
+        <is>
+          <t>🔴 promos &lt; point mort :</t>
+        </is>
+      </c>
+      <c r="L2" s="69">
+        <f>SUMPRODUCT(--('08_Moteur'!$AM$3:$AM$60&lt;0))</f>
+        <v/>
+      </c>
+      <c r="M2" s="70" t="inlineStr">
+        <is>
+          <t>→ gain potentiel si recos appliquées (col. « € si reco ») :</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
@@ -2414,30 +2440,45 @@
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
-          <t>Remplissage</t>
+          <t>Rempl.</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
+          <t>🤖 Reco</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>€ si reco</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Motif</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
           <t>Décision</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>Cl. après</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>Eff. après</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Contrib après</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>Δ EBITDA</t>
         </is>
@@ -2472,29 +2513,41 @@
         <f>'08_Moteur'!M3</f>
         <v/>
       </c>
-      <c r="H4" s="69">
+      <c r="H4" s="71">
         <f>'08_Moteur'!AN3</f>
         <v/>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="72">
+        <f>IF('08_Moteur'!AM3&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN3&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN3&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J4" s="17">
+        <f>IF('08_Moteur'!AM3&lt;0,-'08_Moteur'!AM3,IF('08_Moteur'!AN3&gt;=0.95,'08_Moteur'!O3*'08_Moteur'!AO3-'08_Moteur'!U3,0))</f>
+        <v/>
+      </c>
+      <c r="K4" s="29">
+        <f>IF('08_Moteur'!AM3&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN3&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN3&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J4" s="51">
-        <f>IF(I4="Ne pas lancer",0,IF(I4="Statu quo",MAX('08_Moteur'!AI3,'08_Moteur'!M3),IF(I4="Ouvrir +1",'08_Moteur'!AI3+1,'08_Moteur'!AI3)))</f>
-        <v/>
-      </c>
-      <c r="K4" s="51">
-        <f>IF(I4="Ne pas lancer",0,'08_Moteur'!AD3)</f>
-        <v/>
-      </c>
-      <c r="L4" s="17">
-        <f>K4*'08_Moteur'!AE3*'08_Moteur'!AF3+IF(I4="Ne pas lancer",0,'08_Moteur'!AB3)*'02_Leviers'!$D$17-J4*'08_Moteur'!U3-K4*'08_Moteur'!R3*(1+'02_Leviers'!$G$11)-IF(I4="Ne pas lancer",0,'08_Moteur'!AL3)</f>
-        <v/>
-      </c>
-      <c r="M4" s="55">
-        <f>L4-'08_Moteur'!AM3</f>
+      <c r="M4" s="51">
+        <f>IF(L4="Ne pas lancer",0,IF(L4="Statu quo",MAX('08_Moteur'!AI3,'08_Moteur'!M3),IF(L4="Ouvrir +1",'08_Moteur'!AI3+1,'08_Moteur'!AI3)))</f>
+        <v/>
+      </c>
+      <c r="N4" s="51">
+        <f>IF(L4="Ne pas lancer",0,'08_Moteur'!AD3)</f>
+        <v/>
+      </c>
+      <c r="O4" s="17">
+        <f>N4*'08_Moteur'!AE3*'08_Moteur'!AF3+IF(L4="Ne pas lancer",0,'08_Moteur'!AB3)*'02_Leviers'!$D$16-M4*'08_Moteur'!U3-N4*'08_Moteur'!R3*(1+'02_Leviers'!$G$11)-IF(L4="Ne pas lancer",0,'08_Moteur'!AL3)</f>
+        <v/>
+      </c>
+      <c r="P4" s="55">
+        <f>O4-'08_Moteur'!AM3</f>
         <v/>
       </c>
     </row>
@@ -2527,29 +2580,41 @@
         <f>'08_Moteur'!M4</f>
         <v/>
       </c>
-      <c r="H5" s="69">
+      <c r="H5" s="71">
         <f>'08_Moteur'!AN4</f>
         <v/>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="72">
+        <f>IF('08_Moteur'!AM4&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN4&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN4&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J5" s="17">
+        <f>IF('08_Moteur'!AM4&lt;0,-'08_Moteur'!AM4,IF('08_Moteur'!AN4&gt;=0.95,'08_Moteur'!O4*'08_Moteur'!AO4-'08_Moteur'!U4,0))</f>
+        <v/>
+      </c>
+      <c r="K5" s="29">
+        <f>IF('08_Moteur'!AM4&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN4&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN4&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J5" s="51">
-        <f>IF(I5="Ne pas lancer",0,IF(I5="Statu quo",MAX('08_Moteur'!AI4,'08_Moteur'!M4),IF(I5="Ouvrir +1",'08_Moteur'!AI4+1,'08_Moteur'!AI4)))</f>
-        <v/>
-      </c>
-      <c r="K5" s="51">
-        <f>IF(I5="Ne pas lancer",0,'08_Moteur'!AD4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="17">
-        <f>K5*'08_Moteur'!AE4*'08_Moteur'!AF4+IF(I5="Ne pas lancer",0,'08_Moteur'!AB4)*'02_Leviers'!$D$17-J5*'08_Moteur'!U4-K5*'08_Moteur'!R4*(1+'02_Leviers'!$G$11)-IF(I5="Ne pas lancer",0,'08_Moteur'!AL4)</f>
-        <v/>
-      </c>
-      <c r="M5" s="55">
-        <f>L5-'08_Moteur'!AM4</f>
+      <c r="M5" s="51">
+        <f>IF(L5="Ne pas lancer",0,IF(L5="Statu quo",MAX('08_Moteur'!AI4,'08_Moteur'!M4),IF(L5="Ouvrir +1",'08_Moteur'!AI4+1,'08_Moteur'!AI4)))</f>
+        <v/>
+      </c>
+      <c r="N5" s="51">
+        <f>IF(L5="Ne pas lancer",0,'08_Moteur'!AD4)</f>
+        <v/>
+      </c>
+      <c r="O5" s="17">
+        <f>N5*'08_Moteur'!AE4*'08_Moteur'!AF4+IF(L5="Ne pas lancer",0,'08_Moteur'!AB4)*'02_Leviers'!$D$16-M5*'08_Moteur'!U4-N5*'08_Moteur'!R4*(1+'02_Leviers'!$G$11)-IF(L5="Ne pas lancer",0,'08_Moteur'!AL4)</f>
+        <v/>
+      </c>
+      <c r="P5" s="55">
+        <f>O5-'08_Moteur'!AM4</f>
         <v/>
       </c>
     </row>
@@ -2582,29 +2647,41 @@
         <f>'08_Moteur'!M5</f>
         <v/>
       </c>
-      <c r="H6" s="69">
+      <c r="H6" s="71">
         <f>'08_Moteur'!AN5</f>
         <v/>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I6" s="72">
+        <f>IF('08_Moteur'!AM5&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN5&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN5&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>IF('08_Moteur'!AM5&lt;0,-'08_Moteur'!AM5,IF('08_Moteur'!AN5&gt;=0.95,'08_Moteur'!O5*'08_Moteur'!AO5-'08_Moteur'!U5,0))</f>
+        <v/>
+      </c>
+      <c r="K6" s="29">
+        <f>IF('08_Moteur'!AM5&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN5&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN5&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J6" s="51">
-        <f>IF(I6="Ne pas lancer",0,IF(I6="Statu quo",MAX('08_Moteur'!AI5,'08_Moteur'!M5),IF(I6="Ouvrir +1",'08_Moteur'!AI5+1,'08_Moteur'!AI5)))</f>
-        <v/>
-      </c>
-      <c r="K6" s="51">
-        <f>IF(I6="Ne pas lancer",0,'08_Moteur'!AD5)</f>
-        <v/>
-      </c>
-      <c r="L6" s="17">
-        <f>K6*'08_Moteur'!AE5*'08_Moteur'!AF5+IF(I6="Ne pas lancer",0,'08_Moteur'!AB5)*'02_Leviers'!$D$17-J6*'08_Moteur'!U5-K6*'08_Moteur'!R5*(1+'02_Leviers'!$G$11)-IF(I6="Ne pas lancer",0,'08_Moteur'!AL5)</f>
-        <v/>
-      </c>
-      <c r="M6" s="55">
-        <f>L6-'08_Moteur'!AM5</f>
+      <c r="M6" s="51">
+        <f>IF(L6="Ne pas lancer",0,IF(L6="Statu quo",MAX('08_Moteur'!AI5,'08_Moteur'!M5),IF(L6="Ouvrir +1",'08_Moteur'!AI5+1,'08_Moteur'!AI5)))</f>
+        <v/>
+      </c>
+      <c r="N6" s="51">
+        <f>IF(L6="Ne pas lancer",0,'08_Moteur'!AD5)</f>
+        <v/>
+      </c>
+      <c r="O6" s="17">
+        <f>N6*'08_Moteur'!AE5*'08_Moteur'!AF5+IF(L6="Ne pas lancer",0,'08_Moteur'!AB5)*'02_Leviers'!$D$16-M6*'08_Moteur'!U5-N6*'08_Moteur'!R5*(1+'02_Leviers'!$G$11)-IF(L6="Ne pas lancer",0,'08_Moteur'!AL5)</f>
+        <v/>
+      </c>
+      <c r="P6" s="55">
+        <f>O6-'08_Moteur'!AM5</f>
         <v/>
       </c>
     </row>
@@ -2637,29 +2714,41 @@
         <f>'08_Moteur'!M6</f>
         <v/>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="71">
         <f>'08_Moteur'!AN6</f>
         <v/>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="72">
+        <f>IF('08_Moteur'!AM6&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN6&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN6&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>IF('08_Moteur'!AM6&lt;0,-'08_Moteur'!AM6,IF('08_Moteur'!AN6&gt;=0.95,'08_Moteur'!O6*'08_Moteur'!AO6-'08_Moteur'!U6,0))</f>
+        <v/>
+      </c>
+      <c r="K7" s="29">
+        <f>IF('08_Moteur'!AM6&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN6&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN6&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J7" s="51">
-        <f>IF(I7="Ne pas lancer",0,IF(I7="Statu quo",MAX('08_Moteur'!AI6,'08_Moteur'!M6),IF(I7="Ouvrir +1",'08_Moteur'!AI6+1,'08_Moteur'!AI6)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="51">
-        <f>IF(I7="Ne pas lancer",0,'08_Moteur'!AD6)</f>
-        <v/>
-      </c>
-      <c r="L7" s="17">
-        <f>K7*'08_Moteur'!AE6*'08_Moteur'!AF6+IF(I7="Ne pas lancer",0,'08_Moteur'!AB6)*'02_Leviers'!$D$17-J7*'08_Moteur'!U6-K7*'08_Moteur'!R6*(1+'02_Leviers'!$G$11)-IF(I7="Ne pas lancer",0,'08_Moteur'!AL6)</f>
-        <v/>
-      </c>
-      <c r="M7" s="55">
-        <f>L7-'08_Moteur'!AM6</f>
+      <c r="M7" s="51">
+        <f>IF(L7="Ne pas lancer",0,IF(L7="Statu quo",MAX('08_Moteur'!AI6,'08_Moteur'!M6),IF(L7="Ouvrir +1",'08_Moteur'!AI6+1,'08_Moteur'!AI6)))</f>
+        <v/>
+      </c>
+      <c r="N7" s="51">
+        <f>IF(L7="Ne pas lancer",0,'08_Moteur'!AD6)</f>
+        <v/>
+      </c>
+      <c r="O7" s="17">
+        <f>N7*'08_Moteur'!AE6*'08_Moteur'!AF6+IF(L7="Ne pas lancer",0,'08_Moteur'!AB6)*'02_Leviers'!$D$16-M7*'08_Moteur'!U6-N7*'08_Moteur'!R6*(1+'02_Leviers'!$G$11)-IF(L7="Ne pas lancer",0,'08_Moteur'!AL6)</f>
+        <v/>
+      </c>
+      <c r="P7" s="55">
+        <f>O7-'08_Moteur'!AM6</f>
         <v/>
       </c>
     </row>
@@ -2692,29 +2781,41 @@
         <f>'08_Moteur'!M7</f>
         <v/>
       </c>
-      <c r="H8" s="69">
+      <c r="H8" s="71">
         <f>'08_Moteur'!AN7</f>
         <v/>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="72">
+        <f>IF('08_Moteur'!AM7&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN7&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN7&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>IF('08_Moteur'!AM7&lt;0,-'08_Moteur'!AM7,IF('08_Moteur'!AN7&gt;=0.95,'08_Moteur'!O7*'08_Moteur'!AO7-'08_Moteur'!U7,0))</f>
+        <v/>
+      </c>
+      <c r="K8" s="29">
+        <f>IF('08_Moteur'!AM7&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN7&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN7&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J8" s="51">
-        <f>IF(I8="Ne pas lancer",0,IF(I8="Statu quo",MAX('08_Moteur'!AI7,'08_Moteur'!M7),IF(I8="Ouvrir +1",'08_Moteur'!AI7+1,'08_Moteur'!AI7)))</f>
-        <v/>
-      </c>
-      <c r="K8" s="51">
-        <f>IF(I8="Ne pas lancer",0,'08_Moteur'!AD7)</f>
-        <v/>
-      </c>
-      <c r="L8" s="17">
-        <f>K8*'08_Moteur'!AE7*'08_Moteur'!AF7+IF(I8="Ne pas lancer",0,'08_Moteur'!AB7)*'02_Leviers'!$D$17-J8*'08_Moteur'!U7-K8*'08_Moteur'!R7*(1+'02_Leviers'!$G$11)-IF(I8="Ne pas lancer",0,'08_Moteur'!AL7)</f>
-        <v/>
-      </c>
-      <c r="M8" s="55">
-        <f>L8-'08_Moteur'!AM7</f>
+      <c r="M8" s="51">
+        <f>IF(L8="Ne pas lancer",0,IF(L8="Statu quo",MAX('08_Moteur'!AI7,'08_Moteur'!M7),IF(L8="Ouvrir +1",'08_Moteur'!AI7+1,'08_Moteur'!AI7)))</f>
+        <v/>
+      </c>
+      <c r="N8" s="51">
+        <f>IF(L8="Ne pas lancer",0,'08_Moteur'!AD7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="17">
+        <f>N8*'08_Moteur'!AE7*'08_Moteur'!AF7+IF(L8="Ne pas lancer",0,'08_Moteur'!AB7)*'02_Leviers'!$D$16-M8*'08_Moteur'!U7-N8*'08_Moteur'!R7*(1+'02_Leviers'!$G$11)-IF(L8="Ne pas lancer",0,'08_Moteur'!AL7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="55">
+        <f>O8-'08_Moteur'!AM7</f>
         <v/>
       </c>
     </row>
@@ -2747,29 +2848,41 @@
         <f>'08_Moteur'!M8</f>
         <v/>
       </c>
-      <c r="H9" s="69">
+      <c r="H9" s="71">
         <f>'08_Moteur'!AN8</f>
         <v/>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="72">
+        <f>IF('08_Moteur'!AM8&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN8&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN8&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>IF('08_Moteur'!AM8&lt;0,-'08_Moteur'!AM8,IF('08_Moteur'!AN8&gt;=0.95,'08_Moteur'!O8*'08_Moteur'!AO8-'08_Moteur'!U8,0))</f>
+        <v/>
+      </c>
+      <c r="K9" s="29">
+        <f>IF('08_Moteur'!AM8&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN8&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN8&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J9" s="51">
-        <f>IF(I9="Ne pas lancer",0,IF(I9="Statu quo",MAX('08_Moteur'!AI8,'08_Moteur'!M8),IF(I9="Ouvrir +1",'08_Moteur'!AI8+1,'08_Moteur'!AI8)))</f>
-        <v/>
-      </c>
-      <c r="K9" s="51">
-        <f>IF(I9="Ne pas lancer",0,'08_Moteur'!AD8)</f>
-        <v/>
-      </c>
-      <c r="L9" s="17">
-        <f>K9*'08_Moteur'!AE8*'08_Moteur'!AF8+IF(I9="Ne pas lancer",0,'08_Moteur'!AB8)*'02_Leviers'!$D$17-J9*'08_Moteur'!U8-K9*'08_Moteur'!R8*(1+'02_Leviers'!$G$11)-IF(I9="Ne pas lancer",0,'08_Moteur'!AL8)</f>
-        <v/>
-      </c>
-      <c r="M9" s="55">
-        <f>L9-'08_Moteur'!AM8</f>
+      <c r="M9" s="51">
+        <f>IF(L9="Ne pas lancer",0,IF(L9="Statu quo",MAX('08_Moteur'!AI8,'08_Moteur'!M8),IF(L9="Ouvrir +1",'08_Moteur'!AI8+1,'08_Moteur'!AI8)))</f>
+        <v/>
+      </c>
+      <c r="N9" s="51">
+        <f>IF(L9="Ne pas lancer",0,'08_Moteur'!AD8)</f>
+        <v/>
+      </c>
+      <c r="O9" s="17">
+        <f>N9*'08_Moteur'!AE8*'08_Moteur'!AF8+IF(L9="Ne pas lancer",0,'08_Moteur'!AB8)*'02_Leviers'!$D$16-M9*'08_Moteur'!U8-N9*'08_Moteur'!R8*(1+'02_Leviers'!$G$11)-IF(L9="Ne pas lancer",0,'08_Moteur'!AL8)</f>
+        <v/>
+      </c>
+      <c r="P9" s="55">
+        <f>O9-'08_Moteur'!AM8</f>
         <v/>
       </c>
     </row>
@@ -2802,29 +2915,41 @@
         <f>'08_Moteur'!M9</f>
         <v/>
       </c>
-      <c r="H10" s="69">
+      <c r="H10" s="71">
         <f>'08_Moteur'!AN9</f>
         <v/>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="72">
+        <f>IF('08_Moteur'!AM9&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN9&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN9&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>IF('08_Moteur'!AM9&lt;0,-'08_Moteur'!AM9,IF('08_Moteur'!AN9&gt;=0.95,'08_Moteur'!O9*'08_Moteur'!AO9-'08_Moteur'!U9,0))</f>
+        <v/>
+      </c>
+      <c r="K10" s="29">
+        <f>IF('08_Moteur'!AM9&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN9&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN9&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J10" s="51">
-        <f>IF(I10="Ne pas lancer",0,IF(I10="Statu quo",MAX('08_Moteur'!AI9,'08_Moteur'!M9),IF(I10="Ouvrir +1",'08_Moteur'!AI9+1,'08_Moteur'!AI9)))</f>
-        <v/>
-      </c>
-      <c r="K10" s="51">
-        <f>IF(I10="Ne pas lancer",0,'08_Moteur'!AD9)</f>
-        <v/>
-      </c>
-      <c r="L10" s="17">
-        <f>K10*'08_Moteur'!AE9*'08_Moteur'!AF9+IF(I10="Ne pas lancer",0,'08_Moteur'!AB9)*'02_Leviers'!$D$17-J10*'08_Moteur'!U9-K10*'08_Moteur'!R9*(1+'02_Leviers'!$G$11)-IF(I10="Ne pas lancer",0,'08_Moteur'!AL9)</f>
-        <v/>
-      </c>
-      <c r="M10" s="55">
-        <f>L10-'08_Moteur'!AM9</f>
+      <c r="M10" s="51">
+        <f>IF(L10="Ne pas lancer",0,IF(L10="Statu quo",MAX('08_Moteur'!AI9,'08_Moteur'!M9),IF(L10="Ouvrir +1",'08_Moteur'!AI9+1,'08_Moteur'!AI9)))</f>
+        <v/>
+      </c>
+      <c r="N10" s="51">
+        <f>IF(L10="Ne pas lancer",0,'08_Moteur'!AD9)</f>
+        <v/>
+      </c>
+      <c r="O10" s="17">
+        <f>N10*'08_Moteur'!AE9*'08_Moteur'!AF9+IF(L10="Ne pas lancer",0,'08_Moteur'!AB9)*'02_Leviers'!$D$16-M10*'08_Moteur'!U9-N10*'08_Moteur'!R9*(1+'02_Leviers'!$G$11)-IF(L10="Ne pas lancer",0,'08_Moteur'!AL9)</f>
+        <v/>
+      </c>
+      <c r="P10" s="55">
+        <f>O10-'08_Moteur'!AM9</f>
         <v/>
       </c>
     </row>
@@ -2857,29 +2982,41 @@
         <f>'08_Moteur'!M10</f>
         <v/>
       </c>
-      <c r="H11" s="69">
+      <c r="H11" s="71">
         <f>'08_Moteur'!AN10</f>
         <v/>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="72">
+        <f>IF('08_Moteur'!AM10&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN10&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN10&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>IF('08_Moteur'!AM10&lt;0,-'08_Moteur'!AM10,IF('08_Moteur'!AN10&gt;=0.95,'08_Moteur'!O10*'08_Moteur'!AO10-'08_Moteur'!U10,0))</f>
+        <v/>
+      </c>
+      <c r="K11" s="29">
+        <f>IF('08_Moteur'!AM10&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN10&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN10&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J11" s="51">
-        <f>IF(I11="Ne pas lancer",0,IF(I11="Statu quo",MAX('08_Moteur'!AI10,'08_Moteur'!M10),IF(I11="Ouvrir +1",'08_Moteur'!AI10+1,'08_Moteur'!AI10)))</f>
-        <v/>
-      </c>
-      <c r="K11" s="51">
-        <f>IF(I11="Ne pas lancer",0,'08_Moteur'!AD10)</f>
-        <v/>
-      </c>
-      <c r="L11" s="17">
-        <f>K11*'08_Moteur'!AE10*'08_Moteur'!AF10+IF(I11="Ne pas lancer",0,'08_Moteur'!AB10)*'02_Leviers'!$D$17-J11*'08_Moteur'!U10-K11*'08_Moteur'!R10*(1+'02_Leviers'!$G$11)-IF(I11="Ne pas lancer",0,'08_Moteur'!AL10)</f>
-        <v/>
-      </c>
-      <c r="M11" s="55">
-        <f>L11-'08_Moteur'!AM10</f>
+      <c r="M11" s="51">
+        <f>IF(L11="Ne pas lancer",0,IF(L11="Statu quo",MAX('08_Moteur'!AI10,'08_Moteur'!M10),IF(L11="Ouvrir +1",'08_Moteur'!AI10+1,'08_Moteur'!AI10)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="51">
+        <f>IF(L11="Ne pas lancer",0,'08_Moteur'!AD10)</f>
+        <v/>
+      </c>
+      <c r="O11" s="17">
+        <f>N11*'08_Moteur'!AE10*'08_Moteur'!AF10+IF(L11="Ne pas lancer",0,'08_Moteur'!AB10)*'02_Leviers'!$D$16-M11*'08_Moteur'!U10-N11*'08_Moteur'!R10*(1+'02_Leviers'!$G$11)-IF(L11="Ne pas lancer",0,'08_Moteur'!AL10)</f>
+        <v/>
+      </c>
+      <c r="P11" s="55">
+        <f>O11-'08_Moteur'!AM10</f>
         <v/>
       </c>
     </row>
@@ -2912,29 +3049,41 @@
         <f>'08_Moteur'!M11</f>
         <v/>
       </c>
-      <c r="H12" s="69">
+      <c r="H12" s="71">
         <f>'08_Moteur'!AN11</f>
         <v/>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="72">
+        <f>IF('08_Moteur'!AM11&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN11&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN11&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J12" s="17">
+        <f>IF('08_Moteur'!AM11&lt;0,-'08_Moteur'!AM11,IF('08_Moteur'!AN11&gt;=0.95,'08_Moteur'!O11*'08_Moteur'!AO11-'08_Moteur'!U11,0))</f>
+        <v/>
+      </c>
+      <c r="K12" s="29">
+        <f>IF('08_Moteur'!AM11&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN11&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN11&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J12" s="51">
-        <f>IF(I12="Ne pas lancer",0,IF(I12="Statu quo",MAX('08_Moteur'!AI11,'08_Moteur'!M11),IF(I12="Ouvrir +1",'08_Moteur'!AI11+1,'08_Moteur'!AI11)))</f>
-        <v/>
-      </c>
-      <c r="K12" s="51">
-        <f>IF(I12="Ne pas lancer",0,'08_Moteur'!AD11)</f>
-        <v/>
-      </c>
-      <c r="L12" s="17">
-        <f>K12*'08_Moteur'!AE11*'08_Moteur'!AF11+IF(I12="Ne pas lancer",0,'08_Moteur'!AB11)*'02_Leviers'!$D$17-J12*'08_Moteur'!U11-K12*'08_Moteur'!R11*(1+'02_Leviers'!$G$11)-IF(I12="Ne pas lancer",0,'08_Moteur'!AL11)</f>
-        <v/>
-      </c>
-      <c r="M12" s="55">
-        <f>L12-'08_Moteur'!AM11</f>
+      <c r="M12" s="51">
+        <f>IF(L12="Ne pas lancer",0,IF(L12="Statu quo",MAX('08_Moteur'!AI11,'08_Moteur'!M11),IF(L12="Ouvrir +1",'08_Moteur'!AI11+1,'08_Moteur'!AI11)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="51">
+        <f>IF(L12="Ne pas lancer",0,'08_Moteur'!AD11)</f>
+        <v/>
+      </c>
+      <c r="O12" s="17">
+        <f>N12*'08_Moteur'!AE11*'08_Moteur'!AF11+IF(L12="Ne pas lancer",0,'08_Moteur'!AB11)*'02_Leviers'!$D$16-M12*'08_Moteur'!U11-N12*'08_Moteur'!R11*(1+'02_Leviers'!$G$11)-IF(L12="Ne pas lancer",0,'08_Moteur'!AL11)</f>
+        <v/>
+      </c>
+      <c r="P12" s="55">
+        <f>O12-'08_Moteur'!AM11</f>
         <v/>
       </c>
     </row>
@@ -2967,29 +3116,41 @@
         <f>'08_Moteur'!M12</f>
         <v/>
       </c>
-      <c r="H13" s="69">
+      <c r="H13" s="71">
         <f>'08_Moteur'!AN12</f>
         <v/>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="72">
+        <f>IF('08_Moteur'!AM12&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN12&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN12&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>IF('08_Moteur'!AM12&lt;0,-'08_Moteur'!AM12,IF('08_Moteur'!AN12&gt;=0.95,'08_Moteur'!O12*'08_Moteur'!AO12-'08_Moteur'!U12,0))</f>
+        <v/>
+      </c>
+      <c r="K13" s="29">
+        <f>IF('08_Moteur'!AM12&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN12&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN12&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J13" s="51">
-        <f>IF(I13="Ne pas lancer",0,IF(I13="Statu quo",MAX('08_Moteur'!AI12,'08_Moteur'!M12),IF(I13="Ouvrir +1",'08_Moteur'!AI12+1,'08_Moteur'!AI12)))</f>
-        <v/>
-      </c>
-      <c r="K13" s="51">
-        <f>IF(I13="Ne pas lancer",0,'08_Moteur'!AD12)</f>
-        <v/>
-      </c>
-      <c r="L13" s="17">
-        <f>K13*'08_Moteur'!AE12*'08_Moteur'!AF12+IF(I13="Ne pas lancer",0,'08_Moteur'!AB12)*'02_Leviers'!$D$17-J13*'08_Moteur'!U12-K13*'08_Moteur'!R12*(1+'02_Leviers'!$G$11)-IF(I13="Ne pas lancer",0,'08_Moteur'!AL12)</f>
-        <v/>
-      </c>
-      <c r="M13" s="55">
-        <f>L13-'08_Moteur'!AM12</f>
+      <c r="M13" s="51">
+        <f>IF(L13="Ne pas lancer",0,IF(L13="Statu quo",MAX('08_Moteur'!AI12,'08_Moteur'!M12),IF(L13="Ouvrir +1",'08_Moteur'!AI12+1,'08_Moteur'!AI12)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="51">
+        <f>IF(L13="Ne pas lancer",0,'08_Moteur'!AD12)</f>
+        <v/>
+      </c>
+      <c r="O13" s="17">
+        <f>N13*'08_Moteur'!AE12*'08_Moteur'!AF12+IF(L13="Ne pas lancer",0,'08_Moteur'!AB12)*'02_Leviers'!$D$16-M13*'08_Moteur'!U12-N13*'08_Moteur'!R12*(1+'02_Leviers'!$G$11)-IF(L13="Ne pas lancer",0,'08_Moteur'!AL12)</f>
+        <v/>
+      </c>
+      <c r="P13" s="55">
+        <f>O13-'08_Moteur'!AM12</f>
         <v/>
       </c>
     </row>
@@ -3022,29 +3183,41 @@
         <f>'08_Moteur'!M13</f>
         <v/>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="71">
         <f>'08_Moteur'!AN13</f>
         <v/>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="72">
+        <f>IF('08_Moteur'!AM13&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN13&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN13&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>IF('08_Moteur'!AM13&lt;0,-'08_Moteur'!AM13,IF('08_Moteur'!AN13&gt;=0.95,'08_Moteur'!O13*'08_Moteur'!AO13-'08_Moteur'!U13,0))</f>
+        <v/>
+      </c>
+      <c r="K14" s="29">
+        <f>IF('08_Moteur'!AM13&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN13&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN13&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J14" s="51">
-        <f>IF(I14="Ne pas lancer",0,IF(I14="Statu quo",MAX('08_Moteur'!AI13,'08_Moteur'!M13),IF(I14="Ouvrir +1",'08_Moteur'!AI13+1,'08_Moteur'!AI13)))</f>
-        <v/>
-      </c>
-      <c r="K14" s="51">
-        <f>IF(I14="Ne pas lancer",0,'08_Moteur'!AD13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="17">
-        <f>K14*'08_Moteur'!AE13*'08_Moteur'!AF13+IF(I14="Ne pas lancer",0,'08_Moteur'!AB13)*'02_Leviers'!$D$17-J14*'08_Moteur'!U13-K14*'08_Moteur'!R13*(1+'02_Leviers'!$G$11)-IF(I14="Ne pas lancer",0,'08_Moteur'!AL13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="55">
-        <f>L14-'08_Moteur'!AM13</f>
+      <c r="M14" s="51">
+        <f>IF(L14="Ne pas lancer",0,IF(L14="Statu quo",MAX('08_Moteur'!AI13,'08_Moteur'!M13),IF(L14="Ouvrir +1",'08_Moteur'!AI13+1,'08_Moteur'!AI13)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="51">
+        <f>IF(L14="Ne pas lancer",0,'08_Moteur'!AD13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="17">
+        <f>N14*'08_Moteur'!AE13*'08_Moteur'!AF13+IF(L14="Ne pas lancer",0,'08_Moteur'!AB13)*'02_Leviers'!$D$16-M14*'08_Moteur'!U13-N14*'08_Moteur'!R13*(1+'02_Leviers'!$G$11)-IF(L14="Ne pas lancer",0,'08_Moteur'!AL13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="55">
+        <f>O14-'08_Moteur'!AM13</f>
         <v/>
       </c>
     </row>
@@ -3077,29 +3250,41 @@
         <f>'08_Moteur'!M14</f>
         <v/>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="71">
         <f>'08_Moteur'!AN14</f>
         <v/>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="72">
+        <f>IF('08_Moteur'!AM14&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN14&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN14&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>IF('08_Moteur'!AM14&lt;0,-'08_Moteur'!AM14,IF('08_Moteur'!AN14&gt;=0.95,'08_Moteur'!O14*'08_Moteur'!AO14-'08_Moteur'!U14,0))</f>
+        <v/>
+      </c>
+      <c r="K15" s="29">
+        <f>IF('08_Moteur'!AM14&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN14&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN14&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J15" s="51">
-        <f>IF(I15="Ne pas lancer",0,IF(I15="Statu quo",MAX('08_Moteur'!AI14,'08_Moteur'!M14),IF(I15="Ouvrir +1",'08_Moteur'!AI14+1,'08_Moteur'!AI14)))</f>
-        <v/>
-      </c>
-      <c r="K15" s="51">
-        <f>IF(I15="Ne pas lancer",0,'08_Moteur'!AD14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="17">
-        <f>K15*'08_Moteur'!AE14*'08_Moteur'!AF14+IF(I15="Ne pas lancer",0,'08_Moteur'!AB14)*'02_Leviers'!$D$17-J15*'08_Moteur'!U14-K15*'08_Moteur'!R14*(1+'02_Leviers'!$G$11)-IF(I15="Ne pas lancer",0,'08_Moteur'!AL14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="55">
-        <f>L15-'08_Moteur'!AM14</f>
+      <c r="M15" s="51">
+        <f>IF(L15="Ne pas lancer",0,IF(L15="Statu quo",MAX('08_Moteur'!AI14,'08_Moteur'!M14),IF(L15="Ouvrir +1",'08_Moteur'!AI14+1,'08_Moteur'!AI14)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="51">
+        <f>IF(L15="Ne pas lancer",0,'08_Moteur'!AD14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="17">
+        <f>N15*'08_Moteur'!AE14*'08_Moteur'!AF14+IF(L15="Ne pas lancer",0,'08_Moteur'!AB14)*'02_Leviers'!$D$16-M15*'08_Moteur'!U14-N15*'08_Moteur'!R14*(1+'02_Leviers'!$G$11)-IF(L15="Ne pas lancer",0,'08_Moteur'!AL14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="55">
+        <f>O15-'08_Moteur'!AM14</f>
         <v/>
       </c>
     </row>
@@ -3132,29 +3317,41 @@
         <f>'08_Moteur'!M15</f>
         <v/>
       </c>
-      <c r="H16" s="69">
+      <c r="H16" s="71">
         <f>'08_Moteur'!AN15</f>
         <v/>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="72">
+        <f>IF('08_Moteur'!AM15&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN15&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN15&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>IF('08_Moteur'!AM15&lt;0,-'08_Moteur'!AM15,IF('08_Moteur'!AN15&gt;=0.95,'08_Moteur'!O15*'08_Moteur'!AO15-'08_Moteur'!U15,0))</f>
+        <v/>
+      </c>
+      <c r="K16" s="29">
+        <f>IF('08_Moteur'!AM15&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN15&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN15&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J16" s="51">
-        <f>IF(I16="Ne pas lancer",0,IF(I16="Statu quo",MAX('08_Moteur'!AI15,'08_Moteur'!M15),IF(I16="Ouvrir +1",'08_Moteur'!AI15+1,'08_Moteur'!AI15)))</f>
-        <v/>
-      </c>
-      <c r="K16" s="51">
-        <f>IF(I16="Ne pas lancer",0,'08_Moteur'!AD15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="17">
-        <f>K16*'08_Moteur'!AE15*'08_Moteur'!AF15+IF(I16="Ne pas lancer",0,'08_Moteur'!AB15)*'02_Leviers'!$D$17-J16*'08_Moteur'!U15-K16*'08_Moteur'!R15*(1+'02_Leviers'!$G$11)-IF(I16="Ne pas lancer",0,'08_Moteur'!AL15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="55">
-        <f>L16-'08_Moteur'!AM15</f>
+      <c r="M16" s="51">
+        <f>IF(L16="Ne pas lancer",0,IF(L16="Statu quo",MAX('08_Moteur'!AI15,'08_Moteur'!M15),IF(L16="Ouvrir +1",'08_Moteur'!AI15+1,'08_Moteur'!AI15)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="51">
+        <f>IF(L16="Ne pas lancer",0,'08_Moteur'!AD15)</f>
+        <v/>
+      </c>
+      <c r="O16" s="17">
+        <f>N16*'08_Moteur'!AE15*'08_Moteur'!AF15+IF(L16="Ne pas lancer",0,'08_Moteur'!AB15)*'02_Leviers'!$D$16-M16*'08_Moteur'!U15-N16*'08_Moteur'!R15*(1+'02_Leviers'!$G$11)-IF(L16="Ne pas lancer",0,'08_Moteur'!AL15)</f>
+        <v/>
+      </c>
+      <c r="P16" s="55">
+        <f>O16-'08_Moteur'!AM15</f>
         <v/>
       </c>
     </row>
@@ -3187,29 +3384,41 @@
         <f>'08_Moteur'!M16</f>
         <v/>
       </c>
-      <c r="H17" s="69">
+      <c r="H17" s="71">
         <f>'08_Moteur'!AN16</f>
         <v/>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="72">
+        <f>IF('08_Moteur'!AM16&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN16&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN16&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J17" s="17">
+        <f>IF('08_Moteur'!AM16&lt;0,-'08_Moteur'!AM16,IF('08_Moteur'!AN16&gt;=0.95,'08_Moteur'!O16*'08_Moteur'!AO16-'08_Moteur'!U16,0))</f>
+        <v/>
+      </c>
+      <c r="K17" s="29">
+        <f>IF('08_Moteur'!AM16&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN16&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN16&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J17" s="51">
-        <f>IF(I17="Ne pas lancer",0,IF(I17="Statu quo",MAX('08_Moteur'!AI16,'08_Moteur'!M16),IF(I17="Ouvrir +1",'08_Moteur'!AI16+1,'08_Moteur'!AI16)))</f>
-        <v/>
-      </c>
-      <c r="K17" s="51">
-        <f>IF(I17="Ne pas lancer",0,'08_Moteur'!AD16)</f>
-        <v/>
-      </c>
-      <c r="L17" s="17">
-        <f>K17*'08_Moteur'!AE16*'08_Moteur'!AF16+IF(I17="Ne pas lancer",0,'08_Moteur'!AB16)*'02_Leviers'!$D$17-J17*'08_Moteur'!U16-K17*'08_Moteur'!R16*(1+'02_Leviers'!$G$11)-IF(I17="Ne pas lancer",0,'08_Moteur'!AL16)</f>
-        <v/>
-      </c>
-      <c r="M17" s="55">
-        <f>L17-'08_Moteur'!AM16</f>
+      <c r="M17" s="51">
+        <f>IF(L17="Ne pas lancer",0,IF(L17="Statu quo",MAX('08_Moteur'!AI16,'08_Moteur'!M16),IF(L17="Ouvrir +1",'08_Moteur'!AI16+1,'08_Moteur'!AI16)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="51">
+        <f>IF(L17="Ne pas lancer",0,'08_Moteur'!AD16)</f>
+        <v/>
+      </c>
+      <c r="O17" s="17">
+        <f>N17*'08_Moteur'!AE16*'08_Moteur'!AF16+IF(L17="Ne pas lancer",0,'08_Moteur'!AB16)*'02_Leviers'!$D$16-M17*'08_Moteur'!U16-N17*'08_Moteur'!R16*(1+'02_Leviers'!$G$11)-IF(L17="Ne pas lancer",0,'08_Moteur'!AL16)</f>
+        <v/>
+      </c>
+      <c r="P17" s="55">
+        <f>O17-'08_Moteur'!AM16</f>
         <v/>
       </c>
     </row>
@@ -3242,29 +3451,41 @@
         <f>'08_Moteur'!M17</f>
         <v/>
       </c>
-      <c r="H18" s="69">
+      <c r="H18" s="71">
         <f>'08_Moteur'!AN17</f>
         <v/>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="72">
+        <f>IF('08_Moteur'!AM17&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN17&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN17&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>IF('08_Moteur'!AM17&lt;0,-'08_Moteur'!AM17,IF('08_Moteur'!AN17&gt;=0.95,'08_Moteur'!O17*'08_Moteur'!AO17-'08_Moteur'!U17,0))</f>
+        <v/>
+      </c>
+      <c r="K18" s="29">
+        <f>IF('08_Moteur'!AM17&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN17&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN17&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J18" s="51">
-        <f>IF(I18="Ne pas lancer",0,IF(I18="Statu quo",MAX('08_Moteur'!AI17,'08_Moteur'!M17),IF(I18="Ouvrir +1",'08_Moteur'!AI17+1,'08_Moteur'!AI17)))</f>
-        <v/>
-      </c>
-      <c r="K18" s="51">
-        <f>IF(I18="Ne pas lancer",0,'08_Moteur'!AD17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="17">
-        <f>K18*'08_Moteur'!AE17*'08_Moteur'!AF17+IF(I18="Ne pas lancer",0,'08_Moteur'!AB17)*'02_Leviers'!$D$17-J18*'08_Moteur'!U17-K18*'08_Moteur'!R17*(1+'02_Leviers'!$G$11)-IF(I18="Ne pas lancer",0,'08_Moteur'!AL17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="55">
-        <f>L18-'08_Moteur'!AM17</f>
+      <c r="M18" s="51">
+        <f>IF(L18="Ne pas lancer",0,IF(L18="Statu quo",MAX('08_Moteur'!AI17,'08_Moteur'!M17),IF(L18="Ouvrir +1",'08_Moteur'!AI17+1,'08_Moteur'!AI17)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="51">
+        <f>IF(L18="Ne pas lancer",0,'08_Moteur'!AD17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="17">
+        <f>N18*'08_Moteur'!AE17*'08_Moteur'!AF17+IF(L18="Ne pas lancer",0,'08_Moteur'!AB17)*'02_Leviers'!$D$16-M18*'08_Moteur'!U17-N18*'08_Moteur'!R17*(1+'02_Leviers'!$G$11)-IF(L18="Ne pas lancer",0,'08_Moteur'!AL17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="55">
+        <f>O18-'08_Moteur'!AM17</f>
         <v/>
       </c>
     </row>
@@ -3297,29 +3518,41 @@
         <f>'08_Moteur'!M18</f>
         <v/>
       </c>
-      <c r="H19" s="69">
+      <c r="H19" s="71">
         <f>'08_Moteur'!AN18</f>
         <v/>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="72">
+        <f>IF('08_Moteur'!AM18&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN18&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN18&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J19" s="17">
+        <f>IF('08_Moteur'!AM18&lt;0,-'08_Moteur'!AM18,IF('08_Moteur'!AN18&gt;=0.95,'08_Moteur'!O18*'08_Moteur'!AO18-'08_Moteur'!U18,0))</f>
+        <v/>
+      </c>
+      <c r="K19" s="29">
+        <f>IF('08_Moteur'!AM18&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN18&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN18&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J19" s="51">
-        <f>IF(I19="Ne pas lancer",0,IF(I19="Statu quo",MAX('08_Moteur'!AI18,'08_Moteur'!M18),IF(I19="Ouvrir +1",'08_Moteur'!AI18+1,'08_Moteur'!AI18)))</f>
-        <v/>
-      </c>
-      <c r="K19" s="51">
-        <f>IF(I19="Ne pas lancer",0,'08_Moteur'!AD18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="17">
-        <f>K19*'08_Moteur'!AE18*'08_Moteur'!AF18+IF(I19="Ne pas lancer",0,'08_Moteur'!AB18)*'02_Leviers'!$D$17-J19*'08_Moteur'!U18-K19*'08_Moteur'!R18*(1+'02_Leviers'!$G$11)-IF(I19="Ne pas lancer",0,'08_Moteur'!AL18)</f>
-        <v/>
-      </c>
-      <c r="M19" s="55">
-        <f>L19-'08_Moteur'!AM18</f>
+      <c r="M19" s="51">
+        <f>IF(L19="Ne pas lancer",0,IF(L19="Statu quo",MAX('08_Moteur'!AI18,'08_Moteur'!M18),IF(L19="Ouvrir +1",'08_Moteur'!AI18+1,'08_Moteur'!AI18)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="51">
+        <f>IF(L19="Ne pas lancer",0,'08_Moteur'!AD18)</f>
+        <v/>
+      </c>
+      <c r="O19" s="17">
+        <f>N19*'08_Moteur'!AE18*'08_Moteur'!AF18+IF(L19="Ne pas lancer",0,'08_Moteur'!AB18)*'02_Leviers'!$D$16-M19*'08_Moteur'!U18-N19*'08_Moteur'!R18*(1+'02_Leviers'!$G$11)-IF(L19="Ne pas lancer",0,'08_Moteur'!AL18)</f>
+        <v/>
+      </c>
+      <c r="P19" s="55">
+        <f>O19-'08_Moteur'!AM18</f>
         <v/>
       </c>
     </row>
@@ -3352,29 +3585,41 @@
         <f>'08_Moteur'!M19</f>
         <v/>
       </c>
-      <c r="H20" s="69">
+      <c r="H20" s="71">
         <f>'08_Moteur'!AN19</f>
         <v/>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="72">
+        <f>IF('08_Moteur'!AM19&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN19&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN19&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J20" s="17">
+        <f>IF('08_Moteur'!AM19&lt;0,-'08_Moteur'!AM19,IF('08_Moteur'!AN19&gt;=0.95,'08_Moteur'!O19*'08_Moteur'!AO19-'08_Moteur'!U19,0))</f>
+        <v/>
+      </c>
+      <c r="K20" s="29">
+        <f>IF('08_Moteur'!AM19&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN19&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN19&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J20" s="51">
-        <f>IF(I20="Ne pas lancer",0,IF(I20="Statu quo",MAX('08_Moteur'!AI19,'08_Moteur'!M19),IF(I20="Ouvrir +1",'08_Moteur'!AI19+1,'08_Moteur'!AI19)))</f>
-        <v/>
-      </c>
-      <c r="K20" s="51">
-        <f>IF(I20="Ne pas lancer",0,'08_Moteur'!AD19)</f>
-        <v/>
-      </c>
-      <c r="L20" s="17">
-        <f>K20*'08_Moteur'!AE19*'08_Moteur'!AF19+IF(I20="Ne pas lancer",0,'08_Moteur'!AB19)*'02_Leviers'!$D$17-J20*'08_Moteur'!U19-K20*'08_Moteur'!R19*(1+'02_Leviers'!$G$11)-IF(I20="Ne pas lancer",0,'08_Moteur'!AL19)</f>
-        <v/>
-      </c>
-      <c r="M20" s="55">
-        <f>L20-'08_Moteur'!AM19</f>
+      <c r="M20" s="51">
+        <f>IF(L20="Ne pas lancer",0,IF(L20="Statu quo",MAX('08_Moteur'!AI19,'08_Moteur'!M19),IF(L20="Ouvrir +1",'08_Moteur'!AI19+1,'08_Moteur'!AI19)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="51">
+        <f>IF(L20="Ne pas lancer",0,'08_Moteur'!AD19)</f>
+        <v/>
+      </c>
+      <c r="O20" s="17">
+        <f>N20*'08_Moteur'!AE19*'08_Moteur'!AF19+IF(L20="Ne pas lancer",0,'08_Moteur'!AB19)*'02_Leviers'!$D$16-M20*'08_Moteur'!U19-N20*'08_Moteur'!R19*(1+'02_Leviers'!$G$11)-IF(L20="Ne pas lancer",0,'08_Moteur'!AL19)</f>
+        <v/>
+      </c>
+      <c r="P20" s="55">
+        <f>O20-'08_Moteur'!AM19</f>
         <v/>
       </c>
     </row>
@@ -3407,29 +3652,41 @@
         <f>'08_Moteur'!M20</f>
         <v/>
       </c>
-      <c r="H21" s="69">
+      <c r="H21" s="71">
         <f>'08_Moteur'!AN20</f>
         <v/>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="72">
+        <f>IF('08_Moteur'!AM20&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN20&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN20&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J21" s="17">
+        <f>IF('08_Moteur'!AM20&lt;0,-'08_Moteur'!AM20,IF('08_Moteur'!AN20&gt;=0.95,'08_Moteur'!O20*'08_Moteur'!AO20-'08_Moteur'!U20,0))</f>
+        <v/>
+      </c>
+      <c r="K21" s="29">
+        <f>IF('08_Moteur'!AM20&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN20&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN20&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J21" s="51">
-        <f>IF(I21="Ne pas lancer",0,IF(I21="Statu quo",MAX('08_Moteur'!AI20,'08_Moteur'!M20),IF(I21="Ouvrir +1",'08_Moteur'!AI20+1,'08_Moteur'!AI20)))</f>
-        <v/>
-      </c>
-      <c r="K21" s="51">
-        <f>IF(I21="Ne pas lancer",0,'08_Moteur'!AD20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="17">
-        <f>K21*'08_Moteur'!AE20*'08_Moteur'!AF20+IF(I21="Ne pas lancer",0,'08_Moteur'!AB20)*'02_Leviers'!$D$17-J21*'08_Moteur'!U20-K21*'08_Moteur'!R20*(1+'02_Leviers'!$G$11)-IF(I21="Ne pas lancer",0,'08_Moteur'!AL20)</f>
-        <v/>
-      </c>
-      <c r="M21" s="55">
-        <f>L21-'08_Moteur'!AM20</f>
+      <c r="M21" s="51">
+        <f>IF(L21="Ne pas lancer",0,IF(L21="Statu quo",MAX('08_Moteur'!AI20,'08_Moteur'!M20),IF(L21="Ouvrir +1",'08_Moteur'!AI20+1,'08_Moteur'!AI20)))</f>
+        <v/>
+      </c>
+      <c r="N21" s="51">
+        <f>IF(L21="Ne pas lancer",0,'08_Moteur'!AD20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="17">
+        <f>N21*'08_Moteur'!AE20*'08_Moteur'!AF20+IF(L21="Ne pas lancer",0,'08_Moteur'!AB20)*'02_Leviers'!$D$16-M21*'08_Moteur'!U20-N21*'08_Moteur'!R20*(1+'02_Leviers'!$G$11)-IF(L21="Ne pas lancer",0,'08_Moteur'!AL20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="55">
+        <f>O21-'08_Moteur'!AM20</f>
         <v/>
       </c>
     </row>
@@ -3462,29 +3719,41 @@
         <f>'08_Moteur'!M21</f>
         <v/>
       </c>
-      <c r="H22" s="69">
+      <c r="H22" s="71">
         <f>'08_Moteur'!AN21</f>
         <v/>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="72">
+        <f>IF('08_Moteur'!AM21&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN21&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN21&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>IF('08_Moteur'!AM21&lt;0,-'08_Moteur'!AM21,IF('08_Moteur'!AN21&gt;=0.95,'08_Moteur'!O21*'08_Moteur'!AO21-'08_Moteur'!U21,0))</f>
+        <v/>
+      </c>
+      <c r="K22" s="29">
+        <f>IF('08_Moteur'!AM21&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN21&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN21&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J22" s="51">
-        <f>IF(I22="Ne pas lancer",0,IF(I22="Statu quo",MAX('08_Moteur'!AI21,'08_Moteur'!M21),IF(I22="Ouvrir +1",'08_Moteur'!AI21+1,'08_Moteur'!AI21)))</f>
-        <v/>
-      </c>
-      <c r="K22" s="51">
-        <f>IF(I22="Ne pas lancer",0,'08_Moteur'!AD21)</f>
-        <v/>
-      </c>
-      <c r="L22" s="17">
-        <f>K22*'08_Moteur'!AE21*'08_Moteur'!AF21+IF(I22="Ne pas lancer",0,'08_Moteur'!AB21)*'02_Leviers'!$D$17-J22*'08_Moteur'!U21-K22*'08_Moteur'!R21*(1+'02_Leviers'!$G$11)-IF(I22="Ne pas lancer",0,'08_Moteur'!AL21)</f>
-        <v/>
-      </c>
-      <c r="M22" s="55">
-        <f>L22-'08_Moteur'!AM21</f>
+      <c r="M22" s="51">
+        <f>IF(L22="Ne pas lancer",0,IF(L22="Statu quo",MAX('08_Moteur'!AI21,'08_Moteur'!M21),IF(L22="Ouvrir +1",'08_Moteur'!AI21+1,'08_Moteur'!AI21)))</f>
+        <v/>
+      </c>
+      <c r="N22" s="51">
+        <f>IF(L22="Ne pas lancer",0,'08_Moteur'!AD21)</f>
+        <v/>
+      </c>
+      <c r="O22" s="17">
+        <f>N22*'08_Moteur'!AE21*'08_Moteur'!AF21+IF(L22="Ne pas lancer",0,'08_Moteur'!AB21)*'02_Leviers'!$D$16-M22*'08_Moteur'!U21-N22*'08_Moteur'!R21*(1+'02_Leviers'!$G$11)-IF(L22="Ne pas lancer",0,'08_Moteur'!AL21)</f>
+        <v/>
+      </c>
+      <c r="P22" s="55">
+        <f>O22-'08_Moteur'!AM21</f>
         <v/>
       </c>
     </row>
@@ -3517,29 +3786,41 @@
         <f>'08_Moteur'!M22</f>
         <v/>
       </c>
-      <c r="H23" s="69">
+      <c r="H23" s="71">
         <f>'08_Moteur'!AN22</f>
         <v/>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="72">
+        <f>IF('08_Moteur'!AM22&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN22&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN22&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J23" s="17">
+        <f>IF('08_Moteur'!AM22&lt;0,-'08_Moteur'!AM22,IF('08_Moteur'!AN22&gt;=0.95,'08_Moteur'!O22*'08_Moteur'!AO22-'08_Moteur'!U22,0))</f>
+        <v/>
+      </c>
+      <c r="K23" s="29">
+        <f>IF('08_Moteur'!AM22&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN22&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN22&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J23" s="51">
-        <f>IF(I23="Ne pas lancer",0,IF(I23="Statu quo",MAX('08_Moteur'!AI22,'08_Moteur'!M22),IF(I23="Ouvrir +1",'08_Moteur'!AI22+1,'08_Moteur'!AI22)))</f>
-        <v/>
-      </c>
-      <c r="K23" s="51">
-        <f>IF(I23="Ne pas lancer",0,'08_Moteur'!AD22)</f>
-        <v/>
-      </c>
-      <c r="L23" s="17">
-        <f>K23*'08_Moteur'!AE22*'08_Moteur'!AF22+IF(I23="Ne pas lancer",0,'08_Moteur'!AB22)*'02_Leviers'!$D$17-J23*'08_Moteur'!U22-K23*'08_Moteur'!R22*(1+'02_Leviers'!$G$11)-IF(I23="Ne pas lancer",0,'08_Moteur'!AL22)</f>
-        <v/>
-      </c>
-      <c r="M23" s="55">
-        <f>L23-'08_Moteur'!AM22</f>
+      <c r="M23" s="51">
+        <f>IF(L23="Ne pas lancer",0,IF(L23="Statu quo",MAX('08_Moteur'!AI22,'08_Moteur'!M22),IF(L23="Ouvrir +1",'08_Moteur'!AI22+1,'08_Moteur'!AI22)))</f>
+        <v/>
+      </c>
+      <c r="N23" s="51">
+        <f>IF(L23="Ne pas lancer",0,'08_Moteur'!AD22)</f>
+        <v/>
+      </c>
+      <c r="O23" s="17">
+        <f>N23*'08_Moteur'!AE22*'08_Moteur'!AF22+IF(L23="Ne pas lancer",0,'08_Moteur'!AB22)*'02_Leviers'!$D$16-M23*'08_Moteur'!U22-N23*'08_Moteur'!R22*(1+'02_Leviers'!$G$11)-IF(L23="Ne pas lancer",0,'08_Moteur'!AL22)</f>
+        <v/>
+      </c>
+      <c r="P23" s="55">
+        <f>O23-'08_Moteur'!AM22</f>
         <v/>
       </c>
     </row>
@@ -3572,29 +3853,41 @@
         <f>'08_Moteur'!M23</f>
         <v/>
       </c>
-      <c r="H24" s="69">
+      <c r="H24" s="71">
         <f>'08_Moteur'!AN23</f>
         <v/>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="72">
+        <f>IF('08_Moteur'!AM23&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN23&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN23&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J24" s="17">
+        <f>IF('08_Moteur'!AM23&lt;0,-'08_Moteur'!AM23,IF('08_Moteur'!AN23&gt;=0.95,'08_Moteur'!O23*'08_Moteur'!AO23-'08_Moteur'!U23,0))</f>
+        <v/>
+      </c>
+      <c r="K24" s="29">
+        <f>IF('08_Moteur'!AM23&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN23&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN23&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J24" s="51">
-        <f>IF(I24="Ne pas lancer",0,IF(I24="Statu quo",MAX('08_Moteur'!AI23,'08_Moteur'!M23),IF(I24="Ouvrir +1",'08_Moteur'!AI23+1,'08_Moteur'!AI23)))</f>
-        <v/>
-      </c>
-      <c r="K24" s="51">
-        <f>IF(I24="Ne pas lancer",0,'08_Moteur'!AD23)</f>
-        <v/>
-      </c>
-      <c r="L24" s="17">
-        <f>K24*'08_Moteur'!AE23*'08_Moteur'!AF23+IF(I24="Ne pas lancer",0,'08_Moteur'!AB23)*'02_Leviers'!$D$17-J24*'08_Moteur'!U23-K24*'08_Moteur'!R23*(1+'02_Leviers'!$G$11)-IF(I24="Ne pas lancer",0,'08_Moteur'!AL23)</f>
-        <v/>
-      </c>
-      <c r="M24" s="55">
-        <f>L24-'08_Moteur'!AM23</f>
+      <c r="M24" s="51">
+        <f>IF(L24="Ne pas lancer",0,IF(L24="Statu quo",MAX('08_Moteur'!AI23,'08_Moteur'!M23),IF(L24="Ouvrir +1",'08_Moteur'!AI23+1,'08_Moteur'!AI23)))</f>
+        <v/>
+      </c>
+      <c r="N24" s="51">
+        <f>IF(L24="Ne pas lancer",0,'08_Moteur'!AD23)</f>
+        <v/>
+      </c>
+      <c r="O24" s="17">
+        <f>N24*'08_Moteur'!AE23*'08_Moteur'!AF23+IF(L24="Ne pas lancer",0,'08_Moteur'!AB23)*'02_Leviers'!$D$16-M24*'08_Moteur'!U23-N24*'08_Moteur'!R23*(1+'02_Leviers'!$G$11)-IF(L24="Ne pas lancer",0,'08_Moteur'!AL23)</f>
+        <v/>
+      </c>
+      <c r="P24" s="55">
+        <f>O24-'08_Moteur'!AM23</f>
         <v/>
       </c>
     </row>
@@ -3627,29 +3920,41 @@
         <f>'08_Moteur'!M24</f>
         <v/>
       </c>
-      <c r="H25" s="69">
+      <c r="H25" s="71">
         <f>'08_Moteur'!AN24</f>
         <v/>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="72">
+        <f>IF('08_Moteur'!AM24&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN24&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN24&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>IF('08_Moteur'!AM24&lt;0,-'08_Moteur'!AM24,IF('08_Moteur'!AN24&gt;=0.95,'08_Moteur'!O24*'08_Moteur'!AO24-'08_Moteur'!U24,0))</f>
+        <v/>
+      </c>
+      <c r="K25" s="29">
+        <f>IF('08_Moteur'!AM24&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN24&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN24&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J25" s="51">
-        <f>IF(I25="Ne pas lancer",0,IF(I25="Statu quo",MAX('08_Moteur'!AI24,'08_Moteur'!M24),IF(I25="Ouvrir +1",'08_Moteur'!AI24+1,'08_Moteur'!AI24)))</f>
-        <v/>
-      </c>
-      <c r="K25" s="51">
-        <f>IF(I25="Ne pas lancer",0,'08_Moteur'!AD24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="17">
-        <f>K25*'08_Moteur'!AE24*'08_Moteur'!AF24+IF(I25="Ne pas lancer",0,'08_Moteur'!AB24)*'02_Leviers'!$D$17-J25*'08_Moteur'!U24-K25*'08_Moteur'!R24*(1+'02_Leviers'!$G$11)-IF(I25="Ne pas lancer",0,'08_Moteur'!AL24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="55">
-        <f>L25-'08_Moteur'!AM24</f>
+      <c r="M25" s="51">
+        <f>IF(L25="Ne pas lancer",0,IF(L25="Statu quo",MAX('08_Moteur'!AI24,'08_Moteur'!M24),IF(L25="Ouvrir +1",'08_Moteur'!AI24+1,'08_Moteur'!AI24)))</f>
+        <v/>
+      </c>
+      <c r="N25" s="51">
+        <f>IF(L25="Ne pas lancer",0,'08_Moteur'!AD24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="17">
+        <f>N25*'08_Moteur'!AE24*'08_Moteur'!AF24+IF(L25="Ne pas lancer",0,'08_Moteur'!AB24)*'02_Leviers'!$D$16-M25*'08_Moteur'!U24-N25*'08_Moteur'!R24*(1+'02_Leviers'!$G$11)-IF(L25="Ne pas lancer",0,'08_Moteur'!AL24)</f>
+        <v/>
+      </c>
+      <c r="P25" s="55">
+        <f>O25-'08_Moteur'!AM24</f>
         <v/>
       </c>
     </row>
@@ -3682,29 +3987,41 @@
         <f>'08_Moteur'!M25</f>
         <v/>
       </c>
-      <c r="H26" s="69">
+      <c r="H26" s="71">
         <f>'08_Moteur'!AN25</f>
         <v/>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="72">
+        <f>IF('08_Moteur'!AM25&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN25&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN25&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J26" s="17">
+        <f>IF('08_Moteur'!AM25&lt;0,-'08_Moteur'!AM25,IF('08_Moteur'!AN25&gt;=0.95,'08_Moteur'!O25*'08_Moteur'!AO25-'08_Moteur'!U25,0))</f>
+        <v/>
+      </c>
+      <c r="K26" s="29">
+        <f>IF('08_Moteur'!AM25&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN25&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN25&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J26" s="51">
-        <f>IF(I26="Ne pas lancer",0,IF(I26="Statu quo",MAX('08_Moteur'!AI25,'08_Moteur'!M25),IF(I26="Ouvrir +1",'08_Moteur'!AI25+1,'08_Moteur'!AI25)))</f>
-        <v/>
-      </c>
-      <c r="K26" s="51">
-        <f>IF(I26="Ne pas lancer",0,'08_Moteur'!AD25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="17">
-        <f>K26*'08_Moteur'!AE25*'08_Moteur'!AF25+IF(I26="Ne pas lancer",0,'08_Moteur'!AB25)*'02_Leviers'!$D$17-J26*'08_Moteur'!U25-K26*'08_Moteur'!R25*(1+'02_Leviers'!$G$11)-IF(I26="Ne pas lancer",0,'08_Moteur'!AL25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="55">
-        <f>L26-'08_Moteur'!AM25</f>
+      <c r="M26" s="51">
+        <f>IF(L26="Ne pas lancer",0,IF(L26="Statu quo",MAX('08_Moteur'!AI25,'08_Moteur'!M25),IF(L26="Ouvrir +1",'08_Moteur'!AI25+1,'08_Moteur'!AI25)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="51">
+        <f>IF(L26="Ne pas lancer",0,'08_Moteur'!AD25)</f>
+        <v/>
+      </c>
+      <c r="O26" s="17">
+        <f>N26*'08_Moteur'!AE25*'08_Moteur'!AF25+IF(L26="Ne pas lancer",0,'08_Moteur'!AB25)*'02_Leviers'!$D$16-M26*'08_Moteur'!U25-N26*'08_Moteur'!R25*(1+'02_Leviers'!$G$11)-IF(L26="Ne pas lancer",0,'08_Moteur'!AL25)</f>
+        <v/>
+      </c>
+      <c r="P26" s="55">
+        <f>O26-'08_Moteur'!AM25</f>
         <v/>
       </c>
     </row>
@@ -3737,29 +4054,41 @@
         <f>'08_Moteur'!M26</f>
         <v/>
       </c>
-      <c r="H27" s="69">
+      <c r="H27" s="71">
         <f>'08_Moteur'!AN26</f>
         <v/>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="72">
+        <f>IF('08_Moteur'!AM26&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN26&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN26&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J27" s="17">
+        <f>IF('08_Moteur'!AM26&lt;0,-'08_Moteur'!AM26,IF('08_Moteur'!AN26&gt;=0.95,'08_Moteur'!O26*'08_Moteur'!AO26-'08_Moteur'!U26,0))</f>
+        <v/>
+      </c>
+      <c r="K27" s="29">
+        <f>IF('08_Moteur'!AM26&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN26&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN26&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J27" s="51">
-        <f>IF(I27="Ne pas lancer",0,IF(I27="Statu quo",MAX('08_Moteur'!AI26,'08_Moteur'!M26),IF(I27="Ouvrir +1",'08_Moteur'!AI26+1,'08_Moteur'!AI26)))</f>
-        <v/>
-      </c>
-      <c r="K27" s="51">
-        <f>IF(I27="Ne pas lancer",0,'08_Moteur'!AD26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="17">
-        <f>K27*'08_Moteur'!AE26*'08_Moteur'!AF26+IF(I27="Ne pas lancer",0,'08_Moteur'!AB26)*'02_Leviers'!$D$17-J27*'08_Moteur'!U26-K27*'08_Moteur'!R26*(1+'02_Leviers'!$G$11)-IF(I27="Ne pas lancer",0,'08_Moteur'!AL26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="55">
-        <f>L27-'08_Moteur'!AM26</f>
+      <c r="M27" s="51">
+        <f>IF(L27="Ne pas lancer",0,IF(L27="Statu quo",MAX('08_Moteur'!AI26,'08_Moteur'!M26),IF(L27="Ouvrir +1",'08_Moteur'!AI26+1,'08_Moteur'!AI26)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="51">
+        <f>IF(L27="Ne pas lancer",0,'08_Moteur'!AD26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="17">
+        <f>N27*'08_Moteur'!AE26*'08_Moteur'!AF26+IF(L27="Ne pas lancer",0,'08_Moteur'!AB26)*'02_Leviers'!$D$16-M27*'08_Moteur'!U26-N27*'08_Moteur'!R26*(1+'02_Leviers'!$G$11)-IF(L27="Ne pas lancer",0,'08_Moteur'!AL26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="55">
+        <f>O27-'08_Moteur'!AM26</f>
         <v/>
       </c>
     </row>
@@ -3792,29 +4121,41 @@
         <f>'08_Moteur'!M27</f>
         <v/>
       </c>
-      <c r="H28" s="69">
+      <c r="H28" s="71">
         <f>'08_Moteur'!AN27</f>
         <v/>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="72">
+        <f>IF('08_Moteur'!AM27&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN27&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN27&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>IF('08_Moteur'!AM27&lt;0,-'08_Moteur'!AM27,IF('08_Moteur'!AN27&gt;=0.95,'08_Moteur'!O27*'08_Moteur'!AO27-'08_Moteur'!U27,0))</f>
+        <v/>
+      </c>
+      <c r="K28" s="29">
+        <f>IF('08_Moteur'!AM27&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN27&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN27&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J28" s="51">
-        <f>IF(I28="Ne pas lancer",0,IF(I28="Statu quo",MAX('08_Moteur'!AI27,'08_Moteur'!M27),IF(I28="Ouvrir +1",'08_Moteur'!AI27+1,'08_Moteur'!AI27)))</f>
-        <v/>
-      </c>
-      <c r="K28" s="51">
-        <f>IF(I28="Ne pas lancer",0,'08_Moteur'!AD27)</f>
-        <v/>
-      </c>
-      <c r="L28" s="17">
-        <f>K28*'08_Moteur'!AE27*'08_Moteur'!AF27+IF(I28="Ne pas lancer",0,'08_Moteur'!AB27)*'02_Leviers'!$D$17-J28*'08_Moteur'!U27-K28*'08_Moteur'!R27*(1+'02_Leviers'!$G$11)-IF(I28="Ne pas lancer",0,'08_Moteur'!AL27)</f>
-        <v/>
-      </c>
-      <c r="M28" s="55">
-        <f>L28-'08_Moteur'!AM27</f>
+      <c r="M28" s="51">
+        <f>IF(L28="Ne pas lancer",0,IF(L28="Statu quo",MAX('08_Moteur'!AI27,'08_Moteur'!M27),IF(L28="Ouvrir +1",'08_Moteur'!AI27+1,'08_Moteur'!AI27)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="51">
+        <f>IF(L28="Ne pas lancer",0,'08_Moteur'!AD27)</f>
+        <v/>
+      </c>
+      <c r="O28" s="17">
+        <f>N28*'08_Moteur'!AE27*'08_Moteur'!AF27+IF(L28="Ne pas lancer",0,'08_Moteur'!AB27)*'02_Leviers'!$D$16-M28*'08_Moteur'!U27-N28*'08_Moteur'!R27*(1+'02_Leviers'!$G$11)-IF(L28="Ne pas lancer",0,'08_Moteur'!AL27)</f>
+        <v/>
+      </c>
+      <c r="P28" s="55">
+        <f>O28-'08_Moteur'!AM27</f>
         <v/>
       </c>
     </row>
@@ -3847,29 +4188,41 @@
         <f>'08_Moteur'!M28</f>
         <v/>
       </c>
-      <c r="H29" s="69">
+      <c r="H29" s="71">
         <f>'08_Moteur'!AN28</f>
         <v/>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="72">
+        <f>IF('08_Moteur'!AM28&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN28&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN28&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>IF('08_Moteur'!AM28&lt;0,-'08_Moteur'!AM28,IF('08_Moteur'!AN28&gt;=0.95,'08_Moteur'!O28*'08_Moteur'!AO28-'08_Moteur'!U28,0))</f>
+        <v/>
+      </c>
+      <c r="K29" s="29">
+        <f>IF('08_Moteur'!AM28&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN28&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN28&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J29" s="51">
-        <f>IF(I29="Ne pas lancer",0,IF(I29="Statu quo",MAX('08_Moteur'!AI28,'08_Moteur'!M28),IF(I29="Ouvrir +1",'08_Moteur'!AI28+1,'08_Moteur'!AI28)))</f>
-        <v/>
-      </c>
-      <c r="K29" s="51">
-        <f>IF(I29="Ne pas lancer",0,'08_Moteur'!AD28)</f>
-        <v/>
-      </c>
-      <c r="L29" s="17">
-        <f>K29*'08_Moteur'!AE28*'08_Moteur'!AF28+IF(I29="Ne pas lancer",0,'08_Moteur'!AB28)*'02_Leviers'!$D$17-J29*'08_Moteur'!U28-K29*'08_Moteur'!R28*(1+'02_Leviers'!$G$11)-IF(I29="Ne pas lancer",0,'08_Moteur'!AL28)</f>
-        <v/>
-      </c>
-      <c r="M29" s="55">
-        <f>L29-'08_Moteur'!AM28</f>
+      <c r="M29" s="51">
+        <f>IF(L29="Ne pas lancer",0,IF(L29="Statu quo",MAX('08_Moteur'!AI28,'08_Moteur'!M28),IF(L29="Ouvrir +1",'08_Moteur'!AI28+1,'08_Moteur'!AI28)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="51">
+        <f>IF(L29="Ne pas lancer",0,'08_Moteur'!AD28)</f>
+        <v/>
+      </c>
+      <c r="O29" s="17">
+        <f>N29*'08_Moteur'!AE28*'08_Moteur'!AF28+IF(L29="Ne pas lancer",0,'08_Moteur'!AB28)*'02_Leviers'!$D$16-M29*'08_Moteur'!U28-N29*'08_Moteur'!R28*(1+'02_Leviers'!$G$11)-IF(L29="Ne pas lancer",0,'08_Moteur'!AL28)</f>
+        <v/>
+      </c>
+      <c r="P29" s="55">
+        <f>O29-'08_Moteur'!AM28</f>
         <v/>
       </c>
     </row>
@@ -3902,29 +4255,41 @@
         <f>'08_Moteur'!M29</f>
         <v/>
       </c>
-      <c r="H30" s="69">
+      <c r="H30" s="71">
         <f>'08_Moteur'!AN29</f>
         <v/>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="72">
+        <f>IF('08_Moteur'!AM29&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN29&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN29&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J30" s="17">
+        <f>IF('08_Moteur'!AM29&lt;0,-'08_Moteur'!AM29,IF('08_Moteur'!AN29&gt;=0.95,'08_Moteur'!O29*'08_Moteur'!AO29-'08_Moteur'!U29,0))</f>
+        <v/>
+      </c>
+      <c r="K30" s="29">
+        <f>IF('08_Moteur'!AM29&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN29&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN29&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J30" s="51">
-        <f>IF(I30="Ne pas lancer",0,IF(I30="Statu quo",MAX('08_Moteur'!AI29,'08_Moteur'!M29),IF(I30="Ouvrir +1",'08_Moteur'!AI29+1,'08_Moteur'!AI29)))</f>
-        <v/>
-      </c>
-      <c r="K30" s="51">
-        <f>IF(I30="Ne pas lancer",0,'08_Moteur'!AD29)</f>
-        <v/>
-      </c>
-      <c r="L30" s="17">
-        <f>K30*'08_Moteur'!AE29*'08_Moteur'!AF29+IF(I30="Ne pas lancer",0,'08_Moteur'!AB29)*'02_Leviers'!$D$17-J30*'08_Moteur'!U29-K30*'08_Moteur'!R29*(1+'02_Leviers'!$G$11)-IF(I30="Ne pas lancer",0,'08_Moteur'!AL29)</f>
-        <v/>
-      </c>
-      <c r="M30" s="55">
-        <f>L30-'08_Moteur'!AM29</f>
+      <c r="M30" s="51">
+        <f>IF(L30="Ne pas lancer",0,IF(L30="Statu quo",MAX('08_Moteur'!AI29,'08_Moteur'!M29),IF(L30="Ouvrir +1",'08_Moteur'!AI29+1,'08_Moteur'!AI29)))</f>
+        <v/>
+      </c>
+      <c r="N30" s="51">
+        <f>IF(L30="Ne pas lancer",0,'08_Moteur'!AD29)</f>
+        <v/>
+      </c>
+      <c r="O30" s="17">
+        <f>N30*'08_Moteur'!AE29*'08_Moteur'!AF29+IF(L30="Ne pas lancer",0,'08_Moteur'!AB29)*'02_Leviers'!$D$16-M30*'08_Moteur'!U29-N30*'08_Moteur'!R29*(1+'02_Leviers'!$G$11)-IF(L30="Ne pas lancer",0,'08_Moteur'!AL29)</f>
+        <v/>
+      </c>
+      <c r="P30" s="55">
+        <f>O30-'08_Moteur'!AM29</f>
         <v/>
       </c>
     </row>
@@ -3957,29 +4322,41 @@
         <f>'08_Moteur'!M30</f>
         <v/>
       </c>
-      <c r="H31" s="69">
+      <c r="H31" s="71">
         <f>'08_Moteur'!AN30</f>
         <v/>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="72">
+        <f>IF('08_Moteur'!AM30&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN30&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN30&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>IF('08_Moteur'!AM30&lt;0,-'08_Moteur'!AM30,IF('08_Moteur'!AN30&gt;=0.95,'08_Moteur'!O30*'08_Moteur'!AO30-'08_Moteur'!U30,0))</f>
+        <v/>
+      </c>
+      <c r="K31" s="29">
+        <f>IF('08_Moteur'!AM30&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN30&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN30&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J31" s="51">
-        <f>IF(I31="Ne pas lancer",0,IF(I31="Statu quo",MAX('08_Moteur'!AI30,'08_Moteur'!M30),IF(I31="Ouvrir +1",'08_Moteur'!AI30+1,'08_Moteur'!AI30)))</f>
-        <v/>
-      </c>
-      <c r="K31" s="51">
-        <f>IF(I31="Ne pas lancer",0,'08_Moteur'!AD30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="17">
-        <f>K31*'08_Moteur'!AE30*'08_Moteur'!AF30+IF(I31="Ne pas lancer",0,'08_Moteur'!AB30)*'02_Leviers'!$D$17-J31*'08_Moteur'!U30-K31*'08_Moteur'!R30*(1+'02_Leviers'!$G$11)-IF(I31="Ne pas lancer",0,'08_Moteur'!AL30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="55">
-        <f>L31-'08_Moteur'!AM30</f>
+      <c r="M31" s="51">
+        <f>IF(L31="Ne pas lancer",0,IF(L31="Statu quo",MAX('08_Moteur'!AI30,'08_Moteur'!M30),IF(L31="Ouvrir +1",'08_Moteur'!AI30+1,'08_Moteur'!AI30)))</f>
+        <v/>
+      </c>
+      <c r="N31" s="51">
+        <f>IF(L31="Ne pas lancer",0,'08_Moteur'!AD30)</f>
+        <v/>
+      </c>
+      <c r="O31" s="17">
+        <f>N31*'08_Moteur'!AE30*'08_Moteur'!AF30+IF(L31="Ne pas lancer",0,'08_Moteur'!AB30)*'02_Leviers'!$D$16-M31*'08_Moteur'!U30-N31*'08_Moteur'!R30*(1+'02_Leviers'!$G$11)-IF(L31="Ne pas lancer",0,'08_Moteur'!AL30)</f>
+        <v/>
+      </c>
+      <c r="P31" s="55">
+        <f>O31-'08_Moteur'!AM30</f>
         <v/>
       </c>
     </row>
@@ -4012,29 +4389,41 @@
         <f>'08_Moteur'!M31</f>
         <v/>
       </c>
-      <c r="H32" s="69">
+      <c r="H32" s="71">
         <f>'08_Moteur'!AN31</f>
         <v/>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="72">
+        <f>IF('08_Moteur'!AM31&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN31&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN31&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J32" s="17">
+        <f>IF('08_Moteur'!AM31&lt;0,-'08_Moteur'!AM31,IF('08_Moteur'!AN31&gt;=0.95,'08_Moteur'!O31*'08_Moteur'!AO31-'08_Moteur'!U31,0))</f>
+        <v/>
+      </c>
+      <c r="K32" s="29">
+        <f>IF('08_Moteur'!AM31&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN31&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN31&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J32" s="51">
-        <f>IF(I32="Ne pas lancer",0,IF(I32="Statu quo",MAX('08_Moteur'!AI31,'08_Moteur'!M31),IF(I32="Ouvrir +1",'08_Moteur'!AI31+1,'08_Moteur'!AI31)))</f>
-        <v/>
-      </c>
-      <c r="K32" s="51">
-        <f>IF(I32="Ne pas lancer",0,'08_Moteur'!AD31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="17">
-        <f>K32*'08_Moteur'!AE31*'08_Moteur'!AF31+IF(I32="Ne pas lancer",0,'08_Moteur'!AB31)*'02_Leviers'!$D$17-J32*'08_Moteur'!U31-K32*'08_Moteur'!R31*(1+'02_Leviers'!$G$11)-IF(I32="Ne pas lancer",0,'08_Moteur'!AL31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="55">
-        <f>L32-'08_Moteur'!AM31</f>
+      <c r="M32" s="51">
+        <f>IF(L32="Ne pas lancer",0,IF(L32="Statu quo",MAX('08_Moteur'!AI31,'08_Moteur'!M31),IF(L32="Ouvrir +1",'08_Moteur'!AI31+1,'08_Moteur'!AI31)))</f>
+        <v/>
+      </c>
+      <c r="N32" s="51">
+        <f>IF(L32="Ne pas lancer",0,'08_Moteur'!AD31)</f>
+        <v/>
+      </c>
+      <c r="O32" s="17">
+        <f>N32*'08_Moteur'!AE31*'08_Moteur'!AF31+IF(L32="Ne pas lancer",0,'08_Moteur'!AB31)*'02_Leviers'!$D$16-M32*'08_Moteur'!U31-N32*'08_Moteur'!R31*(1+'02_Leviers'!$G$11)-IF(L32="Ne pas lancer",0,'08_Moteur'!AL31)</f>
+        <v/>
+      </c>
+      <c r="P32" s="55">
+        <f>O32-'08_Moteur'!AM31</f>
         <v/>
       </c>
     </row>
@@ -4067,29 +4456,41 @@
         <f>'08_Moteur'!M32</f>
         <v/>
       </c>
-      <c r="H33" s="69">
+      <c r="H33" s="71">
         <f>'08_Moteur'!AN32</f>
         <v/>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="72">
+        <f>IF('08_Moteur'!AM32&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN32&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN32&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J33" s="17">
+        <f>IF('08_Moteur'!AM32&lt;0,-'08_Moteur'!AM32,IF('08_Moteur'!AN32&gt;=0.95,'08_Moteur'!O32*'08_Moteur'!AO32-'08_Moteur'!U32,0))</f>
+        <v/>
+      </c>
+      <c r="K33" s="29">
+        <f>IF('08_Moteur'!AM32&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN32&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN32&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J33" s="51">
-        <f>IF(I33="Ne pas lancer",0,IF(I33="Statu quo",MAX('08_Moteur'!AI32,'08_Moteur'!M32),IF(I33="Ouvrir +1",'08_Moteur'!AI32+1,'08_Moteur'!AI32)))</f>
-        <v/>
-      </c>
-      <c r="K33" s="51">
-        <f>IF(I33="Ne pas lancer",0,'08_Moteur'!AD32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="17">
-        <f>K33*'08_Moteur'!AE32*'08_Moteur'!AF32+IF(I33="Ne pas lancer",0,'08_Moteur'!AB32)*'02_Leviers'!$D$17-J33*'08_Moteur'!U32-K33*'08_Moteur'!R32*(1+'02_Leviers'!$G$11)-IF(I33="Ne pas lancer",0,'08_Moteur'!AL32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="55">
-        <f>L33-'08_Moteur'!AM32</f>
+      <c r="M33" s="51">
+        <f>IF(L33="Ne pas lancer",0,IF(L33="Statu quo",MAX('08_Moteur'!AI32,'08_Moteur'!M32),IF(L33="Ouvrir +1",'08_Moteur'!AI32+1,'08_Moteur'!AI32)))</f>
+        <v/>
+      </c>
+      <c r="N33" s="51">
+        <f>IF(L33="Ne pas lancer",0,'08_Moteur'!AD32)</f>
+        <v/>
+      </c>
+      <c r="O33" s="17">
+        <f>N33*'08_Moteur'!AE32*'08_Moteur'!AF32+IF(L33="Ne pas lancer",0,'08_Moteur'!AB32)*'02_Leviers'!$D$16-M33*'08_Moteur'!U32-N33*'08_Moteur'!R32*(1+'02_Leviers'!$G$11)-IF(L33="Ne pas lancer",0,'08_Moteur'!AL32)</f>
+        <v/>
+      </c>
+      <c r="P33" s="55">
+        <f>O33-'08_Moteur'!AM32</f>
         <v/>
       </c>
     </row>
@@ -4122,29 +4523,41 @@
         <f>'08_Moteur'!M33</f>
         <v/>
       </c>
-      <c r="H34" s="69">
+      <c r="H34" s="71">
         <f>'08_Moteur'!AN33</f>
         <v/>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="72">
+        <f>IF('08_Moteur'!AM33&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN33&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN33&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J34" s="17">
+        <f>IF('08_Moteur'!AM33&lt;0,-'08_Moteur'!AM33,IF('08_Moteur'!AN33&gt;=0.95,'08_Moteur'!O33*'08_Moteur'!AO33-'08_Moteur'!U33,0))</f>
+        <v/>
+      </c>
+      <c r="K34" s="29">
+        <f>IF('08_Moteur'!AM33&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN33&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN33&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J34" s="51">
-        <f>IF(I34="Ne pas lancer",0,IF(I34="Statu quo",MAX('08_Moteur'!AI33,'08_Moteur'!M33),IF(I34="Ouvrir +1",'08_Moteur'!AI33+1,'08_Moteur'!AI33)))</f>
-        <v/>
-      </c>
-      <c r="K34" s="51">
-        <f>IF(I34="Ne pas lancer",0,'08_Moteur'!AD33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="17">
-        <f>K34*'08_Moteur'!AE33*'08_Moteur'!AF33+IF(I34="Ne pas lancer",0,'08_Moteur'!AB33)*'02_Leviers'!$D$17-J34*'08_Moteur'!U33-K34*'08_Moteur'!R33*(1+'02_Leviers'!$G$11)-IF(I34="Ne pas lancer",0,'08_Moteur'!AL33)</f>
-        <v/>
-      </c>
-      <c r="M34" s="55">
-        <f>L34-'08_Moteur'!AM33</f>
+      <c r="M34" s="51">
+        <f>IF(L34="Ne pas lancer",0,IF(L34="Statu quo",MAX('08_Moteur'!AI33,'08_Moteur'!M33),IF(L34="Ouvrir +1",'08_Moteur'!AI33+1,'08_Moteur'!AI33)))</f>
+        <v/>
+      </c>
+      <c r="N34" s="51">
+        <f>IF(L34="Ne pas lancer",0,'08_Moteur'!AD33)</f>
+        <v/>
+      </c>
+      <c r="O34" s="17">
+        <f>N34*'08_Moteur'!AE33*'08_Moteur'!AF33+IF(L34="Ne pas lancer",0,'08_Moteur'!AB33)*'02_Leviers'!$D$16-M34*'08_Moteur'!U33-N34*'08_Moteur'!R33*(1+'02_Leviers'!$G$11)-IF(L34="Ne pas lancer",0,'08_Moteur'!AL33)</f>
+        <v/>
+      </c>
+      <c r="P34" s="55">
+        <f>O34-'08_Moteur'!AM33</f>
         <v/>
       </c>
     </row>
@@ -4177,29 +4590,41 @@
         <f>'08_Moteur'!M34</f>
         <v/>
       </c>
-      <c r="H35" s="69">
+      <c r="H35" s="71">
         <f>'08_Moteur'!AN34</f>
         <v/>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="I35" s="72">
+        <f>IF('08_Moteur'!AM34&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN34&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN34&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J35" s="17">
+        <f>IF('08_Moteur'!AM34&lt;0,-'08_Moteur'!AM34,IF('08_Moteur'!AN34&gt;=0.95,'08_Moteur'!O34*'08_Moteur'!AO34-'08_Moteur'!U34,0))</f>
+        <v/>
+      </c>
+      <c r="K35" s="29">
+        <f>IF('08_Moteur'!AM34&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN34&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN34&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J35" s="51">
-        <f>IF(I35="Ne pas lancer",0,IF(I35="Statu quo",MAX('08_Moteur'!AI34,'08_Moteur'!M34),IF(I35="Ouvrir +1",'08_Moteur'!AI34+1,'08_Moteur'!AI34)))</f>
-        <v/>
-      </c>
-      <c r="K35" s="51">
-        <f>IF(I35="Ne pas lancer",0,'08_Moteur'!AD34)</f>
-        <v/>
-      </c>
-      <c r="L35" s="17">
-        <f>K35*'08_Moteur'!AE34*'08_Moteur'!AF34+IF(I35="Ne pas lancer",0,'08_Moteur'!AB34)*'02_Leviers'!$D$17-J35*'08_Moteur'!U34-K35*'08_Moteur'!R34*(1+'02_Leviers'!$G$11)-IF(I35="Ne pas lancer",0,'08_Moteur'!AL34)</f>
-        <v/>
-      </c>
-      <c r="M35" s="55">
-        <f>L35-'08_Moteur'!AM34</f>
+      <c r="M35" s="51">
+        <f>IF(L35="Ne pas lancer",0,IF(L35="Statu quo",MAX('08_Moteur'!AI34,'08_Moteur'!M34),IF(L35="Ouvrir +1",'08_Moteur'!AI34+1,'08_Moteur'!AI34)))</f>
+        <v/>
+      </c>
+      <c r="N35" s="51">
+        <f>IF(L35="Ne pas lancer",0,'08_Moteur'!AD34)</f>
+        <v/>
+      </c>
+      <c r="O35" s="17">
+        <f>N35*'08_Moteur'!AE34*'08_Moteur'!AF34+IF(L35="Ne pas lancer",0,'08_Moteur'!AB34)*'02_Leviers'!$D$16-M35*'08_Moteur'!U34-N35*'08_Moteur'!R34*(1+'02_Leviers'!$G$11)-IF(L35="Ne pas lancer",0,'08_Moteur'!AL34)</f>
+        <v/>
+      </c>
+      <c r="P35" s="55">
+        <f>O35-'08_Moteur'!AM34</f>
         <v/>
       </c>
     </row>
@@ -4232,29 +4657,41 @@
         <f>'08_Moteur'!M35</f>
         <v/>
       </c>
-      <c r="H36" s="69">
+      <c r="H36" s="71">
         <f>'08_Moteur'!AN35</f>
         <v/>
       </c>
-      <c r="I36" s="21" t="inlineStr">
+      <c r="I36" s="72">
+        <f>IF('08_Moteur'!AM35&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN35&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN35&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J36" s="17">
+        <f>IF('08_Moteur'!AM35&lt;0,-'08_Moteur'!AM35,IF('08_Moteur'!AN35&gt;=0.95,'08_Moteur'!O35*'08_Moteur'!AO35-'08_Moteur'!U35,0))</f>
+        <v/>
+      </c>
+      <c r="K36" s="29">
+        <f>IF('08_Moteur'!AM35&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN35&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN35&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J36" s="51">
-        <f>IF(I36="Ne pas lancer",0,IF(I36="Statu quo",MAX('08_Moteur'!AI35,'08_Moteur'!M35),IF(I36="Ouvrir +1",'08_Moteur'!AI35+1,'08_Moteur'!AI35)))</f>
-        <v/>
-      </c>
-      <c r="K36" s="51">
-        <f>IF(I36="Ne pas lancer",0,'08_Moteur'!AD35)</f>
-        <v/>
-      </c>
-      <c r="L36" s="17">
-        <f>K36*'08_Moteur'!AE35*'08_Moteur'!AF35+IF(I36="Ne pas lancer",0,'08_Moteur'!AB35)*'02_Leviers'!$D$17-J36*'08_Moteur'!U35-K36*'08_Moteur'!R35*(1+'02_Leviers'!$G$11)-IF(I36="Ne pas lancer",0,'08_Moteur'!AL35)</f>
-        <v/>
-      </c>
-      <c r="M36" s="55">
-        <f>L36-'08_Moteur'!AM35</f>
+      <c r="M36" s="51">
+        <f>IF(L36="Ne pas lancer",0,IF(L36="Statu quo",MAX('08_Moteur'!AI35,'08_Moteur'!M35),IF(L36="Ouvrir +1",'08_Moteur'!AI35+1,'08_Moteur'!AI35)))</f>
+        <v/>
+      </c>
+      <c r="N36" s="51">
+        <f>IF(L36="Ne pas lancer",0,'08_Moteur'!AD35)</f>
+        <v/>
+      </c>
+      <c r="O36" s="17">
+        <f>N36*'08_Moteur'!AE35*'08_Moteur'!AF35+IF(L36="Ne pas lancer",0,'08_Moteur'!AB35)*'02_Leviers'!$D$16-M36*'08_Moteur'!U35-N36*'08_Moteur'!R35*(1+'02_Leviers'!$G$11)-IF(L36="Ne pas lancer",0,'08_Moteur'!AL35)</f>
+        <v/>
+      </c>
+      <c r="P36" s="55">
+        <f>O36-'08_Moteur'!AM35</f>
         <v/>
       </c>
     </row>
@@ -4287,29 +4724,41 @@
         <f>'08_Moteur'!M36</f>
         <v/>
       </c>
-      <c r="H37" s="69">
+      <c r="H37" s="71">
         <f>'08_Moteur'!AN36</f>
         <v/>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="I37" s="72">
+        <f>IF('08_Moteur'!AM36&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN36&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN36&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J37" s="17">
+        <f>IF('08_Moteur'!AM36&lt;0,-'08_Moteur'!AM36,IF('08_Moteur'!AN36&gt;=0.95,'08_Moteur'!O36*'08_Moteur'!AO36-'08_Moteur'!U36,0))</f>
+        <v/>
+      </c>
+      <c r="K37" s="29">
+        <f>IF('08_Moteur'!AM36&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN36&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN36&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J37" s="51">
-        <f>IF(I37="Ne pas lancer",0,IF(I37="Statu quo",MAX('08_Moteur'!AI36,'08_Moteur'!M36),IF(I37="Ouvrir +1",'08_Moteur'!AI36+1,'08_Moteur'!AI36)))</f>
-        <v/>
-      </c>
-      <c r="K37" s="51">
-        <f>IF(I37="Ne pas lancer",0,'08_Moteur'!AD36)</f>
-        <v/>
-      </c>
-      <c r="L37" s="17">
-        <f>K37*'08_Moteur'!AE36*'08_Moteur'!AF36+IF(I37="Ne pas lancer",0,'08_Moteur'!AB36)*'02_Leviers'!$D$17-J37*'08_Moteur'!U36-K37*'08_Moteur'!R36*(1+'02_Leviers'!$G$11)-IF(I37="Ne pas lancer",0,'08_Moteur'!AL36)</f>
-        <v/>
-      </c>
-      <c r="M37" s="55">
-        <f>L37-'08_Moteur'!AM36</f>
+      <c r="M37" s="51">
+        <f>IF(L37="Ne pas lancer",0,IF(L37="Statu quo",MAX('08_Moteur'!AI36,'08_Moteur'!M36),IF(L37="Ouvrir +1",'08_Moteur'!AI36+1,'08_Moteur'!AI36)))</f>
+        <v/>
+      </c>
+      <c r="N37" s="51">
+        <f>IF(L37="Ne pas lancer",0,'08_Moteur'!AD36)</f>
+        <v/>
+      </c>
+      <c r="O37" s="17">
+        <f>N37*'08_Moteur'!AE36*'08_Moteur'!AF36+IF(L37="Ne pas lancer",0,'08_Moteur'!AB36)*'02_Leviers'!$D$16-M37*'08_Moteur'!U36-N37*'08_Moteur'!R36*(1+'02_Leviers'!$G$11)-IF(L37="Ne pas lancer",0,'08_Moteur'!AL36)</f>
+        <v/>
+      </c>
+      <c r="P37" s="55">
+        <f>O37-'08_Moteur'!AM36</f>
         <v/>
       </c>
     </row>
@@ -4342,29 +4791,41 @@
         <f>'08_Moteur'!M37</f>
         <v/>
       </c>
-      <c r="H38" s="69">
+      <c r="H38" s="71">
         <f>'08_Moteur'!AN37</f>
         <v/>
       </c>
-      <c r="I38" s="21" t="inlineStr">
+      <c r="I38" s="72">
+        <f>IF('08_Moteur'!AM37&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN37&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN37&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J38" s="17">
+        <f>IF('08_Moteur'!AM37&lt;0,-'08_Moteur'!AM37,IF('08_Moteur'!AN37&gt;=0.95,'08_Moteur'!O37*'08_Moteur'!AO37-'08_Moteur'!U37,0))</f>
+        <v/>
+      </c>
+      <c r="K38" s="29">
+        <f>IF('08_Moteur'!AM37&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN37&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN37&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J38" s="51">
-        <f>IF(I38="Ne pas lancer",0,IF(I38="Statu quo",MAX('08_Moteur'!AI37,'08_Moteur'!M37),IF(I38="Ouvrir +1",'08_Moteur'!AI37+1,'08_Moteur'!AI37)))</f>
-        <v/>
-      </c>
-      <c r="K38" s="51">
-        <f>IF(I38="Ne pas lancer",0,'08_Moteur'!AD37)</f>
-        <v/>
-      </c>
-      <c r="L38" s="17">
-        <f>K38*'08_Moteur'!AE37*'08_Moteur'!AF37+IF(I38="Ne pas lancer",0,'08_Moteur'!AB37)*'02_Leviers'!$D$17-J38*'08_Moteur'!U37-K38*'08_Moteur'!R37*(1+'02_Leviers'!$G$11)-IF(I38="Ne pas lancer",0,'08_Moteur'!AL37)</f>
-        <v/>
-      </c>
-      <c r="M38" s="55">
-        <f>L38-'08_Moteur'!AM37</f>
+      <c r="M38" s="51">
+        <f>IF(L38="Ne pas lancer",0,IF(L38="Statu quo",MAX('08_Moteur'!AI37,'08_Moteur'!M37),IF(L38="Ouvrir +1",'08_Moteur'!AI37+1,'08_Moteur'!AI37)))</f>
+        <v/>
+      </c>
+      <c r="N38" s="51">
+        <f>IF(L38="Ne pas lancer",0,'08_Moteur'!AD37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="17">
+        <f>N38*'08_Moteur'!AE37*'08_Moteur'!AF37+IF(L38="Ne pas lancer",0,'08_Moteur'!AB37)*'02_Leviers'!$D$16-M38*'08_Moteur'!U37-N38*'08_Moteur'!R37*(1+'02_Leviers'!$G$11)-IF(L38="Ne pas lancer",0,'08_Moteur'!AL37)</f>
+        <v/>
+      </c>
+      <c r="P38" s="55">
+        <f>O38-'08_Moteur'!AM37</f>
         <v/>
       </c>
     </row>
@@ -4397,29 +4858,41 @@
         <f>'08_Moteur'!M38</f>
         <v/>
       </c>
-      <c r="H39" s="69">
+      <c r="H39" s="71">
         <f>'08_Moteur'!AN38</f>
         <v/>
       </c>
-      <c r="I39" s="21" t="inlineStr">
+      <c r="I39" s="72">
+        <f>IF('08_Moteur'!AM38&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN38&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN38&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J39" s="17">
+        <f>IF('08_Moteur'!AM38&lt;0,-'08_Moteur'!AM38,IF('08_Moteur'!AN38&gt;=0.95,'08_Moteur'!O38*'08_Moteur'!AO38-'08_Moteur'!U38,0))</f>
+        <v/>
+      </c>
+      <c r="K39" s="29">
+        <f>IF('08_Moteur'!AM38&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN38&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN38&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J39" s="51">
-        <f>IF(I39="Ne pas lancer",0,IF(I39="Statu quo",MAX('08_Moteur'!AI38,'08_Moteur'!M38),IF(I39="Ouvrir +1",'08_Moteur'!AI38+1,'08_Moteur'!AI38)))</f>
-        <v/>
-      </c>
-      <c r="K39" s="51">
-        <f>IF(I39="Ne pas lancer",0,'08_Moteur'!AD38)</f>
-        <v/>
-      </c>
-      <c r="L39" s="17">
-        <f>K39*'08_Moteur'!AE38*'08_Moteur'!AF38+IF(I39="Ne pas lancer",0,'08_Moteur'!AB38)*'02_Leviers'!$D$17-J39*'08_Moteur'!U38-K39*'08_Moteur'!R38*(1+'02_Leviers'!$G$11)-IF(I39="Ne pas lancer",0,'08_Moteur'!AL38)</f>
-        <v/>
-      </c>
-      <c r="M39" s="55">
-        <f>L39-'08_Moteur'!AM38</f>
+      <c r="M39" s="51">
+        <f>IF(L39="Ne pas lancer",0,IF(L39="Statu quo",MAX('08_Moteur'!AI38,'08_Moteur'!M38),IF(L39="Ouvrir +1",'08_Moteur'!AI38+1,'08_Moteur'!AI38)))</f>
+        <v/>
+      </c>
+      <c r="N39" s="51">
+        <f>IF(L39="Ne pas lancer",0,'08_Moteur'!AD38)</f>
+        <v/>
+      </c>
+      <c r="O39" s="17">
+        <f>N39*'08_Moteur'!AE38*'08_Moteur'!AF38+IF(L39="Ne pas lancer",0,'08_Moteur'!AB38)*'02_Leviers'!$D$16-M39*'08_Moteur'!U38-N39*'08_Moteur'!R38*(1+'02_Leviers'!$G$11)-IF(L39="Ne pas lancer",0,'08_Moteur'!AL38)</f>
+        <v/>
+      </c>
+      <c r="P39" s="55">
+        <f>O39-'08_Moteur'!AM38</f>
         <v/>
       </c>
     </row>
@@ -4452,29 +4925,41 @@
         <f>'08_Moteur'!M39</f>
         <v/>
       </c>
-      <c r="H40" s="69">
+      <c r="H40" s="71">
         <f>'08_Moteur'!AN39</f>
         <v/>
       </c>
-      <c r="I40" s="21" t="inlineStr">
+      <c r="I40" s="72">
+        <f>IF('08_Moteur'!AM39&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN39&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN39&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J40" s="17">
+        <f>IF('08_Moteur'!AM39&lt;0,-'08_Moteur'!AM39,IF('08_Moteur'!AN39&gt;=0.95,'08_Moteur'!O39*'08_Moteur'!AO39-'08_Moteur'!U39,0))</f>
+        <v/>
+      </c>
+      <c r="K40" s="29">
+        <f>IF('08_Moteur'!AM39&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN39&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN39&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J40" s="51">
-        <f>IF(I40="Ne pas lancer",0,IF(I40="Statu quo",MAX('08_Moteur'!AI39,'08_Moteur'!M39),IF(I40="Ouvrir +1",'08_Moteur'!AI39+1,'08_Moteur'!AI39)))</f>
-        <v/>
-      </c>
-      <c r="K40" s="51">
-        <f>IF(I40="Ne pas lancer",0,'08_Moteur'!AD39)</f>
-        <v/>
-      </c>
-      <c r="L40" s="17">
-        <f>K40*'08_Moteur'!AE39*'08_Moteur'!AF39+IF(I40="Ne pas lancer",0,'08_Moteur'!AB39)*'02_Leviers'!$D$17-J40*'08_Moteur'!U39-K40*'08_Moteur'!R39*(1+'02_Leviers'!$G$11)-IF(I40="Ne pas lancer",0,'08_Moteur'!AL39)</f>
-        <v/>
-      </c>
-      <c r="M40" s="55">
-        <f>L40-'08_Moteur'!AM39</f>
+      <c r="M40" s="51">
+        <f>IF(L40="Ne pas lancer",0,IF(L40="Statu quo",MAX('08_Moteur'!AI39,'08_Moteur'!M39),IF(L40="Ouvrir +1",'08_Moteur'!AI39+1,'08_Moteur'!AI39)))</f>
+        <v/>
+      </c>
+      <c r="N40" s="51">
+        <f>IF(L40="Ne pas lancer",0,'08_Moteur'!AD39)</f>
+        <v/>
+      </c>
+      <c r="O40" s="17">
+        <f>N40*'08_Moteur'!AE39*'08_Moteur'!AF39+IF(L40="Ne pas lancer",0,'08_Moteur'!AB39)*'02_Leviers'!$D$16-M40*'08_Moteur'!U39-N40*'08_Moteur'!R39*(1+'02_Leviers'!$G$11)-IF(L40="Ne pas lancer",0,'08_Moteur'!AL39)</f>
+        <v/>
+      </c>
+      <c r="P40" s="55">
+        <f>O40-'08_Moteur'!AM39</f>
         <v/>
       </c>
     </row>
@@ -4507,29 +4992,41 @@
         <f>'08_Moteur'!M40</f>
         <v/>
       </c>
-      <c r="H41" s="69">
+      <c r="H41" s="71">
         <f>'08_Moteur'!AN40</f>
         <v/>
       </c>
-      <c r="I41" s="21" t="inlineStr">
+      <c r="I41" s="72">
+        <f>IF('08_Moteur'!AM40&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN40&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN40&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J41" s="17">
+        <f>IF('08_Moteur'!AM40&lt;0,-'08_Moteur'!AM40,IF('08_Moteur'!AN40&gt;=0.95,'08_Moteur'!O40*'08_Moteur'!AO40-'08_Moteur'!U40,0))</f>
+        <v/>
+      </c>
+      <c r="K41" s="29">
+        <f>IF('08_Moteur'!AM40&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN40&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN40&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J41" s="51">
-        <f>IF(I41="Ne pas lancer",0,IF(I41="Statu quo",MAX('08_Moteur'!AI40,'08_Moteur'!M40),IF(I41="Ouvrir +1",'08_Moteur'!AI40+1,'08_Moteur'!AI40)))</f>
-        <v/>
-      </c>
-      <c r="K41" s="51">
-        <f>IF(I41="Ne pas lancer",0,'08_Moteur'!AD40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="17">
-        <f>K41*'08_Moteur'!AE40*'08_Moteur'!AF40+IF(I41="Ne pas lancer",0,'08_Moteur'!AB40)*'02_Leviers'!$D$17-J41*'08_Moteur'!U40-K41*'08_Moteur'!R40*(1+'02_Leviers'!$G$11)-IF(I41="Ne pas lancer",0,'08_Moteur'!AL40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="55">
-        <f>L41-'08_Moteur'!AM40</f>
+      <c r="M41" s="51">
+        <f>IF(L41="Ne pas lancer",0,IF(L41="Statu quo",MAX('08_Moteur'!AI40,'08_Moteur'!M40),IF(L41="Ouvrir +1",'08_Moteur'!AI40+1,'08_Moteur'!AI40)))</f>
+        <v/>
+      </c>
+      <c r="N41" s="51">
+        <f>IF(L41="Ne pas lancer",0,'08_Moteur'!AD40)</f>
+        <v/>
+      </c>
+      <c r="O41" s="17">
+        <f>N41*'08_Moteur'!AE40*'08_Moteur'!AF40+IF(L41="Ne pas lancer",0,'08_Moteur'!AB40)*'02_Leviers'!$D$16-M41*'08_Moteur'!U40-N41*'08_Moteur'!R40*(1+'02_Leviers'!$G$11)-IF(L41="Ne pas lancer",0,'08_Moteur'!AL40)</f>
+        <v/>
+      </c>
+      <c r="P41" s="55">
+        <f>O41-'08_Moteur'!AM40</f>
         <v/>
       </c>
     </row>
@@ -4562,29 +5059,41 @@
         <f>'08_Moteur'!M41</f>
         <v/>
       </c>
-      <c r="H42" s="69">
+      <c r="H42" s="71">
         <f>'08_Moteur'!AN41</f>
         <v/>
       </c>
-      <c r="I42" s="21" t="inlineStr">
+      <c r="I42" s="72">
+        <f>IF('08_Moteur'!AM41&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN41&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN41&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J42" s="17">
+        <f>IF('08_Moteur'!AM41&lt;0,-'08_Moteur'!AM41,IF('08_Moteur'!AN41&gt;=0.95,'08_Moteur'!O41*'08_Moteur'!AO41-'08_Moteur'!U41,0))</f>
+        <v/>
+      </c>
+      <c r="K42" s="29">
+        <f>IF('08_Moteur'!AM41&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN41&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN41&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L42" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J42" s="51">
-        <f>IF(I42="Ne pas lancer",0,IF(I42="Statu quo",MAX('08_Moteur'!AI41,'08_Moteur'!M41),IF(I42="Ouvrir +1",'08_Moteur'!AI41+1,'08_Moteur'!AI41)))</f>
-        <v/>
-      </c>
-      <c r="K42" s="51">
-        <f>IF(I42="Ne pas lancer",0,'08_Moteur'!AD41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="17">
-        <f>K42*'08_Moteur'!AE41*'08_Moteur'!AF41+IF(I42="Ne pas lancer",0,'08_Moteur'!AB41)*'02_Leviers'!$D$17-J42*'08_Moteur'!U41-K42*'08_Moteur'!R41*(1+'02_Leviers'!$G$11)-IF(I42="Ne pas lancer",0,'08_Moteur'!AL41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="55">
-        <f>L42-'08_Moteur'!AM41</f>
+      <c r="M42" s="51">
+        <f>IF(L42="Ne pas lancer",0,IF(L42="Statu quo",MAX('08_Moteur'!AI41,'08_Moteur'!M41),IF(L42="Ouvrir +1",'08_Moteur'!AI41+1,'08_Moteur'!AI41)))</f>
+        <v/>
+      </c>
+      <c r="N42" s="51">
+        <f>IF(L42="Ne pas lancer",0,'08_Moteur'!AD41)</f>
+        <v/>
+      </c>
+      <c r="O42" s="17">
+        <f>N42*'08_Moteur'!AE41*'08_Moteur'!AF41+IF(L42="Ne pas lancer",0,'08_Moteur'!AB41)*'02_Leviers'!$D$16-M42*'08_Moteur'!U41-N42*'08_Moteur'!R41*(1+'02_Leviers'!$G$11)-IF(L42="Ne pas lancer",0,'08_Moteur'!AL41)</f>
+        <v/>
+      </c>
+      <c r="P42" s="55">
+        <f>O42-'08_Moteur'!AM41</f>
         <v/>
       </c>
     </row>
@@ -4617,29 +5126,41 @@
         <f>'08_Moteur'!M42</f>
         <v/>
       </c>
-      <c r="H43" s="69">
+      <c r="H43" s="71">
         <f>'08_Moteur'!AN42</f>
         <v/>
       </c>
-      <c r="I43" s="21" t="inlineStr">
+      <c r="I43" s="72">
+        <f>IF('08_Moteur'!AM42&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN42&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN42&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J43" s="17">
+        <f>IF('08_Moteur'!AM42&lt;0,-'08_Moteur'!AM42,IF('08_Moteur'!AN42&gt;=0.95,'08_Moteur'!O42*'08_Moteur'!AO42-'08_Moteur'!U42,0))</f>
+        <v/>
+      </c>
+      <c r="K43" s="29">
+        <f>IF('08_Moteur'!AM42&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN42&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN42&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L43" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J43" s="51">
-        <f>IF(I43="Ne pas lancer",0,IF(I43="Statu quo",MAX('08_Moteur'!AI42,'08_Moteur'!M42),IF(I43="Ouvrir +1",'08_Moteur'!AI42+1,'08_Moteur'!AI42)))</f>
-        <v/>
-      </c>
-      <c r="K43" s="51">
-        <f>IF(I43="Ne pas lancer",0,'08_Moteur'!AD42)</f>
-        <v/>
-      </c>
-      <c r="L43" s="17">
-        <f>K43*'08_Moteur'!AE42*'08_Moteur'!AF42+IF(I43="Ne pas lancer",0,'08_Moteur'!AB42)*'02_Leviers'!$D$17-J43*'08_Moteur'!U42-K43*'08_Moteur'!R42*(1+'02_Leviers'!$G$11)-IF(I43="Ne pas lancer",0,'08_Moteur'!AL42)</f>
-        <v/>
-      </c>
-      <c r="M43" s="55">
-        <f>L43-'08_Moteur'!AM42</f>
+      <c r="M43" s="51">
+        <f>IF(L43="Ne pas lancer",0,IF(L43="Statu quo",MAX('08_Moteur'!AI42,'08_Moteur'!M42),IF(L43="Ouvrir +1",'08_Moteur'!AI42+1,'08_Moteur'!AI42)))</f>
+        <v/>
+      </c>
+      <c r="N43" s="51">
+        <f>IF(L43="Ne pas lancer",0,'08_Moteur'!AD42)</f>
+        <v/>
+      </c>
+      <c r="O43" s="17">
+        <f>N43*'08_Moteur'!AE42*'08_Moteur'!AF42+IF(L43="Ne pas lancer",0,'08_Moteur'!AB42)*'02_Leviers'!$D$16-M43*'08_Moteur'!U42-N43*'08_Moteur'!R42*(1+'02_Leviers'!$G$11)-IF(L43="Ne pas lancer",0,'08_Moteur'!AL42)</f>
+        <v/>
+      </c>
+      <c r="P43" s="55">
+        <f>O43-'08_Moteur'!AM42</f>
         <v/>
       </c>
     </row>
@@ -4672,29 +5193,41 @@
         <f>'08_Moteur'!M43</f>
         <v/>
       </c>
-      <c r="H44" s="69">
+      <c r="H44" s="71">
         <f>'08_Moteur'!AN43</f>
         <v/>
       </c>
-      <c r="I44" s="21" t="inlineStr">
+      <c r="I44" s="72">
+        <f>IF('08_Moteur'!AM43&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN43&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN43&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J44" s="17">
+        <f>IF('08_Moteur'!AM43&lt;0,-'08_Moteur'!AM43,IF('08_Moteur'!AN43&gt;=0.95,'08_Moteur'!O43*'08_Moteur'!AO43-'08_Moteur'!U43,0))</f>
+        <v/>
+      </c>
+      <c r="K44" s="29">
+        <f>IF('08_Moteur'!AM43&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN43&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN43&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L44" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J44" s="51">
-        <f>IF(I44="Ne pas lancer",0,IF(I44="Statu quo",MAX('08_Moteur'!AI43,'08_Moteur'!M43),IF(I44="Ouvrir +1",'08_Moteur'!AI43+1,'08_Moteur'!AI43)))</f>
-        <v/>
-      </c>
-      <c r="K44" s="51">
-        <f>IF(I44="Ne pas lancer",0,'08_Moteur'!AD43)</f>
-        <v/>
-      </c>
-      <c r="L44" s="17">
-        <f>K44*'08_Moteur'!AE43*'08_Moteur'!AF43+IF(I44="Ne pas lancer",0,'08_Moteur'!AB43)*'02_Leviers'!$D$17-J44*'08_Moteur'!U43-K44*'08_Moteur'!R43*(1+'02_Leviers'!$G$11)-IF(I44="Ne pas lancer",0,'08_Moteur'!AL43)</f>
-        <v/>
-      </c>
-      <c r="M44" s="55">
-        <f>L44-'08_Moteur'!AM43</f>
+      <c r="M44" s="51">
+        <f>IF(L44="Ne pas lancer",0,IF(L44="Statu quo",MAX('08_Moteur'!AI43,'08_Moteur'!M43),IF(L44="Ouvrir +1",'08_Moteur'!AI43+1,'08_Moteur'!AI43)))</f>
+        <v/>
+      </c>
+      <c r="N44" s="51">
+        <f>IF(L44="Ne pas lancer",0,'08_Moteur'!AD43)</f>
+        <v/>
+      </c>
+      <c r="O44" s="17">
+        <f>N44*'08_Moteur'!AE43*'08_Moteur'!AF43+IF(L44="Ne pas lancer",0,'08_Moteur'!AB43)*'02_Leviers'!$D$16-M44*'08_Moteur'!U43-N44*'08_Moteur'!R43*(1+'02_Leviers'!$G$11)-IF(L44="Ne pas lancer",0,'08_Moteur'!AL43)</f>
+        <v/>
+      </c>
+      <c r="P44" s="55">
+        <f>O44-'08_Moteur'!AM43</f>
         <v/>
       </c>
     </row>
@@ -4727,29 +5260,41 @@
         <f>'08_Moteur'!M44</f>
         <v/>
       </c>
-      <c r="H45" s="69">
+      <c r="H45" s="71">
         <f>'08_Moteur'!AN44</f>
         <v/>
       </c>
-      <c r="I45" s="21" t="inlineStr">
+      <c r="I45" s="72">
+        <f>IF('08_Moteur'!AM44&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN44&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN44&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J45" s="17">
+        <f>IF('08_Moteur'!AM44&lt;0,-'08_Moteur'!AM44,IF('08_Moteur'!AN44&gt;=0.95,'08_Moteur'!O44*'08_Moteur'!AO44-'08_Moteur'!U44,0))</f>
+        <v/>
+      </c>
+      <c r="K45" s="29">
+        <f>IF('08_Moteur'!AM44&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN44&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN44&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L45" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J45" s="51">
-        <f>IF(I45="Ne pas lancer",0,IF(I45="Statu quo",MAX('08_Moteur'!AI44,'08_Moteur'!M44),IF(I45="Ouvrir +1",'08_Moteur'!AI44+1,'08_Moteur'!AI44)))</f>
-        <v/>
-      </c>
-      <c r="K45" s="51">
-        <f>IF(I45="Ne pas lancer",0,'08_Moteur'!AD44)</f>
-        <v/>
-      </c>
-      <c r="L45" s="17">
-        <f>K45*'08_Moteur'!AE44*'08_Moteur'!AF44+IF(I45="Ne pas lancer",0,'08_Moteur'!AB44)*'02_Leviers'!$D$17-J45*'08_Moteur'!U44-K45*'08_Moteur'!R44*(1+'02_Leviers'!$G$11)-IF(I45="Ne pas lancer",0,'08_Moteur'!AL44)</f>
-        <v/>
-      </c>
-      <c r="M45" s="55">
-        <f>L45-'08_Moteur'!AM44</f>
+      <c r="M45" s="51">
+        <f>IF(L45="Ne pas lancer",0,IF(L45="Statu quo",MAX('08_Moteur'!AI44,'08_Moteur'!M44),IF(L45="Ouvrir +1",'08_Moteur'!AI44+1,'08_Moteur'!AI44)))</f>
+        <v/>
+      </c>
+      <c r="N45" s="51">
+        <f>IF(L45="Ne pas lancer",0,'08_Moteur'!AD44)</f>
+        <v/>
+      </c>
+      <c r="O45" s="17">
+        <f>N45*'08_Moteur'!AE44*'08_Moteur'!AF44+IF(L45="Ne pas lancer",0,'08_Moteur'!AB44)*'02_Leviers'!$D$16-M45*'08_Moteur'!U44-N45*'08_Moteur'!R44*(1+'02_Leviers'!$G$11)-IF(L45="Ne pas lancer",0,'08_Moteur'!AL44)</f>
+        <v/>
+      </c>
+      <c r="P45" s="55">
+        <f>O45-'08_Moteur'!AM44</f>
         <v/>
       </c>
     </row>
@@ -4782,29 +5327,41 @@
         <f>'08_Moteur'!M45</f>
         <v/>
       </c>
-      <c r="H46" s="69">
+      <c r="H46" s="71">
         <f>'08_Moteur'!AN45</f>
         <v/>
       </c>
-      <c r="I46" s="21" t="inlineStr">
+      <c r="I46" s="72">
+        <f>IF('08_Moteur'!AM45&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN45&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN45&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J46" s="17">
+        <f>IF('08_Moteur'!AM45&lt;0,-'08_Moteur'!AM45,IF('08_Moteur'!AN45&gt;=0.95,'08_Moteur'!O45*'08_Moteur'!AO45-'08_Moteur'!U45,0))</f>
+        <v/>
+      </c>
+      <c r="K46" s="29">
+        <f>IF('08_Moteur'!AM45&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN45&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN45&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L46" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J46" s="51">
-        <f>IF(I46="Ne pas lancer",0,IF(I46="Statu quo",MAX('08_Moteur'!AI45,'08_Moteur'!M45),IF(I46="Ouvrir +1",'08_Moteur'!AI45+1,'08_Moteur'!AI45)))</f>
-        <v/>
-      </c>
-      <c r="K46" s="51">
-        <f>IF(I46="Ne pas lancer",0,'08_Moteur'!AD45)</f>
-        <v/>
-      </c>
-      <c r="L46" s="17">
-        <f>K46*'08_Moteur'!AE45*'08_Moteur'!AF45+IF(I46="Ne pas lancer",0,'08_Moteur'!AB45)*'02_Leviers'!$D$17-J46*'08_Moteur'!U45-K46*'08_Moteur'!R45*(1+'02_Leviers'!$G$11)-IF(I46="Ne pas lancer",0,'08_Moteur'!AL45)</f>
-        <v/>
-      </c>
-      <c r="M46" s="55">
-        <f>L46-'08_Moteur'!AM45</f>
+      <c r="M46" s="51">
+        <f>IF(L46="Ne pas lancer",0,IF(L46="Statu quo",MAX('08_Moteur'!AI45,'08_Moteur'!M45),IF(L46="Ouvrir +1",'08_Moteur'!AI45+1,'08_Moteur'!AI45)))</f>
+        <v/>
+      </c>
+      <c r="N46" s="51">
+        <f>IF(L46="Ne pas lancer",0,'08_Moteur'!AD45)</f>
+        <v/>
+      </c>
+      <c r="O46" s="17">
+        <f>N46*'08_Moteur'!AE45*'08_Moteur'!AF45+IF(L46="Ne pas lancer",0,'08_Moteur'!AB45)*'02_Leviers'!$D$16-M46*'08_Moteur'!U45-N46*'08_Moteur'!R45*(1+'02_Leviers'!$G$11)-IF(L46="Ne pas lancer",0,'08_Moteur'!AL45)</f>
+        <v/>
+      </c>
+      <c r="P46" s="55">
+        <f>O46-'08_Moteur'!AM45</f>
         <v/>
       </c>
     </row>
@@ -4837,29 +5394,41 @@
         <f>'08_Moteur'!M46</f>
         <v/>
       </c>
-      <c r="H47" s="69">
+      <c r="H47" s="71">
         <f>'08_Moteur'!AN46</f>
         <v/>
       </c>
-      <c r="I47" s="21" t="inlineStr">
+      <c r="I47" s="72">
+        <f>IF('08_Moteur'!AM46&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN46&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN46&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J47" s="17">
+        <f>IF('08_Moteur'!AM46&lt;0,-'08_Moteur'!AM46,IF('08_Moteur'!AN46&gt;=0.95,'08_Moteur'!O46*'08_Moteur'!AO46-'08_Moteur'!U46,0))</f>
+        <v/>
+      </c>
+      <c r="K47" s="29">
+        <f>IF('08_Moteur'!AM46&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN46&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN46&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L47" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J47" s="51">
-        <f>IF(I47="Ne pas lancer",0,IF(I47="Statu quo",MAX('08_Moteur'!AI46,'08_Moteur'!M46),IF(I47="Ouvrir +1",'08_Moteur'!AI46+1,'08_Moteur'!AI46)))</f>
-        <v/>
-      </c>
-      <c r="K47" s="51">
-        <f>IF(I47="Ne pas lancer",0,'08_Moteur'!AD46)</f>
-        <v/>
-      </c>
-      <c r="L47" s="17">
-        <f>K47*'08_Moteur'!AE46*'08_Moteur'!AF46+IF(I47="Ne pas lancer",0,'08_Moteur'!AB46)*'02_Leviers'!$D$17-J47*'08_Moteur'!U46-K47*'08_Moteur'!R46*(1+'02_Leviers'!$G$11)-IF(I47="Ne pas lancer",0,'08_Moteur'!AL46)</f>
-        <v/>
-      </c>
-      <c r="M47" s="55">
-        <f>L47-'08_Moteur'!AM46</f>
+      <c r="M47" s="51">
+        <f>IF(L47="Ne pas lancer",0,IF(L47="Statu quo",MAX('08_Moteur'!AI46,'08_Moteur'!M46),IF(L47="Ouvrir +1",'08_Moteur'!AI46+1,'08_Moteur'!AI46)))</f>
+        <v/>
+      </c>
+      <c r="N47" s="51">
+        <f>IF(L47="Ne pas lancer",0,'08_Moteur'!AD46)</f>
+        <v/>
+      </c>
+      <c r="O47" s="17">
+        <f>N47*'08_Moteur'!AE46*'08_Moteur'!AF46+IF(L47="Ne pas lancer",0,'08_Moteur'!AB46)*'02_Leviers'!$D$16-M47*'08_Moteur'!U46-N47*'08_Moteur'!R46*(1+'02_Leviers'!$G$11)-IF(L47="Ne pas lancer",0,'08_Moteur'!AL46)</f>
+        <v/>
+      </c>
+      <c r="P47" s="55">
+        <f>O47-'08_Moteur'!AM46</f>
         <v/>
       </c>
     </row>
@@ -4892,29 +5461,41 @@
         <f>'08_Moteur'!M47</f>
         <v/>
       </c>
-      <c r="H48" s="69">
+      <c r="H48" s="71">
         <f>'08_Moteur'!AN47</f>
         <v/>
       </c>
-      <c r="I48" s="21" t="inlineStr">
+      <c r="I48" s="72">
+        <f>IF('08_Moteur'!AM47&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN47&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN47&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J48" s="17">
+        <f>IF('08_Moteur'!AM47&lt;0,-'08_Moteur'!AM47,IF('08_Moteur'!AN47&gt;=0.95,'08_Moteur'!O47*'08_Moteur'!AO47-'08_Moteur'!U47,0))</f>
+        <v/>
+      </c>
+      <c r="K48" s="29">
+        <f>IF('08_Moteur'!AM47&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN47&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN47&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L48" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J48" s="51">
-        <f>IF(I48="Ne pas lancer",0,IF(I48="Statu quo",MAX('08_Moteur'!AI47,'08_Moteur'!M47),IF(I48="Ouvrir +1",'08_Moteur'!AI47+1,'08_Moteur'!AI47)))</f>
-        <v/>
-      </c>
-      <c r="K48" s="51">
-        <f>IF(I48="Ne pas lancer",0,'08_Moteur'!AD47)</f>
-        <v/>
-      </c>
-      <c r="L48" s="17">
-        <f>K48*'08_Moteur'!AE47*'08_Moteur'!AF47+IF(I48="Ne pas lancer",0,'08_Moteur'!AB47)*'02_Leviers'!$D$17-J48*'08_Moteur'!U47-K48*'08_Moteur'!R47*(1+'02_Leviers'!$G$11)-IF(I48="Ne pas lancer",0,'08_Moteur'!AL47)</f>
-        <v/>
-      </c>
-      <c r="M48" s="55">
-        <f>L48-'08_Moteur'!AM47</f>
+      <c r="M48" s="51">
+        <f>IF(L48="Ne pas lancer",0,IF(L48="Statu quo",MAX('08_Moteur'!AI47,'08_Moteur'!M47),IF(L48="Ouvrir +1",'08_Moteur'!AI47+1,'08_Moteur'!AI47)))</f>
+        <v/>
+      </c>
+      <c r="N48" s="51">
+        <f>IF(L48="Ne pas lancer",0,'08_Moteur'!AD47)</f>
+        <v/>
+      </c>
+      <c r="O48" s="17">
+        <f>N48*'08_Moteur'!AE47*'08_Moteur'!AF47+IF(L48="Ne pas lancer",0,'08_Moteur'!AB47)*'02_Leviers'!$D$16-M48*'08_Moteur'!U47-N48*'08_Moteur'!R47*(1+'02_Leviers'!$G$11)-IF(L48="Ne pas lancer",0,'08_Moteur'!AL47)</f>
+        <v/>
+      </c>
+      <c r="P48" s="55">
+        <f>O48-'08_Moteur'!AM47</f>
         <v/>
       </c>
     </row>
@@ -4947,29 +5528,41 @@
         <f>'08_Moteur'!M48</f>
         <v/>
       </c>
-      <c r="H49" s="69">
+      <c r="H49" s="71">
         <f>'08_Moteur'!AN48</f>
         <v/>
       </c>
-      <c r="I49" s="21" t="inlineStr">
+      <c r="I49" s="72">
+        <f>IF('08_Moteur'!AM48&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN48&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN48&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J49" s="17">
+        <f>IF('08_Moteur'!AM48&lt;0,-'08_Moteur'!AM48,IF('08_Moteur'!AN48&gt;=0.95,'08_Moteur'!O48*'08_Moteur'!AO48-'08_Moteur'!U48,0))</f>
+        <v/>
+      </c>
+      <c r="K49" s="29">
+        <f>IF('08_Moteur'!AM48&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN48&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN48&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L49" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J49" s="51">
-        <f>IF(I49="Ne pas lancer",0,IF(I49="Statu quo",MAX('08_Moteur'!AI48,'08_Moteur'!M48),IF(I49="Ouvrir +1",'08_Moteur'!AI48+1,'08_Moteur'!AI48)))</f>
-        <v/>
-      </c>
-      <c r="K49" s="51">
-        <f>IF(I49="Ne pas lancer",0,'08_Moteur'!AD48)</f>
-        <v/>
-      </c>
-      <c r="L49" s="17">
-        <f>K49*'08_Moteur'!AE48*'08_Moteur'!AF48+IF(I49="Ne pas lancer",0,'08_Moteur'!AB48)*'02_Leviers'!$D$17-J49*'08_Moteur'!U48-K49*'08_Moteur'!R48*(1+'02_Leviers'!$G$11)-IF(I49="Ne pas lancer",0,'08_Moteur'!AL48)</f>
-        <v/>
-      </c>
-      <c r="M49" s="55">
-        <f>L49-'08_Moteur'!AM48</f>
+      <c r="M49" s="51">
+        <f>IF(L49="Ne pas lancer",0,IF(L49="Statu quo",MAX('08_Moteur'!AI48,'08_Moteur'!M48),IF(L49="Ouvrir +1",'08_Moteur'!AI48+1,'08_Moteur'!AI48)))</f>
+        <v/>
+      </c>
+      <c r="N49" s="51">
+        <f>IF(L49="Ne pas lancer",0,'08_Moteur'!AD48)</f>
+        <v/>
+      </c>
+      <c r="O49" s="17">
+        <f>N49*'08_Moteur'!AE48*'08_Moteur'!AF48+IF(L49="Ne pas lancer",0,'08_Moteur'!AB48)*'02_Leviers'!$D$16-M49*'08_Moteur'!U48-N49*'08_Moteur'!R48*(1+'02_Leviers'!$G$11)-IF(L49="Ne pas lancer",0,'08_Moteur'!AL48)</f>
+        <v/>
+      </c>
+      <c r="P49" s="55">
+        <f>O49-'08_Moteur'!AM48</f>
         <v/>
       </c>
     </row>
@@ -5002,29 +5595,41 @@
         <f>'08_Moteur'!M49</f>
         <v/>
       </c>
-      <c r="H50" s="69">
+      <c r="H50" s="71">
         <f>'08_Moteur'!AN49</f>
         <v/>
       </c>
-      <c r="I50" s="21" t="inlineStr">
+      <c r="I50" s="72">
+        <f>IF('08_Moteur'!AM49&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN49&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN49&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J50" s="17">
+        <f>IF('08_Moteur'!AM49&lt;0,-'08_Moteur'!AM49,IF('08_Moteur'!AN49&gt;=0.95,'08_Moteur'!O49*'08_Moteur'!AO49-'08_Moteur'!U49,0))</f>
+        <v/>
+      </c>
+      <c r="K50" s="29">
+        <f>IF('08_Moteur'!AM49&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN49&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN49&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L50" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J50" s="51">
-        <f>IF(I50="Ne pas lancer",0,IF(I50="Statu quo",MAX('08_Moteur'!AI49,'08_Moteur'!M49),IF(I50="Ouvrir +1",'08_Moteur'!AI49+1,'08_Moteur'!AI49)))</f>
-        <v/>
-      </c>
-      <c r="K50" s="51">
-        <f>IF(I50="Ne pas lancer",0,'08_Moteur'!AD49)</f>
-        <v/>
-      </c>
-      <c r="L50" s="17">
-        <f>K50*'08_Moteur'!AE49*'08_Moteur'!AF49+IF(I50="Ne pas lancer",0,'08_Moteur'!AB49)*'02_Leviers'!$D$17-J50*'08_Moteur'!U49-K50*'08_Moteur'!R49*(1+'02_Leviers'!$G$11)-IF(I50="Ne pas lancer",0,'08_Moteur'!AL49)</f>
-        <v/>
-      </c>
-      <c r="M50" s="55">
-        <f>L50-'08_Moteur'!AM49</f>
+      <c r="M50" s="51">
+        <f>IF(L50="Ne pas lancer",0,IF(L50="Statu quo",MAX('08_Moteur'!AI49,'08_Moteur'!M49),IF(L50="Ouvrir +1",'08_Moteur'!AI49+1,'08_Moteur'!AI49)))</f>
+        <v/>
+      </c>
+      <c r="N50" s="51">
+        <f>IF(L50="Ne pas lancer",0,'08_Moteur'!AD49)</f>
+        <v/>
+      </c>
+      <c r="O50" s="17">
+        <f>N50*'08_Moteur'!AE49*'08_Moteur'!AF49+IF(L50="Ne pas lancer",0,'08_Moteur'!AB49)*'02_Leviers'!$D$16-M50*'08_Moteur'!U49-N50*'08_Moteur'!R49*(1+'02_Leviers'!$G$11)-IF(L50="Ne pas lancer",0,'08_Moteur'!AL49)</f>
+        <v/>
+      </c>
+      <c r="P50" s="55">
+        <f>O50-'08_Moteur'!AM49</f>
         <v/>
       </c>
     </row>
@@ -5057,29 +5662,41 @@
         <f>'08_Moteur'!M50</f>
         <v/>
       </c>
-      <c r="H51" s="69">
+      <c r="H51" s="71">
         <f>'08_Moteur'!AN50</f>
         <v/>
       </c>
-      <c r="I51" s="21" t="inlineStr">
+      <c r="I51" s="72">
+        <f>IF('08_Moteur'!AM50&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN50&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN50&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J51" s="17">
+        <f>IF('08_Moteur'!AM50&lt;0,-'08_Moteur'!AM50,IF('08_Moteur'!AN50&gt;=0.95,'08_Moteur'!O50*'08_Moteur'!AO50-'08_Moteur'!U50,0))</f>
+        <v/>
+      </c>
+      <c r="K51" s="29">
+        <f>IF('08_Moteur'!AM50&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN50&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN50&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L51" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J51" s="51">
-        <f>IF(I51="Ne pas lancer",0,IF(I51="Statu quo",MAX('08_Moteur'!AI50,'08_Moteur'!M50),IF(I51="Ouvrir +1",'08_Moteur'!AI50+1,'08_Moteur'!AI50)))</f>
-        <v/>
-      </c>
-      <c r="K51" s="51">
-        <f>IF(I51="Ne pas lancer",0,'08_Moteur'!AD50)</f>
-        <v/>
-      </c>
-      <c r="L51" s="17">
-        <f>K51*'08_Moteur'!AE50*'08_Moteur'!AF50+IF(I51="Ne pas lancer",0,'08_Moteur'!AB50)*'02_Leviers'!$D$17-J51*'08_Moteur'!U50-K51*'08_Moteur'!R50*(1+'02_Leviers'!$G$11)-IF(I51="Ne pas lancer",0,'08_Moteur'!AL50)</f>
-        <v/>
-      </c>
-      <c r="M51" s="55">
-        <f>L51-'08_Moteur'!AM50</f>
+      <c r="M51" s="51">
+        <f>IF(L51="Ne pas lancer",0,IF(L51="Statu quo",MAX('08_Moteur'!AI50,'08_Moteur'!M50),IF(L51="Ouvrir +1",'08_Moteur'!AI50+1,'08_Moteur'!AI50)))</f>
+        <v/>
+      </c>
+      <c r="N51" s="51">
+        <f>IF(L51="Ne pas lancer",0,'08_Moteur'!AD50)</f>
+        <v/>
+      </c>
+      <c r="O51" s="17">
+        <f>N51*'08_Moteur'!AE50*'08_Moteur'!AF50+IF(L51="Ne pas lancer",0,'08_Moteur'!AB50)*'02_Leviers'!$D$16-M51*'08_Moteur'!U50-N51*'08_Moteur'!R50*(1+'02_Leviers'!$G$11)-IF(L51="Ne pas lancer",0,'08_Moteur'!AL50)</f>
+        <v/>
+      </c>
+      <c r="P51" s="55">
+        <f>O51-'08_Moteur'!AM50</f>
         <v/>
       </c>
     </row>
@@ -5112,29 +5729,41 @@
         <f>'08_Moteur'!M51</f>
         <v/>
       </c>
-      <c r="H52" s="69">
+      <c r="H52" s="71">
         <f>'08_Moteur'!AN51</f>
         <v/>
       </c>
-      <c r="I52" s="21" t="inlineStr">
+      <c r="I52" s="72">
+        <f>IF('08_Moteur'!AM51&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN51&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN51&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J52" s="17">
+        <f>IF('08_Moteur'!AM51&lt;0,-'08_Moteur'!AM51,IF('08_Moteur'!AN51&gt;=0.95,'08_Moteur'!O51*'08_Moteur'!AO51-'08_Moteur'!U51,0))</f>
+        <v/>
+      </c>
+      <c r="K52" s="29">
+        <f>IF('08_Moteur'!AM51&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN51&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN51&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L52" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J52" s="51">
-        <f>IF(I52="Ne pas lancer",0,IF(I52="Statu quo",MAX('08_Moteur'!AI51,'08_Moteur'!M51),IF(I52="Ouvrir +1",'08_Moteur'!AI51+1,'08_Moteur'!AI51)))</f>
-        <v/>
-      </c>
-      <c r="K52" s="51">
-        <f>IF(I52="Ne pas lancer",0,'08_Moteur'!AD51)</f>
-        <v/>
-      </c>
-      <c r="L52" s="17">
-        <f>K52*'08_Moteur'!AE51*'08_Moteur'!AF51+IF(I52="Ne pas lancer",0,'08_Moteur'!AB51)*'02_Leviers'!$D$17-J52*'08_Moteur'!U51-K52*'08_Moteur'!R51*(1+'02_Leviers'!$G$11)-IF(I52="Ne pas lancer",0,'08_Moteur'!AL51)</f>
-        <v/>
-      </c>
-      <c r="M52" s="55">
-        <f>L52-'08_Moteur'!AM51</f>
+      <c r="M52" s="51">
+        <f>IF(L52="Ne pas lancer",0,IF(L52="Statu quo",MAX('08_Moteur'!AI51,'08_Moteur'!M51),IF(L52="Ouvrir +1",'08_Moteur'!AI51+1,'08_Moteur'!AI51)))</f>
+        <v/>
+      </c>
+      <c r="N52" s="51">
+        <f>IF(L52="Ne pas lancer",0,'08_Moteur'!AD51)</f>
+        <v/>
+      </c>
+      <c r="O52" s="17">
+        <f>N52*'08_Moteur'!AE51*'08_Moteur'!AF51+IF(L52="Ne pas lancer",0,'08_Moteur'!AB51)*'02_Leviers'!$D$16-M52*'08_Moteur'!U51-N52*'08_Moteur'!R51*(1+'02_Leviers'!$G$11)-IF(L52="Ne pas lancer",0,'08_Moteur'!AL51)</f>
+        <v/>
+      </c>
+      <c r="P52" s="55">
+        <f>O52-'08_Moteur'!AM51</f>
         <v/>
       </c>
     </row>
@@ -5167,29 +5796,41 @@
         <f>'08_Moteur'!M52</f>
         <v/>
       </c>
-      <c r="H53" s="69">
+      <c r="H53" s="71">
         <f>'08_Moteur'!AN52</f>
         <v/>
       </c>
-      <c r="I53" s="21" t="inlineStr">
+      <c r="I53" s="72">
+        <f>IF('08_Moteur'!AM52&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN52&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN52&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J53" s="17">
+        <f>IF('08_Moteur'!AM52&lt;0,-'08_Moteur'!AM52,IF('08_Moteur'!AN52&gt;=0.95,'08_Moteur'!O52*'08_Moteur'!AO52-'08_Moteur'!U52,0))</f>
+        <v/>
+      </c>
+      <c r="K53" s="29">
+        <f>IF('08_Moteur'!AM52&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN52&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN52&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J53" s="51">
-        <f>IF(I53="Ne pas lancer",0,IF(I53="Statu quo",MAX('08_Moteur'!AI52,'08_Moteur'!M52),IF(I53="Ouvrir +1",'08_Moteur'!AI52+1,'08_Moteur'!AI52)))</f>
-        <v/>
-      </c>
-      <c r="K53" s="51">
-        <f>IF(I53="Ne pas lancer",0,'08_Moteur'!AD52)</f>
-        <v/>
-      </c>
-      <c r="L53" s="17">
-        <f>K53*'08_Moteur'!AE52*'08_Moteur'!AF52+IF(I53="Ne pas lancer",0,'08_Moteur'!AB52)*'02_Leviers'!$D$17-J53*'08_Moteur'!U52-K53*'08_Moteur'!R52*(1+'02_Leviers'!$G$11)-IF(I53="Ne pas lancer",0,'08_Moteur'!AL52)</f>
-        <v/>
-      </c>
-      <c r="M53" s="55">
-        <f>L53-'08_Moteur'!AM52</f>
+      <c r="M53" s="51">
+        <f>IF(L53="Ne pas lancer",0,IF(L53="Statu quo",MAX('08_Moteur'!AI52,'08_Moteur'!M52),IF(L53="Ouvrir +1",'08_Moteur'!AI52+1,'08_Moteur'!AI52)))</f>
+        <v/>
+      </c>
+      <c r="N53" s="51">
+        <f>IF(L53="Ne pas lancer",0,'08_Moteur'!AD52)</f>
+        <v/>
+      </c>
+      <c r="O53" s="17">
+        <f>N53*'08_Moteur'!AE52*'08_Moteur'!AF52+IF(L53="Ne pas lancer",0,'08_Moteur'!AB52)*'02_Leviers'!$D$16-M53*'08_Moteur'!U52-N53*'08_Moteur'!R52*(1+'02_Leviers'!$G$11)-IF(L53="Ne pas lancer",0,'08_Moteur'!AL52)</f>
+        <v/>
+      </c>
+      <c r="P53" s="55">
+        <f>O53-'08_Moteur'!AM52</f>
         <v/>
       </c>
     </row>
@@ -5222,29 +5863,41 @@
         <f>'08_Moteur'!M53</f>
         <v/>
       </c>
-      <c r="H54" s="69">
+      <c r="H54" s="71">
         <f>'08_Moteur'!AN53</f>
         <v/>
       </c>
-      <c r="I54" s="21" t="inlineStr">
+      <c r="I54" s="72">
+        <f>IF('08_Moteur'!AM53&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN53&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN53&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J54" s="17">
+        <f>IF('08_Moteur'!AM53&lt;0,-'08_Moteur'!AM53,IF('08_Moteur'!AN53&gt;=0.95,'08_Moteur'!O53*'08_Moteur'!AO53-'08_Moteur'!U53,0))</f>
+        <v/>
+      </c>
+      <c r="K54" s="29">
+        <f>IF('08_Moteur'!AM53&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN53&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN53&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L54" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J54" s="51">
-        <f>IF(I54="Ne pas lancer",0,IF(I54="Statu quo",MAX('08_Moteur'!AI53,'08_Moteur'!M53),IF(I54="Ouvrir +1",'08_Moteur'!AI53+1,'08_Moteur'!AI53)))</f>
-        <v/>
-      </c>
-      <c r="K54" s="51">
-        <f>IF(I54="Ne pas lancer",0,'08_Moteur'!AD53)</f>
-        <v/>
-      </c>
-      <c r="L54" s="17">
-        <f>K54*'08_Moteur'!AE53*'08_Moteur'!AF53+IF(I54="Ne pas lancer",0,'08_Moteur'!AB53)*'02_Leviers'!$D$17-J54*'08_Moteur'!U53-K54*'08_Moteur'!R53*(1+'02_Leviers'!$G$11)-IF(I54="Ne pas lancer",0,'08_Moteur'!AL53)</f>
-        <v/>
-      </c>
-      <c r="M54" s="55">
-        <f>L54-'08_Moteur'!AM53</f>
+      <c r="M54" s="51">
+        <f>IF(L54="Ne pas lancer",0,IF(L54="Statu quo",MAX('08_Moteur'!AI53,'08_Moteur'!M53),IF(L54="Ouvrir +1",'08_Moteur'!AI53+1,'08_Moteur'!AI53)))</f>
+        <v/>
+      </c>
+      <c r="N54" s="51">
+        <f>IF(L54="Ne pas lancer",0,'08_Moteur'!AD53)</f>
+        <v/>
+      </c>
+      <c r="O54" s="17">
+        <f>N54*'08_Moteur'!AE53*'08_Moteur'!AF53+IF(L54="Ne pas lancer",0,'08_Moteur'!AB53)*'02_Leviers'!$D$16-M54*'08_Moteur'!U53-N54*'08_Moteur'!R53*(1+'02_Leviers'!$G$11)-IF(L54="Ne pas lancer",0,'08_Moteur'!AL53)</f>
+        <v/>
+      </c>
+      <c r="P54" s="55">
+        <f>O54-'08_Moteur'!AM53</f>
         <v/>
       </c>
     </row>
@@ -5277,29 +5930,41 @@
         <f>'08_Moteur'!M54</f>
         <v/>
       </c>
-      <c r="H55" s="69">
+      <c r="H55" s="71">
         <f>'08_Moteur'!AN54</f>
         <v/>
       </c>
-      <c r="I55" s="21" t="inlineStr">
+      <c r="I55" s="72">
+        <f>IF('08_Moteur'!AM54&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN54&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN54&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J55" s="17">
+        <f>IF('08_Moteur'!AM54&lt;0,-'08_Moteur'!AM54,IF('08_Moteur'!AN54&gt;=0.95,'08_Moteur'!O54*'08_Moteur'!AO54-'08_Moteur'!U54,0))</f>
+        <v/>
+      </c>
+      <c r="K55" s="29">
+        <f>IF('08_Moteur'!AM54&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN54&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN54&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L55" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J55" s="51">
-        <f>IF(I55="Ne pas lancer",0,IF(I55="Statu quo",MAX('08_Moteur'!AI54,'08_Moteur'!M54),IF(I55="Ouvrir +1",'08_Moteur'!AI54+1,'08_Moteur'!AI54)))</f>
-        <v/>
-      </c>
-      <c r="K55" s="51">
-        <f>IF(I55="Ne pas lancer",0,'08_Moteur'!AD54)</f>
-        <v/>
-      </c>
-      <c r="L55" s="17">
-        <f>K55*'08_Moteur'!AE54*'08_Moteur'!AF54+IF(I55="Ne pas lancer",0,'08_Moteur'!AB54)*'02_Leviers'!$D$17-J55*'08_Moteur'!U54-K55*'08_Moteur'!R54*(1+'02_Leviers'!$G$11)-IF(I55="Ne pas lancer",0,'08_Moteur'!AL54)</f>
-        <v/>
-      </c>
-      <c r="M55" s="55">
-        <f>L55-'08_Moteur'!AM54</f>
+      <c r="M55" s="51">
+        <f>IF(L55="Ne pas lancer",0,IF(L55="Statu quo",MAX('08_Moteur'!AI54,'08_Moteur'!M54),IF(L55="Ouvrir +1",'08_Moteur'!AI54+1,'08_Moteur'!AI54)))</f>
+        <v/>
+      </c>
+      <c r="N55" s="51">
+        <f>IF(L55="Ne pas lancer",0,'08_Moteur'!AD54)</f>
+        <v/>
+      </c>
+      <c r="O55" s="17">
+        <f>N55*'08_Moteur'!AE54*'08_Moteur'!AF54+IF(L55="Ne pas lancer",0,'08_Moteur'!AB54)*'02_Leviers'!$D$16-M55*'08_Moteur'!U54-N55*'08_Moteur'!R54*(1+'02_Leviers'!$G$11)-IF(L55="Ne pas lancer",0,'08_Moteur'!AL54)</f>
+        <v/>
+      </c>
+      <c r="P55" s="55">
+        <f>O55-'08_Moteur'!AM54</f>
         <v/>
       </c>
     </row>
@@ -5332,29 +5997,41 @@
         <f>'08_Moteur'!M55</f>
         <v/>
       </c>
-      <c r="H56" s="69">
+      <c r="H56" s="71">
         <f>'08_Moteur'!AN55</f>
         <v/>
       </c>
-      <c r="I56" s="21" t="inlineStr">
+      <c r="I56" s="72">
+        <f>IF('08_Moteur'!AM55&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN55&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN55&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J56" s="17">
+        <f>IF('08_Moteur'!AM55&lt;0,-'08_Moteur'!AM55,IF('08_Moteur'!AN55&gt;=0.95,'08_Moteur'!O55*'08_Moteur'!AO55-'08_Moteur'!U55,0))</f>
+        <v/>
+      </c>
+      <c r="K56" s="29">
+        <f>IF('08_Moteur'!AM55&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN55&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN55&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J56" s="51">
-        <f>IF(I56="Ne pas lancer",0,IF(I56="Statu quo",MAX('08_Moteur'!AI55,'08_Moteur'!M55),IF(I56="Ouvrir +1",'08_Moteur'!AI55+1,'08_Moteur'!AI55)))</f>
-        <v/>
-      </c>
-      <c r="K56" s="51">
-        <f>IF(I56="Ne pas lancer",0,'08_Moteur'!AD55)</f>
-        <v/>
-      </c>
-      <c r="L56" s="17">
-        <f>K56*'08_Moteur'!AE55*'08_Moteur'!AF55+IF(I56="Ne pas lancer",0,'08_Moteur'!AB55)*'02_Leviers'!$D$17-J56*'08_Moteur'!U55-K56*'08_Moteur'!R55*(1+'02_Leviers'!$G$11)-IF(I56="Ne pas lancer",0,'08_Moteur'!AL55)</f>
-        <v/>
-      </c>
-      <c r="M56" s="55">
-        <f>L56-'08_Moteur'!AM55</f>
+      <c r="M56" s="51">
+        <f>IF(L56="Ne pas lancer",0,IF(L56="Statu quo",MAX('08_Moteur'!AI55,'08_Moteur'!M55),IF(L56="Ouvrir +1",'08_Moteur'!AI55+1,'08_Moteur'!AI55)))</f>
+        <v/>
+      </c>
+      <c r="N56" s="51">
+        <f>IF(L56="Ne pas lancer",0,'08_Moteur'!AD55)</f>
+        <v/>
+      </c>
+      <c r="O56" s="17">
+        <f>N56*'08_Moteur'!AE55*'08_Moteur'!AF55+IF(L56="Ne pas lancer",0,'08_Moteur'!AB55)*'02_Leviers'!$D$16-M56*'08_Moteur'!U55-N56*'08_Moteur'!R55*(1+'02_Leviers'!$G$11)-IF(L56="Ne pas lancer",0,'08_Moteur'!AL55)</f>
+        <v/>
+      </c>
+      <c r="P56" s="55">
+        <f>O56-'08_Moteur'!AM55</f>
         <v/>
       </c>
     </row>
@@ -5387,29 +6064,41 @@
         <f>'08_Moteur'!M56</f>
         <v/>
       </c>
-      <c r="H57" s="69">
+      <c r="H57" s="71">
         <f>'08_Moteur'!AN56</f>
         <v/>
       </c>
-      <c r="I57" s="21" t="inlineStr">
+      <c r="I57" s="72">
+        <f>IF('08_Moteur'!AM56&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN56&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN56&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J57" s="17">
+        <f>IF('08_Moteur'!AM56&lt;0,-'08_Moteur'!AM56,IF('08_Moteur'!AN56&gt;=0.95,'08_Moteur'!O56*'08_Moteur'!AO56-'08_Moteur'!U56,0))</f>
+        <v/>
+      </c>
+      <c r="K57" s="29">
+        <f>IF('08_Moteur'!AM56&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN56&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN56&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L57" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J57" s="51">
-        <f>IF(I57="Ne pas lancer",0,IF(I57="Statu quo",MAX('08_Moteur'!AI56,'08_Moteur'!M56),IF(I57="Ouvrir +1",'08_Moteur'!AI56+1,'08_Moteur'!AI56)))</f>
-        <v/>
-      </c>
-      <c r="K57" s="51">
-        <f>IF(I57="Ne pas lancer",0,'08_Moteur'!AD56)</f>
-        <v/>
-      </c>
-      <c r="L57" s="17">
-        <f>K57*'08_Moteur'!AE56*'08_Moteur'!AF56+IF(I57="Ne pas lancer",0,'08_Moteur'!AB56)*'02_Leviers'!$D$17-J57*'08_Moteur'!U56-K57*'08_Moteur'!R56*(1+'02_Leviers'!$G$11)-IF(I57="Ne pas lancer",0,'08_Moteur'!AL56)</f>
-        <v/>
-      </c>
-      <c r="M57" s="55">
-        <f>L57-'08_Moteur'!AM56</f>
+      <c r="M57" s="51">
+        <f>IF(L57="Ne pas lancer",0,IF(L57="Statu quo",MAX('08_Moteur'!AI56,'08_Moteur'!M56),IF(L57="Ouvrir +1",'08_Moteur'!AI56+1,'08_Moteur'!AI56)))</f>
+        <v/>
+      </c>
+      <c r="N57" s="51">
+        <f>IF(L57="Ne pas lancer",0,'08_Moteur'!AD56)</f>
+        <v/>
+      </c>
+      <c r="O57" s="17">
+        <f>N57*'08_Moteur'!AE56*'08_Moteur'!AF56+IF(L57="Ne pas lancer",0,'08_Moteur'!AB56)*'02_Leviers'!$D$16-M57*'08_Moteur'!U56-N57*'08_Moteur'!R56*(1+'02_Leviers'!$G$11)-IF(L57="Ne pas lancer",0,'08_Moteur'!AL56)</f>
+        <v/>
+      </c>
+      <c r="P57" s="55">
+        <f>O57-'08_Moteur'!AM56</f>
         <v/>
       </c>
     </row>
@@ -5442,29 +6131,41 @@
         <f>'08_Moteur'!M57</f>
         <v/>
       </c>
-      <c r="H58" s="69">
+      <c r="H58" s="71">
         <f>'08_Moteur'!AN57</f>
         <v/>
       </c>
-      <c r="I58" s="21" t="inlineStr">
+      <c r="I58" s="72">
+        <f>IF('08_Moteur'!AM57&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN57&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN57&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J58" s="17">
+        <f>IF('08_Moteur'!AM57&lt;0,-'08_Moteur'!AM57,IF('08_Moteur'!AN57&gt;=0.95,'08_Moteur'!O57*'08_Moteur'!AO57-'08_Moteur'!U57,0))</f>
+        <v/>
+      </c>
+      <c r="K58" s="29">
+        <f>IF('08_Moteur'!AM57&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN57&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN57&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L58" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J58" s="51">
-        <f>IF(I58="Ne pas lancer",0,IF(I58="Statu quo",MAX('08_Moteur'!AI57,'08_Moteur'!M57),IF(I58="Ouvrir +1",'08_Moteur'!AI57+1,'08_Moteur'!AI57)))</f>
-        <v/>
-      </c>
-      <c r="K58" s="51">
-        <f>IF(I58="Ne pas lancer",0,'08_Moteur'!AD57)</f>
-        <v/>
-      </c>
-      <c r="L58" s="17">
-        <f>K58*'08_Moteur'!AE57*'08_Moteur'!AF57+IF(I58="Ne pas lancer",0,'08_Moteur'!AB57)*'02_Leviers'!$D$17-J58*'08_Moteur'!U57-K58*'08_Moteur'!R57*(1+'02_Leviers'!$G$11)-IF(I58="Ne pas lancer",0,'08_Moteur'!AL57)</f>
-        <v/>
-      </c>
-      <c r="M58" s="55">
-        <f>L58-'08_Moteur'!AM57</f>
+      <c r="M58" s="51">
+        <f>IF(L58="Ne pas lancer",0,IF(L58="Statu quo",MAX('08_Moteur'!AI57,'08_Moteur'!M57),IF(L58="Ouvrir +1",'08_Moteur'!AI57+1,'08_Moteur'!AI57)))</f>
+        <v/>
+      </c>
+      <c r="N58" s="51">
+        <f>IF(L58="Ne pas lancer",0,'08_Moteur'!AD57)</f>
+        <v/>
+      </c>
+      <c r="O58" s="17">
+        <f>N58*'08_Moteur'!AE57*'08_Moteur'!AF57+IF(L58="Ne pas lancer",0,'08_Moteur'!AB57)*'02_Leviers'!$D$16-M58*'08_Moteur'!U57-N58*'08_Moteur'!R57*(1+'02_Leviers'!$G$11)-IF(L58="Ne pas lancer",0,'08_Moteur'!AL57)</f>
+        <v/>
+      </c>
+      <c r="P58" s="55">
+        <f>O58-'08_Moteur'!AM57</f>
         <v/>
       </c>
     </row>
@@ -5497,29 +6198,41 @@
         <f>'08_Moteur'!M58</f>
         <v/>
       </c>
-      <c r="H59" s="69">
+      <c r="H59" s="71">
         <f>'08_Moteur'!AN58</f>
         <v/>
       </c>
-      <c r="I59" s="21" t="inlineStr">
+      <c r="I59" s="72">
+        <f>IF('08_Moteur'!AM58&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN58&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN58&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J59" s="17">
+        <f>IF('08_Moteur'!AM58&lt;0,-'08_Moteur'!AM58,IF('08_Moteur'!AN58&gt;=0.95,'08_Moteur'!O58*'08_Moteur'!AO58-'08_Moteur'!U58,0))</f>
+        <v/>
+      </c>
+      <c r="K59" s="29">
+        <f>IF('08_Moteur'!AM58&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN58&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN58&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L59" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J59" s="51">
-        <f>IF(I59="Ne pas lancer",0,IF(I59="Statu quo",MAX('08_Moteur'!AI58,'08_Moteur'!M58),IF(I59="Ouvrir +1",'08_Moteur'!AI58+1,'08_Moteur'!AI58)))</f>
-        <v/>
-      </c>
-      <c r="K59" s="51">
-        <f>IF(I59="Ne pas lancer",0,'08_Moteur'!AD58)</f>
-        <v/>
-      </c>
-      <c r="L59" s="17">
-        <f>K59*'08_Moteur'!AE58*'08_Moteur'!AF58+IF(I59="Ne pas lancer",0,'08_Moteur'!AB58)*'02_Leviers'!$D$17-J59*'08_Moteur'!U58-K59*'08_Moteur'!R58*(1+'02_Leviers'!$G$11)-IF(I59="Ne pas lancer",0,'08_Moteur'!AL58)</f>
-        <v/>
-      </c>
-      <c r="M59" s="55">
-        <f>L59-'08_Moteur'!AM58</f>
+      <c r="M59" s="51">
+        <f>IF(L59="Ne pas lancer",0,IF(L59="Statu quo",MAX('08_Moteur'!AI58,'08_Moteur'!M58),IF(L59="Ouvrir +1",'08_Moteur'!AI58+1,'08_Moteur'!AI58)))</f>
+        <v/>
+      </c>
+      <c r="N59" s="51">
+        <f>IF(L59="Ne pas lancer",0,'08_Moteur'!AD58)</f>
+        <v/>
+      </c>
+      <c r="O59" s="17">
+        <f>N59*'08_Moteur'!AE58*'08_Moteur'!AF58+IF(L59="Ne pas lancer",0,'08_Moteur'!AB58)*'02_Leviers'!$D$16-M59*'08_Moteur'!U58-N59*'08_Moteur'!R58*(1+'02_Leviers'!$G$11)-IF(L59="Ne pas lancer",0,'08_Moteur'!AL58)</f>
+        <v/>
+      </c>
+      <c r="P59" s="55">
+        <f>O59-'08_Moteur'!AM58</f>
         <v/>
       </c>
     </row>
@@ -5552,29 +6265,41 @@
         <f>'08_Moteur'!M59</f>
         <v/>
       </c>
-      <c r="H60" s="69">
+      <c r="H60" s="71">
         <f>'08_Moteur'!AN59</f>
         <v/>
       </c>
-      <c r="I60" s="21" t="inlineStr">
+      <c r="I60" s="72">
+        <f>IF('08_Moteur'!AM59&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN59&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN59&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J60" s="17">
+        <f>IF('08_Moteur'!AM59&lt;0,-'08_Moteur'!AM59,IF('08_Moteur'!AN59&gt;=0.95,'08_Moteur'!O59*'08_Moteur'!AO59-'08_Moteur'!U59,0))</f>
+        <v/>
+      </c>
+      <c r="K60" s="29">
+        <f>IF('08_Moteur'!AM59&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN59&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN59&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L60" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J60" s="51">
-        <f>IF(I60="Ne pas lancer",0,IF(I60="Statu quo",MAX('08_Moteur'!AI59,'08_Moteur'!M59),IF(I60="Ouvrir +1",'08_Moteur'!AI59+1,'08_Moteur'!AI59)))</f>
-        <v/>
-      </c>
-      <c r="K60" s="51">
-        <f>IF(I60="Ne pas lancer",0,'08_Moteur'!AD59)</f>
-        <v/>
-      </c>
-      <c r="L60" s="17">
-        <f>K60*'08_Moteur'!AE59*'08_Moteur'!AF59+IF(I60="Ne pas lancer",0,'08_Moteur'!AB59)*'02_Leviers'!$D$17-J60*'08_Moteur'!U59-K60*'08_Moteur'!R59*(1+'02_Leviers'!$G$11)-IF(I60="Ne pas lancer",0,'08_Moteur'!AL59)</f>
-        <v/>
-      </c>
-      <c r="M60" s="55">
-        <f>L60-'08_Moteur'!AM59</f>
+      <c r="M60" s="51">
+        <f>IF(L60="Ne pas lancer",0,IF(L60="Statu quo",MAX('08_Moteur'!AI59,'08_Moteur'!M59),IF(L60="Ouvrir +1",'08_Moteur'!AI59+1,'08_Moteur'!AI59)))</f>
+        <v/>
+      </c>
+      <c r="N60" s="51">
+        <f>IF(L60="Ne pas lancer",0,'08_Moteur'!AD59)</f>
+        <v/>
+      </c>
+      <c r="O60" s="17">
+        <f>N60*'08_Moteur'!AE59*'08_Moteur'!AF59+IF(L60="Ne pas lancer",0,'08_Moteur'!AB59)*'02_Leviers'!$D$16-M60*'08_Moteur'!U59-N60*'08_Moteur'!R59*(1+'02_Leviers'!$G$11)-IF(L60="Ne pas lancer",0,'08_Moteur'!AL59)</f>
+        <v/>
+      </c>
+      <c r="P60" s="55">
+        <f>O60-'08_Moteur'!AM59</f>
         <v/>
       </c>
     </row>
@@ -5607,41 +6332,54 @@
         <f>'08_Moteur'!M60</f>
         <v/>
       </c>
-      <c r="H61" s="69">
+      <c r="H61" s="71">
         <f>'08_Moteur'!AN60</f>
         <v/>
       </c>
-      <c r="I61" s="21" t="inlineStr">
+      <c r="I61" s="72">
+        <f>IF('08_Moteur'!AM60&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN60&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN60&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="J61" s="17">
+        <f>IF('08_Moteur'!AM60&lt;0,-'08_Moteur'!AM60,IF('08_Moteur'!AN60&gt;=0.95,'08_Moteur'!O60*'08_Moteur'!AO60-'08_Moteur'!U60,0))</f>
+        <v/>
+      </c>
+      <c r="K61" s="29">
+        <f>IF('08_Moteur'!AM60&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN60&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN60&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L61" s="21" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
       </c>
-      <c r="J61" s="51">
-        <f>IF(I61="Ne pas lancer",0,IF(I61="Statu quo",MAX('08_Moteur'!AI60,'08_Moteur'!M60),IF(I61="Ouvrir +1",'08_Moteur'!AI60+1,'08_Moteur'!AI60)))</f>
-        <v/>
-      </c>
-      <c r="K61" s="51">
-        <f>IF(I61="Ne pas lancer",0,'08_Moteur'!AD60)</f>
-        <v/>
-      </c>
-      <c r="L61" s="17">
-        <f>K61*'08_Moteur'!AE60*'08_Moteur'!AF60+IF(I61="Ne pas lancer",0,'08_Moteur'!AB60)*'02_Leviers'!$D$17-J61*'08_Moteur'!U60-K61*'08_Moteur'!R60*(1+'02_Leviers'!$G$11)-IF(I61="Ne pas lancer",0,'08_Moteur'!AL60)</f>
-        <v/>
-      </c>
-      <c r="M61" s="55">
-        <f>L61-'08_Moteur'!AM60</f>
+      <c r="M61" s="51">
+        <f>IF(L61="Ne pas lancer",0,IF(L61="Statu quo",MAX('08_Moteur'!AI60,'08_Moteur'!M60),IF(L61="Ouvrir +1",'08_Moteur'!AI60+1,'08_Moteur'!AI60)))</f>
+        <v/>
+      </c>
+      <c r="N61" s="51">
+        <f>IF(L61="Ne pas lancer",0,'08_Moteur'!AD60)</f>
+        <v/>
+      </c>
+      <c r="O61" s="17">
+        <f>N61*'08_Moteur'!AE60*'08_Moteur'!AF60+IF(L61="Ne pas lancer",0,'08_Moteur'!AB60)*'02_Leviers'!$D$16-M61*'08_Moteur'!U60-N61*'08_Moteur'!R60*(1+'02_Leviers'!$G$11)-IF(L61="Ne pas lancer",0,'08_Moteur'!AL60)</f>
+        <v/>
+      </c>
+      <c r="P61" s="55">
+        <f>O61-'08_Moteur'!AM60</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="J2:K2"/>
+  <mergeCells count="5">
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="M2:P2"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Optimal,Statu quo,Ne pas lancer,Ouvrir +1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5705,7 +6443,7 @@
         <f>0.01*SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60*'08_Moteur'!$AF$3:$AF$60)</f>
         <v/>
       </c>
-      <c r="D6" s="70" t="inlineStr">
+      <c r="D6" s="73" t="inlineStr">
         <is>
           <t>Tombe quasi intégralement en EBITDA.</t>
         </is>
@@ -5718,10 +6456,10 @@
         </is>
       </c>
       <c r="C7" s="17">
-        <f>0.01*SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$D$19)</f>
-        <v/>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
+        <f>0.01*SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="D7" s="73" t="inlineStr">
         <is>
           <t>Nul si recouvrement=100 % ; sinon réduit la perte.</t>
         </is>
@@ -5734,10 +6472,10 @@
         </is>
       </c>
       <c r="C8" s="17">
-        <f>0.01*'02_Leviers'!$D$21*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
-        <v/>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
+        <f>0.01*'02_Leviers'!$D$20*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
+        <v/>
+      </c>
+      <c r="D8" s="73" t="inlineStr">
         <is>
           <t>Plus de leads → plus d'inscrits, net du coût.</t>
         </is>
@@ -5753,7 +6491,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=0)*'08_Moteur'!$K$3:$K$60)*IFERROR(SUM('08_Moteur'!$AM$3:$AM$60)/SUM('08_Moteur'!$AD$3:$AD$60),0)</f>
         <v/>
       </c>
-      <c r="D9" s="70" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
         <is>
           <t>Rétention : + d'étudiants qui poursuivent.</t>
         </is>
@@ -5765,7 +6503,7 @@
           <t>Exposition financement alternance (€ à sécuriser) :</t>
         </is>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="74">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
@@ -5904,7 +6642,7 @@
         <v/>
       </c>
       <c r="D9" s="52">
-        <f>'07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-'02_Leviers'!$D$18*'07_Structure'!D18</f>
+        <f>'07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-2000000</f>
         <v/>
       </c>
       <c r="E9" s="53">
@@ -5923,7 +6661,7 @@
         <v/>
       </c>
       <c r="D10" s="53">
-        <f>IFERROR(('07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-'02_Leviers'!$D$18*'07_Structure'!D18)/'07_Structure'!D18,0)</f>
+        <f>IFERROR(('07_Structure'!E18-'07_Structure'!F18-'07_Structure'!H18-2000000)/'07_Structure'!D18,0)</f>
         <v/>
       </c>
       <c r="E10" s="53">
@@ -5999,7 +6737,7 @@
         <v/>
       </c>
       <c r="D14" s="53">
-        <f>'02_Leviers'!$D$20</f>
+        <f>'02_Leviers'!$D$19</f>
         <v/>
       </c>
       <c r="E14" s="53">
@@ -6008,20 +6746,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="72" t="inlineStr">
+      <c r="B15" s="75" t="inlineStr">
         <is>
           <t>€ à sécuriser (exposition)</t>
         </is>
       </c>
-      <c r="C15" s="73">
+      <c r="C15" s="76">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
-      <c r="D15" s="73">
-        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
-        <v/>
-      </c>
-      <c r="E15" s="74">
+      <c r="D15" s="76">
+        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$19)</f>
+        <v/>
+      </c>
+      <c r="E15" s="77">
         <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
@@ -6083,7 +6821,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="78" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -6100,7 +6838,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="78" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -6117,7 +6855,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -6134,7 +6872,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -6151,7 +6889,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="78" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -6168,7 +6906,7 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>Sécurisation &amp; recouvrement</t>
         </is>
@@ -6185,7 +6923,7 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>Objectifs (cadrage)</t>
         </is>
@@ -6202,7 +6940,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="75" t="inlineStr">
+      <c r="B13" s="78" t="inlineStr">
         <is>
           <t>Décisions ouvrir/fermer</t>
         </is>
@@ -6219,7 +6957,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="75" t="inlineStr">
+      <c r="B14" s="78" t="inlineStr">
         <is>
           <t>Allocation structure</t>
         </is>
@@ -6388,7 +7126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G24"/>
+  <dimension ref="B2:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6634,7 +7372,7 @@
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>Constantes de référence (le réel / hypothèses à charger)</t>
+          <t>Constantes de référence (le réel = à charger · repli = si historique mince)</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -6666,7 +7404,7 @@
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>CAC global partagé (€/inscrit)</t>
+          <t>Coût chargé / ETP permanent</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -6675,11 +7413,11 @@
         </is>
       </c>
       <c r="D15" s="28" t="n">
-        <v>450</v>
+        <v>58000</v>
       </c>
       <c r="E15" s="29" t="inlineStr">
         <is>
-          <t>réel</t>
+          <t>réel (SIRH)</t>
         </is>
       </c>
       <c r="F15" s="30" t="n"/>
@@ -6691,7 +7429,7 @@
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Coût chargé / ETP permanent</t>
+          <t>Frais de dossier / nouvel inscrit</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -6700,7 +7438,7 @@
         </is>
       </c>
       <c r="D16" s="28" t="n">
-        <v>48000</v>
+        <v>90</v>
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
@@ -6716,7 +7454,7 @@
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Frais de dossier / nouvel inscrit</t>
+          <t>Frais de structure &amp; marketing groupe (€ FIXE)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -6725,11 +7463,11 @@
         </is>
       </c>
       <c r="D17" s="28" t="n">
-        <v>90</v>
+        <v>2000000</v>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>réel</t>
+          <t>réel (siège, IT, marque)</t>
         </is>
       </c>
       <c r="F17" s="30" t="n"/>
@@ -6741,7 +7479,7 @@
     <row r="18">
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Frais de structure groupe (% CA)</t>
+          <t>Recouvrement reste à charge (employeur)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -6749,12 +7487,12 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
-        <v>0.08</v>
+      <c r="D18" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>réel</t>
+          <t>hypothèse (100% légal)</t>
         </is>
       </c>
       <c r="F18" s="30" t="n"/>
@@ -6766,7 +7504,7 @@
     <row r="19">
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Recouvrement reste à charge (employeur)</t>
+          <t>Sécurisation N-1 — REPLI</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6775,11 +7513,11 @@
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>hypothèse (100% légal)</t>
+          <t>repli (sinon mesuré par programme)</t>
         </is>
       </c>
       <c r="F19" s="30" t="n"/>
@@ -6791,24 +7529,24 @@
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Réf. taux de sécurisation N-1</t>
+          <t>Élasticité marketing — REPLI</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="n">
-        <v>0.86</v>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>0.5</v>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>réel</t>
+          <t>repli (sinon mesurée N-2/N-1)</t>
         </is>
       </c>
       <c r="F20" s="30" t="n"/>
-      <c r="G20" s="26">
+      <c r="G20" s="34">
         <f>D20</f>
         <v/>
       </c>
@@ -6816,74 +7554,48 @@
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Élasticité marketing (repli si historique mince)</t>
+          <t>Conversion candidature→inscrit — REPLI</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>0.5</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>0.372</v>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>hypothèse</t>
+          <t>repli (sinon mesurée par cellule)</t>
         </is>
       </c>
       <c r="F21" s="30" t="n"/>
-      <c r="G21" s="34">
+      <c r="G21" s="26">
         <f>D21</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Conversion candidature→inscrit (réf N-1)</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="E22" s="29" t="inlineStr">
-        <is>
-          <t>réel</t>
-        </is>
-      </c>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="26">
-        <f>D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="19" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Driver d'allocation :</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>Effectifs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
@@ -6893,7 +7605,7 @@
     <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Cadrage,Optimiste,Prudent"</formula1>
     </dataValidation>
-    <dataValidation sqref="D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Effectifs,Chiffre d'affaires,Surface m2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7967,7 +8679,7 @@
         <v>320</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="6">
@@ -8007,7 +8719,7 @@
         <v>320</v>
       </c>
       <c r="J6" s="25" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -8085,7 +8797,7 @@
         <v>600</v>
       </c>
       <c r="J8" s="25" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9">
@@ -8163,7 +8875,7 @@
         <v>320</v>
       </c>
       <c r="J10" s="25" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11">
@@ -8203,7 +8915,7 @@
         <v>320</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -8281,7 +8993,7 @@
         <v>600</v>
       </c>
       <c r="J13" s="25" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="14">
@@ -8359,7 +9071,7 @@
         <v>320</v>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="16">
@@ -8399,7 +9111,7 @@
         <v>320</v>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -8477,7 +9189,7 @@
         <v>250</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19">
@@ -8555,7 +9267,7 @@
         <v>320</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -8633,7 +9345,7 @@
         <v>320</v>
       </c>
       <c r="J22" s="25" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23">
@@ -8673,7 +9385,7 @@
         <v>320</v>
       </c>
       <c r="J23" s="25" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -12040,7 +12752,7 @@
     <row r="64">
       <c r="A64" s="41" t="inlineStr">
         <is>
-          <t>Historique marketing par programme → élasticité mesurée</t>
+          <t>Historique marketing &amp; sécurisation par programme (issu du réalisé)</t>
         </is>
       </c>
     </row>
@@ -12075,6 +12787,11 @@
           <t>Élasticité mesurée</t>
         </is>
       </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>Sécurisation N-1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
@@ -12089,14 +12806,17 @@
         <v>685</v>
       </c>
       <c r="D66" s="42" t="n">
-        <v>178500</v>
+        <v>74182</v>
       </c>
       <c r="E66" s="42" t="n">
-        <v>196350</v>
+        <v>81600</v>
       </c>
       <c r="F66" s="43">
-        <f>IFERROR((C66/B66-1)/(E66/D66-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C66/B66-1)/(E66/D66-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G66" s="25" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="67">
@@ -12112,14 +12832,17 @@
         <v>414</v>
       </c>
       <c r="D67" s="42" t="n">
-        <v>147000</v>
+        <v>84000</v>
       </c>
       <c r="E67" s="42" t="n">
-        <v>161700</v>
+        <v>92400</v>
       </c>
       <c r="F67" s="43">
-        <f>IFERROR((C67/B67-1)/(E67/D67-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C67/B67-1)/(E67/D67-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G67" s="25" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="68">
@@ -12135,14 +12858,17 @@
         <v>454</v>
       </c>
       <c r="D68" s="42" t="n">
-        <v>118300</v>
+        <v>49164</v>
       </c>
       <c r="E68" s="42" t="n">
-        <v>130130</v>
+        <v>54080</v>
       </c>
       <c r="F68" s="43">
-        <f>IFERROR((C68/B68-1)/(E68/D68-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C68/B68-1)/(E68/D68-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G68" s="25" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="69">
@@ -12158,14 +12884,17 @@
         <v>272</v>
       </c>
       <c r="D69" s="42" t="n">
-        <v>96409</v>
+        <v>55091</v>
       </c>
       <c r="E69" s="42" t="n">
-        <v>106050</v>
+        <v>60600</v>
       </c>
       <c r="F69" s="43">
-        <f>IFERROR((C69/B69-1)/(E69/D69-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C69/B69-1)/(E69/D69-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G69" s="25" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="70">
@@ -12181,14 +12910,17 @@
         <v>350</v>
       </c>
       <c r="D70" s="42" t="n">
-        <v>91000</v>
+        <v>37818</v>
       </c>
       <c r="E70" s="42" t="n">
-        <v>100100</v>
+        <v>41600</v>
       </c>
       <c r="F70" s="43">
-        <f>IFERROR((C70/B70-1)/(E70/D70-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C70/B70-1)/(E70/D70-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G70" s="25" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="71">
@@ -12204,14 +12936,17 @@
         <v>177</v>
       </c>
       <c r="D71" s="42" t="n">
-        <v>42000</v>
+        <v>15000</v>
       </c>
       <c r="E71" s="42" t="n">
-        <v>46200</v>
+        <v>16500</v>
       </c>
       <c r="F71" s="43">
-        <f>IFERROR((C71/B71-1)/(E71/D71-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C71/B71-1)/(E71/D71-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G71" s="25" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="72">
@@ -12227,14 +12962,17 @@
         <v>221</v>
       </c>
       <c r="D72" s="42" t="n">
-        <v>57400</v>
+        <v>23855</v>
       </c>
       <c r="E72" s="42" t="n">
-        <v>63140</v>
+        <v>26240</v>
       </c>
       <c r="F72" s="43">
-        <f>IFERROR((C72/B72-1)/(E72/D72-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C72/B72-1)/(E72/D72-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G72" s="25" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="73">
@@ -12250,19 +12988,22 @@
         <v>234</v>
       </c>
       <c r="D73" s="42" t="n">
-        <v>60900</v>
+        <v>25309</v>
       </c>
       <c r="E73" s="42" t="n">
-        <v>66990</v>
+        <v>27840</v>
       </c>
       <c r="F73" s="43">
-        <f>IFERROR((C73/B73-1)/(E73/D73-1),'02_Leviers'!$D$21)</f>
-        <v/>
+        <f>IFERROR((C73/B73-1)/(E73/D73-1),'02_Leviers'!$D$20)</f>
+        <v/>
+      </c>
+      <c r="G73" s="25" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12373,16 +13114,16 @@
         <v>2467250</v>
       </c>
       <c r="E4" s="42" t="n">
-        <v>1839800</v>
+        <v>1896050</v>
       </c>
       <c r="F4" s="42" t="n">
         <v>271000</v>
       </c>
       <c r="G4" s="40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H4" s="17">
-        <f>G4*'02_Leviers'!$D$16</f>
+        <f>G4*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I4" s="42" t="n">
@@ -12414,16 +13155,16 @@
         <v>2102540</v>
       </c>
       <c r="E5" s="42" t="n">
-        <v>1577720</v>
+        <v>1625420</v>
       </c>
       <c r="F5" s="42" t="n">
         <v>231000</v>
       </c>
       <c r="G5" s="40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H5" s="17">
-        <f>G5*'02_Leviers'!$D$16</f>
+        <f>G5*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I5" s="42" t="n">
@@ -12455,16 +13196,16 @@
         <v>1898640</v>
       </c>
       <c r="E6" s="42" t="n">
-        <v>1393200</v>
+        <v>1436400</v>
       </c>
       <c r="F6" s="42" t="n">
         <v>209000</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" s="17">
-        <f>G6*'02_Leviers'!$D$16</f>
+        <f>G6*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I6" s="42" t="n">
@@ -12496,16 +13237,16 @@
         <v>1619880</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>1140900</v>
+        <v>1177800</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>178000</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H7" s="17">
-        <f>G7*'02_Leviers'!$D$16</f>
+        <f>G7*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I7" s="42" t="n">
@@ -12537,16 +13278,16 @@
         <v>2280350</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>1640290</v>
+        <v>1692040</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>251000</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H8" s="17">
-        <f>G8*'02_Leviers'!$D$16</f>
+        <f>G8*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I8" s="42" t="n">
@@ -12578,16 +13319,16 @@
         <v>1585200</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>1061030</v>
+        <v>1097030</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>174000</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="17">
-        <f>G9*'02_Leviers'!$D$16</f>
+        <f>G9*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I9" s="42" t="n">
@@ -12619,16 +13360,16 @@
         <v>1483250</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>970570</v>
+        <v>1004320</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>163000</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H10" s="17">
-        <f>G10*'02_Leviers'!$D$16</f>
+        <f>G10*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I10" s="42" t="n">
@@ -12660,16 +13401,16 @@
         <v>1044500</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>761720</v>
+        <v>784220</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>115000</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" s="17">
-        <f>G11*'02_Leviers'!$D$16</f>
+        <f>G11*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I11" s="42" t="n">
@@ -12701,16 +13442,16 @@
         <v>835600</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>600560</v>
+        <v>618560</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>92000</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="17">
-        <f>G12*'02_Leviers'!$D$16</f>
+        <f>G12*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I12" s="42" t="n">
@@ -12742,16 +13483,16 @@
         <v>835600</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>600560</v>
+        <v>618560</v>
       </c>
       <c r="F13" s="42" t="n">
         <v>92000</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="17">
-        <f>G13*'02_Leviers'!$D$16</f>
+        <f>G13*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I13" s="42" t="n">
@@ -12783,16 +13524,16 @@
         <v>1130470</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>730680</v>
+        <v>768030</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>124000</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" s="17">
-        <f>G14*'02_Leviers'!$D$16</f>
+        <f>G14*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I14" s="42" t="n">
@@ -12824,16 +13565,16 @@
         <v>887850</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>620230</v>
+        <v>649480</v>
       </c>
       <c r="F15" s="42" t="n">
         <v>98000</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="17">
-        <f>G15*'02_Leviers'!$D$16</f>
+        <f>G15*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I15" s="42" t="n">
@@ -12865,16 +13606,16 @@
         <v>980230</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>700980</v>
+        <v>722130</v>
       </c>
       <c r="F16" s="42" t="n">
         <v>108000</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="17">
-        <f>G16*'02_Leviers'!$D$16</f>
+        <f>G16*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I16" s="42" t="n">
@@ -12906,16 +13647,16 @@
         <v>835600</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>598960</v>
+        <v>616960</v>
       </c>
       <c r="F17" s="42" t="n">
         <v>92000</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="17">
-        <f>G17*'02_Leviers'!$D$16</f>
+        <f>G17*'02_Leviers'!$D$15</f>
         <v/>
       </c>
       <c r="I17" s="42" t="n">
@@ -13351,7 +14092,7 @@
         <v/>
       </c>
       <c r="X3" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y3" s="53">
@@ -13363,7 +14104,7 @@
         <v/>
       </c>
       <c r="AA3" s="53">
-        <f>IF(F3=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F3=1,IFERROR(H3/J3,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB3" s="51">
@@ -13383,15 +14124,15 @@
         <v/>
       </c>
       <c r="AF3" s="43">
-        <f>IF(E3="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E3="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG3" s="43">
-        <f>IF(E3="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E3="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH3" s="17">
-        <f>AD3*AE3*AF3+AB3*'02_Leviers'!$D$17</f>
+        <f>AD3*AE3*AF3+AB3*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI3" s="51">
@@ -13407,7 +14148,7 @@
         <v/>
       </c>
       <c r="AL3" s="17">
-        <f>AB3*'02_Leviers'!$D$15+H3*S3*(1+Y3)</f>
+        <f>H3*S3*(1+Y3)</f>
         <v/>
       </c>
       <c r="AM3" s="55">
@@ -13521,7 +14262,7 @@
         <v/>
       </c>
       <c r="X4" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y4" s="53">
@@ -13533,7 +14274,7 @@
         <v/>
       </c>
       <c r="AA4" s="53">
-        <f>IF(F4=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F4=1,IFERROR(H4/J4,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB4" s="51">
@@ -13553,15 +14294,15 @@
         <v/>
       </c>
       <c r="AF4" s="43">
-        <f>IF(E4="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E4="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG4" s="43">
-        <f>IF(E4="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E4="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH4" s="17">
-        <f>AD4*AE4*AF4+AB4*'02_Leviers'!$D$17</f>
+        <f>AD4*AE4*AF4+AB4*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI4" s="51">
@@ -13577,7 +14318,7 @@
         <v/>
       </c>
       <c r="AL4" s="17">
-        <f>AB4*'02_Leviers'!$D$15+H4*S4*(1+Y4)</f>
+        <f>H4*S4*(1+Y4)</f>
         <v/>
       </c>
       <c r="AM4" s="55">
@@ -13691,7 +14432,7 @@
         <v/>
       </c>
       <c r="X5" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y5" s="53">
@@ -13703,7 +14444,7 @@
         <v/>
       </c>
       <c r="AA5" s="53">
-        <f>IF(F5=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F5=1,IFERROR(H5/J5,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB5" s="51">
@@ -13723,15 +14464,15 @@
         <v/>
       </c>
       <c r="AF5" s="43">
-        <f>IF(E5="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E5="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG5" s="43">
-        <f>IF(E5="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E5="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH5" s="17">
-        <f>AD5*AE5*AF5+AB5*'02_Leviers'!$D$17</f>
+        <f>AD5*AE5*AF5+AB5*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI5" s="51">
@@ -13747,7 +14488,7 @@
         <v/>
       </c>
       <c r="AL5" s="17">
-        <f>AB5*'02_Leviers'!$D$15+H5*S5*(1+Y5)</f>
+        <f>H5*S5*(1+Y5)</f>
         <v/>
       </c>
       <c r="AM5" s="55">
@@ -13861,7 +14602,7 @@
         <v/>
       </c>
       <c r="X6" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y6" s="53">
@@ -13873,7 +14614,7 @@
         <v/>
       </c>
       <c r="AA6" s="53">
-        <f>IF(F6=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F6=1,IFERROR(H6/J6,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB6" s="51">
@@ -13893,15 +14634,15 @@
         <v/>
       </c>
       <c r="AF6" s="43">
-        <f>IF(E6="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E6="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG6" s="43">
-        <f>IF(E6="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E6="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH6" s="17">
-        <f>AD6*AE6*AF6+AB6*'02_Leviers'!$D$17</f>
+        <f>AD6*AE6*AF6+AB6*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI6" s="51">
@@ -13917,7 +14658,7 @@
         <v/>
       </c>
       <c r="AL6" s="17">
-        <f>AB6*'02_Leviers'!$D$15+H6*S6*(1+Y6)</f>
+        <f>H6*S6*(1+Y6)</f>
         <v/>
       </c>
       <c r="AM6" s="55">
@@ -14031,7 +14772,7 @@
         <v/>
       </c>
       <c r="X7" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y7" s="53">
@@ -14043,7 +14784,7 @@
         <v/>
       </c>
       <c r="AA7" s="53">
-        <f>IF(F7=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F7=1,IFERROR(H7/J7,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB7" s="51">
@@ -14063,15 +14804,15 @@
         <v/>
       </c>
       <c r="AF7" s="43">
-        <f>IF(E7="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E7="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG7" s="43">
-        <f>IF(E7="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E7="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH7" s="17">
-        <f>AD7*AE7*AF7+AB7*'02_Leviers'!$D$17</f>
+        <f>AD7*AE7*AF7+AB7*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI7" s="51">
@@ -14087,7 +14828,7 @@
         <v/>
       </c>
       <c r="AL7" s="17">
-        <f>AB7*'02_Leviers'!$D$15+H7*S7*(1+Y7)</f>
+        <f>H7*S7*(1+Y7)</f>
         <v/>
       </c>
       <c r="AM7" s="55">
@@ -14201,7 +14942,7 @@
         <v/>
       </c>
       <c r="X8" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y8" s="53">
@@ -14213,7 +14954,7 @@
         <v/>
       </c>
       <c r="AA8" s="53">
-        <f>IF(F8=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F8=1,IFERROR(H8/J8,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB8" s="51">
@@ -14233,15 +14974,15 @@
         <v/>
       </c>
       <c r="AF8" s="43">
-        <f>IF(E8="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E8="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG8" s="43">
-        <f>IF(E8="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E8="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH8" s="17">
-        <f>AD8*AE8*AF8+AB8*'02_Leviers'!$D$17</f>
+        <f>AD8*AE8*AF8+AB8*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI8" s="51">
@@ -14257,7 +14998,7 @@
         <v/>
       </c>
       <c r="AL8" s="17">
-        <f>AB8*'02_Leviers'!$D$15+H8*S8*(1+Y8)</f>
+        <f>H8*S8*(1+Y8)</f>
         <v/>
       </c>
       <c r="AM8" s="55">
@@ -14371,7 +15112,7 @@
         <v/>
       </c>
       <c r="X9" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y9" s="53">
@@ -14383,7 +15124,7 @@
         <v/>
       </c>
       <c r="AA9" s="53">
-        <f>IF(F9=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F9=1,IFERROR(H9/J9,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB9" s="51">
@@ -14403,15 +15144,15 @@
         <v/>
       </c>
       <c r="AF9" s="43">
-        <f>IF(E9="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E9="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG9" s="43">
-        <f>IF(E9="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E9="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH9" s="17">
-        <f>AD9*AE9*AF9+AB9*'02_Leviers'!$D$17</f>
+        <f>AD9*AE9*AF9+AB9*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI9" s="51">
@@ -14427,7 +15168,7 @@
         <v/>
       </c>
       <c r="AL9" s="17">
-        <f>AB9*'02_Leviers'!$D$15+H9*S9*(1+Y9)</f>
+        <f>H9*S9*(1+Y9)</f>
         <v/>
       </c>
       <c r="AM9" s="55">
@@ -14541,7 +15282,7 @@
         <v/>
       </c>
       <c r="X10" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y10" s="53">
@@ -14553,7 +15294,7 @@
         <v/>
       </c>
       <c r="AA10" s="53">
-        <f>IF(F10=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F10=1,IFERROR(H10/J10,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB10" s="51">
@@ -14573,15 +15314,15 @@
         <v/>
       </c>
       <c r="AF10" s="43">
-        <f>IF(E10="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E10="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG10" s="43">
-        <f>IF(E10="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E10="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH10" s="17">
-        <f>AD10*AE10*AF10+AB10*'02_Leviers'!$D$17</f>
+        <f>AD10*AE10*AF10+AB10*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI10" s="51">
@@ -14597,7 +15338,7 @@
         <v/>
       </c>
       <c r="AL10" s="17">
-        <f>AB10*'02_Leviers'!$D$15+H10*S10*(1+Y10)</f>
+        <f>H10*S10*(1+Y10)</f>
         <v/>
       </c>
       <c r="AM10" s="55">
@@ -14711,7 +15452,7 @@
         <v/>
       </c>
       <c r="X11" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y11" s="53">
@@ -14723,7 +15464,7 @@
         <v/>
       </c>
       <c r="AA11" s="53">
-        <f>IF(F11=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F11=1,IFERROR(H11/J11,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB11" s="51">
@@ -14743,15 +15484,15 @@
         <v/>
       </c>
       <c r="AF11" s="43">
-        <f>IF(E11="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E11="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG11" s="43">
-        <f>IF(E11="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E11="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH11" s="17">
-        <f>AD11*AE11*AF11+AB11*'02_Leviers'!$D$17</f>
+        <f>AD11*AE11*AF11+AB11*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI11" s="51">
@@ -14767,7 +15508,7 @@
         <v/>
       </c>
       <c r="AL11" s="17">
-        <f>AB11*'02_Leviers'!$D$15+H11*S11*(1+Y11)</f>
+        <f>H11*S11*(1+Y11)</f>
         <v/>
       </c>
       <c r="AM11" s="55">
@@ -14881,7 +15622,7 @@
         <v/>
       </c>
       <c r="X12" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y12" s="53">
@@ -14893,7 +15634,7 @@
         <v/>
       </c>
       <c r="AA12" s="53">
-        <f>IF(F12=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F12=1,IFERROR(H12/J12,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB12" s="51">
@@ -14913,15 +15654,15 @@
         <v/>
       </c>
       <c r="AF12" s="43">
-        <f>IF(E12="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E12="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG12" s="43">
-        <f>IF(E12="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E12="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH12" s="17">
-        <f>AD12*AE12*AF12+AB12*'02_Leviers'!$D$17</f>
+        <f>AD12*AE12*AF12+AB12*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI12" s="51">
@@ -14937,7 +15678,7 @@
         <v/>
       </c>
       <c r="AL12" s="17">
-        <f>AB12*'02_Leviers'!$D$15+H12*S12*(1+Y12)</f>
+        <f>H12*S12*(1+Y12)</f>
         <v/>
       </c>
       <c r="AM12" s="55">
@@ -15051,7 +15792,7 @@
         <v/>
       </c>
       <c r="X13" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y13" s="53">
@@ -15063,7 +15804,7 @@
         <v/>
       </c>
       <c r="AA13" s="53">
-        <f>IF(F13=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F13=1,IFERROR(H13/J13,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB13" s="51">
@@ -15083,15 +15824,15 @@
         <v/>
       </c>
       <c r="AF13" s="43">
-        <f>IF(E13="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E13="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG13" s="43">
-        <f>IF(E13="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E13="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH13" s="17">
-        <f>AD13*AE13*AF13+AB13*'02_Leviers'!$D$17</f>
+        <f>AD13*AE13*AF13+AB13*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI13" s="51">
@@ -15107,7 +15848,7 @@
         <v/>
       </c>
       <c r="AL13" s="17">
-        <f>AB13*'02_Leviers'!$D$15+H13*S13*(1+Y13)</f>
+        <f>H13*S13*(1+Y13)</f>
         <v/>
       </c>
       <c r="AM13" s="55">
@@ -15221,7 +15962,7 @@
         <v/>
       </c>
       <c r="X14" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y14" s="53">
@@ -15233,7 +15974,7 @@
         <v/>
       </c>
       <c r="AA14" s="53">
-        <f>IF(F14=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F14=1,IFERROR(H14/J14,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB14" s="51">
@@ -15253,15 +15994,15 @@
         <v/>
       </c>
       <c r="AF14" s="43">
-        <f>IF(E14="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E14="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG14" s="43">
-        <f>IF(E14="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E14="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH14" s="17">
-        <f>AD14*AE14*AF14+AB14*'02_Leviers'!$D$17</f>
+        <f>AD14*AE14*AF14+AB14*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI14" s="51">
@@ -15277,7 +16018,7 @@
         <v/>
       </c>
       <c r="AL14" s="17">
-        <f>AB14*'02_Leviers'!$D$15+H14*S14*(1+Y14)</f>
+        <f>H14*S14*(1+Y14)</f>
         <v/>
       </c>
       <c r="AM14" s="55">
@@ -15391,7 +16132,7 @@
         <v/>
       </c>
       <c r="X15" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y15" s="53">
@@ -15403,7 +16144,7 @@
         <v/>
       </c>
       <c r="AA15" s="53">
-        <f>IF(F15=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F15=1,IFERROR(H15/J15,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB15" s="51">
@@ -15423,15 +16164,15 @@
         <v/>
       </c>
       <c r="AF15" s="43">
-        <f>IF(E15="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E15="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG15" s="43">
-        <f>IF(E15="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E15="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH15" s="17">
-        <f>AD15*AE15*AF15+AB15*'02_Leviers'!$D$17</f>
+        <f>AD15*AE15*AF15+AB15*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI15" s="51">
@@ -15447,7 +16188,7 @@
         <v/>
       </c>
       <c r="AL15" s="17">
-        <f>AB15*'02_Leviers'!$D$15+H15*S15*(1+Y15)</f>
+        <f>H15*S15*(1+Y15)</f>
         <v/>
       </c>
       <c r="AM15" s="55">
@@ -15561,7 +16302,7 @@
         <v/>
       </c>
       <c r="X16" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y16" s="53">
@@ -15573,7 +16314,7 @@
         <v/>
       </c>
       <c r="AA16" s="53">
-        <f>IF(F16=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F16=1,IFERROR(H16/J16,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB16" s="51">
@@ -15593,15 +16334,15 @@
         <v/>
       </c>
       <c r="AF16" s="43">
-        <f>IF(E16="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E16="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG16" s="43">
-        <f>IF(E16="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E16="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH16" s="17">
-        <f>AD16*AE16*AF16+AB16*'02_Leviers'!$D$17</f>
+        <f>AD16*AE16*AF16+AB16*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI16" s="51">
@@ -15617,7 +16358,7 @@
         <v/>
       </c>
       <c r="AL16" s="17">
-        <f>AB16*'02_Leviers'!$D$15+H16*S16*(1+Y16)</f>
+        <f>H16*S16*(1+Y16)</f>
         <v/>
       </c>
       <c r="AM16" s="55">
@@ -15731,7 +16472,7 @@
         <v/>
       </c>
       <c r="X17" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y17" s="53">
@@ -15743,7 +16484,7 @@
         <v/>
       </c>
       <c r="AA17" s="53">
-        <f>IF(F17=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F17=1,IFERROR(H17/J17,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB17" s="51">
@@ -15763,15 +16504,15 @@
         <v/>
       </c>
       <c r="AF17" s="43">
-        <f>IF(E17="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E17="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG17" s="43">
-        <f>IF(E17="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E17="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH17" s="17">
-        <f>AD17*AE17*AF17+AB17*'02_Leviers'!$D$17</f>
+        <f>AD17*AE17*AF17+AB17*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI17" s="51">
@@ -15787,7 +16528,7 @@
         <v/>
       </c>
       <c r="AL17" s="17">
-        <f>AB17*'02_Leviers'!$D$15+H17*S17*(1+Y17)</f>
+        <f>H17*S17*(1+Y17)</f>
         <v/>
       </c>
       <c r="AM17" s="55">
@@ -15901,7 +16642,7 @@
         <v/>
       </c>
       <c r="X18" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y18" s="53">
@@ -15913,7 +16654,7 @@
         <v/>
       </c>
       <c r="AA18" s="53">
-        <f>IF(F18=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F18=1,IFERROR(H18/J18,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB18" s="51">
@@ -15933,15 +16674,15 @@
         <v/>
       </c>
       <c r="AF18" s="43">
-        <f>IF(E18="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E18="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>IF(E18="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E18="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH18" s="17">
-        <f>AD18*AE18*AF18+AB18*'02_Leviers'!$D$17</f>
+        <f>AD18*AE18*AF18+AB18*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI18" s="51">
@@ -15957,7 +16698,7 @@
         <v/>
       </c>
       <c r="AL18" s="17">
-        <f>AB18*'02_Leviers'!$D$15+H18*S18*(1+Y18)</f>
+        <f>H18*S18*(1+Y18)</f>
         <v/>
       </c>
       <c r="AM18" s="55">
@@ -16071,7 +16812,7 @@
         <v/>
       </c>
       <c r="X19" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y19" s="53">
@@ -16083,7 +16824,7 @@
         <v/>
       </c>
       <c r="AA19" s="53">
-        <f>IF(F19=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F19=1,IFERROR(H19/J19,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB19" s="51">
@@ -16103,15 +16844,15 @@
         <v/>
       </c>
       <c r="AF19" s="43">
-        <f>IF(E19="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E19="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG19" s="43">
-        <f>IF(E19="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E19="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH19" s="17">
-        <f>AD19*AE19*AF19+AB19*'02_Leviers'!$D$17</f>
+        <f>AD19*AE19*AF19+AB19*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI19" s="51">
@@ -16127,7 +16868,7 @@
         <v/>
       </c>
       <c r="AL19" s="17">
-        <f>AB19*'02_Leviers'!$D$15+H19*S19*(1+Y19)</f>
+        <f>H19*S19*(1+Y19)</f>
         <v/>
       </c>
       <c r="AM19" s="55">
@@ -16241,7 +16982,7 @@
         <v/>
       </c>
       <c r="X20" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y20" s="53">
@@ -16253,7 +16994,7 @@
         <v/>
       </c>
       <c r="AA20" s="53">
-        <f>IF(F20=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F20=1,IFERROR(H20/J20,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB20" s="51">
@@ -16273,15 +17014,15 @@
         <v/>
       </c>
       <c r="AF20" s="43">
-        <f>IF(E20="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E20="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG20" s="43">
-        <f>IF(E20="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E20="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH20" s="17">
-        <f>AD20*AE20*AF20+AB20*'02_Leviers'!$D$17</f>
+        <f>AD20*AE20*AF20+AB20*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI20" s="51">
@@ -16297,7 +17038,7 @@
         <v/>
       </c>
       <c r="AL20" s="17">
-        <f>AB20*'02_Leviers'!$D$15+H20*S20*(1+Y20)</f>
+        <f>H20*S20*(1+Y20)</f>
         <v/>
       </c>
       <c r="AM20" s="55">
@@ -16411,7 +17152,7 @@
         <v/>
       </c>
       <c r="X21" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y21" s="53">
@@ -16423,7 +17164,7 @@
         <v/>
       </c>
       <c r="AA21" s="53">
-        <f>IF(F21=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F21=1,IFERROR(H21/J21,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB21" s="51">
@@ -16443,15 +17184,15 @@
         <v/>
       </c>
       <c r="AF21" s="43">
-        <f>IF(E21="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E21="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG21" s="43">
-        <f>IF(E21="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E21="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH21" s="17">
-        <f>AD21*AE21*AF21+AB21*'02_Leviers'!$D$17</f>
+        <f>AD21*AE21*AF21+AB21*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI21" s="51">
@@ -16467,7 +17208,7 @@
         <v/>
       </c>
       <c r="AL21" s="17">
-        <f>AB21*'02_Leviers'!$D$15+H21*S21*(1+Y21)</f>
+        <f>H21*S21*(1+Y21)</f>
         <v/>
       </c>
       <c r="AM21" s="55">
@@ -16581,7 +17322,7 @@
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y22" s="53">
@@ -16593,7 +17334,7 @@
         <v/>
       </c>
       <c r="AA22" s="53">
-        <f>IF(F22=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F22=1,IFERROR(H22/J22,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB22" s="51">
@@ -16613,15 +17354,15 @@
         <v/>
       </c>
       <c r="AF22" s="43">
-        <f>IF(E22="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E22="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>IF(E22="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E22="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH22" s="17">
-        <f>AD22*AE22*AF22+AB22*'02_Leviers'!$D$17</f>
+        <f>AD22*AE22*AF22+AB22*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI22" s="51">
@@ -16637,7 +17378,7 @@
         <v/>
       </c>
       <c r="AL22" s="17">
-        <f>AB22*'02_Leviers'!$D$15+H22*S22*(1+Y22)</f>
+        <f>H22*S22*(1+Y22)</f>
         <v/>
       </c>
       <c r="AM22" s="55">
@@ -16751,7 +17492,7 @@
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y23" s="53">
@@ -16763,7 +17504,7 @@
         <v/>
       </c>
       <c r="AA23" s="53">
-        <f>IF(F23=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F23=1,IFERROR(H23/J23,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB23" s="51">
@@ -16783,15 +17524,15 @@
         <v/>
       </c>
       <c r="AF23" s="43">
-        <f>IF(E23="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E23="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG23" s="43">
-        <f>IF(E23="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E23="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH23" s="17">
-        <f>AD23*AE23*AF23+AB23*'02_Leviers'!$D$17</f>
+        <f>AD23*AE23*AF23+AB23*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI23" s="51">
@@ -16807,7 +17548,7 @@
         <v/>
       </c>
       <c r="AL23" s="17">
-        <f>AB23*'02_Leviers'!$D$15+H23*S23*(1+Y23)</f>
+        <f>H23*S23*(1+Y23)</f>
         <v/>
       </c>
       <c r="AM23" s="55">
@@ -16921,7 +17662,7 @@
         <v/>
       </c>
       <c r="X24" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y24" s="53">
@@ -16933,7 +17674,7 @@
         <v/>
       </c>
       <c r="AA24" s="53">
-        <f>IF(F24=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F24=1,IFERROR(H24/J24,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB24" s="51">
@@ -16953,15 +17694,15 @@
         <v/>
       </c>
       <c r="AF24" s="43">
-        <f>IF(E24="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E24="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG24" s="43">
-        <f>IF(E24="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E24="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH24" s="17">
-        <f>AD24*AE24*AF24+AB24*'02_Leviers'!$D$17</f>
+        <f>AD24*AE24*AF24+AB24*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI24" s="51">
@@ -16977,7 +17718,7 @@
         <v/>
       </c>
       <c r="AL24" s="17">
-        <f>AB24*'02_Leviers'!$D$15+H24*S24*(1+Y24)</f>
+        <f>H24*S24*(1+Y24)</f>
         <v/>
       </c>
       <c r="AM24" s="55">
@@ -17091,7 +17832,7 @@
         <v/>
       </c>
       <c r="X25" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y25" s="53">
@@ -17103,7 +17844,7 @@
         <v/>
       </c>
       <c r="AA25" s="53">
-        <f>IF(F25=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F25=1,IFERROR(H25/J25,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB25" s="51">
@@ -17123,15 +17864,15 @@
         <v/>
       </c>
       <c r="AF25" s="43">
-        <f>IF(E25="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E25="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG25" s="43">
-        <f>IF(E25="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E25="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH25" s="17">
-        <f>AD25*AE25*AF25+AB25*'02_Leviers'!$D$17</f>
+        <f>AD25*AE25*AF25+AB25*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI25" s="51">
@@ -17147,7 +17888,7 @@
         <v/>
       </c>
       <c r="AL25" s="17">
-        <f>AB25*'02_Leviers'!$D$15+H25*S25*(1+Y25)</f>
+        <f>H25*S25*(1+Y25)</f>
         <v/>
       </c>
       <c r="AM25" s="55">
@@ -17261,7 +18002,7 @@
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y26" s="53">
@@ -17273,7 +18014,7 @@
         <v/>
       </c>
       <c r="AA26" s="53">
-        <f>IF(F26=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F26=1,IFERROR(H26/J26,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB26" s="51">
@@ -17293,15 +18034,15 @@
         <v/>
       </c>
       <c r="AF26" s="43">
-        <f>IF(E26="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E26="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>IF(E26="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E26="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH26" s="17">
-        <f>AD26*AE26*AF26+AB26*'02_Leviers'!$D$17</f>
+        <f>AD26*AE26*AF26+AB26*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI26" s="51">
@@ -17317,7 +18058,7 @@
         <v/>
       </c>
       <c r="AL26" s="17">
-        <f>AB26*'02_Leviers'!$D$15+H26*S26*(1+Y26)</f>
+        <f>H26*S26*(1+Y26)</f>
         <v/>
       </c>
       <c r="AM26" s="55">
@@ -17431,7 +18172,7 @@
         <v/>
       </c>
       <c r="X27" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y27" s="53">
@@ -17443,7 +18184,7 @@
         <v/>
       </c>
       <c r="AA27" s="53">
-        <f>IF(F27=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F27=1,IFERROR(H27/J27,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB27" s="51">
@@ -17463,15 +18204,15 @@
         <v/>
       </c>
       <c r="AF27" s="43">
-        <f>IF(E27="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E27="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG27" s="43">
-        <f>IF(E27="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E27="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH27" s="17">
-        <f>AD27*AE27*AF27+AB27*'02_Leviers'!$D$17</f>
+        <f>AD27*AE27*AF27+AB27*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI27" s="51">
@@ -17487,7 +18228,7 @@
         <v/>
       </c>
       <c r="AL27" s="17">
-        <f>AB27*'02_Leviers'!$D$15+H27*S27*(1+Y27)</f>
+        <f>H27*S27*(1+Y27)</f>
         <v/>
       </c>
       <c r="AM27" s="55">
@@ -17601,7 +18342,7 @@
         <v/>
       </c>
       <c r="X28" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y28" s="53">
@@ -17613,7 +18354,7 @@
         <v/>
       </c>
       <c r="AA28" s="53">
-        <f>IF(F28=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F28=1,IFERROR(H28/J28,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB28" s="51">
@@ -17633,15 +18374,15 @@
         <v/>
       </c>
       <c r="AF28" s="43">
-        <f>IF(E28="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E28="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG28" s="43">
-        <f>IF(E28="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E28="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH28" s="17">
-        <f>AD28*AE28*AF28+AB28*'02_Leviers'!$D$17</f>
+        <f>AD28*AE28*AF28+AB28*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI28" s="51">
@@ -17657,7 +18398,7 @@
         <v/>
       </c>
       <c r="AL28" s="17">
-        <f>AB28*'02_Leviers'!$D$15+H28*S28*(1+Y28)</f>
+        <f>H28*S28*(1+Y28)</f>
         <v/>
       </c>
       <c r="AM28" s="55">
@@ -17771,7 +18512,7 @@
         <v/>
       </c>
       <c r="X29" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y29" s="53">
@@ -17783,7 +18524,7 @@
         <v/>
       </c>
       <c r="AA29" s="53">
-        <f>IF(F29=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F29=1,IFERROR(H29/J29,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB29" s="51">
@@ -17803,15 +18544,15 @@
         <v/>
       </c>
       <c r="AF29" s="43">
-        <f>IF(E29="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E29="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG29" s="43">
-        <f>IF(E29="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E29="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH29" s="17">
-        <f>AD29*AE29*AF29+AB29*'02_Leviers'!$D$17</f>
+        <f>AD29*AE29*AF29+AB29*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI29" s="51">
@@ -17827,7 +18568,7 @@
         <v/>
       </c>
       <c r="AL29" s="17">
-        <f>AB29*'02_Leviers'!$D$15+H29*S29*(1+Y29)</f>
+        <f>H29*S29*(1+Y29)</f>
         <v/>
       </c>
       <c r="AM29" s="55">
@@ -17941,7 +18682,7 @@
         <v/>
       </c>
       <c r="X30" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y30" s="53">
@@ -17953,7 +18694,7 @@
         <v/>
       </c>
       <c r="AA30" s="53">
-        <f>IF(F30=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F30=1,IFERROR(H30/J30,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB30" s="51">
@@ -17973,15 +18714,15 @@
         <v/>
       </c>
       <c r="AF30" s="43">
-        <f>IF(E30="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E30="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG30" s="43">
-        <f>IF(E30="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E30="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH30" s="17">
-        <f>AD30*AE30*AF30+AB30*'02_Leviers'!$D$17</f>
+        <f>AD30*AE30*AF30+AB30*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI30" s="51">
@@ -17997,7 +18738,7 @@
         <v/>
       </c>
       <c r="AL30" s="17">
-        <f>AB30*'02_Leviers'!$D$15+H30*S30*(1+Y30)</f>
+        <f>H30*S30*(1+Y30)</f>
         <v/>
       </c>
       <c r="AM30" s="55">
@@ -18111,7 +18852,7 @@
         <v/>
       </c>
       <c r="X31" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y31" s="53">
@@ -18123,7 +18864,7 @@
         <v/>
       </c>
       <c r="AA31" s="53">
-        <f>IF(F31=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F31=1,IFERROR(H31/J31,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB31" s="51">
@@ -18143,15 +18884,15 @@
         <v/>
       </c>
       <c r="AF31" s="43">
-        <f>IF(E31="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E31="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG31" s="43">
-        <f>IF(E31="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E31="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH31" s="17">
-        <f>AD31*AE31*AF31+AB31*'02_Leviers'!$D$17</f>
+        <f>AD31*AE31*AF31+AB31*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI31" s="51">
@@ -18167,7 +18908,7 @@
         <v/>
       </c>
       <c r="AL31" s="17">
-        <f>AB31*'02_Leviers'!$D$15+H31*S31*(1+Y31)</f>
+        <f>H31*S31*(1+Y31)</f>
         <v/>
       </c>
       <c r="AM31" s="55">
@@ -18281,7 +19022,7 @@
         <v/>
       </c>
       <c r="X32" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y32" s="53">
@@ -18293,7 +19034,7 @@
         <v/>
       </c>
       <c r="AA32" s="53">
-        <f>IF(F32=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F32=1,IFERROR(H32/J32,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB32" s="51">
@@ -18313,15 +19054,15 @@
         <v/>
       </c>
       <c r="AF32" s="43">
-        <f>IF(E32="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E32="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG32" s="43">
-        <f>IF(E32="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E32="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH32" s="17">
-        <f>AD32*AE32*AF32+AB32*'02_Leviers'!$D$17</f>
+        <f>AD32*AE32*AF32+AB32*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI32" s="51">
@@ -18337,7 +19078,7 @@
         <v/>
       </c>
       <c r="AL32" s="17">
-        <f>AB32*'02_Leviers'!$D$15+H32*S32*(1+Y32)</f>
+        <f>H32*S32*(1+Y32)</f>
         <v/>
       </c>
       <c r="AM32" s="55">
@@ -18451,7 +19192,7 @@
         <v/>
       </c>
       <c r="X33" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y33" s="53">
@@ -18463,7 +19204,7 @@
         <v/>
       </c>
       <c r="AA33" s="53">
-        <f>IF(F33=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F33=1,IFERROR(H33/J33,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB33" s="51">
@@ -18483,15 +19224,15 @@
         <v/>
       </c>
       <c r="AF33" s="43">
-        <f>IF(E33="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E33="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG33" s="43">
-        <f>IF(E33="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E33="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH33" s="17">
-        <f>AD33*AE33*AF33+AB33*'02_Leviers'!$D$17</f>
+        <f>AD33*AE33*AF33+AB33*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI33" s="51">
@@ -18507,7 +19248,7 @@
         <v/>
       </c>
       <c r="AL33" s="17">
-        <f>AB33*'02_Leviers'!$D$15+H33*S33*(1+Y33)</f>
+        <f>H33*S33*(1+Y33)</f>
         <v/>
       </c>
       <c r="AM33" s="55">
@@ -18621,7 +19362,7 @@
         <v/>
       </c>
       <c r="X34" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y34" s="53">
@@ -18633,7 +19374,7 @@
         <v/>
       </c>
       <c r="AA34" s="53">
-        <f>IF(F34=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F34=1,IFERROR(H34/J34,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB34" s="51">
@@ -18653,15 +19394,15 @@
         <v/>
       </c>
       <c r="AF34" s="43">
-        <f>IF(E34="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E34="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG34" s="43">
-        <f>IF(E34="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E34="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH34" s="17">
-        <f>AD34*AE34*AF34+AB34*'02_Leviers'!$D$17</f>
+        <f>AD34*AE34*AF34+AB34*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI34" s="51">
@@ -18677,7 +19418,7 @@
         <v/>
       </c>
       <c r="AL34" s="17">
-        <f>AB34*'02_Leviers'!$D$15+H34*S34*(1+Y34)</f>
+        <f>H34*S34*(1+Y34)</f>
         <v/>
       </c>
       <c r="AM34" s="55">
@@ -18791,7 +19532,7 @@
         <v/>
       </c>
       <c r="X35" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y35" s="53">
@@ -18803,7 +19544,7 @@
         <v/>
       </c>
       <c r="AA35" s="53">
-        <f>IF(F35=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F35=1,IFERROR(H35/J35,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB35" s="51">
@@ -18823,15 +19564,15 @@
         <v/>
       </c>
       <c r="AF35" s="43">
-        <f>IF(E35="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E35="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG35" s="43">
-        <f>IF(E35="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E35="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH35" s="17">
-        <f>AD35*AE35*AF35+AB35*'02_Leviers'!$D$17</f>
+        <f>AD35*AE35*AF35+AB35*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI35" s="51">
@@ -18847,7 +19588,7 @@
         <v/>
       </c>
       <c r="AL35" s="17">
-        <f>AB35*'02_Leviers'!$D$15+H35*S35*(1+Y35)</f>
+        <f>H35*S35*(1+Y35)</f>
         <v/>
       </c>
       <c r="AM35" s="55">
@@ -18961,7 +19702,7 @@
         <v/>
       </c>
       <c r="X36" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y36" s="53">
@@ -18973,7 +19714,7 @@
         <v/>
       </c>
       <c r="AA36" s="53">
-        <f>IF(F36=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F36=1,IFERROR(H36/J36,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB36" s="51">
@@ -18993,15 +19734,15 @@
         <v/>
       </c>
       <c r="AF36" s="43">
-        <f>IF(E36="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E36="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG36" s="43">
-        <f>IF(E36="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E36="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH36" s="17">
-        <f>AD36*AE36*AF36+AB36*'02_Leviers'!$D$17</f>
+        <f>AD36*AE36*AF36+AB36*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI36" s="51">
@@ -19017,7 +19758,7 @@
         <v/>
       </c>
       <c r="AL36" s="17">
-        <f>AB36*'02_Leviers'!$D$15+H36*S36*(1+Y36)</f>
+        <f>H36*S36*(1+Y36)</f>
         <v/>
       </c>
       <c r="AM36" s="55">
@@ -19131,7 +19872,7 @@
         <v/>
       </c>
       <c r="X37" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y37" s="53">
@@ -19143,7 +19884,7 @@
         <v/>
       </c>
       <c r="AA37" s="53">
-        <f>IF(F37=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F37=1,IFERROR(H37/J37,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB37" s="51">
@@ -19163,15 +19904,15 @@
         <v/>
       </c>
       <c r="AF37" s="43">
-        <f>IF(E37="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E37="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG37" s="43">
-        <f>IF(E37="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E37="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH37" s="17">
-        <f>AD37*AE37*AF37+AB37*'02_Leviers'!$D$17</f>
+        <f>AD37*AE37*AF37+AB37*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI37" s="51">
@@ -19187,7 +19928,7 @@
         <v/>
       </c>
       <c r="AL37" s="17">
-        <f>AB37*'02_Leviers'!$D$15+H37*S37*(1+Y37)</f>
+        <f>H37*S37*(1+Y37)</f>
         <v/>
       </c>
       <c r="AM37" s="55">
@@ -19301,7 +20042,7 @@
         <v/>
       </c>
       <c r="X38" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y38" s="53">
@@ -19313,7 +20054,7 @@
         <v/>
       </c>
       <c r="AA38" s="53">
-        <f>IF(F38=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F38=1,IFERROR(H38/J38,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB38" s="51">
@@ -19333,15 +20074,15 @@
         <v/>
       </c>
       <c r="AF38" s="43">
-        <f>IF(E38="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E38="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG38" s="43">
-        <f>IF(E38="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E38="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH38" s="17">
-        <f>AD38*AE38*AF38+AB38*'02_Leviers'!$D$17</f>
+        <f>AD38*AE38*AF38+AB38*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI38" s="51">
@@ -19357,7 +20098,7 @@
         <v/>
       </c>
       <c r="AL38" s="17">
-        <f>AB38*'02_Leviers'!$D$15+H38*S38*(1+Y38)</f>
+        <f>H38*S38*(1+Y38)</f>
         <v/>
       </c>
       <c r="AM38" s="55">
@@ -19471,7 +20212,7 @@
         <v/>
       </c>
       <c r="X39" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y39" s="53">
@@ -19483,7 +20224,7 @@
         <v/>
       </c>
       <c r="AA39" s="53">
-        <f>IF(F39=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F39=1,IFERROR(H39/J39,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB39" s="51">
@@ -19503,15 +20244,15 @@
         <v/>
       </c>
       <c r="AF39" s="43">
-        <f>IF(E39="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E39="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG39" s="43">
-        <f>IF(E39="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E39="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH39" s="17">
-        <f>AD39*AE39*AF39+AB39*'02_Leviers'!$D$17</f>
+        <f>AD39*AE39*AF39+AB39*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI39" s="51">
@@ -19527,7 +20268,7 @@
         <v/>
       </c>
       <c r="AL39" s="17">
-        <f>AB39*'02_Leviers'!$D$15+H39*S39*(1+Y39)</f>
+        <f>H39*S39*(1+Y39)</f>
         <v/>
       </c>
       <c r="AM39" s="55">
@@ -19641,7 +20382,7 @@
         <v/>
       </c>
       <c r="X40" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y40" s="53">
@@ -19653,7 +20394,7 @@
         <v/>
       </c>
       <c r="AA40" s="53">
-        <f>IF(F40=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F40=1,IFERROR(H40/J40,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB40" s="51">
@@ -19673,15 +20414,15 @@
         <v/>
       </c>
       <c r="AF40" s="43">
-        <f>IF(E40="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E40="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG40" s="43">
-        <f>IF(E40="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E40="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH40" s="17">
-        <f>AD40*AE40*AF40+AB40*'02_Leviers'!$D$17</f>
+        <f>AD40*AE40*AF40+AB40*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI40" s="51">
@@ -19697,7 +20438,7 @@
         <v/>
       </c>
       <c r="AL40" s="17">
-        <f>AB40*'02_Leviers'!$D$15+H40*S40*(1+Y40)</f>
+        <f>H40*S40*(1+Y40)</f>
         <v/>
       </c>
       <c r="AM40" s="55">
@@ -19811,7 +20552,7 @@
         <v/>
       </c>
       <c r="X41" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y41" s="53">
@@ -19823,7 +20564,7 @@
         <v/>
       </c>
       <c r="AA41" s="53">
-        <f>IF(F41=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F41=1,IFERROR(H41/J41,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB41" s="51">
@@ -19843,15 +20584,15 @@
         <v/>
       </c>
       <c r="AF41" s="43">
-        <f>IF(E41="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E41="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG41" s="43">
-        <f>IF(E41="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E41="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH41" s="17">
-        <f>AD41*AE41*AF41+AB41*'02_Leviers'!$D$17</f>
+        <f>AD41*AE41*AF41+AB41*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI41" s="51">
@@ -19867,7 +20608,7 @@
         <v/>
       </c>
       <c r="AL41" s="17">
-        <f>AB41*'02_Leviers'!$D$15+H41*S41*(1+Y41)</f>
+        <f>H41*S41*(1+Y41)</f>
         <v/>
       </c>
       <c r="AM41" s="55">
@@ -19981,7 +20722,7 @@
         <v/>
       </c>
       <c r="X42" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y42" s="53">
@@ -19993,7 +20734,7 @@
         <v/>
       </c>
       <c r="AA42" s="53">
-        <f>IF(F42=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F42=1,IFERROR(H42/J42,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB42" s="51">
@@ -20013,15 +20754,15 @@
         <v/>
       </c>
       <c r="AF42" s="43">
-        <f>IF(E42="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E42="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG42" s="43">
-        <f>IF(E42="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E42="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH42" s="17">
-        <f>AD42*AE42*AF42+AB42*'02_Leviers'!$D$17</f>
+        <f>AD42*AE42*AF42+AB42*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI42" s="51">
@@ -20037,7 +20778,7 @@
         <v/>
       </c>
       <c r="AL42" s="17">
-        <f>AB42*'02_Leviers'!$D$15+H42*S42*(1+Y42)</f>
+        <f>H42*S42*(1+Y42)</f>
         <v/>
       </c>
       <c r="AM42" s="55">
@@ -20151,7 +20892,7 @@
         <v/>
       </c>
       <c r="X43" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y43" s="53">
@@ -20163,7 +20904,7 @@
         <v/>
       </c>
       <c r="AA43" s="53">
-        <f>IF(F43=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F43=1,IFERROR(H43/J43,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB43" s="51">
@@ -20183,15 +20924,15 @@
         <v/>
       </c>
       <c r="AF43" s="43">
-        <f>IF(E43="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E43="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG43" s="43">
-        <f>IF(E43="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E43="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH43" s="17">
-        <f>AD43*AE43*AF43+AB43*'02_Leviers'!$D$17</f>
+        <f>AD43*AE43*AF43+AB43*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI43" s="51">
@@ -20207,7 +20948,7 @@
         <v/>
       </c>
       <c r="AL43" s="17">
-        <f>AB43*'02_Leviers'!$D$15+H43*S43*(1+Y43)</f>
+        <f>H43*S43*(1+Y43)</f>
         <v/>
       </c>
       <c r="AM43" s="55">
@@ -20321,7 +21062,7 @@
         <v/>
       </c>
       <c r="X44" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y44" s="53">
@@ -20333,7 +21074,7 @@
         <v/>
       </c>
       <c r="AA44" s="53">
-        <f>IF(F44=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F44=1,IFERROR(H44/J44,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB44" s="51">
@@ -20353,15 +21094,15 @@
         <v/>
       </c>
       <c r="AF44" s="43">
-        <f>IF(E44="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E44="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG44" s="43">
-        <f>IF(E44="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E44="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH44" s="17">
-        <f>AD44*AE44*AF44+AB44*'02_Leviers'!$D$17</f>
+        <f>AD44*AE44*AF44+AB44*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI44" s="51">
@@ -20377,7 +21118,7 @@
         <v/>
       </c>
       <c r="AL44" s="17">
-        <f>AB44*'02_Leviers'!$D$15+H44*S44*(1+Y44)</f>
+        <f>H44*S44*(1+Y44)</f>
         <v/>
       </c>
       <c r="AM44" s="55">
@@ -20491,7 +21232,7 @@
         <v/>
       </c>
       <c r="X45" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y45" s="53">
@@ -20503,7 +21244,7 @@
         <v/>
       </c>
       <c r="AA45" s="53">
-        <f>IF(F45=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F45=1,IFERROR(H45/J45,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB45" s="51">
@@ -20523,15 +21264,15 @@
         <v/>
       </c>
       <c r="AF45" s="43">
-        <f>IF(E45="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E45="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG45" s="43">
-        <f>IF(E45="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E45="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH45" s="17">
-        <f>AD45*AE45*AF45+AB45*'02_Leviers'!$D$17</f>
+        <f>AD45*AE45*AF45+AB45*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI45" s="51">
@@ -20547,7 +21288,7 @@
         <v/>
       </c>
       <c r="AL45" s="17">
-        <f>AB45*'02_Leviers'!$D$15+H45*S45*(1+Y45)</f>
+        <f>H45*S45*(1+Y45)</f>
         <v/>
       </c>
       <c r="AM45" s="55">
@@ -20661,7 +21402,7 @@
         <v/>
       </c>
       <c r="X46" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y46" s="53">
@@ -20673,7 +21414,7 @@
         <v/>
       </c>
       <c r="AA46" s="53">
-        <f>IF(F46=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F46=1,IFERROR(H46/J46,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB46" s="51">
@@ -20693,15 +21434,15 @@
         <v/>
       </c>
       <c r="AF46" s="43">
-        <f>IF(E46="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E46="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG46" s="43">
-        <f>IF(E46="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E46="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH46" s="17">
-        <f>AD46*AE46*AF46+AB46*'02_Leviers'!$D$17</f>
+        <f>AD46*AE46*AF46+AB46*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI46" s="51">
@@ -20717,7 +21458,7 @@
         <v/>
       </c>
       <c r="AL46" s="17">
-        <f>AB46*'02_Leviers'!$D$15+H46*S46*(1+Y46)</f>
+        <f>H46*S46*(1+Y46)</f>
         <v/>
       </c>
       <c r="AM46" s="55">
@@ -20831,7 +21572,7 @@
         <v/>
       </c>
       <c r="X47" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y47" s="53">
@@ -20843,7 +21584,7 @@
         <v/>
       </c>
       <c r="AA47" s="53">
-        <f>IF(F47=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F47=1,IFERROR(H47/J47,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB47" s="51">
@@ -20863,15 +21604,15 @@
         <v/>
       </c>
       <c r="AF47" s="43">
-        <f>IF(E47="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E47="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG47" s="43">
-        <f>IF(E47="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E47="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH47" s="17">
-        <f>AD47*AE47*AF47+AB47*'02_Leviers'!$D$17</f>
+        <f>AD47*AE47*AF47+AB47*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI47" s="51">
@@ -20887,7 +21628,7 @@
         <v/>
       </c>
       <c r="AL47" s="17">
-        <f>AB47*'02_Leviers'!$D$15+H47*S47*(1+Y47)</f>
+        <f>H47*S47*(1+Y47)</f>
         <v/>
       </c>
       <c r="AM47" s="55">
@@ -21001,7 +21742,7 @@
         <v/>
       </c>
       <c r="X48" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y48" s="53">
@@ -21013,7 +21754,7 @@
         <v/>
       </c>
       <c r="AA48" s="53">
-        <f>IF(F48=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F48=1,IFERROR(H48/J48,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB48" s="51">
@@ -21033,15 +21774,15 @@
         <v/>
       </c>
       <c r="AF48" s="43">
-        <f>IF(E48="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E48="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG48" s="43">
-        <f>IF(E48="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E48="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH48" s="17">
-        <f>AD48*AE48*AF48+AB48*'02_Leviers'!$D$17</f>
+        <f>AD48*AE48*AF48+AB48*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI48" s="51">
@@ -21057,7 +21798,7 @@
         <v/>
       </c>
       <c r="AL48" s="17">
-        <f>AB48*'02_Leviers'!$D$15+H48*S48*(1+Y48)</f>
+        <f>H48*S48*(1+Y48)</f>
         <v/>
       </c>
       <c r="AM48" s="55">
@@ -21171,7 +21912,7 @@
         <v/>
       </c>
       <c r="X49" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y49" s="53">
@@ -21183,7 +21924,7 @@
         <v/>
       </c>
       <c r="AA49" s="53">
-        <f>IF(F49=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F49=1,IFERROR(H49/J49,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB49" s="51">
@@ -21203,15 +21944,15 @@
         <v/>
       </c>
       <c r="AF49" s="43">
-        <f>IF(E49="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E49="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG49" s="43">
-        <f>IF(E49="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E49="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH49" s="17">
-        <f>AD49*AE49*AF49+AB49*'02_Leviers'!$D$17</f>
+        <f>AD49*AE49*AF49+AB49*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI49" s="51">
@@ -21227,7 +21968,7 @@
         <v/>
       </c>
       <c r="AL49" s="17">
-        <f>AB49*'02_Leviers'!$D$15+H49*S49*(1+Y49)</f>
+        <f>H49*S49*(1+Y49)</f>
         <v/>
       </c>
       <c r="AM49" s="55">
@@ -21341,7 +22082,7 @@
         <v/>
       </c>
       <c r="X50" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y50" s="53">
@@ -21353,7 +22094,7 @@
         <v/>
       </c>
       <c r="AA50" s="53">
-        <f>IF(F50=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F50=1,IFERROR(H50/J50,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB50" s="51">
@@ -21373,15 +22114,15 @@
         <v/>
       </c>
       <c r="AF50" s="43">
-        <f>IF(E50="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E50="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG50" s="43">
-        <f>IF(E50="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E50="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH50" s="17">
-        <f>AD50*AE50*AF50+AB50*'02_Leviers'!$D$17</f>
+        <f>AD50*AE50*AF50+AB50*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI50" s="51">
@@ -21397,7 +22138,7 @@
         <v/>
       </c>
       <c r="AL50" s="17">
-        <f>AB50*'02_Leviers'!$D$15+H50*S50*(1+Y50)</f>
+        <f>H50*S50*(1+Y50)</f>
         <v/>
       </c>
       <c r="AM50" s="55">
@@ -21511,7 +22252,7 @@
         <v/>
       </c>
       <c r="X51" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y51" s="53">
@@ -21523,7 +22264,7 @@
         <v/>
       </c>
       <c r="AA51" s="53">
-        <f>IF(F51=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F51=1,IFERROR(H51/J51,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB51" s="51">
@@ -21543,15 +22284,15 @@
         <v/>
       </c>
       <c r="AF51" s="43">
-        <f>IF(E51="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E51="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG51" s="43">
-        <f>IF(E51="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E51="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH51" s="17">
-        <f>AD51*AE51*AF51+AB51*'02_Leviers'!$D$17</f>
+        <f>AD51*AE51*AF51+AB51*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI51" s="51">
@@ -21567,7 +22308,7 @@
         <v/>
       </c>
       <c r="AL51" s="17">
-        <f>AB51*'02_Leviers'!$D$15+H51*S51*(1+Y51)</f>
+        <f>H51*S51*(1+Y51)</f>
         <v/>
       </c>
       <c r="AM51" s="55">
@@ -21681,7 +22422,7 @@
         <v/>
       </c>
       <c r="X52" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y52" s="53">
@@ -21693,7 +22434,7 @@
         <v/>
       </c>
       <c r="AA52" s="53">
-        <f>IF(F52=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F52=1,IFERROR(H52/J52,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB52" s="51">
@@ -21713,15 +22454,15 @@
         <v/>
       </c>
       <c r="AF52" s="43">
-        <f>IF(E52="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E52="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG52" s="43">
-        <f>IF(E52="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E52="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH52" s="17">
-        <f>AD52*AE52*AF52+AB52*'02_Leviers'!$D$17</f>
+        <f>AD52*AE52*AF52+AB52*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI52" s="51">
@@ -21737,7 +22478,7 @@
         <v/>
       </c>
       <c r="AL52" s="17">
-        <f>AB52*'02_Leviers'!$D$15+H52*S52*(1+Y52)</f>
+        <f>H52*S52*(1+Y52)</f>
         <v/>
       </c>
       <c r="AM52" s="55">
@@ -21851,7 +22592,7 @@
         <v/>
       </c>
       <c r="X53" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y53" s="53">
@@ -21863,7 +22604,7 @@
         <v/>
       </c>
       <c r="AA53" s="53">
-        <f>IF(F53=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F53=1,IFERROR(H53/J53,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB53" s="51">
@@ -21883,15 +22624,15 @@
         <v/>
       </c>
       <c r="AF53" s="43">
-        <f>IF(E53="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E53="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG53" s="43">
-        <f>IF(E53="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E53="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH53" s="17">
-        <f>AD53*AE53*AF53+AB53*'02_Leviers'!$D$17</f>
+        <f>AD53*AE53*AF53+AB53*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI53" s="51">
@@ -21907,7 +22648,7 @@
         <v/>
       </c>
       <c r="AL53" s="17">
-        <f>AB53*'02_Leviers'!$D$15+H53*S53*(1+Y53)</f>
+        <f>H53*S53*(1+Y53)</f>
         <v/>
       </c>
       <c r="AM53" s="55">
@@ -22021,7 +22762,7 @@
         <v/>
       </c>
       <c r="X54" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y54" s="53">
@@ -22033,7 +22774,7 @@
         <v/>
       </c>
       <c r="AA54" s="53">
-        <f>IF(F54=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F54=1,IFERROR(H54/J54,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB54" s="51">
@@ -22053,15 +22794,15 @@
         <v/>
       </c>
       <c r="AF54" s="43">
-        <f>IF(E54="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E54="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG54" s="43">
-        <f>IF(E54="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E54="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH54" s="17">
-        <f>AD54*AE54*AF54+AB54*'02_Leviers'!$D$17</f>
+        <f>AD54*AE54*AF54+AB54*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI54" s="51">
@@ -22077,7 +22818,7 @@
         <v/>
       </c>
       <c r="AL54" s="17">
-        <f>AB54*'02_Leviers'!$D$15+H54*S54*(1+Y54)</f>
+        <f>H54*S54*(1+Y54)</f>
         <v/>
       </c>
       <c r="AM54" s="55">
@@ -22191,7 +22932,7 @@
         <v/>
       </c>
       <c r="X55" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y55" s="53">
@@ -22203,7 +22944,7 @@
         <v/>
       </c>
       <c r="AA55" s="53">
-        <f>IF(F55=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F55=1,IFERROR(H55/J55,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB55" s="51">
@@ -22223,15 +22964,15 @@
         <v/>
       </c>
       <c r="AF55" s="43">
-        <f>IF(E55="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E55="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG55" s="43">
-        <f>IF(E55="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E55="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH55" s="17">
-        <f>AD55*AE55*AF55+AB55*'02_Leviers'!$D$17</f>
+        <f>AD55*AE55*AF55+AB55*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI55" s="51">
@@ -22247,7 +22988,7 @@
         <v/>
       </c>
       <c r="AL55" s="17">
-        <f>AB55*'02_Leviers'!$D$15+H55*S55*(1+Y55)</f>
+        <f>H55*S55*(1+Y55)</f>
         <v/>
       </c>
       <c r="AM55" s="55">
@@ -22361,7 +23102,7 @@
         <v/>
       </c>
       <c r="X56" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y56" s="53">
@@ -22373,7 +23114,7 @@
         <v/>
       </c>
       <c r="AA56" s="53">
-        <f>IF(F56=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F56=1,IFERROR(H56/J56,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB56" s="51">
@@ -22393,15 +23134,15 @@
         <v/>
       </c>
       <c r="AF56" s="43">
-        <f>IF(E56="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E56="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG56" s="43">
-        <f>IF(E56="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E56="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH56" s="17">
-        <f>AD56*AE56*AF56+AB56*'02_Leviers'!$D$17</f>
+        <f>AD56*AE56*AF56+AB56*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI56" s="51">
@@ -22417,7 +23158,7 @@
         <v/>
       </c>
       <c r="AL56" s="17">
-        <f>AB56*'02_Leviers'!$D$15+H56*S56*(1+Y56)</f>
+        <f>H56*S56*(1+Y56)</f>
         <v/>
       </c>
       <c r="AM56" s="55">
@@ -22531,7 +23272,7 @@
         <v/>
       </c>
       <c r="X57" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y57" s="53">
@@ -22543,7 +23284,7 @@
         <v/>
       </c>
       <c r="AA57" s="53">
-        <f>IF(F57=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F57=1,IFERROR(H57/J57,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB57" s="51">
@@ -22563,15 +23304,15 @@
         <v/>
       </c>
       <c r="AF57" s="43">
-        <f>IF(E57="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E57="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG57" s="43">
-        <f>IF(E57="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E57="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH57" s="17">
-        <f>AD57*AE57*AF57+AB57*'02_Leviers'!$D$17</f>
+        <f>AD57*AE57*AF57+AB57*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI57" s="51">
@@ -22587,7 +23328,7 @@
         <v/>
       </c>
       <c r="AL57" s="17">
-        <f>AB57*'02_Leviers'!$D$15+H57*S57*(1+Y57)</f>
+        <f>H57*S57*(1+Y57)</f>
         <v/>
       </c>
       <c r="AM57" s="55">
@@ -22701,7 +23442,7 @@
         <v/>
       </c>
       <c r="X58" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y58" s="53">
@@ -22713,7 +23454,7 @@
         <v/>
       </c>
       <c r="AA58" s="53">
-        <f>IF(F58=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F58=1,IFERROR(H58/J58,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB58" s="51">
@@ -22733,15 +23474,15 @@
         <v/>
       </c>
       <c r="AF58" s="43">
-        <f>IF(E58="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E58="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG58" s="43">
-        <f>IF(E58="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E58="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH58" s="17">
-        <f>AD58*AE58*AF58+AB58*'02_Leviers'!$D$17</f>
+        <f>AD58*AE58*AF58+AB58*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI58" s="51">
@@ -22757,7 +23498,7 @@
         <v/>
       </c>
       <c r="AL58" s="17">
-        <f>AB58*'02_Leviers'!$D$15+H58*S58*(1+Y58)</f>
+        <f>H58*S58*(1+Y58)</f>
         <v/>
       </c>
       <c r="AM58" s="55">
@@ -22871,7 +23612,7 @@
         <v/>
       </c>
       <c r="X59" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y59" s="53">
@@ -22883,7 +23624,7 @@
         <v/>
       </c>
       <c r="AA59" s="53">
-        <f>IF(F59=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F59=1,IFERROR(H59/J59,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB59" s="51">
@@ -22903,15 +23644,15 @@
         <v/>
       </c>
       <c r="AF59" s="43">
-        <f>IF(E59="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E59="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG59" s="43">
-        <f>IF(E59="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E59="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH59" s="17">
-        <f>AD59*AE59*AF59+AB59*'02_Leviers'!$D$17</f>
+        <f>AD59*AE59*AF59+AB59*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI59" s="51">
@@ -22927,7 +23668,7 @@
         <v/>
       </c>
       <c r="AL59" s="17">
-        <f>AB59*'02_Leviers'!$D$15+H59*S59*(1+Y59)</f>
+        <f>H59*S59*(1+Y59)</f>
         <v/>
       </c>
       <c r="AM59" s="55">
@@ -23041,7 +23782,7 @@
         <v/>
       </c>
       <c r="X60" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="Y60" s="53">
@@ -23053,7 +23794,7 @@
         <v/>
       </c>
       <c r="AA60" s="53">
-        <f>IF(F60=1,'02_Leviers'!$D$22+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F60=1,IFERROR(H60/J60,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB60" s="51">
@@ -23073,15 +23814,15 @@
         <v/>
       </c>
       <c r="AF60" s="43">
-        <f>IF(E60="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E60="ALT",'02_Leviers'!$G$9+(1-'02_Leviers'!$G$9)*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AG60" s="43">
-        <f>IF(E60="ALT",'02_Leviers'!$D$20+(1-'02_Leviers'!$D$20)*'02_Leviers'!$D$19,1)</f>
+        <f>IF(E60="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH60" s="17">
-        <f>AD60*AE60*AF60+AB60*'02_Leviers'!$D$17</f>
+        <f>AD60*AE60*AF60+AB60*'02_Leviers'!$D$16</f>
         <v/>
       </c>
       <c r="AI60" s="51">
@@ -23097,7 +23838,7 @@
         <v/>
       </c>
       <c r="AL60" s="17">
-        <f>AB60*'02_Leviers'!$D$15+H60*S60*(1+Y60)</f>
+        <f>H60*S60*(1+Y60)</f>
         <v/>
       </c>
       <c r="AM60" s="55">

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="C3" s="56">
-        <f>'02_Leviers'!$D$23</f>
+        <f>'02_Leviers'!$D$24</f>
         <v/>
       </c>
       <c r="E3" s="19" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Coûts directs (ens.+pédago+mktg)</t>
+          <t xml:space="preserve">  Coûts directs (ens.+pédago+mktg+autres)</t>
         </is>
       </c>
       <c r="C8" s="16">
@@ -2029,7 +2029,7 @@
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>-(SUM('08_Moteur'!$AJ$3:$AJ$60)+SUM('08_Moteur'!$AK$3:$AK$60)+SUM('08_Moteur'!$AL$3:$AL$60))</f>
+        <f>-(SUM('08_Moteur'!$AJ$3:$AJ$60)+SUM('08_Moteur'!$AK$3:$AK$60)+SUM('08_Moteur'!$AL$3:$AL$60)+'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)*SUM('08_Moteur'!$AD$3:$AD$60))</f>
         <v/>
       </c>
       <c r="E8" s="66">
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="C8" s="17">
-        <f>0.01*'02_Leviers'!$D$20*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
+        <f>0.01*'02_Leviers'!$D$21*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
         <v/>
       </c>
       <c r="D8" s="73" t="inlineStr">
@@ -6737,7 +6737,7 @@
         <v/>
       </c>
       <c r="D14" s="53">
-        <f>'02_Leviers'!$D$19</f>
+        <f>'02_Leviers'!$D$20</f>
         <v/>
       </c>
       <c r="E14" s="53">
@@ -6756,7 +6756,7 @@
         <v/>
       </c>
       <c r="D15" s="76">
-        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$19)</f>
+        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
         <v/>
       </c>
       <c r="E15" s="77">
@@ -7126,7 +7126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G23"/>
+  <dimension ref="B2:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7504,24 +7504,24 @@
     <row r="19">
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sécurisation N-1 — REPLI</t>
+          <t>Autres charges d'exploitation / étudiant</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>0.86</v>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>380</v>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>repli (sinon mesuré par programme)</t>
+          <t>réel (achats, sous-traitance, IT)</t>
         </is>
       </c>
       <c r="F19" s="30" t="n"/>
-      <c r="G19" s="26">
+      <c r="G19" s="31">
         <f>D19</f>
         <v/>
       </c>
@@ -7529,24 +7529,24 @@
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Élasticité marketing — REPLI</t>
+          <t>Sécurisation N-1 — REPLI</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D20" s="33" t="n">
-        <v>0.5</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>0.86</v>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>repli (sinon mesurée N-2/N-1)</t>
+          <t>repli (sinon mesuré par programme)</t>
         </is>
       </c>
       <c r="F20" s="30" t="n"/>
-      <c r="G20" s="34">
+      <c r="G20" s="26">
         <f>D20</f>
         <v/>
       </c>
@@ -7554,48 +7554,74 @@
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
+          <t>Élasticité marketing — REPLI</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>repli (sinon mesurée N-2/N-1)</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="34">
+        <f>D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>Conversion candidature→inscrit — REPLI</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D21" s="32" t="n">
+      <c r="D22" s="32" t="n">
         <v>0.372</v>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>repli (sinon mesurée par cellule)</t>
         </is>
       </c>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="26">
-        <f>D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="26">
+        <f>D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Driver d'allocation :</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>Effectifs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
@@ -7605,7 +7631,7 @@
     <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Cadrage,Optimiste,Prudent"</formula1>
     </dataValidation>
-    <dataValidation sqref="D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Effectifs,Chiffre d'affaires,Surface m2"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12812,7 +12838,7 @@
         <v>81600</v>
       </c>
       <c r="F66" s="43">
-        <f>IFERROR((C66/B66-1)/(E66/D66-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C66/B66-1)/(E66/D66-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G66" s="25" t="n">
@@ -12838,7 +12864,7 @@
         <v>92400</v>
       </c>
       <c r="F67" s="43">
-        <f>IFERROR((C67/B67-1)/(E67/D67-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C67/B67-1)/(E67/D67-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G67" s="25" t="n">
@@ -12864,7 +12890,7 @@
         <v>54080</v>
       </c>
       <c r="F68" s="43">
-        <f>IFERROR((C68/B68-1)/(E68/D68-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C68/B68-1)/(E68/D68-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G68" s="25" t="n">
@@ -12890,7 +12916,7 @@
         <v>60600</v>
       </c>
       <c r="F69" s="43">
-        <f>IFERROR((C69/B69-1)/(E69/D69-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C69/B69-1)/(E69/D69-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G69" s="25" t="n">
@@ -12916,7 +12942,7 @@
         <v>41600</v>
       </c>
       <c r="F70" s="43">
-        <f>IFERROR((C70/B70-1)/(E70/D70-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C70/B70-1)/(E70/D70-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G70" s="25" t="n">
@@ -12942,7 +12968,7 @@
         <v>16500</v>
       </c>
       <c r="F71" s="43">
-        <f>IFERROR((C71/B71-1)/(E71/D71-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C71/B71-1)/(E71/D71-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G71" s="25" t="n">
@@ -12968,7 +12994,7 @@
         <v>26240</v>
       </c>
       <c r="F72" s="43">
-        <f>IFERROR((C72/B72-1)/(E72/D72-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C72/B72-1)/(E72/D72-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G72" s="25" t="n">
@@ -12994,7 +13020,7 @@
         <v>27840</v>
       </c>
       <c r="F73" s="43">
-        <f>IFERROR((C73/B73-1)/(E73/D73-1),'02_Leviers'!$D$20)</f>
+        <f>IFERROR((C73/B73-1)/(E73/D73-1),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="G73" s="25" t="n">
@@ -13114,7 +13140,7 @@
         <v>2467250</v>
       </c>
       <c r="E4" s="42" t="n">
-        <v>1896050</v>
+        <v>1785470</v>
       </c>
       <c r="F4" s="42" t="n">
         <v>271000</v>
@@ -13127,7 +13153,7 @@
         <v/>
       </c>
       <c r="I4" s="42" t="n">
-        <v>74000</v>
+        <v>148000</v>
       </c>
       <c r="J4" s="40" t="n">
         <v>2328</v>
@@ -13155,7 +13181,7 @@
         <v>2102540</v>
       </c>
       <c r="E5" s="42" t="n">
-        <v>1625420</v>
+        <v>1531180</v>
       </c>
       <c r="F5" s="42" t="n">
         <v>231000</v>
@@ -13168,7 +13194,7 @@
         <v/>
       </c>
       <c r="I5" s="42" t="n">
-        <v>63000</v>
+        <v>126000</v>
       </c>
       <c r="J5" s="40" t="n">
         <v>1984</v>
@@ -13196,7 +13222,7 @@
         <v>1898640</v>
       </c>
       <c r="E6" s="42" t="n">
-        <v>1436400</v>
+        <v>1351280</v>
       </c>
       <c r="F6" s="42" t="n">
         <v>209000</v>
@@ -13209,7 +13235,7 @@
         <v/>
       </c>
       <c r="I6" s="42" t="n">
-        <v>57000</v>
+        <v>114000</v>
       </c>
       <c r="J6" s="40" t="n">
         <v>1792</v>
@@ -13237,7 +13263,7 @@
         <v>1619880</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>1177800</v>
+        <v>1105220</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>178000</v>
@@ -13250,7 +13276,7 @@
         <v/>
       </c>
       <c r="I7" s="42" t="n">
-        <v>49000</v>
+        <v>97000</v>
       </c>
       <c r="J7" s="40" t="n">
         <v>1528</v>
@@ -13278,7 +13304,7 @@
         <v>2280350</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>1692040</v>
+        <v>1589820</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>251000</v>
@@ -13291,7 +13317,7 @@
         <v/>
       </c>
       <c r="I8" s="42" t="n">
-        <v>68000</v>
+        <v>137000</v>
       </c>
       <c r="J8" s="40" t="n">
         <v>2152</v>
@@ -13319,7 +13345,7 @@
         <v>1585200</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>1097030</v>
+        <v>1025970</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>174000</v>
@@ -13332,7 +13358,7 @@
         <v/>
       </c>
       <c r="I9" s="42" t="n">
-        <v>48000</v>
+        <v>95000</v>
       </c>
       <c r="J9" s="40" t="n">
         <v>1496</v>
@@ -13360,7 +13386,7 @@
         <v>1483250</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>1004320</v>
+        <v>937820</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>163000</v>
@@ -13373,7 +13399,7 @@
         <v/>
       </c>
       <c r="I10" s="42" t="n">
-        <v>44000</v>
+        <v>89000</v>
       </c>
       <c r="J10" s="40" t="n">
         <v>1400</v>
@@ -13401,7 +13427,7 @@
         <v>1044500</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>784220</v>
+        <v>734820</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>115000</v>
@@ -13414,7 +13440,7 @@
         <v/>
       </c>
       <c r="I11" s="42" t="n">
-        <v>31000</v>
+        <v>63000</v>
       </c>
       <c r="J11" s="40" t="n">
         <v>1040</v>
@@ -13442,7 +13468,7 @@
         <v>835600</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>618560</v>
+        <v>579040</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>92000</v>
@@ -13455,7 +13481,7 @@
         <v/>
       </c>
       <c r="I12" s="42" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="J12" s="40" t="n">
         <v>832</v>
@@ -13483,7 +13509,7 @@
         <v>835600</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>618560</v>
+        <v>579040</v>
       </c>
       <c r="F13" s="42" t="n">
         <v>92000</v>
@@ -13496,7 +13522,7 @@
         <v/>
       </c>
       <c r="I13" s="42" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="J13" s="40" t="n">
         <v>832</v>
@@ -13524,7 +13550,7 @@
         <v>1130470</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>768030</v>
+        <v>711410</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>124000</v>
@@ -13537,7 +13563,7 @@
         <v/>
       </c>
       <c r="I14" s="42" t="n">
-        <v>34000</v>
+        <v>68000</v>
       </c>
       <c r="J14" s="40" t="n">
         <v>1192</v>
@@ -13565,7 +13591,7 @@
         <v>887850</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>649480</v>
+        <v>605020</v>
       </c>
       <c r="F15" s="42" t="n">
         <v>98000</v>
@@ -13578,7 +13604,7 @@
         <v/>
       </c>
       <c r="I15" s="42" t="n">
-        <v>27000</v>
+        <v>53000</v>
       </c>
       <c r="J15" s="40" t="n">
         <v>936</v>
@@ -13606,7 +13632,7 @@
         <v>980230</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>722130</v>
+        <v>675770</v>
       </c>
       <c r="F16" s="42" t="n">
         <v>108000</v>
@@ -13619,7 +13645,7 @@
         <v/>
       </c>
       <c r="I16" s="42" t="n">
-        <v>29000</v>
+        <v>59000</v>
       </c>
       <c r="J16" s="40" t="n">
         <v>976</v>
@@ -13647,7 +13673,7 @@
         <v>835600</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>616960</v>
+        <v>577440</v>
       </c>
       <c r="F17" s="42" t="n">
         <v>92000</v>
@@ -13660,7 +13686,7 @@
         <v/>
       </c>
       <c r="I17" s="42" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="J17" s="40" t="n">
         <v>832</v>
@@ -14092,7 +14118,7 @@
         <v/>
       </c>
       <c r="X3" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y3" s="53">
@@ -14104,7 +14130,7 @@
         <v/>
       </c>
       <c r="AA3" s="53">
-        <f>IF(F3=1,IFERROR(H3/J3,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F3=1,IFERROR(H3/J3,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB3" s="51">
@@ -14128,7 +14154,7 @@
         <v/>
       </c>
       <c r="AG3" s="43">
-        <f>IF(E3="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E3="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH3" s="17">
@@ -14152,7 +14178,7 @@
         <v/>
       </c>
       <c r="AM3" s="55">
-        <f>AH3-AJ3-AK3-AL3</f>
+        <f>AH3-AJ3-AK3-AL3-AD3*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN3" s="53">
@@ -14262,7 +14288,7 @@
         <v/>
       </c>
       <c r="X4" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y4" s="53">
@@ -14274,7 +14300,7 @@
         <v/>
       </c>
       <c r="AA4" s="53">
-        <f>IF(F4=1,IFERROR(H4/J4,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F4=1,IFERROR(H4/J4,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB4" s="51">
@@ -14298,7 +14324,7 @@
         <v/>
       </c>
       <c r="AG4" s="43">
-        <f>IF(E4="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E4="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH4" s="17">
@@ -14322,7 +14348,7 @@
         <v/>
       </c>
       <c r="AM4" s="55">
-        <f>AH4-AJ4-AK4-AL4</f>
+        <f>AH4-AJ4-AK4-AL4-AD4*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN4" s="53">
@@ -14432,7 +14458,7 @@
         <v/>
       </c>
       <c r="X5" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y5" s="53">
@@ -14444,7 +14470,7 @@
         <v/>
       </c>
       <c r="AA5" s="53">
-        <f>IF(F5=1,IFERROR(H5/J5,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F5=1,IFERROR(H5/J5,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB5" s="51">
@@ -14468,7 +14494,7 @@
         <v/>
       </c>
       <c r="AG5" s="43">
-        <f>IF(E5="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E5="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH5" s="17">
@@ -14492,7 +14518,7 @@
         <v/>
       </c>
       <c r="AM5" s="55">
-        <f>AH5-AJ5-AK5-AL5</f>
+        <f>AH5-AJ5-AK5-AL5-AD5*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN5" s="53">
@@ -14602,7 +14628,7 @@
         <v/>
       </c>
       <c r="X6" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y6" s="53">
@@ -14614,7 +14640,7 @@
         <v/>
       </c>
       <c r="AA6" s="53">
-        <f>IF(F6=1,IFERROR(H6/J6,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F6=1,IFERROR(H6/J6,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB6" s="51">
@@ -14638,7 +14664,7 @@
         <v/>
       </c>
       <c r="AG6" s="43">
-        <f>IF(E6="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E6="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH6" s="17">
@@ -14662,7 +14688,7 @@
         <v/>
       </c>
       <c r="AM6" s="55">
-        <f>AH6-AJ6-AK6-AL6</f>
+        <f>AH6-AJ6-AK6-AL6-AD6*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN6" s="53">
@@ -14772,7 +14798,7 @@
         <v/>
       </c>
       <c r="X7" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y7" s="53">
@@ -14784,7 +14810,7 @@
         <v/>
       </c>
       <c r="AA7" s="53">
-        <f>IF(F7=1,IFERROR(H7/J7,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F7=1,IFERROR(H7/J7,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB7" s="51">
@@ -14808,7 +14834,7 @@
         <v/>
       </c>
       <c r="AG7" s="43">
-        <f>IF(E7="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E7="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH7" s="17">
@@ -14832,7 +14858,7 @@
         <v/>
       </c>
       <c r="AM7" s="55">
-        <f>AH7-AJ7-AK7-AL7</f>
+        <f>AH7-AJ7-AK7-AL7-AD7*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN7" s="53">
@@ -14942,7 +14968,7 @@
         <v/>
       </c>
       <c r="X8" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y8" s="53">
@@ -14954,7 +14980,7 @@
         <v/>
       </c>
       <c r="AA8" s="53">
-        <f>IF(F8=1,IFERROR(H8/J8,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F8=1,IFERROR(H8/J8,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB8" s="51">
@@ -14978,7 +15004,7 @@
         <v/>
       </c>
       <c r="AG8" s="43">
-        <f>IF(E8="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E8="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH8" s="17">
@@ -15002,7 +15028,7 @@
         <v/>
       </c>
       <c r="AM8" s="55">
-        <f>AH8-AJ8-AK8-AL8</f>
+        <f>AH8-AJ8-AK8-AL8-AD8*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN8" s="53">
@@ -15112,7 +15138,7 @@
         <v/>
       </c>
       <c r="X9" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y9" s="53">
@@ -15124,7 +15150,7 @@
         <v/>
       </c>
       <c r="AA9" s="53">
-        <f>IF(F9=1,IFERROR(H9/J9,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F9=1,IFERROR(H9/J9,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB9" s="51">
@@ -15148,7 +15174,7 @@
         <v/>
       </c>
       <c r="AG9" s="43">
-        <f>IF(E9="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E9="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH9" s="17">
@@ -15172,7 +15198,7 @@
         <v/>
       </c>
       <c r="AM9" s="55">
-        <f>AH9-AJ9-AK9-AL9</f>
+        <f>AH9-AJ9-AK9-AL9-AD9*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN9" s="53">
@@ -15282,7 +15308,7 @@
         <v/>
       </c>
       <c r="X10" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y10" s="53">
@@ -15294,7 +15320,7 @@
         <v/>
       </c>
       <c r="AA10" s="53">
-        <f>IF(F10=1,IFERROR(H10/J10,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F10=1,IFERROR(H10/J10,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB10" s="51">
@@ -15318,7 +15344,7 @@
         <v/>
       </c>
       <c r="AG10" s="43">
-        <f>IF(E10="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E10="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH10" s="17">
@@ -15342,7 +15368,7 @@
         <v/>
       </c>
       <c r="AM10" s="55">
-        <f>AH10-AJ10-AK10-AL10</f>
+        <f>AH10-AJ10-AK10-AL10-AD10*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN10" s="53">
@@ -15452,7 +15478,7 @@
         <v/>
       </c>
       <c r="X11" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y11" s="53">
@@ -15464,7 +15490,7 @@
         <v/>
       </c>
       <c r="AA11" s="53">
-        <f>IF(F11=1,IFERROR(H11/J11,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F11=1,IFERROR(H11/J11,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB11" s="51">
@@ -15488,7 +15514,7 @@
         <v/>
       </c>
       <c r="AG11" s="43">
-        <f>IF(E11="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E11="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH11" s="17">
@@ -15512,7 +15538,7 @@
         <v/>
       </c>
       <c r="AM11" s="55">
-        <f>AH11-AJ11-AK11-AL11</f>
+        <f>AH11-AJ11-AK11-AL11-AD11*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN11" s="53">
@@ -15622,7 +15648,7 @@
         <v/>
       </c>
       <c r="X12" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y12" s="53">
@@ -15634,7 +15660,7 @@
         <v/>
       </c>
       <c r="AA12" s="53">
-        <f>IF(F12=1,IFERROR(H12/J12,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F12=1,IFERROR(H12/J12,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB12" s="51">
@@ -15658,7 +15684,7 @@
         <v/>
       </c>
       <c r="AG12" s="43">
-        <f>IF(E12="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E12="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH12" s="17">
@@ -15682,7 +15708,7 @@
         <v/>
       </c>
       <c r="AM12" s="55">
-        <f>AH12-AJ12-AK12-AL12</f>
+        <f>AH12-AJ12-AK12-AL12-AD12*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN12" s="53">
@@ -15792,7 +15818,7 @@
         <v/>
       </c>
       <c r="X13" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y13" s="53">
@@ -15804,7 +15830,7 @@
         <v/>
       </c>
       <c r="AA13" s="53">
-        <f>IF(F13=1,IFERROR(H13/J13,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F13=1,IFERROR(H13/J13,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB13" s="51">
@@ -15828,7 +15854,7 @@
         <v/>
       </c>
       <c r="AG13" s="43">
-        <f>IF(E13="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E13="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH13" s="17">
@@ -15852,7 +15878,7 @@
         <v/>
       </c>
       <c r="AM13" s="55">
-        <f>AH13-AJ13-AK13-AL13</f>
+        <f>AH13-AJ13-AK13-AL13-AD13*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN13" s="53">
@@ -15962,7 +15988,7 @@
         <v/>
       </c>
       <c r="X14" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y14" s="53">
@@ -15974,7 +16000,7 @@
         <v/>
       </c>
       <c r="AA14" s="53">
-        <f>IF(F14=1,IFERROR(H14/J14,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F14=1,IFERROR(H14/J14,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB14" s="51">
@@ -15998,7 +16024,7 @@
         <v/>
       </c>
       <c r="AG14" s="43">
-        <f>IF(E14="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E14="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH14" s="17">
@@ -16022,7 +16048,7 @@
         <v/>
       </c>
       <c r="AM14" s="55">
-        <f>AH14-AJ14-AK14-AL14</f>
+        <f>AH14-AJ14-AK14-AL14-AD14*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN14" s="53">
@@ -16132,7 +16158,7 @@
         <v/>
       </c>
       <c r="X15" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y15" s="53">
@@ -16144,7 +16170,7 @@
         <v/>
       </c>
       <c r="AA15" s="53">
-        <f>IF(F15=1,IFERROR(H15/J15,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F15=1,IFERROR(H15/J15,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB15" s="51">
@@ -16168,7 +16194,7 @@
         <v/>
       </c>
       <c r="AG15" s="43">
-        <f>IF(E15="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E15="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH15" s="17">
@@ -16192,7 +16218,7 @@
         <v/>
       </c>
       <c r="AM15" s="55">
-        <f>AH15-AJ15-AK15-AL15</f>
+        <f>AH15-AJ15-AK15-AL15-AD15*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN15" s="53">
@@ -16302,7 +16328,7 @@
         <v/>
       </c>
       <c r="X16" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y16" s="53">
@@ -16314,7 +16340,7 @@
         <v/>
       </c>
       <c r="AA16" s="53">
-        <f>IF(F16=1,IFERROR(H16/J16,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F16=1,IFERROR(H16/J16,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB16" s="51">
@@ -16338,7 +16364,7 @@
         <v/>
       </c>
       <c r="AG16" s="43">
-        <f>IF(E16="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E16="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH16" s="17">
@@ -16362,7 +16388,7 @@
         <v/>
       </c>
       <c r="AM16" s="55">
-        <f>AH16-AJ16-AK16-AL16</f>
+        <f>AH16-AJ16-AK16-AL16-AD16*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN16" s="53">
@@ -16472,7 +16498,7 @@
         <v/>
       </c>
       <c r="X17" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y17" s="53">
@@ -16484,7 +16510,7 @@
         <v/>
       </c>
       <c r="AA17" s="53">
-        <f>IF(F17=1,IFERROR(H17/J17,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F17=1,IFERROR(H17/J17,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB17" s="51">
@@ -16508,7 +16534,7 @@
         <v/>
       </c>
       <c r="AG17" s="43">
-        <f>IF(E17="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E17="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH17" s="17">
@@ -16532,7 +16558,7 @@
         <v/>
       </c>
       <c r="AM17" s="55">
-        <f>AH17-AJ17-AK17-AL17</f>
+        <f>AH17-AJ17-AK17-AL17-AD17*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN17" s="53">
@@ -16642,7 +16668,7 @@
         <v/>
       </c>
       <c r="X18" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y18" s="53">
@@ -16654,7 +16680,7 @@
         <v/>
       </c>
       <c r="AA18" s="53">
-        <f>IF(F18=1,IFERROR(H18/J18,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F18=1,IFERROR(H18/J18,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB18" s="51">
@@ -16678,7 +16704,7 @@
         <v/>
       </c>
       <c r="AG18" s="43">
-        <f>IF(E18="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E18="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH18" s="17">
@@ -16702,7 +16728,7 @@
         <v/>
       </c>
       <c r="AM18" s="55">
-        <f>AH18-AJ18-AK18-AL18</f>
+        <f>AH18-AJ18-AK18-AL18-AD18*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN18" s="53">
@@ -16812,7 +16838,7 @@
         <v/>
       </c>
       <c r="X19" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y19" s="53">
@@ -16824,7 +16850,7 @@
         <v/>
       </c>
       <c r="AA19" s="53">
-        <f>IF(F19=1,IFERROR(H19/J19,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F19=1,IFERROR(H19/J19,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB19" s="51">
@@ -16848,7 +16874,7 @@
         <v/>
       </c>
       <c r="AG19" s="43">
-        <f>IF(E19="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E19="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH19" s="17">
@@ -16872,7 +16898,7 @@
         <v/>
       </c>
       <c r="AM19" s="55">
-        <f>AH19-AJ19-AK19-AL19</f>
+        <f>AH19-AJ19-AK19-AL19-AD19*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN19" s="53">
@@ -16982,7 +17008,7 @@
         <v/>
       </c>
       <c r="X20" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y20" s="53">
@@ -16994,7 +17020,7 @@
         <v/>
       </c>
       <c r="AA20" s="53">
-        <f>IF(F20=1,IFERROR(H20/J20,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F20=1,IFERROR(H20/J20,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB20" s="51">
@@ -17018,7 +17044,7 @@
         <v/>
       </c>
       <c r="AG20" s="43">
-        <f>IF(E20="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E20="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH20" s="17">
@@ -17042,7 +17068,7 @@
         <v/>
       </c>
       <c r="AM20" s="55">
-        <f>AH20-AJ20-AK20-AL20</f>
+        <f>AH20-AJ20-AK20-AL20-AD20*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN20" s="53">
@@ -17152,7 +17178,7 @@
         <v/>
       </c>
       <c r="X21" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y21" s="53">
@@ -17164,7 +17190,7 @@
         <v/>
       </c>
       <c r="AA21" s="53">
-        <f>IF(F21=1,IFERROR(H21/J21,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F21=1,IFERROR(H21/J21,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB21" s="51">
@@ -17188,7 +17214,7 @@
         <v/>
       </c>
       <c r="AG21" s="43">
-        <f>IF(E21="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E21="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH21" s="17">
@@ -17212,7 +17238,7 @@
         <v/>
       </c>
       <c r="AM21" s="55">
-        <f>AH21-AJ21-AK21-AL21</f>
+        <f>AH21-AJ21-AK21-AL21-AD21*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN21" s="53">
@@ -17322,7 +17348,7 @@
         <v/>
       </c>
       <c r="X22" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y22" s="53">
@@ -17334,7 +17360,7 @@
         <v/>
       </c>
       <c r="AA22" s="53">
-        <f>IF(F22=1,IFERROR(H22/J22,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F22=1,IFERROR(H22/J22,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB22" s="51">
@@ -17358,7 +17384,7 @@
         <v/>
       </c>
       <c r="AG22" s="43">
-        <f>IF(E22="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E22="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH22" s="17">
@@ -17382,7 +17408,7 @@
         <v/>
       </c>
       <c r="AM22" s="55">
-        <f>AH22-AJ22-AK22-AL22</f>
+        <f>AH22-AJ22-AK22-AL22-AD22*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN22" s="53">
@@ -17492,7 +17518,7 @@
         <v/>
       </c>
       <c r="X23" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y23" s="53">
@@ -17504,7 +17530,7 @@
         <v/>
       </c>
       <c r="AA23" s="53">
-        <f>IF(F23=1,IFERROR(H23/J23,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F23=1,IFERROR(H23/J23,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB23" s="51">
@@ -17528,7 +17554,7 @@
         <v/>
       </c>
       <c r="AG23" s="43">
-        <f>IF(E23="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E23="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH23" s="17">
@@ -17552,7 +17578,7 @@
         <v/>
       </c>
       <c r="AM23" s="55">
-        <f>AH23-AJ23-AK23-AL23</f>
+        <f>AH23-AJ23-AK23-AL23-AD23*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN23" s="53">
@@ -17662,7 +17688,7 @@
         <v/>
       </c>
       <c r="X24" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y24" s="53">
@@ -17674,7 +17700,7 @@
         <v/>
       </c>
       <c r="AA24" s="53">
-        <f>IF(F24=1,IFERROR(H24/J24,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F24=1,IFERROR(H24/J24,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB24" s="51">
@@ -17698,7 +17724,7 @@
         <v/>
       </c>
       <c r="AG24" s="43">
-        <f>IF(E24="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E24="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH24" s="17">
@@ -17722,7 +17748,7 @@
         <v/>
       </c>
       <c r="AM24" s="55">
-        <f>AH24-AJ24-AK24-AL24</f>
+        <f>AH24-AJ24-AK24-AL24-AD24*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN24" s="53">
@@ -17832,7 +17858,7 @@
         <v/>
       </c>
       <c r="X25" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y25" s="53">
@@ -17844,7 +17870,7 @@
         <v/>
       </c>
       <c r="AA25" s="53">
-        <f>IF(F25=1,IFERROR(H25/J25,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F25=1,IFERROR(H25/J25,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB25" s="51">
@@ -17868,7 +17894,7 @@
         <v/>
       </c>
       <c r="AG25" s="43">
-        <f>IF(E25="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E25="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH25" s="17">
@@ -17892,7 +17918,7 @@
         <v/>
       </c>
       <c r="AM25" s="55">
-        <f>AH25-AJ25-AK25-AL25</f>
+        <f>AH25-AJ25-AK25-AL25-AD25*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN25" s="53">
@@ -18002,7 +18028,7 @@
         <v/>
       </c>
       <c r="X26" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y26" s="53">
@@ -18014,7 +18040,7 @@
         <v/>
       </c>
       <c r="AA26" s="53">
-        <f>IF(F26=1,IFERROR(H26/J26,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F26=1,IFERROR(H26/J26,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB26" s="51">
@@ -18038,7 +18064,7 @@
         <v/>
       </c>
       <c r="AG26" s="43">
-        <f>IF(E26="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E26="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH26" s="17">
@@ -18062,7 +18088,7 @@
         <v/>
       </c>
       <c r="AM26" s="55">
-        <f>AH26-AJ26-AK26-AL26</f>
+        <f>AH26-AJ26-AK26-AL26-AD26*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN26" s="53">
@@ -18172,7 +18198,7 @@
         <v/>
       </c>
       <c r="X27" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y27" s="53">
@@ -18184,7 +18210,7 @@
         <v/>
       </c>
       <c r="AA27" s="53">
-        <f>IF(F27=1,IFERROR(H27/J27,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F27=1,IFERROR(H27/J27,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB27" s="51">
@@ -18208,7 +18234,7 @@
         <v/>
       </c>
       <c r="AG27" s="43">
-        <f>IF(E27="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E27="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH27" s="17">
@@ -18232,7 +18258,7 @@
         <v/>
       </c>
       <c r="AM27" s="55">
-        <f>AH27-AJ27-AK27-AL27</f>
+        <f>AH27-AJ27-AK27-AL27-AD27*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN27" s="53">
@@ -18342,7 +18368,7 @@
         <v/>
       </c>
       <c r="X28" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y28" s="53">
@@ -18354,7 +18380,7 @@
         <v/>
       </c>
       <c r="AA28" s="53">
-        <f>IF(F28=1,IFERROR(H28/J28,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F28=1,IFERROR(H28/J28,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB28" s="51">
@@ -18378,7 +18404,7 @@
         <v/>
       </c>
       <c r="AG28" s="43">
-        <f>IF(E28="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E28="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH28" s="17">
@@ -18402,7 +18428,7 @@
         <v/>
       </c>
       <c r="AM28" s="55">
-        <f>AH28-AJ28-AK28-AL28</f>
+        <f>AH28-AJ28-AK28-AL28-AD28*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN28" s="53">
@@ -18512,7 +18538,7 @@
         <v/>
       </c>
       <c r="X29" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y29" s="53">
@@ -18524,7 +18550,7 @@
         <v/>
       </c>
       <c r="AA29" s="53">
-        <f>IF(F29=1,IFERROR(H29/J29,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F29=1,IFERROR(H29/J29,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB29" s="51">
@@ -18548,7 +18574,7 @@
         <v/>
       </c>
       <c r="AG29" s="43">
-        <f>IF(E29="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E29="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH29" s="17">
@@ -18572,7 +18598,7 @@
         <v/>
       </c>
       <c r="AM29" s="55">
-        <f>AH29-AJ29-AK29-AL29</f>
+        <f>AH29-AJ29-AK29-AL29-AD29*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN29" s="53">
@@ -18682,7 +18708,7 @@
         <v/>
       </c>
       <c r="X30" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y30" s="53">
@@ -18694,7 +18720,7 @@
         <v/>
       </c>
       <c r="AA30" s="53">
-        <f>IF(F30=1,IFERROR(H30/J30,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F30=1,IFERROR(H30/J30,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB30" s="51">
@@ -18718,7 +18744,7 @@
         <v/>
       </c>
       <c r="AG30" s="43">
-        <f>IF(E30="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E30="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH30" s="17">
@@ -18742,7 +18768,7 @@
         <v/>
       </c>
       <c r="AM30" s="55">
-        <f>AH30-AJ30-AK30-AL30</f>
+        <f>AH30-AJ30-AK30-AL30-AD30*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN30" s="53">
@@ -18852,7 +18878,7 @@
         <v/>
       </c>
       <c r="X31" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y31" s="53">
@@ -18864,7 +18890,7 @@
         <v/>
       </c>
       <c r="AA31" s="53">
-        <f>IF(F31=1,IFERROR(H31/J31,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F31=1,IFERROR(H31/J31,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB31" s="51">
@@ -18888,7 +18914,7 @@
         <v/>
       </c>
       <c r="AG31" s="43">
-        <f>IF(E31="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E31="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH31" s="17">
@@ -18912,7 +18938,7 @@
         <v/>
       </c>
       <c r="AM31" s="55">
-        <f>AH31-AJ31-AK31-AL31</f>
+        <f>AH31-AJ31-AK31-AL31-AD31*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN31" s="53">
@@ -19022,7 +19048,7 @@
         <v/>
       </c>
       <c r="X32" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y32" s="53">
@@ -19034,7 +19060,7 @@
         <v/>
       </c>
       <c r="AA32" s="53">
-        <f>IF(F32=1,IFERROR(H32/J32,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F32=1,IFERROR(H32/J32,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB32" s="51">
@@ -19058,7 +19084,7 @@
         <v/>
       </c>
       <c r="AG32" s="43">
-        <f>IF(E32="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E32="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH32" s="17">
@@ -19082,7 +19108,7 @@
         <v/>
       </c>
       <c r="AM32" s="55">
-        <f>AH32-AJ32-AK32-AL32</f>
+        <f>AH32-AJ32-AK32-AL32-AD32*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN32" s="53">
@@ -19192,7 +19218,7 @@
         <v/>
       </c>
       <c r="X33" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y33" s="53">
@@ -19204,7 +19230,7 @@
         <v/>
       </c>
       <c r="AA33" s="53">
-        <f>IF(F33=1,IFERROR(H33/J33,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F33=1,IFERROR(H33/J33,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB33" s="51">
@@ -19228,7 +19254,7 @@
         <v/>
       </c>
       <c r="AG33" s="43">
-        <f>IF(E33="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E33="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH33" s="17">
@@ -19252,7 +19278,7 @@
         <v/>
       </c>
       <c r="AM33" s="55">
-        <f>AH33-AJ33-AK33-AL33</f>
+        <f>AH33-AJ33-AK33-AL33-AD33*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN33" s="53">
@@ -19362,7 +19388,7 @@
         <v/>
       </c>
       <c r="X34" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y34" s="53">
@@ -19374,7 +19400,7 @@
         <v/>
       </c>
       <c r="AA34" s="53">
-        <f>IF(F34=1,IFERROR(H34/J34,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F34=1,IFERROR(H34/J34,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB34" s="51">
@@ -19398,7 +19424,7 @@
         <v/>
       </c>
       <c r="AG34" s="43">
-        <f>IF(E34="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E34="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH34" s="17">
@@ -19422,7 +19448,7 @@
         <v/>
       </c>
       <c r="AM34" s="55">
-        <f>AH34-AJ34-AK34-AL34</f>
+        <f>AH34-AJ34-AK34-AL34-AD34*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN34" s="53">
@@ -19532,7 +19558,7 @@
         <v/>
       </c>
       <c r="X35" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y35" s="53">
@@ -19544,7 +19570,7 @@
         <v/>
       </c>
       <c r="AA35" s="53">
-        <f>IF(F35=1,IFERROR(H35/J35,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F35=1,IFERROR(H35/J35,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB35" s="51">
@@ -19568,7 +19594,7 @@
         <v/>
       </c>
       <c r="AG35" s="43">
-        <f>IF(E35="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E35="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH35" s="17">
@@ -19592,7 +19618,7 @@
         <v/>
       </c>
       <c r="AM35" s="55">
-        <f>AH35-AJ35-AK35-AL35</f>
+        <f>AH35-AJ35-AK35-AL35-AD35*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN35" s="53">
@@ -19702,7 +19728,7 @@
         <v/>
       </c>
       <c r="X36" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y36" s="53">
@@ -19714,7 +19740,7 @@
         <v/>
       </c>
       <c r="AA36" s="53">
-        <f>IF(F36=1,IFERROR(H36/J36,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F36=1,IFERROR(H36/J36,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB36" s="51">
@@ -19738,7 +19764,7 @@
         <v/>
       </c>
       <c r="AG36" s="43">
-        <f>IF(E36="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E36="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH36" s="17">
@@ -19762,7 +19788,7 @@
         <v/>
       </c>
       <c r="AM36" s="55">
-        <f>AH36-AJ36-AK36-AL36</f>
+        <f>AH36-AJ36-AK36-AL36-AD36*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN36" s="53">
@@ -19872,7 +19898,7 @@
         <v/>
       </c>
       <c r="X37" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y37" s="53">
@@ -19884,7 +19910,7 @@
         <v/>
       </c>
       <c r="AA37" s="53">
-        <f>IF(F37=1,IFERROR(H37/J37,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F37=1,IFERROR(H37/J37,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB37" s="51">
@@ -19908,7 +19934,7 @@
         <v/>
       </c>
       <c r="AG37" s="43">
-        <f>IF(E37="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E37="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH37" s="17">
@@ -19932,7 +19958,7 @@
         <v/>
       </c>
       <c r="AM37" s="55">
-        <f>AH37-AJ37-AK37-AL37</f>
+        <f>AH37-AJ37-AK37-AL37-AD37*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN37" s="53">
@@ -20042,7 +20068,7 @@
         <v/>
       </c>
       <c r="X38" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y38" s="53">
@@ -20054,7 +20080,7 @@
         <v/>
       </c>
       <c r="AA38" s="53">
-        <f>IF(F38=1,IFERROR(H38/J38,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F38=1,IFERROR(H38/J38,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB38" s="51">
@@ -20078,7 +20104,7 @@
         <v/>
       </c>
       <c r="AG38" s="43">
-        <f>IF(E38="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E38="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH38" s="17">
@@ -20102,7 +20128,7 @@
         <v/>
       </c>
       <c r="AM38" s="55">
-        <f>AH38-AJ38-AK38-AL38</f>
+        <f>AH38-AJ38-AK38-AL38-AD38*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN38" s="53">
@@ -20212,7 +20238,7 @@
         <v/>
       </c>
       <c r="X39" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y39" s="53">
@@ -20224,7 +20250,7 @@
         <v/>
       </c>
       <c r="AA39" s="53">
-        <f>IF(F39=1,IFERROR(H39/J39,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F39=1,IFERROR(H39/J39,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB39" s="51">
@@ -20248,7 +20274,7 @@
         <v/>
       </c>
       <c r="AG39" s="43">
-        <f>IF(E39="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E39="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH39" s="17">
@@ -20272,7 +20298,7 @@
         <v/>
       </c>
       <c r="AM39" s="55">
-        <f>AH39-AJ39-AK39-AL39</f>
+        <f>AH39-AJ39-AK39-AL39-AD39*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN39" s="53">
@@ -20382,7 +20408,7 @@
         <v/>
       </c>
       <c r="X40" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y40" s="53">
@@ -20394,7 +20420,7 @@
         <v/>
       </c>
       <c r="AA40" s="53">
-        <f>IF(F40=1,IFERROR(H40/J40,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F40=1,IFERROR(H40/J40,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB40" s="51">
@@ -20418,7 +20444,7 @@
         <v/>
       </c>
       <c r="AG40" s="43">
-        <f>IF(E40="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E40="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH40" s="17">
@@ -20442,7 +20468,7 @@
         <v/>
       </c>
       <c r="AM40" s="55">
-        <f>AH40-AJ40-AK40-AL40</f>
+        <f>AH40-AJ40-AK40-AL40-AD40*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN40" s="53">
@@ -20552,7 +20578,7 @@
         <v/>
       </c>
       <c r="X41" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y41" s="53">
@@ -20564,7 +20590,7 @@
         <v/>
       </c>
       <c r="AA41" s="53">
-        <f>IF(F41=1,IFERROR(H41/J41,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F41=1,IFERROR(H41/J41,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB41" s="51">
@@ -20588,7 +20614,7 @@
         <v/>
       </c>
       <c r="AG41" s="43">
-        <f>IF(E41="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E41="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH41" s="17">
@@ -20612,7 +20638,7 @@
         <v/>
       </c>
       <c r="AM41" s="55">
-        <f>AH41-AJ41-AK41-AL41</f>
+        <f>AH41-AJ41-AK41-AL41-AD41*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN41" s="53">
@@ -20722,7 +20748,7 @@
         <v/>
       </c>
       <c r="X42" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y42" s="53">
@@ -20734,7 +20760,7 @@
         <v/>
       </c>
       <c r="AA42" s="53">
-        <f>IF(F42=1,IFERROR(H42/J42,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F42=1,IFERROR(H42/J42,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB42" s="51">
@@ -20758,7 +20784,7 @@
         <v/>
       </c>
       <c r="AG42" s="43">
-        <f>IF(E42="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E42="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH42" s="17">
@@ -20782,7 +20808,7 @@
         <v/>
       </c>
       <c r="AM42" s="55">
-        <f>AH42-AJ42-AK42-AL42</f>
+        <f>AH42-AJ42-AK42-AL42-AD42*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN42" s="53">
@@ -20892,7 +20918,7 @@
         <v/>
       </c>
       <c r="X43" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y43" s="53">
@@ -20904,7 +20930,7 @@
         <v/>
       </c>
       <c r="AA43" s="53">
-        <f>IF(F43=1,IFERROR(H43/J43,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F43=1,IFERROR(H43/J43,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB43" s="51">
@@ -20928,7 +20954,7 @@
         <v/>
       </c>
       <c r="AG43" s="43">
-        <f>IF(E43="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E43="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH43" s="17">
@@ -20952,7 +20978,7 @@
         <v/>
       </c>
       <c r="AM43" s="55">
-        <f>AH43-AJ43-AK43-AL43</f>
+        <f>AH43-AJ43-AK43-AL43-AD43*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN43" s="53">
@@ -21062,7 +21088,7 @@
         <v/>
       </c>
       <c r="X44" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y44" s="53">
@@ -21074,7 +21100,7 @@
         <v/>
       </c>
       <c r="AA44" s="53">
-        <f>IF(F44=1,IFERROR(H44/J44,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F44=1,IFERROR(H44/J44,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB44" s="51">
@@ -21098,7 +21124,7 @@
         <v/>
       </c>
       <c r="AG44" s="43">
-        <f>IF(E44="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E44="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH44" s="17">
@@ -21122,7 +21148,7 @@
         <v/>
       </c>
       <c r="AM44" s="55">
-        <f>AH44-AJ44-AK44-AL44</f>
+        <f>AH44-AJ44-AK44-AL44-AD44*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN44" s="53">
@@ -21232,7 +21258,7 @@
         <v/>
       </c>
       <c r="X45" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y45" s="53">
@@ -21244,7 +21270,7 @@
         <v/>
       </c>
       <c r="AA45" s="53">
-        <f>IF(F45=1,IFERROR(H45/J45,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F45=1,IFERROR(H45/J45,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB45" s="51">
@@ -21268,7 +21294,7 @@
         <v/>
       </c>
       <c r="AG45" s="43">
-        <f>IF(E45="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E45="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH45" s="17">
@@ -21292,7 +21318,7 @@
         <v/>
       </c>
       <c r="AM45" s="55">
-        <f>AH45-AJ45-AK45-AL45</f>
+        <f>AH45-AJ45-AK45-AL45-AD45*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN45" s="53">
@@ -21402,7 +21428,7 @@
         <v/>
       </c>
       <c r="X46" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y46" s="53">
@@ -21414,7 +21440,7 @@
         <v/>
       </c>
       <c r="AA46" s="53">
-        <f>IF(F46=1,IFERROR(H46/J46,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F46=1,IFERROR(H46/J46,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB46" s="51">
@@ -21438,7 +21464,7 @@
         <v/>
       </c>
       <c r="AG46" s="43">
-        <f>IF(E46="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E46="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH46" s="17">
@@ -21462,7 +21488,7 @@
         <v/>
       </c>
       <c r="AM46" s="55">
-        <f>AH46-AJ46-AK46-AL46</f>
+        <f>AH46-AJ46-AK46-AL46-AD46*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN46" s="53">
@@ -21572,7 +21598,7 @@
         <v/>
       </c>
       <c r="X47" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y47" s="53">
@@ -21584,7 +21610,7 @@
         <v/>
       </c>
       <c r="AA47" s="53">
-        <f>IF(F47=1,IFERROR(H47/J47,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F47=1,IFERROR(H47/J47,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB47" s="51">
@@ -21608,7 +21634,7 @@
         <v/>
       </c>
       <c r="AG47" s="43">
-        <f>IF(E47="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E47="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH47" s="17">
@@ -21632,7 +21658,7 @@
         <v/>
       </c>
       <c r="AM47" s="55">
-        <f>AH47-AJ47-AK47-AL47</f>
+        <f>AH47-AJ47-AK47-AL47-AD47*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN47" s="53">
@@ -21742,7 +21768,7 @@
         <v/>
       </c>
       <c r="X48" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y48" s="53">
@@ -21754,7 +21780,7 @@
         <v/>
       </c>
       <c r="AA48" s="53">
-        <f>IF(F48=1,IFERROR(H48/J48,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F48=1,IFERROR(H48/J48,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB48" s="51">
@@ -21778,7 +21804,7 @@
         <v/>
       </c>
       <c r="AG48" s="43">
-        <f>IF(E48="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E48="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH48" s="17">
@@ -21802,7 +21828,7 @@
         <v/>
       </c>
       <c r="AM48" s="55">
-        <f>AH48-AJ48-AK48-AL48</f>
+        <f>AH48-AJ48-AK48-AL48-AD48*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN48" s="53">
@@ -21912,7 +21938,7 @@
         <v/>
       </c>
       <c r="X49" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y49" s="53">
@@ -21924,7 +21950,7 @@
         <v/>
       </c>
       <c r="AA49" s="53">
-        <f>IF(F49=1,IFERROR(H49/J49,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F49=1,IFERROR(H49/J49,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB49" s="51">
@@ -21948,7 +21974,7 @@
         <v/>
       </c>
       <c r="AG49" s="43">
-        <f>IF(E49="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E49="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH49" s="17">
@@ -21972,7 +21998,7 @@
         <v/>
       </c>
       <c r="AM49" s="55">
-        <f>AH49-AJ49-AK49-AL49</f>
+        <f>AH49-AJ49-AK49-AL49-AD49*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN49" s="53">
@@ -22082,7 +22108,7 @@
         <v/>
       </c>
       <c r="X50" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y50" s="53">
@@ -22094,7 +22120,7 @@
         <v/>
       </c>
       <c r="AA50" s="53">
-        <f>IF(F50=1,IFERROR(H50/J50,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F50=1,IFERROR(H50/J50,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB50" s="51">
@@ -22118,7 +22144,7 @@
         <v/>
       </c>
       <c r="AG50" s="43">
-        <f>IF(E50="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E50="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH50" s="17">
@@ -22142,7 +22168,7 @@
         <v/>
       </c>
       <c r="AM50" s="55">
-        <f>AH50-AJ50-AK50-AL50</f>
+        <f>AH50-AJ50-AK50-AL50-AD50*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN50" s="53">
@@ -22252,7 +22278,7 @@
         <v/>
       </c>
       <c r="X51" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y51" s="53">
@@ -22264,7 +22290,7 @@
         <v/>
       </c>
       <c r="AA51" s="53">
-        <f>IF(F51=1,IFERROR(H51/J51,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F51=1,IFERROR(H51/J51,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB51" s="51">
@@ -22288,7 +22314,7 @@
         <v/>
       </c>
       <c r="AG51" s="43">
-        <f>IF(E51="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E51="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH51" s="17">
@@ -22312,7 +22338,7 @@
         <v/>
       </c>
       <c r="AM51" s="55">
-        <f>AH51-AJ51-AK51-AL51</f>
+        <f>AH51-AJ51-AK51-AL51-AD51*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN51" s="53">
@@ -22422,7 +22448,7 @@
         <v/>
       </c>
       <c r="X52" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y52" s="53">
@@ -22434,7 +22460,7 @@
         <v/>
       </c>
       <c r="AA52" s="53">
-        <f>IF(F52=1,IFERROR(H52/J52,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F52=1,IFERROR(H52/J52,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB52" s="51">
@@ -22458,7 +22484,7 @@
         <v/>
       </c>
       <c r="AG52" s="43">
-        <f>IF(E52="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E52="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH52" s="17">
@@ -22482,7 +22508,7 @@
         <v/>
       </c>
       <c r="AM52" s="55">
-        <f>AH52-AJ52-AK52-AL52</f>
+        <f>AH52-AJ52-AK52-AL52-AD52*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN52" s="53">
@@ -22592,7 +22618,7 @@
         <v/>
       </c>
       <c r="X53" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y53" s="53">
@@ -22604,7 +22630,7 @@
         <v/>
       </c>
       <c r="AA53" s="53">
-        <f>IF(F53=1,IFERROR(H53/J53,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F53=1,IFERROR(H53/J53,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB53" s="51">
@@ -22628,7 +22654,7 @@
         <v/>
       </c>
       <c r="AG53" s="43">
-        <f>IF(E53="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E53="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH53" s="17">
@@ -22652,7 +22678,7 @@
         <v/>
       </c>
       <c r="AM53" s="55">
-        <f>AH53-AJ53-AK53-AL53</f>
+        <f>AH53-AJ53-AK53-AL53-AD53*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN53" s="53">
@@ -22762,7 +22788,7 @@
         <v/>
       </c>
       <c r="X54" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y54" s="53">
@@ -22774,7 +22800,7 @@
         <v/>
       </c>
       <c r="AA54" s="53">
-        <f>IF(F54=1,IFERROR(H54/J54,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F54=1,IFERROR(H54/J54,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB54" s="51">
@@ -22798,7 +22824,7 @@
         <v/>
       </c>
       <c r="AG54" s="43">
-        <f>IF(E54="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E54="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH54" s="17">
@@ -22822,7 +22848,7 @@
         <v/>
       </c>
       <c r="AM54" s="55">
-        <f>AH54-AJ54-AK54-AL54</f>
+        <f>AH54-AJ54-AK54-AL54-AD54*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN54" s="53">
@@ -22932,7 +22958,7 @@
         <v/>
       </c>
       <c r="X55" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y55" s="53">
@@ -22944,7 +22970,7 @@
         <v/>
       </c>
       <c r="AA55" s="53">
-        <f>IF(F55=1,IFERROR(H55/J55,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F55=1,IFERROR(H55/J55,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB55" s="51">
@@ -22968,7 +22994,7 @@
         <v/>
       </c>
       <c r="AG55" s="43">
-        <f>IF(E55="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E55="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH55" s="17">
@@ -22992,7 +23018,7 @@
         <v/>
       </c>
       <c r="AM55" s="55">
-        <f>AH55-AJ55-AK55-AL55</f>
+        <f>AH55-AJ55-AK55-AL55-AD55*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN55" s="53">
@@ -23102,7 +23128,7 @@
         <v/>
       </c>
       <c r="X56" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y56" s="53">
@@ -23114,7 +23140,7 @@
         <v/>
       </c>
       <c r="AA56" s="53">
-        <f>IF(F56=1,IFERROR(H56/J56,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F56=1,IFERROR(H56/J56,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB56" s="51">
@@ -23138,7 +23164,7 @@
         <v/>
       </c>
       <c r="AG56" s="43">
-        <f>IF(E56="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E56="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH56" s="17">
@@ -23162,7 +23188,7 @@
         <v/>
       </c>
       <c r="AM56" s="55">
-        <f>AH56-AJ56-AK56-AL56</f>
+        <f>AH56-AJ56-AK56-AL56-AD56*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN56" s="53">
@@ -23272,7 +23298,7 @@
         <v/>
       </c>
       <c r="X57" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y57" s="53">
@@ -23284,7 +23310,7 @@
         <v/>
       </c>
       <c r="AA57" s="53">
-        <f>IF(F57=1,IFERROR(H57/J57,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F57=1,IFERROR(H57/J57,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB57" s="51">
@@ -23308,7 +23334,7 @@
         <v/>
       </c>
       <c r="AG57" s="43">
-        <f>IF(E57="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E57="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH57" s="17">
@@ -23332,7 +23358,7 @@
         <v/>
       </c>
       <c r="AM57" s="55">
-        <f>AH57-AJ57-AK57-AL57</f>
+        <f>AH57-AJ57-AK57-AL57-AD57*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN57" s="53">
@@ -23442,7 +23468,7 @@
         <v/>
       </c>
       <c r="X58" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y58" s="53">
@@ -23454,7 +23480,7 @@
         <v/>
       </c>
       <c r="AA58" s="53">
-        <f>IF(F58=1,IFERROR(H58/J58,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F58=1,IFERROR(H58/J58,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB58" s="51">
@@ -23478,7 +23504,7 @@
         <v/>
       </c>
       <c r="AG58" s="43">
-        <f>IF(E58="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E58="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH58" s="17">
@@ -23502,7 +23528,7 @@
         <v/>
       </c>
       <c r="AM58" s="55">
-        <f>AH58-AJ58-AK58-AL58</f>
+        <f>AH58-AJ58-AK58-AL58-AD58*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN58" s="53">
@@ -23612,7 +23638,7 @@
         <v/>
       </c>
       <c r="X59" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y59" s="53">
@@ -23624,7 +23650,7 @@
         <v/>
       </c>
       <c r="AA59" s="53">
-        <f>IF(F59=1,IFERROR(H59/J59,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F59=1,IFERROR(H59/J59,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB59" s="51">
@@ -23648,7 +23674,7 @@
         <v/>
       </c>
       <c r="AG59" s="43">
-        <f>IF(E59="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E59="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH59" s="17">
@@ -23672,7 +23698,7 @@
         <v/>
       </c>
       <c r="AM59" s="55">
-        <f>AH59-AJ59-AK59-AL59</f>
+        <f>AH59-AJ59-AK59-AL59-AD59*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN59" s="53">
@@ -23782,7 +23808,7 @@
         <v/>
       </c>
       <c r="X60" s="43">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$21)</f>
         <v/>
       </c>
       <c r="Y60" s="53">
@@ -23794,7 +23820,7 @@
         <v/>
       </c>
       <c r="AA60" s="53">
-        <f>IF(F60=1,IFERROR(H60/J60,'02_Leviers'!$D$21)+'02_Leviers'!$G$8,0)</f>
+        <f>IF(F60=1,IFERROR(H60/J60,'02_Leviers'!$D$22)+'02_Leviers'!$G$8,0)</f>
         <v/>
       </c>
       <c r="AB60" s="51">
@@ -23818,7 +23844,7 @@
         <v/>
       </c>
       <c r="AG60" s="43">
-        <f>IF(E60="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$19))*'02_Leviers'!$D$18,1)</f>
+        <f>IF(E60="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'02_Leviers'!$D$20))*'02_Leviers'!$D$18,1)</f>
         <v/>
       </c>
       <c r="AH60" s="17">
@@ -23842,7 +23868,7 @@
         <v/>
       </c>
       <c r="AM60" s="55">
-        <f>AH60-AJ60-AK60-AL60</f>
+        <f>AH60-AJ60-AK60-AL60-AD60*'02_Leviers'!$D$19*(1+'02_Leviers'!$G$11)</f>
         <v/>
       </c>
       <c r="AN60" s="53">

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -383,9 +383,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2330,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2338,15 +2335,15 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2354,14 +2351,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Simulateur &amp; conseil de décisions (planification rentrée) — impact AVANT → APRÈS</t>
+          <t>Simulateur &amp; conseil de décisions — logique CFO : on décide sur la MARGE DE CONTRIBUTION (col. H)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>EBITDA avant (optimal) :</t>
+          <t>EBITDA groupe AVANT :</t>
         </is>
       </c>
       <c r="D2" s="55">
@@ -2370,4017 +2367,4050 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>Somme Δ décisions :</t>
+          <t>Σ Δ décisions :</t>
         </is>
       </c>
       <c r="G2" s="55">
-        <f>SUM(P4:P61)</f>
+        <f>SUM(P6:P63)</f>
         <v/>
       </c>
       <c r="H2" s="30" t="n"/>
       <c r="I2" s="19" t="inlineStr">
         <is>
-          <t>EBITDA après :</t>
-        </is>
-      </c>
-      <c r="J2" s="47">
+          <t>EBITDA groupe APRÈS :</t>
+        </is>
+      </c>
+      <c r="K2" s="47">
         <f>D2+G2</f>
         <v/>
       </c>
-      <c r="K2" s="19" t="inlineStr">
-        <is>
-          <t>🔴 promos &lt; point mort :</t>
-        </is>
-      </c>
-      <c r="L2" s="69">
+      <c r="L2" s="30" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Structure / étudiant — AVANT :</t>
+        </is>
+      </c>
+      <c r="D3" s="55">
+        <f>('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>APRÈS (dilution) :</t>
+        </is>
+      </c>
+      <c r="G3" s="20">
+        <f>IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
+        <v/>
+      </c>
+      <c r="H3" s="30" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>🔴 promos contribution &lt; 0 :</t>
+        </is>
+      </c>
+      <c r="K3" s="69">
         <f>SUMPRODUCT(--('08_Moteur'!$AM$3:$AM$60&lt;0))</f>
         <v/>
       </c>
-      <c r="M2" s="70" t="inlineStr">
-        <is>
-          <t>→ gain potentiel si recos appliquées (col. « € si reco ») :</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>⚠ Fermer une promo n'économise PAS la structure (loyer, permanents, siège) : elle RESTE et se redilue sur les autres → on ferme UNIQUEMENT si la contribution (H) est négative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Marque</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Ville</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Programme</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Eff. Bud</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>Cl. auto</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>Cl. N-1</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Coûts directs
+évitables</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>MARGE DE
+CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Structure
+allouée</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Résultat
+tout compris</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>Rempl.</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>🤖 Reco</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>€ si reco</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>Motif</t>
         </is>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>Décision</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
-        <is>
-          <t>Cl. après</t>
-        </is>
-      </c>
-      <c r="N3" s="13" t="inlineStr">
-        <is>
-          <t>Eff. après</t>
-        </is>
-      </c>
-      <c r="O3" s="13" t="inlineStr">
-        <is>
-          <t>Contrib après</t>
-        </is>
-      </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>Contribution
+après</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>Δ EBITDA</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="48">
-        <f>'08_Moteur'!A3</f>
-        <v/>
-      </c>
-      <c r="B4" s="10">
-        <f>'08_Moteur'!B3</f>
-        <v/>
-      </c>
-      <c r="C4" s="48">
-        <f>'08_Moteur'!C3</f>
-        <v/>
-      </c>
-      <c r="D4" s="10">
-        <f>'08_Moteur'!D3</f>
-        <v/>
-      </c>
-      <c r="E4" s="49">
-        <f>'08_Moteur'!AD3</f>
-        <v/>
-      </c>
-      <c r="F4" s="49">
-        <f>'08_Moteur'!AI3</f>
-        <v/>
-      </c>
-      <c r="G4" s="49">
-        <f>'08_Moteur'!M3</f>
-        <v/>
-      </c>
-      <c r="H4" s="71">
-        <f>'08_Moteur'!AN3</f>
-        <v/>
-      </c>
-      <c r="I4" s="72">
-        <f>IF('08_Moteur'!AM3&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN3&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN3&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="J4" s="17">
-        <f>IF('08_Moteur'!AM3&lt;0,-'08_Moteur'!AM3,IF('08_Moteur'!AN3&gt;=0.95,'08_Moteur'!O3*'08_Moteur'!AO3-'08_Moteur'!U3,0))</f>
-        <v/>
-      </c>
-      <c r="K4" s="29">
-        <f>IF('08_Moteur'!AM3&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN3&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN3&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M4" s="51">
-        <f>IF(L4="Ne pas lancer",0,IF(L4="Statu quo",MAX('08_Moteur'!AI3,'08_Moteur'!M3),IF(L4="Ouvrir +1",'08_Moteur'!AI3+1,'08_Moteur'!AI3)))</f>
-        <v/>
-      </c>
-      <c r="N4" s="51">
-        <f>IF(L4="Ne pas lancer",0,'08_Moteur'!AD3)</f>
-        <v/>
-      </c>
-      <c r="O4" s="17">
-        <f>N4*'08_Moteur'!AE3*'08_Moteur'!AF3+IF(L4="Ne pas lancer",0,'08_Moteur'!AB3)*'02_Leviers'!$D$16-M4*'08_Moteur'!U3-N4*'08_Moteur'!R3*(1+'02_Leviers'!$G$11)-IF(L4="Ne pas lancer",0,'08_Moteur'!AL3)</f>
-        <v/>
-      </c>
-      <c r="P4" s="55">
-        <f>O4-'08_Moteur'!AM3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="48">
-        <f>'08_Moteur'!A4</f>
-        <v/>
-      </c>
-      <c r="B5" s="10">
-        <f>'08_Moteur'!B4</f>
-        <v/>
-      </c>
-      <c r="C5" s="48">
-        <f>'08_Moteur'!C4</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'08_Moteur'!D4</f>
-        <v/>
-      </c>
-      <c r="E5" s="49">
-        <f>'08_Moteur'!AD4</f>
-        <v/>
-      </c>
-      <c r="F5" s="49">
-        <f>'08_Moteur'!AI4</f>
-        <v/>
-      </c>
-      <c r="G5" s="49">
-        <f>'08_Moteur'!M4</f>
-        <v/>
-      </c>
-      <c r="H5" s="71">
-        <f>'08_Moteur'!AN4</f>
-        <v/>
-      </c>
-      <c r="I5" s="72">
-        <f>IF('08_Moteur'!AM4&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN4&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN4&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="J5" s="17">
-        <f>IF('08_Moteur'!AM4&lt;0,-'08_Moteur'!AM4,IF('08_Moteur'!AN4&gt;=0.95,'08_Moteur'!O4*'08_Moteur'!AO4-'08_Moteur'!U4,0))</f>
-        <v/>
-      </c>
-      <c r="K5" s="29">
-        <f>IF('08_Moteur'!AM4&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN4&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN4&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M5" s="51">
-        <f>IF(L5="Ne pas lancer",0,IF(L5="Statu quo",MAX('08_Moteur'!AI4,'08_Moteur'!M4),IF(L5="Ouvrir +1",'08_Moteur'!AI4+1,'08_Moteur'!AI4)))</f>
-        <v/>
-      </c>
-      <c r="N5" s="51">
-        <f>IF(L5="Ne pas lancer",0,'08_Moteur'!AD4)</f>
-        <v/>
-      </c>
-      <c r="O5" s="17">
-        <f>N5*'08_Moteur'!AE4*'08_Moteur'!AF4+IF(L5="Ne pas lancer",0,'08_Moteur'!AB4)*'02_Leviers'!$D$16-M5*'08_Moteur'!U4-N5*'08_Moteur'!R4*(1+'02_Leviers'!$G$11)-IF(L5="Ne pas lancer",0,'08_Moteur'!AL4)</f>
-        <v/>
-      </c>
-      <c r="P5" s="55">
-        <f>O5-'08_Moteur'!AM4</f>
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="48">
-        <f>'08_Moteur'!A5</f>
+        <f>'08_Moteur'!A3</f>
         <v/>
       </c>
       <c r="B6" s="10">
-        <f>'08_Moteur'!B5</f>
+        <f>'08_Moteur'!B3</f>
         <v/>
       </c>
       <c r="C6" s="48">
-        <f>'08_Moteur'!C5</f>
+        <f>'08_Moteur'!C3</f>
         <v/>
       </c>
       <c r="D6" s="10">
-        <f>'08_Moteur'!D5</f>
+        <f>'08_Moteur'!D3</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>'08_Moteur'!AD5</f>
-        <v/>
-      </c>
-      <c r="F6" s="49">
-        <f>'08_Moteur'!AI5</f>
-        <v/>
-      </c>
-      <c r="G6" s="49">
-        <f>'08_Moteur'!M5</f>
-        <v/>
-      </c>
-      <c r="H6" s="71">
-        <f>'08_Moteur'!AN5</f>
-        <v/>
-      </c>
-      <c r="I6" s="72">
-        <f>IF('08_Moteur'!AM5&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN5&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN5&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD3</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>'08_Moteur'!AH3</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>F6-'08_Moteur'!AM3</f>
+        <v/>
+      </c>
+      <c r="H6" s="64">
+        <f>'08_Moteur'!AM3</f>
+        <v/>
+      </c>
+      <c r="I6" s="17">
+        <f>E6*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J6" s="17">
-        <f>IF('08_Moteur'!AM5&lt;0,-'08_Moteur'!AM5,IF('08_Moteur'!AN5&gt;=0.95,'08_Moteur'!O5*'08_Moteur'!AO5-'08_Moteur'!U5,0))</f>
-        <v/>
-      </c>
-      <c r="K6" s="29">
-        <f>IF('08_Moteur'!AM5&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN5&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN5&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M6" s="51">
-        <f>IF(L6="Ne pas lancer",0,IF(L6="Statu quo",MAX('08_Moteur'!AI5,'08_Moteur'!M5),IF(L6="Ouvrir +1",'08_Moteur'!AI5+1,'08_Moteur'!AI5)))</f>
-        <v/>
-      </c>
-      <c r="N6" s="51">
-        <f>IF(L6="Ne pas lancer",0,'08_Moteur'!AD5)</f>
-        <v/>
+        <f>H6-I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="70">
+        <f>'08_Moteur'!AN3</f>
+        <v/>
+      </c>
+      <c r="L6" s="71">
+        <f>IF(H6&lt;0,"🔴 Ne pas ouvrir",IF(K6&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K6&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M6" s="72">
+        <f>IF(H6&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K6&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K6&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O6" s="17">
-        <f>N6*'08_Moteur'!AE5*'08_Moteur'!AF5+IF(L6="Ne pas lancer",0,'08_Moteur'!AB5)*'02_Leviers'!$D$16-M6*'08_Moteur'!U5-N6*'08_Moteur'!R5*(1+'02_Leviers'!$G$11)-IF(L6="Ne pas lancer",0,'08_Moteur'!AL5)</f>
+        <f>IF(N6="Ne pas ouvrir",0,IF(N6="Ouvrir +1 classe",H6-'08_Moteur'!U3,IF(N6="Économiser 1 classe",H6+('08_Moteur'!AI3-MAX(1,'08_Moteur'!AI3-1))*'08_Moteur'!U3,H6)))</f>
         <v/>
       </c>
       <c r="P6" s="55">
-        <f>O6-'08_Moteur'!AM5</f>
+        <f>O6-H6</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="48">
-        <f>'08_Moteur'!A6</f>
+        <f>'08_Moteur'!A4</f>
         <v/>
       </c>
       <c r="B7" s="10">
-        <f>'08_Moteur'!B6</f>
+        <f>'08_Moteur'!B4</f>
         <v/>
       </c>
       <c r="C7" s="48">
-        <f>'08_Moteur'!C6</f>
+        <f>'08_Moteur'!C4</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>'08_Moteur'!D6</f>
+        <f>'08_Moteur'!D4</f>
         <v/>
       </c>
       <c r="E7" s="49">
-        <f>'08_Moteur'!AD6</f>
-        <v/>
-      </c>
-      <c r="F7" s="49">
-        <f>'08_Moteur'!AI6</f>
-        <v/>
-      </c>
-      <c r="G7" s="49">
-        <f>'08_Moteur'!M6</f>
-        <v/>
-      </c>
-      <c r="H7" s="71">
-        <f>'08_Moteur'!AN6</f>
-        <v/>
-      </c>
-      <c r="I7" s="72">
-        <f>IF('08_Moteur'!AM6&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN6&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN6&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD4</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>'08_Moteur'!AH4</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>F7-'08_Moteur'!AM4</f>
+        <v/>
+      </c>
+      <c r="H7" s="64">
+        <f>'08_Moteur'!AM4</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>E7*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J7" s="17">
-        <f>IF('08_Moteur'!AM6&lt;0,-'08_Moteur'!AM6,IF('08_Moteur'!AN6&gt;=0.95,'08_Moteur'!O6*'08_Moteur'!AO6-'08_Moteur'!U6,0))</f>
-        <v/>
-      </c>
-      <c r="K7" s="29">
-        <f>IF('08_Moteur'!AM6&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN6&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN6&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M7" s="51">
-        <f>IF(L7="Ne pas lancer",0,IF(L7="Statu quo",MAX('08_Moteur'!AI6,'08_Moteur'!M6),IF(L7="Ouvrir +1",'08_Moteur'!AI6+1,'08_Moteur'!AI6)))</f>
-        <v/>
-      </c>
-      <c r="N7" s="51">
-        <f>IF(L7="Ne pas lancer",0,'08_Moteur'!AD6)</f>
-        <v/>
+        <f>H7-I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="70">
+        <f>'08_Moteur'!AN4</f>
+        <v/>
+      </c>
+      <c r="L7" s="71">
+        <f>IF(H7&lt;0,"🔴 Ne pas ouvrir",IF(K7&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K7&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M7" s="72">
+        <f>IF(H7&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K7&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K7&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O7" s="17">
-        <f>N7*'08_Moteur'!AE6*'08_Moteur'!AF6+IF(L7="Ne pas lancer",0,'08_Moteur'!AB6)*'02_Leviers'!$D$16-M7*'08_Moteur'!U6-N7*'08_Moteur'!R6*(1+'02_Leviers'!$G$11)-IF(L7="Ne pas lancer",0,'08_Moteur'!AL6)</f>
+        <f>IF(N7="Ne pas ouvrir",0,IF(N7="Ouvrir +1 classe",H7-'08_Moteur'!U4,IF(N7="Économiser 1 classe",H7+('08_Moteur'!AI4-MAX(1,'08_Moteur'!AI4-1))*'08_Moteur'!U4,H7)))</f>
         <v/>
       </c>
       <c r="P7" s="55">
-        <f>O7-'08_Moteur'!AM6</f>
+        <f>O7-H7</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="48">
-        <f>'08_Moteur'!A7</f>
+        <f>'08_Moteur'!A5</f>
         <v/>
       </c>
       <c r="B8" s="10">
-        <f>'08_Moteur'!B7</f>
+        <f>'08_Moteur'!B5</f>
         <v/>
       </c>
       <c r="C8" s="48">
-        <f>'08_Moteur'!C7</f>
+        <f>'08_Moteur'!C5</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>'08_Moteur'!D7</f>
+        <f>'08_Moteur'!D5</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>'08_Moteur'!AD7</f>
-        <v/>
-      </c>
-      <c r="F8" s="49">
-        <f>'08_Moteur'!AI7</f>
-        <v/>
-      </c>
-      <c r="G8" s="49">
-        <f>'08_Moteur'!M7</f>
-        <v/>
-      </c>
-      <c r="H8" s="71">
-        <f>'08_Moteur'!AN7</f>
-        <v/>
-      </c>
-      <c r="I8" s="72">
-        <f>IF('08_Moteur'!AM7&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN7&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN7&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD5</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>'08_Moteur'!AH5</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>F8-'08_Moteur'!AM5</f>
+        <v/>
+      </c>
+      <c r="H8" s="64">
+        <f>'08_Moteur'!AM5</f>
+        <v/>
+      </c>
+      <c r="I8" s="17">
+        <f>E8*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>IF('08_Moteur'!AM7&lt;0,-'08_Moteur'!AM7,IF('08_Moteur'!AN7&gt;=0.95,'08_Moteur'!O7*'08_Moteur'!AO7-'08_Moteur'!U7,0))</f>
-        <v/>
-      </c>
-      <c r="K8" s="29">
-        <f>IF('08_Moteur'!AM7&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN7&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN7&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M8" s="51">
-        <f>IF(L8="Ne pas lancer",0,IF(L8="Statu quo",MAX('08_Moteur'!AI7,'08_Moteur'!M7),IF(L8="Ouvrir +1",'08_Moteur'!AI7+1,'08_Moteur'!AI7)))</f>
-        <v/>
-      </c>
-      <c r="N8" s="51">
-        <f>IF(L8="Ne pas lancer",0,'08_Moteur'!AD7)</f>
-        <v/>
+        <f>H8-I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="70">
+        <f>'08_Moteur'!AN5</f>
+        <v/>
+      </c>
+      <c r="L8" s="71">
+        <f>IF(H8&lt;0,"🔴 Ne pas ouvrir",IF(K8&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K8&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M8" s="72">
+        <f>IF(H8&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K8&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K8&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O8" s="17">
-        <f>N8*'08_Moteur'!AE7*'08_Moteur'!AF7+IF(L8="Ne pas lancer",0,'08_Moteur'!AB7)*'02_Leviers'!$D$16-M8*'08_Moteur'!U7-N8*'08_Moteur'!R7*(1+'02_Leviers'!$G$11)-IF(L8="Ne pas lancer",0,'08_Moteur'!AL7)</f>
+        <f>IF(N8="Ne pas ouvrir",0,IF(N8="Ouvrir +1 classe",H8-'08_Moteur'!U5,IF(N8="Économiser 1 classe",H8+('08_Moteur'!AI5-MAX(1,'08_Moteur'!AI5-1))*'08_Moteur'!U5,H8)))</f>
         <v/>
       </c>
       <c r="P8" s="55">
-        <f>O8-'08_Moteur'!AM7</f>
+        <f>O8-H8</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="48">
-        <f>'08_Moteur'!A8</f>
+        <f>'08_Moteur'!A6</f>
         <v/>
       </c>
       <c r="B9" s="10">
-        <f>'08_Moteur'!B8</f>
+        <f>'08_Moteur'!B6</f>
         <v/>
       </c>
       <c r="C9" s="48">
-        <f>'08_Moteur'!C8</f>
+        <f>'08_Moteur'!C6</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>'08_Moteur'!D8</f>
+        <f>'08_Moteur'!D6</f>
         <v/>
       </c>
       <c r="E9" s="49">
-        <f>'08_Moteur'!AD8</f>
-        <v/>
-      </c>
-      <c r="F9" s="49">
-        <f>'08_Moteur'!AI8</f>
-        <v/>
-      </c>
-      <c r="G9" s="49">
-        <f>'08_Moteur'!M8</f>
-        <v/>
-      </c>
-      <c r="H9" s="71">
-        <f>'08_Moteur'!AN8</f>
-        <v/>
-      </c>
-      <c r="I9" s="72">
-        <f>IF('08_Moteur'!AM8&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN8&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN8&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD6</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>'08_Moteur'!AH6</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>F9-'08_Moteur'!AM6</f>
+        <v/>
+      </c>
+      <c r="H9" s="64">
+        <f>'08_Moteur'!AM6</f>
+        <v/>
+      </c>
+      <c r="I9" s="17">
+        <f>E9*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IF('08_Moteur'!AM8&lt;0,-'08_Moteur'!AM8,IF('08_Moteur'!AN8&gt;=0.95,'08_Moteur'!O8*'08_Moteur'!AO8-'08_Moteur'!U8,0))</f>
-        <v/>
-      </c>
-      <c r="K9" s="29">
-        <f>IF('08_Moteur'!AM8&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN8&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN8&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M9" s="51">
-        <f>IF(L9="Ne pas lancer",0,IF(L9="Statu quo",MAX('08_Moteur'!AI8,'08_Moteur'!M8),IF(L9="Ouvrir +1",'08_Moteur'!AI8+1,'08_Moteur'!AI8)))</f>
-        <v/>
-      </c>
-      <c r="N9" s="51">
-        <f>IF(L9="Ne pas lancer",0,'08_Moteur'!AD8)</f>
-        <v/>
+        <f>H9-I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="70">
+        <f>'08_Moteur'!AN6</f>
+        <v/>
+      </c>
+      <c r="L9" s="71">
+        <f>IF(H9&lt;0,"🔴 Ne pas ouvrir",IF(K9&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K9&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M9" s="72">
+        <f>IF(H9&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K9&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K9&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O9" s="17">
-        <f>N9*'08_Moteur'!AE8*'08_Moteur'!AF8+IF(L9="Ne pas lancer",0,'08_Moteur'!AB8)*'02_Leviers'!$D$16-M9*'08_Moteur'!U8-N9*'08_Moteur'!R8*(1+'02_Leviers'!$G$11)-IF(L9="Ne pas lancer",0,'08_Moteur'!AL8)</f>
+        <f>IF(N9="Ne pas ouvrir",0,IF(N9="Ouvrir +1 classe",H9-'08_Moteur'!U6,IF(N9="Économiser 1 classe",H9+('08_Moteur'!AI6-MAX(1,'08_Moteur'!AI6-1))*'08_Moteur'!U6,H9)))</f>
         <v/>
       </c>
       <c r="P9" s="55">
-        <f>O9-'08_Moteur'!AM8</f>
+        <f>O9-H9</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="48">
-        <f>'08_Moteur'!A9</f>
+        <f>'08_Moteur'!A7</f>
         <v/>
       </c>
       <c r="B10" s="10">
-        <f>'08_Moteur'!B9</f>
+        <f>'08_Moteur'!B7</f>
         <v/>
       </c>
       <c r="C10" s="48">
-        <f>'08_Moteur'!C9</f>
+        <f>'08_Moteur'!C7</f>
         <v/>
       </c>
       <c r="D10" s="10">
-        <f>'08_Moteur'!D9</f>
+        <f>'08_Moteur'!D7</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>'08_Moteur'!AD9</f>
-        <v/>
-      </c>
-      <c r="F10" s="49">
-        <f>'08_Moteur'!AI9</f>
-        <v/>
-      </c>
-      <c r="G10" s="49">
-        <f>'08_Moteur'!M9</f>
-        <v/>
-      </c>
-      <c r="H10" s="71">
-        <f>'08_Moteur'!AN9</f>
-        <v/>
-      </c>
-      <c r="I10" s="72">
-        <f>IF('08_Moteur'!AM9&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN9&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN9&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD7</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>'08_Moteur'!AH7</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>F10-'08_Moteur'!AM7</f>
+        <v/>
+      </c>
+      <c r="H10" s="64">
+        <f>'08_Moteur'!AM7</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>E10*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>IF('08_Moteur'!AM9&lt;0,-'08_Moteur'!AM9,IF('08_Moteur'!AN9&gt;=0.95,'08_Moteur'!O9*'08_Moteur'!AO9-'08_Moteur'!U9,0))</f>
-        <v/>
-      </c>
-      <c r="K10" s="29">
-        <f>IF('08_Moteur'!AM9&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN9&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN9&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M10" s="51">
-        <f>IF(L10="Ne pas lancer",0,IF(L10="Statu quo",MAX('08_Moteur'!AI9,'08_Moteur'!M9),IF(L10="Ouvrir +1",'08_Moteur'!AI9+1,'08_Moteur'!AI9)))</f>
-        <v/>
-      </c>
-      <c r="N10" s="51">
-        <f>IF(L10="Ne pas lancer",0,'08_Moteur'!AD9)</f>
-        <v/>
+        <f>H10-I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="70">
+        <f>'08_Moteur'!AN7</f>
+        <v/>
+      </c>
+      <c r="L10" s="71">
+        <f>IF(H10&lt;0,"🔴 Ne pas ouvrir",IF(K10&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K10&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M10" s="72">
+        <f>IF(H10&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K10&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K10&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O10" s="17">
-        <f>N10*'08_Moteur'!AE9*'08_Moteur'!AF9+IF(L10="Ne pas lancer",0,'08_Moteur'!AB9)*'02_Leviers'!$D$16-M10*'08_Moteur'!U9-N10*'08_Moteur'!R9*(1+'02_Leviers'!$G$11)-IF(L10="Ne pas lancer",0,'08_Moteur'!AL9)</f>
+        <f>IF(N10="Ne pas ouvrir",0,IF(N10="Ouvrir +1 classe",H10-'08_Moteur'!U7,IF(N10="Économiser 1 classe",H10+('08_Moteur'!AI7-MAX(1,'08_Moteur'!AI7-1))*'08_Moteur'!U7,H10)))</f>
         <v/>
       </c>
       <c r="P10" s="55">
-        <f>O10-'08_Moteur'!AM9</f>
+        <f>O10-H10</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="48">
-        <f>'08_Moteur'!A10</f>
+        <f>'08_Moteur'!A8</f>
         <v/>
       </c>
       <c r="B11" s="10">
-        <f>'08_Moteur'!B10</f>
+        <f>'08_Moteur'!B8</f>
         <v/>
       </c>
       <c r="C11" s="48">
-        <f>'08_Moteur'!C10</f>
+        <f>'08_Moteur'!C8</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>'08_Moteur'!D10</f>
+        <f>'08_Moteur'!D8</f>
         <v/>
       </c>
       <c r="E11" s="49">
-        <f>'08_Moteur'!AD10</f>
-        <v/>
-      </c>
-      <c r="F11" s="49">
-        <f>'08_Moteur'!AI10</f>
-        <v/>
-      </c>
-      <c r="G11" s="49">
-        <f>'08_Moteur'!M10</f>
-        <v/>
-      </c>
-      <c r="H11" s="71">
-        <f>'08_Moteur'!AN10</f>
-        <v/>
-      </c>
-      <c r="I11" s="72">
-        <f>IF('08_Moteur'!AM10&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN10&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN10&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD8</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>'08_Moteur'!AH8</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>F11-'08_Moteur'!AM8</f>
+        <v/>
+      </c>
+      <c r="H11" s="64">
+        <f>'08_Moteur'!AM8</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>E11*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>IF('08_Moteur'!AM10&lt;0,-'08_Moteur'!AM10,IF('08_Moteur'!AN10&gt;=0.95,'08_Moteur'!O10*'08_Moteur'!AO10-'08_Moteur'!U10,0))</f>
-        <v/>
-      </c>
-      <c r="K11" s="29">
-        <f>IF('08_Moteur'!AM10&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN10&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN10&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M11" s="51">
-        <f>IF(L11="Ne pas lancer",0,IF(L11="Statu quo",MAX('08_Moteur'!AI10,'08_Moteur'!M10),IF(L11="Ouvrir +1",'08_Moteur'!AI10+1,'08_Moteur'!AI10)))</f>
-        <v/>
-      </c>
-      <c r="N11" s="51">
-        <f>IF(L11="Ne pas lancer",0,'08_Moteur'!AD10)</f>
-        <v/>
+        <f>H11-I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="70">
+        <f>'08_Moteur'!AN8</f>
+        <v/>
+      </c>
+      <c r="L11" s="71">
+        <f>IF(H11&lt;0,"🔴 Ne pas ouvrir",IF(K11&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K11&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M11" s="72">
+        <f>IF(H11&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K11&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K11&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O11" s="17">
-        <f>N11*'08_Moteur'!AE10*'08_Moteur'!AF10+IF(L11="Ne pas lancer",0,'08_Moteur'!AB10)*'02_Leviers'!$D$16-M11*'08_Moteur'!U10-N11*'08_Moteur'!R10*(1+'02_Leviers'!$G$11)-IF(L11="Ne pas lancer",0,'08_Moteur'!AL10)</f>
+        <f>IF(N11="Ne pas ouvrir",0,IF(N11="Ouvrir +1 classe",H11-'08_Moteur'!U8,IF(N11="Économiser 1 classe",H11+('08_Moteur'!AI8-MAX(1,'08_Moteur'!AI8-1))*'08_Moteur'!U8,H11)))</f>
         <v/>
       </c>
       <c r="P11" s="55">
-        <f>O11-'08_Moteur'!AM10</f>
+        <f>O11-H11</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="48">
-        <f>'08_Moteur'!A11</f>
+        <f>'08_Moteur'!A9</f>
         <v/>
       </c>
       <c r="B12" s="10">
-        <f>'08_Moteur'!B11</f>
+        <f>'08_Moteur'!B9</f>
         <v/>
       </c>
       <c r="C12" s="48">
-        <f>'08_Moteur'!C11</f>
+        <f>'08_Moteur'!C9</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>'08_Moteur'!D11</f>
+        <f>'08_Moteur'!D9</f>
         <v/>
       </c>
       <c r="E12" s="49">
-        <f>'08_Moteur'!AD11</f>
-        <v/>
-      </c>
-      <c r="F12" s="49">
-        <f>'08_Moteur'!AI11</f>
-        <v/>
-      </c>
-      <c r="G12" s="49">
-        <f>'08_Moteur'!M11</f>
-        <v/>
-      </c>
-      <c r="H12" s="71">
-        <f>'08_Moteur'!AN11</f>
-        <v/>
-      </c>
-      <c r="I12" s="72">
-        <f>IF('08_Moteur'!AM11&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN11&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN11&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD9</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>'08_Moteur'!AH9</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>F12-'08_Moteur'!AM9</f>
+        <v/>
+      </c>
+      <c r="H12" s="64">
+        <f>'08_Moteur'!AM9</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>E12*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>IF('08_Moteur'!AM11&lt;0,-'08_Moteur'!AM11,IF('08_Moteur'!AN11&gt;=0.95,'08_Moteur'!O11*'08_Moteur'!AO11-'08_Moteur'!U11,0))</f>
-        <v/>
-      </c>
-      <c r="K12" s="29">
-        <f>IF('08_Moteur'!AM11&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN11&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN11&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M12" s="51">
-        <f>IF(L12="Ne pas lancer",0,IF(L12="Statu quo",MAX('08_Moteur'!AI11,'08_Moteur'!M11),IF(L12="Ouvrir +1",'08_Moteur'!AI11+1,'08_Moteur'!AI11)))</f>
-        <v/>
-      </c>
-      <c r="N12" s="51">
-        <f>IF(L12="Ne pas lancer",0,'08_Moteur'!AD11)</f>
-        <v/>
+        <f>H12-I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="70">
+        <f>'08_Moteur'!AN9</f>
+        <v/>
+      </c>
+      <c r="L12" s="71">
+        <f>IF(H12&lt;0,"🔴 Ne pas ouvrir",IF(K12&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K12&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M12" s="72">
+        <f>IF(H12&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K12&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K12&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O12" s="17">
-        <f>N12*'08_Moteur'!AE11*'08_Moteur'!AF11+IF(L12="Ne pas lancer",0,'08_Moteur'!AB11)*'02_Leviers'!$D$16-M12*'08_Moteur'!U11-N12*'08_Moteur'!R11*(1+'02_Leviers'!$G$11)-IF(L12="Ne pas lancer",0,'08_Moteur'!AL11)</f>
+        <f>IF(N12="Ne pas ouvrir",0,IF(N12="Ouvrir +1 classe",H12-'08_Moteur'!U9,IF(N12="Économiser 1 classe",H12+('08_Moteur'!AI9-MAX(1,'08_Moteur'!AI9-1))*'08_Moteur'!U9,H12)))</f>
         <v/>
       </c>
       <c r="P12" s="55">
-        <f>O12-'08_Moteur'!AM11</f>
+        <f>O12-H12</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="48">
-        <f>'08_Moteur'!A12</f>
+        <f>'08_Moteur'!A10</f>
         <v/>
       </c>
       <c r="B13" s="10">
-        <f>'08_Moteur'!B12</f>
+        <f>'08_Moteur'!B10</f>
         <v/>
       </c>
       <c r="C13" s="48">
-        <f>'08_Moteur'!C12</f>
+        <f>'08_Moteur'!C10</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>'08_Moteur'!D12</f>
+        <f>'08_Moteur'!D10</f>
         <v/>
       </c>
       <c r="E13" s="49">
-        <f>'08_Moteur'!AD12</f>
-        <v/>
-      </c>
-      <c r="F13" s="49">
-        <f>'08_Moteur'!AI12</f>
-        <v/>
-      </c>
-      <c r="G13" s="49">
-        <f>'08_Moteur'!M12</f>
-        <v/>
-      </c>
-      <c r="H13" s="71">
-        <f>'08_Moteur'!AN12</f>
-        <v/>
-      </c>
-      <c r="I13" s="72">
-        <f>IF('08_Moteur'!AM12&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN12&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN12&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD10</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>'08_Moteur'!AH10</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>F13-'08_Moteur'!AM10</f>
+        <v/>
+      </c>
+      <c r="H13" s="64">
+        <f>'08_Moteur'!AM10</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>E13*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>IF('08_Moteur'!AM12&lt;0,-'08_Moteur'!AM12,IF('08_Moteur'!AN12&gt;=0.95,'08_Moteur'!O12*'08_Moteur'!AO12-'08_Moteur'!U12,0))</f>
-        <v/>
-      </c>
-      <c r="K13" s="29">
-        <f>IF('08_Moteur'!AM12&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN12&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN12&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M13" s="51">
-        <f>IF(L13="Ne pas lancer",0,IF(L13="Statu quo",MAX('08_Moteur'!AI12,'08_Moteur'!M12),IF(L13="Ouvrir +1",'08_Moteur'!AI12+1,'08_Moteur'!AI12)))</f>
-        <v/>
-      </c>
-      <c r="N13" s="51">
-        <f>IF(L13="Ne pas lancer",0,'08_Moteur'!AD12)</f>
-        <v/>
+        <f>H13-I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="70">
+        <f>'08_Moteur'!AN10</f>
+        <v/>
+      </c>
+      <c r="L13" s="71">
+        <f>IF(H13&lt;0,"🔴 Ne pas ouvrir",IF(K13&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K13&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M13" s="72">
+        <f>IF(H13&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K13&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K13&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O13" s="17">
-        <f>N13*'08_Moteur'!AE12*'08_Moteur'!AF12+IF(L13="Ne pas lancer",0,'08_Moteur'!AB12)*'02_Leviers'!$D$16-M13*'08_Moteur'!U12-N13*'08_Moteur'!R12*(1+'02_Leviers'!$G$11)-IF(L13="Ne pas lancer",0,'08_Moteur'!AL12)</f>
+        <f>IF(N13="Ne pas ouvrir",0,IF(N13="Ouvrir +1 classe",H13-'08_Moteur'!U10,IF(N13="Économiser 1 classe",H13+('08_Moteur'!AI10-MAX(1,'08_Moteur'!AI10-1))*'08_Moteur'!U10,H13)))</f>
         <v/>
       </c>
       <c r="P13" s="55">
-        <f>O13-'08_Moteur'!AM12</f>
+        <f>O13-H13</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="48">
-        <f>'08_Moteur'!A13</f>
+        <f>'08_Moteur'!A11</f>
         <v/>
       </c>
       <c r="B14" s="10">
-        <f>'08_Moteur'!B13</f>
+        <f>'08_Moteur'!B11</f>
         <v/>
       </c>
       <c r="C14" s="48">
-        <f>'08_Moteur'!C13</f>
+        <f>'08_Moteur'!C11</f>
         <v/>
       </c>
       <c r="D14" s="10">
-        <f>'08_Moteur'!D13</f>
+        <f>'08_Moteur'!D11</f>
         <v/>
       </c>
       <c r="E14" s="49">
-        <f>'08_Moteur'!AD13</f>
-        <v/>
-      </c>
-      <c r="F14" s="49">
-        <f>'08_Moteur'!AI13</f>
-        <v/>
-      </c>
-      <c r="G14" s="49">
-        <f>'08_Moteur'!M13</f>
-        <v/>
-      </c>
-      <c r="H14" s="71">
-        <f>'08_Moteur'!AN13</f>
-        <v/>
-      </c>
-      <c r="I14" s="72">
-        <f>IF('08_Moteur'!AM13&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN13&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN13&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD11</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>'08_Moteur'!AH11</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>F14-'08_Moteur'!AM11</f>
+        <v/>
+      </c>
+      <c r="H14" s="64">
+        <f>'08_Moteur'!AM11</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>E14*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>IF('08_Moteur'!AM13&lt;0,-'08_Moteur'!AM13,IF('08_Moteur'!AN13&gt;=0.95,'08_Moteur'!O13*'08_Moteur'!AO13-'08_Moteur'!U13,0))</f>
-        <v/>
-      </c>
-      <c r="K14" s="29">
-        <f>IF('08_Moteur'!AM13&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN13&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN13&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M14" s="51">
-        <f>IF(L14="Ne pas lancer",0,IF(L14="Statu quo",MAX('08_Moteur'!AI13,'08_Moteur'!M13),IF(L14="Ouvrir +1",'08_Moteur'!AI13+1,'08_Moteur'!AI13)))</f>
-        <v/>
-      </c>
-      <c r="N14" s="51">
-        <f>IF(L14="Ne pas lancer",0,'08_Moteur'!AD13)</f>
-        <v/>
+        <f>H14-I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="70">
+        <f>'08_Moteur'!AN11</f>
+        <v/>
+      </c>
+      <c r="L14" s="71">
+        <f>IF(H14&lt;0,"🔴 Ne pas ouvrir",IF(K14&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K14&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M14" s="72">
+        <f>IF(H14&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K14&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K14&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O14" s="17">
-        <f>N14*'08_Moteur'!AE13*'08_Moteur'!AF13+IF(L14="Ne pas lancer",0,'08_Moteur'!AB13)*'02_Leviers'!$D$16-M14*'08_Moteur'!U13-N14*'08_Moteur'!R13*(1+'02_Leviers'!$G$11)-IF(L14="Ne pas lancer",0,'08_Moteur'!AL13)</f>
+        <f>IF(N14="Ne pas ouvrir",0,IF(N14="Ouvrir +1 classe",H14-'08_Moteur'!U11,IF(N14="Économiser 1 classe",H14+('08_Moteur'!AI11-MAX(1,'08_Moteur'!AI11-1))*'08_Moteur'!U11,H14)))</f>
         <v/>
       </c>
       <c r="P14" s="55">
-        <f>O14-'08_Moteur'!AM13</f>
+        <f>O14-H14</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="48">
-        <f>'08_Moteur'!A14</f>
+        <f>'08_Moteur'!A12</f>
         <v/>
       </c>
       <c r="B15" s="10">
-        <f>'08_Moteur'!B14</f>
+        <f>'08_Moteur'!B12</f>
         <v/>
       </c>
       <c r="C15" s="48">
-        <f>'08_Moteur'!C14</f>
+        <f>'08_Moteur'!C12</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>'08_Moteur'!D14</f>
+        <f>'08_Moteur'!D12</f>
         <v/>
       </c>
       <c r="E15" s="49">
-        <f>'08_Moteur'!AD14</f>
-        <v/>
-      </c>
-      <c r="F15" s="49">
-        <f>'08_Moteur'!AI14</f>
-        <v/>
-      </c>
-      <c r="G15" s="49">
-        <f>'08_Moteur'!M14</f>
-        <v/>
-      </c>
-      <c r="H15" s="71">
-        <f>'08_Moteur'!AN14</f>
-        <v/>
-      </c>
-      <c r="I15" s="72">
-        <f>IF('08_Moteur'!AM14&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN14&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN14&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD12</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>'08_Moteur'!AH12</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>F15-'08_Moteur'!AM12</f>
+        <v/>
+      </c>
+      <c r="H15" s="64">
+        <f>'08_Moteur'!AM12</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>E15*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>IF('08_Moteur'!AM14&lt;0,-'08_Moteur'!AM14,IF('08_Moteur'!AN14&gt;=0.95,'08_Moteur'!O14*'08_Moteur'!AO14-'08_Moteur'!U14,0))</f>
-        <v/>
-      </c>
-      <c r="K15" s="29">
-        <f>IF('08_Moteur'!AM14&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN14&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN14&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M15" s="51">
-        <f>IF(L15="Ne pas lancer",0,IF(L15="Statu quo",MAX('08_Moteur'!AI14,'08_Moteur'!M14),IF(L15="Ouvrir +1",'08_Moteur'!AI14+1,'08_Moteur'!AI14)))</f>
-        <v/>
-      </c>
-      <c r="N15" s="51">
-        <f>IF(L15="Ne pas lancer",0,'08_Moteur'!AD14)</f>
-        <v/>
+        <f>H15-I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="70">
+        <f>'08_Moteur'!AN12</f>
+        <v/>
+      </c>
+      <c r="L15" s="71">
+        <f>IF(H15&lt;0,"🔴 Ne pas ouvrir",IF(K15&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K15&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M15" s="72">
+        <f>IF(H15&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K15&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K15&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O15" s="17">
-        <f>N15*'08_Moteur'!AE14*'08_Moteur'!AF14+IF(L15="Ne pas lancer",0,'08_Moteur'!AB14)*'02_Leviers'!$D$16-M15*'08_Moteur'!U14-N15*'08_Moteur'!R14*(1+'02_Leviers'!$G$11)-IF(L15="Ne pas lancer",0,'08_Moteur'!AL14)</f>
+        <f>IF(N15="Ne pas ouvrir",0,IF(N15="Ouvrir +1 classe",H15-'08_Moteur'!U12,IF(N15="Économiser 1 classe",H15+('08_Moteur'!AI12-MAX(1,'08_Moteur'!AI12-1))*'08_Moteur'!U12,H15)))</f>
         <v/>
       </c>
       <c r="P15" s="55">
-        <f>O15-'08_Moteur'!AM14</f>
+        <f>O15-H15</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="48">
-        <f>'08_Moteur'!A15</f>
+        <f>'08_Moteur'!A13</f>
         <v/>
       </c>
       <c r="B16" s="10">
-        <f>'08_Moteur'!B15</f>
+        <f>'08_Moteur'!B13</f>
         <v/>
       </c>
       <c r="C16" s="48">
-        <f>'08_Moteur'!C15</f>
+        <f>'08_Moteur'!C13</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>'08_Moteur'!D15</f>
+        <f>'08_Moteur'!D13</f>
         <v/>
       </c>
       <c r="E16" s="49">
-        <f>'08_Moteur'!AD15</f>
-        <v/>
-      </c>
-      <c r="F16" s="49">
-        <f>'08_Moteur'!AI15</f>
-        <v/>
-      </c>
-      <c r="G16" s="49">
-        <f>'08_Moteur'!M15</f>
-        <v/>
-      </c>
-      <c r="H16" s="71">
-        <f>'08_Moteur'!AN15</f>
-        <v/>
-      </c>
-      <c r="I16" s="72">
-        <f>IF('08_Moteur'!AM15&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN15&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN15&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD13</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>'08_Moteur'!AH13</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>F16-'08_Moteur'!AM13</f>
+        <v/>
+      </c>
+      <c r="H16" s="64">
+        <f>'08_Moteur'!AM13</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>E16*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>IF('08_Moteur'!AM15&lt;0,-'08_Moteur'!AM15,IF('08_Moteur'!AN15&gt;=0.95,'08_Moteur'!O15*'08_Moteur'!AO15-'08_Moteur'!U15,0))</f>
-        <v/>
-      </c>
-      <c r="K16" s="29">
-        <f>IF('08_Moteur'!AM15&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN15&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN15&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M16" s="51">
-        <f>IF(L16="Ne pas lancer",0,IF(L16="Statu quo",MAX('08_Moteur'!AI15,'08_Moteur'!M15),IF(L16="Ouvrir +1",'08_Moteur'!AI15+1,'08_Moteur'!AI15)))</f>
-        <v/>
-      </c>
-      <c r="N16" s="51">
-        <f>IF(L16="Ne pas lancer",0,'08_Moteur'!AD15)</f>
-        <v/>
+        <f>H16-I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="70">
+        <f>'08_Moteur'!AN13</f>
+        <v/>
+      </c>
+      <c r="L16" s="71">
+        <f>IF(H16&lt;0,"🔴 Ne pas ouvrir",IF(K16&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K16&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M16" s="72">
+        <f>IF(H16&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K16&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K16&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O16" s="17">
-        <f>N16*'08_Moteur'!AE15*'08_Moteur'!AF15+IF(L16="Ne pas lancer",0,'08_Moteur'!AB15)*'02_Leviers'!$D$16-M16*'08_Moteur'!U15-N16*'08_Moteur'!R15*(1+'02_Leviers'!$G$11)-IF(L16="Ne pas lancer",0,'08_Moteur'!AL15)</f>
+        <f>IF(N16="Ne pas ouvrir",0,IF(N16="Ouvrir +1 classe",H16-'08_Moteur'!U13,IF(N16="Économiser 1 classe",H16+('08_Moteur'!AI13-MAX(1,'08_Moteur'!AI13-1))*'08_Moteur'!U13,H16)))</f>
         <v/>
       </c>
       <c r="P16" s="55">
-        <f>O16-'08_Moteur'!AM15</f>
+        <f>O16-H16</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="48">
-        <f>'08_Moteur'!A16</f>
+        <f>'08_Moteur'!A14</f>
         <v/>
       </c>
       <c r="B17" s="10">
-        <f>'08_Moteur'!B16</f>
+        <f>'08_Moteur'!B14</f>
         <v/>
       </c>
       <c r="C17" s="48">
-        <f>'08_Moteur'!C16</f>
+        <f>'08_Moteur'!C14</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>'08_Moteur'!D16</f>
+        <f>'08_Moteur'!D14</f>
         <v/>
       </c>
       <c r="E17" s="49">
-        <f>'08_Moteur'!AD16</f>
-        <v/>
-      </c>
-      <c r="F17" s="49">
-        <f>'08_Moteur'!AI16</f>
-        <v/>
-      </c>
-      <c r="G17" s="49">
-        <f>'08_Moteur'!M16</f>
-        <v/>
-      </c>
-      <c r="H17" s="71">
-        <f>'08_Moteur'!AN16</f>
-        <v/>
-      </c>
-      <c r="I17" s="72">
-        <f>IF('08_Moteur'!AM16&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN16&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN16&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD14</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>'08_Moteur'!AH14</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>F17-'08_Moteur'!AM14</f>
+        <v/>
+      </c>
+      <c r="H17" s="64">
+        <f>'08_Moteur'!AM14</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>E17*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IF('08_Moteur'!AM16&lt;0,-'08_Moteur'!AM16,IF('08_Moteur'!AN16&gt;=0.95,'08_Moteur'!O16*'08_Moteur'!AO16-'08_Moteur'!U16,0))</f>
-        <v/>
-      </c>
-      <c r="K17" s="29">
-        <f>IF('08_Moteur'!AM16&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN16&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN16&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M17" s="51">
-        <f>IF(L17="Ne pas lancer",0,IF(L17="Statu quo",MAX('08_Moteur'!AI16,'08_Moteur'!M16),IF(L17="Ouvrir +1",'08_Moteur'!AI16+1,'08_Moteur'!AI16)))</f>
-        <v/>
-      </c>
-      <c r="N17" s="51">
-        <f>IF(L17="Ne pas lancer",0,'08_Moteur'!AD16)</f>
-        <v/>
+        <f>H17-I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="70">
+        <f>'08_Moteur'!AN14</f>
+        <v/>
+      </c>
+      <c r="L17" s="71">
+        <f>IF(H17&lt;0,"🔴 Ne pas ouvrir",IF(K17&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K17&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M17" s="72">
+        <f>IF(H17&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K17&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K17&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O17" s="17">
-        <f>N17*'08_Moteur'!AE16*'08_Moteur'!AF16+IF(L17="Ne pas lancer",0,'08_Moteur'!AB16)*'02_Leviers'!$D$16-M17*'08_Moteur'!U16-N17*'08_Moteur'!R16*(1+'02_Leviers'!$G$11)-IF(L17="Ne pas lancer",0,'08_Moteur'!AL16)</f>
+        <f>IF(N17="Ne pas ouvrir",0,IF(N17="Ouvrir +1 classe",H17-'08_Moteur'!U14,IF(N17="Économiser 1 classe",H17+('08_Moteur'!AI14-MAX(1,'08_Moteur'!AI14-1))*'08_Moteur'!U14,H17)))</f>
         <v/>
       </c>
       <c r="P17" s="55">
-        <f>O17-'08_Moteur'!AM16</f>
+        <f>O17-H17</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="48">
-        <f>'08_Moteur'!A17</f>
+        <f>'08_Moteur'!A15</f>
         <v/>
       </c>
       <c r="B18" s="10">
-        <f>'08_Moteur'!B17</f>
+        <f>'08_Moteur'!B15</f>
         <v/>
       </c>
       <c r="C18" s="48">
-        <f>'08_Moteur'!C17</f>
+        <f>'08_Moteur'!C15</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>'08_Moteur'!D17</f>
+        <f>'08_Moteur'!D15</f>
         <v/>
       </c>
       <c r="E18" s="49">
-        <f>'08_Moteur'!AD17</f>
-        <v/>
-      </c>
-      <c r="F18" s="49">
-        <f>'08_Moteur'!AI17</f>
-        <v/>
-      </c>
-      <c r="G18" s="49">
-        <f>'08_Moteur'!M17</f>
-        <v/>
-      </c>
-      <c r="H18" s="71">
-        <f>'08_Moteur'!AN17</f>
-        <v/>
-      </c>
-      <c r="I18" s="72">
-        <f>IF('08_Moteur'!AM17&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN17&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN17&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD15</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>'08_Moteur'!AH15</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>F18-'08_Moteur'!AM15</f>
+        <v/>
+      </c>
+      <c r="H18" s="64">
+        <f>'08_Moteur'!AM15</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>E18*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IF('08_Moteur'!AM17&lt;0,-'08_Moteur'!AM17,IF('08_Moteur'!AN17&gt;=0.95,'08_Moteur'!O17*'08_Moteur'!AO17-'08_Moteur'!U17,0))</f>
-        <v/>
-      </c>
-      <c r="K18" s="29">
-        <f>IF('08_Moteur'!AM17&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN17&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN17&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M18" s="51">
-        <f>IF(L18="Ne pas lancer",0,IF(L18="Statu quo",MAX('08_Moteur'!AI17,'08_Moteur'!M17),IF(L18="Ouvrir +1",'08_Moteur'!AI17+1,'08_Moteur'!AI17)))</f>
-        <v/>
-      </c>
-      <c r="N18" s="51">
-        <f>IF(L18="Ne pas lancer",0,'08_Moteur'!AD17)</f>
-        <v/>
+        <f>H18-I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="70">
+        <f>'08_Moteur'!AN15</f>
+        <v/>
+      </c>
+      <c r="L18" s="71">
+        <f>IF(H18&lt;0,"🔴 Ne pas ouvrir",IF(K18&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K18&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M18" s="72">
+        <f>IF(H18&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K18&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K18&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O18" s="17">
-        <f>N18*'08_Moteur'!AE17*'08_Moteur'!AF17+IF(L18="Ne pas lancer",0,'08_Moteur'!AB17)*'02_Leviers'!$D$16-M18*'08_Moteur'!U17-N18*'08_Moteur'!R17*(1+'02_Leviers'!$G$11)-IF(L18="Ne pas lancer",0,'08_Moteur'!AL17)</f>
+        <f>IF(N18="Ne pas ouvrir",0,IF(N18="Ouvrir +1 classe",H18-'08_Moteur'!U15,IF(N18="Économiser 1 classe",H18+('08_Moteur'!AI15-MAX(1,'08_Moteur'!AI15-1))*'08_Moteur'!U15,H18)))</f>
         <v/>
       </c>
       <c r="P18" s="55">
-        <f>O18-'08_Moteur'!AM17</f>
+        <f>O18-H18</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="48">
-        <f>'08_Moteur'!A18</f>
+        <f>'08_Moteur'!A16</f>
         <v/>
       </c>
       <c r="B19" s="10">
-        <f>'08_Moteur'!B18</f>
+        <f>'08_Moteur'!B16</f>
         <v/>
       </c>
       <c r="C19" s="48">
-        <f>'08_Moteur'!C18</f>
+        <f>'08_Moteur'!C16</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>'08_Moteur'!D18</f>
+        <f>'08_Moteur'!D16</f>
         <v/>
       </c>
       <c r="E19" s="49">
-        <f>'08_Moteur'!AD18</f>
-        <v/>
-      </c>
-      <c r="F19" s="49">
-        <f>'08_Moteur'!AI18</f>
-        <v/>
-      </c>
-      <c r="G19" s="49">
-        <f>'08_Moteur'!M18</f>
-        <v/>
-      </c>
-      <c r="H19" s="71">
-        <f>'08_Moteur'!AN18</f>
-        <v/>
-      </c>
-      <c r="I19" s="72">
-        <f>IF('08_Moteur'!AM18&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN18&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN18&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD16</f>
+        <v/>
+      </c>
+      <c r="F19" s="16">
+        <f>'08_Moteur'!AH16</f>
+        <v/>
+      </c>
+      <c r="G19" s="17">
+        <f>F19-'08_Moteur'!AM16</f>
+        <v/>
+      </c>
+      <c r="H19" s="64">
+        <f>'08_Moteur'!AM16</f>
+        <v/>
+      </c>
+      <c r="I19" s="17">
+        <f>E19*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IF('08_Moteur'!AM18&lt;0,-'08_Moteur'!AM18,IF('08_Moteur'!AN18&gt;=0.95,'08_Moteur'!O18*'08_Moteur'!AO18-'08_Moteur'!U18,0))</f>
-        <v/>
-      </c>
-      <c r="K19" s="29">
-        <f>IF('08_Moteur'!AM18&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN18&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN18&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M19" s="51">
-        <f>IF(L19="Ne pas lancer",0,IF(L19="Statu quo",MAX('08_Moteur'!AI18,'08_Moteur'!M18),IF(L19="Ouvrir +1",'08_Moteur'!AI18+1,'08_Moteur'!AI18)))</f>
-        <v/>
-      </c>
-      <c r="N19" s="51">
-        <f>IF(L19="Ne pas lancer",0,'08_Moteur'!AD18)</f>
-        <v/>
+        <f>H19-I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="70">
+        <f>'08_Moteur'!AN16</f>
+        <v/>
+      </c>
+      <c r="L19" s="71">
+        <f>IF(H19&lt;0,"🔴 Ne pas ouvrir",IF(K19&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K19&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M19" s="72">
+        <f>IF(H19&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K19&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K19&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O19" s="17">
-        <f>N19*'08_Moteur'!AE18*'08_Moteur'!AF18+IF(L19="Ne pas lancer",0,'08_Moteur'!AB18)*'02_Leviers'!$D$16-M19*'08_Moteur'!U18-N19*'08_Moteur'!R18*(1+'02_Leviers'!$G$11)-IF(L19="Ne pas lancer",0,'08_Moteur'!AL18)</f>
+        <f>IF(N19="Ne pas ouvrir",0,IF(N19="Ouvrir +1 classe",H19-'08_Moteur'!U16,IF(N19="Économiser 1 classe",H19+('08_Moteur'!AI16-MAX(1,'08_Moteur'!AI16-1))*'08_Moteur'!U16,H19)))</f>
         <v/>
       </c>
       <c r="P19" s="55">
-        <f>O19-'08_Moteur'!AM18</f>
+        <f>O19-H19</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="48">
-        <f>'08_Moteur'!A19</f>
+        <f>'08_Moteur'!A17</f>
         <v/>
       </c>
       <c r="B20" s="10">
-        <f>'08_Moteur'!B19</f>
+        <f>'08_Moteur'!B17</f>
         <v/>
       </c>
       <c r="C20" s="48">
-        <f>'08_Moteur'!C19</f>
+        <f>'08_Moteur'!C17</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>'08_Moteur'!D19</f>
+        <f>'08_Moteur'!D17</f>
         <v/>
       </c>
       <c r="E20" s="49">
-        <f>'08_Moteur'!AD19</f>
-        <v/>
-      </c>
-      <c r="F20" s="49">
-        <f>'08_Moteur'!AI19</f>
-        <v/>
-      </c>
-      <c r="G20" s="49">
-        <f>'08_Moteur'!M19</f>
-        <v/>
-      </c>
-      <c r="H20" s="71">
-        <f>'08_Moteur'!AN19</f>
-        <v/>
-      </c>
-      <c r="I20" s="72">
-        <f>IF('08_Moteur'!AM19&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN19&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN19&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD17</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
+        <f>'08_Moteur'!AH17</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>F20-'08_Moteur'!AM17</f>
+        <v/>
+      </c>
+      <c r="H20" s="64">
+        <f>'08_Moteur'!AM17</f>
+        <v/>
+      </c>
+      <c r="I20" s="17">
+        <f>E20*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IF('08_Moteur'!AM19&lt;0,-'08_Moteur'!AM19,IF('08_Moteur'!AN19&gt;=0.95,'08_Moteur'!O19*'08_Moteur'!AO19-'08_Moteur'!U19,0))</f>
-        <v/>
-      </c>
-      <c r="K20" s="29">
-        <f>IF('08_Moteur'!AM19&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN19&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN19&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M20" s="51">
-        <f>IF(L20="Ne pas lancer",0,IF(L20="Statu quo",MAX('08_Moteur'!AI19,'08_Moteur'!M19),IF(L20="Ouvrir +1",'08_Moteur'!AI19+1,'08_Moteur'!AI19)))</f>
-        <v/>
-      </c>
-      <c r="N20" s="51">
-        <f>IF(L20="Ne pas lancer",0,'08_Moteur'!AD19)</f>
-        <v/>
+        <f>H20-I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="70">
+        <f>'08_Moteur'!AN17</f>
+        <v/>
+      </c>
+      <c r="L20" s="71">
+        <f>IF(H20&lt;0,"🔴 Ne pas ouvrir",IF(K20&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K20&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M20" s="72">
+        <f>IF(H20&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K20&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K20&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O20" s="17">
-        <f>N20*'08_Moteur'!AE19*'08_Moteur'!AF19+IF(L20="Ne pas lancer",0,'08_Moteur'!AB19)*'02_Leviers'!$D$16-M20*'08_Moteur'!U19-N20*'08_Moteur'!R19*(1+'02_Leviers'!$G$11)-IF(L20="Ne pas lancer",0,'08_Moteur'!AL19)</f>
+        <f>IF(N20="Ne pas ouvrir",0,IF(N20="Ouvrir +1 classe",H20-'08_Moteur'!U17,IF(N20="Économiser 1 classe",H20+('08_Moteur'!AI17-MAX(1,'08_Moteur'!AI17-1))*'08_Moteur'!U17,H20)))</f>
         <v/>
       </c>
       <c r="P20" s="55">
-        <f>O20-'08_Moteur'!AM19</f>
+        <f>O20-H20</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="48">
-        <f>'08_Moteur'!A20</f>
+        <f>'08_Moteur'!A18</f>
         <v/>
       </c>
       <c r="B21" s="10">
-        <f>'08_Moteur'!B20</f>
+        <f>'08_Moteur'!B18</f>
         <v/>
       </c>
       <c r="C21" s="48">
-        <f>'08_Moteur'!C20</f>
+        <f>'08_Moteur'!C18</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>'08_Moteur'!D20</f>
+        <f>'08_Moteur'!D18</f>
         <v/>
       </c>
       <c r="E21" s="49">
-        <f>'08_Moteur'!AD20</f>
-        <v/>
-      </c>
-      <c r="F21" s="49">
-        <f>'08_Moteur'!AI20</f>
-        <v/>
-      </c>
-      <c r="G21" s="49">
-        <f>'08_Moteur'!M20</f>
-        <v/>
-      </c>
-      <c r="H21" s="71">
-        <f>'08_Moteur'!AN20</f>
-        <v/>
-      </c>
-      <c r="I21" s="72">
-        <f>IF('08_Moteur'!AM20&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN20&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN20&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD18</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>'08_Moteur'!AH18</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f>F21-'08_Moteur'!AM18</f>
+        <v/>
+      </c>
+      <c r="H21" s="64">
+        <f>'08_Moteur'!AM18</f>
+        <v/>
+      </c>
+      <c r="I21" s="17">
+        <f>E21*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IF('08_Moteur'!AM20&lt;0,-'08_Moteur'!AM20,IF('08_Moteur'!AN20&gt;=0.95,'08_Moteur'!O20*'08_Moteur'!AO20-'08_Moteur'!U20,0))</f>
-        <v/>
-      </c>
-      <c r="K21" s="29">
-        <f>IF('08_Moteur'!AM20&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN20&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN20&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M21" s="51">
-        <f>IF(L21="Ne pas lancer",0,IF(L21="Statu quo",MAX('08_Moteur'!AI20,'08_Moteur'!M20),IF(L21="Ouvrir +1",'08_Moteur'!AI20+1,'08_Moteur'!AI20)))</f>
-        <v/>
-      </c>
-      <c r="N21" s="51">
-        <f>IF(L21="Ne pas lancer",0,'08_Moteur'!AD20)</f>
-        <v/>
+        <f>H21-I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="70">
+        <f>'08_Moteur'!AN18</f>
+        <v/>
+      </c>
+      <c r="L21" s="71">
+        <f>IF(H21&lt;0,"🔴 Ne pas ouvrir",IF(K21&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K21&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M21" s="72">
+        <f>IF(H21&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K21&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K21&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O21" s="17">
-        <f>N21*'08_Moteur'!AE20*'08_Moteur'!AF20+IF(L21="Ne pas lancer",0,'08_Moteur'!AB20)*'02_Leviers'!$D$16-M21*'08_Moteur'!U20-N21*'08_Moteur'!R20*(1+'02_Leviers'!$G$11)-IF(L21="Ne pas lancer",0,'08_Moteur'!AL20)</f>
+        <f>IF(N21="Ne pas ouvrir",0,IF(N21="Ouvrir +1 classe",H21-'08_Moteur'!U18,IF(N21="Économiser 1 classe",H21+('08_Moteur'!AI18-MAX(1,'08_Moteur'!AI18-1))*'08_Moteur'!U18,H21)))</f>
         <v/>
       </c>
       <c r="P21" s="55">
-        <f>O21-'08_Moteur'!AM20</f>
+        <f>O21-H21</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="48">
-        <f>'08_Moteur'!A21</f>
+        <f>'08_Moteur'!A19</f>
         <v/>
       </c>
       <c r="B22" s="10">
-        <f>'08_Moteur'!B21</f>
+        <f>'08_Moteur'!B19</f>
         <v/>
       </c>
       <c r="C22" s="48">
-        <f>'08_Moteur'!C21</f>
+        <f>'08_Moteur'!C19</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>'08_Moteur'!D21</f>
+        <f>'08_Moteur'!D19</f>
         <v/>
       </c>
       <c r="E22" s="49">
-        <f>'08_Moteur'!AD21</f>
-        <v/>
-      </c>
-      <c r="F22" s="49">
-        <f>'08_Moteur'!AI21</f>
-        <v/>
-      </c>
-      <c r="G22" s="49">
-        <f>'08_Moteur'!M21</f>
-        <v/>
-      </c>
-      <c r="H22" s="71">
-        <f>'08_Moteur'!AN21</f>
-        <v/>
-      </c>
-      <c r="I22" s="72">
-        <f>IF('08_Moteur'!AM21&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN21&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN21&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD19</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>'08_Moteur'!AH19</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f>F22-'08_Moteur'!AM19</f>
+        <v/>
+      </c>
+      <c r="H22" s="64">
+        <f>'08_Moteur'!AM19</f>
+        <v/>
+      </c>
+      <c r="I22" s="17">
+        <f>E22*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IF('08_Moteur'!AM21&lt;0,-'08_Moteur'!AM21,IF('08_Moteur'!AN21&gt;=0.95,'08_Moteur'!O21*'08_Moteur'!AO21-'08_Moteur'!U21,0))</f>
-        <v/>
-      </c>
-      <c r="K22" s="29">
-        <f>IF('08_Moteur'!AM21&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN21&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN21&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M22" s="51">
-        <f>IF(L22="Ne pas lancer",0,IF(L22="Statu quo",MAX('08_Moteur'!AI21,'08_Moteur'!M21),IF(L22="Ouvrir +1",'08_Moteur'!AI21+1,'08_Moteur'!AI21)))</f>
-        <v/>
-      </c>
-      <c r="N22" s="51">
-        <f>IF(L22="Ne pas lancer",0,'08_Moteur'!AD21)</f>
-        <v/>
+        <f>H22-I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="70">
+        <f>'08_Moteur'!AN19</f>
+        <v/>
+      </c>
+      <c r="L22" s="71">
+        <f>IF(H22&lt;0,"🔴 Ne pas ouvrir",IF(K22&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K22&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M22" s="72">
+        <f>IF(H22&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K22&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K22&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O22" s="17">
-        <f>N22*'08_Moteur'!AE21*'08_Moteur'!AF21+IF(L22="Ne pas lancer",0,'08_Moteur'!AB21)*'02_Leviers'!$D$16-M22*'08_Moteur'!U21-N22*'08_Moteur'!R21*(1+'02_Leviers'!$G$11)-IF(L22="Ne pas lancer",0,'08_Moteur'!AL21)</f>
+        <f>IF(N22="Ne pas ouvrir",0,IF(N22="Ouvrir +1 classe",H22-'08_Moteur'!U19,IF(N22="Économiser 1 classe",H22+('08_Moteur'!AI19-MAX(1,'08_Moteur'!AI19-1))*'08_Moteur'!U19,H22)))</f>
         <v/>
       </c>
       <c r="P22" s="55">
-        <f>O22-'08_Moteur'!AM21</f>
+        <f>O22-H22</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="48">
-        <f>'08_Moteur'!A22</f>
+        <f>'08_Moteur'!A20</f>
         <v/>
       </c>
       <c r="B23" s="10">
-        <f>'08_Moteur'!B22</f>
+        <f>'08_Moteur'!B20</f>
         <v/>
       </c>
       <c r="C23" s="48">
-        <f>'08_Moteur'!C22</f>
+        <f>'08_Moteur'!C20</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>'08_Moteur'!D22</f>
+        <f>'08_Moteur'!D20</f>
         <v/>
       </c>
       <c r="E23" s="49">
-        <f>'08_Moteur'!AD22</f>
-        <v/>
-      </c>
-      <c r="F23" s="49">
-        <f>'08_Moteur'!AI22</f>
-        <v/>
-      </c>
-      <c r="G23" s="49">
-        <f>'08_Moteur'!M22</f>
-        <v/>
-      </c>
-      <c r="H23" s="71">
-        <f>'08_Moteur'!AN22</f>
-        <v/>
-      </c>
-      <c r="I23" s="72">
-        <f>IF('08_Moteur'!AM22&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN22&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN22&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD20</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>'08_Moteur'!AH20</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>F23-'08_Moteur'!AM20</f>
+        <v/>
+      </c>
+      <c r="H23" s="64">
+        <f>'08_Moteur'!AM20</f>
+        <v/>
+      </c>
+      <c r="I23" s="17">
+        <f>E23*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IF('08_Moteur'!AM22&lt;0,-'08_Moteur'!AM22,IF('08_Moteur'!AN22&gt;=0.95,'08_Moteur'!O22*'08_Moteur'!AO22-'08_Moteur'!U22,0))</f>
-        <v/>
-      </c>
-      <c r="K23" s="29">
-        <f>IF('08_Moteur'!AM22&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN22&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN22&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M23" s="51">
-        <f>IF(L23="Ne pas lancer",0,IF(L23="Statu quo",MAX('08_Moteur'!AI22,'08_Moteur'!M22),IF(L23="Ouvrir +1",'08_Moteur'!AI22+1,'08_Moteur'!AI22)))</f>
-        <v/>
-      </c>
-      <c r="N23" s="51">
-        <f>IF(L23="Ne pas lancer",0,'08_Moteur'!AD22)</f>
-        <v/>
+        <f>H23-I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="70">
+        <f>'08_Moteur'!AN20</f>
+        <v/>
+      </c>
+      <c r="L23" s="71">
+        <f>IF(H23&lt;0,"🔴 Ne pas ouvrir",IF(K23&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K23&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M23" s="72">
+        <f>IF(H23&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K23&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K23&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O23" s="17">
-        <f>N23*'08_Moteur'!AE22*'08_Moteur'!AF22+IF(L23="Ne pas lancer",0,'08_Moteur'!AB22)*'02_Leviers'!$D$16-M23*'08_Moteur'!U22-N23*'08_Moteur'!R22*(1+'02_Leviers'!$G$11)-IF(L23="Ne pas lancer",0,'08_Moteur'!AL22)</f>
+        <f>IF(N23="Ne pas ouvrir",0,IF(N23="Ouvrir +1 classe",H23-'08_Moteur'!U20,IF(N23="Économiser 1 classe",H23+('08_Moteur'!AI20-MAX(1,'08_Moteur'!AI20-1))*'08_Moteur'!U20,H23)))</f>
         <v/>
       </c>
       <c r="P23" s="55">
-        <f>O23-'08_Moteur'!AM22</f>
+        <f>O23-H23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="48">
-        <f>'08_Moteur'!A23</f>
+        <f>'08_Moteur'!A21</f>
         <v/>
       </c>
       <c r="B24" s="10">
-        <f>'08_Moteur'!B23</f>
+        <f>'08_Moteur'!B21</f>
         <v/>
       </c>
       <c r="C24" s="48">
-        <f>'08_Moteur'!C23</f>
+        <f>'08_Moteur'!C21</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>'08_Moteur'!D23</f>
+        <f>'08_Moteur'!D21</f>
         <v/>
       </c>
       <c r="E24" s="49">
-        <f>'08_Moteur'!AD23</f>
-        <v/>
-      </c>
-      <c r="F24" s="49">
-        <f>'08_Moteur'!AI23</f>
-        <v/>
-      </c>
-      <c r="G24" s="49">
-        <f>'08_Moteur'!M23</f>
-        <v/>
-      </c>
-      <c r="H24" s="71">
-        <f>'08_Moteur'!AN23</f>
-        <v/>
-      </c>
-      <c r="I24" s="72">
-        <f>IF('08_Moteur'!AM23&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN23&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN23&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD21</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>'08_Moteur'!AH21</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f>F24-'08_Moteur'!AM21</f>
+        <v/>
+      </c>
+      <c r="H24" s="64">
+        <f>'08_Moteur'!AM21</f>
+        <v/>
+      </c>
+      <c r="I24" s="17">
+        <f>E24*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IF('08_Moteur'!AM23&lt;0,-'08_Moteur'!AM23,IF('08_Moteur'!AN23&gt;=0.95,'08_Moteur'!O23*'08_Moteur'!AO23-'08_Moteur'!U23,0))</f>
-        <v/>
-      </c>
-      <c r="K24" s="29">
-        <f>IF('08_Moteur'!AM23&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN23&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN23&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M24" s="51">
-        <f>IF(L24="Ne pas lancer",0,IF(L24="Statu quo",MAX('08_Moteur'!AI23,'08_Moteur'!M23),IF(L24="Ouvrir +1",'08_Moteur'!AI23+1,'08_Moteur'!AI23)))</f>
-        <v/>
-      </c>
-      <c r="N24" s="51">
-        <f>IF(L24="Ne pas lancer",0,'08_Moteur'!AD23)</f>
-        <v/>
+        <f>H24-I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="70">
+        <f>'08_Moteur'!AN21</f>
+        <v/>
+      </c>
+      <c r="L24" s="71">
+        <f>IF(H24&lt;0,"🔴 Ne pas ouvrir",IF(K24&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K24&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M24" s="72">
+        <f>IF(H24&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K24&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K24&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O24" s="17">
-        <f>N24*'08_Moteur'!AE23*'08_Moteur'!AF23+IF(L24="Ne pas lancer",0,'08_Moteur'!AB23)*'02_Leviers'!$D$16-M24*'08_Moteur'!U23-N24*'08_Moteur'!R23*(1+'02_Leviers'!$G$11)-IF(L24="Ne pas lancer",0,'08_Moteur'!AL23)</f>
+        <f>IF(N24="Ne pas ouvrir",0,IF(N24="Ouvrir +1 classe",H24-'08_Moteur'!U21,IF(N24="Économiser 1 classe",H24+('08_Moteur'!AI21-MAX(1,'08_Moteur'!AI21-1))*'08_Moteur'!U21,H24)))</f>
         <v/>
       </c>
       <c r="P24" s="55">
-        <f>O24-'08_Moteur'!AM23</f>
+        <f>O24-H24</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="48">
-        <f>'08_Moteur'!A24</f>
+        <f>'08_Moteur'!A22</f>
         <v/>
       </c>
       <c r="B25" s="10">
-        <f>'08_Moteur'!B24</f>
+        <f>'08_Moteur'!B22</f>
         <v/>
       </c>
       <c r="C25" s="48">
-        <f>'08_Moteur'!C24</f>
+        <f>'08_Moteur'!C22</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>'08_Moteur'!D24</f>
+        <f>'08_Moteur'!D22</f>
         <v/>
       </c>
       <c r="E25" s="49">
-        <f>'08_Moteur'!AD24</f>
-        <v/>
-      </c>
-      <c r="F25" s="49">
-        <f>'08_Moteur'!AI24</f>
-        <v/>
-      </c>
-      <c r="G25" s="49">
-        <f>'08_Moteur'!M24</f>
-        <v/>
-      </c>
-      <c r="H25" s="71">
-        <f>'08_Moteur'!AN24</f>
-        <v/>
-      </c>
-      <c r="I25" s="72">
-        <f>IF('08_Moteur'!AM24&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN24&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN24&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD22</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>'08_Moteur'!AH22</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>F25-'08_Moteur'!AM22</f>
+        <v/>
+      </c>
+      <c r="H25" s="64">
+        <f>'08_Moteur'!AM22</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>E25*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IF('08_Moteur'!AM24&lt;0,-'08_Moteur'!AM24,IF('08_Moteur'!AN24&gt;=0.95,'08_Moteur'!O24*'08_Moteur'!AO24-'08_Moteur'!U24,0))</f>
-        <v/>
-      </c>
-      <c r="K25" s="29">
-        <f>IF('08_Moteur'!AM24&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN24&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN24&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M25" s="51">
-        <f>IF(L25="Ne pas lancer",0,IF(L25="Statu quo",MAX('08_Moteur'!AI24,'08_Moteur'!M24),IF(L25="Ouvrir +1",'08_Moteur'!AI24+1,'08_Moteur'!AI24)))</f>
-        <v/>
-      </c>
-      <c r="N25" s="51">
-        <f>IF(L25="Ne pas lancer",0,'08_Moteur'!AD24)</f>
-        <v/>
+        <f>H25-I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="70">
+        <f>'08_Moteur'!AN22</f>
+        <v/>
+      </c>
+      <c r="L25" s="71">
+        <f>IF(H25&lt;0,"🔴 Ne pas ouvrir",IF(K25&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K25&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M25" s="72">
+        <f>IF(H25&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K25&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K25&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O25" s="17">
-        <f>N25*'08_Moteur'!AE24*'08_Moteur'!AF24+IF(L25="Ne pas lancer",0,'08_Moteur'!AB24)*'02_Leviers'!$D$16-M25*'08_Moteur'!U24-N25*'08_Moteur'!R24*(1+'02_Leviers'!$G$11)-IF(L25="Ne pas lancer",0,'08_Moteur'!AL24)</f>
+        <f>IF(N25="Ne pas ouvrir",0,IF(N25="Ouvrir +1 classe",H25-'08_Moteur'!U22,IF(N25="Économiser 1 classe",H25+('08_Moteur'!AI22-MAX(1,'08_Moteur'!AI22-1))*'08_Moteur'!U22,H25)))</f>
         <v/>
       </c>
       <c r="P25" s="55">
-        <f>O25-'08_Moteur'!AM24</f>
+        <f>O25-H25</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="48">
-        <f>'08_Moteur'!A25</f>
+        <f>'08_Moteur'!A23</f>
         <v/>
       </c>
       <c r="B26" s="10">
-        <f>'08_Moteur'!B25</f>
+        <f>'08_Moteur'!B23</f>
         <v/>
       </c>
       <c r="C26" s="48">
-        <f>'08_Moteur'!C25</f>
+        <f>'08_Moteur'!C23</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>'08_Moteur'!D25</f>
+        <f>'08_Moteur'!D23</f>
         <v/>
       </c>
       <c r="E26" s="49">
-        <f>'08_Moteur'!AD25</f>
-        <v/>
-      </c>
-      <c r="F26" s="49">
-        <f>'08_Moteur'!AI25</f>
-        <v/>
-      </c>
-      <c r="G26" s="49">
-        <f>'08_Moteur'!M25</f>
-        <v/>
-      </c>
-      <c r="H26" s="71">
-        <f>'08_Moteur'!AN25</f>
-        <v/>
-      </c>
-      <c r="I26" s="72">
-        <f>IF('08_Moteur'!AM25&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN25&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN25&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD23</f>
+        <v/>
+      </c>
+      <c r="F26" s="16">
+        <f>'08_Moteur'!AH23</f>
+        <v/>
+      </c>
+      <c r="G26" s="17">
+        <f>F26-'08_Moteur'!AM23</f>
+        <v/>
+      </c>
+      <c r="H26" s="64">
+        <f>'08_Moteur'!AM23</f>
+        <v/>
+      </c>
+      <c r="I26" s="17">
+        <f>E26*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IF('08_Moteur'!AM25&lt;0,-'08_Moteur'!AM25,IF('08_Moteur'!AN25&gt;=0.95,'08_Moteur'!O25*'08_Moteur'!AO25-'08_Moteur'!U25,0))</f>
-        <v/>
-      </c>
-      <c r="K26" s="29">
-        <f>IF('08_Moteur'!AM25&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN25&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN25&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M26" s="51">
-        <f>IF(L26="Ne pas lancer",0,IF(L26="Statu quo",MAX('08_Moteur'!AI25,'08_Moteur'!M25),IF(L26="Ouvrir +1",'08_Moteur'!AI25+1,'08_Moteur'!AI25)))</f>
-        <v/>
-      </c>
-      <c r="N26" s="51">
-        <f>IF(L26="Ne pas lancer",0,'08_Moteur'!AD25)</f>
-        <v/>
+        <f>H26-I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="70">
+        <f>'08_Moteur'!AN23</f>
+        <v/>
+      </c>
+      <c r="L26" s="71">
+        <f>IF(H26&lt;0,"🔴 Ne pas ouvrir",IF(K26&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K26&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M26" s="72">
+        <f>IF(H26&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K26&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K26&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O26" s="17">
-        <f>N26*'08_Moteur'!AE25*'08_Moteur'!AF25+IF(L26="Ne pas lancer",0,'08_Moteur'!AB25)*'02_Leviers'!$D$16-M26*'08_Moteur'!U25-N26*'08_Moteur'!R25*(1+'02_Leviers'!$G$11)-IF(L26="Ne pas lancer",0,'08_Moteur'!AL25)</f>
+        <f>IF(N26="Ne pas ouvrir",0,IF(N26="Ouvrir +1 classe",H26-'08_Moteur'!U23,IF(N26="Économiser 1 classe",H26+('08_Moteur'!AI23-MAX(1,'08_Moteur'!AI23-1))*'08_Moteur'!U23,H26)))</f>
         <v/>
       </c>
       <c r="P26" s="55">
-        <f>O26-'08_Moteur'!AM25</f>
+        <f>O26-H26</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="48">
-        <f>'08_Moteur'!A26</f>
+        <f>'08_Moteur'!A24</f>
         <v/>
       </c>
       <c r="B27" s="10">
-        <f>'08_Moteur'!B26</f>
+        <f>'08_Moteur'!B24</f>
         <v/>
       </c>
       <c r="C27" s="48">
-        <f>'08_Moteur'!C26</f>
+        <f>'08_Moteur'!C24</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>'08_Moteur'!D26</f>
+        <f>'08_Moteur'!D24</f>
         <v/>
       </c>
       <c r="E27" s="49">
-        <f>'08_Moteur'!AD26</f>
-        <v/>
-      </c>
-      <c r="F27" s="49">
-        <f>'08_Moteur'!AI26</f>
-        <v/>
-      </c>
-      <c r="G27" s="49">
-        <f>'08_Moteur'!M26</f>
-        <v/>
-      </c>
-      <c r="H27" s="71">
-        <f>'08_Moteur'!AN26</f>
-        <v/>
-      </c>
-      <c r="I27" s="72">
-        <f>IF('08_Moteur'!AM26&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN26&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN26&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD24</f>
+        <v/>
+      </c>
+      <c r="F27" s="16">
+        <f>'08_Moteur'!AH24</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>F27-'08_Moteur'!AM24</f>
+        <v/>
+      </c>
+      <c r="H27" s="64">
+        <f>'08_Moteur'!AM24</f>
+        <v/>
+      </c>
+      <c r="I27" s="17">
+        <f>E27*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IF('08_Moteur'!AM26&lt;0,-'08_Moteur'!AM26,IF('08_Moteur'!AN26&gt;=0.95,'08_Moteur'!O26*'08_Moteur'!AO26-'08_Moteur'!U26,0))</f>
-        <v/>
-      </c>
-      <c r="K27" s="29">
-        <f>IF('08_Moteur'!AM26&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN26&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN26&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M27" s="51">
-        <f>IF(L27="Ne pas lancer",0,IF(L27="Statu quo",MAX('08_Moteur'!AI26,'08_Moteur'!M26),IF(L27="Ouvrir +1",'08_Moteur'!AI26+1,'08_Moteur'!AI26)))</f>
-        <v/>
-      </c>
-      <c r="N27" s="51">
-        <f>IF(L27="Ne pas lancer",0,'08_Moteur'!AD26)</f>
-        <v/>
+        <f>H27-I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="70">
+        <f>'08_Moteur'!AN24</f>
+        <v/>
+      </c>
+      <c r="L27" s="71">
+        <f>IF(H27&lt;0,"🔴 Ne pas ouvrir",IF(K27&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K27&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M27" s="72">
+        <f>IF(H27&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K27&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K27&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O27" s="17">
-        <f>N27*'08_Moteur'!AE26*'08_Moteur'!AF26+IF(L27="Ne pas lancer",0,'08_Moteur'!AB26)*'02_Leviers'!$D$16-M27*'08_Moteur'!U26-N27*'08_Moteur'!R26*(1+'02_Leviers'!$G$11)-IF(L27="Ne pas lancer",0,'08_Moteur'!AL26)</f>
+        <f>IF(N27="Ne pas ouvrir",0,IF(N27="Ouvrir +1 classe",H27-'08_Moteur'!U24,IF(N27="Économiser 1 classe",H27+('08_Moteur'!AI24-MAX(1,'08_Moteur'!AI24-1))*'08_Moteur'!U24,H27)))</f>
         <v/>
       </c>
       <c r="P27" s="55">
-        <f>O27-'08_Moteur'!AM26</f>
+        <f>O27-H27</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="48">
-        <f>'08_Moteur'!A27</f>
+        <f>'08_Moteur'!A25</f>
         <v/>
       </c>
       <c r="B28" s="10">
-        <f>'08_Moteur'!B27</f>
+        <f>'08_Moteur'!B25</f>
         <v/>
       </c>
       <c r="C28" s="48">
-        <f>'08_Moteur'!C27</f>
+        <f>'08_Moteur'!C25</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>'08_Moteur'!D27</f>
+        <f>'08_Moteur'!D25</f>
         <v/>
       </c>
       <c r="E28" s="49">
-        <f>'08_Moteur'!AD27</f>
-        <v/>
-      </c>
-      <c r="F28" s="49">
-        <f>'08_Moteur'!AI27</f>
-        <v/>
-      </c>
-      <c r="G28" s="49">
-        <f>'08_Moteur'!M27</f>
-        <v/>
-      </c>
-      <c r="H28" s="71">
-        <f>'08_Moteur'!AN27</f>
-        <v/>
-      </c>
-      <c r="I28" s="72">
-        <f>IF('08_Moteur'!AM27&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN27&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN27&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD25</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f>'08_Moteur'!AH25</f>
+        <v/>
+      </c>
+      <c r="G28" s="17">
+        <f>F28-'08_Moteur'!AM25</f>
+        <v/>
+      </c>
+      <c r="H28" s="64">
+        <f>'08_Moteur'!AM25</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>E28*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IF('08_Moteur'!AM27&lt;0,-'08_Moteur'!AM27,IF('08_Moteur'!AN27&gt;=0.95,'08_Moteur'!O27*'08_Moteur'!AO27-'08_Moteur'!U27,0))</f>
-        <v/>
-      </c>
-      <c r="K28" s="29">
-        <f>IF('08_Moteur'!AM27&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN27&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN27&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M28" s="51">
-        <f>IF(L28="Ne pas lancer",0,IF(L28="Statu quo",MAX('08_Moteur'!AI27,'08_Moteur'!M27),IF(L28="Ouvrir +1",'08_Moteur'!AI27+1,'08_Moteur'!AI27)))</f>
-        <v/>
-      </c>
-      <c r="N28" s="51">
-        <f>IF(L28="Ne pas lancer",0,'08_Moteur'!AD27)</f>
-        <v/>
+        <f>H28-I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="70">
+        <f>'08_Moteur'!AN25</f>
+        <v/>
+      </c>
+      <c r="L28" s="71">
+        <f>IF(H28&lt;0,"🔴 Ne pas ouvrir",IF(K28&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K28&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M28" s="72">
+        <f>IF(H28&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K28&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K28&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O28" s="17">
-        <f>N28*'08_Moteur'!AE27*'08_Moteur'!AF27+IF(L28="Ne pas lancer",0,'08_Moteur'!AB27)*'02_Leviers'!$D$16-M28*'08_Moteur'!U27-N28*'08_Moteur'!R27*(1+'02_Leviers'!$G$11)-IF(L28="Ne pas lancer",0,'08_Moteur'!AL27)</f>
+        <f>IF(N28="Ne pas ouvrir",0,IF(N28="Ouvrir +1 classe",H28-'08_Moteur'!U25,IF(N28="Économiser 1 classe",H28+('08_Moteur'!AI25-MAX(1,'08_Moteur'!AI25-1))*'08_Moteur'!U25,H28)))</f>
         <v/>
       </c>
       <c r="P28" s="55">
-        <f>O28-'08_Moteur'!AM27</f>
+        <f>O28-H28</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="48">
-        <f>'08_Moteur'!A28</f>
+        <f>'08_Moteur'!A26</f>
         <v/>
       </c>
       <c r="B29" s="10">
-        <f>'08_Moteur'!B28</f>
+        <f>'08_Moteur'!B26</f>
         <v/>
       </c>
       <c r="C29" s="48">
-        <f>'08_Moteur'!C28</f>
+        <f>'08_Moteur'!C26</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>'08_Moteur'!D28</f>
+        <f>'08_Moteur'!D26</f>
         <v/>
       </c>
       <c r="E29" s="49">
-        <f>'08_Moteur'!AD28</f>
-        <v/>
-      </c>
-      <c r="F29" s="49">
-        <f>'08_Moteur'!AI28</f>
-        <v/>
-      </c>
-      <c r="G29" s="49">
-        <f>'08_Moteur'!M28</f>
-        <v/>
-      </c>
-      <c r="H29" s="71">
-        <f>'08_Moteur'!AN28</f>
-        <v/>
-      </c>
-      <c r="I29" s="72">
-        <f>IF('08_Moteur'!AM28&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN28&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN28&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD26</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f>'08_Moteur'!AH26</f>
+        <v/>
+      </c>
+      <c r="G29" s="17">
+        <f>F29-'08_Moteur'!AM26</f>
+        <v/>
+      </c>
+      <c r="H29" s="64">
+        <f>'08_Moteur'!AM26</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>E29*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IF('08_Moteur'!AM28&lt;0,-'08_Moteur'!AM28,IF('08_Moteur'!AN28&gt;=0.95,'08_Moteur'!O28*'08_Moteur'!AO28-'08_Moteur'!U28,0))</f>
-        <v/>
-      </c>
-      <c r="K29" s="29">
-        <f>IF('08_Moteur'!AM28&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN28&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN28&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M29" s="51">
-        <f>IF(L29="Ne pas lancer",0,IF(L29="Statu quo",MAX('08_Moteur'!AI28,'08_Moteur'!M28),IF(L29="Ouvrir +1",'08_Moteur'!AI28+1,'08_Moteur'!AI28)))</f>
-        <v/>
-      </c>
-      <c r="N29" s="51">
-        <f>IF(L29="Ne pas lancer",0,'08_Moteur'!AD28)</f>
-        <v/>
+        <f>H29-I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="70">
+        <f>'08_Moteur'!AN26</f>
+        <v/>
+      </c>
+      <c r="L29" s="71">
+        <f>IF(H29&lt;0,"🔴 Ne pas ouvrir",IF(K29&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K29&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M29" s="72">
+        <f>IF(H29&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K29&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K29&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O29" s="17">
-        <f>N29*'08_Moteur'!AE28*'08_Moteur'!AF28+IF(L29="Ne pas lancer",0,'08_Moteur'!AB28)*'02_Leviers'!$D$16-M29*'08_Moteur'!U28-N29*'08_Moteur'!R28*(1+'02_Leviers'!$G$11)-IF(L29="Ne pas lancer",0,'08_Moteur'!AL28)</f>
+        <f>IF(N29="Ne pas ouvrir",0,IF(N29="Ouvrir +1 classe",H29-'08_Moteur'!U26,IF(N29="Économiser 1 classe",H29+('08_Moteur'!AI26-MAX(1,'08_Moteur'!AI26-1))*'08_Moteur'!U26,H29)))</f>
         <v/>
       </c>
       <c r="P29" s="55">
-        <f>O29-'08_Moteur'!AM28</f>
+        <f>O29-H29</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="48">
-        <f>'08_Moteur'!A29</f>
+        <f>'08_Moteur'!A27</f>
         <v/>
       </c>
       <c r="B30" s="10">
-        <f>'08_Moteur'!B29</f>
+        <f>'08_Moteur'!B27</f>
         <v/>
       </c>
       <c r="C30" s="48">
-        <f>'08_Moteur'!C29</f>
+        <f>'08_Moteur'!C27</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>'08_Moteur'!D29</f>
+        <f>'08_Moteur'!D27</f>
         <v/>
       </c>
       <c r="E30" s="49">
-        <f>'08_Moteur'!AD29</f>
-        <v/>
-      </c>
-      <c r="F30" s="49">
-        <f>'08_Moteur'!AI29</f>
-        <v/>
-      </c>
-      <c r="G30" s="49">
-        <f>'08_Moteur'!M29</f>
-        <v/>
-      </c>
-      <c r="H30" s="71">
-        <f>'08_Moteur'!AN29</f>
-        <v/>
-      </c>
-      <c r="I30" s="72">
-        <f>IF('08_Moteur'!AM29&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN29&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN29&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD27</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f>'08_Moteur'!AH27</f>
+        <v/>
+      </c>
+      <c r="G30" s="17">
+        <f>F30-'08_Moteur'!AM27</f>
+        <v/>
+      </c>
+      <c r="H30" s="64">
+        <f>'08_Moteur'!AM27</f>
+        <v/>
+      </c>
+      <c r="I30" s="17">
+        <f>E30*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IF('08_Moteur'!AM29&lt;0,-'08_Moteur'!AM29,IF('08_Moteur'!AN29&gt;=0.95,'08_Moteur'!O29*'08_Moteur'!AO29-'08_Moteur'!U29,0))</f>
-        <v/>
-      </c>
-      <c r="K30" s="29">
-        <f>IF('08_Moteur'!AM29&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN29&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN29&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L30" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M30" s="51">
-        <f>IF(L30="Ne pas lancer",0,IF(L30="Statu quo",MAX('08_Moteur'!AI29,'08_Moteur'!M29),IF(L30="Ouvrir +1",'08_Moteur'!AI29+1,'08_Moteur'!AI29)))</f>
-        <v/>
-      </c>
-      <c r="N30" s="51">
-        <f>IF(L30="Ne pas lancer",0,'08_Moteur'!AD29)</f>
-        <v/>
+        <f>H30-I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="70">
+        <f>'08_Moteur'!AN27</f>
+        <v/>
+      </c>
+      <c r="L30" s="71">
+        <f>IF(H30&lt;0,"🔴 Ne pas ouvrir",IF(K30&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K30&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M30" s="72">
+        <f>IF(H30&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K30&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K30&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O30" s="17">
-        <f>N30*'08_Moteur'!AE29*'08_Moteur'!AF29+IF(L30="Ne pas lancer",0,'08_Moteur'!AB29)*'02_Leviers'!$D$16-M30*'08_Moteur'!U29-N30*'08_Moteur'!R29*(1+'02_Leviers'!$G$11)-IF(L30="Ne pas lancer",0,'08_Moteur'!AL29)</f>
+        <f>IF(N30="Ne pas ouvrir",0,IF(N30="Ouvrir +1 classe",H30-'08_Moteur'!U27,IF(N30="Économiser 1 classe",H30+('08_Moteur'!AI27-MAX(1,'08_Moteur'!AI27-1))*'08_Moteur'!U27,H30)))</f>
         <v/>
       </c>
       <c r="P30" s="55">
-        <f>O30-'08_Moteur'!AM29</f>
+        <f>O30-H30</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="48">
-        <f>'08_Moteur'!A30</f>
+        <f>'08_Moteur'!A28</f>
         <v/>
       </c>
       <c r="B31" s="10">
-        <f>'08_Moteur'!B30</f>
+        <f>'08_Moteur'!B28</f>
         <v/>
       </c>
       <c r="C31" s="48">
-        <f>'08_Moteur'!C30</f>
+        <f>'08_Moteur'!C28</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>'08_Moteur'!D30</f>
+        <f>'08_Moteur'!D28</f>
         <v/>
       </c>
       <c r="E31" s="49">
-        <f>'08_Moteur'!AD30</f>
-        <v/>
-      </c>
-      <c r="F31" s="49">
-        <f>'08_Moteur'!AI30</f>
-        <v/>
-      </c>
-      <c r="G31" s="49">
-        <f>'08_Moteur'!M30</f>
-        <v/>
-      </c>
-      <c r="H31" s="71">
-        <f>'08_Moteur'!AN30</f>
-        <v/>
-      </c>
-      <c r="I31" s="72">
-        <f>IF('08_Moteur'!AM30&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN30&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN30&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD28</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>'08_Moteur'!AH28</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>F31-'08_Moteur'!AM28</f>
+        <v/>
+      </c>
+      <c r="H31" s="64">
+        <f>'08_Moteur'!AM28</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>E31*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IF('08_Moteur'!AM30&lt;0,-'08_Moteur'!AM30,IF('08_Moteur'!AN30&gt;=0.95,'08_Moteur'!O30*'08_Moteur'!AO30-'08_Moteur'!U30,0))</f>
-        <v/>
-      </c>
-      <c r="K31" s="29">
-        <f>IF('08_Moteur'!AM30&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN30&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN30&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M31" s="51">
-        <f>IF(L31="Ne pas lancer",0,IF(L31="Statu quo",MAX('08_Moteur'!AI30,'08_Moteur'!M30),IF(L31="Ouvrir +1",'08_Moteur'!AI30+1,'08_Moteur'!AI30)))</f>
-        <v/>
-      </c>
-      <c r="N31" s="51">
-        <f>IF(L31="Ne pas lancer",0,'08_Moteur'!AD30)</f>
-        <v/>
+        <f>H31-I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="70">
+        <f>'08_Moteur'!AN28</f>
+        <v/>
+      </c>
+      <c r="L31" s="71">
+        <f>IF(H31&lt;0,"🔴 Ne pas ouvrir",IF(K31&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K31&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M31" s="72">
+        <f>IF(H31&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K31&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K31&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O31" s="17">
-        <f>N31*'08_Moteur'!AE30*'08_Moteur'!AF30+IF(L31="Ne pas lancer",0,'08_Moteur'!AB30)*'02_Leviers'!$D$16-M31*'08_Moteur'!U30-N31*'08_Moteur'!R30*(1+'02_Leviers'!$G$11)-IF(L31="Ne pas lancer",0,'08_Moteur'!AL30)</f>
+        <f>IF(N31="Ne pas ouvrir",0,IF(N31="Ouvrir +1 classe",H31-'08_Moteur'!U28,IF(N31="Économiser 1 classe",H31+('08_Moteur'!AI28-MAX(1,'08_Moteur'!AI28-1))*'08_Moteur'!U28,H31)))</f>
         <v/>
       </c>
       <c r="P31" s="55">
-        <f>O31-'08_Moteur'!AM30</f>
+        <f>O31-H31</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="48">
-        <f>'08_Moteur'!A31</f>
+        <f>'08_Moteur'!A29</f>
         <v/>
       </c>
       <c r="B32" s="10">
-        <f>'08_Moteur'!B31</f>
+        <f>'08_Moteur'!B29</f>
         <v/>
       </c>
       <c r="C32" s="48">
-        <f>'08_Moteur'!C31</f>
+        <f>'08_Moteur'!C29</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>'08_Moteur'!D31</f>
+        <f>'08_Moteur'!D29</f>
         <v/>
       </c>
       <c r="E32" s="49">
-        <f>'08_Moteur'!AD31</f>
-        <v/>
-      </c>
-      <c r="F32" s="49">
-        <f>'08_Moteur'!AI31</f>
-        <v/>
-      </c>
-      <c r="G32" s="49">
-        <f>'08_Moteur'!M31</f>
-        <v/>
-      </c>
-      <c r="H32" s="71">
-        <f>'08_Moteur'!AN31</f>
-        <v/>
-      </c>
-      <c r="I32" s="72">
-        <f>IF('08_Moteur'!AM31&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN31&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN31&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD29</f>
+        <v/>
+      </c>
+      <c r="F32" s="16">
+        <f>'08_Moteur'!AH29</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>F32-'08_Moteur'!AM29</f>
+        <v/>
+      </c>
+      <c r="H32" s="64">
+        <f>'08_Moteur'!AM29</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>E32*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IF('08_Moteur'!AM31&lt;0,-'08_Moteur'!AM31,IF('08_Moteur'!AN31&gt;=0.95,'08_Moteur'!O31*'08_Moteur'!AO31-'08_Moteur'!U31,0))</f>
-        <v/>
-      </c>
-      <c r="K32" s="29">
-        <f>IF('08_Moteur'!AM31&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN31&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN31&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L32" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M32" s="51">
-        <f>IF(L32="Ne pas lancer",0,IF(L32="Statu quo",MAX('08_Moteur'!AI31,'08_Moteur'!M31),IF(L32="Ouvrir +1",'08_Moteur'!AI31+1,'08_Moteur'!AI31)))</f>
-        <v/>
-      </c>
-      <c r="N32" s="51">
-        <f>IF(L32="Ne pas lancer",0,'08_Moteur'!AD31)</f>
-        <v/>
+        <f>H32-I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="70">
+        <f>'08_Moteur'!AN29</f>
+        <v/>
+      </c>
+      <c r="L32" s="71">
+        <f>IF(H32&lt;0,"🔴 Ne pas ouvrir",IF(K32&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K32&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M32" s="72">
+        <f>IF(H32&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K32&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K32&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N32" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O32" s="17">
-        <f>N32*'08_Moteur'!AE31*'08_Moteur'!AF31+IF(L32="Ne pas lancer",0,'08_Moteur'!AB31)*'02_Leviers'!$D$16-M32*'08_Moteur'!U31-N32*'08_Moteur'!R31*(1+'02_Leviers'!$G$11)-IF(L32="Ne pas lancer",0,'08_Moteur'!AL31)</f>
+        <f>IF(N32="Ne pas ouvrir",0,IF(N32="Ouvrir +1 classe",H32-'08_Moteur'!U29,IF(N32="Économiser 1 classe",H32+('08_Moteur'!AI29-MAX(1,'08_Moteur'!AI29-1))*'08_Moteur'!U29,H32)))</f>
         <v/>
       </c>
       <c r="P32" s="55">
-        <f>O32-'08_Moteur'!AM31</f>
+        <f>O32-H32</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="48">
-        <f>'08_Moteur'!A32</f>
+        <f>'08_Moteur'!A30</f>
         <v/>
       </c>
       <c r="B33" s="10">
-        <f>'08_Moteur'!B32</f>
+        <f>'08_Moteur'!B30</f>
         <v/>
       </c>
       <c r="C33" s="48">
-        <f>'08_Moteur'!C32</f>
+        <f>'08_Moteur'!C30</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>'08_Moteur'!D32</f>
+        <f>'08_Moteur'!D30</f>
         <v/>
       </c>
       <c r="E33" s="49">
-        <f>'08_Moteur'!AD32</f>
-        <v/>
-      </c>
-      <c r="F33" s="49">
-        <f>'08_Moteur'!AI32</f>
-        <v/>
-      </c>
-      <c r="G33" s="49">
-        <f>'08_Moteur'!M32</f>
-        <v/>
-      </c>
-      <c r="H33" s="71">
-        <f>'08_Moteur'!AN32</f>
-        <v/>
-      </c>
-      <c r="I33" s="72">
-        <f>IF('08_Moteur'!AM32&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN32&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN32&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD30</f>
+        <v/>
+      </c>
+      <c r="F33" s="16">
+        <f>'08_Moteur'!AH30</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>F33-'08_Moteur'!AM30</f>
+        <v/>
+      </c>
+      <c r="H33" s="64">
+        <f>'08_Moteur'!AM30</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>E33*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IF('08_Moteur'!AM32&lt;0,-'08_Moteur'!AM32,IF('08_Moteur'!AN32&gt;=0.95,'08_Moteur'!O32*'08_Moteur'!AO32-'08_Moteur'!U32,0))</f>
-        <v/>
-      </c>
-      <c r="K33" s="29">
-        <f>IF('08_Moteur'!AM32&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN32&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN32&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M33" s="51">
-        <f>IF(L33="Ne pas lancer",0,IF(L33="Statu quo",MAX('08_Moteur'!AI32,'08_Moteur'!M32),IF(L33="Ouvrir +1",'08_Moteur'!AI32+1,'08_Moteur'!AI32)))</f>
-        <v/>
-      </c>
-      <c r="N33" s="51">
-        <f>IF(L33="Ne pas lancer",0,'08_Moteur'!AD32)</f>
-        <v/>
+        <f>H33-I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="70">
+        <f>'08_Moteur'!AN30</f>
+        <v/>
+      </c>
+      <c r="L33" s="71">
+        <f>IF(H33&lt;0,"🔴 Ne pas ouvrir",IF(K33&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K33&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M33" s="72">
+        <f>IF(H33&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K33&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K33&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N33" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O33" s="17">
-        <f>N33*'08_Moteur'!AE32*'08_Moteur'!AF32+IF(L33="Ne pas lancer",0,'08_Moteur'!AB32)*'02_Leviers'!$D$16-M33*'08_Moteur'!U32-N33*'08_Moteur'!R32*(1+'02_Leviers'!$G$11)-IF(L33="Ne pas lancer",0,'08_Moteur'!AL32)</f>
+        <f>IF(N33="Ne pas ouvrir",0,IF(N33="Ouvrir +1 classe",H33-'08_Moteur'!U30,IF(N33="Économiser 1 classe",H33+('08_Moteur'!AI30-MAX(1,'08_Moteur'!AI30-1))*'08_Moteur'!U30,H33)))</f>
         <v/>
       </c>
       <c r="P33" s="55">
-        <f>O33-'08_Moteur'!AM32</f>
+        <f>O33-H33</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="48">
-        <f>'08_Moteur'!A33</f>
+        <f>'08_Moteur'!A31</f>
         <v/>
       </c>
       <c r="B34" s="10">
-        <f>'08_Moteur'!B33</f>
+        <f>'08_Moteur'!B31</f>
         <v/>
       </c>
       <c r="C34" s="48">
-        <f>'08_Moteur'!C33</f>
+        <f>'08_Moteur'!C31</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>'08_Moteur'!D33</f>
+        <f>'08_Moteur'!D31</f>
         <v/>
       </c>
       <c r="E34" s="49">
-        <f>'08_Moteur'!AD33</f>
-        <v/>
-      </c>
-      <c r="F34" s="49">
-        <f>'08_Moteur'!AI33</f>
-        <v/>
-      </c>
-      <c r="G34" s="49">
-        <f>'08_Moteur'!M33</f>
-        <v/>
-      </c>
-      <c r="H34" s="71">
-        <f>'08_Moteur'!AN33</f>
-        <v/>
-      </c>
-      <c r="I34" s="72">
-        <f>IF('08_Moteur'!AM33&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN33&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN33&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD31</f>
+        <v/>
+      </c>
+      <c r="F34" s="16">
+        <f>'08_Moteur'!AH31</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>F34-'08_Moteur'!AM31</f>
+        <v/>
+      </c>
+      <c r="H34" s="64">
+        <f>'08_Moteur'!AM31</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>E34*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IF('08_Moteur'!AM33&lt;0,-'08_Moteur'!AM33,IF('08_Moteur'!AN33&gt;=0.95,'08_Moteur'!O33*'08_Moteur'!AO33-'08_Moteur'!U33,0))</f>
-        <v/>
-      </c>
-      <c r="K34" s="29">
-        <f>IF('08_Moteur'!AM33&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN33&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN33&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L34" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M34" s="51">
-        <f>IF(L34="Ne pas lancer",0,IF(L34="Statu quo",MAX('08_Moteur'!AI33,'08_Moteur'!M33),IF(L34="Ouvrir +1",'08_Moteur'!AI33+1,'08_Moteur'!AI33)))</f>
-        <v/>
-      </c>
-      <c r="N34" s="51">
-        <f>IF(L34="Ne pas lancer",0,'08_Moteur'!AD33)</f>
-        <v/>
+        <f>H34-I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="70">
+        <f>'08_Moteur'!AN31</f>
+        <v/>
+      </c>
+      <c r="L34" s="71">
+        <f>IF(H34&lt;0,"🔴 Ne pas ouvrir",IF(K34&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K34&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M34" s="72">
+        <f>IF(H34&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K34&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K34&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O34" s="17">
-        <f>N34*'08_Moteur'!AE33*'08_Moteur'!AF33+IF(L34="Ne pas lancer",0,'08_Moteur'!AB33)*'02_Leviers'!$D$16-M34*'08_Moteur'!U33-N34*'08_Moteur'!R33*(1+'02_Leviers'!$G$11)-IF(L34="Ne pas lancer",0,'08_Moteur'!AL33)</f>
+        <f>IF(N34="Ne pas ouvrir",0,IF(N34="Ouvrir +1 classe",H34-'08_Moteur'!U31,IF(N34="Économiser 1 classe",H34+('08_Moteur'!AI31-MAX(1,'08_Moteur'!AI31-1))*'08_Moteur'!U31,H34)))</f>
         <v/>
       </c>
       <c r="P34" s="55">
-        <f>O34-'08_Moteur'!AM33</f>
+        <f>O34-H34</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="48">
-        <f>'08_Moteur'!A34</f>
+        <f>'08_Moteur'!A32</f>
         <v/>
       </c>
       <c r="B35" s="10">
-        <f>'08_Moteur'!B34</f>
+        <f>'08_Moteur'!B32</f>
         <v/>
       </c>
       <c r="C35" s="48">
-        <f>'08_Moteur'!C34</f>
+        <f>'08_Moteur'!C32</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>'08_Moteur'!D34</f>
+        <f>'08_Moteur'!D32</f>
         <v/>
       </c>
       <c r="E35" s="49">
-        <f>'08_Moteur'!AD34</f>
-        <v/>
-      </c>
-      <c r="F35" s="49">
-        <f>'08_Moteur'!AI34</f>
-        <v/>
-      </c>
-      <c r="G35" s="49">
-        <f>'08_Moteur'!M34</f>
-        <v/>
-      </c>
-      <c r="H35" s="71">
-        <f>'08_Moteur'!AN34</f>
-        <v/>
-      </c>
-      <c r="I35" s="72">
-        <f>IF('08_Moteur'!AM34&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN34&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN34&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD32</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>'08_Moteur'!AH32</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>F35-'08_Moteur'!AM32</f>
+        <v/>
+      </c>
+      <c r="H35" s="64">
+        <f>'08_Moteur'!AM32</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>E35*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IF('08_Moteur'!AM34&lt;0,-'08_Moteur'!AM34,IF('08_Moteur'!AN34&gt;=0.95,'08_Moteur'!O34*'08_Moteur'!AO34-'08_Moteur'!U34,0))</f>
-        <v/>
-      </c>
-      <c r="K35" s="29">
-        <f>IF('08_Moteur'!AM34&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN34&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN34&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M35" s="51">
-        <f>IF(L35="Ne pas lancer",0,IF(L35="Statu quo",MAX('08_Moteur'!AI34,'08_Moteur'!M34),IF(L35="Ouvrir +1",'08_Moteur'!AI34+1,'08_Moteur'!AI34)))</f>
-        <v/>
-      </c>
-      <c r="N35" s="51">
-        <f>IF(L35="Ne pas lancer",0,'08_Moteur'!AD34)</f>
-        <v/>
+        <f>H35-I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="70">
+        <f>'08_Moteur'!AN32</f>
+        <v/>
+      </c>
+      <c r="L35" s="71">
+        <f>IF(H35&lt;0,"🔴 Ne pas ouvrir",IF(K35&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K35&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M35" s="72">
+        <f>IF(H35&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K35&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K35&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O35" s="17">
-        <f>N35*'08_Moteur'!AE34*'08_Moteur'!AF34+IF(L35="Ne pas lancer",0,'08_Moteur'!AB34)*'02_Leviers'!$D$16-M35*'08_Moteur'!U34-N35*'08_Moteur'!R34*(1+'02_Leviers'!$G$11)-IF(L35="Ne pas lancer",0,'08_Moteur'!AL34)</f>
+        <f>IF(N35="Ne pas ouvrir",0,IF(N35="Ouvrir +1 classe",H35-'08_Moteur'!U32,IF(N35="Économiser 1 classe",H35+('08_Moteur'!AI32-MAX(1,'08_Moteur'!AI32-1))*'08_Moteur'!U32,H35)))</f>
         <v/>
       </c>
       <c r="P35" s="55">
-        <f>O35-'08_Moteur'!AM34</f>
+        <f>O35-H35</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="48">
-        <f>'08_Moteur'!A35</f>
+        <f>'08_Moteur'!A33</f>
         <v/>
       </c>
       <c r="B36" s="10">
-        <f>'08_Moteur'!B35</f>
+        <f>'08_Moteur'!B33</f>
         <v/>
       </c>
       <c r="C36" s="48">
-        <f>'08_Moteur'!C35</f>
+        <f>'08_Moteur'!C33</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>'08_Moteur'!D35</f>
+        <f>'08_Moteur'!D33</f>
         <v/>
       </c>
       <c r="E36" s="49">
-        <f>'08_Moteur'!AD35</f>
-        <v/>
-      </c>
-      <c r="F36" s="49">
-        <f>'08_Moteur'!AI35</f>
-        <v/>
-      </c>
-      <c r="G36" s="49">
-        <f>'08_Moteur'!M35</f>
-        <v/>
-      </c>
-      <c r="H36" s="71">
-        <f>'08_Moteur'!AN35</f>
-        <v/>
-      </c>
-      <c r="I36" s="72">
-        <f>IF('08_Moteur'!AM35&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN35&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN35&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD33</f>
+        <v/>
+      </c>
+      <c r="F36" s="16">
+        <f>'08_Moteur'!AH33</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>F36-'08_Moteur'!AM33</f>
+        <v/>
+      </c>
+      <c r="H36" s="64">
+        <f>'08_Moteur'!AM33</f>
+        <v/>
+      </c>
+      <c r="I36" s="17">
+        <f>E36*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J36" s="17">
-        <f>IF('08_Moteur'!AM35&lt;0,-'08_Moteur'!AM35,IF('08_Moteur'!AN35&gt;=0.95,'08_Moteur'!O35*'08_Moteur'!AO35-'08_Moteur'!U35,0))</f>
-        <v/>
-      </c>
-      <c r="K36" s="29">
-        <f>IF('08_Moteur'!AM35&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN35&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN35&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M36" s="51">
-        <f>IF(L36="Ne pas lancer",0,IF(L36="Statu quo",MAX('08_Moteur'!AI35,'08_Moteur'!M35),IF(L36="Ouvrir +1",'08_Moteur'!AI35+1,'08_Moteur'!AI35)))</f>
-        <v/>
-      </c>
-      <c r="N36" s="51">
-        <f>IF(L36="Ne pas lancer",0,'08_Moteur'!AD35)</f>
-        <v/>
+        <f>H36-I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="70">
+        <f>'08_Moteur'!AN33</f>
+        <v/>
+      </c>
+      <c r="L36" s="71">
+        <f>IF(H36&lt;0,"🔴 Ne pas ouvrir",IF(K36&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K36&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M36" s="72">
+        <f>IF(H36&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K36&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K36&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N36" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O36" s="17">
-        <f>N36*'08_Moteur'!AE35*'08_Moteur'!AF35+IF(L36="Ne pas lancer",0,'08_Moteur'!AB35)*'02_Leviers'!$D$16-M36*'08_Moteur'!U35-N36*'08_Moteur'!R35*(1+'02_Leviers'!$G$11)-IF(L36="Ne pas lancer",0,'08_Moteur'!AL35)</f>
+        <f>IF(N36="Ne pas ouvrir",0,IF(N36="Ouvrir +1 classe",H36-'08_Moteur'!U33,IF(N36="Économiser 1 classe",H36+('08_Moteur'!AI33-MAX(1,'08_Moteur'!AI33-1))*'08_Moteur'!U33,H36)))</f>
         <v/>
       </c>
       <c r="P36" s="55">
-        <f>O36-'08_Moteur'!AM35</f>
+        <f>O36-H36</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="48">
-        <f>'08_Moteur'!A36</f>
+        <f>'08_Moteur'!A34</f>
         <v/>
       </c>
       <c r="B37" s="10">
-        <f>'08_Moteur'!B36</f>
+        <f>'08_Moteur'!B34</f>
         <v/>
       </c>
       <c r="C37" s="48">
-        <f>'08_Moteur'!C36</f>
+        <f>'08_Moteur'!C34</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>'08_Moteur'!D36</f>
+        <f>'08_Moteur'!D34</f>
         <v/>
       </c>
       <c r="E37" s="49">
-        <f>'08_Moteur'!AD36</f>
-        <v/>
-      </c>
-      <c r="F37" s="49">
-        <f>'08_Moteur'!AI36</f>
-        <v/>
-      </c>
-      <c r="G37" s="49">
-        <f>'08_Moteur'!M36</f>
-        <v/>
-      </c>
-      <c r="H37" s="71">
-        <f>'08_Moteur'!AN36</f>
-        <v/>
-      </c>
-      <c r="I37" s="72">
-        <f>IF('08_Moteur'!AM36&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN36&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN36&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD34</f>
+        <v/>
+      </c>
+      <c r="F37" s="16">
+        <f>'08_Moteur'!AH34</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>F37-'08_Moteur'!AM34</f>
+        <v/>
+      </c>
+      <c r="H37" s="64">
+        <f>'08_Moteur'!AM34</f>
+        <v/>
+      </c>
+      <c r="I37" s="17">
+        <f>E37*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J37" s="17">
-        <f>IF('08_Moteur'!AM36&lt;0,-'08_Moteur'!AM36,IF('08_Moteur'!AN36&gt;=0.95,'08_Moteur'!O36*'08_Moteur'!AO36-'08_Moteur'!U36,0))</f>
-        <v/>
-      </c>
-      <c r="K37" s="29">
-        <f>IF('08_Moteur'!AM36&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN36&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN36&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M37" s="51">
-        <f>IF(L37="Ne pas lancer",0,IF(L37="Statu quo",MAX('08_Moteur'!AI36,'08_Moteur'!M36),IF(L37="Ouvrir +1",'08_Moteur'!AI36+1,'08_Moteur'!AI36)))</f>
-        <v/>
-      </c>
-      <c r="N37" s="51">
-        <f>IF(L37="Ne pas lancer",0,'08_Moteur'!AD36)</f>
-        <v/>
+        <f>H37-I37</f>
+        <v/>
+      </c>
+      <c r="K37" s="70">
+        <f>'08_Moteur'!AN34</f>
+        <v/>
+      </c>
+      <c r="L37" s="71">
+        <f>IF(H37&lt;0,"🔴 Ne pas ouvrir",IF(K37&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K37&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M37" s="72">
+        <f>IF(H37&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K37&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K37&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N37" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O37" s="17">
-        <f>N37*'08_Moteur'!AE36*'08_Moteur'!AF36+IF(L37="Ne pas lancer",0,'08_Moteur'!AB36)*'02_Leviers'!$D$16-M37*'08_Moteur'!U36-N37*'08_Moteur'!R36*(1+'02_Leviers'!$G$11)-IF(L37="Ne pas lancer",0,'08_Moteur'!AL36)</f>
+        <f>IF(N37="Ne pas ouvrir",0,IF(N37="Ouvrir +1 classe",H37-'08_Moteur'!U34,IF(N37="Économiser 1 classe",H37+('08_Moteur'!AI34-MAX(1,'08_Moteur'!AI34-1))*'08_Moteur'!U34,H37)))</f>
         <v/>
       </c>
       <c r="P37" s="55">
-        <f>O37-'08_Moteur'!AM36</f>
+        <f>O37-H37</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="48">
-        <f>'08_Moteur'!A37</f>
+        <f>'08_Moteur'!A35</f>
         <v/>
       </c>
       <c r="B38" s="10">
-        <f>'08_Moteur'!B37</f>
+        <f>'08_Moteur'!B35</f>
         <v/>
       </c>
       <c r="C38" s="48">
-        <f>'08_Moteur'!C37</f>
+        <f>'08_Moteur'!C35</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>'08_Moteur'!D37</f>
+        <f>'08_Moteur'!D35</f>
         <v/>
       </c>
       <c r="E38" s="49">
-        <f>'08_Moteur'!AD37</f>
-        <v/>
-      </c>
-      <c r="F38" s="49">
-        <f>'08_Moteur'!AI37</f>
-        <v/>
-      </c>
-      <c r="G38" s="49">
-        <f>'08_Moteur'!M37</f>
-        <v/>
-      </c>
-      <c r="H38" s="71">
-        <f>'08_Moteur'!AN37</f>
-        <v/>
-      </c>
-      <c r="I38" s="72">
-        <f>IF('08_Moteur'!AM37&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN37&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN37&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD35</f>
+        <v/>
+      </c>
+      <c r="F38" s="16">
+        <f>'08_Moteur'!AH35</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>F38-'08_Moteur'!AM35</f>
+        <v/>
+      </c>
+      <c r="H38" s="64">
+        <f>'08_Moteur'!AM35</f>
+        <v/>
+      </c>
+      <c r="I38" s="17">
+        <f>E38*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J38" s="17">
-        <f>IF('08_Moteur'!AM37&lt;0,-'08_Moteur'!AM37,IF('08_Moteur'!AN37&gt;=0.95,'08_Moteur'!O37*'08_Moteur'!AO37-'08_Moteur'!U37,0))</f>
-        <v/>
-      </c>
-      <c r="K38" s="29">
-        <f>IF('08_Moteur'!AM37&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN37&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN37&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L38" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M38" s="51">
-        <f>IF(L38="Ne pas lancer",0,IF(L38="Statu quo",MAX('08_Moteur'!AI37,'08_Moteur'!M37),IF(L38="Ouvrir +1",'08_Moteur'!AI37+1,'08_Moteur'!AI37)))</f>
-        <v/>
-      </c>
-      <c r="N38" s="51">
-        <f>IF(L38="Ne pas lancer",0,'08_Moteur'!AD37)</f>
-        <v/>
+        <f>H38-I38</f>
+        <v/>
+      </c>
+      <c r="K38" s="70">
+        <f>'08_Moteur'!AN35</f>
+        <v/>
+      </c>
+      <c r="L38" s="71">
+        <f>IF(H38&lt;0,"🔴 Ne pas ouvrir",IF(K38&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K38&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M38" s="72">
+        <f>IF(H38&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K38&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K38&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N38" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O38" s="17">
-        <f>N38*'08_Moteur'!AE37*'08_Moteur'!AF37+IF(L38="Ne pas lancer",0,'08_Moteur'!AB37)*'02_Leviers'!$D$16-M38*'08_Moteur'!U37-N38*'08_Moteur'!R37*(1+'02_Leviers'!$G$11)-IF(L38="Ne pas lancer",0,'08_Moteur'!AL37)</f>
+        <f>IF(N38="Ne pas ouvrir",0,IF(N38="Ouvrir +1 classe",H38-'08_Moteur'!U35,IF(N38="Économiser 1 classe",H38+('08_Moteur'!AI35-MAX(1,'08_Moteur'!AI35-1))*'08_Moteur'!U35,H38)))</f>
         <v/>
       </c>
       <c r="P38" s="55">
-        <f>O38-'08_Moteur'!AM37</f>
+        <f>O38-H38</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="48">
-        <f>'08_Moteur'!A38</f>
+        <f>'08_Moteur'!A36</f>
         <v/>
       </c>
       <c r="B39" s="10">
-        <f>'08_Moteur'!B38</f>
+        <f>'08_Moteur'!B36</f>
         <v/>
       </c>
       <c r="C39" s="48">
-        <f>'08_Moteur'!C38</f>
+        <f>'08_Moteur'!C36</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>'08_Moteur'!D38</f>
+        <f>'08_Moteur'!D36</f>
         <v/>
       </c>
       <c r="E39" s="49">
-        <f>'08_Moteur'!AD38</f>
-        <v/>
-      </c>
-      <c r="F39" s="49">
-        <f>'08_Moteur'!AI38</f>
-        <v/>
-      </c>
-      <c r="G39" s="49">
-        <f>'08_Moteur'!M38</f>
-        <v/>
-      </c>
-      <c r="H39" s="71">
-        <f>'08_Moteur'!AN38</f>
-        <v/>
-      </c>
-      <c r="I39" s="72">
-        <f>IF('08_Moteur'!AM38&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN38&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN38&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD36</f>
+        <v/>
+      </c>
+      <c r="F39" s="16">
+        <f>'08_Moteur'!AH36</f>
+        <v/>
+      </c>
+      <c r="G39" s="17">
+        <f>F39-'08_Moteur'!AM36</f>
+        <v/>
+      </c>
+      <c r="H39" s="64">
+        <f>'08_Moteur'!AM36</f>
+        <v/>
+      </c>
+      <c r="I39" s="17">
+        <f>E39*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J39" s="17">
-        <f>IF('08_Moteur'!AM38&lt;0,-'08_Moteur'!AM38,IF('08_Moteur'!AN38&gt;=0.95,'08_Moteur'!O38*'08_Moteur'!AO38-'08_Moteur'!U38,0))</f>
-        <v/>
-      </c>
-      <c r="K39" s="29">
-        <f>IF('08_Moteur'!AM38&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN38&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN38&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L39" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M39" s="51">
-        <f>IF(L39="Ne pas lancer",0,IF(L39="Statu quo",MAX('08_Moteur'!AI38,'08_Moteur'!M38),IF(L39="Ouvrir +1",'08_Moteur'!AI38+1,'08_Moteur'!AI38)))</f>
-        <v/>
-      </c>
-      <c r="N39" s="51">
-        <f>IF(L39="Ne pas lancer",0,'08_Moteur'!AD38)</f>
-        <v/>
+        <f>H39-I39</f>
+        <v/>
+      </c>
+      <c r="K39" s="70">
+        <f>'08_Moteur'!AN36</f>
+        <v/>
+      </c>
+      <c r="L39" s="71">
+        <f>IF(H39&lt;0,"🔴 Ne pas ouvrir",IF(K39&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K39&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M39" s="72">
+        <f>IF(H39&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K39&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K39&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N39" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O39" s="17">
-        <f>N39*'08_Moteur'!AE38*'08_Moteur'!AF38+IF(L39="Ne pas lancer",0,'08_Moteur'!AB38)*'02_Leviers'!$D$16-M39*'08_Moteur'!U38-N39*'08_Moteur'!R38*(1+'02_Leviers'!$G$11)-IF(L39="Ne pas lancer",0,'08_Moteur'!AL38)</f>
+        <f>IF(N39="Ne pas ouvrir",0,IF(N39="Ouvrir +1 classe",H39-'08_Moteur'!U36,IF(N39="Économiser 1 classe",H39+('08_Moteur'!AI36-MAX(1,'08_Moteur'!AI36-1))*'08_Moteur'!U36,H39)))</f>
         <v/>
       </c>
       <c r="P39" s="55">
-        <f>O39-'08_Moteur'!AM38</f>
+        <f>O39-H39</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="48">
-        <f>'08_Moteur'!A39</f>
+        <f>'08_Moteur'!A37</f>
         <v/>
       </c>
       <c r="B40" s="10">
-        <f>'08_Moteur'!B39</f>
+        <f>'08_Moteur'!B37</f>
         <v/>
       </c>
       <c r="C40" s="48">
-        <f>'08_Moteur'!C39</f>
+        <f>'08_Moteur'!C37</f>
         <v/>
       </c>
       <c r="D40" s="10">
-        <f>'08_Moteur'!D39</f>
+        <f>'08_Moteur'!D37</f>
         <v/>
       </c>
       <c r="E40" s="49">
-        <f>'08_Moteur'!AD39</f>
-        <v/>
-      </c>
-      <c r="F40" s="49">
-        <f>'08_Moteur'!AI39</f>
-        <v/>
-      </c>
-      <c r="G40" s="49">
-        <f>'08_Moteur'!M39</f>
-        <v/>
-      </c>
-      <c r="H40" s="71">
-        <f>'08_Moteur'!AN39</f>
-        <v/>
-      </c>
-      <c r="I40" s="72">
-        <f>IF('08_Moteur'!AM39&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN39&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN39&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD37</f>
+        <v/>
+      </c>
+      <c r="F40" s="16">
+        <f>'08_Moteur'!AH37</f>
+        <v/>
+      </c>
+      <c r="G40" s="17">
+        <f>F40-'08_Moteur'!AM37</f>
+        <v/>
+      </c>
+      <c r="H40" s="64">
+        <f>'08_Moteur'!AM37</f>
+        <v/>
+      </c>
+      <c r="I40" s="17">
+        <f>E40*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J40" s="17">
-        <f>IF('08_Moteur'!AM39&lt;0,-'08_Moteur'!AM39,IF('08_Moteur'!AN39&gt;=0.95,'08_Moteur'!O39*'08_Moteur'!AO39-'08_Moteur'!U39,0))</f>
-        <v/>
-      </c>
-      <c r="K40" s="29">
-        <f>IF('08_Moteur'!AM39&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN39&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN39&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L40" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M40" s="51">
-        <f>IF(L40="Ne pas lancer",0,IF(L40="Statu quo",MAX('08_Moteur'!AI39,'08_Moteur'!M39),IF(L40="Ouvrir +1",'08_Moteur'!AI39+1,'08_Moteur'!AI39)))</f>
-        <v/>
-      </c>
-      <c r="N40" s="51">
-        <f>IF(L40="Ne pas lancer",0,'08_Moteur'!AD39)</f>
-        <v/>
+        <f>H40-I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="70">
+        <f>'08_Moteur'!AN37</f>
+        <v/>
+      </c>
+      <c r="L40" s="71">
+        <f>IF(H40&lt;0,"🔴 Ne pas ouvrir",IF(K40&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K40&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M40" s="72">
+        <f>IF(H40&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K40&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K40&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N40" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O40" s="17">
-        <f>N40*'08_Moteur'!AE39*'08_Moteur'!AF39+IF(L40="Ne pas lancer",0,'08_Moteur'!AB39)*'02_Leviers'!$D$16-M40*'08_Moteur'!U39-N40*'08_Moteur'!R39*(1+'02_Leviers'!$G$11)-IF(L40="Ne pas lancer",0,'08_Moteur'!AL39)</f>
+        <f>IF(N40="Ne pas ouvrir",0,IF(N40="Ouvrir +1 classe",H40-'08_Moteur'!U37,IF(N40="Économiser 1 classe",H40+('08_Moteur'!AI37-MAX(1,'08_Moteur'!AI37-1))*'08_Moteur'!U37,H40)))</f>
         <v/>
       </c>
       <c r="P40" s="55">
-        <f>O40-'08_Moteur'!AM39</f>
+        <f>O40-H40</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="48">
-        <f>'08_Moteur'!A40</f>
+        <f>'08_Moteur'!A38</f>
         <v/>
       </c>
       <c r="B41" s="10">
-        <f>'08_Moteur'!B40</f>
+        <f>'08_Moteur'!B38</f>
         <v/>
       </c>
       <c r="C41" s="48">
-        <f>'08_Moteur'!C40</f>
+        <f>'08_Moteur'!C38</f>
         <v/>
       </c>
       <c r="D41" s="10">
-        <f>'08_Moteur'!D40</f>
+        <f>'08_Moteur'!D38</f>
         <v/>
       </c>
       <c r="E41" s="49">
-        <f>'08_Moteur'!AD40</f>
-        <v/>
-      </c>
-      <c r="F41" s="49">
-        <f>'08_Moteur'!AI40</f>
-        <v/>
-      </c>
-      <c r="G41" s="49">
-        <f>'08_Moteur'!M40</f>
-        <v/>
-      </c>
-      <c r="H41" s="71">
-        <f>'08_Moteur'!AN40</f>
-        <v/>
-      </c>
-      <c r="I41" s="72">
-        <f>IF('08_Moteur'!AM40&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN40&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN40&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD38</f>
+        <v/>
+      </c>
+      <c r="F41" s="16">
+        <f>'08_Moteur'!AH38</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>F41-'08_Moteur'!AM38</f>
+        <v/>
+      </c>
+      <c r="H41" s="64">
+        <f>'08_Moteur'!AM38</f>
+        <v/>
+      </c>
+      <c r="I41" s="17">
+        <f>E41*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J41" s="17">
-        <f>IF('08_Moteur'!AM40&lt;0,-'08_Moteur'!AM40,IF('08_Moteur'!AN40&gt;=0.95,'08_Moteur'!O40*'08_Moteur'!AO40-'08_Moteur'!U40,0))</f>
-        <v/>
-      </c>
-      <c r="K41" s="29">
-        <f>IF('08_Moteur'!AM40&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN40&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN40&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M41" s="51">
-        <f>IF(L41="Ne pas lancer",0,IF(L41="Statu quo",MAX('08_Moteur'!AI40,'08_Moteur'!M40),IF(L41="Ouvrir +1",'08_Moteur'!AI40+1,'08_Moteur'!AI40)))</f>
-        <v/>
-      </c>
-      <c r="N41" s="51">
-        <f>IF(L41="Ne pas lancer",0,'08_Moteur'!AD40)</f>
-        <v/>
+        <f>H41-I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="70">
+        <f>'08_Moteur'!AN38</f>
+        <v/>
+      </c>
+      <c r="L41" s="71">
+        <f>IF(H41&lt;0,"🔴 Ne pas ouvrir",IF(K41&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K41&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M41" s="72">
+        <f>IF(H41&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K41&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K41&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N41" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O41" s="17">
-        <f>N41*'08_Moteur'!AE40*'08_Moteur'!AF40+IF(L41="Ne pas lancer",0,'08_Moteur'!AB40)*'02_Leviers'!$D$16-M41*'08_Moteur'!U40-N41*'08_Moteur'!R40*(1+'02_Leviers'!$G$11)-IF(L41="Ne pas lancer",0,'08_Moteur'!AL40)</f>
+        <f>IF(N41="Ne pas ouvrir",0,IF(N41="Ouvrir +1 classe",H41-'08_Moteur'!U38,IF(N41="Économiser 1 classe",H41+('08_Moteur'!AI38-MAX(1,'08_Moteur'!AI38-1))*'08_Moteur'!U38,H41)))</f>
         <v/>
       </c>
       <c r="P41" s="55">
-        <f>O41-'08_Moteur'!AM40</f>
+        <f>O41-H41</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="48">
-        <f>'08_Moteur'!A41</f>
+        <f>'08_Moteur'!A39</f>
         <v/>
       </c>
       <c r="B42" s="10">
-        <f>'08_Moteur'!B41</f>
+        <f>'08_Moteur'!B39</f>
         <v/>
       </c>
       <c r="C42" s="48">
-        <f>'08_Moteur'!C41</f>
+        <f>'08_Moteur'!C39</f>
         <v/>
       </c>
       <c r="D42" s="10">
-        <f>'08_Moteur'!D41</f>
+        <f>'08_Moteur'!D39</f>
         <v/>
       </c>
       <c r="E42" s="49">
-        <f>'08_Moteur'!AD41</f>
-        <v/>
-      </c>
-      <c r="F42" s="49">
-        <f>'08_Moteur'!AI41</f>
-        <v/>
-      </c>
-      <c r="G42" s="49">
-        <f>'08_Moteur'!M41</f>
-        <v/>
-      </c>
-      <c r="H42" s="71">
-        <f>'08_Moteur'!AN41</f>
-        <v/>
-      </c>
-      <c r="I42" s="72">
-        <f>IF('08_Moteur'!AM41&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN41&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN41&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD39</f>
+        <v/>
+      </c>
+      <c r="F42" s="16">
+        <f>'08_Moteur'!AH39</f>
+        <v/>
+      </c>
+      <c r="G42" s="17">
+        <f>F42-'08_Moteur'!AM39</f>
+        <v/>
+      </c>
+      <c r="H42" s="64">
+        <f>'08_Moteur'!AM39</f>
+        <v/>
+      </c>
+      <c r="I42" s="17">
+        <f>E42*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J42" s="17">
-        <f>IF('08_Moteur'!AM41&lt;0,-'08_Moteur'!AM41,IF('08_Moteur'!AN41&gt;=0.95,'08_Moteur'!O41*'08_Moteur'!AO41-'08_Moteur'!U41,0))</f>
-        <v/>
-      </c>
-      <c r="K42" s="29">
-        <f>IF('08_Moteur'!AM41&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN41&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN41&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M42" s="51">
-        <f>IF(L42="Ne pas lancer",0,IF(L42="Statu quo",MAX('08_Moteur'!AI41,'08_Moteur'!M41),IF(L42="Ouvrir +1",'08_Moteur'!AI41+1,'08_Moteur'!AI41)))</f>
-        <v/>
-      </c>
-      <c r="N42" s="51">
-        <f>IF(L42="Ne pas lancer",0,'08_Moteur'!AD41)</f>
-        <v/>
+        <f>H42-I42</f>
+        <v/>
+      </c>
+      <c r="K42" s="70">
+        <f>'08_Moteur'!AN39</f>
+        <v/>
+      </c>
+      <c r="L42" s="71">
+        <f>IF(H42&lt;0,"🔴 Ne pas ouvrir",IF(K42&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K42&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M42" s="72">
+        <f>IF(H42&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K42&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K42&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N42" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O42" s="17">
-        <f>N42*'08_Moteur'!AE41*'08_Moteur'!AF41+IF(L42="Ne pas lancer",0,'08_Moteur'!AB41)*'02_Leviers'!$D$16-M42*'08_Moteur'!U41-N42*'08_Moteur'!R41*(1+'02_Leviers'!$G$11)-IF(L42="Ne pas lancer",0,'08_Moteur'!AL41)</f>
+        <f>IF(N42="Ne pas ouvrir",0,IF(N42="Ouvrir +1 classe",H42-'08_Moteur'!U39,IF(N42="Économiser 1 classe",H42+('08_Moteur'!AI39-MAX(1,'08_Moteur'!AI39-1))*'08_Moteur'!U39,H42)))</f>
         <v/>
       </c>
       <c r="P42" s="55">
-        <f>O42-'08_Moteur'!AM41</f>
+        <f>O42-H42</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="48">
-        <f>'08_Moteur'!A42</f>
+        <f>'08_Moteur'!A40</f>
         <v/>
       </c>
       <c r="B43" s="10">
-        <f>'08_Moteur'!B42</f>
+        <f>'08_Moteur'!B40</f>
         <v/>
       </c>
       <c r="C43" s="48">
-        <f>'08_Moteur'!C42</f>
+        <f>'08_Moteur'!C40</f>
         <v/>
       </c>
       <c r="D43" s="10">
-        <f>'08_Moteur'!D42</f>
+        <f>'08_Moteur'!D40</f>
         <v/>
       </c>
       <c r="E43" s="49">
-        <f>'08_Moteur'!AD42</f>
-        <v/>
-      </c>
-      <c r="F43" s="49">
-        <f>'08_Moteur'!AI42</f>
-        <v/>
-      </c>
-      <c r="G43" s="49">
-        <f>'08_Moteur'!M42</f>
-        <v/>
-      </c>
-      <c r="H43" s="71">
-        <f>'08_Moteur'!AN42</f>
-        <v/>
-      </c>
-      <c r="I43" s="72">
-        <f>IF('08_Moteur'!AM42&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN42&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN42&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD40</f>
+        <v/>
+      </c>
+      <c r="F43" s="16">
+        <f>'08_Moteur'!AH40</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>F43-'08_Moteur'!AM40</f>
+        <v/>
+      </c>
+      <c r="H43" s="64">
+        <f>'08_Moteur'!AM40</f>
+        <v/>
+      </c>
+      <c r="I43" s="17">
+        <f>E43*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J43" s="17">
-        <f>IF('08_Moteur'!AM42&lt;0,-'08_Moteur'!AM42,IF('08_Moteur'!AN42&gt;=0.95,'08_Moteur'!O42*'08_Moteur'!AO42-'08_Moteur'!U42,0))</f>
-        <v/>
-      </c>
-      <c r="K43" s="29">
-        <f>IF('08_Moteur'!AM42&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN42&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN42&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L43" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M43" s="51">
-        <f>IF(L43="Ne pas lancer",0,IF(L43="Statu quo",MAX('08_Moteur'!AI42,'08_Moteur'!M42),IF(L43="Ouvrir +1",'08_Moteur'!AI42+1,'08_Moteur'!AI42)))</f>
-        <v/>
-      </c>
-      <c r="N43" s="51">
-        <f>IF(L43="Ne pas lancer",0,'08_Moteur'!AD42)</f>
-        <v/>
+        <f>H43-I43</f>
+        <v/>
+      </c>
+      <c r="K43" s="70">
+        <f>'08_Moteur'!AN40</f>
+        <v/>
+      </c>
+      <c r="L43" s="71">
+        <f>IF(H43&lt;0,"🔴 Ne pas ouvrir",IF(K43&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K43&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M43" s="72">
+        <f>IF(H43&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K43&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K43&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N43" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O43" s="17">
-        <f>N43*'08_Moteur'!AE42*'08_Moteur'!AF42+IF(L43="Ne pas lancer",0,'08_Moteur'!AB42)*'02_Leviers'!$D$16-M43*'08_Moteur'!U42-N43*'08_Moteur'!R42*(1+'02_Leviers'!$G$11)-IF(L43="Ne pas lancer",0,'08_Moteur'!AL42)</f>
+        <f>IF(N43="Ne pas ouvrir",0,IF(N43="Ouvrir +1 classe",H43-'08_Moteur'!U40,IF(N43="Économiser 1 classe",H43+('08_Moteur'!AI40-MAX(1,'08_Moteur'!AI40-1))*'08_Moteur'!U40,H43)))</f>
         <v/>
       </c>
       <c r="P43" s="55">
-        <f>O43-'08_Moteur'!AM42</f>
+        <f>O43-H43</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="48">
-        <f>'08_Moteur'!A43</f>
+        <f>'08_Moteur'!A41</f>
         <v/>
       </c>
       <c r="B44" s="10">
-        <f>'08_Moteur'!B43</f>
+        <f>'08_Moteur'!B41</f>
         <v/>
       </c>
       <c r="C44" s="48">
-        <f>'08_Moteur'!C43</f>
+        <f>'08_Moteur'!C41</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>'08_Moteur'!D43</f>
+        <f>'08_Moteur'!D41</f>
         <v/>
       </c>
       <c r="E44" s="49">
-        <f>'08_Moteur'!AD43</f>
-        <v/>
-      </c>
-      <c r="F44" s="49">
-        <f>'08_Moteur'!AI43</f>
-        <v/>
-      </c>
-      <c r="G44" s="49">
-        <f>'08_Moteur'!M43</f>
-        <v/>
-      </c>
-      <c r="H44" s="71">
-        <f>'08_Moteur'!AN43</f>
-        <v/>
-      </c>
-      <c r="I44" s="72">
-        <f>IF('08_Moteur'!AM43&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN43&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN43&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD41</f>
+        <v/>
+      </c>
+      <c r="F44" s="16">
+        <f>'08_Moteur'!AH41</f>
+        <v/>
+      </c>
+      <c r="G44" s="17">
+        <f>F44-'08_Moteur'!AM41</f>
+        <v/>
+      </c>
+      <c r="H44" s="64">
+        <f>'08_Moteur'!AM41</f>
+        <v/>
+      </c>
+      <c r="I44" s="17">
+        <f>E44*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J44" s="17">
-        <f>IF('08_Moteur'!AM43&lt;0,-'08_Moteur'!AM43,IF('08_Moteur'!AN43&gt;=0.95,'08_Moteur'!O43*'08_Moteur'!AO43-'08_Moteur'!U43,0))</f>
-        <v/>
-      </c>
-      <c r="K44" s="29">
-        <f>IF('08_Moteur'!AM43&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN43&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN43&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L44" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M44" s="51">
-        <f>IF(L44="Ne pas lancer",0,IF(L44="Statu quo",MAX('08_Moteur'!AI43,'08_Moteur'!M43),IF(L44="Ouvrir +1",'08_Moteur'!AI43+1,'08_Moteur'!AI43)))</f>
-        <v/>
-      </c>
-      <c r="N44" s="51">
-        <f>IF(L44="Ne pas lancer",0,'08_Moteur'!AD43)</f>
-        <v/>
+        <f>H44-I44</f>
+        <v/>
+      </c>
+      <c r="K44" s="70">
+        <f>'08_Moteur'!AN41</f>
+        <v/>
+      </c>
+      <c r="L44" s="71">
+        <f>IF(H44&lt;0,"🔴 Ne pas ouvrir",IF(K44&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K44&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M44" s="72">
+        <f>IF(H44&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K44&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K44&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N44" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O44" s="17">
-        <f>N44*'08_Moteur'!AE43*'08_Moteur'!AF43+IF(L44="Ne pas lancer",0,'08_Moteur'!AB43)*'02_Leviers'!$D$16-M44*'08_Moteur'!U43-N44*'08_Moteur'!R43*(1+'02_Leviers'!$G$11)-IF(L44="Ne pas lancer",0,'08_Moteur'!AL43)</f>
+        <f>IF(N44="Ne pas ouvrir",0,IF(N44="Ouvrir +1 classe",H44-'08_Moteur'!U41,IF(N44="Économiser 1 classe",H44+('08_Moteur'!AI41-MAX(1,'08_Moteur'!AI41-1))*'08_Moteur'!U41,H44)))</f>
         <v/>
       </c>
       <c r="P44" s="55">
-        <f>O44-'08_Moteur'!AM43</f>
+        <f>O44-H44</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="48">
-        <f>'08_Moteur'!A44</f>
+        <f>'08_Moteur'!A42</f>
         <v/>
       </c>
       <c r="B45" s="10">
-        <f>'08_Moteur'!B44</f>
+        <f>'08_Moteur'!B42</f>
         <v/>
       </c>
       <c r="C45" s="48">
-        <f>'08_Moteur'!C44</f>
+        <f>'08_Moteur'!C42</f>
         <v/>
       </c>
       <c r="D45" s="10">
-        <f>'08_Moteur'!D44</f>
+        <f>'08_Moteur'!D42</f>
         <v/>
       </c>
       <c r="E45" s="49">
-        <f>'08_Moteur'!AD44</f>
-        <v/>
-      </c>
-      <c r="F45" s="49">
-        <f>'08_Moteur'!AI44</f>
-        <v/>
-      </c>
-      <c r="G45" s="49">
-        <f>'08_Moteur'!M44</f>
-        <v/>
-      </c>
-      <c r="H45" s="71">
-        <f>'08_Moteur'!AN44</f>
-        <v/>
-      </c>
-      <c r="I45" s="72">
-        <f>IF('08_Moteur'!AM44&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN44&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN44&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD42</f>
+        <v/>
+      </c>
+      <c r="F45" s="16">
+        <f>'08_Moteur'!AH42</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>F45-'08_Moteur'!AM42</f>
+        <v/>
+      </c>
+      <c r="H45" s="64">
+        <f>'08_Moteur'!AM42</f>
+        <v/>
+      </c>
+      <c r="I45" s="17">
+        <f>E45*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J45" s="17">
-        <f>IF('08_Moteur'!AM44&lt;0,-'08_Moteur'!AM44,IF('08_Moteur'!AN44&gt;=0.95,'08_Moteur'!O44*'08_Moteur'!AO44-'08_Moteur'!U44,0))</f>
-        <v/>
-      </c>
-      <c r="K45" s="29">
-        <f>IF('08_Moteur'!AM44&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN44&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN44&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L45" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M45" s="51">
-        <f>IF(L45="Ne pas lancer",0,IF(L45="Statu quo",MAX('08_Moteur'!AI44,'08_Moteur'!M44),IF(L45="Ouvrir +1",'08_Moteur'!AI44+1,'08_Moteur'!AI44)))</f>
-        <v/>
-      </c>
-      <c r="N45" s="51">
-        <f>IF(L45="Ne pas lancer",0,'08_Moteur'!AD44)</f>
-        <v/>
+        <f>H45-I45</f>
+        <v/>
+      </c>
+      <c r="K45" s="70">
+        <f>'08_Moteur'!AN42</f>
+        <v/>
+      </c>
+      <c r="L45" s="71">
+        <f>IF(H45&lt;0,"🔴 Ne pas ouvrir",IF(K45&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K45&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M45" s="72">
+        <f>IF(H45&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K45&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K45&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N45" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O45" s="17">
-        <f>N45*'08_Moteur'!AE44*'08_Moteur'!AF44+IF(L45="Ne pas lancer",0,'08_Moteur'!AB44)*'02_Leviers'!$D$16-M45*'08_Moteur'!U44-N45*'08_Moteur'!R44*(1+'02_Leviers'!$G$11)-IF(L45="Ne pas lancer",0,'08_Moteur'!AL44)</f>
+        <f>IF(N45="Ne pas ouvrir",0,IF(N45="Ouvrir +1 classe",H45-'08_Moteur'!U42,IF(N45="Économiser 1 classe",H45+('08_Moteur'!AI42-MAX(1,'08_Moteur'!AI42-1))*'08_Moteur'!U42,H45)))</f>
         <v/>
       </c>
       <c r="P45" s="55">
-        <f>O45-'08_Moteur'!AM44</f>
+        <f>O45-H45</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="48">
-        <f>'08_Moteur'!A45</f>
+        <f>'08_Moteur'!A43</f>
         <v/>
       </c>
       <c r="B46" s="10">
-        <f>'08_Moteur'!B45</f>
+        <f>'08_Moteur'!B43</f>
         <v/>
       </c>
       <c r="C46" s="48">
-        <f>'08_Moteur'!C45</f>
+        <f>'08_Moteur'!C43</f>
         <v/>
       </c>
       <c r="D46" s="10">
-        <f>'08_Moteur'!D45</f>
+        <f>'08_Moteur'!D43</f>
         <v/>
       </c>
       <c r="E46" s="49">
-        <f>'08_Moteur'!AD45</f>
-        <v/>
-      </c>
-      <c r="F46" s="49">
-        <f>'08_Moteur'!AI45</f>
-        <v/>
-      </c>
-      <c r="G46" s="49">
-        <f>'08_Moteur'!M45</f>
-        <v/>
-      </c>
-      <c r="H46" s="71">
-        <f>'08_Moteur'!AN45</f>
-        <v/>
-      </c>
-      <c r="I46" s="72">
-        <f>IF('08_Moteur'!AM45&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN45&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN45&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD43</f>
+        <v/>
+      </c>
+      <c r="F46" s="16">
+        <f>'08_Moteur'!AH43</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>F46-'08_Moteur'!AM43</f>
+        <v/>
+      </c>
+      <c r="H46" s="64">
+        <f>'08_Moteur'!AM43</f>
+        <v/>
+      </c>
+      <c r="I46" s="17">
+        <f>E46*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J46" s="17">
-        <f>IF('08_Moteur'!AM45&lt;0,-'08_Moteur'!AM45,IF('08_Moteur'!AN45&gt;=0.95,'08_Moteur'!O45*'08_Moteur'!AO45-'08_Moteur'!U45,0))</f>
-        <v/>
-      </c>
-      <c r="K46" s="29">
-        <f>IF('08_Moteur'!AM45&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN45&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN45&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L46" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M46" s="51">
-        <f>IF(L46="Ne pas lancer",0,IF(L46="Statu quo",MAX('08_Moteur'!AI45,'08_Moteur'!M45),IF(L46="Ouvrir +1",'08_Moteur'!AI45+1,'08_Moteur'!AI45)))</f>
-        <v/>
-      </c>
-      <c r="N46" s="51">
-        <f>IF(L46="Ne pas lancer",0,'08_Moteur'!AD45)</f>
-        <v/>
+        <f>H46-I46</f>
+        <v/>
+      </c>
+      <c r="K46" s="70">
+        <f>'08_Moteur'!AN43</f>
+        <v/>
+      </c>
+      <c r="L46" s="71">
+        <f>IF(H46&lt;0,"🔴 Ne pas ouvrir",IF(K46&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K46&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M46" s="72">
+        <f>IF(H46&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K46&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K46&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N46" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O46" s="17">
-        <f>N46*'08_Moteur'!AE45*'08_Moteur'!AF45+IF(L46="Ne pas lancer",0,'08_Moteur'!AB45)*'02_Leviers'!$D$16-M46*'08_Moteur'!U45-N46*'08_Moteur'!R45*(1+'02_Leviers'!$G$11)-IF(L46="Ne pas lancer",0,'08_Moteur'!AL45)</f>
+        <f>IF(N46="Ne pas ouvrir",0,IF(N46="Ouvrir +1 classe",H46-'08_Moteur'!U43,IF(N46="Économiser 1 classe",H46+('08_Moteur'!AI43-MAX(1,'08_Moteur'!AI43-1))*'08_Moteur'!U43,H46)))</f>
         <v/>
       </c>
       <c r="P46" s="55">
-        <f>O46-'08_Moteur'!AM45</f>
+        <f>O46-H46</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="48">
-        <f>'08_Moteur'!A46</f>
+        <f>'08_Moteur'!A44</f>
         <v/>
       </c>
       <c r="B47" s="10">
-        <f>'08_Moteur'!B46</f>
+        <f>'08_Moteur'!B44</f>
         <v/>
       </c>
       <c r="C47" s="48">
-        <f>'08_Moteur'!C46</f>
+        <f>'08_Moteur'!C44</f>
         <v/>
       </c>
       <c r="D47" s="10">
-        <f>'08_Moteur'!D46</f>
+        <f>'08_Moteur'!D44</f>
         <v/>
       </c>
       <c r="E47" s="49">
-        <f>'08_Moteur'!AD46</f>
-        <v/>
-      </c>
-      <c r="F47" s="49">
-        <f>'08_Moteur'!AI46</f>
-        <v/>
-      </c>
-      <c r="G47" s="49">
-        <f>'08_Moteur'!M46</f>
-        <v/>
-      </c>
-      <c r="H47" s="71">
-        <f>'08_Moteur'!AN46</f>
-        <v/>
-      </c>
-      <c r="I47" s="72">
-        <f>IF('08_Moteur'!AM46&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN46&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN46&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD44</f>
+        <v/>
+      </c>
+      <c r="F47" s="16">
+        <f>'08_Moteur'!AH44</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>F47-'08_Moteur'!AM44</f>
+        <v/>
+      </c>
+      <c r="H47" s="64">
+        <f>'08_Moteur'!AM44</f>
+        <v/>
+      </c>
+      <c r="I47" s="17">
+        <f>E47*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J47" s="17">
-        <f>IF('08_Moteur'!AM46&lt;0,-'08_Moteur'!AM46,IF('08_Moteur'!AN46&gt;=0.95,'08_Moteur'!O46*'08_Moteur'!AO46-'08_Moteur'!U46,0))</f>
-        <v/>
-      </c>
-      <c r="K47" s="29">
-        <f>IF('08_Moteur'!AM46&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN46&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN46&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L47" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M47" s="51">
-        <f>IF(L47="Ne pas lancer",0,IF(L47="Statu quo",MAX('08_Moteur'!AI46,'08_Moteur'!M46),IF(L47="Ouvrir +1",'08_Moteur'!AI46+1,'08_Moteur'!AI46)))</f>
-        <v/>
-      </c>
-      <c r="N47" s="51">
-        <f>IF(L47="Ne pas lancer",0,'08_Moteur'!AD46)</f>
-        <v/>
+        <f>H47-I47</f>
+        <v/>
+      </c>
+      <c r="K47" s="70">
+        <f>'08_Moteur'!AN44</f>
+        <v/>
+      </c>
+      <c r="L47" s="71">
+        <f>IF(H47&lt;0,"🔴 Ne pas ouvrir",IF(K47&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K47&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M47" s="72">
+        <f>IF(H47&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K47&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K47&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N47" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O47" s="17">
-        <f>N47*'08_Moteur'!AE46*'08_Moteur'!AF46+IF(L47="Ne pas lancer",0,'08_Moteur'!AB46)*'02_Leviers'!$D$16-M47*'08_Moteur'!U46-N47*'08_Moteur'!R46*(1+'02_Leviers'!$G$11)-IF(L47="Ne pas lancer",0,'08_Moteur'!AL46)</f>
+        <f>IF(N47="Ne pas ouvrir",0,IF(N47="Ouvrir +1 classe",H47-'08_Moteur'!U44,IF(N47="Économiser 1 classe",H47+('08_Moteur'!AI44-MAX(1,'08_Moteur'!AI44-1))*'08_Moteur'!U44,H47)))</f>
         <v/>
       </c>
       <c r="P47" s="55">
-        <f>O47-'08_Moteur'!AM46</f>
+        <f>O47-H47</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="48">
-        <f>'08_Moteur'!A47</f>
+        <f>'08_Moteur'!A45</f>
         <v/>
       </c>
       <c r="B48" s="10">
-        <f>'08_Moteur'!B47</f>
+        <f>'08_Moteur'!B45</f>
         <v/>
       </c>
       <c r="C48" s="48">
-        <f>'08_Moteur'!C47</f>
+        <f>'08_Moteur'!C45</f>
         <v/>
       </c>
       <c r="D48" s="10">
-        <f>'08_Moteur'!D47</f>
+        <f>'08_Moteur'!D45</f>
         <v/>
       </c>
       <c r="E48" s="49">
-        <f>'08_Moteur'!AD47</f>
-        <v/>
-      </c>
-      <c r="F48" s="49">
-        <f>'08_Moteur'!AI47</f>
-        <v/>
-      </c>
-      <c r="G48" s="49">
-        <f>'08_Moteur'!M47</f>
-        <v/>
-      </c>
-      <c r="H48" s="71">
-        <f>'08_Moteur'!AN47</f>
-        <v/>
-      </c>
-      <c r="I48" s="72">
-        <f>IF('08_Moteur'!AM47&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN47&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN47&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD45</f>
+        <v/>
+      </c>
+      <c r="F48" s="16">
+        <f>'08_Moteur'!AH45</f>
+        <v/>
+      </c>
+      <c r="G48" s="17">
+        <f>F48-'08_Moteur'!AM45</f>
+        <v/>
+      </c>
+      <c r="H48" s="64">
+        <f>'08_Moteur'!AM45</f>
+        <v/>
+      </c>
+      <c r="I48" s="17">
+        <f>E48*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J48" s="17">
-        <f>IF('08_Moteur'!AM47&lt;0,-'08_Moteur'!AM47,IF('08_Moteur'!AN47&gt;=0.95,'08_Moteur'!O47*'08_Moteur'!AO47-'08_Moteur'!U47,0))</f>
-        <v/>
-      </c>
-      <c r="K48" s="29">
-        <f>IF('08_Moteur'!AM47&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN47&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN47&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L48" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M48" s="51">
-        <f>IF(L48="Ne pas lancer",0,IF(L48="Statu quo",MAX('08_Moteur'!AI47,'08_Moteur'!M47),IF(L48="Ouvrir +1",'08_Moteur'!AI47+1,'08_Moteur'!AI47)))</f>
-        <v/>
-      </c>
-      <c r="N48" s="51">
-        <f>IF(L48="Ne pas lancer",0,'08_Moteur'!AD47)</f>
-        <v/>
+        <f>H48-I48</f>
+        <v/>
+      </c>
+      <c r="K48" s="70">
+        <f>'08_Moteur'!AN45</f>
+        <v/>
+      </c>
+      <c r="L48" s="71">
+        <f>IF(H48&lt;0,"🔴 Ne pas ouvrir",IF(K48&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K48&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M48" s="72">
+        <f>IF(H48&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K48&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K48&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N48" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O48" s="17">
-        <f>N48*'08_Moteur'!AE47*'08_Moteur'!AF47+IF(L48="Ne pas lancer",0,'08_Moteur'!AB47)*'02_Leviers'!$D$16-M48*'08_Moteur'!U47-N48*'08_Moteur'!R47*(1+'02_Leviers'!$G$11)-IF(L48="Ne pas lancer",0,'08_Moteur'!AL47)</f>
+        <f>IF(N48="Ne pas ouvrir",0,IF(N48="Ouvrir +1 classe",H48-'08_Moteur'!U45,IF(N48="Économiser 1 classe",H48+('08_Moteur'!AI45-MAX(1,'08_Moteur'!AI45-1))*'08_Moteur'!U45,H48)))</f>
         <v/>
       </c>
       <c r="P48" s="55">
-        <f>O48-'08_Moteur'!AM47</f>
+        <f>O48-H48</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="48">
-        <f>'08_Moteur'!A48</f>
+        <f>'08_Moteur'!A46</f>
         <v/>
       </c>
       <c r="B49" s="10">
-        <f>'08_Moteur'!B48</f>
+        <f>'08_Moteur'!B46</f>
         <v/>
       </c>
       <c r="C49" s="48">
-        <f>'08_Moteur'!C48</f>
+        <f>'08_Moteur'!C46</f>
         <v/>
       </c>
       <c r="D49" s="10">
-        <f>'08_Moteur'!D48</f>
+        <f>'08_Moteur'!D46</f>
         <v/>
       </c>
       <c r="E49" s="49">
-        <f>'08_Moteur'!AD48</f>
-        <v/>
-      </c>
-      <c r="F49" s="49">
-        <f>'08_Moteur'!AI48</f>
-        <v/>
-      </c>
-      <c r="G49" s="49">
-        <f>'08_Moteur'!M48</f>
-        <v/>
-      </c>
-      <c r="H49" s="71">
-        <f>'08_Moteur'!AN48</f>
-        <v/>
-      </c>
-      <c r="I49" s="72">
-        <f>IF('08_Moteur'!AM48&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN48&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN48&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD46</f>
+        <v/>
+      </c>
+      <c r="F49" s="16">
+        <f>'08_Moteur'!AH46</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>F49-'08_Moteur'!AM46</f>
+        <v/>
+      </c>
+      <c r="H49" s="64">
+        <f>'08_Moteur'!AM46</f>
+        <v/>
+      </c>
+      <c r="I49" s="17">
+        <f>E49*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J49" s="17">
-        <f>IF('08_Moteur'!AM48&lt;0,-'08_Moteur'!AM48,IF('08_Moteur'!AN48&gt;=0.95,'08_Moteur'!O48*'08_Moteur'!AO48-'08_Moteur'!U48,0))</f>
-        <v/>
-      </c>
-      <c r="K49" s="29">
-        <f>IF('08_Moteur'!AM48&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN48&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN48&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L49" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M49" s="51">
-        <f>IF(L49="Ne pas lancer",0,IF(L49="Statu quo",MAX('08_Moteur'!AI48,'08_Moteur'!M48),IF(L49="Ouvrir +1",'08_Moteur'!AI48+1,'08_Moteur'!AI48)))</f>
-        <v/>
-      </c>
-      <c r="N49" s="51">
-        <f>IF(L49="Ne pas lancer",0,'08_Moteur'!AD48)</f>
-        <v/>
+        <f>H49-I49</f>
+        <v/>
+      </c>
+      <c r="K49" s="70">
+        <f>'08_Moteur'!AN46</f>
+        <v/>
+      </c>
+      <c r="L49" s="71">
+        <f>IF(H49&lt;0,"🔴 Ne pas ouvrir",IF(K49&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K49&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M49" s="72">
+        <f>IF(H49&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K49&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K49&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N49" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O49" s="17">
-        <f>N49*'08_Moteur'!AE48*'08_Moteur'!AF48+IF(L49="Ne pas lancer",0,'08_Moteur'!AB48)*'02_Leviers'!$D$16-M49*'08_Moteur'!U48-N49*'08_Moteur'!R48*(1+'02_Leviers'!$G$11)-IF(L49="Ne pas lancer",0,'08_Moteur'!AL48)</f>
+        <f>IF(N49="Ne pas ouvrir",0,IF(N49="Ouvrir +1 classe",H49-'08_Moteur'!U46,IF(N49="Économiser 1 classe",H49+('08_Moteur'!AI46-MAX(1,'08_Moteur'!AI46-1))*'08_Moteur'!U46,H49)))</f>
         <v/>
       </c>
       <c r="P49" s="55">
-        <f>O49-'08_Moteur'!AM48</f>
+        <f>O49-H49</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="48">
-        <f>'08_Moteur'!A49</f>
+        <f>'08_Moteur'!A47</f>
         <v/>
       </c>
       <c r="B50" s="10">
-        <f>'08_Moteur'!B49</f>
+        <f>'08_Moteur'!B47</f>
         <v/>
       </c>
       <c r="C50" s="48">
-        <f>'08_Moteur'!C49</f>
+        <f>'08_Moteur'!C47</f>
         <v/>
       </c>
       <c r="D50" s="10">
-        <f>'08_Moteur'!D49</f>
+        <f>'08_Moteur'!D47</f>
         <v/>
       </c>
       <c r="E50" s="49">
-        <f>'08_Moteur'!AD49</f>
-        <v/>
-      </c>
-      <c r="F50" s="49">
-        <f>'08_Moteur'!AI49</f>
-        <v/>
-      </c>
-      <c r="G50" s="49">
-        <f>'08_Moteur'!M49</f>
-        <v/>
-      </c>
-      <c r="H50" s="71">
-        <f>'08_Moteur'!AN49</f>
-        <v/>
-      </c>
-      <c r="I50" s="72">
-        <f>IF('08_Moteur'!AM49&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN49&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN49&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD47</f>
+        <v/>
+      </c>
+      <c r="F50" s="16">
+        <f>'08_Moteur'!AH47</f>
+        <v/>
+      </c>
+      <c r="G50" s="17">
+        <f>F50-'08_Moteur'!AM47</f>
+        <v/>
+      </c>
+      <c r="H50" s="64">
+        <f>'08_Moteur'!AM47</f>
+        <v/>
+      </c>
+      <c r="I50" s="17">
+        <f>E50*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J50" s="17">
-        <f>IF('08_Moteur'!AM49&lt;0,-'08_Moteur'!AM49,IF('08_Moteur'!AN49&gt;=0.95,'08_Moteur'!O49*'08_Moteur'!AO49-'08_Moteur'!U49,0))</f>
-        <v/>
-      </c>
-      <c r="K50" s="29">
-        <f>IF('08_Moteur'!AM49&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN49&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN49&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L50" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M50" s="51">
-        <f>IF(L50="Ne pas lancer",0,IF(L50="Statu quo",MAX('08_Moteur'!AI49,'08_Moteur'!M49),IF(L50="Ouvrir +1",'08_Moteur'!AI49+1,'08_Moteur'!AI49)))</f>
-        <v/>
-      </c>
-      <c r="N50" s="51">
-        <f>IF(L50="Ne pas lancer",0,'08_Moteur'!AD49)</f>
-        <v/>
+        <f>H50-I50</f>
+        <v/>
+      </c>
+      <c r="K50" s="70">
+        <f>'08_Moteur'!AN47</f>
+        <v/>
+      </c>
+      <c r="L50" s="71">
+        <f>IF(H50&lt;0,"🔴 Ne pas ouvrir",IF(K50&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K50&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M50" s="72">
+        <f>IF(H50&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K50&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K50&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N50" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O50" s="17">
-        <f>N50*'08_Moteur'!AE49*'08_Moteur'!AF49+IF(L50="Ne pas lancer",0,'08_Moteur'!AB49)*'02_Leviers'!$D$16-M50*'08_Moteur'!U49-N50*'08_Moteur'!R49*(1+'02_Leviers'!$G$11)-IF(L50="Ne pas lancer",0,'08_Moteur'!AL49)</f>
+        <f>IF(N50="Ne pas ouvrir",0,IF(N50="Ouvrir +1 classe",H50-'08_Moteur'!U47,IF(N50="Économiser 1 classe",H50+('08_Moteur'!AI47-MAX(1,'08_Moteur'!AI47-1))*'08_Moteur'!U47,H50)))</f>
         <v/>
       </c>
       <c r="P50" s="55">
-        <f>O50-'08_Moteur'!AM49</f>
+        <f>O50-H50</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="48">
-        <f>'08_Moteur'!A50</f>
+        <f>'08_Moteur'!A48</f>
         <v/>
       </c>
       <c r="B51" s="10">
-        <f>'08_Moteur'!B50</f>
+        <f>'08_Moteur'!B48</f>
         <v/>
       </c>
       <c r="C51" s="48">
-        <f>'08_Moteur'!C50</f>
+        <f>'08_Moteur'!C48</f>
         <v/>
       </c>
       <c r="D51" s="10">
-        <f>'08_Moteur'!D50</f>
+        <f>'08_Moteur'!D48</f>
         <v/>
       </c>
       <c r="E51" s="49">
-        <f>'08_Moteur'!AD50</f>
-        <v/>
-      </c>
-      <c r="F51" s="49">
-        <f>'08_Moteur'!AI50</f>
-        <v/>
-      </c>
-      <c r="G51" s="49">
-        <f>'08_Moteur'!M50</f>
-        <v/>
-      </c>
-      <c r="H51" s="71">
-        <f>'08_Moteur'!AN50</f>
-        <v/>
-      </c>
-      <c r="I51" s="72">
-        <f>IF('08_Moteur'!AM50&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN50&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN50&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD48</f>
+        <v/>
+      </c>
+      <c r="F51" s="16">
+        <f>'08_Moteur'!AH48</f>
+        <v/>
+      </c>
+      <c r="G51" s="17">
+        <f>F51-'08_Moteur'!AM48</f>
+        <v/>
+      </c>
+      <c r="H51" s="64">
+        <f>'08_Moteur'!AM48</f>
+        <v/>
+      </c>
+      <c r="I51" s="17">
+        <f>E51*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J51" s="17">
-        <f>IF('08_Moteur'!AM50&lt;0,-'08_Moteur'!AM50,IF('08_Moteur'!AN50&gt;=0.95,'08_Moteur'!O50*'08_Moteur'!AO50-'08_Moteur'!U50,0))</f>
-        <v/>
-      </c>
-      <c r="K51" s="29">
-        <f>IF('08_Moteur'!AM50&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN50&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN50&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L51" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M51" s="51">
-        <f>IF(L51="Ne pas lancer",0,IF(L51="Statu quo",MAX('08_Moteur'!AI50,'08_Moteur'!M50),IF(L51="Ouvrir +1",'08_Moteur'!AI50+1,'08_Moteur'!AI50)))</f>
-        <v/>
-      </c>
-      <c r="N51" s="51">
-        <f>IF(L51="Ne pas lancer",0,'08_Moteur'!AD50)</f>
-        <v/>
+        <f>H51-I51</f>
+        <v/>
+      </c>
+      <c r="K51" s="70">
+        <f>'08_Moteur'!AN48</f>
+        <v/>
+      </c>
+      <c r="L51" s="71">
+        <f>IF(H51&lt;0,"🔴 Ne pas ouvrir",IF(K51&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K51&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M51" s="72">
+        <f>IF(H51&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K51&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K51&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N51" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O51" s="17">
-        <f>N51*'08_Moteur'!AE50*'08_Moteur'!AF50+IF(L51="Ne pas lancer",0,'08_Moteur'!AB50)*'02_Leviers'!$D$16-M51*'08_Moteur'!U50-N51*'08_Moteur'!R50*(1+'02_Leviers'!$G$11)-IF(L51="Ne pas lancer",0,'08_Moteur'!AL50)</f>
+        <f>IF(N51="Ne pas ouvrir",0,IF(N51="Ouvrir +1 classe",H51-'08_Moteur'!U48,IF(N51="Économiser 1 classe",H51+('08_Moteur'!AI48-MAX(1,'08_Moteur'!AI48-1))*'08_Moteur'!U48,H51)))</f>
         <v/>
       </c>
       <c r="P51" s="55">
-        <f>O51-'08_Moteur'!AM50</f>
+        <f>O51-H51</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="48">
-        <f>'08_Moteur'!A51</f>
+        <f>'08_Moteur'!A49</f>
         <v/>
       </c>
       <c r="B52" s="10">
-        <f>'08_Moteur'!B51</f>
+        <f>'08_Moteur'!B49</f>
         <v/>
       </c>
       <c r="C52" s="48">
-        <f>'08_Moteur'!C51</f>
+        <f>'08_Moteur'!C49</f>
         <v/>
       </c>
       <c r="D52" s="10">
-        <f>'08_Moteur'!D51</f>
+        <f>'08_Moteur'!D49</f>
         <v/>
       </c>
       <c r="E52" s="49">
-        <f>'08_Moteur'!AD51</f>
-        <v/>
-      </c>
-      <c r="F52" s="49">
-        <f>'08_Moteur'!AI51</f>
-        <v/>
-      </c>
-      <c r="G52" s="49">
-        <f>'08_Moteur'!M51</f>
-        <v/>
-      </c>
-      <c r="H52" s="71">
-        <f>'08_Moteur'!AN51</f>
-        <v/>
-      </c>
-      <c r="I52" s="72">
-        <f>IF('08_Moteur'!AM51&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN51&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN51&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD49</f>
+        <v/>
+      </c>
+      <c r="F52" s="16">
+        <f>'08_Moteur'!AH49</f>
+        <v/>
+      </c>
+      <c r="G52" s="17">
+        <f>F52-'08_Moteur'!AM49</f>
+        <v/>
+      </c>
+      <c r="H52" s="64">
+        <f>'08_Moteur'!AM49</f>
+        <v/>
+      </c>
+      <c r="I52" s="17">
+        <f>E52*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J52" s="17">
-        <f>IF('08_Moteur'!AM51&lt;0,-'08_Moteur'!AM51,IF('08_Moteur'!AN51&gt;=0.95,'08_Moteur'!O51*'08_Moteur'!AO51-'08_Moteur'!U51,0))</f>
-        <v/>
-      </c>
-      <c r="K52" s="29">
-        <f>IF('08_Moteur'!AM51&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN51&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN51&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L52" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M52" s="51">
-        <f>IF(L52="Ne pas lancer",0,IF(L52="Statu quo",MAX('08_Moteur'!AI51,'08_Moteur'!M51),IF(L52="Ouvrir +1",'08_Moteur'!AI51+1,'08_Moteur'!AI51)))</f>
-        <v/>
-      </c>
-      <c r="N52" s="51">
-        <f>IF(L52="Ne pas lancer",0,'08_Moteur'!AD51)</f>
-        <v/>
+        <f>H52-I52</f>
+        <v/>
+      </c>
+      <c r="K52" s="70">
+        <f>'08_Moteur'!AN49</f>
+        <v/>
+      </c>
+      <c r="L52" s="71">
+        <f>IF(H52&lt;0,"🔴 Ne pas ouvrir",IF(K52&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K52&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M52" s="72">
+        <f>IF(H52&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K52&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K52&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N52" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O52" s="17">
-        <f>N52*'08_Moteur'!AE51*'08_Moteur'!AF51+IF(L52="Ne pas lancer",0,'08_Moteur'!AB51)*'02_Leviers'!$D$16-M52*'08_Moteur'!U51-N52*'08_Moteur'!R51*(1+'02_Leviers'!$G$11)-IF(L52="Ne pas lancer",0,'08_Moteur'!AL51)</f>
+        <f>IF(N52="Ne pas ouvrir",0,IF(N52="Ouvrir +1 classe",H52-'08_Moteur'!U49,IF(N52="Économiser 1 classe",H52+('08_Moteur'!AI49-MAX(1,'08_Moteur'!AI49-1))*'08_Moteur'!U49,H52)))</f>
         <v/>
       </c>
       <c r="P52" s="55">
-        <f>O52-'08_Moteur'!AM51</f>
+        <f>O52-H52</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="48">
-        <f>'08_Moteur'!A52</f>
+        <f>'08_Moteur'!A50</f>
         <v/>
       </c>
       <c r="B53" s="10">
-        <f>'08_Moteur'!B52</f>
+        <f>'08_Moteur'!B50</f>
         <v/>
       </c>
       <c r="C53" s="48">
-        <f>'08_Moteur'!C52</f>
+        <f>'08_Moteur'!C50</f>
         <v/>
       </c>
       <c r="D53" s="10">
-        <f>'08_Moteur'!D52</f>
+        <f>'08_Moteur'!D50</f>
         <v/>
       </c>
       <c r="E53" s="49">
-        <f>'08_Moteur'!AD52</f>
-        <v/>
-      </c>
-      <c r="F53" s="49">
-        <f>'08_Moteur'!AI52</f>
-        <v/>
-      </c>
-      <c r="G53" s="49">
-        <f>'08_Moteur'!M52</f>
-        <v/>
-      </c>
-      <c r="H53" s="71">
-        <f>'08_Moteur'!AN52</f>
-        <v/>
-      </c>
-      <c r="I53" s="72">
-        <f>IF('08_Moteur'!AM52&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN52&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN52&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD50</f>
+        <v/>
+      </c>
+      <c r="F53" s="16">
+        <f>'08_Moteur'!AH50</f>
+        <v/>
+      </c>
+      <c r="G53" s="17">
+        <f>F53-'08_Moteur'!AM50</f>
+        <v/>
+      </c>
+      <c r="H53" s="64">
+        <f>'08_Moteur'!AM50</f>
+        <v/>
+      </c>
+      <c r="I53" s="17">
+        <f>E53*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J53" s="17">
-        <f>IF('08_Moteur'!AM52&lt;0,-'08_Moteur'!AM52,IF('08_Moteur'!AN52&gt;=0.95,'08_Moteur'!O52*'08_Moteur'!AO52-'08_Moteur'!U52,0))</f>
-        <v/>
-      </c>
-      <c r="K53" s="29">
-        <f>IF('08_Moteur'!AM52&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN52&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN52&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L53" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M53" s="51">
-        <f>IF(L53="Ne pas lancer",0,IF(L53="Statu quo",MAX('08_Moteur'!AI52,'08_Moteur'!M52),IF(L53="Ouvrir +1",'08_Moteur'!AI52+1,'08_Moteur'!AI52)))</f>
-        <v/>
-      </c>
-      <c r="N53" s="51">
-        <f>IF(L53="Ne pas lancer",0,'08_Moteur'!AD52)</f>
-        <v/>
+        <f>H53-I53</f>
+        <v/>
+      </c>
+      <c r="K53" s="70">
+        <f>'08_Moteur'!AN50</f>
+        <v/>
+      </c>
+      <c r="L53" s="71">
+        <f>IF(H53&lt;0,"🔴 Ne pas ouvrir",IF(K53&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K53&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M53" s="72">
+        <f>IF(H53&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K53&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K53&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N53" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O53" s="17">
-        <f>N53*'08_Moteur'!AE52*'08_Moteur'!AF52+IF(L53="Ne pas lancer",0,'08_Moteur'!AB52)*'02_Leviers'!$D$16-M53*'08_Moteur'!U52-N53*'08_Moteur'!R52*(1+'02_Leviers'!$G$11)-IF(L53="Ne pas lancer",0,'08_Moteur'!AL52)</f>
+        <f>IF(N53="Ne pas ouvrir",0,IF(N53="Ouvrir +1 classe",H53-'08_Moteur'!U50,IF(N53="Économiser 1 classe",H53+('08_Moteur'!AI50-MAX(1,'08_Moteur'!AI50-1))*'08_Moteur'!U50,H53)))</f>
         <v/>
       </c>
       <c r="P53" s="55">
-        <f>O53-'08_Moteur'!AM52</f>
+        <f>O53-H53</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="48">
-        <f>'08_Moteur'!A53</f>
+        <f>'08_Moteur'!A51</f>
         <v/>
       </c>
       <c r="B54" s="10">
-        <f>'08_Moteur'!B53</f>
+        <f>'08_Moteur'!B51</f>
         <v/>
       </c>
       <c r="C54" s="48">
-        <f>'08_Moteur'!C53</f>
+        <f>'08_Moteur'!C51</f>
         <v/>
       </c>
       <c r="D54" s="10">
-        <f>'08_Moteur'!D53</f>
+        <f>'08_Moteur'!D51</f>
         <v/>
       </c>
       <c r="E54" s="49">
-        <f>'08_Moteur'!AD53</f>
-        <v/>
-      </c>
-      <c r="F54" s="49">
-        <f>'08_Moteur'!AI53</f>
-        <v/>
-      </c>
-      <c r="G54" s="49">
-        <f>'08_Moteur'!M53</f>
-        <v/>
-      </c>
-      <c r="H54" s="71">
-        <f>'08_Moteur'!AN53</f>
-        <v/>
-      </c>
-      <c r="I54" s="72">
-        <f>IF('08_Moteur'!AM53&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN53&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN53&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD51</f>
+        <v/>
+      </c>
+      <c r="F54" s="16">
+        <f>'08_Moteur'!AH51</f>
+        <v/>
+      </c>
+      <c r="G54" s="17">
+        <f>F54-'08_Moteur'!AM51</f>
+        <v/>
+      </c>
+      <c r="H54" s="64">
+        <f>'08_Moteur'!AM51</f>
+        <v/>
+      </c>
+      <c r="I54" s="17">
+        <f>E54*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J54" s="17">
-        <f>IF('08_Moteur'!AM53&lt;0,-'08_Moteur'!AM53,IF('08_Moteur'!AN53&gt;=0.95,'08_Moteur'!O53*'08_Moteur'!AO53-'08_Moteur'!U53,0))</f>
-        <v/>
-      </c>
-      <c r="K54" s="29">
-        <f>IF('08_Moteur'!AM53&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN53&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN53&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L54" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M54" s="51">
-        <f>IF(L54="Ne pas lancer",0,IF(L54="Statu quo",MAX('08_Moteur'!AI53,'08_Moteur'!M53),IF(L54="Ouvrir +1",'08_Moteur'!AI53+1,'08_Moteur'!AI53)))</f>
-        <v/>
-      </c>
-      <c r="N54" s="51">
-        <f>IF(L54="Ne pas lancer",0,'08_Moteur'!AD53)</f>
-        <v/>
+        <f>H54-I54</f>
+        <v/>
+      </c>
+      <c r="K54" s="70">
+        <f>'08_Moteur'!AN51</f>
+        <v/>
+      </c>
+      <c r="L54" s="71">
+        <f>IF(H54&lt;0,"🔴 Ne pas ouvrir",IF(K54&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K54&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M54" s="72">
+        <f>IF(H54&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K54&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K54&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N54" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O54" s="17">
-        <f>N54*'08_Moteur'!AE53*'08_Moteur'!AF53+IF(L54="Ne pas lancer",0,'08_Moteur'!AB53)*'02_Leviers'!$D$16-M54*'08_Moteur'!U53-N54*'08_Moteur'!R53*(1+'02_Leviers'!$G$11)-IF(L54="Ne pas lancer",0,'08_Moteur'!AL53)</f>
+        <f>IF(N54="Ne pas ouvrir",0,IF(N54="Ouvrir +1 classe",H54-'08_Moteur'!U51,IF(N54="Économiser 1 classe",H54+('08_Moteur'!AI51-MAX(1,'08_Moteur'!AI51-1))*'08_Moteur'!U51,H54)))</f>
         <v/>
       </c>
       <c r="P54" s="55">
-        <f>O54-'08_Moteur'!AM53</f>
+        <f>O54-H54</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="48">
-        <f>'08_Moteur'!A54</f>
+        <f>'08_Moteur'!A52</f>
         <v/>
       </c>
       <c r="B55" s="10">
-        <f>'08_Moteur'!B54</f>
+        <f>'08_Moteur'!B52</f>
         <v/>
       </c>
       <c r="C55" s="48">
-        <f>'08_Moteur'!C54</f>
+        <f>'08_Moteur'!C52</f>
         <v/>
       </c>
       <c r="D55" s="10">
-        <f>'08_Moteur'!D54</f>
+        <f>'08_Moteur'!D52</f>
         <v/>
       </c>
       <c r="E55" s="49">
-        <f>'08_Moteur'!AD54</f>
-        <v/>
-      </c>
-      <c r="F55" s="49">
-        <f>'08_Moteur'!AI54</f>
-        <v/>
-      </c>
-      <c r="G55" s="49">
-        <f>'08_Moteur'!M54</f>
-        <v/>
-      </c>
-      <c r="H55" s="71">
-        <f>'08_Moteur'!AN54</f>
-        <v/>
-      </c>
-      <c r="I55" s="72">
-        <f>IF('08_Moteur'!AM54&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN54&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN54&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD52</f>
+        <v/>
+      </c>
+      <c r="F55" s="16">
+        <f>'08_Moteur'!AH52</f>
+        <v/>
+      </c>
+      <c r="G55" s="17">
+        <f>F55-'08_Moteur'!AM52</f>
+        <v/>
+      </c>
+      <c r="H55" s="64">
+        <f>'08_Moteur'!AM52</f>
+        <v/>
+      </c>
+      <c r="I55" s="17">
+        <f>E55*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J55" s="17">
-        <f>IF('08_Moteur'!AM54&lt;0,-'08_Moteur'!AM54,IF('08_Moteur'!AN54&gt;=0.95,'08_Moteur'!O54*'08_Moteur'!AO54-'08_Moteur'!U54,0))</f>
-        <v/>
-      </c>
-      <c r="K55" s="29">
-        <f>IF('08_Moteur'!AM54&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN54&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN54&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L55" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M55" s="51">
-        <f>IF(L55="Ne pas lancer",0,IF(L55="Statu quo",MAX('08_Moteur'!AI54,'08_Moteur'!M54),IF(L55="Ouvrir +1",'08_Moteur'!AI54+1,'08_Moteur'!AI54)))</f>
-        <v/>
-      </c>
-      <c r="N55" s="51">
-        <f>IF(L55="Ne pas lancer",0,'08_Moteur'!AD54)</f>
-        <v/>
+        <f>H55-I55</f>
+        <v/>
+      </c>
+      <c r="K55" s="70">
+        <f>'08_Moteur'!AN52</f>
+        <v/>
+      </c>
+      <c r="L55" s="71">
+        <f>IF(H55&lt;0,"🔴 Ne pas ouvrir",IF(K55&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K55&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M55" s="72">
+        <f>IF(H55&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K55&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K55&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N55" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O55" s="17">
-        <f>N55*'08_Moteur'!AE54*'08_Moteur'!AF54+IF(L55="Ne pas lancer",0,'08_Moteur'!AB54)*'02_Leviers'!$D$16-M55*'08_Moteur'!U54-N55*'08_Moteur'!R54*(1+'02_Leviers'!$G$11)-IF(L55="Ne pas lancer",0,'08_Moteur'!AL54)</f>
+        <f>IF(N55="Ne pas ouvrir",0,IF(N55="Ouvrir +1 classe",H55-'08_Moteur'!U52,IF(N55="Économiser 1 classe",H55+('08_Moteur'!AI52-MAX(1,'08_Moteur'!AI52-1))*'08_Moteur'!U52,H55)))</f>
         <v/>
       </c>
       <c r="P55" s="55">
-        <f>O55-'08_Moteur'!AM54</f>
+        <f>O55-H55</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="48">
-        <f>'08_Moteur'!A55</f>
+        <f>'08_Moteur'!A53</f>
         <v/>
       </c>
       <c r="B56" s="10">
-        <f>'08_Moteur'!B55</f>
+        <f>'08_Moteur'!B53</f>
         <v/>
       </c>
       <c r="C56" s="48">
-        <f>'08_Moteur'!C55</f>
+        <f>'08_Moteur'!C53</f>
         <v/>
       </c>
       <c r="D56" s="10">
-        <f>'08_Moteur'!D55</f>
+        <f>'08_Moteur'!D53</f>
         <v/>
       </c>
       <c r="E56" s="49">
-        <f>'08_Moteur'!AD55</f>
-        <v/>
-      </c>
-      <c r="F56" s="49">
-        <f>'08_Moteur'!AI55</f>
-        <v/>
-      </c>
-      <c r="G56" s="49">
-        <f>'08_Moteur'!M55</f>
-        <v/>
-      </c>
-      <c r="H56" s="71">
-        <f>'08_Moteur'!AN55</f>
-        <v/>
-      </c>
-      <c r="I56" s="72">
-        <f>IF('08_Moteur'!AM55&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN55&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN55&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD53</f>
+        <v/>
+      </c>
+      <c r="F56" s="16">
+        <f>'08_Moteur'!AH53</f>
+        <v/>
+      </c>
+      <c r="G56" s="17">
+        <f>F56-'08_Moteur'!AM53</f>
+        <v/>
+      </c>
+      <c r="H56" s="64">
+        <f>'08_Moteur'!AM53</f>
+        <v/>
+      </c>
+      <c r="I56" s="17">
+        <f>E56*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J56" s="17">
-        <f>IF('08_Moteur'!AM55&lt;0,-'08_Moteur'!AM55,IF('08_Moteur'!AN55&gt;=0.95,'08_Moteur'!O55*'08_Moteur'!AO55-'08_Moteur'!U55,0))</f>
-        <v/>
-      </c>
-      <c r="K56" s="29">
-        <f>IF('08_Moteur'!AM55&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN55&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN55&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L56" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M56" s="51">
-        <f>IF(L56="Ne pas lancer",0,IF(L56="Statu quo",MAX('08_Moteur'!AI55,'08_Moteur'!M55),IF(L56="Ouvrir +1",'08_Moteur'!AI55+1,'08_Moteur'!AI55)))</f>
-        <v/>
-      </c>
-      <c r="N56" s="51">
-        <f>IF(L56="Ne pas lancer",0,'08_Moteur'!AD55)</f>
-        <v/>
+        <f>H56-I56</f>
+        <v/>
+      </c>
+      <c r="K56" s="70">
+        <f>'08_Moteur'!AN53</f>
+        <v/>
+      </c>
+      <c r="L56" s="71">
+        <f>IF(H56&lt;0,"🔴 Ne pas ouvrir",IF(K56&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K56&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M56" s="72">
+        <f>IF(H56&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K56&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K56&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N56" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O56" s="17">
-        <f>N56*'08_Moteur'!AE55*'08_Moteur'!AF55+IF(L56="Ne pas lancer",0,'08_Moteur'!AB55)*'02_Leviers'!$D$16-M56*'08_Moteur'!U55-N56*'08_Moteur'!R55*(1+'02_Leviers'!$G$11)-IF(L56="Ne pas lancer",0,'08_Moteur'!AL55)</f>
+        <f>IF(N56="Ne pas ouvrir",0,IF(N56="Ouvrir +1 classe",H56-'08_Moteur'!U53,IF(N56="Économiser 1 classe",H56+('08_Moteur'!AI53-MAX(1,'08_Moteur'!AI53-1))*'08_Moteur'!U53,H56)))</f>
         <v/>
       </c>
       <c r="P56" s="55">
-        <f>O56-'08_Moteur'!AM55</f>
+        <f>O56-H56</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="48">
-        <f>'08_Moteur'!A56</f>
+        <f>'08_Moteur'!A54</f>
         <v/>
       </c>
       <c r="B57" s="10">
-        <f>'08_Moteur'!B56</f>
+        <f>'08_Moteur'!B54</f>
         <v/>
       </c>
       <c r="C57" s="48">
-        <f>'08_Moteur'!C56</f>
+        <f>'08_Moteur'!C54</f>
         <v/>
       </c>
       <c r="D57" s="10">
-        <f>'08_Moteur'!D56</f>
+        <f>'08_Moteur'!D54</f>
         <v/>
       </c>
       <c r="E57" s="49">
-        <f>'08_Moteur'!AD56</f>
-        <v/>
-      </c>
-      <c r="F57" s="49">
-        <f>'08_Moteur'!AI56</f>
-        <v/>
-      </c>
-      <c r="G57" s="49">
-        <f>'08_Moteur'!M56</f>
-        <v/>
-      </c>
-      <c r="H57" s="71">
-        <f>'08_Moteur'!AN56</f>
-        <v/>
-      </c>
-      <c r="I57" s="72">
-        <f>IF('08_Moteur'!AM56&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN56&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN56&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD54</f>
+        <v/>
+      </c>
+      <c r="F57" s="16">
+        <f>'08_Moteur'!AH54</f>
+        <v/>
+      </c>
+      <c r="G57" s="17">
+        <f>F57-'08_Moteur'!AM54</f>
+        <v/>
+      </c>
+      <c r="H57" s="64">
+        <f>'08_Moteur'!AM54</f>
+        <v/>
+      </c>
+      <c r="I57" s="17">
+        <f>E57*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J57" s="17">
-        <f>IF('08_Moteur'!AM56&lt;0,-'08_Moteur'!AM56,IF('08_Moteur'!AN56&gt;=0.95,'08_Moteur'!O56*'08_Moteur'!AO56-'08_Moteur'!U56,0))</f>
-        <v/>
-      </c>
-      <c r="K57" s="29">
-        <f>IF('08_Moteur'!AM56&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN56&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN56&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L57" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M57" s="51">
-        <f>IF(L57="Ne pas lancer",0,IF(L57="Statu quo",MAX('08_Moteur'!AI56,'08_Moteur'!M56),IF(L57="Ouvrir +1",'08_Moteur'!AI56+1,'08_Moteur'!AI56)))</f>
-        <v/>
-      </c>
-      <c r="N57" s="51">
-        <f>IF(L57="Ne pas lancer",0,'08_Moteur'!AD56)</f>
-        <v/>
+        <f>H57-I57</f>
+        <v/>
+      </c>
+      <c r="K57" s="70">
+        <f>'08_Moteur'!AN54</f>
+        <v/>
+      </c>
+      <c r="L57" s="71">
+        <f>IF(H57&lt;0,"🔴 Ne pas ouvrir",IF(K57&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K57&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M57" s="72">
+        <f>IF(H57&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K57&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K57&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N57" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O57" s="17">
-        <f>N57*'08_Moteur'!AE56*'08_Moteur'!AF56+IF(L57="Ne pas lancer",0,'08_Moteur'!AB56)*'02_Leviers'!$D$16-M57*'08_Moteur'!U56-N57*'08_Moteur'!R56*(1+'02_Leviers'!$G$11)-IF(L57="Ne pas lancer",0,'08_Moteur'!AL56)</f>
+        <f>IF(N57="Ne pas ouvrir",0,IF(N57="Ouvrir +1 classe",H57-'08_Moteur'!U54,IF(N57="Économiser 1 classe",H57+('08_Moteur'!AI54-MAX(1,'08_Moteur'!AI54-1))*'08_Moteur'!U54,H57)))</f>
         <v/>
       </c>
       <c r="P57" s="55">
-        <f>O57-'08_Moteur'!AM56</f>
+        <f>O57-H57</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="48">
-        <f>'08_Moteur'!A57</f>
+        <f>'08_Moteur'!A55</f>
         <v/>
       </c>
       <c r="B58" s="10">
-        <f>'08_Moteur'!B57</f>
+        <f>'08_Moteur'!B55</f>
         <v/>
       </c>
       <c r="C58" s="48">
-        <f>'08_Moteur'!C57</f>
+        <f>'08_Moteur'!C55</f>
         <v/>
       </c>
       <c r="D58" s="10">
-        <f>'08_Moteur'!D57</f>
+        <f>'08_Moteur'!D55</f>
         <v/>
       </c>
       <c r="E58" s="49">
-        <f>'08_Moteur'!AD57</f>
-        <v/>
-      </c>
-      <c r="F58" s="49">
-        <f>'08_Moteur'!AI57</f>
-        <v/>
-      </c>
-      <c r="G58" s="49">
-        <f>'08_Moteur'!M57</f>
-        <v/>
-      </c>
-      <c r="H58" s="71">
-        <f>'08_Moteur'!AN57</f>
-        <v/>
-      </c>
-      <c r="I58" s="72">
-        <f>IF('08_Moteur'!AM57&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN57&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN57&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD55</f>
+        <v/>
+      </c>
+      <c r="F58" s="16">
+        <f>'08_Moteur'!AH55</f>
+        <v/>
+      </c>
+      <c r="G58" s="17">
+        <f>F58-'08_Moteur'!AM55</f>
+        <v/>
+      </c>
+      <c r="H58" s="64">
+        <f>'08_Moteur'!AM55</f>
+        <v/>
+      </c>
+      <c r="I58" s="17">
+        <f>E58*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J58" s="17">
-        <f>IF('08_Moteur'!AM57&lt;0,-'08_Moteur'!AM57,IF('08_Moteur'!AN57&gt;=0.95,'08_Moteur'!O57*'08_Moteur'!AO57-'08_Moteur'!U57,0))</f>
-        <v/>
-      </c>
-      <c r="K58" s="29">
-        <f>IF('08_Moteur'!AM57&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN57&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN57&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L58" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M58" s="51">
-        <f>IF(L58="Ne pas lancer",0,IF(L58="Statu quo",MAX('08_Moteur'!AI57,'08_Moteur'!M57),IF(L58="Ouvrir +1",'08_Moteur'!AI57+1,'08_Moteur'!AI57)))</f>
-        <v/>
-      </c>
-      <c r="N58" s="51">
-        <f>IF(L58="Ne pas lancer",0,'08_Moteur'!AD57)</f>
-        <v/>
+        <f>H58-I58</f>
+        <v/>
+      </c>
+      <c r="K58" s="70">
+        <f>'08_Moteur'!AN55</f>
+        <v/>
+      </c>
+      <c r="L58" s="71">
+        <f>IF(H58&lt;0,"🔴 Ne pas ouvrir",IF(K58&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K58&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M58" s="72">
+        <f>IF(H58&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K58&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K58&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N58" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O58" s="17">
-        <f>N58*'08_Moteur'!AE57*'08_Moteur'!AF57+IF(L58="Ne pas lancer",0,'08_Moteur'!AB57)*'02_Leviers'!$D$16-M58*'08_Moteur'!U57-N58*'08_Moteur'!R57*(1+'02_Leviers'!$G$11)-IF(L58="Ne pas lancer",0,'08_Moteur'!AL57)</f>
+        <f>IF(N58="Ne pas ouvrir",0,IF(N58="Ouvrir +1 classe",H58-'08_Moteur'!U55,IF(N58="Économiser 1 classe",H58+('08_Moteur'!AI55-MAX(1,'08_Moteur'!AI55-1))*'08_Moteur'!U55,H58)))</f>
         <v/>
       </c>
       <c r="P58" s="55">
-        <f>O58-'08_Moteur'!AM57</f>
+        <f>O58-H58</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="48">
-        <f>'08_Moteur'!A58</f>
+        <f>'08_Moteur'!A56</f>
         <v/>
       </c>
       <c r="B59" s="10">
-        <f>'08_Moteur'!B58</f>
+        <f>'08_Moteur'!B56</f>
         <v/>
       </c>
       <c r="C59" s="48">
-        <f>'08_Moteur'!C58</f>
+        <f>'08_Moteur'!C56</f>
         <v/>
       </c>
       <c r="D59" s="10">
-        <f>'08_Moteur'!D58</f>
+        <f>'08_Moteur'!D56</f>
         <v/>
       </c>
       <c r="E59" s="49">
-        <f>'08_Moteur'!AD58</f>
-        <v/>
-      </c>
-      <c r="F59" s="49">
-        <f>'08_Moteur'!AI58</f>
-        <v/>
-      </c>
-      <c r="G59" s="49">
-        <f>'08_Moteur'!M58</f>
-        <v/>
-      </c>
-      <c r="H59" s="71">
-        <f>'08_Moteur'!AN58</f>
-        <v/>
-      </c>
-      <c r="I59" s="72">
-        <f>IF('08_Moteur'!AM58&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN58&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN58&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD56</f>
+        <v/>
+      </c>
+      <c r="F59" s="16">
+        <f>'08_Moteur'!AH56</f>
+        <v/>
+      </c>
+      <c r="G59" s="17">
+        <f>F59-'08_Moteur'!AM56</f>
+        <v/>
+      </c>
+      <c r="H59" s="64">
+        <f>'08_Moteur'!AM56</f>
+        <v/>
+      </c>
+      <c r="I59" s="17">
+        <f>E59*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J59" s="17">
-        <f>IF('08_Moteur'!AM58&lt;0,-'08_Moteur'!AM58,IF('08_Moteur'!AN58&gt;=0.95,'08_Moteur'!O58*'08_Moteur'!AO58-'08_Moteur'!U58,0))</f>
-        <v/>
-      </c>
-      <c r="K59" s="29">
-        <f>IF('08_Moteur'!AM58&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN58&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN58&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L59" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M59" s="51">
-        <f>IF(L59="Ne pas lancer",0,IF(L59="Statu quo",MAX('08_Moteur'!AI58,'08_Moteur'!M58),IF(L59="Ouvrir +1",'08_Moteur'!AI58+1,'08_Moteur'!AI58)))</f>
-        <v/>
-      </c>
-      <c r="N59" s="51">
-        <f>IF(L59="Ne pas lancer",0,'08_Moteur'!AD58)</f>
-        <v/>
+        <f>H59-I59</f>
+        <v/>
+      </c>
+      <c r="K59" s="70">
+        <f>'08_Moteur'!AN56</f>
+        <v/>
+      </c>
+      <c r="L59" s="71">
+        <f>IF(H59&lt;0,"🔴 Ne pas ouvrir",IF(K59&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K59&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M59" s="72">
+        <f>IF(H59&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K59&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K59&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N59" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O59" s="17">
-        <f>N59*'08_Moteur'!AE58*'08_Moteur'!AF58+IF(L59="Ne pas lancer",0,'08_Moteur'!AB58)*'02_Leviers'!$D$16-M59*'08_Moteur'!U58-N59*'08_Moteur'!R58*(1+'02_Leviers'!$G$11)-IF(L59="Ne pas lancer",0,'08_Moteur'!AL58)</f>
+        <f>IF(N59="Ne pas ouvrir",0,IF(N59="Ouvrir +1 classe",H59-'08_Moteur'!U56,IF(N59="Économiser 1 classe",H59+('08_Moteur'!AI56-MAX(1,'08_Moteur'!AI56-1))*'08_Moteur'!U56,H59)))</f>
         <v/>
       </c>
       <c r="P59" s="55">
-        <f>O59-'08_Moteur'!AM58</f>
+        <f>O59-H59</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="48">
-        <f>'08_Moteur'!A59</f>
+        <f>'08_Moteur'!A57</f>
         <v/>
       </c>
       <c r="B60" s="10">
-        <f>'08_Moteur'!B59</f>
+        <f>'08_Moteur'!B57</f>
         <v/>
       </c>
       <c r="C60" s="48">
-        <f>'08_Moteur'!C59</f>
+        <f>'08_Moteur'!C57</f>
         <v/>
       </c>
       <c r="D60" s="10">
-        <f>'08_Moteur'!D59</f>
+        <f>'08_Moteur'!D57</f>
         <v/>
       </c>
       <c r="E60" s="49">
-        <f>'08_Moteur'!AD59</f>
-        <v/>
-      </c>
-      <c r="F60" s="49">
-        <f>'08_Moteur'!AI59</f>
-        <v/>
-      </c>
-      <c r="G60" s="49">
-        <f>'08_Moteur'!M59</f>
-        <v/>
-      </c>
-      <c r="H60" s="71">
-        <f>'08_Moteur'!AN59</f>
-        <v/>
-      </c>
-      <c r="I60" s="72">
-        <f>IF('08_Moteur'!AM59&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN59&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN59&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
+        <f>'08_Moteur'!AD57</f>
+        <v/>
+      </c>
+      <c r="F60" s="16">
+        <f>'08_Moteur'!AH57</f>
+        <v/>
+      </c>
+      <c r="G60" s="17">
+        <f>F60-'08_Moteur'!AM57</f>
+        <v/>
+      </c>
+      <c r="H60" s="64">
+        <f>'08_Moteur'!AM57</f>
+        <v/>
+      </c>
+      <c r="I60" s="17">
+        <f>E60*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
         <v/>
       </c>
       <c r="J60" s="17">
-        <f>IF('08_Moteur'!AM59&lt;0,-'08_Moteur'!AM59,IF('08_Moteur'!AN59&gt;=0.95,'08_Moteur'!O59*'08_Moteur'!AO59-'08_Moteur'!U59,0))</f>
-        <v/>
-      </c>
-      <c r="K60" s="29">
-        <f>IF('08_Moteur'!AM59&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN59&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN59&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L60" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M60" s="51">
-        <f>IF(L60="Ne pas lancer",0,IF(L60="Statu quo",MAX('08_Moteur'!AI59,'08_Moteur'!M59),IF(L60="Ouvrir +1",'08_Moteur'!AI59+1,'08_Moteur'!AI59)))</f>
-        <v/>
-      </c>
-      <c r="N60" s="51">
-        <f>IF(L60="Ne pas lancer",0,'08_Moteur'!AD59)</f>
-        <v/>
+        <f>H60-I60</f>
+        <v/>
+      </c>
+      <c r="K60" s="70">
+        <f>'08_Moteur'!AN57</f>
+        <v/>
+      </c>
+      <c r="L60" s="71">
+        <f>IF(H60&lt;0,"🔴 Ne pas ouvrir",IF(K60&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K60&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M60" s="72">
+        <f>IF(H60&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K60&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K60&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N60" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
       </c>
       <c r="O60" s="17">
-        <f>N60*'08_Moteur'!AE59*'08_Moteur'!AF59+IF(L60="Ne pas lancer",0,'08_Moteur'!AB59)*'02_Leviers'!$D$16-M60*'08_Moteur'!U59-N60*'08_Moteur'!R59*(1+'02_Leviers'!$G$11)-IF(L60="Ne pas lancer",0,'08_Moteur'!AL59)</f>
+        <f>IF(N60="Ne pas ouvrir",0,IF(N60="Ouvrir +1 classe",H60-'08_Moteur'!U57,IF(N60="Économiser 1 classe",H60+('08_Moteur'!AI57-MAX(1,'08_Moteur'!AI57-1))*'08_Moteur'!U57,H60)))</f>
         <v/>
       </c>
       <c r="P60" s="55">
-        <f>O60-'08_Moteur'!AM59</f>
+        <f>O60-H60</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="48">
+        <f>'08_Moteur'!A58</f>
+        <v/>
+      </c>
+      <c r="B61" s="10">
+        <f>'08_Moteur'!B58</f>
+        <v/>
+      </c>
+      <c r="C61" s="48">
+        <f>'08_Moteur'!C58</f>
+        <v/>
+      </c>
+      <c r="D61" s="10">
+        <f>'08_Moteur'!D58</f>
+        <v/>
+      </c>
+      <c r="E61" s="49">
+        <f>'08_Moteur'!AD58</f>
+        <v/>
+      </c>
+      <c r="F61" s="16">
+        <f>'08_Moteur'!AH58</f>
+        <v/>
+      </c>
+      <c r="G61" s="17">
+        <f>F61-'08_Moteur'!AM58</f>
+        <v/>
+      </c>
+      <c r="H61" s="64">
+        <f>'08_Moteur'!AM58</f>
+        <v/>
+      </c>
+      <c r="I61" s="17">
+        <f>E61*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="J61" s="17">
+        <f>H61-I61</f>
+        <v/>
+      </c>
+      <c r="K61" s="70">
+        <f>'08_Moteur'!AN58</f>
+        <v/>
+      </c>
+      <c r="L61" s="71">
+        <f>IF(H61&lt;0,"🔴 Ne pas ouvrir",IF(K61&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K61&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M61" s="72">
+        <f>IF(H61&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K61&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K61&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N61" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="O61" s="17">
+        <f>IF(N61="Ne pas ouvrir",0,IF(N61="Ouvrir +1 classe",H61-'08_Moteur'!U58,IF(N61="Économiser 1 classe",H61+('08_Moteur'!AI58-MAX(1,'08_Moteur'!AI58-1))*'08_Moteur'!U58,H61)))</f>
+        <v/>
+      </c>
+      <c r="P61" s="55">
+        <f>O61-H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48">
+        <f>'08_Moteur'!A59</f>
+        <v/>
+      </c>
+      <c r="B62" s="10">
+        <f>'08_Moteur'!B59</f>
+        <v/>
+      </c>
+      <c r="C62" s="48">
+        <f>'08_Moteur'!C59</f>
+        <v/>
+      </c>
+      <c r="D62" s="10">
+        <f>'08_Moteur'!D59</f>
+        <v/>
+      </c>
+      <c r="E62" s="49">
+        <f>'08_Moteur'!AD59</f>
+        <v/>
+      </c>
+      <c r="F62" s="16">
+        <f>'08_Moteur'!AH59</f>
+        <v/>
+      </c>
+      <c r="G62" s="17">
+        <f>F62-'08_Moteur'!AM59</f>
+        <v/>
+      </c>
+      <c r="H62" s="64">
+        <f>'08_Moteur'!AM59</f>
+        <v/>
+      </c>
+      <c r="I62" s="17">
+        <f>E62*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="J62" s="17">
+        <f>H62-I62</f>
+        <v/>
+      </c>
+      <c r="K62" s="70">
+        <f>'08_Moteur'!AN59</f>
+        <v/>
+      </c>
+      <c r="L62" s="71">
+        <f>IF(H62&lt;0,"🔴 Ne pas ouvrir",IF(K62&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K62&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M62" s="72">
+        <f>IF(H62&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K62&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K62&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N62" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="O62" s="17">
+        <f>IF(N62="Ne pas ouvrir",0,IF(N62="Ouvrir +1 classe",H62-'08_Moteur'!U59,IF(N62="Économiser 1 classe",H62+('08_Moteur'!AI59-MAX(1,'08_Moteur'!AI59-1))*'08_Moteur'!U59,H62)))</f>
+        <v/>
+      </c>
+      <c r="P62" s="55">
+        <f>O62-H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="48">
         <f>'08_Moteur'!A60</f>
         <v/>
       </c>
-      <c r="B61" s="10">
+      <c r="B63" s="10">
         <f>'08_Moteur'!B60</f>
         <v/>
       </c>
-      <c r="C61" s="48">
+      <c r="C63" s="48">
         <f>'08_Moteur'!C60</f>
         <v/>
       </c>
-      <c r="D61" s="10">
+      <c r="D63" s="10">
         <f>'08_Moteur'!D60</f>
         <v/>
       </c>
-      <c r="E61" s="49">
+      <c r="E63" s="49">
         <f>'08_Moteur'!AD60</f>
         <v/>
       </c>
-      <c r="F61" s="49">
-        <f>'08_Moteur'!AI60</f>
-        <v/>
-      </c>
-      <c r="G61" s="49">
-        <f>'08_Moteur'!M60</f>
-        <v/>
-      </c>
-      <c r="H61" s="71">
+      <c r="F63" s="16">
+        <f>'08_Moteur'!AH60</f>
+        <v/>
+      </c>
+      <c r="G63" s="17">
+        <f>F63-'08_Moteur'!AM60</f>
+        <v/>
+      </c>
+      <c r="H63" s="64">
+        <f>'08_Moteur'!AM60</f>
+        <v/>
+      </c>
+      <c r="I63" s="17">
+        <f>E63*('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM('08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="J63" s="17">
+        <f>H63-I63</f>
+        <v/>
+      </c>
+      <c r="K63" s="70">
         <f>'08_Moteur'!AN60</f>
         <v/>
       </c>
-      <c r="I61" s="72">
-        <f>IF('08_Moteur'!AM60&lt;0,"🔴 Ne pas lancer",IF('08_Moteur'!AN60&gt;=0.95,"🟢 Ouvrir +1 classe",IF('08_Moteur'!AN60&lt;0.55,"🟡 Surveiller / regrouper","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="J61" s="17">
-        <f>IF('08_Moteur'!AM60&lt;0,-'08_Moteur'!AM60,IF('08_Moteur'!AN60&gt;=0.95,'08_Moteur'!O60*'08_Moteur'!AO60-'08_Moteur'!U60,0))</f>
-        <v/>
-      </c>
-      <c r="K61" s="29">
-        <f>IF('08_Moteur'!AM60&lt;0,"Contribution négative → annuler / restructurer",IF('08_Moteur'!AN60&gt;=0.95,"Quasi saturé → +1 classe capte la demande",IF('08_Moteur'!AN60&lt;0.55,"Sous-rempli → surveiller / regrouper","Sain")))</f>
-        <v/>
-      </c>
-      <c r="L61" s="21" t="inlineStr">
-        <is>
-          <t>Optimal</t>
-        </is>
-      </c>
-      <c r="M61" s="51">
-        <f>IF(L61="Ne pas lancer",0,IF(L61="Statu quo",MAX('08_Moteur'!AI60,'08_Moteur'!M60),IF(L61="Ouvrir +1",'08_Moteur'!AI60+1,'08_Moteur'!AI60)))</f>
-        <v/>
-      </c>
-      <c r="N61" s="51">
-        <f>IF(L61="Ne pas lancer",0,'08_Moteur'!AD60)</f>
-        <v/>
-      </c>
-      <c r="O61" s="17">
-        <f>N61*'08_Moteur'!AE60*'08_Moteur'!AF60+IF(L61="Ne pas lancer",0,'08_Moteur'!AB60)*'02_Leviers'!$D$16-M61*'08_Moteur'!U60-N61*'08_Moteur'!R60*(1+'02_Leviers'!$G$11)-IF(L61="Ne pas lancer",0,'08_Moteur'!AL60)</f>
-        <v/>
-      </c>
-      <c r="P61" s="55">
-        <f>O61-'08_Moteur'!AM60</f>
+      <c r="L63" s="71">
+        <f>IF(H63&lt;0,"🔴 Ne pas ouvrir",IF(K63&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K63&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="M63" s="72">
+        <f>IF(H63&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K63&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K63&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
+        <v/>
+      </c>
+      <c r="N63" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="O63" s="17">
+        <f>IF(N63="Ne pas ouvrir",0,IF(N63="Ouvrir +1 classe",H63-'08_Moteur'!U60,IF(N63="Économiser 1 classe",H63+('08_Moteur'!AI60-MAX(1,'08_Moteur'!AI60-1))*'08_Moteur'!U60,H63)))</f>
+        <v/>
+      </c>
+      <c r="P63" s="55">
+        <f>O63-H63</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
+    <mergeCell ref="M3:P3"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Optimal,Statu quo,Ne pas lancer,Ouvrir +1"</formula1>
+    <dataValidation sqref="N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 N52 N53 N54 N55 N56 N57 N58 N59 N60 N61 N62 N63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Maintenir,Ne pas ouvrir,Ouvrir +1 classe,Économiser 1 classe"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6443,7 +6473,7 @@
         <f>0.01*SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60*'08_Moteur'!$AF$3:$AF$60)</f>
         <v/>
       </c>
-      <c r="D6" s="73" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>Tombe quasi intégralement en EBITDA.</t>
         </is>
@@ -6459,7 +6489,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$D$18)</f>
         <v/>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>Nul si recouvrement=100 % ; sinon réduit la perte.</t>
         </is>
@@ -6475,7 +6505,7 @@
         <f>0.01*'02_Leviers'!$D$21*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
         <v/>
       </c>
-      <c r="D8" s="73" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>Plus de leads → plus d'inscrits, net du coût.</t>
         </is>
@@ -6491,7 +6521,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=0)*'08_Moteur'!$K$3:$K$60)*IFERROR(SUM('08_Moteur'!$AM$3:$AM$60)/SUM('08_Moteur'!$AD$3:$AD$60),0)</f>
         <v/>
       </c>
-      <c r="D9" s="73" t="inlineStr">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>Rétention : + d'étudiants qui poursuivent.</t>
         </is>
@@ -6503,7 +6533,7 @@
           <t>Exposition financement alternance (€ à sécuriser) :</t>
         </is>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="73">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
@@ -6746,20 +6776,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>€ à sécuriser (exposition)</t>
         </is>
       </c>
-      <c r="C15" s="76">
+      <c r="C15" s="75">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="75">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
         <v/>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="76">
         <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
@@ -6821,7 +6851,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="78" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -6838,7 +6868,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="78" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -6855,7 +6885,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="78" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -6872,7 +6902,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="78" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -6889,7 +6919,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="78" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -6906,7 +6936,7 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="78" t="inlineStr">
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>Sécurisation &amp; recouvrement</t>
         </is>
@@ -6923,7 +6953,7 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="78" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>Objectifs (cadrage)</t>
         </is>
@@ -6940,7 +6970,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="78" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>Décisions ouvrir/fermer</t>
         </is>
@@ -6957,7 +6987,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="78" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>Allocation structure</t>
         </is>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -378,9 +378,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2324,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2335,20 +2332,21 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Simulateur &amp; conseil de décisions — logique CFO : on décide sur la MARGE DE CONTRIBUTION (col. H)</t>
+          <t>Simulateur &amp; conseil de décisions — logique CFO 360° : décider sur la CONTRIBUTION ; ouvrir/fermer redilue la structure sur TOUS</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2366,7 @@
         </is>
       </c>
       <c r="G2" s="54">
-        <f>SUM(P6:P63)</f>
+        <f>SUM(Q6:Q63)</f>
         <v/>
       </c>
       <c r="H2" s="30" t="n"/>
@@ -2383,7 +2381,7 @@
       </c>
       <c r="L2" s="30" t="n"/>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Structure / étudiant — AVANT :</t>
@@ -2395,26 +2393,26 @@
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>APRÈS (dilution) :</t>
+          <t>APRÈS :</t>
         </is>
       </c>
       <c r="G3" s="20">
-        <f>IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
+        <f>IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
         <v/>
       </c>
       <c r="H3" s="30" t="n"/>
       <c r="I3" s="19" t="inlineStr">
         <is>
-          <t>🔴 promos contribution &lt; 0 :</t>
-        </is>
-      </c>
-      <c r="K3" s="68">
-        <f>SUMPRODUCT(--('08_Moteur'!$AM$3:$AM$60&lt;0))</f>
+          <t>Effectif total APRÈS :</t>
+        </is>
+      </c>
+      <c r="K3" s="53">
+        <f>SUM(M6:M63)</f>
         <v/>
       </c>
       <c r="M3" s="12" t="inlineStr">
         <is>
-          <t>⚠ Fermer une promo n'économise PAS la structure (loyer, permanents, siège) : elle RESTE et se redilue sur les autres → on ferme UNIQUEMENT si la contribution (H) est négative.</t>
+          <t>⚠ Fermer retire des étudiants → structure/étudiant ↑ (tous absorbent +). Ouvrir en capte → structure/étudiant ↓ (tous s'enrichissent). La structure totale ne bouge pas ; l'EBITDA groupe ne varie que des contributions.</t>
         </is>
       </c>
     </row>
@@ -2463,43 +2461,49 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
+          <t>Rempl.</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>🤖 Reco</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Motif</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>Décision</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>Effectif
+après</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>Contribution
+après</t>
+        </is>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
           <t>Structure allouée
 (après, dilution)</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>Résultat tout
 compris (après)</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Rempl.</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>🤖 Reco</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>Motif</t>
-        </is>
-      </c>
-      <c r="N5" s="13" t="inlineStr">
-        <is>
-          <t>Décision</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
-        <is>
-          <t>Contribution
-après</t>
-        </is>
-      </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>Δ EBITDA</t>
         </is>
@@ -2538,37 +2542,41 @@
         <f>'08_Moteur'!AM3</f>
         <v/>
       </c>
-      <c r="I6" s="17">
-        <f>IF(N6="Ne pas ouvrir",0,E6)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="17">
-        <f>O6-I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="69">
+      <c r="I6" s="68">
         <f>'08_Moteur'!AN3</f>
         <v/>
       </c>
-      <c r="L6" s="70">
-        <f>IF(H6&lt;0,"🔴 Ne pas ouvrir",IF(K6&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K6&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M6" s="71">
-        <f>IF(H6&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K6&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K6&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="J6" s="69">
+        <f>IF(H6&lt;0,"🔴 Ne pas ouvrir",IF(I6&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I6&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K6" s="70">
+        <f>IF(H6&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I6&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I6&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M6" s="50">
+        <f>IF(L6="Ne pas ouvrir",0,IF(L6="Ouvrir +1 classe",E6+'08_Moteur'!O3,E6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="17">
+        <f>IF(L6="Ne pas ouvrir",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Économiser 1 classe",H6+('08_Moteur'!AI3-MAX(1,'08_Moteur'!AI3-1))*'08_Moteur'!U3,H6)))</f>
+        <v/>
+      </c>
       <c r="O6" s="17">
-        <f>IF(N6="Ne pas ouvrir",0,IF(N6="Ouvrir +1 classe",H6-'08_Moteur'!U3,IF(N6="Économiser 1 classe",H6+('08_Moteur'!AI3-MAX(1,'08_Moteur'!AI3-1))*'08_Moteur'!U3,H6)))</f>
-        <v/>
-      </c>
-      <c r="P6" s="54">
-        <f>O6-H6</f>
+        <f>M6*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P6" s="17">
+        <f>N6-O6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="54">
+        <f>N6-H6</f>
         <v/>
       </c>
     </row>
@@ -2605,37 +2613,41 @@
         <f>'08_Moteur'!AM4</f>
         <v/>
       </c>
-      <c r="I7" s="17">
-        <f>IF(N7="Ne pas ouvrir",0,E7)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="17">
-        <f>O7-I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="69">
+      <c r="I7" s="68">
         <f>'08_Moteur'!AN4</f>
         <v/>
       </c>
-      <c r="L7" s="70">
-        <f>IF(H7&lt;0,"🔴 Ne pas ouvrir",IF(K7&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K7&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M7" s="71">
-        <f>IF(H7&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K7&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K7&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="J7" s="69">
+        <f>IF(H7&lt;0,"🔴 Ne pas ouvrir",IF(I7&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I7&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K7" s="70">
+        <f>IF(H7&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I7&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I7&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M7" s="50">
+        <f>IF(L7="Ne pas ouvrir",0,IF(L7="Ouvrir +1 classe",E7+'08_Moteur'!O4,E7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="17">
+        <f>IF(L7="Ne pas ouvrir",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Économiser 1 classe",H7+('08_Moteur'!AI4-MAX(1,'08_Moteur'!AI4-1))*'08_Moteur'!U4,H7)))</f>
+        <v/>
+      </c>
       <c r="O7" s="17">
-        <f>IF(N7="Ne pas ouvrir",0,IF(N7="Ouvrir +1 classe",H7-'08_Moteur'!U4,IF(N7="Économiser 1 classe",H7+('08_Moteur'!AI4-MAX(1,'08_Moteur'!AI4-1))*'08_Moteur'!U4,H7)))</f>
-        <v/>
-      </c>
-      <c r="P7" s="54">
-        <f>O7-H7</f>
+        <f>M7*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="17">
+        <f>N7-O7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="54">
+        <f>N7-H7</f>
         <v/>
       </c>
     </row>
@@ -2672,37 +2684,41 @@
         <f>'08_Moteur'!AM5</f>
         <v/>
       </c>
-      <c r="I8" s="17">
-        <f>IF(N8="Ne pas ouvrir",0,E8)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="17">
-        <f>O8-I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="69">
+      <c r="I8" s="68">
         <f>'08_Moteur'!AN5</f>
         <v/>
       </c>
-      <c r="L8" s="70">
-        <f>IF(H8&lt;0,"🔴 Ne pas ouvrir",IF(K8&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K8&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M8" s="71">
-        <f>IF(H8&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K8&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K8&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="J8" s="69">
+        <f>IF(H8&lt;0,"🔴 Ne pas ouvrir",IF(I8&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I8&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K8" s="70">
+        <f>IF(H8&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I8&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I8&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M8" s="50">
+        <f>IF(L8="Ne pas ouvrir",0,IF(L8="Ouvrir +1 classe",E8+'08_Moteur'!O5,E8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="17">
+        <f>IF(L8="Ne pas ouvrir",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Économiser 1 classe",H8+('08_Moteur'!AI5-MAX(1,'08_Moteur'!AI5-1))*'08_Moteur'!U5,H8)))</f>
+        <v/>
+      </c>
       <c r="O8" s="17">
-        <f>IF(N8="Ne pas ouvrir",0,IF(N8="Ouvrir +1 classe",H8-'08_Moteur'!U5,IF(N8="Économiser 1 classe",H8+('08_Moteur'!AI5-MAX(1,'08_Moteur'!AI5-1))*'08_Moteur'!U5,H8)))</f>
-        <v/>
-      </c>
-      <c r="P8" s="54">
-        <f>O8-H8</f>
+        <f>M8*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P8" s="17">
+        <f>N8-O8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="54">
+        <f>N8-H8</f>
         <v/>
       </c>
     </row>
@@ -2739,37 +2755,41 @@
         <f>'08_Moteur'!AM6</f>
         <v/>
       </c>
-      <c r="I9" s="17">
-        <f>IF(N9="Ne pas ouvrir",0,E9)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="17">
-        <f>O9-I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="69">
+      <c r="I9" s="68">
         <f>'08_Moteur'!AN6</f>
         <v/>
       </c>
-      <c r="L9" s="70">
-        <f>IF(H9&lt;0,"🔴 Ne pas ouvrir",IF(K9&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K9&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M9" s="71">
-        <f>IF(H9&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K9&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K9&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="J9" s="69">
+        <f>IF(H9&lt;0,"🔴 Ne pas ouvrir",IF(I9&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I9&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K9" s="70">
+        <f>IF(H9&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I9&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I9&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M9" s="50">
+        <f>IF(L9="Ne pas ouvrir",0,IF(L9="Ouvrir +1 classe",E9+'08_Moteur'!O6,E9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="17">
+        <f>IF(L9="Ne pas ouvrir",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Économiser 1 classe",H9+('08_Moteur'!AI6-MAX(1,'08_Moteur'!AI6-1))*'08_Moteur'!U6,H9)))</f>
+        <v/>
+      </c>
       <c r="O9" s="17">
-        <f>IF(N9="Ne pas ouvrir",0,IF(N9="Ouvrir +1 classe",H9-'08_Moteur'!U6,IF(N9="Économiser 1 classe",H9+('08_Moteur'!AI6-MAX(1,'08_Moteur'!AI6-1))*'08_Moteur'!U6,H9)))</f>
-        <v/>
-      </c>
-      <c r="P9" s="54">
-        <f>O9-H9</f>
+        <f>M9*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P9" s="17">
+        <f>N9-O9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="54">
+        <f>N9-H9</f>
         <v/>
       </c>
     </row>
@@ -2806,37 +2826,41 @@
         <f>'08_Moteur'!AM7</f>
         <v/>
       </c>
-      <c r="I10" s="17">
-        <f>IF(N10="Ne pas ouvrir",0,E10)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="17">
-        <f>O10-I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="69">
+      <c r="I10" s="68">
         <f>'08_Moteur'!AN7</f>
         <v/>
       </c>
-      <c r="L10" s="70">
-        <f>IF(H10&lt;0,"🔴 Ne pas ouvrir",IF(K10&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K10&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M10" s="71">
-        <f>IF(H10&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K10&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K10&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
+      <c r="J10" s="69">
+        <f>IF(H10&lt;0,"🔴 Ne pas ouvrir",IF(I10&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I10&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K10" s="70">
+        <f>IF(H10&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I10&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I10&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M10" s="50">
+        <f>IF(L10="Ne pas ouvrir",0,IF(L10="Ouvrir +1 classe",E10+'08_Moteur'!O7,E10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="17">
+        <f>IF(L10="Ne pas ouvrir",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Économiser 1 classe",H10+('08_Moteur'!AI7-MAX(1,'08_Moteur'!AI7-1))*'08_Moteur'!U7,H10)))</f>
+        <v/>
+      </c>
       <c r="O10" s="17">
-        <f>IF(N10="Ne pas ouvrir",0,IF(N10="Ouvrir +1 classe",H10-'08_Moteur'!U7,IF(N10="Économiser 1 classe",H10+('08_Moteur'!AI7-MAX(1,'08_Moteur'!AI7-1))*'08_Moteur'!U7,H10)))</f>
-        <v/>
-      </c>
-      <c r="P10" s="54">
-        <f>O10-H10</f>
+        <f>M10*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="17">
+        <f>N10-O10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="54">
+        <f>N10-H10</f>
         <v/>
       </c>
     </row>
@@ -2873,37 +2897,41 @@
         <f>'08_Moteur'!AM8</f>
         <v/>
       </c>
-      <c r="I11" s="17">
-        <f>IF(N11="Ne pas ouvrir",0,E11)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="17">
-        <f>O11-I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="69">
+      <c r="I11" s="68">
         <f>'08_Moteur'!AN8</f>
         <v/>
       </c>
-      <c r="L11" s="70">
-        <f>IF(H11&lt;0,"🔴 Ne pas ouvrir",IF(K11&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K11&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M11" s="71">
-        <f>IF(H11&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K11&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K11&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="J11" s="69">
+        <f>IF(H11&lt;0,"🔴 Ne pas ouvrir",IF(I11&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I11&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K11" s="70">
+        <f>IF(H11&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I11&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I11&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M11" s="50">
+        <f>IF(L11="Ne pas ouvrir",0,IF(L11="Ouvrir +1 classe",E11+'08_Moteur'!O8,E11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="17">
+        <f>IF(L11="Ne pas ouvrir",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Économiser 1 classe",H11+('08_Moteur'!AI8-MAX(1,'08_Moteur'!AI8-1))*'08_Moteur'!U8,H11)))</f>
+        <v/>
+      </c>
       <c r="O11" s="17">
-        <f>IF(N11="Ne pas ouvrir",0,IF(N11="Ouvrir +1 classe",H11-'08_Moteur'!U8,IF(N11="Économiser 1 classe",H11+('08_Moteur'!AI8-MAX(1,'08_Moteur'!AI8-1))*'08_Moteur'!U8,H11)))</f>
-        <v/>
-      </c>
-      <c r="P11" s="54">
-        <f>O11-H11</f>
+        <f>M11*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P11" s="17">
+        <f>N11-O11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="54">
+        <f>N11-H11</f>
         <v/>
       </c>
     </row>
@@ -2940,37 +2968,41 @@
         <f>'08_Moteur'!AM9</f>
         <v/>
       </c>
-      <c r="I12" s="17">
-        <f>IF(N12="Ne pas ouvrir",0,E12)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="17">
-        <f>O12-I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="69">
+      <c r="I12" s="68">
         <f>'08_Moteur'!AN9</f>
         <v/>
       </c>
-      <c r="L12" s="70">
-        <f>IF(H12&lt;0,"🔴 Ne pas ouvrir",IF(K12&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K12&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M12" s="71">
-        <f>IF(H12&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K12&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K12&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="J12" s="69">
+        <f>IF(H12&lt;0,"🔴 Ne pas ouvrir",IF(I12&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I12&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K12" s="70">
+        <f>IF(H12&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I12&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I12&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M12" s="50">
+        <f>IF(L12="Ne pas ouvrir",0,IF(L12="Ouvrir +1 classe",E12+'08_Moteur'!O9,E12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="17">
+        <f>IF(L12="Ne pas ouvrir",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Économiser 1 classe",H12+('08_Moteur'!AI9-MAX(1,'08_Moteur'!AI9-1))*'08_Moteur'!U9,H12)))</f>
+        <v/>
+      </c>
       <c r="O12" s="17">
-        <f>IF(N12="Ne pas ouvrir",0,IF(N12="Ouvrir +1 classe",H12-'08_Moteur'!U9,IF(N12="Économiser 1 classe",H12+('08_Moteur'!AI9-MAX(1,'08_Moteur'!AI9-1))*'08_Moteur'!U9,H12)))</f>
-        <v/>
-      </c>
-      <c r="P12" s="54">
-        <f>O12-H12</f>
+        <f>M12*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="17">
+        <f>N12-O12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="54">
+        <f>N12-H12</f>
         <v/>
       </c>
     </row>
@@ -3007,37 +3039,41 @@
         <f>'08_Moteur'!AM10</f>
         <v/>
       </c>
-      <c r="I13" s="17">
-        <f>IF(N13="Ne pas ouvrir",0,E13)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="17">
-        <f>O13-I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="69">
+      <c r="I13" s="68">
         <f>'08_Moteur'!AN10</f>
         <v/>
       </c>
-      <c r="L13" s="70">
-        <f>IF(H13&lt;0,"🔴 Ne pas ouvrir",IF(K13&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K13&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M13" s="71">
-        <f>IF(H13&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K13&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K13&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
+      <c r="J13" s="69">
+        <f>IF(H13&lt;0,"🔴 Ne pas ouvrir",IF(I13&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I13&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K13" s="70">
+        <f>IF(H13&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I13&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I13&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M13" s="50">
+        <f>IF(L13="Ne pas ouvrir",0,IF(L13="Ouvrir +1 classe",E13+'08_Moteur'!O10,E13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="17">
+        <f>IF(L13="Ne pas ouvrir",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Économiser 1 classe",H13+('08_Moteur'!AI10-MAX(1,'08_Moteur'!AI10-1))*'08_Moteur'!U10,H13)))</f>
+        <v/>
+      </c>
       <c r="O13" s="17">
-        <f>IF(N13="Ne pas ouvrir",0,IF(N13="Ouvrir +1 classe",H13-'08_Moteur'!U10,IF(N13="Économiser 1 classe",H13+('08_Moteur'!AI10-MAX(1,'08_Moteur'!AI10-1))*'08_Moteur'!U10,H13)))</f>
-        <v/>
-      </c>
-      <c r="P13" s="54">
-        <f>O13-H13</f>
+        <f>M13*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="17">
+        <f>N13-O13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="54">
+        <f>N13-H13</f>
         <v/>
       </c>
     </row>
@@ -3074,37 +3110,41 @@
         <f>'08_Moteur'!AM11</f>
         <v/>
       </c>
-      <c r="I14" s="17">
-        <f>IF(N14="Ne pas ouvrir",0,E14)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="17">
-        <f>O14-I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="69">
+      <c r="I14" s="68">
         <f>'08_Moteur'!AN11</f>
         <v/>
       </c>
-      <c r="L14" s="70">
-        <f>IF(H14&lt;0,"🔴 Ne pas ouvrir",IF(K14&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K14&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M14" s="71">
-        <f>IF(H14&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K14&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K14&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="J14" s="69">
+        <f>IF(H14&lt;0,"🔴 Ne pas ouvrir",IF(I14&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I14&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K14" s="70">
+        <f>IF(H14&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I14&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I14&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M14" s="50">
+        <f>IF(L14="Ne pas ouvrir",0,IF(L14="Ouvrir +1 classe",E14+'08_Moteur'!O11,E14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="17">
+        <f>IF(L14="Ne pas ouvrir",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Économiser 1 classe",H14+('08_Moteur'!AI11-MAX(1,'08_Moteur'!AI11-1))*'08_Moteur'!U11,H14)))</f>
+        <v/>
+      </c>
       <c r="O14" s="17">
-        <f>IF(N14="Ne pas ouvrir",0,IF(N14="Ouvrir +1 classe",H14-'08_Moteur'!U11,IF(N14="Économiser 1 classe",H14+('08_Moteur'!AI11-MAX(1,'08_Moteur'!AI11-1))*'08_Moteur'!U11,H14)))</f>
-        <v/>
-      </c>
-      <c r="P14" s="54">
-        <f>O14-H14</f>
+        <f>M14*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="17">
+        <f>N14-O14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="54">
+        <f>N14-H14</f>
         <v/>
       </c>
     </row>
@@ -3141,37 +3181,41 @@
         <f>'08_Moteur'!AM12</f>
         <v/>
       </c>
-      <c r="I15" s="17">
-        <f>IF(N15="Ne pas ouvrir",0,E15)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="17">
-        <f>O15-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="69">
+      <c r="I15" s="68">
         <f>'08_Moteur'!AN12</f>
         <v/>
       </c>
-      <c r="L15" s="70">
-        <f>IF(H15&lt;0,"🔴 Ne pas ouvrir",IF(K15&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K15&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M15" s="71">
-        <f>IF(H15&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K15&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K15&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
+      <c r="J15" s="69">
+        <f>IF(H15&lt;0,"🔴 Ne pas ouvrir",IF(I15&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I15&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K15" s="70">
+        <f>IF(H15&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I15&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I15&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M15" s="50">
+        <f>IF(L15="Ne pas ouvrir",0,IF(L15="Ouvrir +1 classe",E15+'08_Moteur'!O12,E15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="17">
+        <f>IF(L15="Ne pas ouvrir",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Économiser 1 classe",H15+('08_Moteur'!AI12-MAX(1,'08_Moteur'!AI12-1))*'08_Moteur'!U12,H15)))</f>
+        <v/>
+      </c>
       <c r="O15" s="17">
-        <f>IF(N15="Ne pas ouvrir",0,IF(N15="Ouvrir +1 classe",H15-'08_Moteur'!U12,IF(N15="Économiser 1 classe",H15+('08_Moteur'!AI12-MAX(1,'08_Moteur'!AI12-1))*'08_Moteur'!U12,H15)))</f>
-        <v/>
-      </c>
-      <c r="P15" s="54">
-        <f>O15-H15</f>
+        <f>M15*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="17">
+        <f>N15-O15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="54">
+        <f>N15-H15</f>
         <v/>
       </c>
     </row>
@@ -3208,37 +3252,41 @@
         <f>'08_Moteur'!AM13</f>
         <v/>
       </c>
-      <c r="I16" s="17">
-        <f>IF(N16="Ne pas ouvrir",0,E16)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="17">
-        <f>O16-I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="69">
+      <c r="I16" s="68">
         <f>'08_Moteur'!AN13</f>
         <v/>
       </c>
-      <c r="L16" s="70">
-        <f>IF(H16&lt;0,"🔴 Ne pas ouvrir",IF(K16&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K16&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M16" s="71">
-        <f>IF(H16&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K16&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K16&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
+      <c r="J16" s="69">
+        <f>IF(H16&lt;0,"🔴 Ne pas ouvrir",IF(I16&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I16&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K16" s="70">
+        <f>IF(H16&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I16&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I16&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M16" s="50">
+        <f>IF(L16="Ne pas ouvrir",0,IF(L16="Ouvrir +1 classe",E16+'08_Moteur'!O13,E16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="17">
+        <f>IF(L16="Ne pas ouvrir",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Économiser 1 classe",H16+('08_Moteur'!AI13-MAX(1,'08_Moteur'!AI13-1))*'08_Moteur'!U13,H16)))</f>
+        <v/>
+      </c>
       <c r="O16" s="17">
-        <f>IF(N16="Ne pas ouvrir",0,IF(N16="Ouvrir +1 classe",H16-'08_Moteur'!U13,IF(N16="Économiser 1 classe",H16+('08_Moteur'!AI13-MAX(1,'08_Moteur'!AI13-1))*'08_Moteur'!U13,H16)))</f>
-        <v/>
-      </c>
-      <c r="P16" s="54">
-        <f>O16-H16</f>
+        <f>M16*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="17">
+        <f>N16-O16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="54">
+        <f>N16-H16</f>
         <v/>
       </c>
     </row>
@@ -3275,37 +3323,41 @@
         <f>'08_Moteur'!AM14</f>
         <v/>
       </c>
-      <c r="I17" s="17">
-        <f>IF(N17="Ne pas ouvrir",0,E17)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="17">
-        <f>O17-I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="69">
+      <c r="I17" s="68">
         <f>'08_Moteur'!AN14</f>
         <v/>
       </c>
-      <c r="L17" s="70">
-        <f>IF(H17&lt;0,"🔴 Ne pas ouvrir",IF(K17&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K17&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M17" s="71">
-        <f>IF(H17&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K17&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K17&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N17" s="21" t="inlineStr">
+      <c r="J17" s="69">
+        <f>IF(H17&lt;0,"🔴 Ne pas ouvrir",IF(I17&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I17&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K17" s="70">
+        <f>IF(H17&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I17&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I17&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M17" s="50">
+        <f>IF(L17="Ne pas ouvrir",0,IF(L17="Ouvrir +1 classe",E17+'08_Moteur'!O14,E17))</f>
+        <v/>
+      </c>
+      <c r="N17" s="17">
+        <f>IF(L17="Ne pas ouvrir",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Économiser 1 classe",H17+('08_Moteur'!AI14-MAX(1,'08_Moteur'!AI14-1))*'08_Moteur'!U14,H17)))</f>
+        <v/>
+      </c>
       <c r="O17" s="17">
-        <f>IF(N17="Ne pas ouvrir",0,IF(N17="Ouvrir +1 classe",H17-'08_Moteur'!U14,IF(N17="Économiser 1 classe",H17+('08_Moteur'!AI14-MAX(1,'08_Moteur'!AI14-1))*'08_Moteur'!U14,H17)))</f>
-        <v/>
-      </c>
-      <c r="P17" s="54">
-        <f>O17-H17</f>
+        <f>M17*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="17">
+        <f>N17-O17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="54">
+        <f>N17-H17</f>
         <v/>
       </c>
     </row>
@@ -3342,37 +3394,41 @@
         <f>'08_Moteur'!AM15</f>
         <v/>
       </c>
-      <c r="I18" s="17">
-        <f>IF(N18="Ne pas ouvrir",0,E18)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J18" s="17">
-        <f>O18-I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="69">
+      <c r="I18" s="68">
         <f>'08_Moteur'!AN15</f>
         <v/>
       </c>
-      <c r="L18" s="70">
-        <f>IF(H18&lt;0,"🔴 Ne pas ouvrir",IF(K18&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K18&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M18" s="71">
-        <f>IF(H18&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K18&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K18&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N18" s="21" t="inlineStr">
+      <c r="J18" s="69">
+        <f>IF(H18&lt;0,"🔴 Ne pas ouvrir",IF(I18&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I18&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K18" s="70">
+        <f>IF(H18&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I18&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I18&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M18" s="50">
+        <f>IF(L18="Ne pas ouvrir",0,IF(L18="Ouvrir +1 classe",E18+'08_Moteur'!O15,E18))</f>
+        <v/>
+      </c>
+      <c r="N18" s="17">
+        <f>IF(L18="Ne pas ouvrir",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Économiser 1 classe",H18+('08_Moteur'!AI15-MAX(1,'08_Moteur'!AI15-1))*'08_Moteur'!U15,H18)))</f>
+        <v/>
+      </c>
       <c r="O18" s="17">
-        <f>IF(N18="Ne pas ouvrir",0,IF(N18="Ouvrir +1 classe",H18-'08_Moteur'!U15,IF(N18="Économiser 1 classe",H18+('08_Moteur'!AI15-MAX(1,'08_Moteur'!AI15-1))*'08_Moteur'!U15,H18)))</f>
-        <v/>
-      </c>
-      <c r="P18" s="54">
-        <f>O18-H18</f>
+        <f>M18*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="17">
+        <f>N18-O18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="54">
+        <f>N18-H18</f>
         <v/>
       </c>
     </row>
@@ -3409,37 +3465,41 @@
         <f>'08_Moteur'!AM16</f>
         <v/>
       </c>
-      <c r="I19" s="17">
-        <f>IF(N19="Ne pas ouvrir",0,E19)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="17">
-        <f>O19-I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="69">
+      <c r="I19" s="68">
         <f>'08_Moteur'!AN16</f>
         <v/>
       </c>
-      <c r="L19" s="70">
-        <f>IF(H19&lt;0,"🔴 Ne pas ouvrir",IF(K19&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K19&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M19" s="71">
-        <f>IF(H19&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K19&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K19&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
+      <c r="J19" s="69">
+        <f>IF(H19&lt;0,"🔴 Ne pas ouvrir",IF(I19&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I19&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K19" s="70">
+        <f>IF(H19&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I19&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I19&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M19" s="50">
+        <f>IF(L19="Ne pas ouvrir",0,IF(L19="Ouvrir +1 classe",E19+'08_Moteur'!O16,E19))</f>
+        <v/>
+      </c>
+      <c r="N19" s="17">
+        <f>IF(L19="Ne pas ouvrir",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Économiser 1 classe",H19+('08_Moteur'!AI16-MAX(1,'08_Moteur'!AI16-1))*'08_Moteur'!U16,H19)))</f>
+        <v/>
+      </c>
       <c r="O19" s="17">
-        <f>IF(N19="Ne pas ouvrir",0,IF(N19="Ouvrir +1 classe",H19-'08_Moteur'!U16,IF(N19="Économiser 1 classe",H19+('08_Moteur'!AI16-MAX(1,'08_Moteur'!AI16-1))*'08_Moteur'!U16,H19)))</f>
-        <v/>
-      </c>
-      <c r="P19" s="54">
-        <f>O19-H19</f>
+        <f>M19*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P19" s="17">
+        <f>N19-O19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="54">
+        <f>N19-H19</f>
         <v/>
       </c>
     </row>
@@ -3476,37 +3536,41 @@
         <f>'08_Moteur'!AM17</f>
         <v/>
       </c>
-      <c r="I20" s="17">
-        <f>IF(N20="Ne pas ouvrir",0,E20)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="17">
-        <f>O20-I20</f>
-        <v/>
-      </c>
-      <c r="K20" s="69">
+      <c r="I20" s="68">
         <f>'08_Moteur'!AN17</f>
         <v/>
       </c>
-      <c r="L20" s="70">
-        <f>IF(H20&lt;0,"🔴 Ne pas ouvrir",IF(K20&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K20&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M20" s="71">
-        <f>IF(H20&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K20&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K20&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
+      <c r="J20" s="69">
+        <f>IF(H20&lt;0,"🔴 Ne pas ouvrir",IF(I20&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I20&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K20" s="70">
+        <f>IF(H20&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I20&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I20&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M20" s="50">
+        <f>IF(L20="Ne pas ouvrir",0,IF(L20="Ouvrir +1 classe",E20+'08_Moteur'!O17,E20))</f>
+        <v/>
+      </c>
+      <c r="N20" s="17">
+        <f>IF(L20="Ne pas ouvrir",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Économiser 1 classe",H20+('08_Moteur'!AI17-MAX(1,'08_Moteur'!AI17-1))*'08_Moteur'!U17,H20)))</f>
+        <v/>
+      </c>
       <c r="O20" s="17">
-        <f>IF(N20="Ne pas ouvrir",0,IF(N20="Ouvrir +1 classe",H20-'08_Moteur'!U17,IF(N20="Économiser 1 classe",H20+('08_Moteur'!AI17-MAX(1,'08_Moteur'!AI17-1))*'08_Moteur'!U17,H20)))</f>
-        <v/>
-      </c>
-      <c r="P20" s="54">
-        <f>O20-H20</f>
+        <f>M20*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P20" s="17">
+        <f>N20-O20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="54">
+        <f>N20-H20</f>
         <v/>
       </c>
     </row>
@@ -3543,37 +3607,41 @@
         <f>'08_Moteur'!AM18</f>
         <v/>
       </c>
-      <c r="I21" s="17">
-        <f>IF(N21="Ne pas ouvrir",0,E21)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="17">
-        <f>O21-I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="69">
+      <c r="I21" s="68">
         <f>'08_Moteur'!AN18</f>
         <v/>
       </c>
-      <c r="L21" s="70">
-        <f>IF(H21&lt;0,"🔴 Ne pas ouvrir",IF(K21&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K21&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M21" s="71">
-        <f>IF(H21&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K21&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K21&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
+      <c r="J21" s="69">
+        <f>IF(H21&lt;0,"🔴 Ne pas ouvrir",IF(I21&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I21&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K21" s="70">
+        <f>IF(H21&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I21&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I21&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M21" s="50">
+        <f>IF(L21="Ne pas ouvrir",0,IF(L21="Ouvrir +1 classe",E21+'08_Moteur'!O18,E21))</f>
+        <v/>
+      </c>
+      <c r="N21" s="17">
+        <f>IF(L21="Ne pas ouvrir",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Économiser 1 classe",H21+('08_Moteur'!AI18-MAX(1,'08_Moteur'!AI18-1))*'08_Moteur'!U18,H21)))</f>
+        <v/>
+      </c>
       <c r="O21" s="17">
-        <f>IF(N21="Ne pas ouvrir",0,IF(N21="Ouvrir +1 classe",H21-'08_Moteur'!U18,IF(N21="Économiser 1 classe",H21+('08_Moteur'!AI18-MAX(1,'08_Moteur'!AI18-1))*'08_Moteur'!U18,H21)))</f>
-        <v/>
-      </c>
-      <c r="P21" s="54">
-        <f>O21-H21</f>
+        <f>M21*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="17">
+        <f>N21-O21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="54">
+        <f>N21-H21</f>
         <v/>
       </c>
     </row>
@@ -3610,37 +3678,41 @@
         <f>'08_Moteur'!AM19</f>
         <v/>
       </c>
-      <c r="I22" s="17">
-        <f>IF(N22="Ne pas ouvrir",0,E22)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="17">
-        <f>O22-I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="69">
+      <c r="I22" s="68">
         <f>'08_Moteur'!AN19</f>
         <v/>
       </c>
-      <c r="L22" s="70">
-        <f>IF(H22&lt;0,"🔴 Ne pas ouvrir",IF(K22&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K22&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M22" s="71">
-        <f>IF(H22&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K22&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K22&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
+      <c r="J22" s="69">
+        <f>IF(H22&lt;0,"🔴 Ne pas ouvrir",IF(I22&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I22&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K22" s="70">
+        <f>IF(H22&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I22&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I22&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M22" s="50">
+        <f>IF(L22="Ne pas ouvrir",0,IF(L22="Ouvrir +1 classe",E22+'08_Moteur'!O19,E22))</f>
+        <v/>
+      </c>
+      <c r="N22" s="17">
+        <f>IF(L22="Ne pas ouvrir",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Économiser 1 classe",H22+('08_Moteur'!AI19-MAX(1,'08_Moteur'!AI19-1))*'08_Moteur'!U19,H22)))</f>
+        <v/>
+      </c>
       <c r="O22" s="17">
-        <f>IF(N22="Ne pas ouvrir",0,IF(N22="Ouvrir +1 classe",H22-'08_Moteur'!U19,IF(N22="Économiser 1 classe",H22+('08_Moteur'!AI19-MAX(1,'08_Moteur'!AI19-1))*'08_Moteur'!U19,H22)))</f>
-        <v/>
-      </c>
-      <c r="P22" s="54">
-        <f>O22-H22</f>
+        <f>M22*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="17">
+        <f>N22-O22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="54">
+        <f>N22-H22</f>
         <v/>
       </c>
     </row>
@@ -3677,37 +3749,41 @@
         <f>'08_Moteur'!AM20</f>
         <v/>
       </c>
-      <c r="I23" s="17">
-        <f>IF(N23="Ne pas ouvrir",0,E23)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="17">
-        <f>O23-I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="69">
+      <c r="I23" s="68">
         <f>'08_Moteur'!AN20</f>
         <v/>
       </c>
-      <c r="L23" s="70">
-        <f>IF(H23&lt;0,"🔴 Ne pas ouvrir",IF(K23&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K23&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M23" s="71">
-        <f>IF(H23&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K23&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K23&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N23" s="21" t="inlineStr">
+      <c r="J23" s="69">
+        <f>IF(H23&lt;0,"🔴 Ne pas ouvrir",IF(I23&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I23&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K23" s="70">
+        <f>IF(H23&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I23&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I23&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M23" s="50">
+        <f>IF(L23="Ne pas ouvrir",0,IF(L23="Ouvrir +1 classe",E23+'08_Moteur'!O20,E23))</f>
+        <v/>
+      </c>
+      <c r="N23" s="17">
+        <f>IF(L23="Ne pas ouvrir",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Économiser 1 classe",H23+('08_Moteur'!AI20-MAX(1,'08_Moteur'!AI20-1))*'08_Moteur'!U20,H23)))</f>
+        <v/>
+      </c>
       <c r="O23" s="17">
-        <f>IF(N23="Ne pas ouvrir",0,IF(N23="Ouvrir +1 classe",H23-'08_Moteur'!U20,IF(N23="Économiser 1 classe",H23+('08_Moteur'!AI20-MAX(1,'08_Moteur'!AI20-1))*'08_Moteur'!U20,H23)))</f>
-        <v/>
-      </c>
-      <c r="P23" s="54">
-        <f>O23-H23</f>
+        <f>M23*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="17">
+        <f>N23-O23</f>
+        <v/>
+      </c>
+      <c r="Q23" s="54">
+        <f>N23-H23</f>
         <v/>
       </c>
     </row>
@@ -3744,37 +3820,41 @@
         <f>'08_Moteur'!AM21</f>
         <v/>
       </c>
-      <c r="I24" s="17">
-        <f>IF(N24="Ne pas ouvrir",0,E24)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="17">
-        <f>O24-I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="69">
+      <c r="I24" s="68">
         <f>'08_Moteur'!AN21</f>
         <v/>
       </c>
-      <c r="L24" s="70">
-        <f>IF(H24&lt;0,"🔴 Ne pas ouvrir",IF(K24&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K24&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M24" s="71">
-        <f>IF(H24&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K24&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K24&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
+      <c r="J24" s="69">
+        <f>IF(H24&lt;0,"🔴 Ne pas ouvrir",IF(I24&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I24&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K24" s="70">
+        <f>IF(H24&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I24&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I24&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M24" s="50">
+        <f>IF(L24="Ne pas ouvrir",0,IF(L24="Ouvrir +1 classe",E24+'08_Moteur'!O21,E24))</f>
+        <v/>
+      </c>
+      <c r="N24" s="17">
+        <f>IF(L24="Ne pas ouvrir",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Économiser 1 classe",H24+('08_Moteur'!AI21-MAX(1,'08_Moteur'!AI21-1))*'08_Moteur'!U21,H24)))</f>
+        <v/>
+      </c>
       <c r="O24" s="17">
-        <f>IF(N24="Ne pas ouvrir",0,IF(N24="Ouvrir +1 classe",H24-'08_Moteur'!U21,IF(N24="Économiser 1 classe",H24+('08_Moteur'!AI21-MAX(1,'08_Moteur'!AI21-1))*'08_Moteur'!U21,H24)))</f>
-        <v/>
-      </c>
-      <c r="P24" s="54">
-        <f>O24-H24</f>
+        <f>M24*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="17">
+        <f>N24-O24</f>
+        <v/>
+      </c>
+      <c r="Q24" s="54">
+        <f>N24-H24</f>
         <v/>
       </c>
     </row>
@@ -3811,37 +3891,41 @@
         <f>'08_Moteur'!AM22</f>
         <v/>
       </c>
-      <c r="I25" s="17">
-        <f>IF(N25="Ne pas ouvrir",0,E25)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="17">
-        <f>O25-I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="69">
+      <c r="I25" s="68">
         <f>'08_Moteur'!AN22</f>
         <v/>
       </c>
-      <c r="L25" s="70">
-        <f>IF(H25&lt;0,"🔴 Ne pas ouvrir",IF(K25&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K25&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M25" s="71">
-        <f>IF(H25&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K25&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K25&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
+      <c r="J25" s="69">
+        <f>IF(H25&lt;0,"🔴 Ne pas ouvrir",IF(I25&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I25&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K25" s="70">
+        <f>IF(H25&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I25&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I25&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M25" s="50">
+        <f>IF(L25="Ne pas ouvrir",0,IF(L25="Ouvrir +1 classe",E25+'08_Moteur'!O22,E25))</f>
+        <v/>
+      </c>
+      <c r="N25" s="17">
+        <f>IF(L25="Ne pas ouvrir",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Économiser 1 classe",H25+('08_Moteur'!AI22-MAX(1,'08_Moteur'!AI22-1))*'08_Moteur'!U22,H25)))</f>
+        <v/>
+      </c>
       <c r="O25" s="17">
-        <f>IF(N25="Ne pas ouvrir",0,IF(N25="Ouvrir +1 classe",H25-'08_Moteur'!U22,IF(N25="Économiser 1 classe",H25+('08_Moteur'!AI22-MAX(1,'08_Moteur'!AI22-1))*'08_Moteur'!U22,H25)))</f>
-        <v/>
-      </c>
-      <c r="P25" s="54">
-        <f>O25-H25</f>
+        <f>M25*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="17">
+        <f>N25-O25</f>
+        <v/>
+      </c>
+      <c r="Q25" s="54">
+        <f>N25-H25</f>
         <v/>
       </c>
     </row>
@@ -3878,37 +3962,41 @@
         <f>'08_Moteur'!AM23</f>
         <v/>
       </c>
-      <c r="I26" s="17">
-        <f>IF(N26="Ne pas ouvrir",0,E26)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="17">
-        <f>O26-I26</f>
-        <v/>
-      </c>
-      <c r="K26" s="69">
+      <c r="I26" s="68">
         <f>'08_Moteur'!AN23</f>
         <v/>
       </c>
-      <c r="L26" s="70">
-        <f>IF(H26&lt;0,"🔴 Ne pas ouvrir",IF(K26&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K26&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M26" s="71">
-        <f>IF(H26&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K26&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K26&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
+      <c r="J26" s="69">
+        <f>IF(H26&lt;0,"🔴 Ne pas ouvrir",IF(I26&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I26&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K26" s="70">
+        <f>IF(H26&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I26&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I26&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M26" s="50">
+        <f>IF(L26="Ne pas ouvrir",0,IF(L26="Ouvrir +1 classe",E26+'08_Moteur'!O23,E26))</f>
+        <v/>
+      </c>
+      <c r="N26" s="17">
+        <f>IF(L26="Ne pas ouvrir",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Économiser 1 classe",H26+('08_Moteur'!AI23-MAX(1,'08_Moteur'!AI23-1))*'08_Moteur'!U23,H26)))</f>
+        <v/>
+      </c>
       <c r="O26" s="17">
-        <f>IF(N26="Ne pas ouvrir",0,IF(N26="Ouvrir +1 classe",H26-'08_Moteur'!U23,IF(N26="Économiser 1 classe",H26+('08_Moteur'!AI23-MAX(1,'08_Moteur'!AI23-1))*'08_Moteur'!U23,H26)))</f>
-        <v/>
-      </c>
-      <c r="P26" s="54">
-        <f>O26-H26</f>
+        <f>M26*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="17">
+        <f>N26-O26</f>
+        <v/>
+      </c>
+      <c r="Q26" s="54">
+        <f>N26-H26</f>
         <v/>
       </c>
     </row>
@@ -3945,37 +4033,41 @@
         <f>'08_Moteur'!AM24</f>
         <v/>
       </c>
-      <c r="I27" s="17">
-        <f>IF(N27="Ne pas ouvrir",0,E27)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="17">
-        <f>O27-I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="69">
+      <c r="I27" s="68">
         <f>'08_Moteur'!AN24</f>
         <v/>
       </c>
-      <c r="L27" s="70">
-        <f>IF(H27&lt;0,"🔴 Ne pas ouvrir",IF(K27&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K27&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M27" s="71">
-        <f>IF(H27&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K27&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K27&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N27" s="21" t="inlineStr">
+      <c r="J27" s="69">
+        <f>IF(H27&lt;0,"🔴 Ne pas ouvrir",IF(I27&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I27&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K27" s="70">
+        <f>IF(H27&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I27&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I27&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M27" s="50">
+        <f>IF(L27="Ne pas ouvrir",0,IF(L27="Ouvrir +1 classe",E27+'08_Moteur'!O24,E27))</f>
+        <v/>
+      </c>
+      <c r="N27" s="17">
+        <f>IF(L27="Ne pas ouvrir",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Économiser 1 classe",H27+('08_Moteur'!AI24-MAX(1,'08_Moteur'!AI24-1))*'08_Moteur'!U24,H27)))</f>
+        <v/>
+      </c>
       <c r="O27" s="17">
-        <f>IF(N27="Ne pas ouvrir",0,IF(N27="Ouvrir +1 classe",H27-'08_Moteur'!U24,IF(N27="Économiser 1 classe",H27+('08_Moteur'!AI24-MAX(1,'08_Moteur'!AI24-1))*'08_Moteur'!U24,H27)))</f>
-        <v/>
-      </c>
-      <c r="P27" s="54">
-        <f>O27-H27</f>
+        <f>M27*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="17">
+        <f>N27-O27</f>
+        <v/>
+      </c>
+      <c r="Q27" s="54">
+        <f>N27-H27</f>
         <v/>
       </c>
     </row>
@@ -4012,37 +4104,41 @@
         <f>'08_Moteur'!AM25</f>
         <v/>
       </c>
-      <c r="I28" s="17">
-        <f>IF(N28="Ne pas ouvrir",0,E28)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="17">
-        <f>O28-I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="69">
+      <c r="I28" s="68">
         <f>'08_Moteur'!AN25</f>
         <v/>
       </c>
-      <c r="L28" s="70">
-        <f>IF(H28&lt;0,"🔴 Ne pas ouvrir",IF(K28&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K28&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M28" s="71">
-        <f>IF(H28&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K28&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K28&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N28" s="21" t="inlineStr">
+      <c r="J28" s="69">
+        <f>IF(H28&lt;0,"🔴 Ne pas ouvrir",IF(I28&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I28&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K28" s="70">
+        <f>IF(H28&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I28&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I28&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M28" s="50">
+        <f>IF(L28="Ne pas ouvrir",0,IF(L28="Ouvrir +1 classe",E28+'08_Moteur'!O25,E28))</f>
+        <v/>
+      </c>
+      <c r="N28" s="17">
+        <f>IF(L28="Ne pas ouvrir",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Économiser 1 classe",H28+('08_Moteur'!AI25-MAX(1,'08_Moteur'!AI25-1))*'08_Moteur'!U25,H28)))</f>
+        <v/>
+      </c>
       <c r="O28" s="17">
-        <f>IF(N28="Ne pas ouvrir",0,IF(N28="Ouvrir +1 classe",H28-'08_Moteur'!U25,IF(N28="Économiser 1 classe",H28+('08_Moteur'!AI25-MAX(1,'08_Moteur'!AI25-1))*'08_Moteur'!U25,H28)))</f>
-        <v/>
-      </c>
-      <c r="P28" s="54">
-        <f>O28-H28</f>
+        <f>M28*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P28" s="17">
+        <f>N28-O28</f>
+        <v/>
+      </c>
+      <c r="Q28" s="54">
+        <f>N28-H28</f>
         <v/>
       </c>
     </row>
@@ -4079,37 +4175,41 @@
         <f>'08_Moteur'!AM26</f>
         <v/>
       </c>
-      <c r="I29" s="17">
-        <f>IF(N29="Ne pas ouvrir",0,E29)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="17">
-        <f>O29-I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="69">
+      <c r="I29" s="68">
         <f>'08_Moteur'!AN26</f>
         <v/>
       </c>
-      <c r="L29" s="70">
-        <f>IF(H29&lt;0,"🔴 Ne pas ouvrir",IF(K29&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K29&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M29" s="71">
-        <f>IF(H29&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K29&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K29&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N29" s="21" t="inlineStr">
+      <c r="J29" s="69">
+        <f>IF(H29&lt;0,"🔴 Ne pas ouvrir",IF(I29&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I29&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K29" s="70">
+        <f>IF(H29&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I29&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I29&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M29" s="50">
+        <f>IF(L29="Ne pas ouvrir",0,IF(L29="Ouvrir +1 classe",E29+'08_Moteur'!O26,E29))</f>
+        <v/>
+      </c>
+      <c r="N29" s="17">
+        <f>IF(L29="Ne pas ouvrir",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Économiser 1 classe",H29+('08_Moteur'!AI26-MAX(1,'08_Moteur'!AI26-1))*'08_Moteur'!U26,H29)))</f>
+        <v/>
+      </c>
       <c r="O29" s="17">
-        <f>IF(N29="Ne pas ouvrir",0,IF(N29="Ouvrir +1 classe",H29-'08_Moteur'!U26,IF(N29="Économiser 1 classe",H29+('08_Moteur'!AI26-MAX(1,'08_Moteur'!AI26-1))*'08_Moteur'!U26,H29)))</f>
-        <v/>
-      </c>
-      <c r="P29" s="54">
-        <f>O29-H29</f>
+        <f>M29*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="17">
+        <f>N29-O29</f>
+        <v/>
+      </c>
+      <c r="Q29" s="54">
+        <f>N29-H29</f>
         <v/>
       </c>
     </row>
@@ -4146,37 +4246,41 @@
         <f>'08_Moteur'!AM27</f>
         <v/>
       </c>
-      <c r="I30" s="17">
-        <f>IF(N30="Ne pas ouvrir",0,E30)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J30" s="17">
-        <f>O30-I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="69">
+      <c r="I30" s="68">
         <f>'08_Moteur'!AN27</f>
         <v/>
       </c>
-      <c r="L30" s="70">
-        <f>IF(H30&lt;0,"🔴 Ne pas ouvrir",IF(K30&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K30&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M30" s="71">
-        <f>IF(H30&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K30&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K30&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N30" s="21" t="inlineStr">
+      <c r="J30" s="69">
+        <f>IF(H30&lt;0,"🔴 Ne pas ouvrir",IF(I30&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I30&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K30" s="70">
+        <f>IF(H30&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I30&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I30&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M30" s="50">
+        <f>IF(L30="Ne pas ouvrir",0,IF(L30="Ouvrir +1 classe",E30+'08_Moteur'!O27,E30))</f>
+        <v/>
+      </c>
+      <c r="N30" s="17">
+        <f>IF(L30="Ne pas ouvrir",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Économiser 1 classe",H30+('08_Moteur'!AI27-MAX(1,'08_Moteur'!AI27-1))*'08_Moteur'!U27,H30)))</f>
+        <v/>
+      </c>
       <c r="O30" s="17">
-        <f>IF(N30="Ne pas ouvrir",0,IF(N30="Ouvrir +1 classe",H30-'08_Moteur'!U27,IF(N30="Économiser 1 classe",H30+('08_Moteur'!AI27-MAX(1,'08_Moteur'!AI27-1))*'08_Moteur'!U27,H30)))</f>
-        <v/>
-      </c>
-      <c r="P30" s="54">
-        <f>O30-H30</f>
+        <f>M30*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="17">
+        <f>N30-O30</f>
+        <v/>
+      </c>
+      <c r="Q30" s="54">
+        <f>N30-H30</f>
         <v/>
       </c>
     </row>
@@ -4213,37 +4317,41 @@
         <f>'08_Moteur'!AM28</f>
         <v/>
       </c>
-      <c r="I31" s="17">
-        <f>IF(N31="Ne pas ouvrir",0,E31)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J31" s="17">
-        <f>O31-I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="69">
+      <c r="I31" s="68">
         <f>'08_Moteur'!AN28</f>
         <v/>
       </c>
-      <c r="L31" s="70">
-        <f>IF(H31&lt;0,"🔴 Ne pas ouvrir",IF(K31&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K31&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M31" s="71">
-        <f>IF(H31&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K31&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K31&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N31" s="21" t="inlineStr">
+      <c r="J31" s="69">
+        <f>IF(H31&lt;0,"🔴 Ne pas ouvrir",IF(I31&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I31&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K31" s="70">
+        <f>IF(H31&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I31&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I31&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M31" s="50">
+        <f>IF(L31="Ne pas ouvrir",0,IF(L31="Ouvrir +1 classe",E31+'08_Moteur'!O28,E31))</f>
+        <v/>
+      </c>
+      <c r="N31" s="17">
+        <f>IF(L31="Ne pas ouvrir",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Économiser 1 classe",H31+('08_Moteur'!AI28-MAX(1,'08_Moteur'!AI28-1))*'08_Moteur'!U28,H31)))</f>
+        <v/>
+      </c>
       <c r="O31" s="17">
-        <f>IF(N31="Ne pas ouvrir",0,IF(N31="Ouvrir +1 classe",H31-'08_Moteur'!U28,IF(N31="Économiser 1 classe",H31+('08_Moteur'!AI28-MAX(1,'08_Moteur'!AI28-1))*'08_Moteur'!U28,H31)))</f>
-        <v/>
-      </c>
-      <c r="P31" s="54">
-        <f>O31-H31</f>
+        <f>M31*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="17">
+        <f>N31-O31</f>
+        <v/>
+      </c>
+      <c r="Q31" s="54">
+        <f>N31-H31</f>
         <v/>
       </c>
     </row>
@@ -4280,37 +4388,41 @@
         <f>'08_Moteur'!AM29</f>
         <v/>
       </c>
-      <c r="I32" s="17">
-        <f>IF(N32="Ne pas ouvrir",0,E32)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="17">
-        <f>O32-I32</f>
-        <v/>
-      </c>
-      <c r="K32" s="69">
+      <c r="I32" s="68">
         <f>'08_Moteur'!AN29</f>
         <v/>
       </c>
-      <c r="L32" s="70">
-        <f>IF(H32&lt;0,"🔴 Ne pas ouvrir",IF(K32&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K32&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M32" s="71">
-        <f>IF(H32&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K32&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K32&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N32" s="21" t="inlineStr">
+      <c r="J32" s="69">
+        <f>IF(H32&lt;0,"🔴 Ne pas ouvrir",IF(I32&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I32&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K32" s="70">
+        <f>IF(H32&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I32&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I32&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M32" s="50">
+        <f>IF(L32="Ne pas ouvrir",0,IF(L32="Ouvrir +1 classe",E32+'08_Moteur'!O29,E32))</f>
+        <v/>
+      </c>
+      <c r="N32" s="17">
+        <f>IF(L32="Ne pas ouvrir",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Économiser 1 classe",H32+('08_Moteur'!AI29-MAX(1,'08_Moteur'!AI29-1))*'08_Moteur'!U29,H32)))</f>
+        <v/>
+      </c>
       <c r="O32" s="17">
-        <f>IF(N32="Ne pas ouvrir",0,IF(N32="Ouvrir +1 classe",H32-'08_Moteur'!U29,IF(N32="Économiser 1 classe",H32+('08_Moteur'!AI29-MAX(1,'08_Moteur'!AI29-1))*'08_Moteur'!U29,H32)))</f>
-        <v/>
-      </c>
-      <c r="P32" s="54">
-        <f>O32-H32</f>
+        <f>M32*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P32" s="17">
+        <f>N32-O32</f>
+        <v/>
+      </c>
+      <c r="Q32" s="54">
+        <f>N32-H32</f>
         <v/>
       </c>
     </row>
@@ -4347,37 +4459,41 @@
         <f>'08_Moteur'!AM30</f>
         <v/>
       </c>
-      <c r="I33" s="17">
-        <f>IF(N33="Ne pas ouvrir",0,E33)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J33" s="17">
-        <f>O33-I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="69">
+      <c r="I33" s="68">
         <f>'08_Moteur'!AN30</f>
         <v/>
       </c>
-      <c r="L33" s="70">
-        <f>IF(H33&lt;0,"🔴 Ne pas ouvrir",IF(K33&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K33&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M33" s="71">
-        <f>IF(H33&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K33&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K33&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N33" s="21" t="inlineStr">
+      <c r="J33" s="69">
+        <f>IF(H33&lt;0,"🔴 Ne pas ouvrir",IF(I33&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I33&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K33" s="70">
+        <f>IF(H33&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I33&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I33&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M33" s="50">
+        <f>IF(L33="Ne pas ouvrir",0,IF(L33="Ouvrir +1 classe",E33+'08_Moteur'!O30,E33))</f>
+        <v/>
+      </c>
+      <c r="N33" s="17">
+        <f>IF(L33="Ne pas ouvrir",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Économiser 1 classe",H33+('08_Moteur'!AI30-MAX(1,'08_Moteur'!AI30-1))*'08_Moteur'!U30,H33)))</f>
+        <v/>
+      </c>
       <c r="O33" s="17">
-        <f>IF(N33="Ne pas ouvrir",0,IF(N33="Ouvrir +1 classe",H33-'08_Moteur'!U30,IF(N33="Économiser 1 classe",H33+('08_Moteur'!AI30-MAX(1,'08_Moteur'!AI30-1))*'08_Moteur'!U30,H33)))</f>
-        <v/>
-      </c>
-      <c r="P33" s="54">
-        <f>O33-H33</f>
+        <f>M33*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P33" s="17">
+        <f>N33-O33</f>
+        <v/>
+      </c>
+      <c r="Q33" s="54">
+        <f>N33-H33</f>
         <v/>
       </c>
     </row>
@@ -4414,37 +4530,41 @@
         <f>'08_Moteur'!AM31</f>
         <v/>
       </c>
-      <c r="I34" s="17">
-        <f>IF(N34="Ne pas ouvrir",0,E34)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J34" s="17">
-        <f>O34-I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="69">
+      <c r="I34" s="68">
         <f>'08_Moteur'!AN31</f>
         <v/>
       </c>
-      <c r="L34" s="70">
-        <f>IF(H34&lt;0,"🔴 Ne pas ouvrir",IF(K34&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K34&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M34" s="71">
-        <f>IF(H34&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K34&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K34&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N34" s="21" t="inlineStr">
+      <c r="J34" s="69">
+        <f>IF(H34&lt;0,"🔴 Ne pas ouvrir",IF(I34&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I34&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K34" s="70">
+        <f>IF(H34&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I34&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I34&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M34" s="50">
+        <f>IF(L34="Ne pas ouvrir",0,IF(L34="Ouvrir +1 classe",E34+'08_Moteur'!O31,E34))</f>
+        <v/>
+      </c>
+      <c r="N34" s="17">
+        <f>IF(L34="Ne pas ouvrir",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Économiser 1 classe",H34+('08_Moteur'!AI31-MAX(1,'08_Moteur'!AI31-1))*'08_Moteur'!U31,H34)))</f>
+        <v/>
+      </c>
       <c r="O34" s="17">
-        <f>IF(N34="Ne pas ouvrir",0,IF(N34="Ouvrir +1 classe",H34-'08_Moteur'!U31,IF(N34="Économiser 1 classe",H34+('08_Moteur'!AI31-MAX(1,'08_Moteur'!AI31-1))*'08_Moteur'!U31,H34)))</f>
-        <v/>
-      </c>
-      <c r="P34" s="54">
-        <f>O34-H34</f>
+        <f>M34*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P34" s="17">
+        <f>N34-O34</f>
+        <v/>
+      </c>
+      <c r="Q34" s="54">
+        <f>N34-H34</f>
         <v/>
       </c>
     </row>
@@ -4481,37 +4601,41 @@
         <f>'08_Moteur'!AM32</f>
         <v/>
       </c>
-      <c r="I35" s="17">
-        <f>IF(N35="Ne pas ouvrir",0,E35)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J35" s="17">
-        <f>O35-I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="69">
+      <c r="I35" s="68">
         <f>'08_Moteur'!AN32</f>
         <v/>
       </c>
-      <c r="L35" s="70">
-        <f>IF(H35&lt;0,"🔴 Ne pas ouvrir",IF(K35&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K35&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M35" s="71">
-        <f>IF(H35&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K35&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K35&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N35" s="21" t="inlineStr">
+      <c r="J35" s="69">
+        <f>IF(H35&lt;0,"🔴 Ne pas ouvrir",IF(I35&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I35&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K35" s="70">
+        <f>IF(H35&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I35&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I35&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M35" s="50">
+        <f>IF(L35="Ne pas ouvrir",0,IF(L35="Ouvrir +1 classe",E35+'08_Moteur'!O32,E35))</f>
+        <v/>
+      </c>
+      <c r="N35" s="17">
+        <f>IF(L35="Ne pas ouvrir",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Économiser 1 classe",H35+('08_Moteur'!AI32-MAX(1,'08_Moteur'!AI32-1))*'08_Moteur'!U32,H35)))</f>
+        <v/>
+      </c>
       <c r="O35" s="17">
-        <f>IF(N35="Ne pas ouvrir",0,IF(N35="Ouvrir +1 classe",H35-'08_Moteur'!U32,IF(N35="Économiser 1 classe",H35+('08_Moteur'!AI32-MAX(1,'08_Moteur'!AI32-1))*'08_Moteur'!U32,H35)))</f>
-        <v/>
-      </c>
-      <c r="P35" s="54">
-        <f>O35-H35</f>
+        <f>M35*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P35" s="17">
+        <f>N35-O35</f>
+        <v/>
+      </c>
+      <c r="Q35" s="54">
+        <f>N35-H35</f>
         <v/>
       </c>
     </row>
@@ -4548,37 +4672,41 @@
         <f>'08_Moteur'!AM33</f>
         <v/>
       </c>
-      <c r="I36" s="17">
-        <f>IF(N36="Ne pas ouvrir",0,E36)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J36" s="17">
-        <f>O36-I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="69">
+      <c r="I36" s="68">
         <f>'08_Moteur'!AN33</f>
         <v/>
       </c>
-      <c r="L36" s="70">
-        <f>IF(H36&lt;0,"🔴 Ne pas ouvrir",IF(K36&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K36&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M36" s="71">
-        <f>IF(H36&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K36&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K36&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N36" s="21" t="inlineStr">
+      <c r="J36" s="69">
+        <f>IF(H36&lt;0,"🔴 Ne pas ouvrir",IF(I36&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I36&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K36" s="70">
+        <f>IF(H36&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I36&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I36&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M36" s="50">
+        <f>IF(L36="Ne pas ouvrir",0,IF(L36="Ouvrir +1 classe",E36+'08_Moteur'!O33,E36))</f>
+        <v/>
+      </c>
+      <c r="N36" s="17">
+        <f>IF(L36="Ne pas ouvrir",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Économiser 1 classe",H36+('08_Moteur'!AI33-MAX(1,'08_Moteur'!AI33-1))*'08_Moteur'!U33,H36)))</f>
+        <v/>
+      </c>
       <c r="O36" s="17">
-        <f>IF(N36="Ne pas ouvrir",0,IF(N36="Ouvrir +1 classe",H36-'08_Moteur'!U33,IF(N36="Économiser 1 classe",H36+('08_Moteur'!AI33-MAX(1,'08_Moteur'!AI33-1))*'08_Moteur'!U33,H36)))</f>
-        <v/>
-      </c>
-      <c r="P36" s="54">
-        <f>O36-H36</f>
+        <f>M36*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P36" s="17">
+        <f>N36-O36</f>
+        <v/>
+      </c>
+      <c r="Q36" s="54">
+        <f>N36-H36</f>
         <v/>
       </c>
     </row>
@@ -4615,37 +4743,41 @@
         <f>'08_Moteur'!AM34</f>
         <v/>
       </c>
-      <c r="I37" s="17">
-        <f>IF(N37="Ne pas ouvrir",0,E37)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J37" s="17">
-        <f>O37-I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="69">
+      <c r="I37" s="68">
         <f>'08_Moteur'!AN34</f>
         <v/>
       </c>
-      <c r="L37" s="70">
-        <f>IF(H37&lt;0,"🔴 Ne pas ouvrir",IF(K37&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K37&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M37" s="71">
-        <f>IF(H37&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K37&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K37&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N37" s="21" t="inlineStr">
+      <c r="J37" s="69">
+        <f>IF(H37&lt;0,"🔴 Ne pas ouvrir",IF(I37&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I37&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K37" s="70">
+        <f>IF(H37&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I37&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I37&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M37" s="50">
+        <f>IF(L37="Ne pas ouvrir",0,IF(L37="Ouvrir +1 classe",E37+'08_Moteur'!O34,E37))</f>
+        <v/>
+      </c>
+      <c r="N37" s="17">
+        <f>IF(L37="Ne pas ouvrir",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Économiser 1 classe",H37+('08_Moteur'!AI34-MAX(1,'08_Moteur'!AI34-1))*'08_Moteur'!U34,H37)))</f>
+        <v/>
+      </c>
       <c r="O37" s="17">
-        <f>IF(N37="Ne pas ouvrir",0,IF(N37="Ouvrir +1 classe",H37-'08_Moteur'!U34,IF(N37="Économiser 1 classe",H37+('08_Moteur'!AI34-MAX(1,'08_Moteur'!AI34-1))*'08_Moteur'!U34,H37)))</f>
-        <v/>
-      </c>
-      <c r="P37" s="54">
-        <f>O37-H37</f>
+        <f>M37*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P37" s="17">
+        <f>N37-O37</f>
+        <v/>
+      </c>
+      <c r="Q37" s="54">
+        <f>N37-H37</f>
         <v/>
       </c>
     </row>
@@ -4682,37 +4814,41 @@
         <f>'08_Moteur'!AM35</f>
         <v/>
       </c>
-      <c r="I38" s="17">
-        <f>IF(N38="Ne pas ouvrir",0,E38)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J38" s="17">
-        <f>O38-I38</f>
-        <v/>
-      </c>
-      <c r="K38" s="69">
+      <c r="I38" s="68">
         <f>'08_Moteur'!AN35</f>
         <v/>
       </c>
-      <c r="L38" s="70">
-        <f>IF(H38&lt;0,"🔴 Ne pas ouvrir",IF(K38&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K38&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M38" s="71">
-        <f>IF(H38&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K38&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K38&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N38" s="21" t="inlineStr">
+      <c r="J38" s="69">
+        <f>IF(H38&lt;0,"🔴 Ne pas ouvrir",IF(I38&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I38&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K38" s="70">
+        <f>IF(H38&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I38&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I38&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M38" s="50">
+        <f>IF(L38="Ne pas ouvrir",0,IF(L38="Ouvrir +1 classe",E38+'08_Moteur'!O35,E38))</f>
+        <v/>
+      </c>
+      <c r="N38" s="17">
+        <f>IF(L38="Ne pas ouvrir",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Économiser 1 classe",H38+('08_Moteur'!AI35-MAX(1,'08_Moteur'!AI35-1))*'08_Moteur'!U35,H38)))</f>
+        <v/>
+      </c>
       <c r="O38" s="17">
-        <f>IF(N38="Ne pas ouvrir",0,IF(N38="Ouvrir +1 classe",H38-'08_Moteur'!U35,IF(N38="Économiser 1 classe",H38+('08_Moteur'!AI35-MAX(1,'08_Moteur'!AI35-1))*'08_Moteur'!U35,H38)))</f>
-        <v/>
-      </c>
-      <c r="P38" s="54">
-        <f>O38-H38</f>
+        <f>M38*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P38" s="17">
+        <f>N38-O38</f>
+        <v/>
+      </c>
+      <c r="Q38" s="54">
+        <f>N38-H38</f>
         <v/>
       </c>
     </row>
@@ -4749,37 +4885,41 @@
         <f>'08_Moteur'!AM36</f>
         <v/>
       </c>
-      <c r="I39" s="17">
-        <f>IF(N39="Ne pas ouvrir",0,E39)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J39" s="17">
-        <f>O39-I39</f>
-        <v/>
-      </c>
-      <c r="K39" s="69">
+      <c r="I39" s="68">
         <f>'08_Moteur'!AN36</f>
         <v/>
       </c>
-      <c r="L39" s="70">
-        <f>IF(H39&lt;0,"🔴 Ne pas ouvrir",IF(K39&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K39&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M39" s="71">
-        <f>IF(H39&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K39&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K39&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N39" s="21" t="inlineStr">
+      <c r="J39" s="69">
+        <f>IF(H39&lt;0,"🔴 Ne pas ouvrir",IF(I39&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I39&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K39" s="70">
+        <f>IF(H39&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I39&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I39&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M39" s="50">
+        <f>IF(L39="Ne pas ouvrir",0,IF(L39="Ouvrir +1 classe",E39+'08_Moteur'!O36,E39))</f>
+        <v/>
+      </c>
+      <c r="N39" s="17">
+        <f>IF(L39="Ne pas ouvrir",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Économiser 1 classe",H39+('08_Moteur'!AI36-MAX(1,'08_Moteur'!AI36-1))*'08_Moteur'!U36,H39)))</f>
+        <v/>
+      </c>
       <c r="O39" s="17">
-        <f>IF(N39="Ne pas ouvrir",0,IF(N39="Ouvrir +1 classe",H39-'08_Moteur'!U36,IF(N39="Économiser 1 classe",H39+('08_Moteur'!AI36-MAX(1,'08_Moteur'!AI36-1))*'08_Moteur'!U36,H39)))</f>
-        <v/>
-      </c>
-      <c r="P39" s="54">
-        <f>O39-H39</f>
+        <f>M39*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P39" s="17">
+        <f>N39-O39</f>
+        <v/>
+      </c>
+      <c r="Q39" s="54">
+        <f>N39-H39</f>
         <v/>
       </c>
     </row>
@@ -4816,37 +4956,41 @@
         <f>'08_Moteur'!AM37</f>
         <v/>
       </c>
-      <c r="I40" s="17">
-        <f>IF(N40="Ne pas ouvrir",0,E40)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J40" s="17">
-        <f>O40-I40</f>
-        <v/>
-      </c>
-      <c r="K40" s="69">
+      <c r="I40" s="68">
         <f>'08_Moteur'!AN37</f>
         <v/>
       </c>
-      <c r="L40" s="70">
-        <f>IF(H40&lt;0,"🔴 Ne pas ouvrir",IF(K40&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K40&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M40" s="71">
-        <f>IF(H40&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K40&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K40&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N40" s="21" t="inlineStr">
+      <c r="J40" s="69">
+        <f>IF(H40&lt;0,"🔴 Ne pas ouvrir",IF(I40&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I40&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K40" s="70">
+        <f>IF(H40&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I40&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I40&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M40" s="50">
+        <f>IF(L40="Ne pas ouvrir",0,IF(L40="Ouvrir +1 classe",E40+'08_Moteur'!O37,E40))</f>
+        <v/>
+      </c>
+      <c r="N40" s="17">
+        <f>IF(L40="Ne pas ouvrir",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Économiser 1 classe",H40+('08_Moteur'!AI37-MAX(1,'08_Moteur'!AI37-1))*'08_Moteur'!U37,H40)))</f>
+        <v/>
+      </c>
       <c r="O40" s="17">
-        <f>IF(N40="Ne pas ouvrir",0,IF(N40="Ouvrir +1 classe",H40-'08_Moteur'!U37,IF(N40="Économiser 1 classe",H40+('08_Moteur'!AI37-MAX(1,'08_Moteur'!AI37-1))*'08_Moteur'!U37,H40)))</f>
-        <v/>
-      </c>
-      <c r="P40" s="54">
-        <f>O40-H40</f>
+        <f>M40*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P40" s="17">
+        <f>N40-O40</f>
+        <v/>
+      </c>
+      <c r="Q40" s="54">
+        <f>N40-H40</f>
         <v/>
       </c>
     </row>
@@ -4883,37 +5027,41 @@
         <f>'08_Moteur'!AM38</f>
         <v/>
       </c>
-      <c r="I41" s="17">
-        <f>IF(N41="Ne pas ouvrir",0,E41)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J41" s="17">
-        <f>O41-I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="69">
+      <c r="I41" s="68">
         <f>'08_Moteur'!AN38</f>
         <v/>
       </c>
-      <c r="L41" s="70">
-        <f>IF(H41&lt;0,"🔴 Ne pas ouvrir",IF(K41&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K41&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M41" s="71">
-        <f>IF(H41&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K41&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K41&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N41" s="21" t="inlineStr">
+      <c r="J41" s="69">
+        <f>IF(H41&lt;0,"🔴 Ne pas ouvrir",IF(I41&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I41&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K41" s="70">
+        <f>IF(H41&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I41&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I41&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M41" s="50">
+        <f>IF(L41="Ne pas ouvrir",0,IF(L41="Ouvrir +1 classe",E41+'08_Moteur'!O38,E41))</f>
+        <v/>
+      </c>
+      <c r="N41" s="17">
+        <f>IF(L41="Ne pas ouvrir",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Économiser 1 classe",H41+('08_Moteur'!AI38-MAX(1,'08_Moteur'!AI38-1))*'08_Moteur'!U38,H41)))</f>
+        <v/>
+      </c>
       <c r="O41" s="17">
-        <f>IF(N41="Ne pas ouvrir",0,IF(N41="Ouvrir +1 classe",H41-'08_Moteur'!U38,IF(N41="Économiser 1 classe",H41+('08_Moteur'!AI38-MAX(1,'08_Moteur'!AI38-1))*'08_Moteur'!U38,H41)))</f>
-        <v/>
-      </c>
-      <c r="P41" s="54">
-        <f>O41-H41</f>
+        <f>M41*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P41" s="17">
+        <f>N41-O41</f>
+        <v/>
+      </c>
+      <c r="Q41" s="54">
+        <f>N41-H41</f>
         <v/>
       </c>
     </row>
@@ -4950,37 +5098,41 @@
         <f>'08_Moteur'!AM39</f>
         <v/>
       </c>
-      <c r="I42" s="17">
-        <f>IF(N42="Ne pas ouvrir",0,E42)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J42" s="17">
-        <f>O42-I42</f>
-        <v/>
-      </c>
-      <c r="K42" s="69">
+      <c r="I42" s="68">
         <f>'08_Moteur'!AN39</f>
         <v/>
       </c>
-      <c r="L42" s="70">
-        <f>IF(H42&lt;0,"🔴 Ne pas ouvrir",IF(K42&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K42&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M42" s="71">
-        <f>IF(H42&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K42&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K42&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N42" s="21" t="inlineStr">
+      <c r="J42" s="69">
+        <f>IF(H42&lt;0,"🔴 Ne pas ouvrir",IF(I42&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I42&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K42" s="70">
+        <f>IF(H42&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I42&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I42&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L42" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M42" s="50">
+        <f>IF(L42="Ne pas ouvrir",0,IF(L42="Ouvrir +1 classe",E42+'08_Moteur'!O39,E42))</f>
+        <v/>
+      </c>
+      <c r="N42" s="17">
+        <f>IF(L42="Ne pas ouvrir",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Économiser 1 classe",H42+('08_Moteur'!AI39-MAX(1,'08_Moteur'!AI39-1))*'08_Moteur'!U39,H42)))</f>
+        <v/>
+      </c>
       <c r="O42" s="17">
-        <f>IF(N42="Ne pas ouvrir",0,IF(N42="Ouvrir +1 classe",H42-'08_Moteur'!U39,IF(N42="Économiser 1 classe",H42+('08_Moteur'!AI39-MAX(1,'08_Moteur'!AI39-1))*'08_Moteur'!U39,H42)))</f>
-        <v/>
-      </c>
-      <c r="P42" s="54">
-        <f>O42-H42</f>
+        <f>M42*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P42" s="17">
+        <f>N42-O42</f>
+        <v/>
+      </c>
+      <c r="Q42" s="54">
+        <f>N42-H42</f>
         <v/>
       </c>
     </row>
@@ -5017,37 +5169,41 @@
         <f>'08_Moteur'!AM40</f>
         <v/>
       </c>
-      <c r="I43" s="17">
-        <f>IF(N43="Ne pas ouvrir",0,E43)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="17">
-        <f>O43-I43</f>
-        <v/>
-      </c>
-      <c r="K43" s="69">
+      <c r="I43" s="68">
         <f>'08_Moteur'!AN40</f>
         <v/>
       </c>
-      <c r="L43" s="70">
-        <f>IF(H43&lt;0,"🔴 Ne pas ouvrir",IF(K43&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K43&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M43" s="71">
-        <f>IF(H43&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K43&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K43&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N43" s="21" t="inlineStr">
+      <c r="J43" s="69">
+        <f>IF(H43&lt;0,"🔴 Ne pas ouvrir",IF(I43&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I43&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K43" s="70">
+        <f>IF(H43&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I43&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I43&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L43" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M43" s="50">
+        <f>IF(L43="Ne pas ouvrir",0,IF(L43="Ouvrir +1 classe",E43+'08_Moteur'!O40,E43))</f>
+        <v/>
+      </c>
+      <c r="N43" s="17">
+        <f>IF(L43="Ne pas ouvrir",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Économiser 1 classe",H43+('08_Moteur'!AI40-MAX(1,'08_Moteur'!AI40-1))*'08_Moteur'!U40,H43)))</f>
+        <v/>
+      </c>
       <c r="O43" s="17">
-        <f>IF(N43="Ne pas ouvrir",0,IF(N43="Ouvrir +1 classe",H43-'08_Moteur'!U40,IF(N43="Économiser 1 classe",H43+('08_Moteur'!AI40-MAX(1,'08_Moteur'!AI40-1))*'08_Moteur'!U40,H43)))</f>
-        <v/>
-      </c>
-      <c r="P43" s="54">
-        <f>O43-H43</f>
+        <f>M43*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P43" s="17">
+        <f>N43-O43</f>
+        <v/>
+      </c>
+      <c r="Q43" s="54">
+        <f>N43-H43</f>
         <v/>
       </c>
     </row>
@@ -5084,37 +5240,41 @@
         <f>'08_Moteur'!AM41</f>
         <v/>
       </c>
-      <c r="I44" s="17">
-        <f>IF(N44="Ne pas ouvrir",0,E44)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="17">
-        <f>O44-I44</f>
-        <v/>
-      </c>
-      <c r="K44" s="69">
+      <c r="I44" s="68">
         <f>'08_Moteur'!AN41</f>
         <v/>
       </c>
-      <c r="L44" s="70">
-        <f>IF(H44&lt;0,"🔴 Ne pas ouvrir",IF(K44&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K44&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M44" s="71">
-        <f>IF(H44&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K44&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K44&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N44" s="21" t="inlineStr">
+      <c r="J44" s="69">
+        <f>IF(H44&lt;0,"🔴 Ne pas ouvrir",IF(I44&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I44&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K44" s="70">
+        <f>IF(H44&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I44&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I44&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L44" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M44" s="50">
+        <f>IF(L44="Ne pas ouvrir",0,IF(L44="Ouvrir +1 classe",E44+'08_Moteur'!O41,E44))</f>
+        <v/>
+      </c>
+      <c r="N44" s="17">
+        <f>IF(L44="Ne pas ouvrir",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Économiser 1 classe",H44+('08_Moteur'!AI41-MAX(1,'08_Moteur'!AI41-1))*'08_Moteur'!U41,H44)))</f>
+        <v/>
+      </c>
       <c r="O44" s="17">
-        <f>IF(N44="Ne pas ouvrir",0,IF(N44="Ouvrir +1 classe",H44-'08_Moteur'!U41,IF(N44="Économiser 1 classe",H44+('08_Moteur'!AI41-MAX(1,'08_Moteur'!AI41-1))*'08_Moteur'!U41,H44)))</f>
-        <v/>
-      </c>
-      <c r="P44" s="54">
-        <f>O44-H44</f>
+        <f>M44*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P44" s="17">
+        <f>N44-O44</f>
+        <v/>
+      </c>
+      <c r="Q44" s="54">
+        <f>N44-H44</f>
         <v/>
       </c>
     </row>
@@ -5151,37 +5311,41 @@
         <f>'08_Moteur'!AM42</f>
         <v/>
       </c>
-      <c r="I45" s="17">
-        <f>IF(N45="Ne pas ouvrir",0,E45)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J45" s="17">
-        <f>O45-I45</f>
-        <v/>
-      </c>
-      <c r="K45" s="69">
+      <c r="I45" s="68">
         <f>'08_Moteur'!AN42</f>
         <v/>
       </c>
-      <c r="L45" s="70">
-        <f>IF(H45&lt;0,"🔴 Ne pas ouvrir",IF(K45&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K45&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M45" s="71">
-        <f>IF(H45&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K45&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K45&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N45" s="21" t="inlineStr">
+      <c r="J45" s="69">
+        <f>IF(H45&lt;0,"🔴 Ne pas ouvrir",IF(I45&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I45&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K45" s="70">
+        <f>IF(H45&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I45&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I45&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L45" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M45" s="50">
+        <f>IF(L45="Ne pas ouvrir",0,IF(L45="Ouvrir +1 classe",E45+'08_Moteur'!O42,E45))</f>
+        <v/>
+      </c>
+      <c r="N45" s="17">
+        <f>IF(L45="Ne pas ouvrir",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Économiser 1 classe",H45+('08_Moteur'!AI42-MAX(1,'08_Moteur'!AI42-1))*'08_Moteur'!U42,H45)))</f>
+        <v/>
+      </c>
       <c r="O45" s="17">
-        <f>IF(N45="Ne pas ouvrir",0,IF(N45="Ouvrir +1 classe",H45-'08_Moteur'!U42,IF(N45="Économiser 1 classe",H45+('08_Moteur'!AI42-MAX(1,'08_Moteur'!AI42-1))*'08_Moteur'!U42,H45)))</f>
-        <v/>
-      </c>
-      <c r="P45" s="54">
-        <f>O45-H45</f>
+        <f>M45*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P45" s="17">
+        <f>N45-O45</f>
+        <v/>
+      </c>
+      <c r="Q45" s="54">
+        <f>N45-H45</f>
         <v/>
       </c>
     </row>
@@ -5218,37 +5382,41 @@
         <f>'08_Moteur'!AM43</f>
         <v/>
       </c>
-      <c r="I46" s="17">
-        <f>IF(N46="Ne pas ouvrir",0,E46)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J46" s="17">
-        <f>O46-I46</f>
-        <v/>
-      </c>
-      <c r="K46" s="69">
+      <c r="I46" s="68">
         <f>'08_Moteur'!AN43</f>
         <v/>
       </c>
-      <c r="L46" s="70">
-        <f>IF(H46&lt;0,"🔴 Ne pas ouvrir",IF(K46&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K46&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M46" s="71">
-        <f>IF(H46&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K46&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K46&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N46" s="21" t="inlineStr">
+      <c r="J46" s="69">
+        <f>IF(H46&lt;0,"🔴 Ne pas ouvrir",IF(I46&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I46&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K46" s="70">
+        <f>IF(H46&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I46&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I46&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L46" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M46" s="50">
+        <f>IF(L46="Ne pas ouvrir",0,IF(L46="Ouvrir +1 classe",E46+'08_Moteur'!O43,E46))</f>
+        <v/>
+      </c>
+      <c r="N46" s="17">
+        <f>IF(L46="Ne pas ouvrir",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Économiser 1 classe",H46+('08_Moteur'!AI43-MAX(1,'08_Moteur'!AI43-1))*'08_Moteur'!U43,H46)))</f>
+        <v/>
+      </c>
       <c r="O46" s="17">
-        <f>IF(N46="Ne pas ouvrir",0,IF(N46="Ouvrir +1 classe",H46-'08_Moteur'!U43,IF(N46="Économiser 1 classe",H46+('08_Moteur'!AI43-MAX(1,'08_Moteur'!AI43-1))*'08_Moteur'!U43,H46)))</f>
-        <v/>
-      </c>
-      <c r="P46" s="54">
-        <f>O46-H46</f>
+        <f>M46*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P46" s="17">
+        <f>N46-O46</f>
+        <v/>
+      </c>
+      <c r="Q46" s="54">
+        <f>N46-H46</f>
         <v/>
       </c>
     </row>
@@ -5285,37 +5453,41 @@
         <f>'08_Moteur'!AM44</f>
         <v/>
       </c>
-      <c r="I47" s="17">
-        <f>IF(N47="Ne pas ouvrir",0,E47)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="17">
-        <f>O47-I47</f>
-        <v/>
-      </c>
-      <c r="K47" s="69">
+      <c r="I47" s="68">
         <f>'08_Moteur'!AN44</f>
         <v/>
       </c>
-      <c r="L47" s="70">
-        <f>IF(H47&lt;0,"🔴 Ne pas ouvrir",IF(K47&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K47&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M47" s="71">
-        <f>IF(H47&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K47&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K47&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N47" s="21" t="inlineStr">
+      <c r="J47" s="69">
+        <f>IF(H47&lt;0,"🔴 Ne pas ouvrir",IF(I47&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I47&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K47" s="70">
+        <f>IF(H47&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I47&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I47&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L47" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M47" s="50">
+        <f>IF(L47="Ne pas ouvrir",0,IF(L47="Ouvrir +1 classe",E47+'08_Moteur'!O44,E47))</f>
+        <v/>
+      </c>
+      <c r="N47" s="17">
+        <f>IF(L47="Ne pas ouvrir",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Économiser 1 classe",H47+('08_Moteur'!AI44-MAX(1,'08_Moteur'!AI44-1))*'08_Moteur'!U44,H47)))</f>
+        <v/>
+      </c>
       <c r="O47" s="17">
-        <f>IF(N47="Ne pas ouvrir",0,IF(N47="Ouvrir +1 classe",H47-'08_Moteur'!U44,IF(N47="Économiser 1 classe",H47+('08_Moteur'!AI44-MAX(1,'08_Moteur'!AI44-1))*'08_Moteur'!U44,H47)))</f>
-        <v/>
-      </c>
-      <c r="P47" s="54">
-        <f>O47-H47</f>
+        <f>M47*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P47" s="17">
+        <f>N47-O47</f>
+        <v/>
+      </c>
+      <c r="Q47" s="54">
+        <f>N47-H47</f>
         <v/>
       </c>
     </row>
@@ -5352,37 +5524,41 @@
         <f>'08_Moteur'!AM45</f>
         <v/>
       </c>
-      <c r="I48" s="17">
-        <f>IF(N48="Ne pas ouvrir",0,E48)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J48" s="17">
-        <f>O48-I48</f>
-        <v/>
-      </c>
-      <c r="K48" s="69">
+      <c r="I48" s="68">
         <f>'08_Moteur'!AN45</f>
         <v/>
       </c>
-      <c r="L48" s="70">
-        <f>IF(H48&lt;0,"🔴 Ne pas ouvrir",IF(K48&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K48&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M48" s="71">
-        <f>IF(H48&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K48&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K48&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N48" s="21" t="inlineStr">
+      <c r="J48" s="69">
+        <f>IF(H48&lt;0,"🔴 Ne pas ouvrir",IF(I48&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I48&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K48" s="70">
+        <f>IF(H48&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I48&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I48&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L48" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M48" s="50">
+        <f>IF(L48="Ne pas ouvrir",0,IF(L48="Ouvrir +1 classe",E48+'08_Moteur'!O45,E48))</f>
+        <v/>
+      </c>
+      <c r="N48" s="17">
+        <f>IF(L48="Ne pas ouvrir",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Économiser 1 classe",H48+('08_Moteur'!AI45-MAX(1,'08_Moteur'!AI45-1))*'08_Moteur'!U45,H48)))</f>
+        <v/>
+      </c>
       <c r="O48" s="17">
-        <f>IF(N48="Ne pas ouvrir",0,IF(N48="Ouvrir +1 classe",H48-'08_Moteur'!U45,IF(N48="Économiser 1 classe",H48+('08_Moteur'!AI45-MAX(1,'08_Moteur'!AI45-1))*'08_Moteur'!U45,H48)))</f>
-        <v/>
-      </c>
-      <c r="P48" s="54">
-        <f>O48-H48</f>
+        <f>M48*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P48" s="17">
+        <f>N48-O48</f>
+        <v/>
+      </c>
+      <c r="Q48" s="54">
+        <f>N48-H48</f>
         <v/>
       </c>
     </row>
@@ -5419,37 +5595,41 @@
         <f>'08_Moteur'!AM46</f>
         <v/>
       </c>
-      <c r="I49" s="17">
-        <f>IF(N49="Ne pas ouvrir",0,E49)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J49" s="17">
-        <f>O49-I49</f>
-        <v/>
-      </c>
-      <c r="K49" s="69">
+      <c r="I49" s="68">
         <f>'08_Moteur'!AN46</f>
         <v/>
       </c>
-      <c r="L49" s="70">
-        <f>IF(H49&lt;0,"🔴 Ne pas ouvrir",IF(K49&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K49&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M49" s="71">
-        <f>IF(H49&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K49&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K49&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N49" s="21" t="inlineStr">
+      <c r="J49" s="69">
+        <f>IF(H49&lt;0,"🔴 Ne pas ouvrir",IF(I49&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I49&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K49" s="70">
+        <f>IF(H49&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I49&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I49&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L49" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M49" s="50">
+        <f>IF(L49="Ne pas ouvrir",0,IF(L49="Ouvrir +1 classe",E49+'08_Moteur'!O46,E49))</f>
+        <v/>
+      </c>
+      <c r="N49" s="17">
+        <f>IF(L49="Ne pas ouvrir",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Économiser 1 classe",H49+('08_Moteur'!AI46-MAX(1,'08_Moteur'!AI46-1))*'08_Moteur'!U46,H49)))</f>
+        <v/>
+      </c>
       <c r="O49" s="17">
-        <f>IF(N49="Ne pas ouvrir",0,IF(N49="Ouvrir +1 classe",H49-'08_Moteur'!U46,IF(N49="Économiser 1 classe",H49+('08_Moteur'!AI46-MAX(1,'08_Moteur'!AI46-1))*'08_Moteur'!U46,H49)))</f>
-        <v/>
-      </c>
-      <c r="P49" s="54">
-        <f>O49-H49</f>
+        <f>M49*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P49" s="17">
+        <f>N49-O49</f>
+        <v/>
+      </c>
+      <c r="Q49" s="54">
+        <f>N49-H49</f>
         <v/>
       </c>
     </row>
@@ -5486,37 +5666,41 @@
         <f>'08_Moteur'!AM47</f>
         <v/>
       </c>
-      <c r="I50" s="17">
-        <f>IF(N50="Ne pas ouvrir",0,E50)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J50" s="17">
-        <f>O50-I50</f>
-        <v/>
-      </c>
-      <c r="K50" s="69">
+      <c r="I50" s="68">
         <f>'08_Moteur'!AN47</f>
         <v/>
       </c>
-      <c r="L50" s="70">
-        <f>IF(H50&lt;0,"🔴 Ne pas ouvrir",IF(K50&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K50&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M50" s="71">
-        <f>IF(H50&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K50&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K50&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N50" s="21" t="inlineStr">
+      <c r="J50" s="69">
+        <f>IF(H50&lt;0,"🔴 Ne pas ouvrir",IF(I50&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I50&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K50" s="70">
+        <f>IF(H50&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I50&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I50&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L50" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M50" s="50">
+        <f>IF(L50="Ne pas ouvrir",0,IF(L50="Ouvrir +1 classe",E50+'08_Moteur'!O47,E50))</f>
+        <v/>
+      </c>
+      <c r="N50" s="17">
+        <f>IF(L50="Ne pas ouvrir",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Économiser 1 classe",H50+('08_Moteur'!AI47-MAX(1,'08_Moteur'!AI47-1))*'08_Moteur'!U47,H50)))</f>
+        <v/>
+      </c>
       <c r="O50" s="17">
-        <f>IF(N50="Ne pas ouvrir",0,IF(N50="Ouvrir +1 classe",H50-'08_Moteur'!U47,IF(N50="Économiser 1 classe",H50+('08_Moteur'!AI47-MAX(1,'08_Moteur'!AI47-1))*'08_Moteur'!U47,H50)))</f>
-        <v/>
-      </c>
-      <c r="P50" s="54">
-        <f>O50-H50</f>
+        <f>M50*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P50" s="17">
+        <f>N50-O50</f>
+        <v/>
+      </c>
+      <c r="Q50" s="54">
+        <f>N50-H50</f>
         <v/>
       </c>
     </row>
@@ -5553,37 +5737,41 @@
         <f>'08_Moteur'!AM48</f>
         <v/>
       </c>
-      <c r="I51" s="17">
-        <f>IF(N51="Ne pas ouvrir",0,E51)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J51" s="17">
-        <f>O51-I51</f>
-        <v/>
-      </c>
-      <c r="K51" s="69">
+      <c r="I51" s="68">
         <f>'08_Moteur'!AN48</f>
         <v/>
       </c>
-      <c r="L51" s="70">
-        <f>IF(H51&lt;0,"🔴 Ne pas ouvrir",IF(K51&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K51&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M51" s="71">
-        <f>IF(H51&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K51&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K51&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N51" s="21" t="inlineStr">
+      <c r="J51" s="69">
+        <f>IF(H51&lt;0,"🔴 Ne pas ouvrir",IF(I51&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I51&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K51" s="70">
+        <f>IF(H51&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I51&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I51&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L51" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M51" s="50">
+        <f>IF(L51="Ne pas ouvrir",0,IF(L51="Ouvrir +1 classe",E51+'08_Moteur'!O48,E51))</f>
+        <v/>
+      </c>
+      <c r="N51" s="17">
+        <f>IF(L51="Ne pas ouvrir",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Économiser 1 classe",H51+('08_Moteur'!AI48-MAX(1,'08_Moteur'!AI48-1))*'08_Moteur'!U48,H51)))</f>
+        <v/>
+      </c>
       <c r="O51" s="17">
-        <f>IF(N51="Ne pas ouvrir",0,IF(N51="Ouvrir +1 classe",H51-'08_Moteur'!U48,IF(N51="Économiser 1 classe",H51+('08_Moteur'!AI48-MAX(1,'08_Moteur'!AI48-1))*'08_Moteur'!U48,H51)))</f>
-        <v/>
-      </c>
-      <c r="P51" s="54">
-        <f>O51-H51</f>
+        <f>M51*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P51" s="17">
+        <f>N51-O51</f>
+        <v/>
+      </c>
+      <c r="Q51" s="54">
+        <f>N51-H51</f>
         <v/>
       </c>
     </row>
@@ -5620,37 +5808,41 @@
         <f>'08_Moteur'!AM49</f>
         <v/>
       </c>
-      <c r="I52" s="17">
-        <f>IF(N52="Ne pas ouvrir",0,E52)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J52" s="17">
-        <f>O52-I52</f>
-        <v/>
-      </c>
-      <c r="K52" s="69">
+      <c r="I52" s="68">
         <f>'08_Moteur'!AN49</f>
         <v/>
       </c>
-      <c r="L52" s="70">
-        <f>IF(H52&lt;0,"🔴 Ne pas ouvrir",IF(K52&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K52&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M52" s="71">
-        <f>IF(H52&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K52&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K52&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N52" s="21" t="inlineStr">
+      <c r="J52" s="69">
+        <f>IF(H52&lt;0,"🔴 Ne pas ouvrir",IF(I52&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I52&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K52" s="70">
+        <f>IF(H52&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I52&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I52&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L52" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M52" s="50">
+        <f>IF(L52="Ne pas ouvrir",0,IF(L52="Ouvrir +1 classe",E52+'08_Moteur'!O49,E52))</f>
+        <v/>
+      </c>
+      <c r="N52" s="17">
+        <f>IF(L52="Ne pas ouvrir",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Économiser 1 classe",H52+('08_Moteur'!AI49-MAX(1,'08_Moteur'!AI49-1))*'08_Moteur'!U49,H52)))</f>
+        <v/>
+      </c>
       <c r="O52" s="17">
-        <f>IF(N52="Ne pas ouvrir",0,IF(N52="Ouvrir +1 classe",H52-'08_Moteur'!U49,IF(N52="Économiser 1 classe",H52+('08_Moteur'!AI49-MAX(1,'08_Moteur'!AI49-1))*'08_Moteur'!U49,H52)))</f>
-        <v/>
-      </c>
-      <c r="P52" s="54">
-        <f>O52-H52</f>
+        <f>M52*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P52" s="17">
+        <f>N52-O52</f>
+        <v/>
+      </c>
+      <c r="Q52" s="54">
+        <f>N52-H52</f>
         <v/>
       </c>
     </row>
@@ -5687,37 +5879,41 @@
         <f>'08_Moteur'!AM50</f>
         <v/>
       </c>
-      <c r="I53" s="17">
-        <f>IF(N53="Ne pas ouvrir",0,E53)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J53" s="17">
-        <f>O53-I53</f>
-        <v/>
-      </c>
-      <c r="K53" s="69">
+      <c r="I53" s="68">
         <f>'08_Moteur'!AN50</f>
         <v/>
       </c>
-      <c r="L53" s="70">
-        <f>IF(H53&lt;0,"🔴 Ne pas ouvrir",IF(K53&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K53&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M53" s="71">
-        <f>IF(H53&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K53&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K53&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N53" s="21" t="inlineStr">
+      <c r="J53" s="69">
+        <f>IF(H53&lt;0,"🔴 Ne pas ouvrir",IF(I53&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I53&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K53" s="70">
+        <f>IF(H53&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I53&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I53&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M53" s="50">
+        <f>IF(L53="Ne pas ouvrir",0,IF(L53="Ouvrir +1 classe",E53+'08_Moteur'!O50,E53))</f>
+        <v/>
+      </c>
+      <c r="N53" s="17">
+        <f>IF(L53="Ne pas ouvrir",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Économiser 1 classe",H53+('08_Moteur'!AI50-MAX(1,'08_Moteur'!AI50-1))*'08_Moteur'!U50,H53)))</f>
+        <v/>
+      </c>
       <c r="O53" s="17">
-        <f>IF(N53="Ne pas ouvrir",0,IF(N53="Ouvrir +1 classe",H53-'08_Moteur'!U50,IF(N53="Économiser 1 classe",H53+('08_Moteur'!AI50-MAX(1,'08_Moteur'!AI50-1))*'08_Moteur'!U50,H53)))</f>
-        <v/>
-      </c>
-      <c r="P53" s="54">
-        <f>O53-H53</f>
+        <f>M53*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P53" s="17">
+        <f>N53-O53</f>
+        <v/>
+      </c>
+      <c r="Q53" s="54">
+        <f>N53-H53</f>
         <v/>
       </c>
     </row>
@@ -5754,37 +5950,41 @@
         <f>'08_Moteur'!AM51</f>
         <v/>
       </c>
-      <c r="I54" s="17">
-        <f>IF(N54="Ne pas ouvrir",0,E54)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J54" s="17">
-        <f>O54-I54</f>
-        <v/>
-      </c>
-      <c r="K54" s="69">
+      <c r="I54" s="68">
         <f>'08_Moteur'!AN51</f>
         <v/>
       </c>
-      <c r="L54" s="70">
-        <f>IF(H54&lt;0,"🔴 Ne pas ouvrir",IF(K54&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K54&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M54" s="71">
-        <f>IF(H54&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K54&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K54&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N54" s="21" t="inlineStr">
+      <c r="J54" s="69">
+        <f>IF(H54&lt;0,"🔴 Ne pas ouvrir",IF(I54&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I54&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K54" s="70">
+        <f>IF(H54&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I54&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I54&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L54" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M54" s="50">
+        <f>IF(L54="Ne pas ouvrir",0,IF(L54="Ouvrir +1 classe",E54+'08_Moteur'!O51,E54))</f>
+        <v/>
+      </c>
+      <c r="N54" s="17">
+        <f>IF(L54="Ne pas ouvrir",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Économiser 1 classe",H54+('08_Moteur'!AI51-MAX(1,'08_Moteur'!AI51-1))*'08_Moteur'!U51,H54)))</f>
+        <v/>
+      </c>
       <c r="O54" s="17">
-        <f>IF(N54="Ne pas ouvrir",0,IF(N54="Ouvrir +1 classe",H54-'08_Moteur'!U51,IF(N54="Économiser 1 classe",H54+('08_Moteur'!AI51-MAX(1,'08_Moteur'!AI51-1))*'08_Moteur'!U51,H54)))</f>
-        <v/>
-      </c>
-      <c r="P54" s="54">
-        <f>O54-H54</f>
+        <f>M54*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P54" s="17">
+        <f>N54-O54</f>
+        <v/>
+      </c>
+      <c r="Q54" s="54">
+        <f>N54-H54</f>
         <v/>
       </c>
     </row>
@@ -5821,37 +6021,41 @@
         <f>'08_Moteur'!AM52</f>
         <v/>
       </c>
-      <c r="I55" s="17">
-        <f>IF(N55="Ne pas ouvrir",0,E55)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J55" s="17">
-        <f>O55-I55</f>
-        <v/>
-      </c>
-      <c r="K55" s="69">
+      <c r="I55" s="68">
         <f>'08_Moteur'!AN52</f>
         <v/>
       </c>
-      <c r="L55" s="70">
-        <f>IF(H55&lt;0,"🔴 Ne pas ouvrir",IF(K55&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K55&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M55" s="71">
-        <f>IF(H55&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K55&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K55&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N55" s="21" t="inlineStr">
+      <c r="J55" s="69">
+        <f>IF(H55&lt;0,"🔴 Ne pas ouvrir",IF(I55&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I55&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K55" s="70">
+        <f>IF(H55&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I55&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I55&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L55" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M55" s="50">
+        <f>IF(L55="Ne pas ouvrir",0,IF(L55="Ouvrir +1 classe",E55+'08_Moteur'!O52,E55))</f>
+        <v/>
+      </c>
+      <c r="N55" s="17">
+        <f>IF(L55="Ne pas ouvrir",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Économiser 1 classe",H55+('08_Moteur'!AI52-MAX(1,'08_Moteur'!AI52-1))*'08_Moteur'!U52,H55)))</f>
+        <v/>
+      </c>
       <c r="O55" s="17">
-        <f>IF(N55="Ne pas ouvrir",0,IF(N55="Ouvrir +1 classe",H55-'08_Moteur'!U52,IF(N55="Économiser 1 classe",H55+('08_Moteur'!AI52-MAX(1,'08_Moteur'!AI52-1))*'08_Moteur'!U52,H55)))</f>
-        <v/>
-      </c>
-      <c r="P55" s="54">
-        <f>O55-H55</f>
+        <f>M55*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P55" s="17">
+        <f>N55-O55</f>
+        <v/>
+      </c>
+      <c r="Q55" s="54">
+        <f>N55-H55</f>
         <v/>
       </c>
     </row>
@@ -5888,37 +6092,41 @@
         <f>'08_Moteur'!AM53</f>
         <v/>
       </c>
-      <c r="I56" s="17">
-        <f>IF(N56="Ne pas ouvrir",0,E56)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J56" s="17">
-        <f>O56-I56</f>
-        <v/>
-      </c>
-      <c r="K56" s="69">
+      <c r="I56" s="68">
         <f>'08_Moteur'!AN53</f>
         <v/>
       </c>
-      <c r="L56" s="70">
-        <f>IF(H56&lt;0,"🔴 Ne pas ouvrir",IF(K56&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K56&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M56" s="71">
-        <f>IF(H56&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K56&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K56&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N56" s="21" t="inlineStr">
+      <c r="J56" s="69">
+        <f>IF(H56&lt;0,"🔴 Ne pas ouvrir",IF(I56&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I56&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K56" s="70">
+        <f>IF(H56&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I56&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I56&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L56" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M56" s="50">
+        <f>IF(L56="Ne pas ouvrir",0,IF(L56="Ouvrir +1 classe",E56+'08_Moteur'!O53,E56))</f>
+        <v/>
+      </c>
+      <c r="N56" s="17">
+        <f>IF(L56="Ne pas ouvrir",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Économiser 1 classe",H56+('08_Moteur'!AI53-MAX(1,'08_Moteur'!AI53-1))*'08_Moteur'!U53,H56)))</f>
+        <v/>
+      </c>
       <c r="O56" s="17">
-        <f>IF(N56="Ne pas ouvrir",0,IF(N56="Ouvrir +1 classe",H56-'08_Moteur'!U53,IF(N56="Économiser 1 classe",H56+('08_Moteur'!AI53-MAX(1,'08_Moteur'!AI53-1))*'08_Moteur'!U53,H56)))</f>
-        <v/>
-      </c>
-      <c r="P56" s="54">
-        <f>O56-H56</f>
+        <f>M56*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P56" s="17">
+        <f>N56-O56</f>
+        <v/>
+      </c>
+      <c r="Q56" s="54">
+        <f>N56-H56</f>
         <v/>
       </c>
     </row>
@@ -5955,37 +6163,41 @@
         <f>'08_Moteur'!AM54</f>
         <v/>
       </c>
-      <c r="I57" s="17">
-        <f>IF(N57="Ne pas ouvrir",0,E57)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J57" s="17">
-        <f>O57-I57</f>
-        <v/>
-      </c>
-      <c r="K57" s="69">
+      <c r="I57" s="68">
         <f>'08_Moteur'!AN54</f>
         <v/>
       </c>
-      <c r="L57" s="70">
-        <f>IF(H57&lt;0,"🔴 Ne pas ouvrir",IF(K57&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K57&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M57" s="71">
-        <f>IF(H57&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K57&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K57&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N57" s="21" t="inlineStr">
+      <c r="J57" s="69">
+        <f>IF(H57&lt;0,"🔴 Ne pas ouvrir",IF(I57&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I57&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K57" s="70">
+        <f>IF(H57&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I57&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I57&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L57" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M57" s="50">
+        <f>IF(L57="Ne pas ouvrir",0,IF(L57="Ouvrir +1 classe",E57+'08_Moteur'!O54,E57))</f>
+        <v/>
+      </c>
+      <c r="N57" s="17">
+        <f>IF(L57="Ne pas ouvrir",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Économiser 1 classe",H57+('08_Moteur'!AI54-MAX(1,'08_Moteur'!AI54-1))*'08_Moteur'!U54,H57)))</f>
+        <v/>
+      </c>
       <c r="O57" s="17">
-        <f>IF(N57="Ne pas ouvrir",0,IF(N57="Ouvrir +1 classe",H57-'08_Moteur'!U54,IF(N57="Économiser 1 classe",H57+('08_Moteur'!AI54-MAX(1,'08_Moteur'!AI54-1))*'08_Moteur'!U54,H57)))</f>
-        <v/>
-      </c>
-      <c r="P57" s="54">
-        <f>O57-H57</f>
+        <f>M57*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P57" s="17">
+        <f>N57-O57</f>
+        <v/>
+      </c>
+      <c r="Q57" s="54">
+        <f>N57-H57</f>
         <v/>
       </c>
     </row>
@@ -6022,37 +6234,41 @@
         <f>'08_Moteur'!AM55</f>
         <v/>
       </c>
-      <c r="I58" s="17">
-        <f>IF(N58="Ne pas ouvrir",0,E58)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J58" s="17">
-        <f>O58-I58</f>
-        <v/>
-      </c>
-      <c r="K58" s="69">
+      <c r="I58" s="68">
         <f>'08_Moteur'!AN55</f>
         <v/>
       </c>
-      <c r="L58" s="70">
-        <f>IF(H58&lt;0,"🔴 Ne pas ouvrir",IF(K58&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K58&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M58" s="71">
-        <f>IF(H58&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K58&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K58&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N58" s="21" t="inlineStr">
+      <c r="J58" s="69">
+        <f>IF(H58&lt;0,"🔴 Ne pas ouvrir",IF(I58&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I58&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K58" s="70">
+        <f>IF(H58&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I58&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I58&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L58" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M58" s="50">
+        <f>IF(L58="Ne pas ouvrir",0,IF(L58="Ouvrir +1 classe",E58+'08_Moteur'!O55,E58))</f>
+        <v/>
+      </c>
+      <c r="N58" s="17">
+        <f>IF(L58="Ne pas ouvrir",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Économiser 1 classe",H58+('08_Moteur'!AI55-MAX(1,'08_Moteur'!AI55-1))*'08_Moteur'!U55,H58)))</f>
+        <v/>
+      </c>
       <c r="O58" s="17">
-        <f>IF(N58="Ne pas ouvrir",0,IF(N58="Ouvrir +1 classe",H58-'08_Moteur'!U55,IF(N58="Économiser 1 classe",H58+('08_Moteur'!AI55-MAX(1,'08_Moteur'!AI55-1))*'08_Moteur'!U55,H58)))</f>
-        <v/>
-      </c>
-      <c r="P58" s="54">
-        <f>O58-H58</f>
+        <f>M58*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P58" s="17">
+        <f>N58-O58</f>
+        <v/>
+      </c>
+      <c r="Q58" s="54">
+        <f>N58-H58</f>
         <v/>
       </c>
     </row>
@@ -6089,37 +6305,41 @@
         <f>'08_Moteur'!AM56</f>
         <v/>
       </c>
-      <c r="I59" s="17">
-        <f>IF(N59="Ne pas ouvrir",0,E59)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J59" s="17">
-        <f>O59-I59</f>
-        <v/>
-      </c>
-      <c r="K59" s="69">
+      <c r="I59" s="68">
         <f>'08_Moteur'!AN56</f>
         <v/>
       </c>
-      <c r="L59" s="70">
-        <f>IF(H59&lt;0,"🔴 Ne pas ouvrir",IF(K59&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K59&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M59" s="71">
-        <f>IF(H59&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K59&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K59&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N59" s="21" t="inlineStr">
+      <c r="J59" s="69">
+        <f>IF(H59&lt;0,"🔴 Ne pas ouvrir",IF(I59&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I59&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K59" s="70">
+        <f>IF(H59&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I59&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I59&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L59" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M59" s="50">
+        <f>IF(L59="Ne pas ouvrir",0,IF(L59="Ouvrir +1 classe",E59+'08_Moteur'!O56,E59))</f>
+        <v/>
+      </c>
+      <c r="N59" s="17">
+        <f>IF(L59="Ne pas ouvrir",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Économiser 1 classe",H59+('08_Moteur'!AI56-MAX(1,'08_Moteur'!AI56-1))*'08_Moteur'!U56,H59)))</f>
+        <v/>
+      </c>
       <c r="O59" s="17">
-        <f>IF(N59="Ne pas ouvrir",0,IF(N59="Ouvrir +1 classe",H59-'08_Moteur'!U56,IF(N59="Économiser 1 classe",H59+('08_Moteur'!AI56-MAX(1,'08_Moteur'!AI56-1))*'08_Moteur'!U56,H59)))</f>
-        <v/>
-      </c>
-      <c r="P59" s="54">
-        <f>O59-H59</f>
+        <f>M59*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P59" s="17">
+        <f>N59-O59</f>
+        <v/>
+      </c>
+      <c r="Q59" s="54">
+        <f>N59-H59</f>
         <v/>
       </c>
     </row>
@@ -6156,37 +6376,41 @@
         <f>'08_Moteur'!AM57</f>
         <v/>
       </c>
-      <c r="I60" s="17">
-        <f>IF(N60="Ne pas ouvrir",0,E60)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J60" s="17">
-        <f>O60-I60</f>
-        <v/>
-      </c>
-      <c r="K60" s="69">
+      <c r="I60" s="68">
         <f>'08_Moteur'!AN57</f>
         <v/>
       </c>
-      <c r="L60" s="70">
-        <f>IF(H60&lt;0,"🔴 Ne pas ouvrir",IF(K60&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K60&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M60" s="71">
-        <f>IF(H60&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K60&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K60&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N60" s="21" t="inlineStr">
+      <c r="J60" s="69">
+        <f>IF(H60&lt;0,"🔴 Ne pas ouvrir",IF(I60&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I60&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K60" s="70">
+        <f>IF(H60&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I60&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I60&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L60" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M60" s="50">
+        <f>IF(L60="Ne pas ouvrir",0,IF(L60="Ouvrir +1 classe",E60+'08_Moteur'!O57,E60))</f>
+        <v/>
+      </c>
+      <c r="N60" s="17">
+        <f>IF(L60="Ne pas ouvrir",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Économiser 1 classe",H60+('08_Moteur'!AI57-MAX(1,'08_Moteur'!AI57-1))*'08_Moteur'!U57,H60)))</f>
+        <v/>
+      </c>
       <c r="O60" s="17">
-        <f>IF(N60="Ne pas ouvrir",0,IF(N60="Ouvrir +1 classe",H60-'08_Moteur'!U57,IF(N60="Économiser 1 classe",H60+('08_Moteur'!AI57-MAX(1,'08_Moteur'!AI57-1))*'08_Moteur'!U57,H60)))</f>
-        <v/>
-      </c>
-      <c r="P60" s="54">
-        <f>O60-H60</f>
+        <f>M60*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P60" s="17">
+        <f>N60-O60</f>
+        <v/>
+      </c>
+      <c r="Q60" s="54">
+        <f>N60-H60</f>
         <v/>
       </c>
     </row>
@@ -6223,37 +6447,41 @@
         <f>'08_Moteur'!AM58</f>
         <v/>
       </c>
-      <c r="I61" s="17">
-        <f>IF(N61="Ne pas ouvrir",0,E61)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J61" s="17">
-        <f>O61-I61</f>
-        <v/>
-      </c>
-      <c r="K61" s="69">
+      <c r="I61" s="68">
         <f>'08_Moteur'!AN58</f>
         <v/>
       </c>
-      <c r="L61" s="70">
-        <f>IF(H61&lt;0,"🔴 Ne pas ouvrir",IF(K61&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K61&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M61" s="71">
-        <f>IF(H61&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K61&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K61&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N61" s="21" t="inlineStr">
+      <c r="J61" s="69">
+        <f>IF(H61&lt;0,"🔴 Ne pas ouvrir",IF(I61&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I61&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K61" s="70">
+        <f>IF(H61&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I61&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I61&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L61" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M61" s="50">
+        <f>IF(L61="Ne pas ouvrir",0,IF(L61="Ouvrir +1 classe",E61+'08_Moteur'!O58,E61))</f>
+        <v/>
+      </c>
+      <c r="N61" s="17">
+        <f>IF(L61="Ne pas ouvrir",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Économiser 1 classe",H61+('08_Moteur'!AI58-MAX(1,'08_Moteur'!AI58-1))*'08_Moteur'!U58,H61)))</f>
+        <v/>
+      </c>
       <c r="O61" s="17">
-        <f>IF(N61="Ne pas ouvrir",0,IF(N61="Ouvrir +1 classe",H61-'08_Moteur'!U58,IF(N61="Économiser 1 classe",H61+('08_Moteur'!AI58-MAX(1,'08_Moteur'!AI58-1))*'08_Moteur'!U58,H61)))</f>
-        <v/>
-      </c>
-      <c r="P61" s="54">
-        <f>O61-H61</f>
+        <f>M61*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P61" s="17">
+        <f>N61-O61</f>
+        <v/>
+      </c>
+      <c r="Q61" s="54">
+        <f>N61-H61</f>
         <v/>
       </c>
     </row>
@@ -6290,37 +6518,41 @@
         <f>'08_Moteur'!AM59</f>
         <v/>
       </c>
-      <c r="I62" s="17">
-        <f>IF(N62="Ne pas ouvrir",0,E62)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="17">
-        <f>O62-I62</f>
-        <v/>
-      </c>
-      <c r="K62" s="69">
+      <c r="I62" s="68">
         <f>'08_Moteur'!AN59</f>
         <v/>
       </c>
-      <c r="L62" s="70">
-        <f>IF(H62&lt;0,"🔴 Ne pas ouvrir",IF(K62&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K62&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M62" s="71">
-        <f>IF(H62&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K62&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K62&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N62" s="21" t="inlineStr">
+      <c r="J62" s="69">
+        <f>IF(H62&lt;0,"🔴 Ne pas ouvrir",IF(I62&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I62&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K62" s="70">
+        <f>IF(H62&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I62&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I62&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L62" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M62" s="50">
+        <f>IF(L62="Ne pas ouvrir",0,IF(L62="Ouvrir +1 classe",E62+'08_Moteur'!O59,E62))</f>
+        <v/>
+      </c>
+      <c r="N62" s="17">
+        <f>IF(L62="Ne pas ouvrir",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Économiser 1 classe",H62+('08_Moteur'!AI59-MAX(1,'08_Moteur'!AI59-1))*'08_Moteur'!U59,H62)))</f>
+        <v/>
+      </c>
       <c r="O62" s="17">
-        <f>IF(N62="Ne pas ouvrir",0,IF(N62="Ouvrir +1 classe",H62-'08_Moteur'!U59,IF(N62="Économiser 1 classe",H62+('08_Moteur'!AI59-MAX(1,'08_Moteur'!AI59-1))*'08_Moteur'!U59,H62)))</f>
-        <v/>
-      </c>
-      <c r="P62" s="54">
-        <f>O62-H62</f>
+        <f>M62*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P62" s="17">
+        <f>N62-O62</f>
+        <v/>
+      </c>
+      <c r="Q62" s="54">
+        <f>N62-H62</f>
         <v/>
       </c>
     </row>
@@ -6357,56 +6589,60 @@
         <f>'08_Moteur'!AM60</f>
         <v/>
       </c>
-      <c r="I63" s="17">
-        <f>IF(N63="Ne pas ouvrir",0,E63)*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUMPRODUCT((N6:N63&lt;&gt;"Ne pas ouvrir")*E6:E63),0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="17">
-        <f>O63-I63</f>
-        <v/>
-      </c>
-      <c r="K63" s="69">
+      <c r="I63" s="68">
         <f>'08_Moteur'!AN60</f>
         <v/>
       </c>
-      <c r="L63" s="70">
-        <f>IF(H63&lt;0,"🔴 Ne pas ouvrir",IF(K63&gt;=0.95,"🟢 Ouvrir +1 classe",IF(K63&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
-        <v/>
-      </c>
-      <c r="M63" s="71">
-        <f>IF(H63&lt;0,"Contribution négative : la fermer améliore l'EBITDA",IF(K63&gt;=0.95,"Quasi saturé : +1 classe capte la demande",IF(K63&lt;0.55,"Sous-rempli MAIS contribution positive → GARDER (fermer perdrait la marge, la structure resterait)","Sain")))</f>
-        <v/>
-      </c>
-      <c r="N63" s="21" t="inlineStr">
+      <c r="J63" s="69">
+        <f>IF(H63&lt;0,"🔴 Ne pas ouvrir",IF(I63&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I63&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <v/>
+      </c>
+      <c r="K63" s="70">
+        <f>IF(H63&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I63&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I63&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <v/>
+      </c>
+      <c r="L63" s="21" t="inlineStr">
         <is>
           <t>Maintenir</t>
         </is>
       </c>
+      <c r="M63" s="50">
+        <f>IF(L63="Ne pas ouvrir",0,IF(L63="Ouvrir +1 classe",E63+'08_Moteur'!O60,E63))</f>
+        <v/>
+      </c>
+      <c r="N63" s="17">
+        <f>IF(L63="Ne pas ouvrir",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Économiser 1 classe",H63+('08_Moteur'!AI60-MAX(1,'08_Moteur'!AI60-1))*'08_Moteur'!U60,H63)))</f>
+        <v/>
+      </c>
       <c r="O63" s="17">
-        <f>IF(N63="Ne pas ouvrir",0,IF(N63="Ouvrir +1 classe",H63-'08_Moteur'!U60,IF(N63="Économiser 1 classe",H63+('08_Moteur'!AI60-MAX(1,'08_Moteur'!AI60-1))*'08_Moteur'!U60,H63)))</f>
-        <v/>
-      </c>
-      <c r="P63" s="54">
-        <f>O63-H63</f>
+        <f>M63*IFERROR(('09_Allocation'!E20+'09_Allocation'!F20+'09_Allocation'!I20)/SUM(M6:M63),0)</f>
+        <v/>
+      </c>
+      <c r="P63" s="17">
+        <f>N63-O63</f>
+        <v/>
+      </c>
+      <c r="Q63" s="54">
+        <f>N63-H63</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="M3:P3"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M3:Q3"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="I3:J3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 N52 N53 N54 N55 N56 N57 N58 N59 N60 N61 N62 N63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Maintenir,Ne pas ouvrir,Ouvrir +1 classe,Économiser 1 classe"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6470,7 +6706,7 @@
         <f>0.01*SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60*'08_Moteur'!$AF$3:$AF$60)</f>
         <v/>
       </c>
-      <c r="D6" s="71" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>Tombe quasi intégralement en EBITDA.</t>
         </is>
@@ -6486,7 +6722,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$D$18)</f>
         <v/>
       </c>
-      <c r="D7" s="71" t="inlineStr">
+      <c r="D7" s="70" t="inlineStr">
         <is>
           <t>Nul si recouvrement=100 % ; sinon réduit la perte.</t>
         </is>
@@ -6502,7 +6738,7 @@
         <f>0.01*'02_Leviers'!$D$21*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
         <v/>
       </c>
-      <c r="D8" s="71" t="inlineStr">
+      <c r="D8" s="70" t="inlineStr">
         <is>
           <t>Plus de leads → plus d'inscrits, net du coût.</t>
         </is>
@@ -6518,7 +6754,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=0)*'08_Moteur'!$K$3:$K$60)*IFERROR(SUM('08_Moteur'!$AM$3:$AM$60)/SUM('08_Moteur'!$AD$3:$AD$60),0)</f>
         <v/>
       </c>
-      <c r="D9" s="71" t="inlineStr">
+      <c r="D9" s="70" t="inlineStr">
         <is>
           <t>Rétention : + d'étudiants qui poursuivent.</t>
         </is>
@@ -6530,7 +6766,7 @@
           <t>Exposition financement alternance (€ à sécuriser) :</t>
         </is>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="71">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
@@ -6773,20 +7009,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>€ à sécuriser (exposition)</t>
         </is>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="73">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="73">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
         <v/>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="74">
         <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
@@ -6848,7 +7084,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -6865,7 +7101,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -6882,7 +7118,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="75" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -6899,7 +7135,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -6916,7 +7152,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="75" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -6933,7 +7169,7 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="75" t="inlineStr">
         <is>
           <t>Sécurisation &amp; recouvrement</t>
         </is>
@@ -6950,7 +7186,7 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>Objectifs (cadrage)</t>
         </is>
@@ -6967,7 +7203,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="76" t="inlineStr">
+      <c r="B13" s="75" t="inlineStr">
         <is>
           <t>Décisions ouvrir/fermer</t>
         </is>
@@ -6984,7 +7220,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="76" t="inlineStr">
+      <c r="B14" s="75" t="inlineStr">
         <is>
           <t>Allocation structure</t>
         </is>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -2547,11 +2547,11 @@
         <v/>
       </c>
       <c r="J6" s="69">
-        <f>IF(H6&lt;0,"🔴 Ne pas ouvrir",IF(I6&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I6&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H6&lt;0,"🔴 Ne pas lancer",IF(I6&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I6&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K6" s="70">
-        <f>IF(H6&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I6&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I6&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H6&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I6&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I6&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -2560,11 +2560,11 @@
         </is>
       </c>
       <c r="M6" s="50">
-        <f>IF(L6="Ne pas ouvrir",0,IF(L6="Ouvrir +1 classe",E6+'08_Moteur'!O3,E6))</f>
+        <f>IF(L6="Ne pas lancer",0,IF(L6="Ouvrir +1 classe",E6+'08_Moteur'!O3,E6))</f>
         <v/>
       </c>
       <c r="N6" s="17">
-        <f>IF(L6="Ne pas ouvrir",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Économiser 1 classe",H6+('08_Moteur'!AI3-MAX(1,'08_Moteur'!AI3-1))*'08_Moteur'!U3,H6)))</f>
+        <f>IF(L6="Ne pas lancer",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Regrouper (-1 classe)",H6+('08_Moteur'!AI3-MAX(1,'08_Moteur'!AI3-1))*'08_Moteur'!U3,H6)))</f>
         <v/>
       </c>
       <c r="O6" s="17">
@@ -2618,11 +2618,11 @@
         <v/>
       </c>
       <c r="J7" s="69">
-        <f>IF(H7&lt;0,"🔴 Ne pas ouvrir",IF(I7&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I7&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H7&lt;0,"🔴 Restructurer (mutualiser)",IF(I7&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K7" s="70">
-        <f>IF(H7&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I7&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I7&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -2631,11 +2631,11 @@
         </is>
       </c>
       <c r="M7" s="50">
-        <f>IF(L7="Ne pas ouvrir",0,IF(L7="Ouvrir +1 classe",E7+'08_Moteur'!O4,E7))</f>
+        <f>IF(L7="Ne pas lancer",0,IF(L7="Ouvrir +1 classe",E7+'08_Moteur'!O4,E7))</f>
         <v/>
       </c>
       <c r="N7" s="17">
-        <f>IF(L7="Ne pas ouvrir",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Économiser 1 classe",H7+('08_Moteur'!AI4-MAX(1,'08_Moteur'!AI4-1))*'08_Moteur'!U4,H7)))</f>
+        <f>IF(L7="Ne pas lancer",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Regrouper (-1 classe)",H7+('08_Moteur'!AI4-MAX(1,'08_Moteur'!AI4-1))*'08_Moteur'!U4,H7)))</f>
         <v/>
       </c>
       <c r="O7" s="17">
@@ -2689,11 +2689,11 @@
         <v/>
       </c>
       <c r="J8" s="69">
-        <f>IF(H8&lt;0,"🔴 Ne pas ouvrir",IF(I8&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I8&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H8&lt;0,"🔴 Restructurer (mutualiser)",IF(I8&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K8" s="70">
-        <f>IF(H8&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I8&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I8&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -2702,11 +2702,11 @@
         </is>
       </c>
       <c r="M8" s="50">
-        <f>IF(L8="Ne pas ouvrir",0,IF(L8="Ouvrir +1 classe",E8+'08_Moteur'!O5,E8))</f>
+        <f>IF(L8="Ne pas lancer",0,IF(L8="Ouvrir +1 classe",E8+'08_Moteur'!O5,E8))</f>
         <v/>
       </c>
       <c r="N8" s="17">
-        <f>IF(L8="Ne pas ouvrir",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Économiser 1 classe",H8+('08_Moteur'!AI5-MAX(1,'08_Moteur'!AI5-1))*'08_Moteur'!U5,H8)))</f>
+        <f>IF(L8="Ne pas lancer",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Regrouper (-1 classe)",H8+('08_Moteur'!AI5-MAX(1,'08_Moteur'!AI5-1))*'08_Moteur'!U5,H8)))</f>
         <v/>
       </c>
       <c r="O8" s="17">
@@ -2760,11 +2760,11 @@
         <v/>
       </c>
       <c r="J9" s="69">
-        <f>IF(H9&lt;0,"🔴 Ne pas ouvrir",IF(I9&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I9&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H9&lt;0,"🔴 Ne pas lancer",IF(I9&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I9&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K9" s="70">
-        <f>IF(H9&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I9&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I9&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H9&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I9&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I9&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -2773,11 +2773,11 @@
         </is>
       </c>
       <c r="M9" s="50">
-        <f>IF(L9="Ne pas ouvrir",0,IF(L9="Ouvrir +1 classe",E9+'08_Moteur'!O6,E9))</f>
+        <f>IF(L9="Ne pas lancer",0,IF(L9="Ouvrir +1 classe",E9+'08_Moteur'!O6,E9))</f>
         <v/>
       </c>
       <c r="N9" s="17">
-        <f>IF(L9="Ne pas ouvrir",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Économiser 1 classe",H9+('08_Moteur'!AI6-MAX(1,'08_Moteur'!AI6-1))*'08_Moteur'!U6,H9)))</f>
+        <f>IF(L9="Ne pas lancer",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Regrouper (-1 classe)",H9+('08_Moteur'!AI6-MAX(1,'08_Moteur'!AI6-1))*'08_Moteur'!U6,H9)))</f>
         <v/>
       </c>
       <c r="O9" s="17">
@@ -2831,11 +2831,11 @@
         <v/>
       </c>
       <c r="J10" s="69">
-        <f>IF(H10&lt;0,"🔴 Ne pas ouvrir",IF(I10&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I10&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H10&lt;0,"🔴 Restructurer (mutualiser)",IF(I10&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K10" s="70">
-        <f>IF(H10&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I10&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I10&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="M10" s="50">
-        <f>IF(L10="Ne pas ouvrir",0,IF(L10="Ouvrir +1 classe",E10+'08_Moteur'!O7,E10))</f>
+        <f>IF(L10="Ne pas lancer",0,IF(L10="Ouvrir +1 classe",E10+'08_Moteur'!O7,E10))</f>
         <v/>
       </c>
       <c r="N10" s="17">
-        <f>IF(L10="Ne pas ouvrir",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Économiser 1 classe",H10+('08_Moteur'!AI7-MAX(1,'08_Moteur'!AI7-1))*'08_Moteur'!U7,H10)))</f>
+        <f>IF(L10="Ne pas lancer",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Regrouper (-1 classe)",H10+('08_Moteur'!AI7-MAX(1,'08_Moteur'!AI7-1))*'08_Moteur'!U7,H10)))</f>
         <v/>
       </c>
       <c r="O10" s="17">
@@ -2902,11 +2902,11 @@
         <v/>
       </c>
       <c r="J11" s="69">
-        <f>IF(H11&lt;0,"🔴 Ne pas ouvrir",IF(I11&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I11&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H11&lt;0,"🔴 Ne pas lancer",IF(I11&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I11&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K11" s="70">
-        <f>IF(H11&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I11&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I11&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H11&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I11&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I11&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -2915,11 +2915,11 @@
         </is>
       </c>
       <c r="M11" s="50">
-        <f>IF(L11="Ne pas ouvrir",0,IF(L11="Ouvrir +1 classe",E11+'08_Moteur'!O8,E11))</f>
+        <f>IF(L11="Ne pas lancer",0,IF(L11="Ouvrir +1 classe",E11+'08_Moteur'!O8,E11))</f>
         <v/>
       </c>
       <c r="N11" s="17">
-        <f>IF(L11="Ne pas ouvrir",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Économiser 1 classe",H11+('08_Moteur'!AI8-MAX(1,'08_Moteur'!AI8-1))*'08_Moteur'!U8,H11)))</f>
+        <f>IF(L11="Ne pas lancer",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Regrouper (-1 classe)",H11+('08_Moteur'!AI8-MAX(1,'08_Moteur'!AI8-1))*'08_Moteur'!U8,H11)))</f>
         <v/>
       </c>
       <c r="O11" s="17">
@@ -2973,11 +2973,11 @@
         <v/>
       </c>
       <c r="J12" s="69">
-        <f>IF(H12&lt;0,"🔴 Ne pas ouvrir",IF(I12&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I12&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H12&lt;0,"🔴 Restructurer (mutualiser)",IF(I12&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K12" s="70">
-        <f>IF(H12&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I12&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I12&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -2986,11 +2986,11 @@
         </is>
       </c>
       <c r="M12" s="50">
-        <f>IF(L12="Ne pas ouvrir",0,IF(L12="Ouvrir +1 classe",E12+'08_Moteur'!O9,E12))</f>
+        <f>IF(L12="Ne pas lancer",0,IF(L12="Ouvrir +1 classe",E12+'08_Moteur'!O9,E12))</f>
         <v/>
       </c>
       <c r="N12" s="17">
-        <f>IF(L12="Ne pas ouvrir",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Économiser 1 classe",H12+('08_Moteur'!AI9-MAX(1,'08_Moteur'!AI9-1))*'08_Moteur'!U9,H12)))</f>
+        <f>IF(L12="Ne pas lancer",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Regrouper (-1 classe)",H12+('08_Moteur'!AI9-MAX(1,'08_Moteur'!AI9-1))*'08_Moteur'!U9,H12)))</f>
         <v/>
       </c>
       <c r="O12" s="17">
@@ -3044,11 +3044,11 @@
         <v/>
       </c>
       <c r="J13" s="69">
-        <f>IF(H13&lt;0,"🔴 Ne pas ouvrir",IF(I13&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I13&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H13&lt;0,"🔴 Restructurer (mutualiser)",IF(I13&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K13" s="70">
-        <f>IF(H13&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I13&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I13&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -3057,11 +3057,11 @@
         </is>
       </c>
       <c r="M13" s="50">
-        <f>IF(L13="Ne pas ouvrir",0,IF(L13="Ouvrir +1 classe",E13+'08_Moteur'!O10,E13))</f>
+        <f>IF(L13="Ne pas lancer",0,IF(L13="Ouvrir +1 classe",E13+'08_Moteur'!O10,E13))</f>
         <v/>
       </c>
       <c r="N13" s="17">
-        <f>IF(L13="Ne pas ouvrir",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Économiser 1 classe",H13+('08_Moteur'!AI10-MAX(1,'08_Moteur'!AI10-1))*'08_Moteur'!U10,H13)))</f>
+        <f>IF(L13="Ne pas lancer",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Regrouper (-1 classe)",H13+('08_Moteur'!AI10-MAX(1,'08_Moteur'!AI10-1))*'08_Moteur'!U10,H13)))</f>
         <v/>
       </c>
       <c r="O13" s="17">
@@ -3115,11 +3115,11 @@
         <v/>
       </c>
       <c r="J14" s="69">
-        <f>IF(H14&lt;0,"🔴 Ne pas ouvrir",IF(I14&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I14&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H14&lt;0,"🔴 Ne pas lancer",IF(I14&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I14&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K14" s="70">
-        <f>IF(H14&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I14&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I14&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H14&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I14&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I14&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -3128,11 +3128,11 @@
         </is>
       </c>
       <c r="M14" s="50">
-        <f>IF(L14="Ne pas ouvrir",0,IF(L14="Ouvrir +1 classe",E14+'08_Moteur'!O11,E14))</f>
+        <f>IF(L14="Ne pas lancer",0,IF(L14="Ouvrir +1 classe",E14+'08_Moteur'!O11,E14))</f>
         <v/>
       </c>
       <c r="N14" s="17">
-        <f>IF(L14="Ne pas ouvrir",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Économiser 1 classe",H14+('08_Moteur'!AI11-MAX(1,'08_Moteur'!AI11-1))*'08_Moteur'!U11,H14)))</f>
+        <f>IF(L14="Ne pas lancer",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Regrouper (-1 classe)",H14+('08_Moteur'!AI11-MAX(1,'08_Moteur'!AI11-1))*'08_Moteur'!U11,H14)))</f>
         <v/>
       </c>
       <c r="O14" s="17">
@@ -3186,11 +3186,11 @@
         <v/>
       </c>
       <c r="J15" s="69">
-        <f>IF(H15&lt;0,"🔴 Ne pas ouvrir",IF(I15&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I15&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H15&lt;0,"🔴 Restructurer (mutualiser)",IF(I15&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K15" s="70">
-        <f>IF(H15&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I15&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I15&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -3199,11 +3199,11 @@
         </is>
       </c>
       <c r="M15" s="50">
-        <f>IF(L15="Ne pas ouvrir",0,IF(L15="Ouvrir +1 classe",E15+'08_Moteur'!O12,E15))</f>
+        <f>IF(L15="Ne pas lancer",0,IF(L15="Ouvrir +1 classe",E15+'08_Moteur'!O12,E15))</f>
         <v/>
       </c>
       <c r="N15" s="17">
-        <f>IF(L15="Ne pas ouvrir",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Économiser 1 classe",H15+('08_Moteur'!AI12-MAX(1,'08_Moteur'!AI12-1))*'08_Moteur'!U12,H15)))</f>
+        <f>IF(L15="Ne pas lancer",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Regrouper (-1 classe)",H15+('08_Moteur'!AI12-MAX(1,'08_Moteur'!AI12-1))*'08_Moteur'!U12,H15)))</f>
         <v/>
       </c>
       <c r="O15" s="17">
@@ -3257,11 +3257,11 @@
         <v/>
       </c>
       <c r="J16" s="69">
-        <f>IF(H16&lt;0,"🔴 Ne pas ouvrir",IF(I16&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I16&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H16&lt;0,"🔴 Ne pas lancer",IF(I16&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I16&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K16" s="70">
-        <f>IF(H16&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I16&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I16&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H16&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I16&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I16&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -3270,11 +3270,11 @@
         </is>
       </c>
       <c r="M16" s="50">
-        <f>IF(L16="Ne pas ouvrir",0,IF(L16="Ouvrir +1 classe",E16+'08_Moteur'!O13,E16))</f>
+        <f>IF(L16="Ne pas lancer",0,IF(L16="Ouvrir +1 classe",E16+'08_Moteur'!O13,E16))</f>
         <v/>
       </c>
       <c r="N16" s="17">
-        <f>IF(L16="Ne pas ouvrir",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Économiser 1 classe",H16+('08_Moteur'!AI13-MAX(1,'08_Moteur'!AI13-1))*'08_Moteur'!U13,H16)))</f>
+        <f>IF(L16="Ne pas lancer",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Regrouper (-1 classe)",H16+('08_Moteur'!AI13-MAX(1,'08_Moteur'!AI13-1))*'08_Moteur'!U13,H16)))</f>
         <v/>
       </c>
       <c r="O16" s="17">
@@ -3328,11 +3328,11 @@
         <v/>
       </c>
       <c r="J17" s="69">
-        <f>IF(H17&lt;0,"🔴 Ne pas ouvrir",IF(I17&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I17&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H17&lt;0,"🔴 Restructurer (mutualiser)",IF(I17&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K17" s="70">
-        <f>IF(H17&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I17&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I17&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -3341,11 +3341,11 @@
         </is>
       </c>
       <c r="M17" s="50">
-        <f>IF(L17="Ne pas ouvrir",0,IF(L17="Ouvrir +1 classe",E17+'08_Moteur'!O14,E17))</f>
+        <f>IF(L17="Ne pas lancer",0,IF(L17="Ouvrir +1 classe",E17+'08_Moteur'!O14,E17))</f>
         <v/>
       </c>
       <c r="N17" s="17">
-        <f>IF(L17="Ne pas ouvrir",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Économiser 1 classe",H17+('08_Moteur'!AI14-MAX(1,'08_Moteur'!AI14-1))*'08_Moteur'!U14,H17)))</f>
+        <f>IF(L17="Ne pas lancer",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Regrouper (-1 classe)",H17+('08_Moteur'!AI14-MAX(1,'08_Moteur'!AI14-1))*'08_Moteur'!U14,H17)))</f>
         <v/>
       </c>
       <c r="O17" s="17">
@@ -3399,11 +3399,11 @@
         <v/>
       </c>
       <c r="J18" s="69">
-        <f>IF(H18&lt;0,"🔴 Ne pas ouvrir",IF(I18&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I18&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H18&lt;0,"🔴 Restructurer (mutualiser)",IF(I18&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K18" s="70">
-        <f>IF(H18&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I18&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I18&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -3412,11 +3412,11 @@
         </is>
       </c>
       <c r="M18" s="50">
-        <f>IF(L18="Ne pas ouvrir",0,IF(L18="Ouvrir +1 classe",E18+'08_Moteur'!O15,E18))</f>
+        <f>IF(L18="Ne pas lancer",0,IF(L18="Ouvrir +1 classe",E18+'08_Moteur'!O15,E18))</f>
         <v/>
       </c>
       <c r="N18" s="17">
-        <f>IF(L18="Ne pas ouvrir",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Économiser 1 classe",H18+('08_Moteur'!AI15-MAX(1,'08_Moteur'!AI15-1))*'08_Moteur'!U15,H18)))</f>
+        <f>IF(L18="Ne pas lancer",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Regrouper (-1 classe)",H18+('08_Moteur'!AI15-MAX(1,'08_Moteur'!AI15-1))*'08_Moteur'!U15,H18)))</f>
         <v/>
       </c>
       <c r="O18" s="17">
@@ -3470,11 +3470,11 @@
         <v/>
       </c>
       <c r="J19" s="69">
-        <f>IF(H19&lt;0,"🔴 Ne pas ouvrir",IF(I19&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I19&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H19&lt;0,"🔴 Ne pas lancer",IF(I19&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I19&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K19" s="70">
-        <f>IF(H19&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I19&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I19&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H19&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I19&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I19&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -3483,11 +3483,11 @@
         </is>
       </c>
       <c r="M19" s="50">
-        <f>IF(L19="Ne pas ouvrir",0,IF(L19="Ouvrir +1 classe",E19+'08_Moteur'!O16,E19))</f>
+        <f>IF(L19="Ne pas lancer",0,IF(L19="Ouvrir +1 classe",E19+'08_Moteur'!O16,E19))</f>
         <v/>
       </c>
       <c r="N19" s="17">
-        <f>IF(L19="Ne pas ouvrir",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Économiser 1 classe",H19+('08_Moteur'!AI16-MAX(1,'08_Moteur'!AI16-1))*'08_Moteur'!U16,H19)))</f>
+        <f>IF(L19="Ne pas lancer",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Regrouper (-1 classe)",H19+('08_Moteur'!AI16-MAX(1,'08_Moteur'!AI16-1))*'08_Moteur'!U16,H19)))</f>
         <v/>
       </c>
       <c r="O19" s="17">
@@ -3541,11 +3541,11 @@
         <v/>
       </c>
       <c r="J20" s="69">
-        <f>IF(H20&lt;0,"🔴 Ne pas ouvrir",IF(I20&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I20&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H20&lt;0,"🔴 Restructurer (mutualiser)",IF(I20&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K20" s="70">
-        <f>IF(H20&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I20&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I20&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -3554,11 +3554,11 @@
         </is>
       </c>
       <c r="M20" s="50">
-        <f>IF(L20="Ne pas ouvrir",0,IF(L20="Ouvrir +1 classe",E20+'08_Moteur'!O17,E20))</f>
+        <f>IF(L20="Ne pas lancer",0,IF(L20="Ouvrir +1 classe",E20+'08_Moteur'!O17,E20))</f>
         <v/>
       </c>
       <c r="N20" s="17">
-        <f>IF(L20="Ne pas ouvrir",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Économiser 1 classe",H20+('08_Moteur'!AI17-MAX(1,'08_Moteur'!AI17-1))*'08_Moteur'!U17,H20)))</f>
+        <f>IF(L20="Ne pas lancer",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Regrouper (-1 classe)",H20+('08_Moteur'!AI17-MAX(1,'08_Moteur'!AI17-1))*'08_Moteur'!U17,H20)))</f>
         <v/>
       </c>
       <c r="O20" s="17">
@@ -3612,11 +3612,11 @@
         <v/>
       </c>
       <c r="J21" s="69">
-        <f>IF(H21&lt;0,"🔴 Ne pas ouvrir",IF(I21&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I21&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H21&lt;0,"🔴 Ne pas lancer",IF(I21&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I21&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K21" s="70">
-        <f>IF(H21&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I21&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I21&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H21&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I21&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I21&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -3625,11 +3625,11 @@
         </is>
       </c>
       <c r="M21" s="50">
-        <f>IF(L21="Ne pas ouvrir",0,IF(L21="Ouvrir +1 classe",E21+'08_Moteur'!O18,E21))</f>
+        <f>IF(L21="Ne pas lancer",0,IF(L21="Ouvrir +1 classe",E21+'08_Moteur'!O18,E21))</f>
         <v/>
       </c>
       <c r="N21" s="17">
-        <f>IF(L21="Ne pas ouvrir",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Économiser 1 classe",H21+('08_Moteur'!AI18-MAX(1,'08_Moteur'!AI18-1))*'08_Moteur'!U18,H21)))</f>
+        <f>IF(L21="Ne pas lancer",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Regrouper (-1 classe)",H21+('08_Moteur'!AI18-MAX(1,'08_Moteur'!AI18-1))*'08_Moteur'!U18,H21)))</f>
         <v/>
       </c>
       <c r="O21" s="17">
@@ -3683,11 +3683,11 @@
         <v/>
       </c>
       <c r="J22" s="69">
-        <f>IF(H22&lt;0,"🔴 Ne pas ouvrir",IF(I22&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I22&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H22&lt;0,"🔴 Restructurer (mutualiser)",IF(I22&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K22" s="70">
-        <f>IF(H22&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I22&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I22&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -3696,11 +3696,11 @@
         </is>
       </c>
       <c r="M22" s="50">
-        <f>IF(L22="Ne pas ouvrir",0,IF(L22="Ouvrir +1 classe",E22+'08_Moteur'!O19,E22))</f>
+        <f>IF(L22="Ne pas lancer",0,IF(L22="Ouvrir +1 classe",E22+'08_Moteur'!O19,E22))</f>
         <v/>
       </c>
       <c r="N22" s="17">
-        <f>IF(L22="Ne pas ouvrir",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Économiser 1 classe",H22+('08_Moteur'!AI19-MAX(1,'08_Moteur'!AI19-1))*'08_Moteur'!U19,H22)))</f>
+        <f>IF(L22="Ne pas lancer",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Regrouper (-1 classe)",H22+('08_Moteur'!AI19-MAX(1,'08_Moteur'!AI19-1))*'08_Moteur'!U19,H22)))</f>
         <v/>
       </c>
       <c r="O22" s="17">
@@ -3754,11 +3754,11 @@
         <v/>
       </c>
       <c r="J23" s="69">
-        <f>IF(H23&lt;0,"🔴 Ne pas ouvrir",IF(I23&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I23&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H23&lt;0,"🔴 Restructurer (mutualiser)",IF(I23&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K23" s="70">
-        <f>IF(H23&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I23&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I23&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -3767,11 +3767,11 @@
         </is>
       </c>
       <c r="M23" s="50">
-        <f>IF(L23="Ne pas ouvrir",0,IF(L23="Ouvrir +1 classe",E23+'08_Moteur'!O20,E23))</f>
+        <f>IF(L23="Ne pas lancer",0,IF(L23="Ouvrir +1 classe",E23+'08_Moteur'!O20,E23))</f>
         <v/>
       </c>
       <c r="N23" s="17">
-        <f>IF(L23="Ne pas ouvrir",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Économiser 1 classe",H23+('08_Moteur'!AI20-MAX(1,'08_Moteur'!AI20-1))*'08_Moteur'!U20,H23)))</f>
+        <f>IF(L23="Ne pas lancer",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Regrouper (-1 classe)",H23+('08_Moteur'!AI20-MAX(1,'08_Moteur'!AI20-1))*'08_Moteur'!U20,H23)))</f>
         <v/>
       </c>
       <c r="O23" s="17">
@@ -3825,11 +3825,11 @@
         <v/>
       </c>
       <c r="J24" s="69">
-        <f>IF(H24&lt;0,"🔴 Ne pas ouvrir",IF(I24&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I24&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H24&lt;0,"🔴 Ne pas lancer",IF(I24&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I24&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K24" s="70">
-        <f>IF(H24&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I24&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I24&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H24&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I24&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I24&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -3838,11 +3838,11 @@
         </is>
       </c>
       <c r="M24" s="50">
-        <f>IF(L24="Ne pas ouvrir",0,IF(L24="Ouvrir +1 classe",E24+'08_Moteur'!O21,E24))</f>
+        <f>IF(L24="Ne pas lancer",0,IF(L24="Ouvrir +1 classe",E24+'08_Moteur'!O21,E24))</f>
         <v/>
       </c>
       <c r="N24" s="17">
-        <f>IF(L24="Ne pas ouvrir",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Économiser 1 classe",H24+('08_Moteur'!AI21-MAX(1,'08_Moteur'!AI21-1))*'08_Moteur'!U21,H24)))</f>
+        <f>IF(L24="Ne pas lancer",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Regrouper (-1 classe)",H24+('08_Moteur'!AI21-MAX(1,'08_Moteur'!AI21-1))*'08_Moteur'!U21,H24)))</f>
         <v/>
       </c>
       <c r="O24" s="17">
@@ -3896,11 +3896,11 @@
         <v/>
       </c>
       <c r="J25" s="69">
-        <f>IF(H25&lt;0,"🔴 Ne pas ouvrir",IF(I25&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I25&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H25&lt;0,"🔴 Restructurer (mutualiser)",IF(I25&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K25" s="70">
-        <f>IF(H25&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I25&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I25&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -3909,11 +3909,11 @@
         </is>
       </c>
       <c r="M25" s="50">
-        <f>IF(L25="Ne pas ouvrir",0,IF(L25="Ouvrir +1 classe",E25+'08_Moteur'!O22,E25))</f>
+        <f>IF(L25="Ne pas lancer",0,IF(L25="Ouvrir +1 classe",E25+'08_Moteur'!O22,E25))</f>
         <v/>
       </c>
       <c r="N25" s="17">
-        <f>IF(L25="Ne pas ouvrir",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Économiser 1 classe",H25+('08_Moteur'!AI22-MAX(1,'08_Moteur'!AI22-1))*'08_Moteur'!U22,H25)))</f>
+        <f>IF(L25="Ne pas lancer",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Regrouper (-1 classe)",H25+('08_Moteur'!AI22-MAX(1,'08_Moteur'!AI22-1))*'08_Moteur'!U22,H25)))</f>
         <v/>
       </c>
       <c r="O25" s="17">
@@ -3967,11 +3967,11 @@
         <v/>
       </c>
       <c r="J26" s="69">
-        <f>IF(H26&lt;0,"🔴 Ne pas ouvrir",IF(I26&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I26&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H26&lt;0,"🔴 Ne pas lancer",IF(I26&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I26&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K26" s="70">
-        <f>IF(H26&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I26&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I26&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H26&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I26&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I26&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -3980,11 +3980,11 @@
         </is>
       </c>
       <c r="M26" s="50">
-        <f>IF(L26="Ne pas ouvrir",0,IF(L26="Ouvrir +1 classe",E26+'08_Moteur'!O23,E26))</f>
+        <f>IF(L26="Ne pas lancer",0,IF(L26="Ouvrir +1 classe",E26+'08_Moteur'!O23,E26))</f>
         <v/>
       </c>
       <c r="N26" s="17">
-        <f>IF(L26="Ne pas ouvrir",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Économiser 1 classe",H26+('08_Moteur'!AI23-MAX(1,'08_Moteur'!AI23-1))*'08_Moteur'!U23,H26)))</f>
+        <f>IF(L26="Ne pas lancer",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Regrouper (-1 classe)",H26+('08_Moteur'!AI23-MAX(1,'08_Moteur'!AI23-1))*'08_Moteur'!U23,H26)))</f>
         <v/>
       </c>
       <c r="O26" s="17">
@@ -4038,11 +4038,11 @@
         <v/>
       </c>
       <c r="J27" s="69">
-        <f>IF(H27&lt;0,"🔴 Ne pas ouvrir",IF(I27&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I27&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H27&lt;0,"🔴 Restructurer (mutualiser)",IF(I27&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K27" s="70">
-        <f>IF(H27&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I27&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I27&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -4051,11 +4051,11 @@
         </is>
       </c>
       <c r="M27" s="50">
-        <f>IF(L27="Ne pas ouvrir",0,IF(L27="Ouvrir +1 classe",E27+'08_Moteur'!O24,E27))</f>
+        <f>IF(L27="Ne pas lancer",0,IF(L27="Ouvrir +1 classe",E27+'08_Moteur'!O24,E27))</f>
         <v/>
       </c>
       <c r="N27" s="17">
-        <f>IF(L27="Ne pas ouvrir",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Économiser 1 classe",H27+('08_Moteur'!AI24-MAX(1,'08_Moteur'!AI24-1))*'08_Moteur'!U24,H27)))</f>
+        <f>IF(L27="Ne pas lancer",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Regrouper (-1 classe)",H27+('08_Moteur'!AI24-MAX(1,'08_Moteur'!AI24-1))*'08_Moteur'!U24,H27)))</f>
         <v/>
       </c>
       <c r="O27" s="17">
@@ -4109,11 +4109,11 @@
         <v/>
       </c>
       <c r="J28" s="69">
-        <f>IF(H28&lt;0,"🔴 Ne pas ouvrir",IF(I28&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I28&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H28&lt;0,"🔴 Restructurer (mutualiser)",IF(I28&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K28" s="70">
-        <f>IF(H28&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I28&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I28&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -4122,11 +4122,11 @@
         </is>
       </c>
       <c r="M28" s="50">
-        <f>IF(L28="Ne pas ouvrir",0,IF(L28="Ouvrir +1 classe",E28+'08_Moteur'!O25,E28))</f>
+        <f>IF(L28="Ne pas lancer",0,IF(L28="Ouvrir +1 classe",E28+'08_Moteur'!O25,E28))</f>
         <v/>
       </c>
       <c r="N28" s="17">
-        <f>IF(L28="Ne pas ouvrir",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Économiser 1 classe",H28+('08_Moteur'!AI25-MAX(1,'08_Moteur'!AI25-1))*'08_Moteur'!U25,H28)))</f>
+        <f>IF(L28="Ne pas lancer",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Regrouper (-1 classe)",H28+('08_Moteur'!AI25-MAX(1,'08_Moteur'!AI25-1))*'08_Moteur'!U25,H28)))</f>
         <v/>
       </c>
       <c r="O28" s="17">
@@ -4180,11 +4180,11 @@
         <v/>
       </c>
       <c r="J29" s="69">
-        <f>IF(H29&lt;0,"🔴 Ne pas ouvrir",IF(I29&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I29&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H29&lt;0,"🔴 Ne pas lancer",IF(I29&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I29&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K29" s="70">
-        <f>IF(H29&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I29&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I29&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H29&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I29&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I29&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -4193,11 +4193,11 @@
         </is>
       </c>
       <c r="M29" s="50">
-        <f>IF(L29="Ne pas ouvrir",0,IF(L29="Ouvrir +1 classe",E29+'08_Moteur'!O26,E29))</f>
+        <f>IF(L29="Ne pas lancer",0,IF(L29="Ouvrir +1 classe",E29+'08_Moteur'!O26,E29))</f>
         <v/>
       </c>
       <c r="N29" s="17">
-        <f>IF(L29="Ne pas ouvrir",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Économiser 1 classe",H29+('08_Moteur'!AI26-MAX(1,'08_Moteur'!AI26-1))*'08_Moteur'!U26,H29)))</f>
+        <f>IF(L29="Ne pas lancer",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Regrouper (-1 classe)",H29+('08_Moteur'!AI26-MAX(1,'08_Moteur'!AI26-1))*'08_Moteur'!U26,H29)))</f>
         <v/>
       </c>
       <c r="O29" s="17">
@@ -4251,11 +4251,11 @@
         <v/>
       </c>
       <c r="J30" s="69">
-        <f>IF(H30&lt;0,"🔴 Ne pas ouvrir",IF(I30&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I30&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H30&lt;0,"🔴 Restructurer (mutualiser)",IF(I30&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K30" s="70">
-        <f>IF(H30&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I30&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I30&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -4264,11 +4264,11 @@
         </is>
       </c>
       <c r="M30" s="50">
-        <f>IF(L30="Ne pas ouvrir",0,IF(L30="Ouvrir +1 classe",E30+'08_Moteur'!O27,E30))</f>
+        <f>IF(L30="Ne pas lancer",0,IF(L30="Ouvrir +1 classe",E30+'08_Moteur'!O27,E30))</f>
         <v/>
       </c>
       <c r="N30" s="17">
-        <f>IF(L30="Ne pas ouvrir",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Économiser 1 classe",H30+('08_Moteur'!AI27-MAX(1,'08_Moteur'!AI27-1))*'08_Moteur'!U27,H30)))</f>
+        <f>IF(L30="Ne pas lancer",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Regrouper (-1 classe)",H30+('08_Moteur'!AI27-MAX(1,'08_Moteur'!AI27-1))*'08_Moteur'!U27,H30)))</f>
         <v/>
       </c>
       <c r="O30" s="17">
@@ -4322,11 +4322,11 @@
         <v/>
       </c>
       <c r="J31" s="69">
-        <f>IF(H31&lt;0,"🔴 Ne pas ouvrir",IF(I31&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I31&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H31&lt;0,"🔴 Ne pas lancer",IF(I31&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I31&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K31" s="70">
-        <f>IF(H31&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I31&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I31&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H31&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I31&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I31&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="M31" s="50">
-        <f>IF(L31="Ne pas ouvrir",0,IF(L31="Ouvrir +1 classe",E31+'08_Moteur'!O28,E31))</f>
+        <f>IF(L31="Ne pas lancer",0,IF(L31="Ouvrir +1 classe",E31+'08_Moteur'!O28,E31))</f>
         <v/>
       </c>
       <c r="N31" s="17">
-        <f>IF(L31="Ne pas ouvrir",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Économiser 1 classe",H31+('08_Moteur'!AI28-MAX(1,'08_Moteur'!AI28-1))*'08_Moteur'!U28,H31)))</f>
+        <f>IF(L31="Ne pas lancer",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Regrouper (-1 classe)",H31+('08_Moteur'!AI28-MAX(1,'08_Moteur'!AI28-1))*'08_Moteur'!U28,H31)))</f>
         <v/>
       </c>
       <c r="O31" s="17">
@@ -4393,11 +4393,11 @@
         <v/>
       </c>
       <c r="J32" s="69">
-        <f>IF(H32&lt;0,"🔴 Ne pas ouvrir",IF(I32&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I32&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H32&lt;0,"🔴 Restructurer (mutualiser)",IF(I32&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K32" s="70">
-        <f>IF(H32&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I32&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I32&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -4406,11 +4406,11 @@
         </is>
       </c>
       <c r="M32" s="50">
-        <f>IF(L32="Ne pas ouvrir",0,IF(L32="Ouvrir +1 classe",E32+'08_Moteur'!O29,E32))</f>
+        <f>IF(L32="Ne pas lancer",0,IF(L32="Ouvrir +1 classe",E32+'08_Moteur'!O29,E32))</f>
         <v/>
       </c>
       <c r="N32" s="17">
-        <f>IF(L32="Ne pas ouvrir",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Économiser 1 classe",H32+('08_Moteur'!AI29-MAX(1,'08_Moteur'!AI29-1))*'08_Moteur'!U29,H32)))</f>
+        <f>IF(L32="Ne pas lancer",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Regrouper (-1 classe)",H32+('08_Moteur'!AI29-MAX(1,'08_Moteur'!AI29-1))*'08_Moteur'!U29,H32)))</f>
         <v/>
       </c>
       <c r="O32" s="17">
@@ -4464,11 +4464,11 @@
         <v/>
       </c>
       <c r="J33" s="69">
-        <f>IF(H33&lt;0,"🔴 Ne pas ouvrir",IF(I33&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I33&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H33&lt;0,"🔴 Restructurer (mutualiser)",IF(I33&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K33" s="70">
-        <f>IF(H33&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I33&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I33&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -4477,11 +4477,11 @@
         </is>
       </c>
       <c r="M33" s="50">
-        <f>IF(L33="Ne pas ouvrir",0,IF(L33="Ouvrir +1 classe",E33+'08_Moteur'!O30,E33))</f>
+        <f>IF(L33="Ne pas lancer",0,IF(L33="Ouvrir +1 classe",E33+'08_Moteur'!O30,E33))</f>
         <v/>
       </c>
       <c r="N33" s="17">
-        <f>IF(L33="Ne pas ouvrir",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Économiser 1 classe",H33+('08_Moteur'!AI30-MAX(1,'08_Moteur'!AI30-1))*'08_Moteur'!U30,H33)))</f>
+        <f>IF(L33="Ne pas lancer",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Regrouper (-1 classe)",H33+('08_Moteur'!AI30-MAX(1,'08_Moteur'!AI30-1))*'08_Moteur'!U30,H33)))</f>
         <v/>
       </c>
       <c r="O33" s="17">
@@ -4535,11 +4535,11 @@
         <v/>
       </c>
       <c r="J34" s="69">
-        <f>IF(H34&lt;0,"🔴 Ne pas ouvrir",IF(I34&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I34&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H34&lt;0,"🔴 Ne pas lancer",IF(I34&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I34&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K34" s="70">
-        <f>IF(H34&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I34&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I34&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H34&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I34&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I34&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L34" s="21" t="inlineStr">
@@ -4548,11 +4548,11 @@
         </is>
       </c>
       <c r="M34" s="50">
-        <f>IF(L34="Ne pas ouvrir",0,IF(L34="Ouvrir +1 classe",E34+'08_Moteur'!O31,E34))</f>
+        <f>IF(L34="Ne pas lancer",0,IF(L34="Ouvrir +1 classe",E34+'08_Moteur'!O31,E34))</f>
         <v/>
       </c>
       <c r="N34" s="17">
-        <f>IF(L34="Ne pas ouvrir",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Économiser 1 classe",H34+('08_Moteur'!AI31-MAX(1,'08_Moteur'!AI31-1))*'08_Moteur'!U31,H34)))</f>
+        <f>IF(L34="Ne pas lancer",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Regrouper (-1 classe)",H34+('08_Moteur'!AI31-MAX(1,'08_Moteur'!AI31-1))*'08_Moteur'!U31,H34)))</f>
         <v/>
       </c>
       <c r="O34" s="17">
@@ -4606,11 +4606,11 @@
         <v/>
       </c>
       <c r="J35" s="69">
-        <f>IF(H35&lt;0,"🔴 Ne pas ouvrir",IF(I35&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I35&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H35&lt;0,"🔴 Restructurer (mutualiser)",IF(I35&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K35" s="70">
-        <f>IF(H35&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I35&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I35&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L35" s="21" t="inlineStr">
@@ -4619,11 +4619,11 @@
         </is>
       </c>
       <c r="M35" s="50">
-        <f>IF(L35="Ne pas ouvrir",0,IF(L35="Ouvrir +1 classe",E35+'08_Moteur'!O32,E35))</f>
+        <f>IF(L35="Ne pas lancer",0,IF(L35="Ouvrir +1 classe",E35+'08_Moteur'!O32,E35))</f>
         <v/>
       </c>
       <c r="N35" s="17">
-        <f>IF(L35="Ne pas ouvrir",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Économiser 1 classe",H35+('08_Moteur'!AI32-MAX(1,'08_Moteur'!AI32-1))*'08_Moteur'!U32,H35)))</f>
+        <f>IF(L35="Ne pas lancer",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Regrouper (-1 classe)",H35+('08_Moteur'!AI32-MAX(1,'08_Moteur'!AI32-1))*'08_Moteur'!U32,H35)))</f>
         <v/>
       </c>
       <c r="O35" s="17">
@@ -4677,11 +4677,11 @@
         <v/>
       </c>
       <c r="J36" s="69">
-        <f>IF(H36&lt;0,"🔴 Ne pas ouvrir",IF(I36&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I36&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H36&lt;0,"🔴 Ne pas lancer",IF(I36&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I36&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K36" s="70">
-        <f>IF(H36&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I36&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I36&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H36&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I36&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I36&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L36" s="21" t="inlineStr">
@@ -4690,11 +4690,11 @@
         </is>
       </c>
       <c r="M36" s="50">
-        <f>IF(L36="Ne pas ouvrir",0,IF(L36="Ouvrir +1 classe",E36+'08_Moteur'!O33,E36))</f>
+        <f>IF(L36="Ne pas lancer",0,IF(L36="Ouvrir +1 classe",E36+'08_Moteur'!O33,E36))</f>
         <v/>
       </c>
       <c r="N36" s="17">
-        <f>IF(L36="Ne pas ouvrir",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Économiser 1 classe",H36+('08_Moteur'!AI33-MAX(1,'08_Moteur'!AI33-1))*'08_Moteur'!U33,H36)))</f>
+        <f>IF(L36="Ne pas lancer",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Regrouper (-1 classe)",H36+('08_Moteur'!AI33-MAX(1,'08_Moteur'!AI33-1))*'08_Moteur'!U33,H36)))</f>
         <v/>
       </c>
       <c r="O36" s="17">
@@ -4748,11 +4748,11 @@
         <v/>
       </c>
       <c r="J37" s="69">
-        <f>IF(H37&lt;0,"🔴 Ne pas ouvrir",IF(I37&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I37&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H37&lt;0,"🔴 Restructurer (mutualiser)",IF(I37&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K37" s="70">
-        <f>IF(H37&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I37&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I37&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L37" s="21" t="inlineStr">
@@ -4761,11 +4761,11 @@
         </is>
       </c>
       <c r="M37" s="50">
-        <f>IF(L37="Ne pas ouvrir",0,IF(L37="Ouvrir +1 classe",E37+'08_Moteur'!O34,E37))</f>
+        <f>IF(L37="Ne pas lancer",0,IF(L37="Ouvrir +1 classe",E37+'08_Moteur'!O34,E37))</f>
         <v/>
       </c>
       <c r="N37" s="17">
-        <f>IF(L37="Ne pas ouvrir",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Économiser 1 classe",H37+('08_Moteur'!AI34-MAX(1,'08_Moteur'!AI34-1))*'08_Moteur'!U34,H37)))</f>
+        <f>IF(L37="Ne pas lancer",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Regrouper (-1 classe)",H37+('08_Moteur'!AI34-MAX(1,'08_Moteur'!AI34-1))*'08_Moteur'!U34,H37)))</f>
         <v/>
       </c>
       <c r="O37" s="17">
@@ -4819,11 +4819,11 @@
         <v/>
       </c>
       <c r="J38" s="69">
-        <f>IF(H38&lt;0,"🔴 Ne pas ouvrir",IF(I38&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I38&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H38&lt;0,"🔴 Restructurer (mutualiser)",IF(I38&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K38" s="70">
-        <f>IF(H38&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I38&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I38&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L38" s="21" t="inlineStr">
@@ -4832,11 +4832,11 @@
         </is>
       </c>
       <c r="M38" s="50">
-        <f>IF(L38="Ne pas ouvrir",0,IF(L38="Ouvrir +1 classe",E38+'08_Moteur'!O35,E38))</f>
+        <f>IF(L38="Ne pas lancer",0,IF(L38="Ouvrir +1 classe",E38+'08_Moteur'!O35,E38))</f>
         <v/>
       </c>
       <c r="N38" s="17">
-        <f>IF(L38="Ne pas ouvrir",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Économiser 1 classe",H38+('08_Moteur'!AI35-MAX(1,'08_Moteur'!AI35-1))*'08_Moteur'!U35,H38)))</f>
+        <f>IF(L38="Ne pas lancer",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Regrouper (-1 classe)",H38+('08_Moteur'!AI35-MAX(1,'08_Moteur'!AI35-1))*'08_Moteur'!U35,H38)))</f>
         <v/>
       </c>
       <c r="O38" s="17">
@@ -4890,11 +4890,11 @@
         <v/>
       </c>
       <c r="J39" s="69">
-        <f>IF(H39&lt;0,"🔴 Ne pas ouvrir",IF(I39&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I39&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H39&lt;0,"🔴 Ne pas lancer",IF(I39&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I39&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K39" s="70">
-        <f>IF(H39&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I39&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I39&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H39&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I39&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I39&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L39" s="21" t="inlineStr">
@@ -4903,11 +4903,11 @@
         </is>
       </c>
       <c r="M39" s="50">
-        <f>IF(L39="Ne pas ouvrir",0,IF(L39="Ouvrir +1 classe",E39+'08_Moteur'!O36,E39))</f>
+        <f>IF(L39="Ne pas lancer",0,IF(L39="Ouvrir +1 classe",E39+'08_Moteur'!O36,E39))</f>
         <v/>
       </c>
       <c r="N39" s="17">
-        <f>IF(L39="Ne pas ouvrir",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Économiser 1 classe",H39+('08_Moteur'!AI36-MAX(1,'08_Moteur'!AI36-1))*'08_Moteur'!U36,H39)))</f>
+        <f>IF(L39="Ne pas lancer",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Regrouper (-1 classe)",H39+('08_Moteur'!AI36-MAX(1,'08_Moteur'!AI36-1))*'08_Moteur'!U36,H39)))</f>
         <v/>
       </c>
       <c r="O39" s="17">
@@ -4961,11 +4961,11 @@
         <v/>
       </c>
       <c r="J40" s="69">
-        <f>IF(H40&lt;0,"🔴 Ne pas ouvrir",IF(I40&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I40&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H40&lt;0,"🔴 Restructurer (mutualiser)",IF(I40&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K40" s="70">
-        <f>IF(H40&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I40&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I40&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L40" s="21" t="inlineStr">
@@ -4974,11 +4974,11 @@
         </is>
       </c>
       <c r="M40" s="50">
-        <f>IF(L40="Ne pas ouvrir",0,IF(L40="Ouvrir +1 classe",E40+'08_Moteur'!O37,E40))</f>
+        <f>IF(L40="Ne pas lancer",0,IF(L40="Ouvrir +1 classe",E40+'08_Moteur'!O37,E40))</f>
         <v/>
       </c>
       <c r="N40" s="17">
-        <f>IF(L40="Ne pas ouvrir",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Économiser 1 classe",H40+('08_Moteur'!AI37-MAX(1,'08_Moteur'!AI37-1))*'08_Moteur'!U37,H40)))</f>
+        <f>IF(L40="Ne pas lancer",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Regrouper (-1 classe)",H40+('08_Moteur'!AI37-MAX(1,'08_Moteur'!AI37-1))*'08_Moteur'!U37,H40)))</f>
         <v/>
       </c>
       <c r="O40" s="17">
@@ -5032,11 +5032,11 @@
         <v/>
       </c>
       <c r="J41" s="69">
-        <f>IF(H41&lt;0,"🔴 Ne pas ouvrir",IF(I41&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I41&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H41&lt;0,"🔴 Ne pas lancer",IF(I41&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I41&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K41" s="70">
-        <f>IF(H41&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I41&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I41&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H41&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I41&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I41&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L41" s="21" t="inlineStr">
@@ -5045,11 +5045,11 @@
         </is>
       </c>
       <c r="M41" s="50">
-        <f>IF(L41="Ne pas ouvrir",0,IF(L41="Ouvrir +1 classe",E41+'08_Moteur'!O38,E41))</f>
+        <f>IF(L41="Ne pas lancer",0,IF(L41="Ouvrir +1 classe",E41+'08_Moteur'!O38,E41))</f>
         <v/>
       </c>
       <c r="N41" s="17">
-        <f>IF(L41="Ne pas ouvrir",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Économiser 1 classe",H41+('08_Moteur'!AI38-MAX(1,'08_Moteur'!AI38-1))*'08_Moteur'!U38,H41)))</f>
+        <f>IF(L41="Ne pas lancer",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Regrouper (-1 classe)",H41+('08_Moteur'!AI38-MAX(1,'08_Moteur'!AI38-1))*'08_Moteur'!U38,H41)))</f>
         <v/>
       </c>
       <c r="O41" s="17">
@@ -5103,11 +5103,11 @@
         <v/>
       </c>
       <c r="J42" s="69">
-        <f>IF(H42&lt;0,"🔴 Ne pas ouvrir",IF(I42&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I42&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H42&lt;0,"🔴 Restructurer (mutualiser)",IF(I42&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K42" s="70">
-        <f>IF(H42&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I42&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I42&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L42" s="21" t="inlineStr">
@@ -5116,11 +5116,11 @@
         </is>
       </c>
       <c r="M42" s="50">
-        <f>IF(L42="Ne pas ouvrir",0,IF(L42="Ouvrir +1 classe",E42+'08_Moteur'!O39,E42))</f>
+        <f>IF(L42="Ne pas lancer",0,IF(L42="Ouvrir +1 classe",E42+'08_Moteur'!O39,E42))</f>
         <v/>
       </c>
       <c r="N42" s="17">
-        <f>IF(L42="Ne pas ouvrir",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Économiser 1 classe",H42+('08_Moteur'!AI39-MAX(1,'08_Moteur'!AI39-1))*'08_Moteur'!U39,H42)))</f>
+        <f>IF(L42="Ne pas lancer",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Regrouper (-1 classe)",H42+('08_Moteur'!AI39-MAX(1,'08_Moteur'!AI39-1))*'08_Moteur'!U39,H42)))</f>
         <v/>
       </c>
       <c r="O42" s="17">
@@ -5174,11 +5174,11 @@
         <v/>
       </c>
       <c r="J43" s="69">
-        <f>IF(H43&lt;0,"🔴 Ne pas ouvrir",IF(I43&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I43&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H43&lt;0,"🔴 Restructurer (mutualiser)",IF(I43&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K43" s="70">
-        <f>IF(H43&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I43&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I43&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L43" s="21" t="inlineStr">
@@ -5187,11 +5187,11 @@
         </is>
       </c>
       <c r="M43" s="50">
-        <f>IF(L43="Ne pas ouvrir",0,IF(L43="Ouvrir +1 classe",E43+'08_Moteur'!O40,E43))</f>
+        <f>IF(L43="Ne pas lancer",0,IF(L43="Ouvrir +1 classe",E43+'08_Moteur'!O40,E43))</f>
         <v/>
       </c>
       <c r="N43" s="17">
-        <f>IF(L43="Ne pas ouvrir",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Économiser 1 classe",H43+('08_Moteur'!AI40-MAX(1,'08_Moteur'!AI40-1))*'08_Moteur'!U40,H43)))</f>
+        <f>IF(L43="Ne pas lancer",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Regrouper (-1 classe)",H43+('08_Moteur'!AI40-MAX(1,'08_Moteur'!AI40-1))*'08_Moteur'!U40,H43)))</f>
         <v/>
       </c>
       <c r="O43" s="17">
@@ -5245,11 +5245,11 @@
         <v/>
       </c>
       <c r="J44" s="69">
-        <f>IF(H44&lt;0,"🔴 Ne pas ouvrir",IF(I44&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I44&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H44&lt;0,"🔴 Ne pas lancer",IF(I44&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I44&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K44" s="70">
-        <f>IF(H44&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I44&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I44&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H44&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I44&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I44&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L44" s="21" t="inlineStr">
@@ -5258,11 +5258,11 @@
         </is>
       </c>
       <c r="M44" s="50">
-        <f>IF(L44="Ne pas ouvrir",0,IF(L44="Ouvrir +1 classe",E44+'08_Moteur'!O41,E44))</f>
+        <f>IF(L44="Ne pas lancer",0,IF(L44="Ouvrir +1 classe",E44+'08_Moteur'!O41,E44))</f>
         <v/>
       </c>
       <c r="N44" s="17">
-        <f>IF(L44="Ne pas ouvrir",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Économiser 1 classe",H44+('08_Moteur'!AI41-MAX(1,'08_Moteur'!AI41-1))*'08_Moteur'!U41,H44)))</f>
+        <f>IF(L44="Ne pas lancer",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Regrouper (-1 classe)",H44+('08_Moteur'!AI41-MAX(1,'08_Moteur'!AI41-1))*'08_Moteur'!U41,H44)))</f>
         <v/>
       </c>
       <c r="O44" s="17">
@@ -5316,11 +5316,11 @@
         <v/>
       </c>
       <c r="J45" s="69">
-        <f>IF(H45&lt;0,"🔴 Ne pas ouvrir",IF(I45&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I45&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H45&lt;0,"🔴 Restructurer (mutualiser)",IF(I45&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K45" s="70">
-        <f>IF(H45&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I45&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I45&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L45" s="21" t="inlineStr">
@@ -5329,11 +5329,11 @@
         </is>
       </c>
       <c r="M45" s="50">
-        <f>IF(L45="Ne pas ouvrir",0,IF(L45="Ouvrir +1 classe",E45+'08_Moteur'!O42,E45))</f>
+        <f>IF(L45="Ne pas lancer",0,IF(L45="Ouvrir +1 classe",E45+'08_Moteur'!O42,E45))</f>
         <v/>
       </c>
       <c r="N45" s="17">
-        <f>IF(L45="Ne pas ouvrir",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Économiser 1 classe",H45+('08_Moteur'!AI42-MAX(1,'08_Moteur'!AI42-1))*'08_Moteur'!U42,H45)))</f>
+        <f>IF(L45="Ne pas lancer",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Regrouper (-1 classe)",H45+('08_Moteur'!AI42-MAX(1,'08_Moteur'!AI42-1))*'08_Moteur'!U42,H45)))</f>
         <v/>
       </c>
       <c r="O45" s="17">
@@ -5387,11 +5387,11 @@
         <v/>
       </c>
       <c r="J46" s="69">
-        <f>IF(H46&lt;0,"🔴 Ne pas ouvrir",IF(I46&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I46&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H46&lt;0,"🔴 Restructurer (mutualiser)",IF(I46&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K46" s="70">
-        <f>IF(H46&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I46&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I46&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L46" s="21" t="inlineStr">
@@ -5400,11 +5400,11 @@
         </is>
       </c>
       <c r="M46" s="50">
-        <f>IF(L46="Ne pas ouvrir",0,IF(L46="Ouvrir +1 classe",E46+'08_Moteur'!O43,E46))</f>
+        <f>IF(L46="Ne pas lancer",0,IF(L46="Ouvrir +1 classe",E46+'08_Moteur'!O43,E46))</f>
         <v/>
       </c>
       <c r="N46" s="17">
-        <f>IF(L46="Ne pas ouvrir",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Économiser 1 classe",H46+('08_Moteur'!AI43-MAX(1,'08_Moteur'!AI43-1))*'08_Moteur'!U43,H46)))</f>
+        <f>IF(L46="Ne pas lancer",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Regrouper (-1 classe)",H46+('08_Moteur'!AI43-MAX(1,'08_Moteur'!AI43-1))*'08_Moteur'!U43,H46)))</f>
         <v/>
       </c>
       <c r="O46" s="17">
@@ -5458,11 +5458,11 @@
         <v/>
       </c>
       <c r="J47" s="69">
-        <f>IF(H47&lt;0,"🔴 Ne pas ouvrir",IF(I47&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I47&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H47&lt;0,"🔴 Ne pas lancer",IF(I47&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I47&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K47" s="70">
-        <f>IF(H47&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I47&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I47&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H47&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I47&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I47&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L47" s="21" t="inlineStr">
@@ -5471,11 +5471,11 @@
         </is>
       </c>
       <c r="M47" s="50">
-        <f>IF(L47="Ne pas ouvrir",0,IF(L47="Ouvrir +1 classe",E47+'08_Moteur'!O44,E47))</f>
+        <f>IF(L47="Ne pas lancer",0,IF(L47="Ouvrir +1 classe",E47+'08_Moteur'!O44,E47))</f>
         <v/>
       </c>
       <c r="N47" s="17">
-        <f>IF(L47="Ne pas ouvrir",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Économiser 1 classe",H47+('08_Moteur'!AI44-MAX(1,'08_Moteur'!AI44-1))*'08_Moteur'!U44,H47)))</f>
+        <f>IF(L47="Ne pas lancer",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Regrouper (-1 classe)",H47+('08_Moteur'!AI44-MAX(1,'08_Moteur'!AI44-1))*'08_Moteur'!U44,H47)))</f>
         <v/>
       </c>
       <c r="O47" s="17">
@@ -5529,11 +5529,11 @@
         <v/>
       </c>
       <c r="J48" s="69">
-        <f>IF(H48&lt;0,"🔴 Ne pas ouvrir",IF(I48&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I48&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H48&lt;0,"🔴 Restructurer (mutualiser)",IF(I48&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K48" s="70">
-        <f>IF(H48&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I48&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I48&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L48" s="21" t="inlineStr">
@@ -5542,11 +5542,11 @@
         </is>
       </c>
       <c r="M48" s="50">
-        <f>IF(L48="Ne pas ouvrir",0,IF(L48="Ouvrir +1 classe",E48+'08_Moteur'!O45,E48))</f>
+        <f>IF(L48="Ne pas lancer",0,IF(L48="Ouvrir +1 classe",E48+'08_Moteur'!O45,E48))</f>
         <v/>
       </c>
       <c r="N48" s="17">
-        <f>IF(L48="Ne pas ouvrir",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Économiser 1 classe",H48+('08_Moteur'!AI45-MAX(1,'08_Moteur'!AI45-1))*'08_Moteur'!U45,H48)))</f>
+        <f>IF(L48="Ne pas lancer",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Regrouper (-1 classe)",H48+('08_Moteur'!AI45-MAX(1,'08_Moteur'!AI45-1))*'08_Moteur'!U45,H48)))</f>
         <v/>
       </c>
       <c r="O48" s="17">
@@ -5600,11 +5600,11 @@
         <v/>
       </c>
       <c r="J49" s="69">
-        <f>IF(H49&lt;0,"🔴 Ne pas ouvrir",IF(I49&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I49&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H49&lt;0,"🔴 Restructurer (mutualiser)",IF(I49&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K49" s="70">
-        <f>IF(H49&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I49&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I49&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L49" s="21" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="M49" s="50">
-        <f>IF(L49="Ne pas ouvrir",0,IF(L49="Ouvrir +1 classe",E49+'08_Moteur'!O46,E49))</f>
+        <f>IF(L49="Ne pas lancer",0,IF(L49="Ouvrir +1 classe",E49+'08_Moteur'!O46,E49))</f>
         <v/>
       </c>
       <c r="N49" s="17">
-        <f>IF(L49="Ne pas ouvrir",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Économiser 1 classe",H49+('08_Moteur'!AI46-MAX(1,'08_Moteur'!AI46-1))*'08_Moteur'!U46,H49)))</f>
+        <f>IF(L49="Ne pas lancer",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Regrouper (-1 classe)",H49+('08_Moteur'!AI46-MAX(1,'08_Moteur'!AI46-1))*'08_Moteur'!U46,H49)))</f>
         <v/>
       </c>
       <c r="O49" s="17">
@@ -5671,11 +5671,11 @@
         <v/>
       </c>
       <c r="J50" s="69">
-        <f>IF(H50&lt;0,"🔴 Ne pas ouvrir",IF(I50&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I50&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H50&lt;0,"🔴 Ne pas lancer",IF(I50&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I50&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K50" s="70">
-        <f>IF(H50&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I50&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I50&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H50&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I50&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I50&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L50" s="21" t="inlineStr">
@@ -5684,11 +5684,11 @@
         </is>
       </c>
       <c r="M50" s="50">
-        <f>IF(L50="Ne pas ouvrir",0,IF(L50="Ouvrir +1 classe",E50+'08_Moteur'!O47,E50))</f>
+        <f>IF(L50="Ne pas lancer",0,IF(L50="Ouvrir +1 classe",E50+'08_Moteur'!O47,E50))</f>
         <v/>
       </c>
       <c r="N50" s="17">
-        <f>IF(L50="Ne pas ouvrir",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Économiser 1 classe",H50+('08_Moteur'!AI47-MAX(1,'08_Moteur'!AI47-1))*'08_Moteur'!U47,H50)))</f>
+        <f>IF(L50="Ne pas lancer",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Regrouper (-1 classe)",H50+('08_Moteur'!AI47-MAX(1,'08_Moteur'!AI47-1))*'08_Moteur'!U47,H50)))</f>
         <v/>
       </c>
       <c r="O50" s="17">
@@ -5742,11 +5742,11 @@
         <v/>
       </c>
       <c r="J51" s="69">
-        <f>IF(H51&lt;0,"🔴 Ne pas ouvrir",IF(I51&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I51&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H51&lt;0,"🔴 Restructurer (mutualiser)",IF(I51&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K51" s="70">
-        <f>IF(H51&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I51&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I51&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L51" s="21" t="inlineStr">
@@ -5755,11 +5755,11 @@
         </is>
       </c>
       <c r="M51" s="50">
-        <f>IF(L51="Ne pas ouvrir",0,IF(L51="Ouvrir +1 classe",E51+'08_Moteur'!O48,E51))</f>
+        <f>IF(L51="Ne pas lancer",0,IF(L51="Ouvrir +1 classe",E51+'08_Moteur'!O48,E51))</f>
         <v/>
       </c>
       <c r="N51" s="17">
-        <f>IF(L51="Ne pas ouvrir",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Économiser 1 classe",H51+('08_Moteur'!AI48-MAX(1,'08_Moteur'!AI48-1))*'08_Moteur'!U48,H51)))</f>
+        <f>IF(L51="Ne pas lancer",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Regrouper (-1 classe)",H51+('08_Moteur'!AI48-MAX(1,'08_Moteur'!AI48-1))*'08_Moteur'!U48,H51)))</f>
         <v/>
       </c>
       <c r="O51" s="17">
@@ -5813,11 +5813,11 @@
         <v/>
       </c>
       <c r="J52" s="69">
-        <f>IF(H52&lt;0,"🔴 Ne pas ouvrir",IF(I52&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I52&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H52&lt;0,"🔴 Ne pas lancer",IF(I52&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I52&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K52" s="70">
-        <f>IF(H52&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I52&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I52&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H52&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I52&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I52&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L52" s="21" t="inlineStr">
@@ -5826,11 +5826,11 @@
         </is>
       </c>
       <c r="M52" s="50">
-        <f>IF(L52="Ne pas ouvrir",0,IF(L52="Ouvrir +1 classe",E52+'08_Moteur'!O49,E52))</f>
+        <f>IF(L52="Ne pas lancer",0,IF(L52="Ouvrir +1 classe",E52+'08_Moteur'!O49,E52))</f>
         <v/>
       </c>
       <c r="N52" s="17">
-        <f>IF(L52="Ne pas ouvrir",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Économiser 1 classe",H52+('08_Moteur'!AI49-MAX(1,'08_Moteur'!AI49-1))*'08_Moteur'!U49,H52)))</f>
+        <f>IF(L52="Ne pas lancer",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Regrouper (-1 classe)",H52+('08_Moteur'!AI49-MAX(1,'08_Moteur'!AI49-1))*'08_Moteur'!U49,H52)))</f>
         <v/>
       </c>
       <c r="O52" s="17">
@@ -5884,11 +5884,11 @@
         <v/>
       </c>
       <c r="J53" s="69">
-        <f>IF(H53&lt;0,"🔴 Ne pas ouvrir",IF(I53&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I53&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H53&lt;0,"🔴 Restructurer (mutualiser)",IF(I53&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K53" s="70">
-        <f>IF(H53&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I53&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I53&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L53" s="21" t="inlineStr">
@@ -5897,11 +5897,11 @@
         </is>
       </c>
       <c r="M53" s="50">
-        <f>IF(L53="Ne pas ouvrir",0,IF(L53="Ouvrir +1 classe",E53+'08_Moteur'!O50,E53))</f>
+        <f>IF(L53="Ne pas lancer",0,IF(L53="Ouvrir +1 classe",E53+'08_Moteur'!O50,E53))</f>
         <v/>
       </c>
       <c r="N53" s="17">
-        <f>IF(L53="Ne pas ouvrir",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Économiser 1 classe",H53+('08_Moteur'!AI50-MAX(1,'08_Moteur'!AI50-1))*'08_Moteur'!U50,H53)))</f>
+        <f>IF(L53="Ne pas lancer",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Regrouper (-1 classe)",H53+('08_Moteur'!AI50-MAX(1,'08_Moteur'!AI50-1))*'08_Moteur'!U50,H53)))</f>
         <v/>
       </c>
       <c r="O53" s="17">
@@ -5955,11 +5955,11 @@
         <v/>
       </c>
       <c r="J54" s="69">
-        <f>IF(H54&lt;0,"🔴 Ne pas ouvrir",IF(I54&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I54&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H54&lt;0,"🔴 Ne pas lancer",IF(I54&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I54&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K54" s="70">
-        <f>IF(H54&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I54&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I54&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H54&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I54&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I54&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L54" s="21" t="inlineStr">
@@ -5968,11 +5968,11 @@
         </is>
       </c>
       <c r="M54" s="50">
-        <f>IF(L54="Ne pas ouvrir",0,IF(L54="Ouvrir +1 classe",E54+'08_Moteur'!O51,E54))</f>
+        <f>IF(L54="Ne pas lancer",0,IF(L54="Ouvrir +1 classe",E54+'08_Moteur'!O51,E54))</f>
         <v/>
       </c>
       <c r="N54" s="17">
-        <f>IF(L54="Ne pas ouvrir",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Économiser 1 classe",H54+('08_Moteur'!AI51-MAX(1,'08_Moteur'!AI51-1))*'08_Moteur'!U51,H54)))</f>
+        <f>IF(L54="Ne pas lancer",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Regrouper (-1 classe)",H54+('08_Moteur'!AI51-MAX(1,'08_Moteur'!AI51-1))*'08_Moteur'!U51,H54)))</f>
         <v/>
       </c>
       <c r="O54" s="17">
@@ -6026,11 +6026,11 @@
         <v/>
       </c>
       <c r="J55" s="69">
-        <f>IF(H55&lt;0,"🔴 Ne pas ouvrir",IF(I55&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I55&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H55&lt;0,"🔴 Restructurer (mutualiser)",IF(I55&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K55" s="70">
-        <f>IF(H55&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I55&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I55&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L55" s="21" t="inlineStr">
@@ -6039,11 +6039,11 @@
         </is>
       </c>
       <c r="M55" s="50">
-        <f>IF(L55="Ne pas ouvrir",0,IF(L55="Ouvrir +1 classe",E55+'08_Moteur'!O52,E55))</f>
+        <f>IF(L55="Ne pas lancer",0,IF(L55="Ouvrir +1 classe",E55+'08_Moteur'!O52,E55))</f>
         <v/>
       </c>
       <c r="N55" s="17">
-        <f>IF(L55="Ne pas ouvrir",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Économiser 1 classe",H55+('08_Moteur'!AI52-MAX(1,'08_Moteur'!AI52-1))*'08_Moteur'!U52,H55)))</f>
+        <f>IF(L55="Ne pas lancer",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Regrouper (-1 classe)",H55+('08_Moteur'!AI52-MAX(1,'08_Moteur'!AI52-1))*'08_Moteur'!U52,H55)))</f>
         <v/>
       </c>
       <c r="O55" s="17">
@@ -6097,11 +6097,11 @@
         <v/>
       </c>
       <c r="J56" s="69">
-        <f>IF(H56&lt;0,"🔴 Ne pas ouvrir",IF(I56&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I56&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H56&lt;0,"🔴 Ne pas lancer",IF(I56&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I56&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K56" s="70">
-        <f>IF(H56&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I56&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I56&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H56&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I56&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I56&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L56" s="21" t="inlineStr">
@@ -6110,11 +6110,11 @@
         </is>
       </c>
       <c r="M56" s="50">
-        <f>IF(L56="Ne pas ouvrir",0,IF(L56="Ouvrir +1 classe",E56+'08_Moteur'!O53,E56))</f>
+        <f>IF(L56="Ne pas lancer",0,IF(L56="Ouvrir +1 classe",E56+'08_Moteur'!O53,E56))</f>
         <v/>
       </c>
       <c r="N56" s="17">
-        <f>IF(L56="Ne pas ouvrir",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Économiser 1 classe",H56+('08_Moteur'!AI53-MAX(1,'08_Moteur'!AI53-1))*'08_Moteur'!U53,H56)))</f>
+        <f>IF(L56="Ne pas lancer",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Regrouper (-1 classe)",H56+('08_Moteur'!AI53-MAX(1,'08_Moteur'!AI53-1))*'08_Moteur'!U53,H56)))</f>
         <v/>
       </c>
       <c r="O56" s="17">
@@ -6168,11 +6168,11 @@
         <v/>
       </c>
       <c r="J57" s="69">
-        <f>IF(H57&lt;0,"🔴 Ne pas ouvrir",IF(I57&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I57&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H57&lt;0,"🔴 Restructurer (mutualiser)",IF(I57&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K57" s="70">
-        <f>IF(H57&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I57&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I57&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L57" s="21" t="inlineStr">
@@ -6181,11 +6181,11 @@
         </is>
       </c>
       <c r="M57" s="50">
-        <f>IF(L57="Ne pas ouvrir",0,IF(L57="Ouvrir +1 classe",E57+'08_Moteur'!O54,E57))</f>
+        <f>IF(L57="Ne pas lancer",0,IF(L57="Ouvrir +1 classe",E57+'08_Moteur'!O54,E57))</f>
         <v/>
       </c>
       <c r="N57" s="17">
-        <f>IF(L57="Ne pas ouvrir",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Économiser 1 classe",H57+('08_Moteur'!AI54-MAX(1,'08_Moteur'!AI54-1))*'08_Moteur'!U54,H57)))</f>
+        <f>IF(L57="Ne pas lancer",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Regrouper (-1 classe)",H57+('08_Moteur'!AI54-MAX(1,'08_Moteur'!AI54-1))*'08_Moteur'!U54,H57)))</f>
         <v/>
       </c>
       <c r="O57" s="17">
@@ -6239,11 +6239,11 @@
         <v/>
       </c>
       <c r="J58" s="69">
-        <f>IF(H58&lt;0,"🔴 Ne pas ouvrir",IF(I58&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I58&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H58&lt;0,"🔴 Ne pas lancer",IF(I58&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I58&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K58" s="70">
-        <f>IF(H58&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I58&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I58&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H58&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I58&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I58&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L58" s="21" t="inlineStr">
@@ -6252,11 +6252,11 @@
         </is>
       </c>
       <c r="M58" s="50">
-        <f>IF(L58="Ne pas ouvrir",0,IF(L58="Ouvrir +1 classe",E58+'08_Moteur'!O55,E58))</f>
+        <f>IF(L58="Ne pas lancer",0,IF(L58="Ouvrir +1 classe",E58+'08_Moteur'!O55,E58))</f>
         <v/>
       </c>
       <c r="N58" s="17">
-        <f>IF(L58="Ne pas ouvrir",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Économiser 1 classe",H58+('08_Moteur'!AI55-MAX(1,'08_Moteur'!AI55-1))*'08_Moteur'!U55,H58)))</f>
+        <f>IF(L58="Ne pas lancer",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Regrouper (-1 classe)",H58+('08_Moteur'!AI55-MAX(1,'08_Moteur'!AI55-1))*'08_Moteur'!U55,H58)))</f>
         <v/>
       </c>
       <c r="O58" s="17">
@@ -6310,11 +6310,11 @@
         <v/>
       </c>
       <c r="J59" s="69">
-        <f>IF(H59&lt;0,"🔴 Ne pas ouvrir",IF(I59&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I59&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H59&lt;0,"🔴 Restructurer (mutualiser)",IF(I59&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K59" s="70">
-        <f>IF(H59&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I59&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I59&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L59" s="21" t="inlineStr">
@@ -6323,11 +6323,11 @@
         </is>
       </c>
       <c r="M59" s="50">
-        <f>IF(L59="Ne pas ouvrir",0,IF(L59="Ouvrir +1 classe",E59+'08_Moteur'!O56,E59))</f>
+        <f>IF(L59="Ne pas lancer",0,IF(L59="Ouvrir +1 classe",E59+'08_Moteur'!O56,E59))</f>
         <v/>
       </c>
       <c r="N59" s="17">
-        <f>IF(L59="Ne pas ouvrir",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Économiser 1 classe",H59+('08_Moteur'!AI56-MAX(1,'08_Moteur'!AI56-1))*'08_Moteur'!U56,H59)))</f>
+        <f>IF(L59="Ne pas lancer",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Regrouper (-1 classe)",H59+('08_Moteur'!AI56-MAX(1,'08_Moteur'!AI56-1))*'08_Moteur'!U56,H59)))</f>
         <v/>
       </c>
       <c r="O59" s="17">
@@ -6381,11 +6381,11 @@
         <v/>
       </c>
       <c r="J60" s="69">
-        <f>IF(H60&lt;0,"🔴 Ne pas ouvrir",IF(I60&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I60&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H60&lt;0,"🔴 Restructurer (mutualiser)",IF(I60&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K60" s="70">
-        <f>IF(H60&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I60&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I60&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L60" s="21" t="inlineStr">
@@ -6394,11 +6394,11 @@
         </is>
       </c>
       <c r="M60" s="50">
-        <f>IF(L60="Ne pas ouvrir",0,IF(L60="Ouvrir +1 classe",E60+'08_Moteur'!O57,E60))</f>
+        <f>IF(L60="Ne pas lancer",0,IF(L60="Ouvrir +1 classe",E60+'08_Moteur'!O57,E60))</f>
         <v/>
       </c>
       <c r="N60" s="17">
-        <f>IF(L60="Ne pas ouvrir",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Économiser 1 classe",H60+('08_Moteur'!AI57-MAX(1,'08_Moteur'!AI57-1))*'08_Moteur'!U57,H60)))</f>
+        <f>IF(L60="Ne pas lancer",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Regrouper (-1 classe)",H60+('08_Moteur'!AI57-MAX(1,'08_Moteur'!AI57-1))*'08_Moteur'!U57,H60)))</f>
         <v/>
       </c>
       <c r="O60" s="17">
@@ -6452,11 +6452,11 @@
         <v/>
       </c>
       <c r="J61" s="69">
-        <f>IF(H61&lt;0,"🔴 Ne pas ouvrir",IF(I61&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I61&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H61&lt;0,"🔴 Ne pas lancer",IF(I61&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I61&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K61" s="70">
-        <f>IF(H61&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I61&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I61&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>IF(H61&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I61&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I61&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
       <c r="L61" s="21" t="inlineStr">
@@ -6465,11 +6465,11 @@
         </is>
       </c>
       <c r="M61" s="50">
-        <f>IF(L61="Ne pas ouvrir",0,IF(L61="Ouvrir +1 classe",E61+'08_Moteur'!O58,E61))</f>
+        <f>IF(L61="Ne pas lancer",0,IF(L61="Ouvrir +1 classe",E61+'08_Moteur'!O58,E61))</f>
         <v/>
       </c>
       <c r="N61" s="17">
-        <f>IF(L61="Ne pas ouvrir",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Économiser 1 classe",H61+('08_Moteur'!AI58-MAX(1,'08_Moteur'!AI58-1))*'08_Moteur'!U58,H61)))</f>
+        <f>IF(L61="Ne pas lancer",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Regrouper (-1 classe)",H61+('08_Moteur'!AI58-MAX(1,'08_Moteur'!AI58-1))*'08_Moteur'!U58,H61)))</f>
         <v/>
       </c>
       <c r="O61" s="17">
@@ -6523,11 +6523,11 @@
         <v/>
       </c>
       <c r="J62" s="69">
-        <f>IF(H62&lt;0,"🔴 Ne pas ouvrir",IF(I62&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I62&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H62&lt;0,"🔴 Restructurer (mutualiser)",IF(I62&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K62" s="70">
-        <f>IF(H62&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I62&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I62&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L62" s="21" t="inlineStr">
@@ -6536,11 +6536,11 @@
         </is>
       </c>
       <c r="M62" s="50">
-        <f>IF(L62="Ne pas ouvrir",0,IF(L62="Ouvrir +1 classe",E62+'08_Moteur'!O59,E62))</f>
+        <f>IF(L62="Ne pas lancer",0,IF(L62="Ouvrir +1 classe",E62+'08_Moteur'!O59,E62))</f>
         <v/>
       </c>
       <c r="N62" s="17">
-        <f>IF(L62="Ne pas ouvrir",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Économiser 1 classe",H62+('08_Moteur'!AI59-MAX(1,'08_Moteur'!AI59-1))*'08_Moteur'!U59,H62)))</f>
+        <f>IF(L62="Ne pas lancer",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Regrouper (-1 classe)",H62+('08_Moteur'!AI59-MAX(1,'08_Moteur'!AI59-1))*'08_Moteur'!U59,H62)))</f>
         <v/>
       </c>
       <c r="O62" s="17">
@@ -6594,11 +6594,11 @@
         <v/>
       </c>
       <c r="J63" s="69">
-        <f>IF(H63&lt;0,"🔴 Ne pas ouvrir",IF(I63&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I63&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
+        <f>IF(H63&lt;0,"🔴 Restructurer (mutualiser)",IF(I63&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
       <c r="K63" s="70">
-        <f>IF(H63&lt;0,"Contribution négative → fermer améliore l'EBITDA",IF(I63&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I63&lt;0.55,"Sous-rempli mais contribution positive → GARDER","Sain")))</f>
+        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
       <c r="L63" s="21" t="inlineStr">
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="M63" s="50">
-        <f>IF(L63="Ne pas ouvrir",0,IF(L63="Ouvrir +1 classe",E63+'08_Moteur'!O60,E63))</f>
+        <f>IF(L63="Ne pas lancer",0,IF(L63="Ouvrir +1 classe",E63+'08_Moteur'!O60,E63))</f>
         <v/>
       </c>
       <c r="N63" s="17">
-        <f>IF(L63="Ne pas ouvrir",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Économiser 1 classe",H63+('08_Moteur'!AI60-MAX(1,'08_Moteur'!AI60-1))*'08_Moteur'!U60,H63)))</f>
+        <f>IF(L63="Ne pas lancer",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Regrouper (-1 classe)",H63+('08_Moteur'!AI60-MAX(1,'08_Moteur'!AI60-1))*'08_Moteur'!U60,H63)))</f>
         <v/>
       </c>
       <c r="O63" s="17">
@@ -6641,9 +6641,12 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="I3:J3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Maintenir,Ne pas ouvrir,Ouvrir +1 classe,Économiser 1 classe"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="L6 L9 L11 L14 L16 L19 L21 L24 L26 L29 L31 L34 L36 L39 L41 L44 L47 L50 L52 L54 L56 L58 L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Maintenir,Ne pas lancer,Ouvrir +1 classe,Regrouper (-1 classe)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L7 L8 L10 L12 L13 L15 L17 L18 L20 L22 L23 L25 L27 L28 L30 L32 L33 L35 L37 L38 L40 L42 L43 L45 L46 L48 L49 L51 L53 L55 L57 L59 L60 L62 L63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Maintenir,Regrouper (-1 classe)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;;(#,##0)&quot; €&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +88,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="8">
@@ -187,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -378,6 +384,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2416,6 +2425,13 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="68" t="inlineStr">
+        <is>
+          <t>🧪 BAC À SABLE : ces décisions montrent un impact SIMULÉ (encadré ci-dessus) — elles n'affectent PAS le budget officiel (feuilles 09_Allocation / 10_PnL / 13_Simulation), qui se pilote via les LEVIERS (feuille 02_Leviers).</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -2542,15 +2558,15 @@
         <f>'08_Moteur'!AM3</f>
         <v/>
       </c>
-      <c r="I6" s="68">
+      <c r="I6" s="69">
         <f>'08_Moteur'!AN3</f>
         <v/>
       </c>
-      <c r="J6" s="69">
+      <c r="J6" s="70">
         <f>IF(H6&lt;0,"🔴 Ne pas lancer",IF(I6&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I6&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K6" s="70">
+      <c r="K6" s="71">
         <f>IF(H6&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I6&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I6&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -2613,15 +2629,15 @@
         <f>'08_Moteur'!AM4</f>
         <v/>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="69">
         <f>'08_Moteur'!AN4</f>
         <v/>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="70">
         <f>IF(H7&lt;0,"🔴 Restructurer (mutualiser)",IF(I7&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -2684,15 +2700,15 @@
         <f>'08_Moteur'!AM5</f>
         <v/>
       </c>
-      <c r="I8" s="68">
+      <c r="I8" s="69">
         <f>'08_Moteur'!AN5</f>
         <v/>
       </c>
-      <c r="J8" s="69">
+      <c r="J8" s="70">
         <f>IF(H8&lt;0,"🔴 Restructurer (mutualiser)",IF(I8&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K8" s="70">
+      <c r="K8" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -2755,15 +2771,15 @@
         <f>'08_Moteur'!AM6</f>
         <v/>
       </c>
-      <c r="I9" s="68">
+      <c r="I9" s="69">
         <f>'08_Moteur'!AN6</f>
         <v/>
       </c>
-      <c r="J9" s="69">
+      <c r="J9" s="70">
         <f>IF(H9&lt;0,"🔴 Ne pas lancer",IF(I9&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I9&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K9" s="70">
+      <c r="K9" s="71">
         <f>IF(H9&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I9&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I9&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -2826,15 +2842,15 @@
         <f>'08_Moteur'!AM7</f>
         <v/>
       </c>
-      <c r="I10" s="68">
+      <c r="I10" s="69">
         <f>'08_Moteur'!AN7</f>
         <v/>
       </c>
-      <c r="J10" s="69">
+      <c r="J10" s="70">
         <f>IF(H10&lt;0,"🔴 Restructurer (mutualiser)",IF(I10&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K10" s="70">
+      <c r="K10" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -2897,15 +2913,15 @@
         <f>'08_Moteur'!AM8</f>
         <v/>
       </c>
-      <c r="I11" s="68">
+      <c r="I11" s="69">
         <f>'08_Moteur'!AN8</f>
         <v/>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="70">
         <f>IF(H11&lt;0,"🔴 Ne pas lancer",IF(I11&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I11&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K11" s="70">
+      <c r="K11" s="71">
         <f>IF(H11&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I11&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I11&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -2968,15 +2984,15 @@
         <f>'08_Moteur'!AM9</f>
         <v/>
       </c>
-      <c r="I12" s="68">
+      <c r="I12" s="69">
         <f>'08_Moteur'!AN9</f>
         <v/>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="70">
         <f>IF(H12&lt;0,"🔴 Restructurer (mutualiser)",IF(I12&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K12" s="70">
+      <c r="K12" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3039,15 +3055,15 @@
         <f>'08_Moteur'!AM10</f>
         <v/>
       </c>
-      <c r="I13" s="68">
+      <c r="I13" s="69">
         <f>'08_Moteur'!AN10</f>
         <v/>
       </c>
-      <c r="J13" s="69">
+      <c r="J13" s="70">
         <f>IF(H13&lt;0,"🔴 Restructurer (mutualiser)",IF(I13&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K13" s="70">
+      <c r="K13" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3110,15 +3126,15 @@
         <f>'08_Moteur'!AM11</f>
         <v/>
       </c>
-      <c r="I14" s="68">
+      <c r="I14" s="69">
         <f>'08_Moteur'!AN11</f>
         <v/>
       </c>
-      <c r="J14" s="69">
+      <c r="J14" s="70">
         <f>IF(H14&lt;0,"🔴 Ne pas lancer",IF(I14&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I14&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K14" s="70">
+      <c r="K14" s="71">
         <f>IF(H14&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I14&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I14&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -3181,15 +3197,15 @@
         <f>'08_Moteur'!AM12</f>
         <v/>
       </c>
-      <c r="I15" s="68">
+      <c r="I15" s="69">
         <f>'08_Moteur'!AN12</f>
         <v/>
       </c>
-      <c r="J15" s="69">
+      <c r="J15" s="70">
         <f>IF(H15&lt;0,"🔴 Restructurer (mutualiser)",IF(I15&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K15" s="70">
+      <c r="K15" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3252,15 +3268,15 @@
         <f>'08_Moteur'!AM13</f>
         <v/>
       </c>
-      <c r="I16" s="68">
+      <c r="I16" s="69">
         <f>'08_Moteur'!AN13</f>
         <v/>
       </c>
-      <c r="J16" s="69">
+      <c r="J16" s="70">
         <f>IF(H16&lt;0,"🔴 Ne pas lancer",IF(I16&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I16&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K16" s="70">
+      <c r="K16" s="71">
         <f>IF(H16&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I16&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I16&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -3323,15 +3339,15 @@
         <f>'08_Moteur'!AM14</f>
         <v/>
       </c>
-      <c r="I17" s="68">
+      <c r="I17" s="69">
         <f>'08_Moteur'!AN14</f>
         <v/>
       </c>
-      <c r="J17" s="69">
+      <c r="J17" s="70">
         <f>IF(H17&lt;0,"🔴 Restructurer (mutualiser)",IF(I17&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K17" s="70">
+      <c r="K17" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3394,15 +3410,15 @@
         <f>'08_Moteur'!AM15</f>
         <v/>
       </c>
-      <c r="I18" s="68">
+      <c r="I18" s="69">
         <f>'08_Moteur'!AN15</f>
         <v/>
       </c>
-      <c r="J18" s="69">
+      <c r="J18" s="70">
         <f>IF(H18&lt;0,"🔴 Restructurer (mutualiser)",IF(I18&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K18" s="70">
+      <c r="K18" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3465,15 +3481,15 @@
         <f>'08_Moteur'!AM16</f>
         <v/>
       </c>
-      <c r="I19" s="68">
+      <c r="I19" s="69">
         <f>'08_Moteur'!AN16</f>
         <v/>
       </c>
-      <c r="J19" s="69">
+      <c r="J19" s="70">
         <f>IF(H19&lt;0,"🔴 Ne pas lancer",IF(I19&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I19&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K19" s="70">
+      <c r="K19" s="71">
         <f>IF(H19&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I19&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I19&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -3536,15 +3552,15 @@
         <f>'08_Moteur'!AM17</f>
         <v/>
       </c>
-      <c r="I20" s="68">
+      <c r="I20" s="69">
         <f>'08_Moteur'!AN17</f>
         <v/>
       </c>
-      <c r="J20" s="69">
+      <c r="J20" s="70">
         <f>IF(H20&lt;0,"🔴 Restructurer (mutualiser)",IF(I20&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K20" s="70">
+      <c r="K20" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3607,15 +3623,15 @@
         <f>'08_Moteur'!AM18</f>
         <v/>
       </c>
-      <c r="I21" s="68">
+      <c r="I21" s="69">
         <f>'08_Moteur'!AN18</f>
         <v/>
       </c>
-      <c r="J21" s="69">
+      <c r="J21" s="70">
         <f>IF(H21&lt;0,"🔴 Ne pas lancer",IF(I21&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I21&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K21" s="70">
+      <c r="K21" s="71">
         <f>IF(H21&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I21&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I21&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -3678,15 +3694,15 @@
         <f>'08_Moteur'!AM19</f>
         <v/>
       </c>
-      <c r="I22" s="68">
+      <c r="I22" s="69">
         <f>'08_Moteur'!AN19</f>
         <v/>
       </c>
-      <c r="J22" s="69">
+      <c r="J22" s="70">
         <f>IF(H22&lt;0,"🔴 Restructurer (mutualiser)",IF(I22&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K22" s="70">
+      <c r="K22" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3749,15 +3765,15 @@
         <f>'08_Moteur'!AM20</f>
         <v/>
       </c>
-      <c r="I23" s="68">
+      <c r="I23" s="69">
         <f>'08_Moteur'!AN20</f>
         <v/>
       </c>
-      <c r="J23" s="69">
+      <c r="J23" s="70">
         <f>IF(H23&lt;0,"🔴 Restructurer (mutualiser)",IF(I23&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K23" s="70">
+      <c r="K23" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3820,15 +3836,15 @@
         <f>'08_Moteur'!AM21</f>
         <v/>
       </c>
-      <c r="I24" s="68">
+      <c r="I24" s="69">
         <f>'08_Moteur'!AN21</f>
         <v/>
       </c>
-      <c r="J24" s="69">
+      <c r="J24" s="70">
         <f>IF(H24&lt;0,"🔴 Ne pas lancer",IF(I24&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I24&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K24" s="70">
+      <c r="K24" s="71">
         <f>IF(H24&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I24&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I24&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -3891,15 +3907,15 @@
         <f>'08_Moteur'!AM22</f>
         <v/>
       </c>
-      <c r="I25" s="68">
+      <c r="I25" s="69">
         <f>'08_Moteur'!AN22</f>
         <v/>
       </c>
-      <c r="J25" s="69">
+      <c r="J25" s="70">
         <f>IF(H25&lt;0,"🔴 Restructurer (mutualiser)",IF(I25&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K25" s="70">
+      <c r="K25" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -3962,15 +3978,15 @@
         <f>'08_Moteur'!AM23</f>
         <v/>
       </c>
-      <c r="I26" s="68">
+      <c r="I26" s="69">
         <f>'08_Moteur'!AN23</f>
         <v/>
       </c>
-      <c r="J26" s="69">
+      <c r="J26" s="70">
         <f>IF(H26&lt;0,"🔴 Ne pas lancer",IF(I26&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I26&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K26" s="70">
+      <c r="K26" s="71">
         <f>IF(H26&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I26&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I26&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -4033,15 +4049,15 @@
         <f>'08_Moteur'!AM24</f>
         <v/>
       </c>
-      <c r="I27" s="68">
+      <c r="I27" s="69">
         <f>'08_Moteur'!AN24</f>
         <v/>
       </c>
-      <c r="J27" s="69">
+      <c r="J27" s="70">
         <f>IF(H27&lt;0,"🔴 Restructurer (mutualiser)",IF(I27&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K27" s="70">
+      <c r="K27" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4104,15 +4120,15 @@
         <f>'08_Moteur'!AM25</f>
         <v/>
       </c>
-      <c r="I28" s="68">
+      <c r="I28" s="69">
         <f>'08_Moteur'!AN25</f>
         <v/>
       </c>
-      <c r="J28" s="69">
+      <c r="J28" s="70">
         <f>IF(H28&lt;0,"🔴 Restructurer (mutualiser)",IF(I28&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K28" s="70">
+      <c r="K28" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4175,15 +4191,15 @@
         <f>'08_Moteur'!AM26</f>
         <v/>
       </c>
-      <c r="I29" s="68">
+      <c r="I29" s="69">
         <f>'08_Moteur'!AN26</f>
         <v/>
       </c>
-      <c r="J29" s="69">
+      <c r="J29" s="70">
         <f>IF(H29&lt;0,"🔴 Ne pas lancer",IF(I29&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I29&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K29" s="70">
+      <c r="K29" s="71">
         <f>IF(H29&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I29&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I29&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -4246,15 +4262,15 @@
         <f>'08_Moteur'!AM27</f>
         <v/>
       </c>
-      <c r="I30" s="68">
+      <c r="I30" s="69">
         <f>'08_Moteur'!AN27</f>
         <v/>
       </c>
-      <c r="J30" s="69">
+      <c r="J30" s="70">
         <f>IF(H30&lt;0,"🔴 Restructurer (mutualiser)",IF(I30&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K30" s="70">
+      <c r="K30" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4317,15 +4333,15 @@
         <f>'08_Moteur'!AM28</f>
         <v/>
       </c>
-      <c r="I31" s="68">
+      <c r="I31" s="69">
         <f>'08_Moteur'!AN28</f>
         <v/>
       </c>
-      <c r="J31" s="69">
+      <c r="J31" s="70">
         <f>IF(H31&lt;0,"🔴 Ne pas lancer",IF(I31&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I31&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K31" s="70">
+      <c r="K31" s="71">
         <f>IF(H31&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I31&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I31&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -4388,15 +4404,15 @@
         <f>'08_Moteur'!AM29</f>
         <v/>
       </c>
-      <c r="I32" s="68">
+      <c r="I32" s="69">
         <f>'08_Moteur'!AN29</f>
         <v/>
       </c>
-      <c r="J32" s="69">
+      <c r="J32" s="70">
         <f>IF(H32&lt;0,"🔴 Restructurer (mutualiser)",IF(I32&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K32" s="70">
+      <c r="K32" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4459,15 +4475,15 @@
         <f>'08_Moteur'!AM30</f>
         <v/>
       </c>
-      <c r="I33" s="68">
+      <c r="I33" s="69">
         <f>'08_Moteur'!AN30</f>
         <v/>
       </c>
-      <c r="J33" s="69">
+      <c r="J33" s="70">
         <f>IF(H33&lt;0,"🔴 Restructurer (mutualiser)",IF(I33&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K33" s="70">
+      <c r="K33" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4530,15 +4546,15 @@
         <f>'08_Moteur'!AM31</f>
         <v/>
       </c>
-      <c r="I34" s="68">
+      <c r="I34" s="69">
         <f>'08_Moteur'!AN31</f>
         <v/>
       </c>
-      <c r="J34" s="69">
+      <c r="J34" s="70">
         <f>IF(H34&lt;0,"🔴 Ne pas lancer",IF(I34&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I34&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K34" s="70">
+      <c r="K34" s="71">
         <f>IF(H34&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I34&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I34&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -4601,15 +4617,15 @@
         <f>'08_Moteur'!AM32</f>
         <v/>
       </c>
-      <c r="I35" s="68">
+      <c r="I35" s="69">
         <f>'08_Moteur'!AN32</f>
         <v/>
       </c>
-      <c r="J35" s="69">
+      <c r="J35" s="70">
         <f>IF(H35&lt;0,"🔴 Restructurer (mutualiser)",IF(I35&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K35" s="70">
+      <c r="K35" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4672,15 +4688,15 @@
         <f>'08_Moteur'!AM33</f>
         <v/>
       </c>
-      <c r="I36" s="68">
+      <c r="I36" s="69">
         <f>'08_Moteur'!AN33</f>
         <v/>
       </c>
-      <c r="J36" s="69">
+      <c r="J36" s="70">
         <f>IF(H36&lt;0,"🔴 Ne pas lancer",IF(I36&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I36&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K36" s="70">
+      <c r="K36" s="71">
         <f>IF(H36&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I36&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I36&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -4743,15 +4759,15 @@
         <f>'08_Moteur'!AM34</f>
         <v/>
       </c>
-      <c r="I37" s="68">
+      <c r="I37" s="69">
         <f>'08_Moteur'!AN34</f>
         <v/>
       </c>
-      <c r="J37" s="69">
+      <c r="J37" s="70">
         <f>IF(H37&lt;0,"🔴 Restructurer (mutualiser)",IF(I37&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K37" s="70">
+      <c r="K37" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4814,15 +4830,15 @@
         <f>'08_Moteur'!AM35</f>
         <v/>
       </c>
-      <c r="I38" s="68">
+      <c r="I38" s="69">
         <f>'08_Moteur'!AN35</f>
         <v/>
       </c>
-      <c r="J38" s="69">
+      <c r="J38" s="70">
         <f>IF(H38&lt;0,"🔴 Restructurer (mutualiser)",IF(I38&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K38" s="70">
+      <c r="K38" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -4885,15 +4901,15 @@
         <f>'08_Moteur'!AM36</f>
         <v/>
       </c>
-      <c r="I39" s="68">
+      <c r="I39" s="69">
         <f>'08_Moteur'!AN36</f>
         <v/>
       </c>
-      <c r="J39" s="69">
+      <c r="J39" s="70">
         <f>IF(H39&lt;0,"🔴 Ne pas lancer",IF(I39&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I39&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K39" s="70">
+      <c r="K39" s="71">
         <f>IF(H39&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I39&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I39&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -4956,15 +4972,15 @@
         <f>'08_Moteur'!AM37</f>
         <v/>
       </c>
-      <c r="I40" s="68">
+      <c r="I40" s="69">
         <f>'08_Moteur'!AN37</f>
         <v/>
       </c>
-      <c r="J40" s="69">
+      <c r="J40" s="70">
         <f>IF(H40&lt;0,"🔴 Restructurer (mutualiser)",IF(I40&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K40" s="70">
+      <c r="K40" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5027,15 +5043,15 @@
         <f>'08_Moteur'!AM38</f>
         <v/>
       </c>
-      <c r="I41" s="68">
+      <c r="I41" s="69">
         <f>'08_Moteur'!AN38</f>
         <v/>
       </c>
-      <c r="J41" s="69">
+      <c r="J41" s="70">
         <f>IF(H41&lt;0,"🔴 Ne pas lancer",IF(I41&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I41&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K41" s="70">
+      <c r="K41" s="71">
         <f>IF(H41&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I41&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I41&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -5098,15 +5114,15 @@
         <f>'08_Moteur'!AM39</f>
         <v/>
       </c>
-      <c r="I42" s="68">
+      <c r="I42" s="69">
         <f>'08_Moteur'!AN39</f>
         <v/>
       </c>
-      <c r="J42" s="69">
+      <c r="J42" s="70">
         <f>IF(H42&lt;0,"🔴 Restructurer (mutualiser)",IF(I42&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K42" s="70">
+      <c r="K42" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5169,15 +5185,15 @@
         <f>'08_Moteur'!AM40</f>
         <v/>
       </c>
-      <c r="I43" s="68">
+      <c r="I43" s="69">
         <f>'08_Moteur'!AN40</f>
         <v/>
       </c>
-      <c r="J43" s="69">
+      <c r="J43" s="70">
         <f>IF(H43&lt;0,"🔴 Restructurer (mutualiser)",IF(I43&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K43" s="70">
+      <c r="K43" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5240,15 +5256,15 @@
         <f>'08_Moteur'!AM41</f>
         <v/>
       </c>
-      <c r="I44" s="68">
+      <c r="I44" s="69">
         <f>'08_Moteur'!AN41</f>
         <v/>
       </c>
-      <c r="J44" s="69">
+      <c r="J44" s="70">
         <f>IF(H44&lt;0,"🔴 Ne pas lancer",IF(I44&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I44&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K44" s="70">
+      <c r="K44" s="71">
         <f>IF(H44&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I44&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I44&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -5311,15 +5327,15 @@
         <f>'08_Moteur'!AM42</f>
         <v/>
       </c>
-      <c r="I45" s="68">
+      <c r="I45" s="69">
         <f>'08_Moteur'!AN42</f>
         <v/>
       </c>
-      <c r="J45" s="69">
+      <c r="J45" s="70">
         <f>IF(H45&lt;0,"🔴 Restructurer (mutualiser)",IF(I45&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K45" s="70">
+      <c r="K45" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5382,15 +5398,15 @@
         <f>'08_Moteur'!AM43</f>
         <v/>
       </c>
-      <c r="I46" s="68">
+      <c r="I46" s="69">
         <f>'08_Moteur'!AN43</f>
         <v/>
       </c>
-      <c r="J46" s="69">
+      <c r="J46" s="70">
         <f>IF(H46&lt;0,"🔴 Restructurer (mutualiser)",IF(I46&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K46" s="70">
+      <c r="K46" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5453,15 +5469,15 @@
         <f>'08_Moteur'!AM44</f>
         <v/>
       </c>
-      <c r="I47" s="68">
+      <c r="I47" s="69">
         <f>'08_Moteur'!AN44</f>
         <v/>
       </c>
-      <c r="J47" s="69">
+      <c r="J47" s="70">
         <f>IF(H47&lt;0,"🔴 Ne pas lancer",IF(I47&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I47&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K47" s="70">
+      <c r="K47" s="71">
         <f>IF(H47&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I47&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I47&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -5524,15 +5540,15 @@
         <f>'08_Moteur'!AM45</f>
         <v/>
       </c>
-      <c r="I48" s="68">
+      <c r="I48" s="69">
         <f>'08_Moteur'!AN45</f>
         <v/>
       </c>
-      <c r="J48" s="69">
+      <c r="J48" s="70">
         <f>IF(H48&lt;0,"🔴 Restructurer (mutualiser)",IF(I48&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K48" s="70">
+      <c r="K48" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5595,15 +5611,15 @@
         <f>'08_Moteur'!AM46</f>
         <v/>
       </c>
-      <c r="I49" s="68">
+      <c r="I49" s="69">
         <f>'08_Moteur'!AN46</f>
         <v/>
       </c>
-      <c r="J49" s="69">
+      <c r="J49" s="70">
         <f>IF(H49&lt;0,"🔴 Restructurer (mutualiser)",IF(I49&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K49" s="70">
+      <c r="K49" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5666,15 +5682,15 @@
         <f>'08_Moteur'!AM47</f>
         <v/>
       </c>
-      <c r="I50" s="68">
+      <c r="I50" s="69">
         <f>'08_Moteur'!AN47</f>
         <v/>
       </c>
-      <c r="J50" s="69">
+      <c r="J50" s="70">
         <f>IF(H50&lt;0,"🔴 Ne pas lancer",IF(I50&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I50&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K50" s="70">
+      <c r="K50" s="71">
         <f>IF(H50&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I50&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I50&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -5737,15 +5753,15 @@
         <f>'08_Moteur'!AM48</f>
         <v/>
       </c>
-      <c r="I51" s="68">
+      <c r="I51" s="69">
         <f>'08_Moteur'!AN48</f>
         <v/>
       </c>
-      <c r="J51" s="69">
+      <c r="J51" s="70">
         <f>IF(H51&lt;0,"🔴 Restructurer (mutualiser)",IF(I51&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K51" s="70">
+      <c r="K51" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5808,15 +5824,15 @@
         <f>'08_Moteur'!AM49</f>
         <v/>
       </c>
-      <c r="I52" s="68">
+      <c r="I52" s="69">
         <f>'08_Moteur'!AN49</f>
         <v/>
       </c>
-      <c r="J52" s="69">
+      <c r="J52" s="70">
         <f>IF(H52&lt;0,"🔴 Ne pas lancer",IF(I52&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I52&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K52" s="70">
+      <c r="K52" s="71">
         <f>IF(H52&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I52&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I52&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -5879,15 +5895,15 @@
         <f>'08_Moteur'!AM50</f>
         <v/>
       </c>
-      <c r="I53" s="68">
+      <c r="I53" s="69">
         <f>'08_Moteur'!AN50</f>
         <v/>
       </c>
-      <c r="J53" s="69">
+      <c r="J53" s="70">
         <f>IF(H53&lt;0,"🔴 Restructurer (mutualiser)",IF(I53&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K53" s="70">
+      <c r="K53" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -5950,15 +5966,15 @@
         <f>'08_Moteur'!AM51</f>
         <v/>
       </c>
-      <c r="I54" s="68">
+      <c r="I54" s="69">
         <f>'08_Moteur'!AN51</f>
         <v/>
       </c>
-      <c r="J54" s="69">
+      <c r="J54" s="70">
         <f>IF(H54&lt;0,"🔴 Ne pas lancer",IF(I54&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I54&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K54" s="70">
+      <c r="K54" s="71">
         <f>IF(H54&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I54&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I54&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -6021,15 +6037,15 @@
         <f>'08_Moteur'!AM52</f>
         <v/>
       </c>
-      <c r="I55" s="68">
+      <c r="I55" s="69">
         <f>'08_Moteur'!AN52</f>
         <v/>
       </c>
-      <c r="J55" s="69">
+      <c r="J55" s="70">
         <f>IF(H55&lt;0,"🔴 Restructurer (mutualiser)",IF(I55&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K55" s="70">
+      <c r="K55" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -6092,15 +6108,15 @@
         <f>'08_Moteur'!AM53</f>
         <v/>
       </c>
-      <c r="I56" s="68">
+      <c r="I56" s="69">
         <f>'08_Moteur'!AN53</f>
         <v/>
       </c>
-      <c r="J56" s="69">
+      <c r="J56" s="70">
         <f>IF(H56&lt;0,"🔴 Ne pas lancer",IF(I56&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I56&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K56" s="70">
+      <c r="K56" s="71">
         <f>IF(H56&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I56&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I56&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -6163,15 +6179,15 @@
         <f>'08_Moteur'!AM54</f>
         <v/>
       </c>
-      <c r="I57" s="68">
+      <c r="I57" s="69">
         <f>'08_Moteur'!AN54</f>
         <v/>
       </c>
-      <c r="J57" s="69">
+      <c r="J57" s="70">
         <f>IF(H57&lt;0,"🔴 Restructurer (mutualiser)",IF(I57&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K57" s="70">
+      <c r="K57" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -6234,15 +6250,15 @@
         <f>'08_Moteur'!AM55</f>
         <v/>
       </c>
-      <c r="I58" s="68">
+      <c r="I58" s="69">
         <f>'08_Moteur'!AN55</f>
         <v/>
       </c>
-      <c r="J58" s="69">
+      <c r="J58" s="70">
         <f>IF(H58&lt;0,"🔴 Ne pas lancer",IF(I58&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I58&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K58" s="70">
+      <c r="K58" s="71">
         <f>IF(H58&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I58&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I58&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -6305,15 +6321,15 @@
         <f>'08_Moteur'!AM56</f>
         <v/>
       </c>
-      <c r="I59" s="68">
+      <c r="I59" s="69">
         <f>'08_Moteur'!AN56</f>
         <v/>
       </c>
-      <c r="J59" s="69">
+      <c r="J59" s="70">
         <f>IF(H59&lt;0,"🔴 Restructurer (mutualiser)",IF(I59&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K59" s="70">
+      <c r="K59" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -6376,15 +6392,15 @@
         <f>'08_Moteur'!AM57</f>
         <v/>
       </c>
-      <c r="I60" s="68">
+      <c r="I60" s="69">
         <f>'08_Moteur'!AN57</f>
         <v/>
       </c>
-      <c r="J60" s="69">
+      <c r="J60" s="70">
         <f>IF(H60&lt;0,"🔴 Restructurer (mutualiser)",IF(I60&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K60" s="70">
+      <c r="K60" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -6447,15 +6463,15 @@
         <f>'08_Moteur'!AM58</f>
         <v/>
       </c>
-      <c r="I61" s="68">
+      <c r="I61" s="69">
         <f>'08_Moteur'!AN58</f>
         <v/>
       </c>
-      <c r="J61" s="69">
+      <c r="J61" s="70">
         <f>IF(H61&lt;0,"🔴 Ne pas lancer",IF(I61&gt;=0.95,"🟢 Ouvrir +1 (capter+diluer)",IF(I61&lt;0.55,"🟡 Surveiller","🟢 Maintenir")))</f>
         <v/>
       </c>
-      <c r="K61" s="70">
+      <c r="K61" s="71">
         <f>IF(H61&lt;0,"Entrée à contribution négative → ne pas lancer cette cohorte",IF(I61&gt;=0.95,"Saturé → ouvrir capte des étudiants ET dilue la structure pour tous",IF(I61&lt;0.55,"Sous-rempli mais contribution positive → garder","Sain")))</f>
         <v/>
       </c>
@@ -6518,15 +6534,15 @@
         <f>'08_Moteur'!AM59</f>
         <v/>
       </c>
-      <c r="I62" s="68">
+      <c r="I62" s="69">
         <f>'08_Moteur'!AN59</f>
         <v/>
       </c>
-      <c r="J62" s="69">
+      <c r="J62" s="70">
         <f>IF(H62&lt;0,"🔴 Restructurer (mutualiser)",IF(I62&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K62" s="70">
+      <c r="K62" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -6589,15 +6605,15 @@
         <f>'08_Moteur'!AM60</f>
         <v/>
       </c>
-      <c r="I63" s="68">
+      <c r="I63" s="69">
         <f>'08_Moteur'!AN60</f>
         <v/>
       </c>
-      <c r="J63" s="69">
+      <c r="J63" s="70">
         <f>IF(H63&lt;0,"🔴 Restructurer (mutualiser)",IF(I63&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
         <v/>
       </c>
-      <c r="K63" s="70">
+      <c r="K63" s="71">
         <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
         <v/>
       </c>
@@ -6628,12 +6644,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
@@ -6709,7 +6726,7 @@
         <f>0.01*SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60*'08_Moteur'!$AF$3:$AF$60)</f>
         <v/>
       </c>
-      <c r="D6" s="70" t="inlineStr">
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>Tombe quasi intégralement en EBITDA.</t>
         </is>
@@ -6725,7 +6742,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$D$18)</f>
         <v/>
       </c>
-      <c r="D7" s="70" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>Nul si recouvrement=100 % ; sinon réduit la perte.</t>
         </is>
@@ -6741,7 +6758,7 @@
         <f>0.01*'02_Leviers'!$D$21*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
         <v/>
       </c>
-      <c r="D8" s="70" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>Plus de leads → plus d'inscrits, net du coût.</t>
         </is>
@@ -6757,7 +6774,7 @@
         <f>0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=0)*'08_Moteur'!$K$3:$K$60)*IFERROR(SUM('08_Moteur'!$AM$3:$AM$60)/SUM('08_Moteur'!$AD$3:$AD$60),0)</f>
         <v/>
       </c>
-      <c r="D9" s="70" t="inlineStr">
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>Rétention : + d'étudiants qui poursuivent.</t>
         </is>
@@ -6769,7 +6786,7 @@
           <t>Exposition financement alternance (€ à sécuriser) :</t>
         </is>
       </c>
-      <c r="D11" s="71">
+      <c r="D11" s="72">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
@@ -7012,20 +7029,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="72" t="inlineStr">
+      <c r="B15" s="73" t="inlineStr">
         <is>
           <t>€ à sécuriser (exposition)</t>
         </is>
       </c>
-      <c r="C15" s="73">
+      <c r="C15" s="74">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
-      <c r="D15" s="73">
+      <c r="D15" s="74">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
         <v/>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="75">
         <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
@@ -7087,7 +7104,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -7104,7 +7121,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -7121,7 +7138,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -7138,7 +7155,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="75" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -7155,7 +7172,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -7172,7 +7189,7 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="76" t="inlineStr">
         <is>
           <t>Sécurisation &amp; recouvrement</t>
         </is>
@@ -7189,7 +7206,7 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>Objectifs (cadrage)</t>
         </is>
@@ -7206,7 +7223,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="75" t="inlineStr">
+      <c r="B13" s="76" t="inlineStr">
         <is>
           <t>Décisions ouvrir/fermer</t>
         </is>
@@ -7223,7 +7240,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="75" t="inlineStr">
+      <c r="B14" s="76" t="inlineStr">
         <is>
           <t>Allocation structure</t>
         </is>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -487,6 +487,836 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Indicateur de pilotage.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Objectif fixé par la direction (saisie).</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Résultat du budget construit par les drivers (moteur).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Budget construit − cible.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Ligne du compte de résultat.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur réelle de l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur budgétée.</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Budget − Réalisé (en €).</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Variation en % vs l'an dernier.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Programme de formation (ex. Bachelor Management).</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Année d'études : B1/B2/B3 (Bachelor), M1/M2 (Mastère), 1/2 (BTS).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif budget de la promo.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Chiffre d'affaires budget de la promo.</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>Coûts qui DISPARAISSENT si on ferme la promo (enseignement, pédago, marketing, autres variables).</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>CA − coûts directs évitables. C'est LA métrique de décision : on ne ferme que si elle est négative.</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <t>Taux de remplissage = effectif / (classes × capacité).</t>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <t>Recommandation automatique (contribution + remplissage). Dépend de l'année : entrée (lancer/capter) vs poursuite (regrouper).</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>Explication de la recommandation.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>Ton choix. Menu restreint selon l'année : entrée = lancer/capter ; poursuite = seulement regrouper.</t>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif après ta décision (0 si 'ne pas lancer' ; +1 classe captée si 'ouvrir').</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>Contribution recalculée selon ta décision.</t>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0" shapeId="0">
+      <text>
+        <t>Quote-part de structure fixe (loyer, permanents, siège) portée par la promo, RECALCULÉE après décisions : moins d'étudiants au total → chacun en porte plus (dilution).</t>
+      </text>
+    </comment>
+    <comment ref="P5" authorId="0" shapeId="0">
+      <text>
+        <t>Contribution après − structure allouée. Vue INFORMATIVE — surtout PAS un critère de fermeture.</t>
+      </text>
+    </comment>
+    <comment ref="Q5" authorId="0" shapeId="0">
+      <text>
+        <t>Impact sur l'EBITDA groupe = contribution après − contribution avant.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Levier testé et son incrément.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Effet € sur l'EBITDA d'un pas du levier (approximation vivante).</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Interprétation.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Indicateur de pilotage.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur budgétée.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur réelle de l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Variation Budget vs N-1.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Scénario actif : change cette cellule et TOUT le budget se recalcule.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeurs du scénario Cadrage (central).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeurs du scénario Optimiste.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeurs du scénario Prudent.</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur ACTIVE = celle du scénario sélectionné en C3.</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Croissance du budget d'acquisition → pilote le volume via l'élasticité mesurée.</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Hausse tarifaire moyenne, modulée par marque (coeff prix).</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>Points de conversion candidature→inscrit gagnés (pilotage admissions).</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>Part des contrats d'alternance sécurisés dans les 3 mois → financement OPCO à 100 %.</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>Amélioration du taux de passage (réinscription) vs l'historique.</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>Inflation appliquée aux charges (pédago, loyers, autres).</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Revalorisation des rémunérations chargées (permanents + enseignement).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Coefficient appliqué à l'effort marketing du cadrage pour cette marque (&gt;1 = on pousse).</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Coefficient appliqué à la hausse tarifaire du cadrage pour cette marque.</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Lecture du positionnement (pousser / défendre / maintenir).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Domaine d'activité de la marque.</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Année d'études (B1, B2, B3, M1, M2…).</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Devise de reporting.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>Clé technique 'programme|année' pour relier les paramètres au moteur.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Programme de formation (ex. Bachelor Management).</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Année d'études : B1/B2/B3 (Bachelor), M1/M2 (Mastère), 1/2 (BTS).</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Modalité : INIT = initial · ALT = alternance (financée OPCO/NPEC).</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Capacité cible d'une classe (nb d'étudiants).</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>Coût horaire chargé de l'enseignement (vacation), en €.</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'acquisition variable (achat de leads) par nouvel inscrit. N'existe qu'en année d'entrée.</t>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0" shapeId="0">
+      <text>
+        <t>Taux de progression de l'année inférieure vers celle-ci (réinscription). Vide en année d'entrée.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Programme de formation (ex. Bachelor Management).</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Type de diplôme : BAC (Bachelor), MAST (Mastère), BTS.</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Année d'études : B1/B2/B3 (Bachelor), M1/M2 (Mastère), 1/2 (BTS).</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>Modalité : INIT = initial · ALT = alternance (financée OPCO/NPEC).</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>1 = année d'entrée (on recrute) · 0 = année de poursuite (cohorte progressée).</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>Candidatures l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>Nouveaux inscrits l'an dernier (entrants).</t>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0" shapeId="0">
+      <text>
+        <t>Réinscrits l'an dernier (étudiants qui poursuivent).</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif réel l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif de l'année juste inférieure l'an dernier — base de la cohorte pour calculer la progression.</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>Tarif moyen l'an dernier (€/étudiant/an).</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>Nombre de classes l'an dernier.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif réel l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Chiffre d'affaires réel l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Marge de contribution réelle l'an dernier (CA − coûts directs).</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>Loyer du campus l'an dernier (coût de structure, fixe).</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>Effectifs permanents (équivalent temps plein) du campus.</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>Masse salariale permanente = ETP × coût chargé par ETP.</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>Dotations aux amortissements l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="J3" authorId="0" shapeId="0">
+      <text>
+        <t>Surface du campus (utilisée comme driver d'allocation possible).</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>EBITDA du campus = contribution − loyer − masse salariale permanente.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>Programme de formation (ex. Bachelor Management).</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>Année d'études : B1/B2/B3 (Bachelor), M1/M2 (Mastère), 1/2 (BTS).</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>Modalité : INIT = initial (payé par la famille) · ALT = alternance (financé OPCO/NPEC).</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>1 = année d'entrée (on recrute) · 0 = année de poursuite (cohorte progressée).</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif réel l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>Nouveaux inscrits l'an dernier (entrants).</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Réinscrits l'an dernier (étudiants qui poursuivent).</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>Candidatures l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif de l'année inférieure l'an dernier (base de progression de la cohorte).</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>Tarif moyen l'an dernier (€/étudiant/an).</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>Nombre de classes l'an dernier.</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Clé programme|année pour retrouver les paramètres (feuille 05).</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>Capacité cible par classe (lue dans 05).</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>Heures d'enseignement par classe/an (05).</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
+        <t>Taux horaire chargé de l'enseignement (05).</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>Coût pédagogique par étudiant (05).</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'acquisition variable par nouvel inscrit (05).</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>Taux de passage de l'année inférieure (05). 0 en année d'entrée.</t>
+      </text>
+    </comment>
+    <comment ref="U2" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'une classe = heures × taux horaire × (1 + politique salariale).</t>
+      </text>
+    </comment>
+    <comment ref="V2" authorId="0" shapeId="0">
+      <text>
+        <t>Coefficient stratégique MARKETING de la marque (feuille 03) — module l'effort par marque.</t>
+      </text>
+    </comment>
+    <comment ref="W2" authorId="0" shapeId="0">
+      <text>
+        <t>Coefficient stratégique PRIX de la marque (feuille 03) — module la hausse tarifaire par marque.</t>
+      </text>
+    </comment>
+    <comment ref="X2" authorId="0" shapeId="0">
+      <text>
+        <t>Élasticité marketing mesurée (06). Repli si historique manquant.</t>
+      </text>
+    </comment>
+    <comment ref="Y2" authorId="0" shapeId="0">
+      <text>
+        <t>Effort marketing appliqué = levier 'variation budget marketing' × coefficient marque.</t>
+      </text>
+    </comment>
+    <comment ref="Z2" authorId="0" shapeId="0">
+      <text>
+        <t>Candidatures budget = candidatures N-1 × (1 + élasticité × effort marketing).</t>
+      </text>
+    </comment>
+    <comment ref="AA2" authorId="0" shapeId="0">
+      <text>
+        <t>Taux de conversion candidature→inscrit (mesuré par cellule) + gain du levier conversion.</t>
+      </text>
+    </comment>
+    <comment ref="AB2" authorId="0" shapeId="0">
+      <text>
+        <t>Nouveaux inscrits budget = candidatures budget × taux de conversion.</t>
+      </text>
+    </comment>
+    <comment ref="AC2" authorId="0" shapeId="0">
+      <text>
+        <t>Réinscrits budget = effectif de l'année inférieure (N-1) × (taux de passage + amélioration).</t>
+      </text>
+    </comment>
+    <comment ref="AD2" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif budget = nouveaux + réinscrits.</t>
+      </text>
+    </comment>
+    <comment ref="AE2" authorId="0" shapeId="0">
+      <text>
+        <t>Tarif budget = tarif N-1 × (1 + hausse prix × coefficient marque).</t>
+      </text>
+    </comment>
+    <comment ref="AF2" authorId="0" shapeId="0">
+      <text>
+        <t>Facteur de financement alternance BUDGET (sécurisation + reste à charge recouvré). = 1 en initial.</t>
+      </text>
+    </comment>
+    <comment ref="AG2" authorId="0" shapeId="0">
+      <text>
+        <t>Facteur de financement alternance N-1 (référence pour le pont).</t>
+      </text>
+    </comment>
+    <comment ref="AH2" authorId="0" shapeId="0">
+      <text>
+        <t>CA budget = effectif × tarif × facteur financement + frais de dossier.</t>
+      </text>
+    </comment>
+    <comment ref="AI2" authorId="0" shapeId="0">
+      <text>
+        <t>Classes nécessaires = arrondi supérieur (effectif / capacité).</t>
+      </text>
+    </comment>
+    <comment ref="AJ2" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'enseignement = classes × coût par classe.</t>
+      </text>
+    </comment>
+    <comment ref="AK2" authorId="0" shapeId="0">
+      <text>
+        <t>Coût pédagogique = effectif × coût pédago/étudiant × (1 + inflation).</t>
+      </text>
+    </comment>
+    <comment ref="AL2" authorId="0" shapeId="0">
+      <text>
+        <t>Marketing = nouveaux × CAC variable × (1 + effort). = 0 en année de poursuite.</t>
+      </text>
+    </comment>
+    <comment ref="AM2" authorId="0" shapeId="0">
+      <text>
+        <t>MARGE DE CONTRIBUTION = CA − enseignement − pédago − marketing − autres charges.</t>
+      </text>
+    </comment>
+    <comment ref="AN2" authorId="0" shapeId="0">
+      <text>
+        <t>Taux de remplissage = effectif / (classes × capacité).</t>
+      </text>
+    </comment>
+    <comment ref="AO2" authorId="0" shapeId="0">
+      <text>
+        <t>Contribution par étudiant.</t>
+      </text>
+    </comment>
+    <comment ref="AP2" authorId="0" shapeId="0">
+      <text>
+        <t>Point mort = nb d'étudiants pour couvrir le coût des classes.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Marge de contribution (CA − coûts directs évitables).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Loyer du campus (structure fixe).</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Masse salariale permanente (structure fixe).</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur du driver d'allocation (effectif, CA ou m² selon 02_Leviers).</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Part du campus dans le driver total.</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <t>Frais de structure groupe alloués à ce campus.</t>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <t>EBITDA du campus = contribution − loyer − permanents − structure allouée.</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>Dotations aux amortissements.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>Résultat d'exploitation = EBITDA − D&amp;A.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1077,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L20"/>
+  <dimension ref="A2:AS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1907,6 +2737,7 @@
     <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1916,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F25"/>
+  <dimension ref="A2:AS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2321,6 +3152,7 @@
     <mergeCell ref="B18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2330,7 +3162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:AS63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6667,6 +7499,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6676,7 +7509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D11"/>
+  <dimension ref="A2:AS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6798,6 +7631,7 @@
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6807,7 +7641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E15"/>
+  <dimension ref="A2:AS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7052,6 +7886,7 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7061,7 +7896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D14"/>
+  <dimension ref="A2:AS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7271,7 +8106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E14"/>
+  <dimension ref="A2:AS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7400,6 +8235,7 @@
     <mergeCell ref="B12:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7919,6 +8755,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7928,7 +8765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E10"/>
+  <dimension ref="A2:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8065,6 +8902,7 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -8074,7 +8912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="A2:AS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8823,6 +9661,7 @@
     <mergeCell ref="B22:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -8832,7 +9671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:AS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9703,6 +10542,7 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -9712,7 +10552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:AS73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -13316,6 +14156,7 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -13325,7 +14166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:AS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -14032,6 +14873,7 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -14041,7 +14883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AS61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -24247,5 +25089,6 @@
     <mergeCell ref="A1:AP1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -9824,7 +9824,7 @@
         <v>400</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>0.85</v>
@@ -9864,7 +9864,7 @@
         <v>400</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>0.9</v>
@@ -9942,7 +9942,7 @@
         <v>520</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J8" s="25" t="n">
         <v>0.92</v>
@@ -10020,7 +10020,7 @@
         <v>550</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>0.85</v>
@@ -10060,7 +10060,7 @@
         <v>550</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>0.9</v>
@@ -10138,7 +10138,7 @@
         <v>670</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J13" s="25" t="n">
         <v>0.92</v>
@@ -10216,7 +10216,7 @@
         <v>380</v>
       </c>
       <c r="I15" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J15" s="25" t="n">
         <v>0.85</v>
@@ -10256,7 +10256,7 @@
         <v>380</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J16" s="25" t="n">
         <v>0.9</v>
@@ -10334,7 +10334,7 @@
         <v>350</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J18" s="25" t="n">
         <v>0.9</v>
@@ -10412,7 +10412,7 @@
         <v>380</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J20" s="25" t="n">
         <v>0.9</v>
@@ -10490,7 +10490,7 @@
         <v>450</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J22" s="25" t="n">
         <v>0.85</v>
@@ -10530,7 +10530,7 @@
         <v>450</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J23" s="25" t="n">
         <v>0.9</v>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="D19" s="28" t="n">
-        <v>380</v>
+        <v>934</v>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
@@ -14264,13 +14264,13 @@
         <v>2467250</v>
       </c>
       <c r="E4" s="41" t="n">
-        <v>1785470</v>
+        <v>1624256</v>
       </c>
       <c r="F4" s="41" t="n">
         <v>271000</v>
       </c>
       <c r="G4" s="39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="17">
         <f>G4*'02_Leviers'!$D$15</f>
@@ -14305,13 +14305,13 @@
         <v>2102540</v>
       </c>
       <c r="E5" s="41" t="n">
-        <v>1531180</v>
+        <v>1393788</v>
       </c>
       <c r="F5" s="41" t="n">
         <v>231000</v>
       </c>
       <c r="G5" s="39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" s="17">
         <f>G5*'02_Leviers'!$D$15</f>
@@ -14346,13 +14346,13 @@
         <v>1898640</v>
       </c>
       <c r="E6" s="41" t="n">
-        <v>1351280</v>
+        <v>1227184</v>
       </c>
       <c r="F6" s="41" t="n">
         <v>209000</v>
       </c>
       <c r="G6" s="39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" s="17">
         <f>G6*'02_Leviers'!$D$15</f>
@@ -14387,13 +14387,13 @@
         <v>1619880</v>
       </c>
       <c r="E7" s="41" t="n">
-        <v>1105220</v>
+        <v>999406</v>
       </c>
       <c r="F7" s="41" t="n">
         <v>178000</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="17">
         <f>G7*'02_Leviers'!$D$15</f>
@@ -14428,13 +14428,13 @@
         <v>2280350</v>
       </c>
       <c r="E8" s="41" t="n">
-        <v>1589820</v>
+        <v>1440794</v>
       </c>
       <c r="F8" s="41" t="n">
         <v>251000</v>
       </c>
       <c r="G8" s="39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" s="17">
         <f>G8*'02_Leviers'!$D$15</f>
@@ -14469,13 +14469,13 @@
         <v>1585200</v>
       </c>
       <c r="E9" s="41" t="n">
-        <v>1025970</v>
+        <v>922372</v>
       </c>
       <c r="F9" s="41" t="n">
         <v>174000</v>
       </c>
       <c r="G9" s="39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="17">
         <f>G9*'02_Leviers'!$D$15</f>
@@ -14510,13 +14510,13 @@
         <v>1483250</v>
       </c>
       <c r="E10" s="41" t="n">
-        <v>937820</v>
+        <v>840870</v>
       </c>
       <c r="F10" s="41" t="n">
         <v>163000</v>
       </c>
       <c r="G10" s="39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" s="17">
         <f>G10*'02_Leviers'!$D$15</f>
@@ -14551,13 +14551,13 @@
         <v>1044500</v>
       </c>
       <c r="E11" s="41" t="n">
-        <v>734820</v>
+        <v>662800</v>
       </c>
       <c r="F11" s="41" t="n">
         <v>115000</v>
       </c>
       <c r="G11" s="39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H11" s="17">
         <f>G11*'02_Leviers'!$D$15</f>
@@ -14592,13 +14592,13 @@
         <v>835600</v>
       </c>
       <c r="E12" s="41" t="n">
-        <v>579040</v>
+        <v>521424</v>
       </c>
       <c r="F12" s="41" t="n">
         <v>92000</v>
       </c>
       <c r="G12" s="39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H12" s="17">
         <f>G12*'02_Leviers'!$D$15</f>
@@ -14633,13 +14633,13 @@
         <v>835600</v>
       </c>
       <c r="E13" s="41" t="n">
-        <v>579040</v>
+        <v>521424</v>
       </c>
       <c r="F13" s="41" t="n">
         <v>92000</v>
       </c>
       <c r="G13" s="39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" s="17">
         <f>G13*'02_Leviers'!$D$15</f>
@@ -14674,13 +14674,13 @@
         <v>1130470</v>
       </c>
       <c r="E14" s="41" t="n">
-        <v>711410</v>
+        <v>628864</v>
       </c>
       <c r="F14" s="41" t="n">
         <v>124000</v>
       </c>
       <c r="G14" s="39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="17">
         <f>G14*'02_Leviers'!$D$15</f>
@@ -14715,13 +14715,13 @@
         <v>887850</v>
       </c>
       <c r="E15" s="41" t="n">
-        <v>605020</v>
+        <v>540202</v>
       </c>
       <c r="F15" s="41" t="n">
         <v>98000</v>
       </c>
       <c r="G15" s="39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="17">
         <f>G15*'02_Leviers'!$D$15</f>
@@ -14756,13 +14756,13 @@
         <v>980230</v>
       </c>
       <c r="E16" s="41" t="n">
-        <v>675770</v>
+        <v>608182</v>
       </c>
       <c r="F16" s="41" t="n">
         <v>108000</v>
       </c>
       <c r="G16" s="39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="17">
         <f>G16*'02_Leviers'!$D$15</f>
@@ -14797,13 +14797,13 @@
         <v>835600</v>
       </c>
       <c r="E17" s="41" t="n">
-        <v>577440</v>
+        <v>519824</v>
       </c>
       <c r="F17" s="41" t="n">
         <v>92000</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H17" s="17">
         <f>G17*'02_Leviers'!$D$15</f>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -625,7 +625,7 @@
     </comment>
     <comment ref="N5" authorId="0" shapeId="0">
       <text>
-        <t>Contribution recalculée selon ta décision.</t>
+        <t>Contribution recalculée selon ta décision. Regrouper (−1 classe) n'est crédité (économie d'une classe) QUE si l'effectif tient dans les classes restantes : effectif ≤ (classes−1) × capacité × 1,10 (tolérance salle +10%). Sinon aucune économie : le regroupement déborderait la capacité.</t>
       </text>
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
@@ -3412,7 +3412,7 @@
         <v/>
       </c>
       <c r="N6" s="17">
-        <f>IF(L6="Ne pas lancer",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Regrouper (-1 classe)",H6+('08_Moteur'!AI3-MAX(1,'08_Moteur'!AI3-1))*'08_Moteur'!U3,H6)))</f>
+        <f>IF(L6="Ne pas lancer",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI3&gt;=2,E6&lt;=('08_Moteur'!AI3-1)*'08_Moteur'!O3*1.1),H6+'08_Moteur'!U3,H6),H6)))</f>
         <v/>
       </c>
       <c r="O6" s="17">
@@ -3466,11 +3466,11 @@
         <v/>
       </c>
       <c r="J7" s="70">
-        <f>IF(H7&lt;0,"🔴 Restructurer (mutualiser)",IF(I7&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H7&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI4&gt;=2,E7&lt;=('08_Moteur'!AI4-1)*'08_Moteur'!O4*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I7&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K7" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI4&gt;=2,TEXT(IFERROR(E7/(('08_Moteur'!AI4-1)*'08_Moteur'!O4),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -3483,7 +3483,7 @@
         <v/>
       </c>
       <c r="N7" s="17">
-        <f>IF(L7="Ne pas lancer",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Regrouper (-1 classe)",H7+('08_Moteur'!AI4-MAX(1,'08_Moteur'!AI4-1))*'08_Moteur'!U4,H7)))</f>
+        <f>IF(L7="Ne pas lancer",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI4&gt;=2,E7&lt;=('08_Moteur'!AI4-1)*'08_Moteur'!O4*1.1),H7+'08_Moteur'!U4,H7),H7)))</f>
         <v/>
       </c>
       <c r="O7" s="17">
@@ -3537,11 +3537,11 @@
         <v/>
       </c>
       <c r="J8" s="70">
-        <f>IF(H8&lt;0,"🔴 Restructurer (mutualiser)",IF(I8&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H8&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI5&gt;=2,E8&lt;=('08_Moteur'!AI5-1)*'08_Moteur'!O5*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I8&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K8" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI5&gt;=2,TEXT(IFERROR(E8/(('08_Moteur'!AI5-1)*'08_Moteur'!O5),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -3554,7 +3554,7 @@
         <v/>
       </c>
       <c r="N8" s="17">
-        <f>IF(L8="Ne pas lancer",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Regrouper (-1 classe)",H8+('08_Moteur'!AI5-MAX(1,'08_Moteur'!AI5-1))*'08_Moteur'!U5,H8)))</f>
+        <f>IF(L8="Ne pas lancer",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI5&gt;=2,E8&lt;=('08_Moteur'!AI5-1)*'08_Moteur'!O5*1.1),H8+'08_Moteur'!U5,H8),H8)))</f>
         <v/>
       </c>
       <c r="O8" s="17">
@@ -3625,7 +3625,7 @@
         <v/>
       </c>
       <c r="N9" s="17">
-        <f>IF(L9="Ne pas lancer",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Regrouper (-1 classe)",H9+('08_Moteur'!AI6-MAX(1,'08_Moteur'!AI6-1))*'08_Moteur'!U6,H9)))</f>
+        <f>IF(L9="Ne pas lancer",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI6&gt;=2,E9&lt;=('08_Moteur'!AI6-1)*'08_Moteur'!O6*1.1),H9+'08_Moteur'!U6,H9),H9)))</f>
         <v/>
       </c>
       <c r="O9" s="17">
@@ -3679,11 +3679,11 @@
         <v/>
       </c>
       <c r="J10" s="70">
-        <f>IF(H10&lt;0,"🔴 Restructurer (mutualiser)",IF(I10&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H10&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI7&gt;=2,E10&lt;=('08_Moteur'!AI7-1)*'08_Moteur'!O7*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I10&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K10" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI7&gt;=2,TEXT(IFERROR(E10/(('08_Moteur'!AI7-1)*'08_Moteur'!O7),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v/>
       </c>
       <c r="N10" s="17">
-        <f>IF(L10="Ne pas lancer",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Regrouper (-1 classe)",H10+('08_Moteur'!AI7-MAX(1,'08_Moteur'!AI7-1))*'08_Moteur'!U7,H10)))</f>
+        <f>IF(L10="Ne pas lancer",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI7&gt;=2,E10&lt;=('08_Moteur'!AI7-1)*'08_Moteur'!O7*1.1),H10+'08_Moteur'!U7,H10),H10)))</f>
         <v/>
       </c>
       <c r="O10" s="17">
@@ -3767,7 +3767,7 @@
         <v/>
       </c>
       <c r="N11" s="17">
-        <f>IF(L11="Ne pas lancer",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Regrouper (-1 classe)",H11+('08_Moteur'!AI8-MAX(1,'08_Moteur'!AI8-1))*'08_Moteur'!U8,H11)))</f>
+        <f>IF(L11="Ne pas lancer",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI8&gt;=2,E11&lt;=('08_Moteur'!AI8-1)*'08_Moteur'!O8*1.1),H11+'08_Moteur'!U8,H11),H11)))</f>
         <v/>
       </c>
       <c r="O11" s="17">
@@ -3821,11 +3821,11 @@
         <v/>
       </c>
       <c r="J12" s="70">
-        <f>IF(H12&lt;0,"🔴 Restructurer (mutualiser)",IF(I12&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H12&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI9&gt;=2,E12&lt;=('08_Moteur'!AI9-1)*'08_Moteur'!O9*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I12&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K12" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI9&gt;=2,TEXT(IFERROR(E12/(('08_Moteur'!AI9-1)*'08_Moteur'!O9),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -3838,7 +3838,7 @@
         <v/>
       </c>
       <c r="N12" s="17">
-        <f>IF(L12="Ne pas lancer",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Regrouper (-1 classe)",H12+('08_Moteur'!AI9-MAX(1,'08_Moteur'!AI9-1))*'08_Moteur'!U9,H12)))</f>
+        <f>IF(L12="Ne pas lancer",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI9&gt;=2,E12&lt;=('08_Moteur'!AI9-1)*'08_Moteur'!O9*1.1),H12+'08_Moteur'!U9,H12),H12)))</f>
         <v/>
       </c>
       <c r="O12" s="17">
@@ -3892,11 +3892,11 @@
         <v/>
       </c>
       <c r="J13" s="70">
-        <f>IF(H13&lt;0,"🔴 Restructurer (mutualiser)",IF(I13&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H13&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI10&gt;=2,E13&lt;=('08_Moteur'!AI10-1)*'08_Moteur'!O10*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I13&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K13" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI10&gt;=2,TEXT(IFERROR(E13/(('08_Moteur'!AI10-1)*'08_Moteur'!O10),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="N13" s="17">
-        <f>IF(L13="Ne pas lancer",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Regrouper (-1 classe)",H13+('08_Moteur'!AI10-MAX(1,'08_Moteur'!AI10-1))*'08_Moteur'!U10,H13)))</f>
+        <f>IF(L13="Ne pas lancer",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI10&gt;=2,E13&lt;=('08_Moteur'!AI10-1)*'08_Moteur'!O10*1.1),H13+'08_Moteur'!U10,H13),H13)))</f>
         <v/>
       </c>
       <c r="O13" s="17">
@@ -3980,7 +3980,7 @@
         <v/>
       </c>
       <c r="N14" s="17">
-        <f>IF(L14="Ne pas lancer",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Regrouper (-1 classe)",H14+('08_Moteur'!AI11-MAX(1,'08_Moteur'!AI11-1))*'08_Moteur'!U11,H14)))</f>
+        <f>IF(L14="Ne pas lancer",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI11&gt;=2,E14&lt;=('08_Moteur'!AI11-1)*'08_Moteur'!O11*1.1),H14+'08_Moteur'!U11,H14),H14)))</f>
         <v/>
       </c>
       <c r="O14" s="17">
@@ -4034,11 +4034,11 @@
         <v/>
       </c>
       <c r="J15" s="70">
-        <f>IF(H15&lt;0,"🔴 Restructurer (mutualiser)",IF(I15&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H15&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI12&gt;=2,E15&lt;=('08_Moteur'!AI12-1)*'08_Moteur'!O12*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I15&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K15" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI12&gt;=2,TEXT(IFERROR(E15/(('08_Moteur'!AI12-1)*'08_Moteur'!O12),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -4051,7 +4051,7 @@
         <v/>
       </c>
       <c r="N15" s="17">
-        <f>IF(L15="Ne pas lancer",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Regrouper (-1 classe)",H15+('08_Moteur'!AI12-MAX(1,'08_Moteur'!AI12-1))*'08_Moteur'!U12,H15)))</f>
+        <f>IF(L15="Ne pas lancer",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI12&gt;=2,E15&lt;=('08_Moteur'!AI12-1)*'08_Moteur'!O12*1.1),H15+'08_Moteur'!U12,H15),H15)))</f>
         <v/>
       </c>
       <c r="O15" s="17">
@@ -4122,7 +4122,7 @@
         <v/>
       </c>
       <c r="N16" s="17">
-        <f>IF(L16="Ne pas lancer",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Regrouper (-1 classe)",H16+('08_Moteur'!AI13-MAX(1,'08_Moteur'!AI13-1))*'08_Moteur'!U13,H16)))</f>
+        <f>IF(L16="Ne pas lancer",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI13&gt;=2,E16&lt;=('08_Moteur'!AI13-1)*'08_Moteur'!O13*1.1),H16+'08_Moteur'!U13,H16),H16)))</f>
         <v/>
       </c>
       <c r="O16" s="17">
@@ -4176,11 +4176,11 @@
         <v/>
       </c>
       <c r="J17" s="70">
-        <f>IF(H17&lt;0,"🔴 Restructurer (mutualiser)",IF(I17&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H17&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI14&gt;=2,E17&lt;=('08_Moteur'!AI14-1)*'08_Moteur'!O14*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I17&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K17" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI14&gt;=2,TEXT(IFERROR(E17/(('08_Moteur'!AI14-1)*'08_Moteur'!O14),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -4193,7 +4193,7 @@
         <v/>
       </c>
       <c r="N17" s="17">
-        <f>IF(L17="Ne pas lancer",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Regrouper (-1 classe)",H17+('08_Moteur'!AI14-MAX(1,'08_Moteur'!AI14-1))*'08_Moteur'!U14,H17)))</f>
+        <f>IF(L17="Ne pas lancer",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI14&gt;=2,E17&lt;=('08_Moteur'!AI14-1)*'08_Moteur'!O14*1.1),H17+'08_Moteur'!U14,H17),H17)))</f>
         <v/>
       </c>
       <c r="O17" s="17">
@@ -4247,11 +4247,11 @@
         <v/>
       </c>
       <c r="J18" s="70">
-        <f>IF(H18&lt;0,"🔴 Restructurer (mutualiser)",IF(I18&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H18&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI15&gt;=2,E18&lt;=('08_Moteur'!AI15-1)*'08_Moteur'!O15*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I18&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K18" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI15&gt;=2,TEXT(IFERROR(E18/(('08_Moteur'!AI15-1)*'08_Moteur'!O15),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -4264,7 +4264,7 @@
         <v/>
       </c>
       <c r="N18" s="17">
-        <f>IF(L18="Ne pas lancer",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Regrouper (-1 classe)",H18+('08_Moteur'!AI15-MAX(1,'08_Moteur'!AI15-1))*'08_Moteur'!U15,H18)))</f>
+        <f>IF(L18="Ne pas lancer",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI15&gt;=2,E18&lt;=('08_Moteur'!AI15-1)*'08_Moteur'!O15*1.1),H18+'08_Moteur'!U15,H18),H18)))</f>
         <v/>
       </c>
       <c r="O18" s="17">
@@ -4335,7 +4335,7 @@
         <v/>
       </c>
       <c r="N19" s="17">
-        <f>IF(L19="Ne pas lancer",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Regrouper (-1 classe)",H19+('08_Moteur'!AI16-MAX(1,'08_Moteur'!AI16-1))*'08_Moteur'!U16,H19)))</f>
+        <f>IF(L19="Ne pas lancer",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI16&gt;=2,E19&lt;=('08_Moteur'!AI16-1)*'08_Moteur'!O16*1.1),H19+'08_Moteur'!U16,H19),H19)))</f>
         <v/>
       </c>
       <c r="O19" s="17">
@@ -4389,11 +4389,11 @@
         <v/>
       </c>
       <c r="J20" s="70">
-        <f>IF(H20&lt;0,"🔴 Restructurer (mutualiser)",IF(I20&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H20&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI17&gt;=2,E20&lt;=('08_Moteur'!AI17-1)*'08_Moteur'!O17*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I20&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K20" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI17&gt;=2,TEXT(IFERROR(E20/(('08_Moteur'!AI17-1)*'08_Moteur'!O17),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -4406,7 +4406,7 @@
         <v/>
       </c>
       <c r="N20" s="17">
-        <f>IF(L20="Ne pas lancer",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Regrouper (-1 classe)",H20+('08_Moteur'!AI17-MAX(1,'08_Moteur'!AI17-1))*'08_Moteur'!U17,H20)))</f>
+        <f>IF(L20="Ne pas lancer",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI17&gt;=2,E20&lt;=('08_Moteur'!AI17-1)*'08_Moteur'!O17*1.1),H20+'08_Moteur'!U17,H20),H20)))</f>
         <v/>
       </c>
       <c r="O20" s="17">
@@ -4477,7 +4477,7 @@
         <v/>
       </c>
       <c r="N21" s="17">
-        <f>IF(L21="Ne pas lancer",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Regrouper (-1 classe)",H21+('08_Moteur'!AI18-MAX(1,'08_Moteur'!AI18-1))*'08_Moteur'!U18,H21)))</f>
+        <f>IF(L21="Ne pas lancer",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI18&gt;=2,E21&lt;=('08_Moteur'!AI18-1)*'08_Moteur'!O18*1.1),H21+'08_Moteur'!U18,H21),H21)))</f>
         <v/>
       </c>
       <c r="O21" s="17">
@@ -4531,11 +4531,11 @@
         <v/>
       </c>
       <c r="J22" s="70">
-        <f>IF(H22&lt;0,"🔴 Restructurer (mutualiser)",IF(I22&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H22&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI19&gt;=2,E22&lt;=('08_Moteur'!AI19-1)*'08_Moteur'!O19*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I22&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K22" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI19&gt;=2,TEXT(IFERROR(E22/(('08_Moteur'!AI19-1)*'08_Moteur'!O19),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -4548,7 +4548,7 @@
         <v/>
       </c>
       <c r="N22" s="17">
-        <f>IF(L22="Ne pas lancer",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Regrouper (-1 classe)",H22+('08_Moteur'!AI19-MAX(1,'08_Moteur'!AI19-1))*'08_Moteur'!U19,H22)))</f>
+        <f>IF(L22="Ne pas lancer",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI19&gt;=2,E22&lt;=('08_Moteur'!AI19-1)*'08_Moteur'!O19*1.1),H22+'08_Moteur'!U19,H22),H22)))</f>
         <v/>
       </c>
       <c r="O22" s="17">
@@ -4602,11 +4602,11 @@
         <v/>
       </c>
       <c r="J23" s="70">
-        <f>IF(H23&lt;0,"🔴 Restructurer (mutualiser)",IF(I23&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H23&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI20&gt;=2,E23&lt;=('08_Moteur'!AI20-1)*'08_Moteur'!O20*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I23&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K23" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI20&gt;=2,TEXT(IFERROR(E23/(('08_Moteur'!AI20-1)*'08_Moteur'!O20),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="N23" s="17">
-        <f>IF(L23="Ne pas lancer",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Regrouper (-1 classe)",H23+('08_Moteur'!AI20-MAX(1,'08_Moteur'!AI20-1))*'08_Moteur'!U20,H23)))</f>
+        <f>IF(L23="Ne pas lancer",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI20&gt;=2,E23&lt;=('08_Moteur'!AI20-1)*'08_Moteur'!O20*1.1),H23+'08_Moteur'!U20,H23),H23)))</f>
         <v/>
       </c>
       <c r="O23" s="17">
@@ -4690,7 +4690,7 @@
         <v/>
       </c>
       <c r="N24" s="17">
-        <f>IF(L24="Ne pas lancer",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Regrouper (-1 classe)",H24+('08_Moteur'!AI21-MAX(1,'08_Moteur'!AI21-1))*'08_Moteur'!U21,H24)))</f>
+        <f>IF(L24="Ne pas lancer",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI21&gt;=2,E24&lt;=('08_Moteur'!AI21-1)*'08_Moteur'!O21*1.1),H24+'08_Moteur'!U21,H24),H24)))</f>
         <v/>
       </c>
       <c r="O24" s="17">
@@ -4744,11 +4744,11 @@
         <v/>
       </c>
       <c r="J25" s="70">
-        <f>IF(H25&lt;0,"🔴 Restructurer (mutualiser)",IF(I25&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H25&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI22&gt;=2,E25&lt;=('08_Moteur'!AI22-1)*'08_Moteur'!O22*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I25&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K25" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI22&gt;=2,TEXT(IFERROR(E25/(('08_Moteur'!AI22-1)*'08_Moteur'!O22),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -4761,7 +4761,7 @@
         <v/>
       </c>
       <c r="N25" s="17">
-        <f>IF(L25="Ne pas lancer",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Regrouper (-1 classe)",H25+('08_Moteur'!AI22-MAX(1,'08_Moteur'!AI22-1))*'08_Moteur'!U22,H25)))</f>
+        <f>IF(L25="Ne pas lancer",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI22&gt;=2,E25&lt;=('08_Moteur'!AI22-1)*'08_Moteur'!O22*1.1),H25+'08_Moteur'!U22,H25),H25)))</f>
         <v/>
       </c>
       <c r="O25" s="17">
@@ -4832,7 +4832,7 @@
         <v/>
       </c>
       <c r="N26" s="17">
-        <f>IF(L26="Ne pas lancer",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Regrouper (-1 classe)",H26+('08_Moteur'!AI23-MAX(1,'08_Moteur'!AI23-1))*'08_Moteur'!U23,H26)))</f>
+        <f>IF(L26="Ne pas lancer",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI23&gt;=2,E26&lt;=('08_Moteur'!AI23-1)*'08_Moteur'!O23*1.1),H26+'08_Moteur'!U23,H26),H26)))</f>
         <v/>
       </c>
       <c r="O26" s="17">
@@ -4886,11 +4886,11 @@
         <v/>
       </c>
       <c r="J27" s="70">
-        <f>IF(H27&lt;0,"🔴 Restructurer (mutualiser)",IF(I27&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H27&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI24&gt;=2,E27&lt;=('08_Moteur'!AI24-1)*'08_Moteur'!O24*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I27&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K27" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI24&gt;=2,TEXT(IFERROR(E27/(('08_Moteur'!AI24-1)*'08_Moteur'!O24),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -4903,7 +4903,7 @@
         <v/>
       </c>
       <c r="N27" s="17">
-        <f>IF(L27="Ne pas lancer",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Regrouper (-1 classe)",H27+('08_Moteur'!AI24-MAX(1,'08_Moteur'!AI24-1))*'08_Moteur'!U24,H27)))</f>
+        <f>IF(L27="Ne pas lancer",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI24&gt;=2,E27&lt;=('08_Moteur'!AI24-1)*'08_Moteur'!O24*1.1),H27+'08_Moteur'!U24,H27),H27)))</f>
         <v/>
       </c>
       <c r="O27" s="17">
@@ -4957,11 +4957,11 @@
         <v/>
       </c>
       <c r="J28" s="70">
-        <f>IF(H28&lt;0,"🔴 Restructurer (mutualiser)",IF(I28&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H28&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI25&gt;=2,E28&lt;=('08_Moteur'!AI25-1)*'08_Moteur'!O25*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I28&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K28" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI25&gt;=2,TEXT(IFERROR(E28/(('08_Moteur'!AI25-1)*'08_Moteur'!O25),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -4974,7 +4974,7 @@
         <v/>
       </c>
       <c r="N28" s="17">
-        <f>IF(L28="Ne pas lancer",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Regrouper (-1 classe)",H28+('08_Moteur'!AI25-MAX(1,'08_Moteur'!AI25-1))*'08_Moteur'!U25,H28)))</f>
+        <f>IF(L28="Ne pas lancer",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI25&gt;=2,E28&lt;=('08_Moteur'!AI25-1)*'08_Moteur'!O25*1.1),H28+'08_Moteur'!U25,H28),H28)))</f>
         <v/>
       </c>
       <c r="O28" s="17">
@@ -5045,7 +5045,7 @@
         <v/>
       </c>
       <c r="N29" s="17">
-        <f>IF(L29="Ne pas lancer",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Regrouper (-1 classe)",H29+('08_Moteur'!AI26-MAX(1,'08_Moteur'!AI26-1))*'08_Moteur'!U26,H29)))</f>
+        <f>IF(L29="Ne pas lancer",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI26&gt;=2,E29&lt;=('08_Moteur'!AI26-1)*'08_Moteur'!O26*1.1),H29+'08_Moteur'!U26,H29),H29)))</f>
         <v/>
       </c>
       <c r="O29" s="17">
@@ -5099,11 +5099,11 @@
         <v/>
       </c>
       <c r="J30" s="70">
-        <f>IF(H30&lt;0,"🔴 Restructurer (mutualiser)",IF(I30&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H30&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI27&gt;=2,E30&lt;=('08_Moteur'!AI27-1)*'08_Moteur'!O27*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I30&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K30" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI27&gt;=2,TEXT(IFERROR(E30/(('08_Moteur'!AI27-1)*'08_Moteur'!O27),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -5116,7 +5116,7 @@
         <v/>
       </c>
       <c r="N30" s="17">
-        <f>IF(L30="Ne pas lancer",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Regrouper (-1 classe)",H30+('08_Moteur'!AI27-MAX(1,'08_Moteur'!AI27-1))*'08_Moteur'!U27,H30)))</f>
+        <f>IF(L30="Ne pas lancer",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI27&gt;=2,E30&lt;=('08_Moteur'!AI27-1)*'08_Moteur'!O27*1.1),H30+'08_Moteur'!U27,H30),H30)))</f>
         <v/>
       </c>
       <c r="O30" s="17">
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="N31" s="17">
-        <f>IF(L31="Ne pas lancer",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Regrouper (-1 classe)",H31+('08_Moteur'!AI28-MAX(1,'08_Moteur'!AI28-1))*'08_Moteur'!U28,H31)))</f>
+        <f>IF(L31="Ne pas lancer",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI28&gt;=2,E31&lt;=('08_Moteur'!AI28-1)*'08_Moteur'!O28*1.1),H31+'08_Moteur'!U28,H31),H31)))</f>
         <v/>
       </c>
       <c r="O31" s="17">
@@ -5241,11 +5241,11 @@
         <v/>
       </c>
       <c r="J32" s="70">
-        <f>IF(H32&lt;0,"🔴 Restructurer (mutualiser)",IF(I32&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H32&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI29&gt;=2,E32&lt;=('08_Moteur'!AI29-1)*'08_Moteur'!O29*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I32&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K32" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI29&gt;=2,TEXT(IFERROR(E32/(('08_Moteur'!AI29-1)*'08_Moteur'!O29),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L32" s="21" t="inlineStr">
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="N32" s="17">
-        <f>IF(L32="Ne pas lancer",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Regrouper (-1 classe)",H32+('08_Moteur'!AI29-MAX(1,'08_Moteur'!AI29-1))*'08_Moteur'!U29,H32)))</f>
+        <f>IF(L32="Ne pas lancer",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI29&gt;=2,E32&lt;=('08_Moteur'!AI29-1)*'08_Moteur'!O29*1.1),H32+'08_Moteur'!U29,H32),H32)))</f>
         <v/>
       </c>
       <c r="O32" s="17">
@@ -5312,11 +5312,11 @@
         <v/>
       </c>
       <c r="J33" s="70">
-        <f>IF(H33&lt;0,"🔴 Restructurer (mutualiser)",IF(I33&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H33&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI30&gt;=2,E33&lt;=('08_Moteur'!AI30-1)*'08_Moteur'!O30*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I33&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K33" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI30&gt;=2,TEXT(IFERROR(E33/(('08_Moteur'!AI30-1)*'08_Moteur'!O30),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -5329,7 +5329,7 @@
         <v/>
       </c>
       <c r="N33" s="17">
-        <f>IF(L33="Ne pas lancer",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Regrouper (-1 classe)",H33+('08_Moteur'!AI30-MAX(1,'08_Moteur'!AI30-1))*'08_Moteur'!U30,H33)))</f>
+        <f>IF(L33="Ne pas lancer",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI30&gt;=2,E33&lt;=('08_Moteur'!AI30-1)*'08_Moteur'!O30*1.1),H33+'08_Moteur'!U30,H33),H33)))</f>
         <v/>
       </c>
       <c r="O33" s="17">
@@ -5400,7 +5400,7 @@
         <v/>
       </c>
       <c r="N34" s="17">
-        <f>IF(L34="Ne pas lancer",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Regrouper (-1 classe)",H34+('08_Moteur'!AI31-MAX(1,'08_Moteur'!AI31-1))*'08_Moteur'!U31,H34)))</f>
+        <f>IF(L34="Ne pas lancer",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI31&gt;=2,E34&lt;=('08_Moteur'!AI31-1)*'08_Moteur'!O31*1.1),H34+'08_Moteur'!U31,H34),H34)))</f>
         <v/>
       </c>
       <c r="O34" s="17">
@@ -5454,11 +5454,11 @@
         <v/>
       </c>
       <c r="J35" s="70">
-        <f>IF(H35&lt;0,"🔴 Restructurer (mutualiser)",IF(I35&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H35&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI32&gt;=2,E35&lt;=('08_Moteur'!AI32-1)*'08_Moteur'!O32*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I35&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K35" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI32&gt;=2,TEXT(IFERROR(E35/(('08_Moteur'!AI32-1)*'08_Moteur'!O32),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L35" s="21" t="inlineStr">
@@ -5471,7 +5471,7 @@
         <v/>
       </c>
       <c r="N35" s="17">
-        <f>IF(L35="Ne pas lancer",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Regrouper (-1 classe)",H35+('08_Moteur'!AI32-MAX(1,'08_Moteur'!AI32-1))*'08_Moteur'!U32,H35)))</f>
+        <f>IF(L35="Ne pas lancer",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI32&gt;=2,E35&lt;=('08_Moteur'!AI32-1)*'08_Moteur'!O32*1.1),H35+'08_Moteur'!U32,H35),H35)))</f>
         <v/>
       </c>
       <c r="O35" s="17">
@@ -5542,7 +5542,7 @@
         <v/>
       </c>
       <c r="N36" s="17">
-        <f>IF(L36="Ne pas lancer",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Regrouper (-1 classe)",H36+('08_Moteur'!AI33-MAX(1,'08_Moteur'!AI33-1))*'08_Moteur'!U33,H36)))</f>
+        <f>IF(L36="Ne pas lancer",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI33&gt;=2,E36&lt;=('08_Moteur'!AI33-1)*'08_Moteur'!O33*1.1),H36+'08_Moteur'!U33,H36),H36)))</f>
         <v/>
       </c>
       <c r="O36" s="17">
@@ -5596,11 +5596,11 @@
         <v/>
       </c>
       <c r="J37" s="70">
-        <f>IF(H37&lt;0,"🔴 Restructurer (mutualiser)",IF(I37&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H37&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI34&gt;=2,E37&lt;=('08_Moteur'!AI34-1)*'08_Moteur'!O34*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I37&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K37" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI34&gt;=2,TEXT(IFERROR(E37/(('08_Moteur'!AI34-1)*'08_Moteur'!O34),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L37" s="21" t="inlineStr">
@@ -5613,7 +5613,7 @@
         <v/>
       </c>
       <c r="N37" s="17">
-        <f>IF(L37="Ne pas lancer",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Regrouper (-1 classe)",H37+('08_Moteur'!AI34-MAX(1,'08_Moteur'!AI34-1))*'08_Moteur'!U34,H37)))</f>
+        <f>IF(L37="Ne pas lancer",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI34&gt;=2,E37&lt;=('08_Moteur'!AI34-1)*'08_Moteur'!O34*1.1),H37+'08_Moteur'!U34,H37),H37)))</f>
         <v/>
       </c>
       <c r="O37" s="17">
@@ -5667,11 +5667,11 @@
         <v/>
       </c>
       <c r="J38" s="70">
-        <f>IF(H38&lt;0,"🔴 Restructurer (mutualiser)",IF(I38&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H38&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI35&gt;=2,E38&lt;=('08_Moteur'!AI35-1)*'08_Moteur'!O35*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I38&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K38" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI35&gt;=2,TEXT(IFERROR(E38/(('08_Moteur'!AI35-1)*'08_Moteur'!O35),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L38" s="21" t="inlineStr">
@@ -5684,7 +5684,7 @@
         <v/>
       </c>
       <c r="N38" s="17">
-        <f>IF(L38="Ne pas lancer",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Regrouper (-1 classe)",H38+('08_Moteur'!AI35-MAX(1,'08_Moteur'!AI35-1))*'08_Moteur'!U35,H38)))</f>
+        <f>IF(L38="Ne pas lancer",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI35&gt;=2,E38&lt;=('08_Moteur'!AI35-1)*'08_Moteur'!O35*1.1),H38+'08_Moteur'!U35,H38),H38)))</f>
         <v/>
       </c>
       <c r="O38" s="17">
@@ -5755,7 +5755,7 @@
         <v/>
       </c>
       <c r="N39" s="17">
-        <f>IF(L39="Ne pas lancer",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Regrouper (-1 classe)",H39+('08_Moteur'!AI36-MAX(1,'08_Moteur'!AI36-1))*'08_Moteur'!U36,H39)))</f>
+        <f>IF(L39="Ne pas lancer",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI36&gt;=2,E39&lt;=('08_Moteur'!AI36-1)*'08_Moteur'!O36*1.1),H39+'08_Moteur'!U36,H39),H39)))</f>
         <v/>
       </c>
       <c r="O39" s="17">
@@ -5809,11 +5809,11 @@
         <v/>
       </c>
       <c r="J40" s="70">
-        <f>IF(H40&lt;0,"🔴 Restructurer (mutualiser)",IF(I40&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H40&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI37&gt;=2,E40&lt;=('08_Moteur'!AI37-1)*'08_Moteur'!O37*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I40&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K40" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI37&gt;=2,TEXT(IFERROR(E40/(('08_Moteur'!AI37-1)*'08_Moteur'!O37),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L40" s="21" t="inlineStr">
@@ -5826,7 +5826,7 @@
         <v/>
       </c>
       <c r="N40" s="17">
-        <f>IF(L40="Ne pas lancer",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Regrouper (-1 classe)",H40+('08_Moteur'!AI37-MAX(1,'08_Moteur'!AI37-1))*'08_Moteur'!U37,H40)))</f>
+        <f>IF(L40="Ne pas lancer",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI37&gt;=2,E40&lt;=('08_Moteur'!AI37-1)*'08_Moteur'!O37*1.1),H40+'08_Moteur'!U37,H40),H40)))</f>
         <v/>
       </c>
       <c r="O40" s="17">
@@ -5897,7 +5897,7 @@
         <v/>
       </c>
       <c r="N41" s="17">
-        <f>IF(L41="Ne pas lancer",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Regrouper (-1 classe)",H41+('08_Moteur'!AI38-MAX(1,'08_Moteur'!AI38-1))*'08_Moteur'!U38,H41)))</f>
+        <f>IF(L41="Ne pas lancer",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI38&gt;=2,E41&lt;=('08_Moteur'!AI38-1)*'08_Moteur'!O38*1.1),H41+'08_Moteur'!U38,H41),H41)))</f>
         <v/>
       </c>
       <c r="O41" s="17">
@@ -5951,11 +5951,11 @@
         <v/>
       </c>
       <c r="J42" s="70">
-        <f>IF(H42&lt;0,"🔴 Restructurer (mutualiser)",IF(I42&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H42&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI39&gt;=2,E42&lt;=('08_Moteur'!AI39-1)*'08_Moteur'!O39*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I42&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K42" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI39&gt;=2,TEXT(IFERROR(E42/(('08_Moteur'!AI39-1)*'08_Moteur'!O39),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L42" s="21" t="inlineStr">
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="N42" s="17">
-        <f>IF(L42="Ne pas lancer",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Regrouper (-1 classe)",H42+('08_Moteur'!AI39-MAX(1,'08_Moteur'!AI39-1))*'08_Moteur'!U39,H42)))</f>
+        <f>IF(L42="Ne pas lancer",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI39&gt;=2,E42&lt;=('08_Moteur'!AI39-1)*'08_Moteur'!O39*1.1),H42+'08_Moteur'!U39,H42),H42)))</f>
         <v/>
       </c>
       <c r="O42" s="17">
@@ -6022,11 +6022,11 @@
         <v/>
       </c>
       <c r="J43" s="70">
-        <f>IF(H43&lt;0,"🔴 Restructurer (mutualiser)",IF(I43&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H43&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI40&gt;=2,E43&lt;=('08_Moteur'!AI40-1)*'08_Moteur'!O40*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I43&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K43" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI40&gt;=2,TEXT(IFERROR(E43/(('08_Moteur'!AI40-1)*'08_Moteur'!O40),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L43" s="21" t="inlineStr">
@@ -6039,7 +6039,7 @@
         <v/>
       </c>
       <c r="N43" s="17">
-        <f>IF(L43="Ne pas lancer",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Regrouper (-1 classe)",H43+('08_Moteur'!AI40-MAX(1,'08_Moteur'!AI40-1))*'08_Moteur'!U40,H43)))</f>
+        <f>IF(L43="Ne pas lancer",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI40&gt;=2,E43&lt;=('08_Moteur'!AI40-1)*'08_Moteur'!O40*1.1),H43+'08_Moteur'!U40,H43),H43)))</f>
         <v/>
       </c>
       <c r="O43" s="17">
@@ -6110,7 +6110,7 @@
         <v/>
       </c>
       <c r="N44" s="17">
-        <f>IF(L44="Ne pas lancer",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Regrouper (-1 classe)",H44+('08_Moteur'!AI41-MAX(1,'08_Moteur'!AI41-1))*'08_Moteur'!U41,H44)))</f>
+        <f>IF(L44="Ne pas lancer",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI41&gt;=2,E44&lt;=('08_Moteur'!AI41-1)*'08_Moteur'!O41*1.1),H44+'08_Moteur'!U41,H44),H44)))</f>
         <v/>
       </c>
       <c r="O44" s="17">
@@ -6164,11 +6164,11 @@
         <v/>
       </c>
       <c r="J45" s="70">
-        <f>IF(H45&lt;0,"🔴 Restructurer (mutualiser)",IF(I45&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H45&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI42&gt;=2,E45&lt;=('08_Moteur'!AI42-1)*'08_Moteur'!O42*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I45&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K45" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI42&gt;=2,TEXT(IFERROR(E45/(('08_Moteur'!AI42-1)*'08_Moteur'!O42),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L45" s="21" t="inlineStr">
@@ -6181,7 +6181,7 @@
         <v/>
       </c>
       <c r="N45" s="17">
-        <f>IF(L45="Ne pas lancer",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Regrouper (-1 classe)",H45+('08_Moteur'!AI42-MAX(1,'08_Moteur'!AI42-1))*'08_Moteur'!U42,H45)))</f>
+        <f>IF(L45="Ne pas lancer",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI42&gt;=2,E45&lt;=('08_Moteur'!AI42-1)*'08_Moteur'!O42*1.1),H45+'08_Moteur'!U42,H45),H45)))</f>
         <v/>
       </c>
       <c r="O45" s="17">
@@ -6235,11 +6235,11 @@
         <v/>
       </c>
       <c r="J46" s="70">
-        <f>IF(H46&lt;0,"🔴 Restructurer (mutualiser)",IF(I46&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H46&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI43&gt;=2,E46&lt;=('08_Moteur'!AI43-1)*'08_Moteur'!O43*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I46&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K46" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI43&gt;=2,TEXT(IFERROR(E46/(('08_Moteur'!AI43-1)*'08_Moteur'!O43),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L46" s="21" t="inlineStr">
@@ -6252,7 +6252,7 @@
         <v/>
       </c>
       <c r="N46" s="17">
-        <f>IF(L46="Ne pas lancer",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Regrouper (-1 classe)",H46+('08_Moteur'!AI43-MAX(1,'08_Moteur'!AI43-1))*'08_Moteur'!U43,H46)))</f>
+        <f>IF(L46="Ne pas lancer",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI43&gt;=2,E46&lt;=('08_Moteur'!AI43-1)*'08_Moteur'!O43*1.1),H46+'08_Moteur'!U43,H46),H46)))</f>
         <v/>
       </c>
       <c r="O46" s="17">
@@ -6323,7 +6323,7 @@
         <v/>
       </c>
       <c r="N47" s="17">
-        <f>IF(L47="Ne pas lancer",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Regrouper (-1 classe)",H47+('08_Moteur'!AI44-MAX(1,'08_Moteur'!AI44-1))*'08_Moteur'!U44,H47)))</f>
+        <f>IF(L47="Ne pas lancer",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI44&gt;=2,E47&lt;=('08_Moteur'!AI44-1)*'08_Moteur'!O44*1.1),H47+'08_Moteur'!U44,H47),H47)))</f>
         <v/>
       </c>
       <c r="O47" s="17">
@@ -6377,11 +6377,11 @@
         <v/>
       </c>
       <c r="J48" s="70">
-        <f>IF(H48&lt;0,"🔴 Restructurer (mutualiser)",IF(I48&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H48&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI45&gt;=2,E48&lt;=('08_Moteur'!AI45-1)*'08_Moteur'!O45*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I48&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K48" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI45&gt;=2,TEXT(IFERROR(E48/(('08_Moteur'!AI45-1)*'08_Moteur'!O45),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L48" s="21" t="inlineStr">
@@ -6394,7 +6394,7 @@
         <v/>
       </c>
       <c r="N48" s="17">
-        <f>IF(L48="Ne pas lancer",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Regrouper (-1 classe)",H48+('08_Moteur'!AI45-MAX(1,'08_Moteur'!AI45-1))*'08_Moteur'!U45,H48)))</f>
+        <f>IF(L48="Ne pas lancer",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI45&gt;=2,E48&lt;=('08_Moteur'!AI45-1)*'08_Moteur'!O45*1.1),H48+'08_Moteur'!U45,H48),H48)))</f>
         <v/>
       </c>
       <c r="O48" s="17">
@@ -6448,11 +6448,11 @@
         <v/>
       </c>
       <c r="J49" s="70">
-        <f>IF(H49&lt;0,"🔴 Restructurer (mutualiser)",IF(I49&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H49&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI46&gt;=2,E49&lt;=('08_Moteur'!AI46-1)*'08_Moteur'!O46*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I49&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K49" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI46&gt;=2,TEXT(IFERROR(E49/(('08_Moteur'!AI46-1)*'08_Moteur'!O46),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L49" s="21" t="inlineStr">
@@ -6465,7 +6465,7 @@
         <v/>
       </c>
       <c r="N49" s="17">
-        <f>IF(L49="Ne pas lancer",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Regrouper (-1 classe)",H49+('08_Moteur'!AI46-MAX(1,'08_Moteur'!AI46-1))*'08_Moteur'!U46,H49)))</f>
+        <f>IF(L49="Ne pas lancer",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI46&gt;=2,E49&lt;=('08_Moteur'!AI46-1)*'08_Moteur'!O46*1.1),H49+'08_Moteur'!U46,H49),H49)))</f>
         <v/>
       </c>
       <c r="O49" s="17">
@@ -6536,7 +6536,7 @@
         <v/>
       </c>
       <c r="N50" s="17">
-        <f>IF(L50="Ne pas lancer",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Regrouper (-1 classe)",H50+('08_Moteur'!AI47-MAX(1,'08_Moteur'!AI47-1))*'08_Moteur'!U47,H50)))</f>
+        <f>IF(L50="Ne pas lancer",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI47&gt;=2,E50&lt;=('08_Moteur'!AI47-1)*'08_Moteur'!O47*1.1),H50+'08_Moteur'!U47,H50),H50)))</f>
         <v/>
       </c>
       <c r="O50" s="17">
@@ -6590,11 +6590,11 @@
         <v/>
       </c>
       <c r="J51" s="70">
-        <f>IF(H51&lt;0,"🔴 Restructurer (mutualiser)",IF(I51&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H51&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI48&gt;=2,E51&lt;=('08_Moteur'!AI48-1)*'08_Moteur'!O48*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I51&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K51" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI48&gt;=2,TEXT(IFERROR(E51/(('08_Moteur'!AI48-1)*'08_Moteur'!O48),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L51" s="21" t="inlineStr">
@@ -6607,7 +6607,7 @@
         <v/>
       </c>
       <c r="N51" s="17">
-        <f>IF(L51="Ne pas lancer",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Regrouper (-1 classe)",H51+('08_Moteur'!AI48-MAX(1,'08_Moteur'!AI48-1))*'08_Moteur'!U48,H51)))</f>
+        <f>IF(L51="Ne pas lancer",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI48&gt;=2,E51&lt;=('08_Moteur'!AI48-1)*'08_Moteur'!O48*1.1),H51+'08_Moteur'!U48,H51),H51)))</f>
         <v/>
       </c>
       <c r="O51" s="17">
@@ -6678,7 +6678,7 @@
         <v/>
       </c>
       <c r="N52" s="17">
-        <f>IF(L52="Ne pas lancer",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Regrouper (-1 classe)",H52+('08_Moteur'!AI49-MAX(1,'08_Moteur'!AI49-1))*'08_Moteur'!U49,H52)))</f>
+        <f>IF(L52="Ne pas lancer",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI49&gt;=2,E52&lt;=('08_Moteur'!AI49-1)*'08_Moteur'!O49*1.1),H52+'08_Moteur'!U49,H52),H52)))</f>
         <v/>
       </c>
       <c r="O52" s="17">
@@ -6732,11 +6732,11 @@
         <v/>
       </c>
       <c r="J53" s="70">
-        <f>IF(H53&lt;0,"🔴 Restructurer (mutualiser)",IF(I53&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H53&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI50&gt;=2,E53&lt;=('08_Moteur'!AI50-1)*'08_Moteur'!O50*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I53&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K53" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI50&gt;=2,TEXT(IFERROR(E53/(('08_Moteur'!AI50-1)*'08_Moteur'!O50),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L53" s="21" t="inlineStr">
@@ -6749,7 +6749,7 @@
         <v/>
       </c>
       <c r="N53" s="17">
-        <f>IF(L53="Ne pas lancer",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Regrouper (-1 classe)",H53+('08_Moteur'!AI50-MAX(1,'08_Moteur'!AI50-1))*'08_Moteur'!U50,H53)))</f>
+        <f>IF(L53="Ne pas lancer",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI50&gt;=2,E53&lt;=('08_Moteur'!AI50-1)*'08_Moteur'!O50*1.1),H53+'08_Moteur'!U50,H53),H53)))</f>
         <v/>
       </c>
       <c r="O53" s="17">
@@ -6820,7 +6820,7 @@
         <v/>
       </c>
       <c r="N54" s="17">
-        <f>IF(L54="Ne pas lancer",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Regrouper (-1 classe)",H54+('08_Moteur'!AI51-MAX(1,'08_Moteur'!AI51-1))*'08_Moteur'!U51,H54)))</f>
+        <f>IF(L54="Ne pas lancer",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI51&gt;=2,E54&lt;=('08_Moteur'!AI51-1)*'08_Moteur'!O51*1.1),H54+'08_Moteur'!U51,H54),H54)))</f>
         <v/>
       </c>
       <c r="O54" s="17">
@@ -6874,11 +6874,11 @@
         <v/>
       </c>
       <c r="J55" s="70">
-        <f>IF(H55&lt;0,"🔴 Restructurer (mutualiser)",IF(I55&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H55&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI52&gt;=2,E55&lt;=('08_Moteur'!AI52-1)*'08_Moteur'!O52*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I55&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K55" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI52&gt;=2,TEXT(IFERROR(E55/(('08_Moteur'!AI52-1)*'08_Moteur'!O52),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L55" s="21" t="inlineStr">
@@ -6891,7 +6891,7 @@
         <v/>
       </c>
       <c r="N55" s="17">
-        <f>IF(L55="Ne pas lancer",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Regrouper (-1 classe)",H55+('08_Moteur'!AI52-MAX(1,'08_Moteur'!AI52-1))*'08_Moteur'!U52,H55)))</f>
+        <f>IF(L55="Ne pas lancer",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI52&gt;=2,E55&lt;=('08_Moteur'!AI52-1)*'08_Moteur'!O52*1.1),H55+'08_Moteur'!U52,H55),H55)))</f>
         <v/>
       </c>
       <c r="O55" s="17">
@@ -6962,7 +6962,7 @@
         <v/>
       </c>
       <c r="N56" s="17">
-        <f>IF(L56="Ne pas lancer",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Regrouper (-1 classe)",H56+('08_Moteur'!AI53-MAX(1,'08_Moteur'!AI53-1))*'08_Moteur'!U53,H56)))</f>
+        <f>IF(L56="Ne pas lancer",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI53&gt;=2,E56&lt;=('08_Moteur'!AI53-1)*'08_Moteur'!O53*1.1),H56+'08_Moteur'!U53,H56),H56)))</f>
         <v/>
       </c>
       <c r="O56" s="17">
@@ -7016,11 +7016,11 @@
         <v/>
       </c>
       <c r="J57" s="70">
-        <f>IF(H57&lt;0,"🔴 Restructurer (mutualiser)",IF(I57&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H57&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI54&gt;=2,E57&lt;=('08_Moteur'!AI54-1)*'08_Moteur'!O54*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I57&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K57" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI54&gt;=2,TEXT(IFERROR(E57/(('08_Moteur'!AI54-1)*'08_Moteur'!O54),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L57" s="21" t="inlineStr">
@@ -7033,7 +7033,7 @@
         <v/>
       </c>
       <c r="N57" s="17">
-        <f>IF(L57="Ne pas lancer",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Regrouper (-1 classe)",H57+('08_Moteur'!AI54-MAX(1,'08_Moteur'!AI54-1))*'08_Moteur'!U54,H57)))</f>
+        <f>IF(L57="Ne pas lancer",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI54&gt;=2,E57&lt;=('08_Moteur'!AI54-1)*'08_Moteur'!O54*1.1),H57+'08_Moteur'!U54,H57),H57)))</f>
         <v/>
       </c>
       <c r="O57" s="17">
@@ -7104,7 +7104,7 @@
         <v/>
       </c>
       <c r="N58" s="17">
-        <f>IF(L58="Ne pas lancer",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Regrouper (-1 classe)",H58+('08_Moteur'!AI55-MAX(1,'08_Moteur'!AI55-1))*'08_Moteur'!U55,H58)))</f>
+        <f>IF(L58="Ne pas lancer",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI55&gt;=2,E58&lt;=('08_Moteur'!AI55-1)*'08_Moteur'!O55*1.1),H58+'08_Moteur'!U55,H58),H58)))</f>
         <v/>
       </c>
       <c r="O58" s="17">
@@ -7158,11 +7158,11 @@
         <v/>
       </c>
       <c r="J59" s="70">
-        <f>IF(H59&lt;0,"🔴 Restructurer (mutualiser)",IF(I59&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H59&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI56&gt;=2,E59&lt;=('08_Moteur'!AI56-1)*'08_Moteur'!O56*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I59&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K59" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI56&gt;=2,TEXT(IFERROR(E59/(('08_Moteur'!AI56-1)*'08_Moteur'!O56),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L59" s="21" t="inlineStr">
@@ -7175,7 +7175,7 @@
         <v/>
       </c>
       <c r="N59" s="17">
-        <f>IF(L59="Ne pas lancer",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Regrouper (-1 classe)",H59+('08_Moteur'!AI56-MAX(1,'08_Moteur'!AI56-1))*'08_Moteur'!U56,H59)))</f>
+        <f>IF(L59="Ne pas lancer",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI56&gt;=2,E59&lt;=('08_Moteur'!AI56-1)*'08_Moteur'!O56*1.1),H59+'08_Moteur'!U56,H59),H59)))</f>
         <v/>
       </c>
       <c r="O59" s="17">
@@ -7229,11 +7229,11 @@
         <v/>
       </c>
       <c r="J60" s="70">
-        <f>IF(H60&lt;0,"🔴 Restructurer (mutualiser)",IF(I60&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H60&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI57&gt;=2,E60&lt;=('08_Moteur'!AI57-1)*'08_Moteur'!O57*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I60&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K60" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI57&gt;=2,TEXT(IFERROR(E60/(('08_Moteur'!AI57-1)*'08_Moteur'!O57),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L60" s="21" t="inlineStr">
@@ -7246,7 +7246,7 @@
         <v/>
       </c>
       <c r="N60" s="17">
-        <f>IF(L60="Ne pas lancer",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Regrouper (-1 classe)",H60+('08_Moteur'!AI57-MAX(1,'08_Moteur'!AI57-1))*'08_Moteur'!U57,H60)))</f>
+        <f>IF(L60="Ne pas lancer",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI57&gt;=2,E60&lt;=('08_Moteur'!AI57-1)*'08_Moteur'!O57*1.1),H60+'08_Moteur'!U57,H60),H60)))</f>
         <v/>
       </c>
       <c r="O60" s="17">
@@ -7317,7 +7317,7 @@
         <v/>
       </c>
       <c r="N61" s="17">
-        <f>IF(L61="Ne pas lancer",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Regrouper (-1 classe)",H61+('08_Moteur'!AI58-MAX(1,'08_Moteur'!AI58-1))*'08_Moteur'!U58,H61)))</f>
+        <f>IF(L61="Ne pas lancer",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI58&gt;=2,E61&lt;=('08_Moteur'!AI58-1)*'08_Moteur'!O58*1.1),H61+'08_Moteur'!U58,H61),H61)))</f>
         <v/>
       </c>
       <c r="O61" s="17">
@@ -7371,11 +7371,11 @@
         <v/>
       </c>
       <c r="J62" s="70">
-        <f>IF(H62&lt;0,"🔴 Restructurer (mutualiser)",IF(I62&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H62&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI59&gt;=2,E62&lt;=('08_Moteur'!AI59-1)*'08_Moteur'!O59*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I62&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K62" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI59&gt;=2,TEXT(IFERROR(E62/(('08_Moteur'!AI59-1)*'08_Moteur'!O59),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L62" s="21" t="inlineStr">
@@ -7388,7 +7388,7 @@
         <v/>
       </c>
       <c r="N62" s="17">
-        <f>IF(L62="Ne pas lancer",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Regrouper (-1 classe)",H62+('08_Moteur'!AI59-MAX(1,'08_Moteur'!AI59-1))*'08_Moteur'!U59,H62)))</f>
+        <f>IF(L62="Ne pas lancer",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI59&gt;=2,E62&lt;=('08_Moteur'!AI59-1)*'08_Moteur'!O59*1.1),H62+'08_Moteur'!U59,H62),H62)))</f>
         <v/>
       </c>
       <c r="O62" s="17">
@@ -7442,11 +7442,11 @@
         <v/>
       </c>
       <c r="J63" s="70">
-        <f>IF(H63&lt;0,"🔴 Restructurer (mutualiser)",IF(I63&lt;0.55,"🟡 Regrouper les classes","🟢 Maintenir"))</f>
+        <f>IF(H63&lt;0,"🔴 Restructurer (mutualiser)",IF(AND('08_Moteur'!AI60&gt;=2,E63&lt;=('08_Moteur'!AI60-1)*'08_Moteur'!O60*1.1),"🟡 Regroupable (−1 classe tient en capacité)",IF(I63&lt;0.55,"🟠 Sous-rempli mais −1 classe déborderait","🟢 Maintenir")))</f>
         <v/>
       </c>
       <c r="K63" s="71">
-        <f>"Poursuite : cohorte déjà inscrite (issue de l'année inférieure) → ni lancement ni capture ; seul levier = regrouper / mutualiser les classes"</f>
+        <f>"Poursuite : cohorte déjà inscrite → seul levier = regrouper. −1 classe créditée uniquement si l'effectif tient dans les classes restantes (capacité +10% tolérée). Remplissage si −1 classe : "&amp;IF('08_Moteur'!AI60&gt;=2,TEXT(IFERROR(E63/(('08_Moteur'!AI60-1)*'08_Moteur'!O60),0),"0%"),"n/a (1 seule classe)")</f>
         <v/>
       </c>
       <c r="L63" s="21" t="inlineStr">
@@ -7459,7 +7459,7 @@
         <v/>
       </c>
       <c r="N63" s="17">
-        <f>IF(L63="Ne pas lancer",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Regrouper (-1 classe)",H63+('08_Moteur'!AI60-MAX(1,'08_Moteur'!AI60-1))*'08_Moteur'!U60,H63)))</f>
+        <f>IF(L63="Ne pas lancer",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'02_Leviers'!$D$19)*(1+'02_Leviers'!$G$11)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI60&gt;=2,E63&lt;=('08_Moteur'!AI60-1)*'08_Moteur'!O60*1.1),H63+'08_Moteur'!U60,H63),H63)))</f>
         <v/>
       </c>
       <c r="O63" s="17">

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -19,9 +19,10 @@
     <sheet name="09_Allocation" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="10_PnL" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="11_Simulateur" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12_Sensibilite" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13_Simulation" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14_Mapping_Tagetik" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="11b_Mutualisation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="12_Sensibilite" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="13_Simulation" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="14_Mapping_Tagetik" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,10 +31,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; €&quot;;(#,##0)&quot; €&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -193,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -395,6 +397,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -655,6 +663,66 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Cycle de diplôme (Bachelor / Mastère / BTS). On ne mutualise qu'au sein d'un même cycle : ses années partagent un tronc commun ; on ne mélange pas des cycles différents.</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif budget de la promo.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Nombre de classes ouvertes aujourd'hui pour ce cycle sur le campus = somme des classes de chaque année (chacune arrondit au minimum de son côté).</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>Capacité moyenne d'une classe sur le campus (pondérée par le nombre de classes).</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Plancher physique = ARRONDI.SUP(effectif total du campus / capacité moyenne). C'est le minimum de classes si on regroupait les étudiants dans des classes pleines — la capacité n'est jamais dépassée.</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <t>Classes récupérables = sections aujourd'hui − plancher. Vient des arrondis : chaque promo arrondit au minimum, mais mises en commun elles remplissent mieux.</t>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'enseignement moyen d'une classe du campus = coût enseignement total / nombre de classes.</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>Sections économisables × coût moyen/classe × % d'heures mutualisables. Potentiel indicatif (bac à sable), pas un impact P&amp;L officiel.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
         <t>Levier testé et son incrément.</t>
       </text>
     </comment>
@@ -672,7 +740,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
@@ -785,15 +853,20 @@
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>Coefficient appliqué à l'effort marketing du cadrage pour cette marque (&gt;1 = on pousse).</t>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
       </text>
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
+        <t>Coefficient appliqué à l'effort marketing du cadrage pour cette marque (&gt;1 = on pousse).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
         <t>Coefficient appliqué à la hausse tarifaire du cadrage pour cette marque.</t>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
+    <comment ref="F5" authorId="0" shapeId="0">
       <text>
         <t>Lecture du positionnement (pousser / défendre / maintenir).</t>
       </text>
@@ -1210,7 +1283,7 @@
     </comment>
     <comment ref="AI2" authorId="0" shapeId="0">
       <text>
-        <t>Classes nécessaires = arrondi supérieur (effectif / capacité).</t>
+        <t>Classes nécessaires = arrondi supérieur (effectif / capacité) — le MINIMUM par cellule (promo). Ce minimum ne se réduit pas au sein d'une promo ; le regroupement de sections parallèles d'un même campus se traite un cran au-dessus (feuille 11b_Mutualisation).</t>
       </text>
     </comment>
     <comment ref="AJ2" authorId="0" shapeId="0">
@@ -1606,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D28"/>
+  <dimension ref="B2:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1670,7 +1743,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Coefficients stratégiques par marque (marketing / prix)</t>
+          <t>Coefficients stratégiques par marque × campus (marketing / prix)</t>
         </is>
       </c>
     </row>
@@ -1766,122 +1839,134 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Décisions ouvrir/fermer/redistribuer → EBITDA AVANT → APRÈS</t>
+          <t>Décisions ouvrir/fermer/redistribuer (maille PROMO) → EBITDA AVANT → APRÈS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>12_Sensibilite</t>
+          <t>11b_Mutualisation</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Impact € sur l'EBITDA par levier (sens unique)</t>
+          <t>Mutualisation inter-sections (maille CAMPUS) : sections économisables &amp; économie potentielle</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>13_Simulation</t>
+          <t>12_Sensibilite</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>KPIs, € à risque, taux d'alternance/sécurisation</t>
+          <t>Impact € sur l'EBITDA par levier (sens unique)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>13_Simulation</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>KPIs, € à risque, taux d'alternance/sécurisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>14_Mapping_Tagetik</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Passerelle Tagetik</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Légende</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Saisie / donnée réelle</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="9" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Formule</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Lien inter-feuilles</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="11" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Hypothèse à remplir</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Marques/campus réels EDUSERVICES ; montants ILLUSTRATIFS calibrés sur des ordres de grandeur sourcés (scolarité 8-11 k€, NPEC ~7-10 k€, marge EBITDA ~20 %, classe ~30). À remplacer par le réel.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
+    <row r="29"/>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="B27:D28"/>
-    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="B5:D5"/>
@@ -1890,10 +1975,11 @@
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B28:D29"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
@@ -3260,7 +3346,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="68" t="inlineStr">
         <is>
-          <t>🧪 BAC À SABLE : ces décisions montrent un impact SIMULÉ (encadré ci-dessus) — elles n'affectent PAS le budget officiel (feuilles 09_Allocation / 10_PnL / 13_Simulation), qui se pilote via les LEVIERS (feuille 02_Leviers).</t>
+          <t>🧪 BAC À SABLE : décisions à la maille d'UNE promo — impact SIMULÉ (encadré ci-dessus), sans effet sur le budget officiel (09/10/13), qui se pilote via les LEVIERS (02). « Regrouper » ici respecte la capacité de la promo ; pour mutualiser des sections parallèles d'un même CAMPUS, voir la feuille 11b_Mutualisation.</t>
         </is>
       </c>
     </row>
@@ -7509,6 +7595,1233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:AS35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Mutualisation inter-sections — maille CAMPUS × CYCLE (un cran au-dessus du simulateur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Le simulateur (11) raisonne à la maille d'UNE promo. Ici on regroupe les promos d'un même CYCLE sur un campus (ex. Bachelor B1+B2+B3, qui partagent un tronc commun) : chacune arrondit au minimum de son côté → de la capacité se gaspille ; la mutualisation en récupère une partie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>% d'heures mutualisables (tronc commun partagé) :</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="72" t="inlineStr">
+        <is>
+          <t>← hypothèse : part des heures réellement partageable au sein d'un cycle (le reste reste spécifique à chaque année).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Sections
+aujourd'hui</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Capacité
+moy.</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Sections si
+mutualisé</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Sections
+économisables</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Coût moyen
+/ classe</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Économie
+potentielle €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E6" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F6" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G6" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F6,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="50">
+        <f>IF(E6&lt;=0,0,MAX(1,ROUNDUP(E6/G6,0)))</f>
+        <v/>
+      </c>
+      <c r="I6" s="53">
+        <f>MAX(0,F6-H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F6,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="54">
+        <f>I6*J6*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E7" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F7" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G7" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F7,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="50">
+        <f>IF(E7&lt;=0,0,MAX(1,ROUNDUP(E7/G7,0)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="53">
+        <f>MAX(0,F7-H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F7,0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="54">
+        <f>I7*J7*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E8" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F8" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G8" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F8,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="50">
+        <f>IF(E8&lt;=0,0,MAX(1,ROUNDUP(E8/G8,0)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="53">
+        <f>MAX(0,F8-H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F8,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="54">
+        <f>I8*J8*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E9" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F9" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G9" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F9,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="50">
+        <f>IF(E9&lt;=0,0,MAX(1,ROUNDUP(E9/G9,0)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="53">
+        <f>MAX(0,F9-H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F9,0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="54">
+        <f>I9*J9*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E10" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F10" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G10" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F10,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="50">
+        <f>IF(E10&lt;=0,0,MAX(1,ROUNDUP(E10/G10,0)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="53">
+        <f>MAX(0,F10-H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F10,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="54">
+        <f>I10*J10*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E11" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F11" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G11" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F11,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="50">
+        <f>IF(E11&lt;=0,0,MAX(1,ROUNDUP(E11/G11,0)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="53">
+        <f>MAX(0,F11-H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F11,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="54">
+        <f>I11*J11*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E12" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F12" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G12" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="50">
+        <f>IF(E12&lt;=0,0,MAX(1,ROUNDUP(E12/G12,0)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="53">
+        <f>MAX(0,F12-H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F12,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="54">
+        <f>I12*J12*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E13" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F13" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G13" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="50">
+        <f>IF(E13&lt;=0,0,MAX(1,ROUNDUP(E13/G13,0)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="53">
+        <f>MAX(0,F13-H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="MBway")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F13,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="54">
+        <f>I13*J13*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E14" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F14" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G14" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="50">
+        <f>IF(E14&lt;=0,0,MAX(1,ROUNDUP(E14/G14,0)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="53">
+        <f>MAX(0,F14-H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F14,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="54">
+        <f>I14*J14*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E15" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F15" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G15" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="50">
+        <f>IF(E15&lt;=0,0,MAX(1,ROUNDUP(E15/G15,0)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="53">
+        <f>MAX(0,F15-H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F15,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="54">
+        <f>I15*J15*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E16" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F16" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G16" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="50">
+        <f>IF(E16&lt;=0,0,MAX(1,ROUNDUP(E16/G16,0)))</f>
+        <v/>
+      </c>
+      <c r="I16" s="53">
+        <f>MAX(0,F16-H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F16,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="54">
+        <f>I16*J16*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E17" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F17" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G17" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F17,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="50">
+        <f>IF(E17&lt;=0,0,MAX(1,ROUNDUP(E17/G17,0)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="53">
+        <f>MAX(0,F17-H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Lille")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F17,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="54">
+        <f>I17*J17*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E18" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F18" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G18" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F18,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="50">
+        <f>IF(E18&lt;=0,0,MAX(1,ROUNDUP(E18/G18,0)))</f>
+        <v/>
+      </c>
+      <c r="I18" s="53">
+        <f>MAX(0,F18-H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F18,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="54">
+        <f>I18*J18*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Mastère</t>
+        </is>
+      </c>
+      <c r="E19" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F19" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G19" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F19,0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="50">
+        <f>IF(E19&lt;=0,0,MAX(1,ROUNDUP(E19/G19,0)))</f>
+        <v/>
+      </c>
+      <c r="I19" s="53">
+        <f>MAX(0,F19-H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="ISCOM")*('08_Moteur'!$B$3:$B$60="Toulouse")*(('08_Moteur'!$D$3:$D$60="M1")+('08_Moteur'!$D$3:$D$60="M2"))*'08_Moteur'!$AJ$3:$AJ$60)/F19,0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="54">
+        <f>I19*J19*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E20" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F20" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G20" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F20,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="50">
+        <f>IF(E20&lt;=0,0,MAX(1,ROUNDUP(E20/G20,0)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="53">
+        <f>MAX(0,F20-H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Nantes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F20,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="54">
+        <f>I20*J20*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E21" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Rennes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F21" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Rennes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G21" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Rennes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F21,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="50">
+        <f>IF(E21&lt;=0,0,MAX(1,ROUNDUP(E21/G21,0)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="53">
+        <f>MAX(0,F21-H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Rennes")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F21,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="54">
+        <f>I21*J21*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E22" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Montpellier")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F22" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Montpellier")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G22" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Montpellier")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F22,0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="50">
+        <f>IF(E22&lt;=0,0,MAX(1,ROUNDUP(E22/G22,0)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="53">
+        <f>MAX(0,F22-H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Ipac Bachelor Factory")*('08_Moteur'!$B$3:$B$60="Montpellier")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F22,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="54">
+        <f>I22*J22*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="E23" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F23" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G23" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F23,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="50">
+        <f>IF(E23&lt;=0,0,MAX(1,ROUNDUP(E23/G23,0)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="53">
+        <f>MAX(0,F23-H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AJ$3:$AJ$60)/F23,0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="54">
+        <f>I23*J23*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E24" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F24" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G24" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F24,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="50">
+        <f>IF(E24&lt;=0,0,MAX(1,ROUNDUP(E24/G24,0)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="53">
+        <f>MAX(0,F24-H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F24,0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="54">
+        <f>I24*J24*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="47" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>BTS</t>
+        </is>
+      </c>
+      <c r="E25" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F25" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G25" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F25,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="50">
+        <f>IF(E25&lt;=0,0,MAX(1,ROUNDUP(E25/G25,0)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="53">
+        <f>MAX(0,F25-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="1")+('08_Moteur'!$D$3:$D$60="2"))*'08_Moteur'!$AJ$3:$AJ$60)/F25,0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="54">
+        <f>I25*J25*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E26" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F26" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G26" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F26,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="50">
+        <f>IF(E26&lt;=0,0,MAX(1,ROUNDUP(E26/G26,0)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="53">
+        <f>MAX(0,F26-H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Pigier")*('08_Moteur'!$B$3:$B$60="Bordeaux")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F26,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="54">
+        <f>I26*J26*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E27" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F27" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G27" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F27,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="50">
+        <f>IF(E27&lt;=0,0,MAX(1,ROUNDUP(E27/G27,0)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="53">
+        <f>MAX(0,F27-H27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Paris")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F27,0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="54">
+        <f>I27*J27*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="E28" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AD$3:$AD$60)</f>
+        <v/>
+      </c>
+      <c r="F28" s="50">
+        <f>SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60)</f>
+        <v/>
+      </c>
+      <c r="G28" s="73">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AI$3:$AI$60*'08_Moteur'!$O$3:$O$60)/F28,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="50">
+        <f>IF(E28&lt;=0,0,MAX(1,ROUNDUP(E28/G28,0)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="53">
+        <f>MAX(0,F28-H28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>IFERROR(SUMPRODUCT(('08_Moteur'!$A$3:$A$60="Tunon")*('08_Moteur'!$B$3:$B$60="Lyon")*(('08_Moteur'!$D$3:$D$60="B1")+('08_Moteur'!$D$3:$D$60="B2")+('08_Moteur'!$D$3:$D$60="B3"))*'08_Moteur'!$AJ$3:$AJ$60)/F28,0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="54">
+        <f>I28*J28*$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="45">
+        <f>SUM(E6:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="45">
+        <f>SUM(F6:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H29" s="45">
+        <f>SUM(H6:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="45">
+        <f>SUM(I6:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K29" s="46">
+        <f>SUM(K6:K28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Économie potentielle totale de mutualisation :</t>
+        </is>
+      </c>
+      <c r="G31" s="20">
+        <f>K29</f>
+        <v/>
+      </c>
+      <c r="H31" s="30" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>🧪 Indicateur de POTENTIEL (bac à sable), maille campus × cycle. « Sections économisables » = classes récupérables si l'on regroupe les étudiants d'un même cycle dans des classes pleines ; le plancher = ARRONDI.SUP(effectif du cycle / capacité) → la capacité n'est JAMAIS dépassée (même garde-fou que le simulateur, mais sur le cycle). On ne mélange PAS des cycles différents (un B1 et un M2 ne partagent pas de classe). L'économie ne porte que sur la part d'heures réellement mutualisable au sein du cycle (tronc commun) — le reste reste spécifique à chaque année. N'affecte PAS le P&amp;L officiel ; à décliner dans Tagetik à la maille de consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B33:K35"/>
+    <mergeCell ref="B3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:AS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7619,7 +8932,7 @@
           <t>Exposition financement alternance (€ à sécuriser) :</t>
         </is>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="74">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
@@ -7635,7 +8948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7863,20 +9176,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="75" t="inlineStr">
         <is>
           <t>€ à sécuriser (exposition)</t>
         </is>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="76">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
-      <c r="D15" s="74">
+      <c r="D15" s="76">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
         <v/>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="77">
         <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
@@ -7890,7 +9203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7939,7 +9252,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="76" t="inlineStr">
+      <c r="B6" s="78" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -7956,7 +9269,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="78" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -7973,7 +9286,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -7990,7 +9303,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -8007,7 +9320,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="78" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -8024,7 +9337,7 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>Sécurisation &amp; recouvrement</t>
         </is>
@@ -8041,7 +9354,7 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>Objectifs (cadrage)</t>
         </is>
@@ -8058,7 +9371,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="76" t="inlineStr">
+      <c r="B13" s="78" t="inlineStr">
         <is>
           <t>Décisions ouvrir/fermer</t>
         </is>
@@ -8075,7 +9388,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="76" t="inlineStr">
+      <c r="B14" s="78" t="inlineStr">
         <is>
           <t>Allocation structure</t>
         </is>
@@ -8765,27 +10078,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS10"/>
+  <dimension ref="A2:AS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Coefficients stratégiques par marque</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Coefficients stratégiques par marque × campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>On pousse + ou – selon la marque : effort appliqué = levier × coefficient.</t>
+          <t>On pousse + ou – selon la marque ET le campus : effort appliqué = levier × coefficient. Par défaut = valeur de la marque ; ajuste une ligne pour cibler un campus.</t>
         </is>
       </c>
     </row>
@@ -8797,17 +10113,27 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
           <t>Intensité MARKETING</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Intensité PRIX</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Posture</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Clé (marque|campus)</t>
         </is>
       </c>
     </row>
@@ -8817,89 +10143,368 @@
           <t>MBway</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="n">
         <v>1.2</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="E6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="9">
-        <f>IF(C6&gt;=1.15,"Pousser",IF(C6&lt;=0.85,"Défendre","Maintenir"))</f>
+      <c r="F6" s="9">
+        <f>IF(D6&gt;=1.15,"Pousser",IF(D6&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>B6&amp;"|"&amp;C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>ISCOM</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>1</v>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
       </c>
       <c r="D7" s="33" t="n">
         <v>1.2</v>
       </c>
-      <c r="E7" s="9">
-        <f>IF(C7&gt;=1.15,"Pousser",IF(C7&lt;=0.85,"Défendre","Maintenir"))</f>
+      <c r="E7" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9">
+        <f>IF(D7&gt;=1.15,"Pousser",IF(D7&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>B7&amp;"|"&amp;C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Ipac Bachelor Factory</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="n">
-        <v>1.3</v>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E8" s="9">
-        <f>IF(C8&gt;=1.15,"Pousser",IF(C8&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v>1.2</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <f>IF(D8&gt;=1.15,"Pousser",IF(D8&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>B8&amp;"|"&amp;C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Pigier</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="n">
-        <v>0.7</v>
+          <t>MBway</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
       </c>
       <c r="D9" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="9">
-        <f>IF(C9&gt;=1.15,"Pousser",IF(C9&lt;=0.85,"Défendre","Maintenir"))</f>
+      <c r="F9" s="9">
+        <f>IF(D9&gt;=1.15,"Pousser",IF(D9&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>B9&amp;"|"&amp;C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="8" t="inlineStr">
         <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="9">
+        <f>IF(D10&gt;=1.15,"Pousser",IF(D10&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>B10&amp;"|"&amp;C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F11" s="9">
+        <f>IF(D11&gt;=1.15,"Pousser",IF(D11&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>B11&amp;"|"&amp;C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F12" s="9">
+        <f>IF(D12&gt;=1.15,"Pousser",IF(D12&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>B12&amp;"|"&amp;C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="9">
+        <f>IF(D13&gt;=1.15,"Pousser",IF(D13&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>B13&amp;"|"&amp;C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="9">
+        <f>IF(D14&gt;=1.15,"Pousser",IF(D14&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>B14&amp;"|"&amp;C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ipac Bachelor Factory</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F15" s="9">
+        <f>IF(D15&gt;=1.15,"Pousser",IF(D15&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>B15&amp;"|"&amp;C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <f>IF(D16&gt;=1.15,"Pousser",IF(D16&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>B16&amp;"|"&amp;C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Bordeaux</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9">
+        <f>IF(D17&gt;=1.15,"Pousser",IF(D17&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>B17&amp;"|"&amp;C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
           <t>Tunon</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="E18" s="33" t="n">
         <v>1.1</v>
       </c>
-      <c r="E10" s="9">
-        <f>IF(C10&gt;=1.15,"Pousser",IF(C10&lt;=0.85,"Défendre","Maintenir"))</f>
+      <c r="F18" s="9">
+        <f>IF(D18&gt;=1.15,"Pousser",IF(D18&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>B18&amp;"|"&amp;C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F19" s="9">
+        <f>IF(D19&gt;=1.15,"Pousser",IF(D19&lt;=0.85,"Défendre","Maintenir"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>B19&amp;"|"&amp;C19</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -9774,7 +11379,7 @@
         </is>
       </c>
       <c r="E4" s="39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F4" s="39" t="n">
         <v>600</v>
@@ -9827,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="6">
@@ -9852,7 +11457,7 @@
         </is>
       </c>
       <c r="E6" s="39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" s="39" t="n">
         <v>520</v>
@@ -9867,7 +11472,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="25" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7">
@@ -9930,7 +11535,7 @@
         </is>
       </c>
       <c r="E8" s="39" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="39" t="n">
         <v>440</v>
@@ -9945,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="25" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="9">
@@ -9970,7 +11575,7 @@
         </is>
       </c>
       <c r="E9" s="39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" s="39" t="n">
         <v>600</v>
@@ -10023,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="25" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="11">
@@ -10048,7 +11653,7 @@
         </is>
       </c>
       <c r="E11" s="39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" s="39" t="n">
         <v>520</v>
@@ -10063,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="12">
@@ -10126,7 +11731,7 @@
         </is>
       </c>
       <c r="E13" s="39" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" s="39" t="n">
         <v>440</v>
@@ -10141,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="25" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14">
@@ -10166,7 +11771,7 @@
         </is>
       </c>
       <c r="E14" s="39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14" s="39" t="n">
         <v>600</v>
@@ -10219,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="16">
@@ -10244,7 +11849,7 @@
         </is>
       </c>
       <c r="E16" s="39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="39" t="n">
         <v>520</v>
@@ -10259,7 +11864,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="17">
@@ -10337,7 +11942,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -10362,7 +11967,7 @@
         </is>
       </c>
       <c r="E19" s="39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F19" s="39" t="n">
         <v>600</v>
@@ -10400,7 +12005,7 @@
         </is>
       </c>
       <c r="E20" s="39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="39" t="n">
         <v>520</v>
@@ -10415,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="21">
@@ -10440,7 +12045,7 @@
         </is>
       </c>
       <c r="E21" s="39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F21" s="39" t="n">
         <v>600</v>
@@ -10493,7 +12098,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="25" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="23">
@@ -10518,7 +12123,7 @@
         </is>
       </c>
       <c r="E23" s="39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F23" s="39" t="n">
         <v>520</v>
@@ -10533,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="25" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -10983,7 +12588,7 @@
         <v>8500</v>
       </c>
       <c r="N9" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -12607,7 +14212,7 @@
         <v>9000</v>
       </c>
       <c r="N38" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -14305,7 +15910,7 @@
         <v>2102540</v>
       </c>
       <c r="E5" s="41" t="n">
-        <v>1393788</v>
+        <v>1358988</v>
       </c>
       <c r="F5" s="41" t="n">
         <v>231000</v>
@@ -14510,7 +16115,7 @@
         <v>1483250</v>
       </c>
       <c r="E10" s="41" t="n">
-        <v>840870</v>
+        <v>873430</v>
       </c>
       <c r="F10" s="41" t="n">
         <v>163000</v>
@@ -15235,11 +16840,11 @@
         <v/>
       </c>
       <c r="V3" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A3,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A3&amp;"|"&amp;B3,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W3" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A3,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A3&amp;"|"&amp;B3,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X3" s="42">
@@ -15405,11 +17010,11 @@
         <v/>
       </c>
       <c r="V4" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A4,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A4&amp;"|"&amp;B4,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W4" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A4,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A4&amp;"|"&amp;B4,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X4" s="42">
@@ -15575,11 +17180,11 @@
         <v/>
       </c>
       <c r="V5" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A5,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A5&amp;"|"&amp;B5,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W5" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A5,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A5&amp;"|"&amp;B5,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X5" s="42">
@@ -15745,11 +17350,11 @@
         <v/>
       </c>
       <c r="V6" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A6,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A6&amp;"|"&amp;B6,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W6" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A6,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A6&amp;"|"&amp;B6,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X6" s="42">
@@ -15915,11 +17520,11 @@
         <v/>
       </c>
       <c r="V7" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A7,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A7&amp;"|"&amp;B7,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W7" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A7,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A7&amp;"|"&amp;B7,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X7" s="42">
@@ -16085,11 +17690,11 @@
         <v/>
       </c>
       <c r="V8" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A8,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A8&amp;"|"&amp;B8,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W8" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A8,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A8&amp;"|"&amp;B8,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X8" s="42">
@@ -16255,11 +17860,11 @@
         <v/>
       </c>
       <c r="V9" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A9,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A9&amp;"|"&amp;B9,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W9" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A9,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A9&amp;"|"&amp;B9,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X9" s="42">
@@ -16425,11 +18030,11 @@
         <v/>
       </c>
       <c r="V10" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A10,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A10&amp;"|"&amp;B10,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W10" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A10,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A10&amp;"|"&amp;B10,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X10" s="42">
@@ -16595,11 +18200,11 @@
         <v/>
       </c>
       <c r="V11" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A11,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A11&amp;"|"&amp;B11,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W11" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A11,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A11&amp;"|"&amp;B11,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X11" s="42">
@@ -16765,11 +18370,11 @@
         <v/>
       </c>
       <c r="V12" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A12,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A12&amp;"|"&amp;B12,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W12" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A12,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A12&amp;"|"&amp;B12,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X12" s="42">
@@ -16935,11 +18540,11 @@
         <v/>
       </c>
       <c r="V13" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A13,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A13&amp;"|"&amp;B13,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W13" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A13,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A13&amp;"|"&amp;B13,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X13" s="42">
@@ -17105,11 +18710,11 @@
         <v/>
       </c>
       <c r="V14" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A14,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A14&amp;"|"&amp;B14,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W14" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A14,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A14&amp;"|"&amp;B14,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X14" s="42">
@@ -17275,11 +18880,11 @@
         <v/>
       </c>
       <c r="V15" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A15,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A15&amp;"|"&amp;B15,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W15" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A15,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A15&amp;"|"&amp;B15,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X15" s="42">
@@ -17445,11 +19050,11 @@
         <v/>
       </c>
       <c r="V16" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A16,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A16&amp;"|"&amp;B16,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W16" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A16,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A16&amp;"|"&amp;B16,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X16" s="42">
@@ -17615,11 +19220,11 @@
         <v/>
       </c>
       <c r="V17" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A17,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A17&amp;"|"&amp;B17,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W17" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A17,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A17&amp;"|"&amp;B17,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X17" s="42">
@@ -17785,11 +19390,11 @@
         <v/>
       </c>
       <c r="V18" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A18,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A18&amp;"|"&amp;B18,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W18" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A18,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A18&amp;"|"&amp;B18,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X18" s="42">
@@ -17955,11 +19560,11 @@
         <v/>
       </c>
       <c r="V19" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A19,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A19&amp;"|"&amp;B19,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W19" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A19,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A19&amp;"|"&amp;B19,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X19" s="42">
@@ -18125,11 +19730,11 @@
         <v/>
       </c>
       <c r="V20" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A20,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A20&amp;"|"&amp;B20,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W20" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A20,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A20&amp;"|"&amp;B20,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X20" s="42">
@@ -18295,11 +19900,11 @@
         <v/>
       </c>
       <c r="V21" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A21,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A21&amp;"|"&amp;B21,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W21" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A21,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A21&amp;"|"&amp;B21,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X21" s="42">
@@ -18465,11 +20070,11 @@
         <v/>
       </c>
       <c r="V22" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A22,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A22&amp;"|"&amp;B22,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W22" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A22,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A22&amp;"|"&amp;B22,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X22" s="42">
@@ -18635,11 +20240,11 @@
         <v/>
       </c>
       <c r="V23" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A23,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A23&amp;"|"&amp;B23,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W23" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A23,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A23&amp;"|"&amp;B23,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X23" s="42">
@@ -18805,11 +20410,11 @@
         <v/>
       </c>
       <c r="V24" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A24,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A24&amp;"|"&amp;B24,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W24" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A24,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A24&amp;"|"&amp;B24,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X24" s="42">
@@ -18975,11 +20580,11 @@
         <v/>
       </c>
       <c r="V25" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A25,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A25&amp;"|"&amp;B25,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W25" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A25,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A25&amp;"|"&amp;B25,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X25" s="42">
@@ -19145,11 +20750,11 @@
         <v/>
       </c>
       <c r="V26" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A26,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A26&amp;"|"&amp;B26,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W26" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A26,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A26&amp;"|"&amp;B26,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X26" s="42">
@@ -19315,11 +20920,11 @@
         <v/>
       </c>
       <c r="V27" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A27,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A27&amp;"|"&amp;B27,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W27" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A27,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A27&amp;"|"&amp;B27,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X27" s="42">
@@ -19485,11 +21090,11 @@
         <v/>
       </c>
       <c r="V28" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A28,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A28&amp;"|"&amp;B28,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W28" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A28,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A28&amp;"|"&amp;B28,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X28" s="42">
@@ -19655,11 +21260,11 @@
         <v/>
       </c>
       <c r="V29" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A29,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A29&amp;"|"&amp;B29,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W29" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A29,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A29&amp;"|"&amp;B29,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X29" s="42">
@@ -19825,11 +21430,11 @@
         <v/>
       </c>
       <c r="V30" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A30,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A30&amp;"|"&amp;B30,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W30" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A30,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A30&amp;"|"&amp;B30,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X30" s="42">
@@ -19995,11 +21600,11 @@
         <v/>
       </c>
       <c r="V31" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A31,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A31&amp;"|"&amp;B31,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W31" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A31,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A31&amp;"|"&amp;B31,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X31" s="42">
@@ -20165,11 +21770,11 @@
         <v/>
       </c>
       <c r="V32" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A32,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A32&amp;"|"&amp;B32,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W32" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A32,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A32&amp;"|"&amp;B32,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X32" s="42">
@@ -20335,11 +21940,11 @@
         <v/>
       </c>
       <c r="V33" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A33,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A33&amp;"|"&amp;B33,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W33" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A33,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A33&amp;"|"&amp;B33,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X33" s="42">
@@ -20505,11 +22110,11 @@
         <v/>
       </c>
       <c r="V34" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A34,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A34&amp;"|"&amp;B34,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W34" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A34,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A34&amp;"|"&amp;B34,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X34" s="42">
@@ -20675,11 +22280,11 @@
         <v/>
       </c>
       <c r="V35" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A35,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A35&amp;"|"&amp;B35,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W35" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A35,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A35&amp;"|"&amp;B35,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X35" s="42">
@@ -20845,11 +22450,11 @@
         <v/>
       </c>
       <c r="V36" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A36,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A36&amp;"|"&amp;B36,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W36" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A36,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A36&amp;"|"&amp;B36,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X36" s="42">
@@ -21015,11 +22620,11 @@
         <v/>
       </c>
       <c r="V37" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A37,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A37&amp;"|"&amp;B37,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W37" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A37,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A37&amp;"|"&amp;B37,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X37" s="42">
@@ -21185,11 +22790,11 @@
         <v/>
       </c>
       <c r="V38" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A38,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A38&amp;"|"&amp;B38,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W38" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A38,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A38&amp;"|"&amp;B38,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X38" s="42">
@@ -21355,11 +22960,11 @@
         <v/>
       </c>
       <c r="V39" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A39,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A39&amp;"|"&amp;B39,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W39" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A39,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A39&amp;"|"&amp;B39,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X39" s="42">
@@ -21525,11 +23130,11 @@
         <v/>
       </c>
       <c r="V40" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A40,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A40&amp;"|"&amp;B40,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W40" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A40,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A40&amp;"|"&amp;B40,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X40" s="42">
@@ -21695,11 +23300,11 @@
         <v/>
       </c>
       <c r="V41" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A41,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A41&amp;"|"&amp;B41,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W41" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A41,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A41&amp;"|"&amp;B41,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X41" s="42">
@@ -21865,11 +23470,11 @@
         <v/>
       </c>
       <c r="V42" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A42,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A42&amp;"|"&amp;B42,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W42" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A42,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A42&amp;"|"&amp;B42,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X42" s="42">
@@ -22035,11 +23640,11 @@
         <v/>
       </c>
       <c r="V43" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A43,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A43&amp;"|"&amp;B43,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W43" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A43,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A43&amp;"|"&amp;B43,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X43" s="42">
@@ -22205,11 +23810,11 @@
         <v/>
       </c>
       <c r="V44" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A44,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A44&amp;"|"&amp;B44,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W44" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A44,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A44&amp;"|"&amp;B44,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X44" s="42">
@@ -22375,11 +23980,11 @@
         <v/>
       </c>
       <c r="V45" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A45,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A45&amp;"|"&amp;B45,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W45" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A45,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A45&amp;"|"&amp;B45,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X45" s="42">
@@ -22545,11 +24150,11 @@
         <v/>
       </c>
       <c r="V46" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A46,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A46&amp;"|"&amp;B46,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W46" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A46,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A46&amp;"|"&amp;B46,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X46" s="42">
@@ -22715,11 +24320,11 @@
         <v/>
       </c>
       <c r="V47" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A47,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A47&amp;"|"&amp;B47,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W47" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A47,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A47&amp;"|"&amp;B47,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X47" s="42">
@@ -22885,11 +24490,11 @@
         <v/>
       </c>
       <c r="V48" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A48,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A48&amp;"|"&amp;B48,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W48" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A48,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A48&amp;"|"&amp;B48,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X48" s="42">
@@ -23055,11 +24660,11 @@
         <v/>
       </c>
       <c r="V49" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A49,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A49&amp;"|"&amp;B49,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W49" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A49,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A49&amp;"|"&amp;B49,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X49" s="42">
@@ -23225,11 +24830,11 @@
         <v/>
       </c>
       <c r="V50" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A50,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A50&amp;"|"&amp;B50,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W50" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A50,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A50&amp;"|"&amp;B50,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X50" s="42">
@@ -23395,11 +25000,11 @@
         <v/>
       </c>
       <c r="V51" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A51,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A51&amp;"|"&amp;B51,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W51" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A51,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A51&amp;"|"&amp;B51,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X51" s="42">
@@ -23565,11 +25170,11 @@
         <v/>
       </c>
       <c r="V52" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A52,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A52&amp;"|"&amp;B52,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W52" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A52,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A52&amp;"|"&amp;B52,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X52" s="42">
@@ -23735,11 +25340,11 @@
         <v/>
       </c>
       <c r="V53" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A53,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A53&amp;"|"&amp;B53,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W53" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A53,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A53&amp;"|"&amp;B53,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X53" s="42">
@@ -23905,11 +25510,11 @@
         <v/>
       </c>
       <c r="V54" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A54,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A54&amp;"|"&amp;B54,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W54" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A54,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A54&amp;"|"&amp;B54,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X54" s="42">
@@ -24075,11 +25680,11 @@
         <v/>
       </c>
       <c r="V55" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A55,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A55&amp;"|"&amp;B55,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W55" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A55,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A55&amp;"|"&amp;B55,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X55" s="42">
@@ -24245,11 +25850,11 @@
         <v/>
       </c>
       <c r="V56" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A56,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A56&amp;"|"&amp;B56,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W56" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A56,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A56&amp;"|"&amp;B56,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X56" s="42">
@@ -24415,11 +26020,11 @@
         <v/>
       </c>
       <c r="V57" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A57,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A57&amp;"|"&amp;B57,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W57" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A57,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A57&amp;"|"&amp;B57,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X57" s="42">
@@ -24585,11 +26190,11 @@
         <v/>
       </c>
       <c r="V58" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A58,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A58&amp;"|"&amp;B58,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W58" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A58,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A58&amp;"|"&amp;B58,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X58" s="42">
@@ -24755,11 +26360,11 @@
         <v/>
       </c>
       <c r="V59" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A59,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A59&amp;"|"&amp;B59,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W59" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A59,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A59&amp;"|"&amp;B59,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X59" s="42">
@@ -24925,11 +26530,11 @@
         <v/>
       </c>
       <c r="V60" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$C$6:$C$10,MATCH(A60,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$19,MATCH(A60&amp;"|"&amp;B60,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="W60" s="42">
-        <f>INDEX('03_Coeff_Strateg'!$D$6:$D$10,MATCH(A60,'03_Coeff_Strateg'!$B$6:$B$10,0))</f>
+        <f>INDEX('03_Coeff_Strateg'!$E$6:$E$19,MATCH(A60&amp;"|"&amp;B60,'03_Coeff_Strateg'!$H$6:$H$19,0))</f>
         <v/>
       </c>
       <c r="X60" s="42">

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -20,9 +20,10 @@
     <sheet name="10_PnL" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="11_Simulateur" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="11b_Mutualisation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="12_Sensibilite" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="13_Simulation" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="14_Mapping_Tagetik" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="11c_Cascade" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="12_Sensibilite" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="13_Simulation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="14_Mapping_Tagetik" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -195,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -404,6 +405,9 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -423,6 +427,20 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -721,6 +739,26 @@
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="C21" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif budget de la promo.</t>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0" shapeId="0">
+      <text>
+        <t>Ton choix. Menu restreint selon l'année : entrée = lancer/capter ; poursuite = seulement regrouper.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Levier testé et son incrément.</t>
@@ -740,7 +778,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
@@ -1679,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1858,109 +1896,122 @@
     <row r="18">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>12_Sensibilite</t>
+          <t>11c_Cascade</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Impact € sur l'EBITDA par levier (sens unique)</t>
+          <t>Allocation EN CASCADE (marque→campus→classe) + effet d'une fermeture (bénéfique vs entraînement)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>13_Simulation</t>
+          <t>12_Sensibilite</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>KPIs, € à risque, taux d'alternance/sécurisation</t>
+          <t>Impact € sur l'EBITDA par levier (sens unique)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>13_Simulation</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>KPIs, € à risque, taux d'alternance/sécurisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>14_Mapping_Tagetik</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Passerelle Tagetik</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Légende</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Saisie / donnée réelle</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="9" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Formule</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="10" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Lien inter-feuilles</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> exemple </t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Hypothèse à remplir</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="12" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Marques/campus réels EDUSERVICES ; montants ILLUSTRATIFS calibrés sur des ordres de grandeur sourcés (scolarité 8-11 k€, NPEC ~7-10 k€, marge EBITDA ~20 %, classe ~30). À remplacer par le réel.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
+    <row r="30"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C20:D20"/>
@@ -1970,14 +2021,14 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B29:D30"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C27:D27"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B28:D29"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B22:D22"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C18:D18"/>
@@ -8822,6 +8873,683 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:AS33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Allocation de la structure EN CASCADE (marque → campus → classe) &amp; effet d'une fermeture</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cas d'école (bac à sable, montants illustratifs). La structure NON-ÉVITABLE descend en cascade : au CA par marque, puis au nb d'étudiants par campus, puis au NB DE CLASSES par promo (3 classes → /3). Fermer une promo ne supprime pas la structure : elle se redivise sur les classes restantes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1) Descente de la structure non-évitable  —  siège groupe → marque (au CA) → campus (au nb d'étudiants)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Siège / structure GROUPE à répartir (€) :</t>
+        </is>
+      </c>
+      <c r="E6" s="74" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Marque</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>CA (€)</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Part CA</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Siège alloué marque</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>MBway (focus)</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D9" s="52">
+        <f>IFERROR(C9/SUM($C$9:$C$11),0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>D9*$E$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ISCOM</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D10" s="52">
+        <f>IFERROR(C10/SUM($C$9:$C$11),0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>D10*$E$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Pigier</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D11" s="52">
+        <f>IFERROR(C11/SUM($C$9:$C$11),0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>D11*$E$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C12" s="46">
+        <f>SUM(C9:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E12" s="46">
+        <f>SUM(E9:E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Campus MBway</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Part effectif</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Siège campus</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Fixe campus (loyer+perm)</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Envelope campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Lyon (focus)</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>260</v>
+      </c>
+      <c r="D15" s="52">
+        <f>IFERROR(C15/SUM($C$15:$C$17),0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>D15*$E$9</f>
+        <v/>
+      </c>
+      <c r="F15" s="41" t="n">
+        <v>205000</v>
+      </c>
+      <c r="G15" s="54">
+        <f>E15+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="n">
+        <v>310</v>
+      </c>
+      <c r="D16" s="52">
+        <f>IFERROR(C16/SUM($C$15:$C$17),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>D16*$E$9</f>
+        <v/>
+      </c>
+      <c r="F16" s="41" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G16" s="54">
+        <f>E16+F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>240</v>
+      </c>
+      <c r="D17" s="52">
+        <f>IFERROR(C17/SUM($C$15:$C$17),0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>D17*$E$9</f>
+        <v/>
+      </c>
+      <c r="F17" s="41" t="n">
+        <v>240000</v>
+      </c>
+      <c r="G17" s="54">
+        <f>E17+F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C18" s="45">
+        <f>SUM(C15:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E18" s="46">
+        <f>SUM(E15:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="46">
+        <f>SUM(F15:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="46">
+        <f>SUM(G15:G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2) Répartition campus → promos AU NOMBRE DE CLASSES  —  Campus focus : MBway Lyon  (décide sur la CONTRIBUTION ; la structure se redivise)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Promo (MBway Lyon)</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Effectif</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Contribution
+(évitable)</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Struct/classe
+(avant)</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Struct allouée
+(avant)</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Résultat t.c.
+(avant)</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>Décision</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Classes
+après</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Struct allouée
+(après)</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>Résultat t.c.
+(après)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor 1</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="n">
+        <v>66</v>
+      </c>
+      <c r="D22" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="41" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F22" s="17">
+        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f>D22*F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="54">
+        <f>E22-G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="J22" s="50">
+        <f>IF(I22="Fermer",0,D22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>IF(I22="Fermer",0,J22*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="54">
+        <f>IF(I22="Fermer",0,E22-K22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor 2</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="n">
+        <v>56</v>
+      </c>
+      <c r="D23" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="41" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F23" s="17">
+        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>D23*F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="54">
+        <f>E23-G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="J23" s="50">
+        <f>IF(I23="Fermer",0,D23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>IF(I23="Fermer",0,J23*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
+        <v/>
+      </c>
+      <c r="L23" s="54">
+        <f>IF(I23="Fermer",0,E23-K23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor 3</t>
+        </is>
+      </c>
+      <c r="C24" s="39" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>105000</v>
+      </c>
+      <c r="F24" s="17">
+        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f>D24*F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="54">
+        <f>E24-G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="J24" s="50">
+        <f>IF(I24="Fermer",0,D24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>IF(I24="Fermer",0,J24*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
+        <v/>
+      </c>
+      <c r="L24" s="54">
+        <f>IF(I24="Fermer",0,E24-K24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Mastère 2 (sous-rempli)</t>
+        </is>
+      </c>
+      <c r="C25" s="39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="F25" s="17">
+        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>D25*F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="54">
+        <f>E25-G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>Fermer</t>
+        </is>
+      </c>
+      <c r="J25" s="50">
+        <f>IF(I25="Fermer",0,D25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF(I25="Fermer",0,J25*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
+        <v/>
+      </c>
+      <c r="L25" s="54">
+        <f>IF(I25="Fermer",0,E25-K25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C26" s="45">
+        <f>SUM(C22:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="45">
+        <f>SUM(D22:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="46">
+        <f>SUM(E22:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G26" s="46">
+        <f>SUM(G22:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="46">
+        <f>SUM(H22:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J26" s="45">
+        <f>SUM(J22:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="46">
+        <f>SUM(K22:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="46">
+        <f>SUM(L22:L25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>EBITDA campus AVANT :</t>
+        </is>
+      </c>
+      <c r="E28" s="54">
+        <f>SUM(E22:E25)-$G$15</f>
+        <v/>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>EBITDA campus APRÈS :</t>
+        </is>
+      </c>
+      <c r="I28" s="46">
+        <f>SUMIFS(E22:E25,I22:I25,"&lt;&gt;Fermer")-$G$15</f>
+        <v/>
+      </c>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="19" t="inlineStr">
+        <is>
+          <t>Δ EBITDA :</t>
+        </is>
+      </c>
+      <c r="L28" s="20">
+        <f>I28-E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>🧪 LECTURE (deux enseignements). ① On DÉCIDE sur la CONTRIBUTION (évitable) : fermer la promo à contribution NÉGATIVE (Mastère 2) fait MONTER l'EBITDA campus (Δ = +15 000 € = la perte évitée). ② MAIS la structure est NON-ÉVITABLE : en fermant, ses classes quittent le dénominateur → la structure se redivise sur les classes restantes (÷ nb de classes) → le « résultat tout compris » d'une promo marginale (Bachelor 3) bascule EN ROUGE, alors même que l'EBITDA groupe s'est amélioré. Le drag est un effet d'ALLOCATION (comptable), pas une vraie perte : la structure était déjà là. À l'inverse, fermer une promo à contribution POSITIVE (essaie Bachelor 1) fait CHUTER l'EBITDA et enfonce toutes les voisines. N'affecte pas le P&amp;L officiel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B30:L33"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H22:H25">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L22:L25">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="I22 I23 I24 I25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Maintenir,Fermer"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:AS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8932,7 +9660,7 @@
           <t>Exposition financement alternance (€ à sécuriser) :</t>
         </is>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="75">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
@@ -8948,7 +9676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9176,20 +9904,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>€ à sécuriser (exposition)</t>
         </is>
       </c>
-      <c r="C15" s="76">
+      <c r="C15" s="77">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'02_Leviers'!$G$9)</f>
         <v/>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="77">
         <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'02_Leviers'!$D$20)</f>
         <v/>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="78">
         <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
@@ -9203,7 +9931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9252,7 +9980,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="78" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -9269,7 +9997,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="78" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -9286,7 +10014,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="78" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -9303,7 +10031,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="78" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -9320,7 +10048,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="78" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -9337,7 +10065,7 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="78" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>Sécurisation &amp; recouvrement</t>
         </is>
@@ -9354,7 +10082,7 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="78" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>Objectifs (cadrage)</t>
         </is>
@@ -9371,7 +10099,7 @@
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="78" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>Décisions ouvrir/fermer</t>
         </is>
@@ -9388,7 +10116,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="78" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>Allocation structure</t>
         </is>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -405,8 +405,8 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -739,14 +739,19 @@
     <author>Guide</author>
   </authors>
   <commentList>
-    <comment ref="C21" authorId="0" shapeId="0">
+    <comment ref="F14" authorId="0" shapeId="0">
       <text>
-        <t>Effectif budget de la promo.</t>
+        <t>Chiffre d'affaires budget de la promo.</t>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0">
+    <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>Ton choix. Menu restreint selon l'année : entrée = lancer/capter ; poursuite = seulement regrouper.</t>
+      </text>
+    </comment>
+    <comment ref="P14" authorId="0" shapeId="0">
+      <text>
+        <t>Capacité cible d'une classe (nb d'étudiants).</t>
       </text>
     </comment>
   </commentList>
@@ -1901,7 +1906,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Allocation EN CASCADE (marque→campus→classe) + effet d'une fermeture (bénéfique vs entraînement)</t>
+          <t>Allocation EN CASCADE sur un VRAI campus (MBway Lyon) + effet d'une fermeture (bénéfique vs entraînement)</t>
         </is>
       </c>
     </row>
@@ -8873,41 +8878,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS33"/>
+  <dimension ref="A2:AS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Allocation de la structure EN CASCADE (marque → campus → classe) &amp; effet d'une fermeture</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Allocation EN CASCADE sur un VRAI campus (MBway Lyon) &amp; effet d'une fermeture</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cas d'école (bac à sable, montants illustratifs). La structure NON-ÉVITABLE descend en cascade : au CA par marque, puis au nb d'étudiants par campus, puis au NB DE CLASSES par promo (3 classes → /3). Fermer une promo ne supprime pas la structure : elle se redivise sur les classes restantes.</t>
+          <t>Chiffres RÉELS du moteur (structure, CA, effectifs, économie unitaire feuille 05). La structure NON-ÉVITABLE descend en cascade : groupe → marque au CA → campus au nb d'étudiants → promo au NOMBRE DE CLASSES. Change l'effectif SCÉNARIO (bleu) d'une promo : sa contribution se recalcule, et tu vois quand fermer devient bénéfique… ou pas.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1) Descente de la structure non-évitable  —  siège groupe → marque (au CA) → campus (au nb d'étudiants)</t>
+          <t>1) Structure non-évitable de MBway Lyon  —  siège groupe cascadé (CA marque → effectif campus) + loyer &amp; permanents directs (réels, feuille 09)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -8920,622 +8932,691 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Siège / structure GROUPE à répartir (€) :</t>
-        </is>
-      </c>
-      <c r="E6" s="74" t="n">
-        <v>900000</v>
+          <t>Siège / structure centrale GROUPE (réel) :</t>
+        </is>
+      </c>
+      <c r="G6" s="16">
+        <f>'02_Leviers'!$D$17*(1+'02_Leviers'!$G$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>× Part MBway au CA :</t>
+        </is>
+      </c>
+      <c r="G7" s="69">
+        <f>IFERROR(SUMIFS('08_Moteur'!$AH$3:$AH$60,'08_Moteur'!$A$3:$A$60,"MBway")/SUM('08_Moteur'!$AH$3:$AH$60),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>→ Siège MBway :</t>
+        </is>
+      </c>
+      <c r="I7" s="17">
+        <f>G6*G7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Marque</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>CA (€)</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Part CA</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Siège alloué marque</t>
-        </is>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>× Part Lyon dans MBway (aux effectifs) :</t>
+        </is>
+      </c>
+      <c r="G8" s="69">
+        <f>IFERROR(SUMIFS('08_Moteur'!$AD$3:$AD$60,'08_Moteur'!$A$3:$A$60,"MBway",'08_Moteur'!$B$3:$B$60,"Lyon")/SUMIFS('08_Moteur'!$AD$3:$AD$60,'08_Moteur'!$A$3:$A$60,"MBway"),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>→ Siège Lyon :</t>
+        </is>
+      </c>
+      <c r="I8" s="17">
+        <f>I7*G8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>MBway (focus)</t>
-        </is>
-      </c>
-      <c r="C9" s="41" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="D9" s="52">
-        <f>IFERROR(C9/SUM($C$9:$C$11),0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="17">
-        <f>D9*$E$6</f>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Loyer Lyon (réel, feuille 09) :</t>
+        </is>
+      </c>
+      <c r="I9" s="16">
+        <f>'09_Allocation'!E7</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>ISCOM</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D10" s="52">
-        <f>IFERROR(C10/SUM($C$9:$C$11),0)</f>
-        <v/>
-      </c>
-      <c r="E10" s="17">
-        <f>D10*$E$6</f>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Permanents Lyon (réel, feuille 09) :</t>
+        </is>
+      </c>
+      <c r="I10" s="16">
+        <f>'09_Allocation'!F7</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Pigier</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D11" s="52">
-        <f>IFERROR(C11/SUM($C$9:$C$11),0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
-        <f>D11*$E$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C12" s="46">
-        <f>SUM(C9:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="44" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E12" s="46">
-        <f>SUM(E9:E11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>ENVELOPE Lyon = siège Lyon + loyer + permanents (NON-ÉVITABLE) :</t>
+        </is>
+      </c>
+      <c r="I11" s="46">
+        <f>I8+I9+I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2) Répartition Lyon → promos AU NOMBRE DE CLASSES + décision  (change l'effectif bleu ; le rouge = résultat tout compris &lt; 0)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="P13" s="72" t="inlineStr">
+        <is>
+          <t>Paramètres unitaires (issus du modèle, feuille 05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Campus MBway</t>
+          <t>Promo (MBway Lyon)</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Effectif</t>
+          <t>Eff. réel
+(moteur)</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Part effectif</t>
+          <t>Eff.
+scénario</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Siège campus</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Fixe campus (loyer+perm)</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Envelope campus</t>
+          <t>Contribution
+(évitable)</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Struct/classe</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>Struct allouée</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Résultat t.c.
+(avant)</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Décision</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>Cl.
+après</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>Struct après</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>Résultat t.c.
+(après)</t>
+        </is>
+      </c>
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <t>Capacité</t>
+        </is>
+      </c>
+      <c r="Q14" s="13" t="inlineStr">
+        <is>
+          <t>Coût/classe</t>
+        </is>
+      </c>
+      <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t>Tarif</t>
+        </is>
+      </c>
+      <c r="S14" s="13" t="inlineStr">
+        <is>
+          <t>Charge/étu</t>
+        </is>
+      </c>
+      <c r="T14" s="13" t="inlineStr">
+        <is>
+          <t>CAC/étu</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Lyon (focus)</t>
-        </is>
-      </c>
-      <c r="C15" s="39" t="n">
-        <v>260</v>
-      </c>
-      <c r="D15" s="52">
-        <f>IFERROR(C15/SUM($C$15:$C$17),0)</f>
-        <v/>
-      </c>
-      <c r="E15" s="17">
-        <f>D15*$E$9</f>
-        <v/>
-      </c>
-      <c r="F15" s="41" t="n">
-        <v>205000</v>
+          <t>Bachelor 1 (INIT)</t>
+        </is>
+      </c>
+      <c r="C15" s="48">
+        <f>'08_Moteur'!AD8</f>
+        <v/>
+      </c>
+      <c r="D15" s="74" t="n">
+        <v>73</v>
+      </c>
+      <c r="E15" s="50">
+        <f>IF(D15&lt;=0,0,MAX(1,ROUNDUP(D15/P15,0)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>D15*R15</f>
+        <v/>
       </c>
       <c r="G15" s="54">
-        <f>E15+F15</f>
-        <v/>
+        <f>F15-E15*Q15-D15*S15-D15*T15</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>IFERROR($I$11/SUM($E$15:$E$19),0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>E15*H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="54">
+        <f>G15-I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="L15" s="50">
+        <f>IF(K15="Fermer",0,E15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="17">
+        <f>IF(K15="Fermer",0,L15*IFERROR($I$11/SUM($L$15:$L$19),0))</f>
+        <v/>
+      </c>
+      <c r="N15" s="54">
+        <f>IF(K15="Fermer",0,G15-M15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="39" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="41" t="n">
+        <v>34800</v>
+      </c>
+      <c r="R15" s="41" t="n">
+        <v>8500</v>
+      </c>
+      <c r="S15" s="41" t="n">
+        <v>1334</v>
+      </c>
+      <c r="T15" s="41" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="C16" s="39" t="n">
-        <v>310</v>
-      </c>
-      <c r="D16" s="52">
-        <f>IFERROR(C16/SUM($C$15:$C$17),0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="17">
-        <f>D16*$E$9</f>
-        <v/>
-      </c>
-      <c r="F16" s="41" t="n">
-        <v>300000</v>
+          <t>Bachelor 2 (ALT)</t>
+        </is>
+      </c>
+      <c r="C16" s="48">
+        <f>'08_Moteur'!AD9</f>
+        <v/>
+      </c>
+      <c r="D16" s="74" t="n">
+        <v>62</v>
+      </c>
+      <c r="E16" s="50">
+        <f>IF(D16&lt;=0,0,MAX(1,ROUNDUP(D16/P16,0)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>D16*R16</f>
+        <v/>
       </c>
       <c r="G16" s="54">
-        <f>E16+F16</f>
-        <v/>
+        <f>F16-E16*Q16-D16*S16-D16*T16</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>IFERROR($I$11/SUM($E$15:$E$19),0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>E16*H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="54">
+        <f>G16-I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="L16" s="50">
+        <f>IF(K16="Fermer",0,E16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="17">
+        <f>IF(K16="Fermer",0,L16*IFERROR($I$11/SUM($L$15:$L$19),0))</f>
+        <v/>
+      </c>
+      <c r="N16" s="54">
+        <f>IF(K16="Fermer",0,G16-M16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="39" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="41" t="n">
+        <v>32480</v>
+      </c>
+      <c r="R16" s="41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S16" s="41" t="n">
+        <v>1334</v>
+      </c>
+      <c r="T16" s="41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="n">
-        <v>240</v>
-      </c>
-      <c r="D17" s="52">
-        <f>IFERROR(C17/SUM($C$15:$C$17),0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="17">
-        <f>D17*$E$9</f>
-        <v/>
-      </c>
-      <c r="F17" s="41" t="n">
-        <v>240000</v>
+          <t>Bachelor 3 (ALT)</t>
+        </is>
+      </c>
+      <c r="C17" s="48">
+        <f>'08_Moteur'!AD10</f>
+        <v/>
+      </c>
+      <c r="D17" s="74" t="n">
+        <v>54</v>
+      </c>
+      <c r="E17" s="50">
+        <f>IF(D17&lt;=0,0,MAX(1,ROUNDUP(D17/P17,0)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>D17*R17</f>
+        <v/>
       </c>
       <c r="G17" s="54">
-        <f>E17+F17</f>
-        <v/>
+        <f>F17-E17*Q17-D17*S17-D17*T17</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>IFERROR($I$11/SUM($E$15:$E$19),0)</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>E17*H17</f>
+        <v/>
+      </c>
+      <c r="J17" s="54">
+        <f>G17-I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="L17" s="50">
+        <f>IF(K17="Fermer",0,E17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="17">
+        <f>IF(K17="Fermer",0,L17*IFERROR($I$11/SUM($L$15:$L$19),0))</f>
+        <v/>
+      </c>
+      <c r="N17" s="54">
+        <f>IF(K17="Fermer",0,G17-M17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="39" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q17" s="41" t="n">
+        <v>30160</v>
+      </c>
+      <c r="R17" s="41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S17" s="41" t="n">
+        <v>1334</v>
+      </c>
+      <c r="T17" s="41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Mastère 1 (ALT)</t>
+        </is>
+      </c>
+      <c r="C18" s="48">
+        <f>'08_Moteur'!AD11</f>
+        <v/>
+      </c>
+      <c r="D18" s="74" t="n">
+        <v>44</v>
+      </c>
+      <c r="E18" s="50">
+        <f>IF(D18&lt;=0,0,MAX(1,ROUNDUP(D18/P18,0)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>D18*R18</f>
+        <v/>
+      </c>
+      <c r="G18" s="54">
+        <f>F18-E18*Q18-D18*S18-D18*T18</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>IFERROR($I$11/SUM($E$15:$E$19),0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>E18*H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="54">
+        <f>G18-I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>Maintenir</t>
+        </is>
+      </c>
+      <c r="L18" s="50">
+        <f>IF(K18="Fermer",0,E18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="17">
+        <f>IF(K18="Fermer",0,L18*IFERROR($I$11/SUM($L$15:$L$19),0))</f>
+        <v/>
+      </c>
+      <c r="N18" s="54">
+        <f>IF(K18="Fermer",0,G18-M18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="39" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="41" t="n">
+        <v>33600</v>
+      </c>
+      <c r="R18" s="41" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S18" s="41" t="n">
+        <v>1454</v>
+      </c>
+      <c r="T18" s="41" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Mastère 2 — extinction</t>
+        </is>
+      </c>
+      <c r="C19" s="48">
+        <f>'08_Moteur'!AD12</f>
+        <v/>
+      </c>
+      <c r="D19" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="50">
+        <f>IF(D19&lt;=0,0,MAX(1,ROUNDUP(D19/P19,0)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="17">
+        <f>D19*R19</f>
+        <v/>
+      </c>
+      <c r="G19" s="54">
+        <f>F19-E19*Q19-D19*S19-D19*T19</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>IFERROR($I$11/SUM($E$15:$E$19),0)</f>
+        <v/>
+      </c>
+      <c r="I19" s="17">
+        <f>E19*H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="54">
+        <f>G19-I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>Fermer</t>
+        </is>
+      </c>
+      <c r="L19" s="50">
+        <f>IF(K19="Fermer",0,E19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="17">
+        <f>IF(K19="Fermer",0,L19*IFERROR($I$11/SUM($L$15:$L$19),0))</f>
+        <v/>
+      </c>
+      <c r="N19" s="54">
+        <f>IF(K19="Fermer",0,G19-M19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="39" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="41" t="n">
+        <v>30800</v>
+      </c>
+      <c r="R19" s="41" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S19" s="41" t="n">
+        <v>1454</v>
+      </c>
+      <c r="T19" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C18" s="45">
-        <f>SUM(C15:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="C20" s="45">
+        <f>SUM(C15:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="45">
+        <f>SUM(D15:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="45">
+        <f>SUM(E15:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="46">
+        <f>SUM(F15:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="46">
+        <f>SUM(G15:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="44" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="E18" s="46">
-        <f>SUM(E15:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="46">
-        <f>SUM(F15:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="46">
-        <f>SUM(G15:G17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2) Répartition campus → promos AU NOMBRE DE CLASSES  —  Campus focus : MBway Lyon  (décide sur la CONTRIBUTION ; la structure se redivise)</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Promo (MBway Lyon)</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Effectif</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Classes</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Contribution
-(évitable)</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>Struct/classe
-(avant)</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>Struct allouée
-(avant)</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>Résultat t.c.
-(avant)</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>Décision</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>Classes
-après</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>Struct allouée
-(après)</t>
-        </is>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>Résultat t.c.
-(après)</t>
-        </is>
+      <c r="I20" s="46">
+        <f>SUM(I15:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="46">
+        <f>SUM(J15:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="L20" s="45">
+        <f>SUM(L15:L19)</f>
+        <v/>
+      </c>
+      <c r="M20" s="46">
+        <f>SUM(M15:M19)</f>
+        <v/>
+      </c>
+      <c r="N20" s="46">
+        <f>SUM(N15:N19)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Bachelor 1</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="n">
-        <v>66</v>
-      </c>
-      <c r="D22" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="41" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F22" s="17">
-        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="17">
-        <f>D22*F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="54">
-        <f>E22-G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>Maintenir</t>
-        </is>
-      </c>
-      <c r="J22" s="50">
-        <f>IF(I22="Fermer",0,D22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="17">
-        <f>IF(I22="Fermer",0,J22*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
-        <v/>
-      </c>
-      <c r="L22" s="54">
-        <f>IF(I22="Fermer",0,E22-K22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Bachelor 2</t>
-        </is>
-      </c>
-      <c r="C23" s="39" t="n">
-        <v>56</v>
-      </c>
-      <c r="D23" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="41" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F23" s="17">
-        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="17">
-        <f>D23*F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="54">
-        <f>E23-G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>Maintenir</t>
-        </is>
-      </c>
-      <c r="J23" s="50">
-        <f>IF(I23="Fermer",0,D23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="17">
-        <f>IF(I23="Fermer",0,J23*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
-        <v/>
-      </c>
-      <c r="L23" s="54">
-        <f>IF(I23="Fermer",0,E23-K23)</f>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>EBITDA campus AVANT :</t>
+        </is>
+      </c>
+      <c r="F22" s="54">
+        <f>SUM(G15:G19)-$I$11</f>
+        <v/>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>EBITDA campus APRÈS :</t>
+        </is>
+      </c>
+      <c r="J22" s="46">
+        <f>SUMIFS(G15:G19,K15:K19,"&lt;&gt;Fermer")-$I$11</f>
+        <v/>
+      </c>
+      <c r="M22" s="19" t="inlineStr">
+        <is>
+          <t>Δ EBITDA :</t>
+        </is>
+      </c>
+      <c r="N22" s="20">
+        <f>J22-F22</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Bachelor 3</t>
-        </is>
-      </c>
-      <c r="C24" s="39" t="n">
-        <v>50</v>
-      </c>
-      <c r="D24" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>105000</v>
-      </c>
-      <c r="F24" s="17">
-        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="17">
-        <f>D24*F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="54">
-        <f>E24-G24</f>
-        <v/>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>Maintenir</t>
-        </is>
-      </c>
-      <c r="J24" s="50">
-        <f>IF(I24="Fermer",0,D24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="17">
-        <f>IF(I24="Fermer",0,J24*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
-        <v/>
-      </c>
-      <c r="L24" s="54">
-        <f>IF(I24="Fermer",0,E24-K24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Mastère 2 (sous-rempli)</t>
-        </is>
-      </c>
-      <c r="C25" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="41" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="F25" s="17">
-        <f>IFERROR($G$15/SUM($D$22:$D$25),0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="17">
-        <f>D25*F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="54">
-        <f>E25-G25</f>
-        <v/>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>Fermer</t>
-        </is>
-      </c>
-      <c r="J25" s="50">
-        <f>IF(I25="Fermer",0,D25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="17">
-        <f>IF(I25="Fermer",0,J25*IFERROR($G$15/SUM($J$22:$J$25),0))</f>
-        <v/>
-      </c>
-      <c r="L25" s="54">
-        <f>IF(I25="Fermer",0,E25-K25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C26" s="45">
-        <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="45">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="46">
-        <f>SUM(E22:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="44" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="G26" s="46">
-        <f>SUM(G22:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="46">
-        <f>SUM(H22:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="44" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J26" s="45">
-        <f>SUM(J22:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="46">
-        <f>SUM(K22:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="46">
-        <f>SUM(L22:L25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>EBITDA campus AVANT :</t>
-        </is>
-      </c>
-      <c r="E28" s="54">
-        <f>SUM(E22:E25)-$G$15</f>
-        <v/>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>EBITDA campus APRÈS :</t>
-        </is>
-      </c>
-      <c r="I28" s="46">
-        <f>SUMIFS(E22:E25,I22:I25,"&lt;&gt;Fermer")-$G$15</f>
-        <v/>
-      </c>
-      <c r="J28" s="30" t="n"/>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>Δ EBITDA :</t>
-        </is>
-      </c>
-      <c r="L28" s="20">
-        <f>I28-E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>🧪 LECTURE (deux enseignements). ① On DÉCIDE sur la CONTRIBUTION (évitable) : fermer la promo à contribution NÉGATIVE (Mastère 2) fait MONTER l'EBITDA campus (Δ = +15 000 € = la perte évitée). ② MAIS la structure est NON-ÉVITABLE : en fermant, ses classes quittent le dénominateur → la structure se redivise sur les classes restantes (÷ nb de classes) → le « résultat tout compris » d'une promo marginale (Bachelor 3) bascule EN ROUGE, alors même que l'EBITDA groupe s'est amélioré. Le drag est un effet d'ALLOCATION (comptable), pas une vraie perte : la structure était déjà là. À l'inverse, fermer une promo à contribution POSITIVE (essaie Bachelor 1) fait CHUTER l'EBITDA et enfonce toutes les voisines. N'affecte pas le P&amp;L officiel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>🧪 LECTURE (vrai campus, bac à sable). On DÉCIDE sur la CONTRIBUTION (évitable). ① Le Mastère 2 est ici en EXTINCTION (3 étudiants) : sa contribution est NÉGATIVE (une classe coûte plus qu'elle ne rapporte, seuil de rentabilité ≈ 4-5 étudiants) → le fermer fait MONTER l'EBITDA campus = fermeture BÉNÉFIQUE. ② À l'inverse, remets une promo bien remplie (Bachelor 1) sur « Fermer » : l'EBITDA CHUTE (on perd sa contribution) et la structure non-évitable se redivise sur les classes restantes (÷ nb de classes) → le résultat tout compris des voisines se dégrade. Remarque HONNÊTE : avec des promos normalement remplies l'économie unitaire est saine (rentables dès ~5 étudiants), donc fermer n'est JAMAIS bénéfique — ça ne le devient que pour une promo réellement sous-remplie / en extinction. Baisse les effectifs bleus pour rendre une promo marginale et voir l'effet d'entraînement basculer une voisine EN ROUGE. N'affecte pas le P&amp;L officiel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B20:L20"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="B30:L33"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B6:D6"/>
+  <mergeCells count="14">
+    <mergeCell ref="B5:N5"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="P13:T13"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B24:N28"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
-  <conditionalFormatting sqref="H22:H25">
+  <conditionalFormatting sqref="J15:J19">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L22:L25">
+  <conditionalFormatting sqref="N15:N19">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I22 I23 I24 I25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="K15 K16 K17 K18 K19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Maintenir,Fermer"</formula1>
     </dataValidation>
   </dataValidations>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -8882,7 +8882,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -8905,21 +8905,21 @@
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Allocation EN CASCADE sur un VRAI campus (MBway Lyon) &amp; effet d'une fermeture</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>Allocation EN CASCADE sur un VRAI campus (ISCOM Toulouse) &amp; effet d'une fermeture</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chiffres RÉELS du moteur (structure, CA, effectifs, économie unitaire feuille 05). La structure NON-ÉVITABLE descend en cascade : groupe → marque au CA → campus au nb d'étudiants → promo au NOMBRE DE CLASSES. Change l'effectif SCÉNARIO (bleu) d'une promo : sa contribution se recalcule, et tu vois quand fermer devient bénéfique… ou pas.</t>
+          <t>OBJET DE L'ONGLET : montrer, sur un vrai campus, QUAND fermer une promo est bénéfique (ou pas). Chiffres RÉELS du moteur. La structure NON-ÉVITABLE descend en cascade : groupe → marque au CA → campus au nb d'étudiants → promo au NOMBRE DE CLASSES. On DÉCIDE sur la CONTRIBUTION (évitable) ; le « résultat tout compris » (après structure) n'est qu'informatif. Change l'effectif SCÉNARIO (bleu) : contribution et classes se recalculent.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1) Structure non-évitable de MBway Lyon  —  siège groupe cascadé (CA marque → effectif campus) + loyer &amp; permanents directs (réels, feuille 09)</t>
+          <t>1) Structure non-évitable de ISCOM Toulouse  —  siège groupe cascadé (CA marque → effectif campus) + loyer &amp; permanents directs (réels, feuille 09)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -8949,16 +8949,16 @@
     <row r="7">
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>× Part MBway au CA :</t>
+          <t>× Part ISCOM au CA :</t>
         </is>
       </c>
       <c r="G7" s="69">
-        <f>IFERROR(SUMIFS('08_Moteur'!$AH$3:$AH$60,'08_Moteur'!$A$3:$A$60,"MBway")/SUM('08_Moteur'!$AH$3:$AH$60),0)</f>
+        <f>IFERROR(SUMIFS('08_Moteur'!$AH$3:$AH$60,'08_Moteur'!$A$3:$A$60,"ISCOM")/SUM('08_Moteur'!$AH$3:$AH$60),0)</f>
         <v/>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>→ Siège MBway :</t>
+          <t>→ Siège ISCOM :</t>
         </is>
       </c>
       <c r="I7" s="17">
@@ -8969,16 +8969,16 @@
     <row r="8">
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>× Part Lyon dans MBway (aux effectifs) :</t>
+          <t>× Part Toulouse dans ISCOM (aux effectifs) :</t>
         </is>
       </c>
       <c r="G8" s="69">
-        <f>IFERROR(SUMIFS('08_Moteur'!$AD$3:$AD$60,'08_Moteur'!$A$3:$A$60,"MBway",'08_Moteur'!$B$3:$B$60,"Lyon")/SUMIFS('08_Moteur'!$AD$3:$AD$60,'08_Moteur'!$A$3:$A$60,"MBway"),0)</f>
+        <f>IFERROR(SUMIFS('08_Moteur'!$AD$3:$AD$60,'08_Moteur'!$A$3:$A$60,"ISCOM",'08_Moteur'!$B$3:$B$60,"Toulouse")/SUMIFS('08_Moteur'!$AD$3:$AD$60,'08_Moteur'!$A$3:$A$60,"ISCOM"),0)</f>
         <v/>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>→ Siège Lyon :</t>
+          <t>→ Siège Toulouse :</t>
         </is>
       </c>
       <c r="I8" s="17">
@@ -8989,29 +8989,29 @@
     <row r="9">
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Loyer Lyon (réel, feuille 09) :</t>
+          <t>Loyer Toulouse (réel, feuille 09) :</t>
         </is>
       </c>
       <c r="I9" s="16">
-        <f>'09_Allocation'!E7</f>
+        <f>'09_Allocation'!E12</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Permanents Lyon (réel, feuille 09) :</t>
+          <t>Permanents Toulouse (réel, feuille 09) :</t>
         </is>
       </c>
       <c r="I10" s="16">
-        <f>'09_Allocation'!F7</f>
+        <f>'09_Allocation'!F12</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>ENVELOPE Lyon = siège Lyon + loyer + permanents (NON-ÉVITABLE) :</t>
+          <t>ENVELOPE Toulouse = siège + loyer + permanents (NON-ÉVITABLE) :</t>
         </is>
       </c>
       <c r="I11" s="46">
@@ -9022,7 +9022,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2) Répartition Lyon → promos AU NOMBRE DE CLASSES + décision  (change l'effectif bleu ; le rouge = résultat tout compris &lt; 0)</t>
+          <t>2) Répartition campus → promos AU NOMBRE DE CLASSES + décision  (change l'effectif bleu ; le rouge = résultat tout compris &lt; 0)</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -9046,7 +9046,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Promo (MBway Lyon)</t>
+          <t>Promo (ISCOM Toulouse)</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -9148,11 +9148,11 @@
         </is>
       </c>
       <c r="C15" s="48">
-        <f>'08_Moteur'!AD8</f>
+        <f>'08_Moteur'!AD33</f>
         <v/>
       </c>
       <c r="D15" s="74" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E15" s="50">
         <f>IF(D15&lt;=0,0,MAX(1,ROUNDUP(D15/P15,0)))</f>
@@ -9199,13 +9199,13 @@
         <v>32</v>
       </c>
       <c r="Q15" s="41" t="n">
-        <v>34800</v>
+        <v>37200</v>
       </c>
       <c r="R15" s="41" t="n">
         <v>8500</v>
       </c>
       <c r="S15" s="41" t="n">
-        <v>1334</v>
+        <v>1484</v>
       </c>
       <c r="T15" s="41" t="n">
         <v>320</v>
@@ -9218,11 +9218,11 @@
         </is>
       </c>
       <c r="C16" s="48">
-        <f>'08_Moteur'!AD9</f>
+        <f>'08_Moteur'!AD34</f>
         <v/>
       </c>
       <c r="D16" s="74" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="E16" s="50">
         <f>IF(D16&lt;=0,0,MAX(1,ROUNDUP(D16/P16,0)))</f>
@@ -9269,13 +9269,13 @@
         <v>32</v>
       </c>
       <c r="Q16" s="41" t="n">
-        <v>32480</v>
+        <v>34720</v>
       </c>
       <c r="R16" s="41" t="n">
         <v>8000</v>
       </c>
       <c r="S16" s="41" t="n">
-        <v>1334</v>
+        <v>1484</v>
       </c>
       <c r="T16" s="41" t="n">
         <v>0</v>
@@ -9288,11 +9288,11 @@
         </is>
       </c>
       <c r="C17" s="48">
-        <f>'08_Moteur'!AD10</f>
+        <f>'08_Moteur'!AD35</f>
         <v/>
       </c>
       <c r="D17" s="74" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E17" s="50">
         <f>IF(D17&lt;=0,0,MAX(1,ROUNDUP(D17/P17,0)))</f>
@@ -9339,13 +9339,13 @@
         <v>32</v>
       </c>
       <c r="Q17" s="41" t="n">
-        <v>30160</v>
+        <v>32240</v>
       </c>
       <c r="R17" s="41" t="n">
         <v>8000</v>
       </c>
       <c r="S17" s="41" t="n">
-        <v>1334</v>
+        <v>1484</v>
       </c>
       <c r="T17" s="41" t="n">
         <v>0</v>
@@ -9354,15 +9354,15 @@
     <row r="18">
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Mastère 1 (ALT)</t>
+          <t>Mastère 1 (ALT — piège)</t>
         </is>
       </c>
       <c r="C18" s="48">
-        <f>'08_Moteur'!AD11</f>
+        <f>'08_Moteur'!AD36</f>
         <v/>
       </c>
       <c r="D18" s="74" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E18" s="50">
         <f>IF(D18&lt;=0,0,MAX(1,ROUNDUP(D18/P18,0)))</f>
@@ -9409,13 +9409,13 @@
         <v>26</v>
       </c>
       <c r="Q18" s="41" t="n">
-        <v>33600</v>
+        <v>35520</v>
       </c>
       <c r="R18" s="41" t="n">
         <v>9000</v>
       </c>
       <c r="S18" s="41" t="n">
-        <v>1454</v>
+        <v>1604</v>
       </c>
       <c r="T18" s="41" t="n">
         <v>600</v>
@@ -9428,11 +9428,11 @@
         </is>
       </c>
       <c r="C19" s="48">
-        <f>'08_Moteur'!AD12</f>
+        <f>'08_Moteur'!AD37</f>
         <v/>
       </c>
       <c r="D19" s="74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="50">
         <f>IF(D19&lt;=0,0,MAX(1,ROUNDUP(D19/P19,0)))</f>
@@ -9479,13 +9479,13 @@
         <v>26</v>
       </c>
       <c r="Q19" s="41" t="n">
-        <v>30800</v>
+        <v>32560</v>
       </c>
       <c r="R19" s="41" t="n">
         <v>9000</v>
       </c>
       <c r="S19" s="41" t="n">
-        <v>1454</v>
+        <v>1604</v>
       </c>
       <c r="T19" s="41" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
     <row r="24">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>🧪 LECTURE (vrai campus, bac à sable). On DÉCIDE sur la CONTRIBUTION (évitable). ① Le Mastère 2 est ici en EXTINCTION (3 étudiants) : sa contribution est NÉGATIVE (une classe coûte plus qu'elle ne rapporte, seuil de rentabilité ≈ 4-5 étudiants) → le fermer fait MONTER l'EBITDA campus = fermeture BÉNÉFIQUE. ② À l'inverse, remets une promo bien remplie (Bachelor 1) sur « Fermer » : l'EBITDA CHUTE (on perd sa contribution) et la structure non-évitable se redivise sur les classes restantes (÷ nb de classes) → le résultat tout compris des voisines se dégrade. Remarque HONNÊTE : avec des promos normalement remplies l'économie unitaire est saine (rentables dès ~5 étudiants), donc fermer n'est JAMAIS bénéfique — ça ne le devient que pour une promo réellement sous-remplie / en extinction. Baisse les effectifs bleus pour rendre une promo marginale et voir l'effet d'entraînement basculer une voisine EN ROUGE. N'affecte pas le P&amp;L officiel.</t>
+          <t>🧪 LECTURE (vrai campus ISCOM Toulouse, bac à sable). On DÉCIDE sur la CONTRIBUTION (évitable), JAMAIS sur le résultat tout compris. Trois enseignements visibles ici : ① FERMER BÉNÉFIQUE — le Mastère 2 est en EXTINCTION (4 étudiants) : sa CONTRIBUTION est négative (une classe coûte plus qu'elle ne rapporte) → le fermer fait MONTER l'EBITDA campus (Δ = perte évitée). ② EFFET D'ENTRAÎNEMENT — en fermant, la structure non-évitable se redivise sur les classes restantes (÷ nb de classes) → le résultat tout compris du Bachelor 3 (déjà mince) bascule EN ROUGE, alors que l'EBITDA s'est amélioré : c'est un effet d'ALLOCATION comptable, pas une vraie perte. ③ LE PIÈGE — le Mastère 1 est EN ROUGE en résultat tout compris (il porte beaucoup de structure) MAIS sa CONTRIBUTION est POSITIVE (~+119 k€) → il NE FAUT PAS le fermer : le fermer FERAIT PERDRE cette contribution et alourdirait tout le monde. Essaie : mets le Mastère 1 sur « Fermer » → l'EBITDA CHUTE. N'affecte pas le P&amp;L officiel.</t>
         </is>
       </c>
     </row>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -519,24 +519,9 @@
     <author>Guide</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0" shapeId="0">
+    <comment ref="B2" authorId="0" shapeId="0">
       <text>
-        <t>Indicateur de pilotage.</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>Objectif fixé par la direction (saisie).</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <t>Résultat du budget construit par les drivers (moteur).</t>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
-      <text>
-        <t>Budget construit − cible.</t>
+        <t>OBJET DE L'ONGLET — Sommaire et mode d'emploi du classeur : rôle de chaque feuille, légende des couleurs, périmètre. Commence ici.</t>
       </text>
     </comment>
   </commentList>
@@ -549,6 +534,81 @@
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Répartir les frais de structure FIXES sur les campus selon un driver (effectifs / CA / m²).</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Campus (ville). Une entité = Marque + Ville.</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Marge de contribution (CA − coûts directs évitables).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Loyer du campus (structure fixe).</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Masse salariale permanente (structure fixe).</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>Valeur du driver d'allocation (effectif, CA ou m² selon 02_Leviers).</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Part du campus dans le driver total.</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <t>Frais de structure groupe alloués à ce campus.</t>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <t>EBITDA du campus = contribution − loyer − permanents − structure allouée.</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>Dotations aux amortissements.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>Résultat d'exploitation = EBITDA − D&amp;A.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Compte de résultat consolidé N-1 vs Budget + PONT d'explication du CA (volume / tarif / sécurisation / frais).</t>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Ligne du compte de résultat.</t>
@@ -578,12 +638,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — BAC À SABLE de décisions à la maille PROMO (ouvrir / fermer / regrouper) → impact EBITDA AVANT/APRÈS. N'affecte PAS le budget officiel.</t>
+      </text>
+    </comment>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -673,12 +738,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — BAC À SABLE à la maille CAMPUS × CYCLE : combien de classes / € récupérables en mutualisant le tronc commun, sans dépasser la capacité.</t>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -733,15 +803,60 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — BAC À SABLE : allocation de la structure EN CASCADE (marque→campus→classe) et démonstration de QUAND fermer une promo est bénéfique ou non, sur un vrai campus.</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Promotion = programme × année du campus focus (ISCOM Toulouse).</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif budget RÉEL calculé par le moteur (feuille 08) pour cette promo — sert de référence en regard du scénario.</t>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0">
+      <text>
+        <t>Effectif que TU testes (bleu, éditable). Baisse-le pour simuler une promo sous-remplie / en extinction et voir l'effet.</t>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0">
+      <text>
+        <t>Nombre de classes = arrondi supérieur (effectif scénario / capacité).</t>
+      </text>
+    </comment>
     <comment ref="F14" authorId="0" shapeId="0">
       <text>
         <t>Chiffre d'affaires budget de la promo.</t>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0">
+      <text>
+        <t>CA − coûts directs évitables (enseignement + charge/étu + CAC). C'est LA métrique de décision : on ne ferme que si elle est négative.</t>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0">
+      <text>
+        <t>Structure non-évitable du campus (envelope) ÷ nombre total de classes. C'est ce qui se REDIVISE quand on ferme une promo.</t>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0">
+      <text>
+        <t>Structure portée par la promo = ses classes × structure/classe.</t>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0" shapeId="0">
+      <text>
+        <t>Résultat TOUT COMPRIS = contribution − structure allouée. INFORMATIF : peut être négatif alors que la contribution est positive (le piège). JAMAIS un critère de fermeture.</t>
       </text>
     </comment>
     <comment ref="K14" authorId="0" shapeId="0">
@@ -749,21 +864,61 @@
         <t>Ton choix. Menu restreint selon l'année : entrée = lancer/capter ; poursuite = seulement regrouper.</t>
       </text>
     </comment>
+    <comment ref="L14" authorId="0" shapeId="0">
+      <text>
+        <t>Nombre de classes après ta décision (0 si Fermer).</t>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0">
+      <text>
+        <t>Structure allouée après décisions : l'envelope (inchangée, non-évitable) se redivise sur les classes RESTANTES → chacune en porte plus.</t>
+      </text>
+    </comment>
+    <comment ref="N14" authorId="0" shapeId="0">
+      <text>
+        <t>Résultat tout compris recalculé après décisions. En ROUGE si &lt; 0 : rend visible l'effet d'entraînement.</t>
+      </text>
+    </comment>
     <comment ref="P14" authorId="0" shapeId="0">
       <text>
         <t>Capacité cible d'une classe (nb d'étudiants).</t>
+      </text>
+    </comment>
+    <comment ref="Q14" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'enseignement d'une classe (heures × taux horaire), issu du modèle (feuille 05).</t>
+      </text>
+    </comment>
+    <comment ref="R14" authorId="0" shapeId="0">
+      <text>
+        <t>Tarif de scolarité par étudiant et par an (feuille 05).</t>
+      </text>
+    </comment>
+    <comment ref="S14" authorId="0" shapeId="0">
+      <text>
+        <t>Charges variables par étudiant = coût pédagogique + autres charges d'exploitation (feuille 05).</t>
+      </text>
+    </comment>
+    <comment ref="T14" authorId="0" shapeId="0">
+      <text>
+        <t>Coût d'acquisition (achat de leads) par étudiant — uniquement en année d'entrée.</t>
       </text>
     </comment>
   </commentList>
 </comments>
 </file>
 
-<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Classer les LEVIERS par impact € sur l'EBITDA, pour savoir lequel actionner afin de combler l'écart de cadrage.</t>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Levier testé et son incrément.</t>
@@ -783,12 +938,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment16.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — TABLEAU DE BORD : KPIs clés Budget vs N-1 (effectif, CA, EBITDA, taux d'alternance, sécurisation, € à sécuriser).</t>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Indicateur de pilotage.</t>
@@ -813,12 +973,82 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment17.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — PASSERELLE : correspondance entre les objets du modèle Excel et leur implémentation dans CCH Tagetik.</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Notion du modèle Excel à transposer dans Tagetik.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Objet CCH Tagetik correspondant (dimension, hiérarchie, règle de calcul, workflow…).</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Précision sur la correspondance et le paramétrage Tagetik.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Cadrage TOP-DOWN : la direction saisit les cibles CA/EBITDA ; la feuille affiche l'écart avec le budget CONSTRUIT par les leviers.</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Indicateur de pilotage.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Objectif fixé par la direction (saisie).</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Résultat du budget construit par les drivers (moteur).</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Budget construit − cible.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Poste de pilotage : régler les hypothèses (en %), choisir le scénario, et voir les constantes de référence (mesuré vs repli). Tout le budget se recalcule à partir d'ici.</t>
+      </text>
+    </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Scénario actif : change cette cellule et TOUT le budget se recalcule.</t>
@@ -883,12 +1113,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Moduler l'intensité MARKETING et PRIX par marque ET par campus : effort appliqué = levier (feuille 02) × coefficient.</t>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -914,16 +1149,26 @@
         <t>Lecture du positionnement (pousser / défendre / maintenir).</t>
       </text>
     </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Clé technique marque|campus : le moteur s'en sert pour retrouver le bon coefficient stratégique du campus.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Dimensions et plan de comptes du modèle (entités Groupe→Marque→Campus, comptes fixe/variable) — le socle de structuration.</t>
+      </text>
+    </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -953,12 +1198,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Données de référence UNITAIRES par programme × année (capacité, heures, taux, pédago, CAC, passage) qui alimentent le moteur. À charger avec le réel.</t>
+      </text>
+    </comment>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Clé technique 'programme|année' pour relier les paramètres au moteur.</t>
@@ -984,9 +1234,19 @@
         <t>Capacité cible d'une classe (nb d'étudiants).</t>
       </text>
     </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>Heures d'enseignement délivrées par classe et par an.</t>
+      </text>
+    </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Coût horaire chargé de l'enseignement (vacation), en €.</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>Coût pédagogique par étudiant/an, HORS salaires des intervenants (supports, licences, LMS, jury/examens, certifications). 350-670 € selon le domaine.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
@@ -1003,12 +1263,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Réalisé N-1 par cellule (funnel + cohorte) et historique marketing N-2/N-1 servant à MESURER la conversion, le passage et l'élasticité (pas d'invention).</t>
+      </text>
+    </comment>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -1083,12 +1348,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — Réalisé N-1 par CAMPUS (loyers, ETP permanents, D&amp;A, m²) : la base des coûts de structure.</t>
+      </text>
+    </comment>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -1148,12 +1418,17 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Guide</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>OBJET DE L'ONGLET — CŒUR DE CALCUL : construit le budget de CHAQUE cellule (cohortes, marketing→volume, tarif, financement alternance, point mort). Toutes les feuilles de résultat en découlent.</t>
+      </text>
+    </comment>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
         <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
@@ -1362,71 +1637,6 @@
     <comment ref="AP2" authorId="0" shapeId="0">
       <text>
         <t>Point mort = nb d'étudiants pour couvrir le coût des classes.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Guide</author>
-  </authors>
-  <commentList>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>Marque / école du groupe (dimension Entity dans Tagetik).</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>Campus (ville). Une entité = Marque + Ville.</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <t>Marge de contribution (CA − coûts directs évitables).</t>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
-      <text>
-        <t>Loyer du campus (structure fixe).</t>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>Masse salariale permanente (structure fixe).</t>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
-      <text>
-        <t>Valeur du driver d'allocation (effectif, CA ou m² selon 02_Leviers).</t>
-      </text>
-    </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
-      <text>
-        <t>Part du campus dans le driver total.</t>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
-      <text>
-        <t>Frais de structure groupe alloués à ce campus.</t>
-      </text>
-    </comment>
-    <comment ref="J5" authorId="0" shapeId="0">
-      <text>
-        <t>EBITDA du campus = contribution − loyer − permanents − structure allouée.</t>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="0" shapeId="0">
-      <text>
-        <t>Dotations aux amortissements.</t>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
-      <text>
-        <t>Résultat d'exploitation = EBITDA − D&amp;A.</t>
       </text>
     </comment>
   </commentList>
@@ -1722,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1731,6 +1941,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2040,6 +2251,7 @@
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2049,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS20"/>
+  <dimension ref="A1:AS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2278,7 @@
     <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2889,7 +3102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS25"/>
+  <dimension ref="A1:AS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2900,6 +3113,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -7651,7 +7865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS35"/>
+  <dimension ref="A1:AS35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7667,6 +7881,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -8878,7 +9093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS28"/>
+  <dimension ref="A1:AS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8902,6 +9117,7 @@
     <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -9631,7 +9847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS11"/>
+  <dimension ref="A1:AS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9640,6 +9856,7 @@
     <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -9763,7 +9980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS15"/>
+  <dimension ref="A1:AS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9773,6 +9990,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -10018,7 +10236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS14"/>
+  <dimension ref="A1:AS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10027,6 +10245,7 @@
     <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -10219,6 +10438,7 @@
     <mergeCell ref="B4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -10228,7 +10448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS14"/>
+  <dimension ref="A1:AS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10238,6 +10458,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -10367,7 +10588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10379,6 +10600,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -10887,7 +11109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS19"/>
+  <dimension ref="A1:AS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10900,6 +11122,7 @@
     <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="28" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -11326,7 +11549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AS32"/>
+  <dimension ref="A1:AS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -11337,6 +11560,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>

--- a/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
+++ b/eduservices/EDUSERVICES_Modele_Pilotage_Budget.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -298,13 +298,13 @@
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -419,18 +419,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,7 +719,7 @@
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
-        <t>OBJET DE L'ONGLET — Compte de résultat consolidé N-1 vs Budget + PONT d'explication du CA (volume / tarif / sécurisation / frais).</t>
+        <t>OBJET DE L'ONGLET — Compte de résultat consolidé N-1 vs Budget + PONT d'explication du CA (volume / tarif / frais).</t>
       </text>
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
@@ -1071,7 +1059,7 @@
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
-        <t>OBJET DE L'ONGLET — TABLEAU DE BORD : KPIs clés Budget vs N-1 (effectif, CA, EBITDA, taux d'alternance, sécurisation, € à sécuriser).</t>
+        <t>OBJET DE L'ONGLET — TABLEAU DE BORD : KPIs clés Budget vs N-1 (effectif, CA, EBITDA, taux d'alternance).</t>
       </text>
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
@@ -1304,22 +1292,22 @@
         <t>Effectif réel l'an dernier.</t>
       </text>
     </comment>
-    <comment ref="AA5" authorId="0" shapeId="0">
+    <comment ref="Y5" authorId="0" shapeId="0">
       <text>
         <t>Nombre de classes l'an dernier.</t>
       </text>
     </comment>
-    <comment ref="AC5" authorId="0" shapeId="0">
+    <comment ref="AA5" authorId="0" shapeId="0">
       <text>
         <t>Capacité cible d'une classe (nb d'étudiants).</t>
       </text>
     </comment>
-    <comment ref="AD5" authorId="0" shapeId="0">
+    <comment ref="AB5" authorId="0" shapeId="0">
       <text>
         <t>Heures d'enseignement délivrées par classe et par an.</t>
       </text>
     </comment>
-    <comment ref="AE5" authorId="0" shapeId="0">
+    <comment ref="AC5" authorId="0" shapeId="0">
       <text>
         <t>Coût horaire chargé de l'enseignement (vacation), en €.</t>
       </text>
@@ -1752,16 +1740,6 @@
     <comment ref="AE2" authorId="0" shapeId="0">
       <text>
         <t>Tarif budget = tarif N-1 × (1 + hausse prix × coefficient marque).</t>
-      </text>
-    </comment>
-    <comment ref="AF2" authorId="0" shapeId="0">
-      <text>
-        <t>Facteur de financement alternance BUDGET (sécurisation + reste à charge recouvré). = 1 en initial.</t>
-      </text>
-    </comment>
-    <comment ref="AG2" authorId="0" shapeId="0">
-      <text>
-        <t>Facteur de financement alternance N-1 (référence pour le pont).</t>
       </text>
     </comment>
     <comment ref="AH2" authorId="0" shapeId="0">
@@ -2418,7 +2396,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>KPIs, € à risque, taux d'alternance/sécurisation</t>
+          <t>KPIs Budget vs N-1 : effectif, CA, EBITDA, taux d'alternance</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS25"/>
+  <dimension ref="A1:AS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2784,7 +2762,7 @@
         <v/>
       </c>
       <c r="D8" s="24">
-        <f>-(SUM('08_Moteur'!$AJ$3:$AJ$60)+SUM('08_Moteur'!$AK$3:$AK$60)+SUM('08_Moteur'!$AL$3:$AL$60)+'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)*SUM('08_Moteur'!$AD$3:$AD$60))</f>
+        <f>-(SUM('08_Moteur'!$AJ$3:$AJ$60)+SUM('08_Moteur'!$AK$3:$AK$60)+SUM('08_Moteur'!$AL$3:$AL$60)+'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)*SUM('08_Moteur'!$AD$3:$AD$60))</f>
         <v/>
       </c>
       <c r="E8" s="69">
@@ -3022,7 +3000,7 @@
         </is>
       </c>
       <c r="C21" s="24">
-        <f>SUMPRODUCT(('08_Moteur'!$AD$3:$AD$60-'08_Moteur'!$G$3:$G$60)*'08_Moteur'!$L$3:$L$60*'08_Moteur'!$AG$3:$AG$60)</f>
+        <f>SUMPRODUCT(('08_Moteur'!$AD$3:$AD$60-'08_Moteur'!$G$3:$G$60)*'08_Moteur'!$L$3:$L$60)</f>
         <v/>
       </c>
     </row>
@@ -3033,39 +3011,28 @@
         </is>
       </c>
       <c r="C22" s="24">
-        <f>SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*('08_Moteur'!$AE$3:$AE$60-'08_Moteur'!$L$3:$L$60)*'08_Moteur'!$AG$3:$AG$60)</f>
+        <f>SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*('08_Moteur'!$AE$3:$AE$60-'08_Moteur'!$L$3:$L$60))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  + Effet Sécurisation</t>
+          <t xml:space="preserve">  + Effet Frais</t>
         </is>
       </c>
       <c r="C23" s="24">
-        <f>SUMPRODUCT('08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60*('08_Moteur'!$AF$3:$AF$60-'08_Moteur'!$AG$3:$AG$60))</f>
+        <f>SUMPRODUCT('08_Moteur'!$AB$3:$AB$60)*'01_Cadrage'!$H$24-SUMPRODUCT('08_Moteur'!$H$3:$H$60)*'01_Cadrage'!$H$24</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  + Effet Frais</t>
-        </is>
-      </c>
-      <c r="C24" s="24">
-        <f>SUMPRODUCT('08_Moteur'!$AB$3:$AB$60)*'01_Cadrage'!$H$24-SUMPRODUCT('08_Moteur'!$H$3:$H$60)*'01_Cadrage'!$H$24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="47" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>CA Budget N+1</t>
         </is>
       </c>
-      <c r="C25" s="50">
+      <c r="C24" s="50">
         <f>SUM('08_Moteur'!$AH$3:$AH$60)</f>
         <v/>
       </c>
@@ -3336,7 +3303,7 @@
         <v/>
       </c>
       <c r="N6" s="24">
-        <f>IF(L6="Ne pas lancer",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI3&gt;=2,E6&lt;=('08_Moteur'!AI3-1)*'08_Moteur'!O3*1.1),H6+'08_Moteur'!U3,H6),H6)))</f>
+        <f>IF(L6="Ne pas lancer",0,IF(L6="Ouvrir +1 classe",H6+'08_Moteur'!O3*('08_Moteur'!AE3*'08_Moteur'!AF3-('08_Moteur'!R3+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S3)-'08_Moteur'!U3,IF(L6="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI3&gt;=2,E6&lt;=('08_Moteur'!AI3-1)*'08_Moteur'!O3*1.1),H6+'08_Moteur'!U3,H6),H6)))</f>
         <v/>
       </c>
       <c r="O6" s="24">
@@ -3407,7 +3374,7 @@
         <v/>
       </c>
       <c r="N7" s="24">
-        <f>IF(L7="Ne pas lancer",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI4&gt;=2,E7&lt;=('08_Moteur'!AI4-1)*'08_Moteur'!O4*1.1),H7+'08_Moteur'!U4,H7),H7)))</f>
+        <f>IF(L7="Ne pas lancer",0,IF(L7="Ouvrir +1 classe",H7+'08_Moteur'!O4*('08_Moteur'!AE4*'08_Moteur'!AF4-('08_Moteur'!R4+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S4)-'08_Moteur'!U4,IF(L7="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI4&gt;=2,E7&lt;=('08_Moteur'!AI4-1)*'08_Moteur'!O4*1.1),H7+'08_Moteur'!U4,H7),H7)))</f>
         <v/>
       </c>
       <c r="O7" s="24">
@@ -3478,7 +3445,7 @@
         <v/>
       </c>
       <c r="N8" s="24">
-        <f>IF(L8="Ne pas lancer",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI5&gt;=2,E8&lt;=('08_Moteur'!AI5-1)*'08_Moteur'!O5*1.1),H8+'08_Moteur'!U5,H8),H8)))</f>
+        <f>IF(L8="Ne pas lancer",0,IF(L8="Ouvrir +1 classe",H8+'08_Moteur'!O5*('08_Moteur'!AE5*'08_Moteur'!AF5-('08_Moteur'!R5+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S5)-'08_Moteur'!U5,IF(L8="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI5&gt;=2,E8&lt;=('08_Moteur'!AI5-1)*'08_Moteur'!O5*1.1),H8+'08_Moteur'!U5,H8),H8)))</f>
         <v/>
       </c>
       <c r="O8" s="24">
@@ -3549,7 +3516,7 @@
         <v/>
       </c>
       <c r="N9" s="24">
-        <f>IF(L9="Ne pas lancer",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI6&gt;=2,E9&lt;=('08_Moteur'!AI6-1)*'08_Moteur'!O6*1.1),H9+'08_Moteur'!U6,H9),H9)))</f>
+        <f>IF(L9="Ne pas lancer",0,IF(L9="Ouvrir +1 classe",H9+'08_Moteur'!O6*('08_Moteur'!AE6*'08_Moteur'!AF6-('08_Moteur'!R6+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S6)-'08_Moteur'!U6,IF(L9="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI6&gt;=2,E9&lt;=('08_Moteur'!AI6-1)*'08_Moteur'!O6*1.1),H9+'08_Moteur'!U6,H9),H9)))</f>
         <v/>
       </c>
       <c r="O9" s="24">
@@ -3620,7 +3587,7 @@
         <v/>
       </c>
       <c r="N10" s="24">
-        <f>IF(L10="Ne pas lancer",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI7&gt;=2,E10&lt;=('08_Moteur'!AI7-1)*'08_Moteur'!O7*1.1),H10+'08_Moteur'!U7,H10),H10)))</f>
+        <f>IF(L10="Ne pas lancer",0,IF(L10="Ouvrir +1 classe",H10+'08_Moteur'!O7*('08_Moteur'!AE7*'08_Moteur'!AF7-('08_Moteur'!R7+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S7)-'08_Moteur'!U7,IF(L10="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI7&gt;=2,E10&lt;=('08_Moteur'!AI7-1)*'08_Moteur'!O7*1.1),H10+'08_Moteur'!U7,H10),H10)))</f>
         <v/>
       </c>
       <c r="O10" s="24">
@@ -3691,7 +3658,7 @@
         <v/>
       </c>
       <c r="N11" s="24">
-        <f>IF(L11="Ne pas lancer",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI8&gt;=2,E11&lt;=('08_Moteur'!AI8-1)*'08_Moteur'!O8*1.1),H11+'08_Moteur'!U8,H11),H11)))</f>
+        <f>IF(L11="Ne pas lancer",0,IF(L11="Ouvrir +1 classe",H11+'08_Moteur'!O8*('08_Moteur'!AE8*'08_Moteur'!AF8-('08_Moteur'!R8+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S8)-'08_Moteur'!U8,IF(L11="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI8&gt;=2,E11&lt;=('08_Moteur'!AI8-1)*'08_Moteur'!O8*1.1),H11+'08_Moteur'!U8,H11),H11)))</f>
         <v/>
       </c>
       <c r="O11" s="24">
@@ -3762,7 +3729,7 @@
         <v/>
       </c>
       <c r="N12" s="24">
-        <f>IF(L12="Ne pas lancer",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI9&gt;=2,E12&lt;=('08_Moteur'!AI9-1)*'08_Moteur'!O9*1.1),H12+'08_Moteur'!U9,H12),H12)))</f>
+        <f>IF(L12="Ne pas lancer",0,IF(L12="Ouvrir +1 classe",H12+'08_Moteur'!O9*('08_Moteur'!AE9*'08_Moteur'!AF9-('08_Moteur'!R9+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S9)-'08_Moteur'!U9,IF(L12="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI9&gt;=2,E12&lt;=('08_Moteur'!AI9-1)*'08_Moteur'!O9*1.1),H12+'08_Moteur'!U9,H12),H12)))</f>
         <v/>
       </c>
       <c r="O12" s="24">
@@ -3833,7 +3800,7 @@
         <v/>
       </c>
       <c r="N13" s="24">
-        <f>IF(L13="Ne pas lancer",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI10&gt;=2,E13&lt;=('08_Moteur'!AI10-1)*'08_Moteur'!O10*1.1),H13+'08_Moteur'!U10,H13),H13)))</f>
+        <f>IF(L13="Ne pas lancer",0,IF(L13="Ouvrir +1 classe",H13+'08_Moteur'!O10*('08_Moteur'!AE10*'08_Moteur'!AF10-('08_Moteur'!R10+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S10)-'08_Moteur'!U10,IF(L13="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI10&gt;=2,E13&lt;=('08_Moteur'!AI10-1)*'08_Moteur'!O10*1.1),H13+'08_Moteur'!U10,H13),H13)))</f>
         <v/>
       </c>
       <c r="O13" s="24">
@@ -3904,7 +3871,7 @@
         <v/>
       </c>
       <c r="N14" s="24">
-        <f>IF(L14="Ne pas lancer",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI11&gt;=2,E14&lt;=('08_Moteur'!AI11-1)*'08_Moteur'!O11*1.1),H14+'08_Moteur'!U11,H14),H14)))</f>
+        <f>IF(L14="Ne pas lancer",0,IF(L14="Ouvrir +1 classe",H14+'08_Moteur'!O11*('08_Moteur'!AE11*'08_Moteur'!AF11-('08_Moteur'!R11+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S11)-'08_Moteur'!U11,IF(L14="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI11&gt;=2,E14&lt;=('08_Moteur'!AI11-1)*'08_Moteur'!O11*1.1),H14+'08_Moteur'!U11,H14),H14)))</f>
         <v/>
       </c>
       <c r="O14" s="24">
@@ -3975,7 +3942,7 @@
         <v/>
       </c>
       <c r="N15" s="24">
-        <f>IF(L15="Ne pas lancer",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI12&gt;=2,E15&lt;=('08_Moteur'!AI12-1)*'08_Moteur'!O12*1.1),H15+'08_Moteur'!U12,H15),H15)))</f>
+        <f>IF(L15="Ne pas lancer",0,IF(L15="Ouvrir +1 classe",H15+'08_Moteur'!O12*('08_Moteur'!AE12*'08_Moteur'!AF12-('08_Moteur'!R12+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S12)-'08_Moteur'!U12,IF(L15="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI12&gt;=2,E15&lt;=('08_Moteur'!AI12-1)*'08_Moteur'!O12*1.1),H15+'08_Moteur'!U12,H15),H15)))</f>
         <v/>
       </c>
       <c r="O15" s="24">
@@ -4046,7 +4013,7 @@
         <v/>
       </c>
       <c r="N16" s="24">
-        <f>IF(L16="Ne pas lancer",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI13&gt;=2,E16&lt;=('08_Moteur'!AI13-1)*'08_Moteur'!O13*1.1),H16+'08_Moteur'!U13,H16),H16)))</f>
+        <f>IF(L16="Ne pas lancer",0,IF(L16="Ouvrir +1 classe",H16+'08_Moteur'!O13*('08_Moteur'!AE13*'08_Moteur'!AF13-('08_Moteur'!R13+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S13)-'08_Moteur'!U13,IF(L16="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI13&gt;=2,E16&lt;=('08_Moteur'!AI13-1)*'08_Moteur'!O13*1.1),H16+'08_Moteur'!U13,H16),H16)))</f>
         <v/>
       </c>
       <c r="O16" s="24">
@@ -4117,7 +4084,7 @@
         <v/>
       </c>
       <c r="N17" s="24">
-        <f>IF(L17="Ne pas lancer",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI14&gt;=2,E17&lt;=('08_Moteur'!AI14-1)*'08_Moteur'!O14*1.1),H17+'08_Moteur'!U14,H17),H17)))</f>
+        <f>IF(L17="Ne pas lancer",0,IF(L17="Ouvrir +1 classe",H17+'08_Moteur'!O14*('08_Moteur'!AE14*'08_Moteur'!AF14-('08_Moteur'!R14+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S14)-'08_Moteur'!U14,IF(L17="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI14&gt;=2,E17&lt;=('08_Moteur'!AI14-1)*'08_Moteur'!O14*1.1),H17+'08_Moteur'!U14,H17),H17)))</f>
         <v/>
       </c>
       <c r="O17" s="24">
@@ -4188,7 +4155,7 @@
         <v/>
       </c>
       <c r="N18" s="24">
-        <f>IF(L18="Ne pas lancer",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI15&gt;=2,E18&lt;=('08_Moteur'!AI15-1)*'08_Moteur'!O15*1.1),H18+'08_Moteur'!U15,H18),H18)))</f>
+        <f>IF(L18="Ne pas lancer",0,IF(L18="Ouvrir +1 classe",H18+'08_Moteur'!O15*('08_Moteur'!AE15*'08_Moteur'!AF15-('08_Moteur'!R15+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S15)-'08_Moteur'!U15,IF(L18="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI15&gt;=2,E18&lt;=('08_Moteur'!AI15-1)*'08_Moteur'!O15*1.1),H18+'08_Moteur'!U15,H18),H18)))</f>
         <v/>
       </c>
       <c r="O18" s="24">
@@ -4259,7 +4226,7 @@
         <v/>
       </c>
       <c r="N19" s="24">
-        <f>IF(L19="Ne pas lancer",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI16&gt;=2,E19&lt;=('08_Moteur'!AI16-1)*'08_Moteur'!O16*1.1),H19+'08_Moteur'!U16,H19),H19)))</f>
+        <f>IF(L19="Ne pas lancer",0,IF(L19="Ouvrir +1 classe",H19+'08_Moteur'!O16*('08_Moteur'!AE16*'08_Moteur'!AF16-('08_Moteur'!R16+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S16)-'08_Moteur'!U16,IF(L19="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI16&gt;=2,E19&lt;=('08_Moteur'!AI16-1)*'08_Moteur'!O16*1.1),H19+'08_Moteur'!U16,H19),H19)))</f>
         <v/>
       </c>
       <c r="O19" s="24">
@@ -4330,7 +4297,7 @@
         <v/>
       </c>
       <c r="N20" s="24">
-        <f>IF(L20="Ne pas lancer",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI17&gt;=2,E20&lt;=('08_Moteur'!AI17-1)*'08_Moteur'!O17*1.1),H20+'08_Moteur'!U17,H20),H20)))</f>
+        <f>IF(L20="Ne pas lancer",0,IF(L20="Ouvrir +1 classe",H20+'08_Moteur'!O17*('08_Moteur'!AE17*'08_Moteur'!AF17-('08_Moteur'!R17+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S17)-'08_Moteur'!U17,IF(L20="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI17&gt;=2,E20&lt;=('08_Moteur'!AI17-1)*'08_Moteur'!O17*1.1),H20+'08_Moteur'!U17,H20),H20)))</f>
         <v/>
       </c>
       <c r="O20" s="24">
@@ -4401,7 +4368,7 @@
         <v/>
       </c>
       <c r="N21" s="24">
-        <f>IF(L21="Ne pas lancer",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI18&gt;=2,E21&lt;=('08_Moteur'!AI18-1)*'08_Moteur'!O18*1.1),H21+'08_Moteur'!U18,H21),H21)))</f>
+        <f>IF(L21="Ne pas lancer",0,IF(L21="Ouvrir +1 classe",H21+'08_Moteur'!O18*('08_Moteur'!AE18*'08_Moteur'!AF18-('08_Moteur'!R18+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S18)-'08_Moteur'!U18,IF(L21="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI18&gt;=2,E21&lt;=('08_Moteur'!AI18-1)*'08_Moteur'!O18*1.1),H21+'08_Moteur'!U18,H21),H21)))</f>
         <v/>
       </c>
       <c r="O21" s="24">
@@ -4472,7 +4439,7 @@
         <v/>
       </c>
       <c r="N22" s="24">
-        <f>IF(L22="Ne pas lancer",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI19&gt;=2,E22&lt;=('08_Moteur'!AI19-1)*'08_Moteur'!O19*1.1),H22+'08_Moteur'!U19,H22),H22)))</f>
+        <f>IF(L22="Ne pas lancer",0,IF(L22="Ouvrir +1 classe",H22+'08_Moteur'!O19*('08_Moteur'!AE19*'08_Moteur'!AF19-('08_Moteur'!R19+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S19)-'08_Moteur'!U19,IF(L22="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI19&gt;=2,E22&lt;=('08_Moteur'!AI19-1)*'08_Moteur'!O19*1.1),H22+'08_Moteur'!U19,H22),H22)))</f>
         <v/>
       </c>
       <c r="O22" s="24">
@@ -4543,7 +4510,7 @@
         <v/>
       </c>
       <c r="N23" s="24">
-        <f>IF(L23="Ne pas lancer",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI20&gt;=2,E23&lt;=('08_Moteur'!AI20-1)*'08_Moteur'!O20*1.1),H23+'08_Moteur'!U20,H23),H23)))</f>
+        <f>IF(L23="Ne pas lancer",0,IF(L23="Ouvrir +1 classe",H23+'08_Moteur'!O20*('08_Moteur'!AE20*'08_Moteur'!AF20-('08_Moteur'!R20+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S20)-'08_Moteur'!U20,IF(L23="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI20&gt;=2,E23&lt;=('08_Moteur'!AI20-1)*'08_Moteur'!O20*1.1),H23+'08_Moteur'!U20,H23),H23)))</f>
         <v/>
       </c>
       <c r="O23" s="24">
@@ -4614,7 +4581,7 @@
         <v/>
       </c>
       <c r="N24" s="24">
-        <f>IF(L24="Ne pas lancer",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI21&gt;=2,E24&lt;=('08_Moteur'!AI21-1)*'08_Moteur'!O21*1.1),H24+'08_Moteur'!U21,H24),H24)))</f>
+        <f>IF(L24="Ne pas lancer",0,IF(L24="Ouvrir +1 classe",H24+'08_Moteur'!O21*('08_Moteur'!AE21*'08_Moteur'!AF21-('08_Moteur'!R21+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S21)-'08_Moteur'!U21,IF(L24="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI21&gt;=2,E24&lt;=('08_Moteur'!AI21-1)*'08_Moteur'!O21*1.1),H24+'08_Moteur'!U21,H24),H24)))</f>
         <v/>
       </c>
       <c r="O24" s="24">
@@ -4685,7 +4652,7 @@
         <v/>
       </c>
       <c r="N25" s="24">
-        <f>IF(L25="Ne pas lancer",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI22&gt;=2,E25&lt;=('08_Moteur'!AI22-1)*'08_Moteur'!O22*1.1),H25+'08_Moteur'!U22,H25),H25)))</f>
+        <f>IF(L25="Ne pas lancer",0,IF(L25="Ouvrir +1 classe",H25+'08_Moteur'!O22*('08_Moteur'!AE22*'08_Moteur'!AF22-('08_Moteur'!R22+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S22)-'08_Moteur'!U22,IF(L25="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI22&gt;=2,E25&lt;=('08_Moteur'!AI22-1)*'08_Moteur'!O22*1.1),H25+'08_Moteur'!U22,H25),H25)))</f>
         <v/>
       </c>
       <c r="O25" s="24">
@@ -4756,7 +4723,7 @@
         <v/>
       </c>
       <c r="N26" s="24">
-        <f>IF(L26="Ne pas lancer",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI23&gt;=2,E26&lt;=('08_Moteur'!AI23-1)*'08_Moteur'!O23*1.1),H26+'08_Moteur'!U23,H26),H26)))</f>
+        <f>IF(L26="Ne pas lancer",0,IF(L26="Ouvrir +1 classe",H26+'08_Moteur'!O23*('08_Moteur'!AE23*'08_Moteur'!AF23-('08_Moteur'!R23+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S23)-'08_Moteur'!U23,IF(L26="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI23&gt;=2,E26&lt;=('08_Moteur'!AI23-1)*'08_Moteur'!O23*1.1),H26+'08_Moteur'!U23,H26),H26)))</f>
         <v/>
       </c>
       <c r="O26" s="24">
@@ -4827,7 +4794,7 @@
         <v/>
       </c>
       <c r="N27" s="24">
-        <f>IF(L27="Ne pas lancer",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI24&gt;=2,E27&lt;=('08_Moteur'!AI24-1)*'08_Moteur'!O24*1.1),H27+'08_Moteur'!U24,H27),H27)))</f>
+        <f>IF(L27="Ne pas lancer",0,IF(L27="Ouvrir +1 classe",H27+'08_Moteur'!O24*('08_Moteur'!AE24*'08_Moteur'!AF24-('08_Moteur'!R24+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S24)-'08_Moteur'!U24,IF(L27="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI24&gt;=2,E27&lt;=('08_Moteur'!AI24-1)*'08_Moteur'!O24*1.1),H27+'08_Moteur'!U24,H27),H27)))</f>
         <v/>
       </c>
       <c r="O27" s="24">
@@ -4898,7 +4865,7 @@
         <v/>
       </c>
       <c r="N28" s="24">
-        <f>IF(L28="Ne pas lancer",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI25&gt;=2,E28&lt;=('08_Moteur'!AI25-1)*'08_Moteur'!O25*1.1),H28+'08_Moteur'!U25,H28),H28)))</f>
+        <f>IF(L28="Ne pas lancer",0,IF(L28="Ouvrir +1 classe",H28+'08_Moteur'!O25*('08_Moteur'!AE25*'08_Moteur'!AF25-('08_Moteur'!R25+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S25)-'08_Moteur'!U25,IF(L28="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI25&gt;=2,E28&lt;=('08_Moteur'!AI25-1)*'08_Moteur'!O25*1.1),H28+'08_Moteur'!U25,H28),H28)))</f>
         <v/>
       </c>
       <c r="O28" s="24">
@@ -4969,7 +4936,7 @@
         <v/>
       </c>
       <c r="N29" s="24">
-        <f>IF(L29="Ne pas lancer",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI26&gt;=2,E29&lt;=('08_Moteur'!AI26-1)*'08_Moteur'!O26*1.1),H29+'08_Moteur'!U26,H29),H29)))</f>
+        <f>IF(L29="Ne pas lancer",0,IF(L29="Ouvrir +1 classe",H29+'08_Moteur'!O26*('08_Moteur'!AE26*'08_Moteur'!AF26-('08_Moteur'!R26+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S26)-'08_Moteur'!U26,IF(L29="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI26&gt;=2,E29&lt;=('08_Moteur'!AI26-1)*'08_Moteur'!O26*1.1),H29+'08_Moteur'!U26,H29),H29)))</f>
         <v/>
       </c>
       <c r="O29" s="24">
@@ -5040,7 +5007,7 @@
         <v/>
       </c>
       <c r="N30" s="24">
-        <f>IF(L30="Ne pas lancer",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI27&gt;=2,E30&lt;=('08_Moteur'!AI27-1)*'08_Moteur'!O27*1.1),H30+'08_Moteur'!U27,H30),H30)))</f>
+        <f>IF(L30="Ne pas lancer",0,IF(L30="Ouvrir +1 classe",H30+'08_Moteur'!O27*('08_Moteur'!AE27*'08_Moteur'!AF27-('08_Moteur'!R27+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S27)-'08_Moteur'!U27,IF(L30="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI27&gt;=2,E30&lt;=('08_Moteur'!AI27-1)*'08_Moteur'!O27*1.1),H30+'08_Moteur'!U27,H30),H30)))</f>
         <v/>
       </c>
       <c r="O30" s="24">
@@ -5111,7 +5078,7 @@
         <v/>
       </c>
       <c r="N31" s="24">
-        <f>IF(L31="Ne pas lancer",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI28&gt;=2,E31&lt;=('08_Moteur'!AI28-1)*'08_Moteur'!O28*1.1),H31+'08_Moteur'!U28,H31),H31)))</f>
+        <f>IF(L31="Ne pas lancer",0,IF(L31="Ouvrir +1 classe",H31+'08_Moteur'!O28*('08_Moteur'!AE28*'08_Moteur'!AF28-('08_Moteur'!R28+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S28)-'08_Moteur'!U28,IF(L31="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI28&gt;=2,E31&lt;=('08_Moteur'!AI28-1)*'08_Moteur'!O28*1.1),H31+'08_Moteur'!U28,H31),H31)))</f>
         <v/>
       </c>
       <c r="O31" s="24">
@@ -5182,7 +5149,7 @@
         <v/>
       </c>
       <c r="N32" s="24">
-        <f>IF(L32="Ne pas lancer",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI29&gt;=2,E32&lt;=('08_Moteur'!AI29-1)*'08_Moteur'!O29*1.1),H32+'08_Moteur'!U29,H32),H32)))</f>
+        <f>IF(L32="Ne pas lancer",0,IF(L32="Ouvrir +1 classe",H32+'08_Moteur'!O29*('08_Moteur'!AE29*'08_Moteur'!AF29-('08_Moteur'!R29+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S29)-'08_Moteur'!U29,IF(L32="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI29&gt;=2,E32&lt;=('08_Moteur'!AI29-1)*'08_Moteur'!O29*1.1),H32+'08_Moteur'!U29,H32),H32)))</f>
         <v/>
       </c>
       <c r="O32" s="24">
@@ -5253,7 +5220,7 @@
         <v/>
       </c>
       <c r="N33" s="24">
-        <f>IF(L33="Ne pas lancer",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI30&gt;=2,E33&lt;=('08_Moteur'!AI30-1)*'08_Moteur'!O30*1.1),H33+'08_Moteur'!U30,H33),H33)))</f>
+        <f>IF(L33="Ne pas lancer",0,IF(L33="Ouvrir +1 classe",H33+'08_Moteur'!O30*('08_Moteur'!AE30*'08_Moteur'!AF30-('08_Moteur'!R30+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S30)-'08_Moteur'!U30,IF(L33="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI30&gt;=2,E33&lt;=('08_Moteur'!AI30-1)*'08_Moteur'!O30*1.1),H33+'08_Moteur'!U30,H33),H33)))</f>
         <v/>
       </c>
       <c r="O33" s="24">
@@ -5324,7 +5291,7 @@
         <v/>
       </c>
       <c r="N34" s="24">
-        <f>IF(L34="Ne pas lancer",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI31&gt;=2,E34&lt;=('08_Moteur'!AI31-1)*'08_Moteur'!O31*1.1),H34+'08_Moteur'!U31,H34),H34)))</f>
+        <f>IF(L34="Ne pas lancer",0,IF(L34="Ouvrir +1 classe",H34+'08_Moteur'!O31*('08_Moteur'!AE31*'08_Moteur'!AF31-('08_Moteur'!R31+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S31)-'08_Moteur'!U31,IF(L34="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI31&gt;=2,E34&lt;=('08_Moteur'!AI31-1)*'08_Moteur'!O31*1.1),H34+'08_Moteur'!U31,H34),H34)))</f>
         <v/>
       </c>
       <c r="O34" s="24">
@@ -5395,7 +5362,7 @@
         <v/>
       </c>
       <c r="N35" s="24">
-        <f>IF(L35="Ne pas lancer",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI32&gt;=2,E35&lt;=('08_Moteur'!AI32-1)*'08_Moteur'!O32*1.1),H35+'08_Moteur'!U32,H35),H35)))</f>
+        <f>IF(L35="Ne pas lancer",0,IF(L35="Ouvrir +1 classe",H35+'08_Moteur'!O32*('08_Moteur'!AE32*'08_Moteur'!AF32-('08_Moteur'!R32+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S32)-'08_Moteur'!U32,IF(L35="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI32&gt;=2,E35&lt;=('08_Moteur'!AI32-1)*'08_Moteur'!O32*1.1),H35+'08_Moteur'!U32,H35),H35)))</f>
         <v/>
       </c>
       <c r="O35" s="24">
@@ -5466,7 +5433,7 @@
         <v/>
       </c>
       <c r="N36" s="24">
-        <f>IF(L36="Ne pas lancer",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI33&gt;=2,E36&lt;=('08_Moteur'!AI33-1)*'08_Moteur'!O33*1.1),H36+'08_Moteur'!U33,H36),H36)))</f>
+        <f>IF(L36="Ne pas lancer",0,IF(L36="Ouvrir +1 classe",H36+'08_Moteur'!O33*('08_Moteur'!AE33*'08_Moteur'!AF33-('08_Moteur'!R33+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S33)-'08_Moteur'!U33,IF(L36="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI33&gt;=2,E36&lt;=('08_Moteur'!AI33-1)*'08_Moteur'!O33*1.1),H36+'08_Moteur'!U33,H36),H36)))</f>
         <v/>
       </c>
       <c r="O36" s="24">
@@ -5537,7 +5504,7 @@
         <v/>
       </c>
       <c r="N37" s="24">
-        <f>IF(L37="Ne pas lancer",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI34&gt;=2,E37&lt;=('08_Moteur'!AI34-1)*'08_Moteur'!O34*1.1),H37+'08_Moteur'!U34,H37),H37)))</f>
+        <f>IF(L37="Ne pas lancer",0,IF(L37="Ouvrir +1 classe",H37+'08_Moteur'!O34*('08_Moteur'!AE34*'08_Moteur'!AF34-('08_Moteur'!R34+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S34)-'08_Moteur'!U34,IF(L37="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI34&gt;=2,E37&lt;=('08_Moteur'!AI34-1)*'08_Moteur'!O34*1.1),H37+'08_Moteur'!U34,H37),H37)))</f>
         <v/>
       </c>
       <c r="O37" s="24">
@@ -5608,7 +5575,7 @@
         <v/>
       </c>
       <c r="N38" s="24">
-        <f>IF(L38="Ne pas lancer",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI35&gt;=2,E38&lt;=('08_Moteur'!AI35-1)*'08_Moteur'!O35*1.1),H38+'08_Moteur'!U35,H38),H38)))</f>
+        <f>IF(L38="Ne pas lancer",0,IF(L38="Ouvrir +1 classe",H38+'08_Moteur'!O35*('08_Moteur'!AE35*'08_Moteur'!AF35-('08_Moteur'!R35+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S35)-'08_Moteur'!U35,IF(L38="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI35&gt;=2,E38&lt;=('08_Moteur'!AI35-1)*'08_Moteur'!O35*1.1),H38+'08_Moteur'!U35,H38),H38)))</f>
         <v/>
       </c>
       <c r="O38" s="24">
@@ -5679,7 +5646,7 @@
         <v/>
       </c>
       <c r="N39" s="24">
-        <f>IF(L39="Ne pas lancer",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI36&gt;=2,E39&lt;=('08_Moteur'!AI36-1)*'08_Moteur'!O36*1.1),H39+'08_Moteur'!U36,H39),H39)))</f>
+        <f>IF(L39="Ne pas lancer",0,IF(L39="Ouvrir +1 classe",H39+'08_Moteur'!O36*('08_Moteur'!AE36*'08_Moteur'!AF36-('08_Moteur'!R36+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S36)-'08_Moteur'!U36,IF(L39="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI36&gt;=2,E39&lt;=('08_Moteur'!AI36-1)*'08_Moteur'!O36*1.1),H39+'08_Moteur'!U36,H39),H39)))</f>
         <v/>
       </c>
       <c r="O39" s="24">
@@ -5750,7 +5717,7 @@
         <v/>
       </c>
       <c r="N40" s="24">
-        <f>IF(L40="Ne pas lancer",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI37&gt;=2,E40&lt;=('08_Moteur'!AI37-1)*'08_Moteur'!O37*1.1),H40+'08_Moteur'!U37,H40),H40)))</f>
+        <f>IF(L40="Ne pas lancer",0,IF(L40="Ouvrir +1 classe",H40+'08_Moteur'!O37*('08_Moteur'!AE37*'08_Moteur'!AF37-('08_Moteur'!R37+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S37)-'08_Moteur'!U37,IF(L40="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI37&gt;=2,E40&lt;=('08_Moteur'!AI37-1)*'08_Moteur'!O37*1.1),H40+'08_Moteur'!U37,H40),H40)))</f>
         <v/>
       </c>
       <c r="O40" s="24">
@@ -5821,7 +5788,7 @@
         <v/>
       </c>
       <c r="N41" s="24">
-        <f>IF(L41="Ne pas lancer",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI38&gt;=2,E41&lt;=('08_Moteur'!AI38-1)*'08_Moteur'!O38*1.1),H41+'08_Moteur'!U38,H41),H41)))</f>
+        <f>IF(L41="Ne pas lancer",0,IF(L41="Ouvrir +1 classe",H41+'08_Moteur'!O38*('08_Moteur'!AE38*'08_Moteur'!AF38-('08_Moteur'!R38+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S38)-'08_Moteur'!U38,IF(L41="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI38&gt;=2,E41&lt;=('08_Moteur'!AI38-1)*'08_Moteur'!O38*1.1),H41+'08_Moteur'!U38,H41),H41)))</f>
         <v/>
       </c>
       <c r="O41" s="24">
@@ -5892,7 +5859,7 @@
         <v/>
       </c>
       <c r="N42" s="24">
-        <f>IF(L42="Ne pas lancer",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI39&gt;=2,E42&lt;=('08_Moteur'!AI39-1)*'08_Moteur'!O39*1.1),H42+'08_Moteur'!U39,H42),H42)))</f>
+        <f>IF(L42="Ne pas lancer",0,IF(L42="Ouvrir +1 classe",H42+'08_Moteur'!O39*('08_Moteur'!AE39*'08_Moteur'!AF39-('08_Moteur'!R39+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S39)-'08_Moteur'!U39,IF(L42="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI39&gt;=2,E42&lt;=('08_Moteur'!AI39-1)*'08_Moteur'!O39*1.1),H42+'08_Moteur'!U39,H42),H42)))</f>
         <v/>
       </c>
       <c r="O42" s="24">
@@ -5963,7 +5930,7 @@
         <v/>
       </c>
       <c r="N43" s="24">
-        <f>IF(L43="Ne pas lancer",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI40&gt;=2,E43&lt;=('08_Moteur'!AI40-1)*'08_Moteur'!O40*1.1),H43+'08_Moteur'!U40,H43),H43)))</f>
+        <f>IF(L43="Ne pas lancer",0,IF(L43="Ouvrir +1 classe",H43+'08_Moteur'!O40*('08_Moteur'!AE40*'08_Moteur'!AF40-('08_Moteur'!R40+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S40)-'08_Moteur'!U40,IF(L43="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI40&gt;=2,E43&lt;=('08_Moteur'!AI40-1)*'08_Moteur'!O40*1.1),H43+'08_Moteur'!U40,H43),H43)))</f>
         <v/>
       </c>
       <c r="O43" s="24">
@@ -6034,7 +6001,7 @@
         <v/>
       </c>
       <c r="N44" s="24">
-        <f>IF(L44="Ne pas lancer",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI41&gt;=2,E44&lt;=('08_Moteur'!AI41-1)*'08_Moteur'!O41*1.1),H44+'08_Moteur'!U41,H44),H44)))</f>
+        <f>IF(L44="Ne pas lancer",0,IF(L44="Ouvrir +1 classe",H44+'08_Moteur'!O41*('08_Moteur'!AE41*'08_Moteur'!AF41-('08_Moteur'!R41+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S41)-'08_Moteur'!U41,IF(L44="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI41&gt;=2,E44&lt;=('08_Moteur'!AI41-1)*'08_Moteur'!O41*1.1),H44+'08_Moteur'!U41,H44),H44)))</f>
         <v/>
       </c>
       <c r="O44" s="24">
@@ -6105,7 +6072,7 @@
         <v/>
       </c>
       <c r="N45" s="24">
-        <f>IF(L45="Ne pas lancer",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI42&gt;=2,E45&lt;=('08_Moteur'!AI42-1)*'08_Moteur'!O42*1.1),H45+'08_Moteur'!U42,H45),H45)))</f>
+        <f>IF(L45="Ne pas lancer",0,IF(L45="Ouvrir +1 classe",H45+'08_Moteur'!O42*('08_Moteur'!AE42*'08_Moteur'!AF42-('08_Moteur'!R42+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S42)-'08_Moteur'!U42,IF(L45="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI42&gt;=2,E45&lt;=('08_Moteur'!AI42-1)*'08_Moteur'!O42*1.1),H45+'08_Moteur'!U42,H45),H45)))</f>
         <v/>
       </c>
       <c r="O45" s="24">
@@ -6176,7 +6143,7 @@
         <v/>
       </c>
       <c r="N46" s="24">
-        <f>IF(L46="Ne pas lancer",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI43&gt;=2,E46&lt;=('08_Moteur'!AI43-1)*'08_Moteur'!O43*1.1),H46+'08_Moteur'!U43,H46),H46)))</f>
+        <f>IF(L46="Ne pas lancer",0,IF(L46="Ouvrir +1 classe",H46+'08_Moteur'!O43*('08_Moteur'!AE43*'08_Moteur'!AF43-('08_Moteur'!R43+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S43)-'08_Moteur'!U43,IF(L46="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI43&gt;=2,E46&lt;=('08_Moteur'!AI43-1)*'08_Moteur'!O43*1.1),H46+'08_Moteur'!U43,H46),H46)))</f>
         <v/>
       </c>
       <c r="O46" s="24">
@@ -6247,7 +6214,7 @@
         <v/>
       </c>
       <c r="N47" s="24">
-        <f>IF(L47="Ne pas lancer",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI44&gt;=2,E47&lt;=('08_Moteur'!AI44-1)*'08_Moteur'!O44*1.1),H47+'08_Moteur'!U44,H47),H47)))</f>
+        <f>IF(L47="Ne pas lancer",0,IF(L47="Ouvrir +1 classe",H47+'08_Moteur'!O44*('08_Moteur'!AE44*'08_Moteur'!AF44-('08_Moteur'!R44+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S44)-'08_Moteur'!U44,IF(L47="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI44&gt;=2,E47&lt;=('08_Moteur'!AI44-1)*'08_Moteur'!O44*1.1),H47+'08_Moteur'!U44,H47),H47)))</f>
         <v/>
       </c>
       <c r="O47" s="24">
@@ -6318,7 +6285,7 @@
         <v/>
       </c>
       <c r="N48" s="24">
-        <f>IF(L48="Ne pas lancer",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI45&gt;=2,E48&lt;=('08_Moteur'!AI45-1)*'08_Moteur'!O45*1.1),H48+'08_Moteur'!U45,H48),H48)))</f>
+        <f>IF(L48="Ne pas lancer",0,IF(L48="Ouvrir +1 classe",H48+'08_Moteur'!O45*('08_Moteur'!AE45*'08_Moteur'!AF45-('08_Moteur'!R45+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S45)-'08_Moteur'!U45,IF(L48="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI45&gt;=2,E48&lt;=('08_Moteur'!AI45-1)*'08_Moteur'!O45*1.1),H48+'08_Moteur'!U45,H48),H48)))</f>
         <v/>
       </c>
       <c r="O48" s="24">
@@ -6389,7 +6356,7 @@
         <v/>
       </c>
       <c r="N49" s="24">
-        <f>IF(L49="Ne pas lancer",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI46&gt;=2,E49&lt;=('08_Moteur'!AI46-1)*'08_Moteur'!O46*1.1),H49+'08_Moteur'!U46,H49),H49)))</f>
+        <f>IF(L49="Ne pas lancer",0,IF(L49="Ouvrir +1 classe",H49+'08_Moteur'!O46*('08_Moteur'!AE46*'08_Moteur'!AF46-('08_Moteur'!R46+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S46)-'08_Moteur'!U46,IF(L49="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI46&gt;=2,E49&lt;=('08_Moteur'!AI46-1)*'08_Moteur'!O46*1.1),H49+'08_Moteur'!U46,H49),H49)))</f>
         <v/>
       </c>
       <c r="O49" s="24">
@@ -6460,7 +6427,7 @@
         <v/>
       </c>
       <c r="N50" s="24">
-        <f>IF(L50="Ne pas lancer",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI47&gt;=2,E50&lt;=('08_Moteur'!AI47-1)*'08_Moteur'!O47*1.1),H50+'08_Moteur'!U47,H50),H50)))</f>
+        <f>IF(L50="Ne pas lancer",0,IF(L50="Ouvrir +1 classe",H50+'08_Moteur'!O47*('08_Moteur'!AE47*'08_Moteur'!AF47-('08_Moteur'!R47+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S47)-'08_Moteur'!U47,IF(L50="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI47&gt;=2,E50&lt;=('08_Moteur'!AI47-1)*'08_Moteur'!O47*1.1),H50+'08_Moteur'!U47,H50),H50)))</f>
         <v/>
       </c>
       <c r="O50" s="24">
@@ -6531,7 +6498,7 @@
         <v/>
       </c>
       <c r="N51" s="24">
-        <f>IF(L51="Ne pas lancer",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI48&gt;=2,E51&lt;=('08_Moteur'!AI48-1)*'08_Moteur'!O48*1.1),H51+'08_Moteur'!U48,H51),H51)))</f>
+        <f>IF(L51="Ne pas lancer",0,IF(L51="Ouvrir +1 classe",H51+'08_Moteur'!O48*('08_Moteur'!AE48*'08_Moteur'!AF48-('08_Moteur'!R48+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S48)-'08_Moteur'!U48,IF(L51="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI48&gt;=2,E51&lt;=('08_Moteur'!AI48-1)*'08_Moteur'!O48*1.1),H51+'08_Moteur'!U48,H51),H51)))</f>
         <v/>
       </c>
       <c r="O51" s="24">
@@ -6602,7 +6569,7 @@
         <v/>
       </c>
       <c r="N52" s="24">
-        <f>IF(L52="Ne pas lancer",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI49&gt;=2,E52&lt;=('08_Moteur'!AI49-1)*'08_Moteur'!O49*1.1),H52+'08_Moteur'!U49,H52),H52)))</f>
+        <f>IF(L52="Ne pas lancer",0,IF(L52="Ouvrir +1 classe",H52+'08_Moteur'!O49*('08_Moteur'!AE49*'08_Moteur'!AF49-('08_Moteur'!R49+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S49)-'08_Moteur'!U49,IF(L52="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI49&gt;=2,E52&lt;=('08_Moteur'!AI49-1)*'08_Moteur'!O49*1.1),H52+'08_Moteur'!U49,H52),H52)))</f>
         <v/>
       </c>
       <c r="O52" s="24">
@@ -6673,7 +6640,7 @@
         <v/>
       </c>
       <c r="N53" s="24">
-        <f>IF(L53="Ne pas lancer",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI50&gt;=2,E53&lt;=('08_Moteur'!AI50-1)*'08_Moteur'!O50*1.1),H53+'08_Moteur'!U50,H53),H53)))</f>
+        <f>IF(L53="Ne pas lancer",0,IF(L53="Ouvrir +1 classe",H53+'08_Moteur'!O50*('08_Moteur'!AE50*'08_Moteur'!AF50-('08_Moteur'!R50+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S50)-'08_Moteur'!U50,IF(L53="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI50&gt;=2,E53&lt;=('08_Moteur'!AI50-1)*'08_Moteur'!O50*1.1),H53+'08_Moteur'!U50,H53),H53)))</f>
         <v/>
       </c>
       <c r="O53" s="24">
@@ -6744,7 +6711,7 @@
         <v/>
       </c>
       <c r="N54" s="24">
-        <f>IF(L54="Ne pas lancer",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI51&gt;=2,E54&lt;=('08_Moteur'!AI51-1)*'08_Moteur'!O51*1.1),H54+'08_Moteur'!U51,H54),H54)))</f>
+        <f>IF(L54="Ne pas lancer",0,IF(L54="Ouvrir +1 classe",H54+'08_Moteur'!O51*('08_Moteur'!AE51*'08_Moteur'!AF51-('08_Moteur'!R51+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S51)-'08_Moteur'!U51,IF(L54="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI51&gt;=2,E54&lt;=('08_Moteur'!AI51-1)*'08_Moteur'!O51*1.1),H54+'08_Moteur'!U51,H54),H54)))</f>
         <v/>
       </c>
       <c r="O54" s="24">
@@ -6815,7 +6782,7 @@
         <v/>
       </c>
       <c r="N55" s="24">
-        <f>IF(L55="Ne pas lancer",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI52&gt;=2,E55&lt;=('08_Moteur'!AI52-1)*'08_Moteur'!O52*1.1),H55+'08_Moteur'!U52,H55),H55)))</f>
+        <f>IF(L55="Ne pas lancer",0,IF(L55="Ouvrir +1 classe",H55+'08_Moteur'!O52*('08_Moteur'!AE52*'08_Moteur'!AF52-('08_Moteur'!R52+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S52)-'08_Moteur'!U52,IF(L55="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI52&gt;=2,E55&lt;=('08_Moteur'!AI52-1)*'08_Moteur'!O52*1.1),H55+'08_Moteur'!U52,H55),H55)))</f>
         <v/>
       </c>
       <c r="O55" s="24">
@@ -6886,7 +6853,7 @@
         <v/>
       </c>
       <c r="N56" s="24">
-        <f>IF(L56="Ne pas lancer",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI53&gt;=2,E56&lt;=('08_Moteur'!AI53-1)*'08_Moteur'!O53*1.1),H56+'08_Moteur'!U53,H56),H56)))</f>
+        <f>IF(L56="Ne pas lancer",0,IF(L56="Ouvrir +1 classe",H56+'08_Moteur'!O53*('08_Moteur'!AE53*'08_Moteur'!AF53-('08_Moteur'!R53+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S53)-'08_Moteur'!U53,IF(L56="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI53&gt;=2,E56&lt;=('08_Moteur'!AI53-1)*'08_Moteur'!O53*1.1),H56+'08_Moteur'!U53,H56),H56)))</f>
         <v/>
       </c>
       <c r="O56" s="24">
@@ -6957,7 +6924,7 @@
         <v/>
       </c>
       <c r="N57" s="24">
-        <f>IF(L57="Ne pas lancer",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI54&gt;=2,E57&lt;=('08_Moteur'!AI54-1)*'08_Moteur'!O54*1.1),H57+'08_Moteur'!U54,H57),H57)))</f>
+        <f>IF(L57="Ne pas lancer",0,IF(L57="Ouvrir +1 classe",H57+'08_Moteur'!O54*('08_Moteur'!AE54*'08_Moteur'!AF54-('08_Moteur'!R54+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S54)-'08_Moteur'!U54,IF(L57="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI54&gt;=2,E57&lt;=('08_Moteur'!AI54-1)*'08_Moteur'!O54*1.1),H57+'08_Moteur'!U54,H57),H57)))</f>
         <v/>
       </c>
       <c r="O57" s="24">
@@ -7028,7 +6995,7 @@
         <v/>
       </c>
       <c r="N58" s="24">
-        <f>IF(L58="Ne pas lancer",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI55&gt;=2,E58&lt;=('08_Moteur'!AI55-1)*'08_Moteur'!O55*1.1),H58+'08_Moteur'!U55,H58),H58)))</f>
+        <f>IF(L58="Ne pas lancer",0,IF(L58="Ouvrir +1 classe",H58+'08_Moteur'!O55*('08_Moteur'!AE55*'08_Moteur'!AF55-('08_Moteur'!R55+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S55)-'08_Moteur'!U55,IF(L58="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI55&gt;=2,E58&lt;=('08_Moteur'!AI55-1)*'08_Moteur'!O55*1.1),H58+'08_Moteur'!U55,H58),H58)))</f>
         <v/>
       </c>
       <c r="O58" s="24">
@@ -7099,7 +7066,7 @@
         <v/>
       </c>
       <c r="N59" s="24">
-        <f>IF(L59="Ne pas lancer",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI56&gt;=2,E59&lt;=('08_Moteur'!AI56-1)*'08_Moteur'!O56*1.1),H59+'08_Moteur'!U56,H59),H59)))</f>
+        <f>IF(L59="Ne pas lancer",0,IF(L59="Ouvrir +1 classe",H59+'08_Moteur'!O56*('08_Moteur'!AE56*'08_Moteur'!AF56-('08_Moteur'!R56+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S56)-'08_Moteur'!U56,IF(L59="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI56&gt;=2,E59&lt;=('08_Moteur'!AI56-1)*'08_Moteur'!O56*1.1),H59+'08_Moteur'!U56,H59),H59)))</f>
         <v/>
       </c>
       <c r="O59" s="24">
@@ -7170,7 +7137,7 @@
         <v/>
       </c>
       <c r="N60" s="24">
-        <f>IF(L60="Ne pas lancer",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI57&gt;=2,E60&lt;=('08_Moteur'!AI57-1)*'08_Moteur'!O57*1.1),H60+'08_Moteur'!U57,H60),H60)))</f>
+        <f>IF(L60="Ne pas lancer",0,IF(L60="Ouvrir +1 classe",H60+'08_Moteur'!O57*('08_Moteur'!AE57*'08_Moteur'!AF57-('08_Moteur'!R57+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S57)-'08_Moteur'!U57,IF(L60="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI57&gt;=2,E60&lt;=('08_Moteur'!AI57-1)*'08_Moteur'!O57*1.1),H60+'08_Moteur'!U57,H60),H60)))</f>
         <v/>
       </c>
       <c r="O60" s="24">
@@ -7241,7 +7208,7 @@
         <v/>
       </c>
       <c r="N61" s="24">
-        <f>IF(L61="Ne pas lancer",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI58&gt;=2,E61&lt;=('08_Moteur'!AI58-1)*'08_Moteur'!O58*1.1),H61+'08_Moteur'!U58,H61),H61)))</f>
+        <f>IF(L61="Ne pas lancer",0,IF(L61="Ouvrir +1 classe",H61+'08_Moteur'!O58*('08_Moteur'!AE58*'08_Moteur'!AF58-('08_Moteur'!R58+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S58)-'08_Moteur'!U58,IF(L61="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI58&gt;=2,E61&lt;=('08_Moteur'!AI58-1)*'08_Moteur'!O58*1.1),H61+'08_Moteur'!U58,H61),H61)))</f>
         <v/>
       </c>
       <c r="O61" s="24">
@@ -7312,7 +7279,7 @@
         <v/>
       </c>
       <c r="N62" s="24">
-        <f>IF(L62="Ne pas lancer",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI59&gt;=2,E62&lt;=('08_Moteur'!AI59-1)*'08_Moteur'!O59*1.1),H62+'08_Moteur'!U59,H62),H62)))</f>
+        <f>IF(L62="Ne pas lancer",0,IF(L62="Ouvrir +1 classe",H62+'08_Moteur'!O59*('08_Moteur'!AE59*'08_Moteur'!AF59-('08_Moteur'!R59+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S59)-'08_Moteur'!U59,IF(L62="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI59&gt;=2,E62&lt;=('08_Moteur'!AI59-1)*'08_Moteur'!O59*1.1),H62+'08_Moteur'!U59,H62),H62)))</f>
         <v/>
       </c>
       <c r="O62" s="24">
@@ -7383,7 +7350,7 @@
         <v/>
       </c>
       <c r="N63" s="24">
-        <f>IF(L63="Ne pas lancer",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'01_Cadrage'!$H$27)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI60&gt;=2,E63&lt;=('08_Moteur'!AI60-1)*'08_Moteur'!O60*1.1),H63+'08_Moteur'!U60,H63),H63)))</f>
+        <f>IF(L63="Ne pas lancer",0,IF(L63="Ouvrir +1 classe",H63+'08_Moteur'!O60*('08_Moteur'!AE60*'08_Moteur'!AF60-('08_Moteur'!R60+'01_Cadrage'!$H$26)*(1+'01_Cadrage'!$H$20)-'08_Moteur'!S60)-'08_Moteur'!U60,IF(L63="Regrouper (-1 classe)",IF(AND('08_Moteur'!AI60&gt;=2,E63&lt;=('08_Moteur'!AI60-1)*'08_Moteur'!O60*1.1),H63+'08_Moteur'!U60,H63),H63)))</f>
         <v/>
       </c>
       <c r="O63" s="24">
@@ -9415,7 +9382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS11"/>
+  <dimension ref="A1:AS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9475,65 +9442,37 @@
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>+1 point de sécurisation (≤3 mois)</t>
+          <t>+1 % de budget marketing</t>
         </is>
       </c>
       <c r="C7" s="24">
-        <f>0.01*SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'01_Cadrage'!$H$26)</f>
+        <f>0.01*'01_Cadrage'!$H$27*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
         <v/>
       </c>
       <c r="D7" s="75" t="inlineStr">
         <is>
-          <t>Nul si recouvrement=100 % ; sinon réduit la perte.</t>
+          <t>Plus de leads → plus d'inscrits, net du coût.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>+1 % de budget marketing</t>
+          <t>+1 point de taux de passage</t>
         </is>
       </c>
       <c r="C8" s="24">
-        <f>0.01*'01_Cadrage'!$H$29*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$AM$3:$AM$60)-0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=1)*'08_Moteur'!$H$3:$H$60*'08_Moteur'!$S$3:$S$60*(1+'08_Moteur'!$Y$3:$Y$60))</f>
+        <f>0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=0)*'08_Moteur'!$K$3:$K$60)*IFERROR(SUM('08_Moteur'!$AM$3:$AM$60)/SUM('08_Moteur'!$AD$3:$AD$60),0)</f>
         <v/>
       </c>
       <c r="D8" s="75" t="inlineStr">
         <is>
-          <t>Plus de leads → plus d'inscrits, net du coût.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>+1 point de taux de passage</t>
-        </is>
-      </c>
-      <c r="C9" s="24">
-        <f>0.01*SUMPRODUCT(('08_Moteur'!$F$3:$F$60=0)*'08_Moteur'!$K$3:$K$60)*IFERROR(SUM('08_Moteur'!$AM$3:$AM$60)/SUM('08_Moteur'!$AD$3:$AD$60),0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="75" t="inlineStr">
-        <is>
           <t>Rétention : + d'étudiants qui poursuivent.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Exposition financement alternance (€ à sécuriser) :</t>
-        </is>
-      </c>
-      <c r="D11" s="79">
-        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'01_Cadrage'!$H$28)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B11:C11"/>
+  <mergeCells count="2">
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
@@ -9548,7 +9487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS15"/>
+  <dimension ref="A1:AS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9748,44 +9687,6 @@
       </c>
       <c r="E13" s="56">
         <f>C13-D13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Taux de sécurisation</t>
-        </is>
-      </c>
-      <c r="C14" s="56">
-        <f>'01_Cadrage'!$H$28</f>
-        <v/>
-      </c>
-      <c r="D14" s="56">
-        <f>'01_Cadrage'!$H$28</f>
-        <v/>
-      </c>
-      <c r="E14" s="56">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="80" t="inlineStr">
-        <is>
-          <t>€ à sécuriser (exposition)</t>
-        </is>
-      </c>
-      <c r="C15" s="81">
-        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$AD$3:$AD$60*'08_Moteur'!$AE$3:$AE$60)*(1-'01_Cadrage'!$H$28)</f>
-        <v/>
-      </c>
-      <c r="D15" s="81">
-        <f>SUMPRODUCT(('08_Moteur'!$E$3:$E$60="ALT")*'08_Moteur'!$G$3:$G$60*'08_Moteur'!$L$3:$L$60)*(1-'01_Cadrage'!$H$28)</f>
-        <v/>
-      </c>
-      <c r="E15" s="82">
-        <f>IFERROR(C15/D15-1,0)</f>
         <v/>
       </c>
     </row>
@@ -9804,7 +9705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS14"/>
+  <dimension ref="A1:AS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9848,7 +9749,7 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>Marque / Campus</t>
         </is>
@@ -9865,7 +9766,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>Programme × Année × Modalité</t>
         </is>
@@ -9882,7 +9783,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>Params (capacité, heures…)</t>
         </is>
@@ -9899,7 +9800,7 @@
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>Historique N-2/N-1</t>
         </is>
@@ -9916,7 +9817,7 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>Cohortes / taux de passage</t>
         </is>
@@ -9933,68 +9834,51 @@
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="83" t="inlineStr">
-        <is>
-          <t>Sécurisation &amp; recouvrement</t>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Objectifs (cadrage)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Comptes techniques</t>
+          <t>Version cible + écart</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Financement alternance, exposition</t>
+          <t>Top-down vs bottom-up</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="83" t="inlineStr">
-        <is>
-          <t>Objectifs (cadrage)</t>
+      <c r="B12" s="79" t="inlineStr">
+        <is>
+          <t>Décisions ouvrir/fermer</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Version cible + écart</t>
+          <t>Scénarios / versions</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Top-down vs bottom-up</t>
+          <t>Simulateur → snapshot</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="B13" s="83" t="inlineStr">
-        <is>
-          <t>Décisions ouvrir/fermer</t>
+      <c r="B13" s="79" t="inlineStr">
+        <is>
+          <t>Allocation structure</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Scénarios / versions</t>
+          <t>Cost allocation (driver)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Simulateur → snapshot</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="B14" s="83" t="inlineStr">
-        <is>
-          <t>Allocation structure</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Cost allocation (driver)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Effectif/CA/m²</t>
         </is>
@@ -10937,63 +10821,63 @@
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Recouvrement reste à charge (employeur)</t>
+          <t>Autres charges d'exploitation / étudiant</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>1</v>
+          <t>€</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="n">
+        <v>934</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="33">
-        <f>INDEX(E26:G26,MATCH($D$3,$E$15:$G$15,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="35">
+        <f>D26*(1+INDEX(E26:G26,MATCH($D$3,$E$15:$G$15,0)))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Autres charges d'exploitation / étudiant</t>
+          <t>Élasticité marketing (défaut)</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>€</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="n">
-        <v>934</v>
-      </c>
-      <c r="E27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="35">
-        <f>D27*(1+INDEX(E27:G27,MATCH($D$3,$E$15:$G$15,0)))</f>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="37">
+        <f>INDEX(E27:G27,MATCH($D$3,$E$15:$G$15,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Sécurisation contrat (défaut, ≤3 mois)</t>
+          <t>Conversion cand.→inscrit (défaut)</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
@@ -11001,76 +10885,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D28" s="36" t="n">
-        <v>0.86</v>
+      <c r="D28" s="38" t="n">
+        <v>0.372</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>0.86</v>
+        <v>0.372</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>0.86</v>
+        <v>0.372</v>
       </c>
       <c r="G28" s="32" t="n">
-        <v>0.86</v>
+        <v>0.372</v>
       </c>
       <c r="H28" s="33">
         <f>INDEX(E28:G28,MATCH($D$3,$E$15:$G$15,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Élasticité marketing (défaut)</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D29" s="37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E29" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F29" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" s="26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H29" s="38">
-        <f>INDEX(E29:G29,MATCH($D$3,$E$15:$G$15,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Conversion cand.→inscrit (défaut)</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="E30" s="32" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="F30" s="32" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="G30" s="32" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="H30" s="33">
-        <f>INDEX(E30:G30,MATCH($D$3,$E$15:$G$15,0))</f>
         <v/>
       </c>
     </row>
@@ -11225,7 +11053,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Une ligne par cellule fine (marque×campus×programme×année×modalité). Charge le réel des sources : 🟦 CRM/admissions · 🟩 compta/scolarité · 🟧 marketing · 🟪 OPCO/alternance · référentiel. Les 2 bases de projection (N-1 réel &amp; atterrissage N) sont chargées côte à côte ; le N-2 donne la profondeur (élasticité).</t>
+          <t>Une ligne par cellule fine (marque×campus×programme×année×modalité). Charge le réel des sources : 🟦 CRM/admissions · 🟩 compta/scolarité · 🟧 marketing · référentiel. Les 2 bases de projection (N-1 réel &amp; atterrissage N) sont chargées côte à côte ; le N-2 donne la profondeur (élasticité).</t>
         </is>
       </c>
     </row>
@@ -11276,22 +11104,16 @@
       <c r="X4" s="4" t="n"/>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>OPCO — Sécurisation alternance</t>
+          <t>RÉFÉRENTIEL — Organisation &amp; coûts unitaires</t>
         </is>
       </c>
       <c r="Z4" s="4" t="n"/>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>RÉFÉRENTIEL — Organisation &amp; coûts unitaires</t>
-        </is>
-      </c>
+      <c r="AA4" s="4" t="n"/>
       <c r="AB4" s="4" t="n"/>
       <c r="AC4" s="4" t="n"/>
       <c r="AD4" s="4" t="n"/>
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
@@ -11416,50 +11238,40 @@
       </c>
       <c r="Y5" s="20" t="inlineStr">
         <is>
-          <t>Sécur. N-1</t>
+          <t>Classes N-1</t>
         </is>
       </c>
       <c r="Z5" s="20" t="inlineStr">
         <is>
-          <t>Sécur. Atterr.</t>
+          <t>Classes Atterr.</t>
         </is>
       </c>
       <c r="AA5" s="20" t="inlineStr">
         <is>
-          <t>Classes N-1</t>
+          <t>Capacité</t>
         </is>
       </c>
       <c r="AB5" s="20" t="inlineStr">
         <is>
-          <t>Classes Atterr.</t>
+          <t>Heures/classe</t>
         </is>
       </c>
       <c r="AC5" s="20" t="inlineStr">
         <is>
-          <t>Capacité</t>
+          <t>Taux horaire</t>
         </is>
       </c>
       <c r="AD5" s="20" t="inlineStr">
         <is>
-          <t>Heures/classe</t>
+          <t>Pédago/étu</t>
         </is>
       </c>
       <c r="AE5" s="20" t="inlineStr">
         <is>
-          <t>Taux horaire</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="AF5" s="20" t="inlineStr">
-        <is>
-          <t>Pédago/étu</t>
-        </is>
-      </c>
-      <c r="AG5" s="20" t="inlineStr">
-        <is>
-          <t>CAC</t>
-        </is>
-      </c>
-      <c r="AH5" s="20" t="inlineStr">
         <is>
           <t>Taux passage</t>
         </is>
@@ -11550,34 +11362,28 @@
       <c r="X6" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y6" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="32" t="n">
-        <v>1</v>
+      <c r="Y6" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="AA6" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB6" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC6" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD6" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE6" s="40" t="n">
+      <c r="AC6" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF6" s="40" t="n">
+      <c r="AD6" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG6" s="39" t="n">
+      <c r="AE6" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH6" s="32" t="n">
+      <c r="AF6" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11666,34 +11472,28 @@
       <c r="X7" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y7" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z7" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y7" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="AA7" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB7" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD7" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE7" s="40" t="n">
+      <c r="AC7" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF7" s="40" t="n">
+      <c r="AD7" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG7" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="32" t="n">
+      <c r="AE7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -11782,34 +11582,28 @@
       <c r="X8" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y8" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z8" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y8" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA8" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB8" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD8" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE8" s="40" t="n">
+      <c r="AC8" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF8" s="40" t="n">
+      <c r="AD8" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG8" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="32" t="n">
+      <c r="AE8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -11898,34 +11692,28 @@
       <c r="X9" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y9" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z9" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y9" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA9" s="39" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AB9" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD9" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE9" s="40" t="n">
+      <c r="AC9" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF9" s="40" t="n">
+      <c r="AD9" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG9" s="39" t="n">
+      <c r="AE9" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH9" s="32" t="n">
+      <c r="AF9" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12014,34 +11802,28 @@
       <c r="X10" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y10" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z10" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y10" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA10" s="39" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AB10" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD10" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE10" s="40" t="n">
+      <c r="AC10" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF10" s="40" t="n">
+      <c r="AD10" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG10" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="32" t="n">
+      <c r="AE10" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -12130,34 +11912,28 @@
       <c r="X11" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y11" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="32" t="n">
-        <v>1</v>
+      <c r="Y11" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="AA11" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB11" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC11" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD11" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE11" s="40" t="n">
+      <c r="AC11" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF11" s="40" t="n">
+      <c r="AD11" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG11" s="39" t="n">
+      <c r="AE11" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH11" s="32" t="n">
+      <c r="AF11" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12246,34 +12022,28 @@
       <c r="X12" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y12" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z12" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y12" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA12" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB12" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD12" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE12" s="40" t="n">
+      <c r="AC12" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF12" s="40" t="n">
+      <c r="AD12" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="32" t="n">
+      <c r="AE12" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -12362,34 +12132,28 @@
       <c r="X13" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y13" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z13" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y13" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA13" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB13" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD13" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE13" s="40" t="n">
+      <c r="AC13" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF13" s="40" t="n">
+      <c r="AD13" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG13" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="32" t="n">
+      <c r="AE13" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -12478,34 +12242,28 @@
       <c r="X14" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y14" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z14" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA14" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB14" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC14" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD14" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE14" s="40" t="n">
+      <c r="AC14" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF14" s="40" t="n">
+      <c r="AD14" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG14" s="39" t="n">
+      <c r="AE14" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH14" s="32" t="n">
+      <c r="AF14" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12594,34 +12352,28 @@
       <c r="X15" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y15" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z15" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA15" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB15" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD15" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE15" s="40" t="n">
+      <c r="AC15" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF15" s="40" t="n">
+      <c r="AD15" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG15" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="32" t="n">
+      <c r="AE15" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -12710,34 +12462,28 @@
       <c r="X16" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y16" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="32" t="n">
-        <v>1</v>
+      <c r="Y16" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA16" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB16" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD16" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE16" s="40" t="n">
+      <c r="AC16" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF16" s="40" t="n">
+      <c r="AD16" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG16" s="39" t="n">
+      <c r="AE16" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH16" s="32" t="n">
+      <c r="AF16" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12826,34 +12572,28 @@
       <c r="X17" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y17" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z17" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y17" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA17" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB17" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD17" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE17" s="40" t="n">
+      <c r="AC17" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF17" s="40" t="n">
+      <c r="AD17" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG17" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="32" t="n">
+      <c r="AE17" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -12942,34 +12682,28 @@
       <c r="X18" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y18" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z18" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y18" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA18" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB18" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC18" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD18" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE18" s="40" t="n">
+      <c r="AC18" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF18" s="40" t="n">
+      <c r="AD18" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG18" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="32" t="n">
+      <c r="AE18" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -13058,34 +12792,28 @@
       <c r="X19" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y19" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z19" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y19" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA19" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB19" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC19" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD19" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE19" s="40" t="n">
+      <c r="AC19" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF19" s="40" t="n">
+      <c r="AD19" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG19" s="39" t="n">
+      <c r="AE19" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH19" s="32" t="n">
+      <c r="AF19" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13174,34 +12902,28 @@
       <c r="X20" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y20" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z20" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y20" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA20" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB20" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC20" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD20" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE20" s="40" t="n">
+      <c r="AC20" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF20" s="40" t="n">
+      <c r="AD20" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG20" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="32" t="n">
+      <c r="AE20" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -13290,34 +13012,28 @@
       <c r="X21" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y21" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="32" t="n">
-        <v>1</v>
+      <c r="Y21" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA21" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB21" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD21" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE21" s="40" t="n">
+      <c r="AC21" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF21" s="40" t="n">
+      <c r="AD21" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG21" s="39" t="n">
+      <c r="AE21" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH21" s="32" t="n">
+      <c r="AF21" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13406,34 +13122,28 @@
       <c r="X22" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y22" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z22" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA22" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB22" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC22" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD22" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE22" s="40" t="n">
+      <c r="AC22" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF22" s="40" t="n">
+      <c r="AD22" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG22" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="32" t="n">
+      <c r="AE22" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -13522,34 +13232,28 @@
       <c r="X23" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y23" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z23" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y23" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA23" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB23" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC23" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD23" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE23" s="40" t="n">
+      <c r="AC23" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF23" s="40" t="n">
+      <c r="AD23" s="40" t="n">
         <v>400</v>
       </c>
-      <c r="AG23" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="32" t="n">
+      <c r="AE23" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -13638,34 +13342,28 @@
       <c r="X24" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y24" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z24" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y24" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA24" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB24" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD24" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE24" s="40" t="n">
+      <c r="AC24" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF24" s="40" t="n">
+      <c r="AD24" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG24" s="39" t="n">
+      <c r="AE24" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH24" s="32" t="n">
+      <c r="AF24" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13754,34 +13452,28 @@
       <c r="X25" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y25" s="32" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Z25" s="32" t="n">
-        <v>0.88</v>
+      <c r="Y25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA25" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB25" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC25" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD25" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE25" s="40" t="n">
+      <c r="AC25" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="AF25" s="40" t="n">
+      <c r="AD25" s="40" t="n">
         <v>520</v>
       </c>
-      <c r="AG25" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="32" t="n">
+      <c r="AE25" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -13870,34 +13562,28 @@
       <c r="X26" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y26" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="32" t="n">
-        <v>1</v>
+      <c r="Y26" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z26" s="39" t="n">
+        <v>3</v>
       </c>
       <c r="AA26" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB26" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC26" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD26" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE26" s="40" t="n">
+      <c r="AC26" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF26" s="40" t="n">
+      <c r="AD26" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG26" s="39" t="n">
+      <c r="AE26" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH26" s="32" t="n">
+      <c r="AF26" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13986,34 +13672,28 @@
       <c r="X27" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y27" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z27" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y27" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA27" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB27" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD27" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE27" s="40" t="n">
+      <c r="AC27" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF27" s="40" t="n">
+      <c r="AD27" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG27" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="32" t="n">
+      <c r="AE27" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -14102,34 +13782,28 @@
       <c r="X28" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y28" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z28" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y28" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA28" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB28" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC28" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD28" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE28" s="40" t="n">
+      <c r="AC28" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF28" s="40" t="n">
+      <c r="AD28" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG28" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="32" t="n">
+      <c r="AE28" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -14218,34 +13892,28 @@
       <c r="X29" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y29" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z29" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y29" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA29" s="39" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AB29" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD29" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE29" s="40" t="n">
+      <c r="AC29" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="AF29" s="40" t="n">
+      <c r="AD29" s="40" t="n">
         <v>670</v>
       </c>
-      <c r="AG29" s="39" t="n">
+      <c r="AE29" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH29" s="32" t="n">
+      <c r="AF29" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14334,34 +14002,28 @@
       <c r="X30" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y30" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z30" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y30" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA30" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB30" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC30" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD30" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE30" s="40" t="n">
+      <c r="AC30" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="AF30" s="40" t="n">
+      <c r="AD30" s="40" t="n">
         <v>670</v>
       </c>
-      <c r="AG30" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" s="32" t="n">
+      <c r="AE30" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -14450,34 +14112,28 @@
       <c r="X31" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y31" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="32" t="n">
-        <v>1</v>
+      <c r="Y31" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z31" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA31" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB31" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC31" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD31" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE31" s="40" t="n">
+      <c r="AC31" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF31" s="40" t="n">
+      <c r="AD31" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG31" s="39" t="n">
+      <c r="AE31" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH31" s="32" t="n">
+      <c r="AF31" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14566,34 +14222,28 @@
       <c r="X32" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y32" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z32" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y32" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA32" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB32" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD32" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE32" s="40" t="n">
+      <c r="AC32" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF32" s="40" t="n">
+      <c r="AD32" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG32" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="32" t="n">
+      <c r="AE32" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -14682,34 +14332,28 @@
       <c r="X33" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y33" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z33" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y33" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA33" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB33" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC33" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD33" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE33" s="40" t="n">
+      <c r="AC33" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF33" s="40" t="n">
+      <c r="AD33" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG33" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="32" t="n">
+      <c r="AE33" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -14798,34 +14442,28 @@
       <c r="X34" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y34" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z34" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y34" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA34" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB34" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC34" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD34" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE34" s="40" t="n">
+      <c r="AC34" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="AF34" s="40" t="n">
+      <c r="AD34" s="40" t="n">
         <v>670</v>
       </c>
-      <c r="AG34" s="39" t="n">
+      <c r="AE34" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH34" s="32" t="n">
+      <c r="AF34" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14914,34 +14552,28 @@
       <c r="X35" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y35" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z35" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y35" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA35" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB35" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC35" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD35" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE35" s="40" t="n">
+      <c r="AC35" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="AF35" s="40" t="n">
+      <c r="AD35" s="40" t="n">
         <v>670</v>
       </c>
-      <c r="AG35" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="32" t="n">
+      <c r="AE35" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -15030,34 +14662,28 @@
       <c r="X36" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="Y36" s="32" t="n">
+      <c r="Y36" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" s="32" t="n">
-        <v>1</v>
+      <c r="Z36" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA36" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB36" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC36" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD36" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE36" s="40" t="n">
+      <c r="AC36" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF36" s="40" t="n">
+      <c r="AD36" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG36" s="39" t="n">
+      <c r="AE36" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH36" s="32" t="n">
+      <c r="AF36" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15146,34 +14772,28 @@
       <c r="X37" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y37" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z37" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y37" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA37" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB37" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC37" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD37" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE37" s="40" t="n">
+      <c r="AC37" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF37" s="40" t="n">
+      <c r="AD37" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG37" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="32" t="n">
+      <c r="AE37" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -15262,34 +14882,28 @@
       <c r="X38" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y38" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z38" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y38" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA38" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB38" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC38" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD38" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE38" s="40" t="n">
+      <c r="AC38" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="AF38" s="40" t="n">
+      <c r="AD38" s="40" t="n">
         <v>550</v>
       </c>
-      <c r="AG38" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="32" t="n">
+      <c r="AE38" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -15378,34 +14992,28 @@
       <c r="X39" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y39" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z39" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y39" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA39" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB39" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC39" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD39" s="39" t="n">
         <v>480</v>
       </c>
-      <c r="AE39" s="40" t="n">
+      <c r="AC39" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="AF39" s="40" t="n">
+      <c r="AD39" s="40" t="n">
         <v>670</v>
       </c>
-      <c r="AG39" s="39" t="n">
+      <c r="AE39" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AH39" s="32" t="n">
+      <c r="AF39" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15494,34 +15102,28 @@
       <c r="X40" s="40" t="n">
         <v>9000</v>
       </c>
-      <c r="Y40" s="32" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Z40" s="32" t="n">
-        <v>0.85</v>
+      <c r="Y40" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="AB40" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD40" s="39" t="n">
         <v>440</v>
       </c>
-      <c r="AE40" s="40" t="n">
+      <c r="AC40" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="AF40" s="40" t="n">
+      <c r="AD40" s="40" t="n">
         <v>670</v>
       </c>
-      <c r="AG40" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="32" t="n">
+      <c r="AE40" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="32" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -15610,34 +15212,28 @@
       <c r="X41" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y41" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z41" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y41" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA41" s="39" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AB41" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC41" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD41" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE41" s="40" t="n">
+      <c r="AC41" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF41" s="40" t="n">
+      <c r="AD41" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG41" s="39" t="n">
+      <c r="AE41" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH41" s="32" t="n">
+      <c r="AF41" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15726,34 +15322,28 @@
       <c r="X42" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y42" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z42" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y42" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA42" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB42" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC42" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD42" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE42" s="40" t="n">
+      <c r="AC42" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF42" s="40" t="n">
+      <c r="AD42" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG42" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="32" t="n">
+      <c r="AE42" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -15842,34 +15432,28 @@
       <c r="X43" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y43" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z43" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y43" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA43" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB43" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC43" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD43" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE43" s="40" t="n">
+      <c r="AC43" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF43" s="40" t="n">
+      <c r="AD43" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG43" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="32" t="n">
+      <c r="AE43" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -15958,34 +15542,28 @@
       <c r="X44" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y44" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z44" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y44" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA44" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB44" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC44" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD44" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE44" s="40" t="n">
+      <c r="AC44" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF44" s="40" t="n">
+      <c r="AD44" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG44" s="39" t="n">
+      <c r="AE44" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH44" s="32" t="n">
+      <c r="AF44" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16074,34 +15652,28 @@
       <c r="X45" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y45" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z45" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y45" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA45" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB45" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC45" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD45" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE45" s="40" t="n">
+      <c r="AC45" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF45" s="40" t="n">
+      <c r="AD45" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG45" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="32" t="n">
+      <c r="AE45" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -16190,34 +15762,28 @@
       <c r="X46" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y46" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z46" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y46" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB46" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD46" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE46" s="40" t="n">
+      <c r="AC46" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF46" s="40" t="n">
+      <c r="AD46" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG46" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="32" t="n">
+      <c r="AE46" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -16306,34 +15872,28 @@
       <c r="X47" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y47" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z47" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y47" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA47" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB47" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC47" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD47" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE47" s="40" t="n">
+      <c r="AC47" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF47" s="40" t="n">
+      <c r="AD47" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG47" s="39" t="n">
+      <c r="AE47" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH47" s="32" t="n">
+      <c r="AF47" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16422,34 +15982,28 @@
       <c r="X48" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y48" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z48" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y48" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA48" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB48" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC48" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD48" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE48" s="40" t="n">
+      <c r="AC48" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF48" s="40" t="n">
+      <c r="AD48" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG48" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="32" t="n">
+      <c r="AE48" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -16538,34 +16092,28 @@
       <c r="X49" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y49" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z49" s="32" t="n">
-        <v>0.87</v>
+      <c r="Y49" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB49" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD49" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE49" s="40" t="n">
+      <c r="AC49" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF49" s="40" t="n">
+      <c r="AD49" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG49" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="32" t="n">
+      <c r="AE49" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -16654,34 +16202,28 @@
       <c r="X50" s="40" t="n">
         <v>7000</v>
       </c>
-      <c r="Y50" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z50" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y50" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA50" s="39" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AB50" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC50" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD50" s="39" t="n">
         <v>720</v>
       </c>
-      <c r="AE50" s="40" t="n">
+      <c r="AC50" s="40" t="n">
         <v>55</v>
       </c>
-      <c r="AF50" s="40" t="n">
+      <c r="AD50" s="40" t="n">
         <v>350</v>
       </c>
-      <c r="AG50" s="39" t="n">
+      <c r="AE50" s="39" t="n">
         <v>250</v>
       </c>
-      <c r="AH50" s="32" t="n">
+      <c r="AF50" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16770,34 +16312,28 @@
       <c r="X51" s="40" t="n">
         <v>7000</v>
       </c>
-      <c r="Y51" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z51" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y51" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA51" s="39" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AB51" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC51" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD51" s="39" t="n">
         <v>680</v>
       </c>
-      <c r="AE51" s="40" t="n">
+      <c r="AC51" s="40" t="n">
         <v>55</v>
       </c>
-      <c r="AF51" s="40" t="n">
+      <c r="AD51" s="40" t="n">
         <v>350</v>
       </c>
-      <c r="AG51" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="32" t="n">
+      <c r="AE51" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="32" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -16886,34 +16422,28 @@
       <c r="X52" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y52" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z52" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y52" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA52" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB52" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC52" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD52" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE52" s="40" t="n">
+      <c r="AC52" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF52" s="40" t="n">
+      <c r="AD52" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG52" s="39" t="n">
+      <c r="AE52" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH52" s="32" t="n">
+      <c r="AF52" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17002,34 +16532,28 @@
       <c r="X53" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y53" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z53" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y53" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA53" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB53" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC53" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD53" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE53" s="40" t="n">
+      <c r="AC53" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF53" s="40" t="n">
+      <c r="AD53" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG53" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" s="32" t="n">
+      <c r="AE53" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -17118,34 +16642,28 @@
       <c r="X54" s="40" t="n">
         <v>7000</v>
       </c>
-      <c r="Y54" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z54" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y54" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="39" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AB54" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC54" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD54" s="39" t="n">
         <v>720</v>
       </c>
-      <c r="AE54" s="40" t="n">
+      <c r="AC54" s="40" t="n">
         <v>55</v>
       </c>
-      <c r="AF54" s="40" t="n">
+      <c r="AD54" s="40" t="n">
         <v>350</v>
       </c>
-      <c r="AG54" s="39" t="n">
+      <c r="AE54" s="39" t="n">
         <v>250</v>
       </c>
-      <c r="AH54" s="32" t="n">
+      <c r="AF54" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17234,34 +16752,28 @@
       <c r="X55" s="40" t="n">
         <v>7000</v>
       </c>
-      <c r="Y55" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z55" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y55" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="39" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AB55" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC55" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD55" s="39" t="n">
         <v>680</v>
       </c>
-      <c r="AE55" s="40" t="n">
+      <c r="AC55" s="40" t="n">
         <v>55</v>
       </c>
-      <c r="AF55" s="40" t="n">
+      <c r="AD55" s="40" t="n">
         <v>350</v>
       </c>
-      <c r="AG55" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" s="32" t="n">
+      <c r="AE55" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="32" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -17350,34 +16862,28 @@
       <c r="X56" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y56" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z56" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y56" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA56" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB56" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC56" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD56" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE56" s="40" t="n">
+      <c r="AC56" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF56" s="40" t="n">
+      <c r="AD56" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG56" s="39" t="n">
+      <c r="AE56" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH56" s="32" t="n">
+      <c r="AF56" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17466,34 +16972,28 @@
       <c r="X57" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y57" s="32" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Z57" s="32" t="n">
-        <v>0.84</v>
+      <c r="Y57" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB57" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD57" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE57" s="40" t="n">
+      <c r="AC57" s="40" t="n">
         <v>58</v>
       </c>
-      <c r="AF57" s="40" t="n">
+      <c r="AD57" s="40" t="n">
         <v>380</v>
       </c>
-      <c r="AG57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="32" t="n">
+      <c r="AE57" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -17582,34 +17082,28 @@
       <c r="X58" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y58" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z58" s="32" t="n">
-        <v>0.83</v>
+      <c r="Y58" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA58" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB58" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC58" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD58" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE58" s="40" t="n">
+      <c r="AC58" s="40" t="n">
         <v>56</v>
       </c>
-      <c r="AF58" s="40" t="n">
+      <c r="AD58" s="40" t="n">
         <v>450</v>
       </c>
-      <c r="AG58" s="39" t="n">
+      <c r="AE58" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH58" s="32" t="n">
+      <c r="AF58" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17698,34 +17192,28 @@
       <c r="X59" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y59" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z59" s="32" t="n">
-        <v>0.83</v>
+      <c r="Y59" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA59" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB59" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC59" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD59" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE59" s="40" t="n">
+      <c r="AC59" s="40" t="n">
         <v>56</v>
       </c>
-      <c r="AF59" s="40" t="n">
+      <c r="AD59" s="40" t="n">
         <v>450</v>
       </c>
-      <c r="AG59" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" s="32" t="n">
+      <c r="AE59" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -17814,34 +17302,28 @@
       <c r="X60" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y60" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z60" s="32" t="n">
-        <v>0.83</v>
+      <c r="Y60" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA60" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB60" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC60" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD60" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE60" s="40" t="n">
+      <c r="AC60" s="40" t="n">
         <v>56</v>
       </c>
-      <c r="AF60" s="40" t="n">
+      <c r="AD60" s="40" t="n">
         <v>450</v>
       </c>
-      <c r="AG60" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="32" t="n">
+      <c r="AE60" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -17930,34 +17412,28 @@
       <c r="X61" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y61" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z61" s="32" t="n">
-        <v>0.83</v>
+      <c r="Y61" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA61" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB61" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC61" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD61" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="AE61" s="40" t="n">
+      <c r="AC61" s="40" t="n">
         <v>56</v>
       </c>
-      <c r="AF61" s="40" t="n">
+      <c r="AD61" s="40" t="n">
         <v>450</v>
       </c>
-      <c r="AG61" s="39" t="n">
+      <c r="AE61" s="39" t="n">
         <v>320</v>
       </c>
-      <c r="AH61" s="32" t="n">
+      <c r="AF61" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18046,34 +17522,28 @@
       <c r="X62" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y62" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z62" s="32" t="n">
-        <v>0.83</v>
+      <c r="Y62" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="39" t="n">
+        <v>2</v>
       </c>
       <c r="AA62" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB62" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC62" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD62" s="39" t="n">
         <v>560</v>
       </c>
-      <c r="AE62" s="40" t="n">
+      <c r="AC62" s="40" t="n">
         <v>56</v>
       </c>
-      <c r="AF62" s="40" t="n">
+      <c r="AD62" s="40" t="n">
         <v>450</v>
       </c>
-      <c r="AG62" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" s="32" t="n">
+      <c r="AE62" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="32" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -18162,34 +17632,28 @@
       <c r="X63" s="40" t="n">
         <v>8000</v>
       </c>
-      <c r="Y63" s="32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Z63" s="32" t="n">
-        <v>0.83</v>
+      <c r="Y63" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="39" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="39" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AB63" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD63" s="39" t="n">
         <v>520</v>
       </c>
-      <c r="AE63" s="40" t="n">
+      <c r="AC63" s="40" t="n">
         <v>56</v>
       </c>
-      <c r="AF63" s="40" t="n">
+      <c r="AD63" s="40" t="n">
         <v>450</v>
       </c>
-      <c r="AG63" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="32" t="n">
+      <c r="AE63" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="32" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -18643,13 +18107,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="W4:X4"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AH4"/>
+    <mergeCell ref="A2:AF2"/>
+    <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="L4:S4"/>
-    <mergeCell ref="A2:AH2"/>
     <mergeCell ref="A66:I66"/>
     <mergeCell ref="T4:V4"/>
     <mergeCell ref="A4:F4"/>
@@ -23656,7 +23119,7 @@
     <row r="64">
       <c r="A64" s="45" t="inlineStr">
         <is>
-          <t>Historique marketing &amp; sécurisation par programme (issu du réalisé)</t>
+          <t>Historique marketing par programme (issu du réalisé) → élasticité mesurée</t>
         </is>
       </c>
     </row>
@@ -23691,11 +23154,6 @@
           <t>Élasticité mesurée</t>
         </is>
       </c>
-      <c r="G65" s="20" t="inlineStr">
-        <is>
-          <t>Sécurisation N-1</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
@@ -23716,11 +23174,8 @@
         <v>81600</v>
       </c>
       <c r="F66" s="18">
-        <f>IFERROR((C66/B66-1)/(E66/D66-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>0.88</v>
+        <f>IFERROR((C66/B66-1)/(E66/D66-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -23742,11 +23197,8 @@
         <v>92400</v>
       </c>
       <c r="F67" s="18">
-        <f>IFERROR((C67/B67-1)/(E67/D67-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>0.88</v>
+        <f>IFERROR((C67/B67-1)/(E67/D67-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -23768,11 +23220,8 @@
         <v>54080</v>
       </c>
       <c r="F68" s="18">
-        <f>IFERROR((C68/B68-1)/(E68/D68-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>0.85</v>
+        <f>IFERROR((C68/B68-1)/(E68/D68-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -23794,11 +23243,8 @@
         <v>60600</v>
       </c>
       <c r="F69" s="18">
-        <f>IFERROR((C69/B69-1)/(E69/D69-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>0.85</v>
+        <f>IFERROR((C69/B69-1)/(E69/D69-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -23820,11 +23266,8 @@
         <v>41600</v>
       </c>
       <c r="F70" s="18">
-        <f>IFERROR((C70/B70-1)/(E70/D70-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>0.87</v>
+        <f>IFERROR((C70/B70-1)/(E70/D70-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -23846,11 +23289,8 @@
         <v>16500</v>
       </c>
       <c r="F71" s="18">
-        <f>IFERROR((C71/B71-1)/(E71/D71-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>0.84</v>
+        <f>IFERROR((C71/B71-1)/(E71/D71-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -23872,11 +23312,8 @@
         <v>26240</v>
       </c>
       <c r="F72" s="18">
-        <f>IFERROR((C72/B72-1)/(E72/D72-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>0.84</v>
+        <f>IFERROR((C72/B72-1)/(E72/D72-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -23898,16 +23335,13 @@
         <v>27840</v>
       </c>
       <c r="F73" s="18">
-        <f>IFERROR((C73/B73-1)/(E73/D73-1),'01_Cadrage'!$H$29)</f>
-        <v/>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>0.83</v>
+        <f>IFERROR((C73/B73-1)/(E73/D73-1),'01_Cadrage'!$H$27)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A64:F64"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24850,12 +24284,12 @@
       </c>
       <c r="AF2" s="20" t="inlineStr">
         <is>
-          <t>SecFac</t>
+          <t>(réservé)</t>
         </is>
       </c>
       <c r="AG2" s="20" t="inlineStr">
         <is>
-          <t>SecN-1</t>
+          <t>(réservé2)</t>
         </is>
       </c>
       <c r="AH2" s="20" t="inlineStr">
@@ -24998,7 +24432,7 @@
         <v/>
       </c>
       <c r="X3" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y3" s="56">
@@ -25010,7 +24444,7 @@
         <v/>
       </c>
       <c r="AA3" s="56">
-        <f>IF(F3=1,IFERROR(H3/J3,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F3=1,IFERROR(H3/J3,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB3" s="54">
@@ -25030,11 +24464,11 @@
         <v/>
       </c>
       <c r="AF3" s="18">
-        <f>IF(E3="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG3" s="18">
-        <f>IF(E3="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C3,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH3" s="24">
@@ -25058,7 +24492,7 @@
         <v/>
       </c>
       <c r="AM3" s="22">
-        <f>AH3-AJ3-AK3-AL3-AD3*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH3-AJ3-AK3-AL3-AD3*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN3" s="56">
@@ -25168,7 +24602,7 @@
         <v/>
       </c>
       <c r="X4" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y4" s="56">
@@ -25180,7 +24614,7 @@
         <v/>
       </c>
       <c r="AA4" s="56">
-        <f>IF(F4=1,IFERROR(H4/J4,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F4=1,IFERROR(H4/J4,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB4" s="54">
@@ -25200,11 +24634,11 @@
         <v/>
       </c>
       <c r="AF4" s="18">
-        <f>IF(E4="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG4" s="18">
-        <f>IF(E4="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C4,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH4" s="24">
@@ -25228,7 +24662,7 @@
         <v/>
       </c>
       <c r="AM4" s="22">
-        <f>AH4-AJ4-AK4-AL4-AD4*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH4-AJ4-AK4-AL4-AD4*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN4" s="56">
@@ -25338,7 +24772,7 @@
         <v/>
       </c>
       <c r="X5" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y5" s="56">
@@ -25350,7 +24784,7 @@
         <v/>
       </c>
       <c r="AA5" s="56">
-        <f>IF(F5=1,IFERROR(H5/J5,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F5=1,IFERROR(H5/J5,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB5" s="54">
@@ -25370,11 +24804,11 @@
         <v/>
       </c>
       <c r="AF5" s="18">
-        <f>IF(E5="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG5" s="18">
-        <f>IF(E5="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C5,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH5" s="24">
@@ -25398,7 +24832,7 @@
         <v/>
       </c>
       <c r="AM5" s="22">
-        <f>AH5-AJ5-AK5-AL5-AD5*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH5-AJ5-AK5-AL5-AD5*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN5" s="56">
@@ -25508,7 +24942,7 @@
         <v/>
       </c>
       <c r="X6" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y6" s="56">
@@ -25520,7 +24954,7 @@
         <v/>
       </c>
       <c r="AA6" s="56">
-        <f>IF(F6=1,IFERROR(H6/J6,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F6=1,IFERROR(H6/J6,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB6" s="54">
@@ -25540,11 +24974,11 @@
         <v/>
       </c>
       <c r="AF6" s="18">
-        <f>IF(E6="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG6" s="18">
-        <f>IF(E6="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C6,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH6" s="24">
@@ -25568,7 +25002,7 @@
         <v/>
       </c>
       <c r="AM6" s="22">
-        <f>AH6-AJ6-AK6-AL6-AD6*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH6-AJ6-AK6-AL6-AD6*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN6" s="56">
@@ -25678,7 +25112,7 @@
         <v/>
       </c>
       <c r="X7" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y7" s="56">
@@ -25690,7 +25124,7 @@
         <v/>
       </c>
       <c r="AA7" s="56">
-        <f>IF(F7=1,IFERROR(H7/J7,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F7=1,IFERROR(H7/J7,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB7" s="54">
@@ -25710,11 +25144,11 @@
         <v/>
       </c>
       <c r="AF7" s="18">
-        <f>IF(E7="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG7" s="18">
-        <f>IF(E7="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C7,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH7" s="24">
@@ -25738,7 +25172,7 @@
         <v/>
       </c>
       <c r="AM7" s="22">
-        <f>AH7-AJ7-AK7-AL7-AD7*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH7-AJ7-AK7-AL7-AD7*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN7" s="56">
@@ -25848,7 +25282,7 @@
         <v/>
       </c>
       <c r="X8" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y8" s="56">
@@ -25860,7 +25294,7 @@
         <v/>
       </c>
       <c r="AA8" s="56">
-        <f>IF(F8=1,IFERROR(H8/J8,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F8=1,IFERROR(H8/J8,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB8" s="54">
@@ -25880,11 +25314,11 @@
         <v/>
       </c>
       <c r="AF8" s="18">
-        <f>IF(E8="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG8" s="18">
-        <f>IF(E8="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C8,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH8" s="24">
@@ -25908,7 +25342,7 @@
         <v/>
       </c>
       <c r="AM8" s="22">
-        <f>AH8-AJ8-AK8-AL8-AD8*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH8-AJ8-AK8-AL8-AD8*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN8" s="56">
@@ -26018,7 +25452,7 @@
         <v/>
       </c>
       <c r="X9" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y9" s="56">
@@ -26030,7 +25464,7 @@
         <v/>
       </c>
       <c r="AA9" s="56">
-        <f>IF(F9=1,IFERROR(H9/J9,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F9=1,IFERROR(H9/J9,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB9" s="54">
@@ -26050,11 +25484,11 @@
         <v/>
       </c>
       <c r="AF9" s="18">
-        <f>IF(E9="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG9" s="18">
-        <f>IF(E9="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C9,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH9" s="24">
@@ -26078,7 +25512,7 @@
         <v/>
       </c>
       <c r="AM9" s="22">
-        <f>AH9-AJ9-AK9-AL9-AD9*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH9-AJ9-AK9-AL9-AD9*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN9" s="56">
@@ -26188,7 +25622,7 @@
         <v/>
       </c>
       <c r="X10" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y10" s="56">
@@ -26200,7 +25634,7 @@
         <v/>
       </c>
       <c r="AA10" s="56">
-        <f>IF(F10=1,IFERROR(H10/J10,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F10=1,IFERROR(H10/J10,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB10" s="54">
@@ -26220,11 +25654,11 @@
         <v/>
       </c>
       <c r="AF10" s="18">
-        <f>IF(E10="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG10" s="18">
-        <f>IF(E10="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C10,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH10" s="24">
@@ -26248,7 +25682,7 @@
         <v/>
       </c>
       <c r="AM10" s="22">
-        <f>AH10-AJ10-AK10-AL10-AD10*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH10-AJ10-AK10-AL10-AD10*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN10" s="56">
@@ -26358,7 +25792,7 @@
         <v/>
       </c>
       <c r="X11" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y11" s="56">
@@ -26370,7 +25804,7 @@
         <v/>
       </c>
       <c r="AA11" s="56">
-        <f>IF(F11=1,IFERROR(H11/J11,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F11=1,IFERROR(H11/J11,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB11" s="54">
@@ -26390,11 +25824,11 @@
         <v/>
       </c>
       <c r="AF11" s="18">
-        <f>IF(E11="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG11" s="18">
-        <f>IF(E11="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C11,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH11" s="24">
@@ -26418,7 +25852,7 @@
         <v/>
       </c>
       <c r="AM11" s="22">
-        <f>AH11-AJ11-AK11-AL11-AD11*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH11-AJ11-AK11-AL11-AD11*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN11" s="56">
@@ -26528,7 +25962,7 @@
         <v/>
       </c>
       <c r="X12" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y12" s="56">
@@ -26540,7 +25974,7 @@
         <v/>
       </c>
       <c r="AA12" s="56">
-        <f>IF(F12=1,IFERROR(H12/J12,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F12=1,IFERROR(H12/J12,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB12" s="54">
@@ -26560,11 +25994,11 @@
         <v/>
       </c>
       <c r="AF12" s="18">
-        <f>IF(E12="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG12" s="18">
-        <f>IF(E12="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C12,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH12" s="24">
@@ -26588,7 +26022,7 @@
         <v/>
       </c>
       <c r="AM12" s="22">
-        <f>AH12-AJ12-AK12-AL12-AD12*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH12-AJ12-AK12-AL12-AD12*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN12" s="56">
@@ -26698,7 +26132,7 @@
         <v/>
       </c>
       <c r="X13" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y13" s="56">
@@ -26710,7 +26144,7 @@
         <v/>
       </c>
       <c r="AA13" s="56">
-        <f>IF(F13=1,IFERROR(H13/J13,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F13=1,IFERROR(H13/J13,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB13" s="54">
@@ -26730,11 +26164,11 @@
         <v/>
       </c>
       <c r="AF13" s="18">
-        <f>IF(E13="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG13" s="18">
-        <f>IF(E13="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C13,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH13" s="24">
@@ -26758,7 +26192,7 @@
         <v/>
       </c>
       <c r="AM13" s="22">
-        <f>AH13-AJ13-AK13-AL13-AD13*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH13-AJ13-AK13-AL13-AD13*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN13" s="56">
@@ -26868,7 +26302,7 @@
         <v/>
       </c>
       <c r="X14" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y14" s="56">
@@ -26880,7 +26314,7 @@
         <v/>
       </c>
       <c r="AA14" s="56">
-        <f>IF(F14=1,IFERROR(H14/J14,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F14=1,IFERROR(H14/J14,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB14" s="54">
@@ -26900,11 +26334,11 @@
         <v/>
       </c>
       <c r="AF14" s="18">
-        <f>IF(E14="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG14" s="18">
-        <f>IF(E14="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C14,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH14" s="24">
@@ -26928,7 +26362,7 @@
         <v/>
       </c>
       <c r="AM14" s="22">
-        <f>AH14-AJ14-AK14-AL14-AD14*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH14-AJ14-AK14-AL14-AD14*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN14" s="56">
@@ -27038,7 +26472,7 @@
         <v/>
       </c>
       <c r="X15" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y15" s="56">
@@ -27050,7 +26484,7 @@
         <v/>
       </c>
       <c r="AA15" s="56">
-        <f>IF(F15=1,IFERROR(H15/J15,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F15=1,IFERROR(H15/J15,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB15" s="54">
@@ -27070,11 +26504,11 @@
         <v/>
       </c>
       <c r="AF15" s="18">
-        <f>IF(E15="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG15" s="18">
-        <f>IF(E15="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C15,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH15" s="24">
@@ -27098,7 +26532,7 @@
         <v/>
       </c>
       <c r="AM15" s="22">
-        <f>AH15-AJ15-AK15-AL15-AD15*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH15-AJ15-AK15-AL15-AD15*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN15" s="56">
@@ -27208,7 +26642,7 @@
         <v/>
       </c>
       <c r="X16" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y16" s="56">
@@ -27220,7 +26654,7 @@
         <v/>
       </c>
       <c r="AA16" s="56">
-        <f>IF(F16=1,IFERROR(H16/J16,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F16=1,IFERROR(H16/J16,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB16" s="54">
@@ -27240,11 +26674,11 @@
         <v/>
       </c>
       <c r="AF16" s="18">
-        <f>IF(E16="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG16" s="18">
-        <f>IF(E16="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C16,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH16" s="24">
@@ -27268,7 +26702,7 @@
         <v/>
       </c>
       <c r="AM16" s="22">
-        <f>AH16-AJ16-AK16-AL16-AD16*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH16-AJ16-AK16-AL16-AD16*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN16" s="56">
@@ -27378,7 +26812,7 @@
         <v/>
       </c>
       <c r="X17" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y17" s="56">
@@ -27390,7 +26824,7 @@
         <v/>
       </c>
       <c r="AA17" s="56">
-        <f>IF(F17=1,IFERROR(H17/J17,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F17=1,IFERROR(H17/J17,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB17" s="54">
@@ -27410,11 +26844,11 @@
         <v/>
       </c>
       <c r="AF17" s="18">
-        <f>IF(E17="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG17" s="18">
-        <f>IF(E17="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C17,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH17" s="24">
@@ -27438,7 +26872,7 @@
         <v/>
       </c>
       <c r="AM17" s="22">
-        <f>AH17-AJ17-AK17-AL17-AD17*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH17-AJ17-AK17-AL17-AD17*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN17" s="56">
@@ -27548,7 +26982,7 @@
         <v/>
       </c>
       <c r="X18" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y18" s="56">
@@ -27560,7 +26994,7 @@
         <v/>
       </c>
       <c r="AA18" s="56">
-        <f>IF(F18=1,IFERROR(H18/J18,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F18=1,IFERROR(H18/J18,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB18" s="54">
@@ -27580,11 +27014,11 @@
         <v/>
       </c>
       <c r="AF18" s="18">
-        <f>IF(E18="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG18" s="18">
-        <f>IF(E18="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C18,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH18" s="24">
@@ -27608,7 +27042,7 @@
         <v/>
       </c>
       <c r="AM18" s="22">
-        <f>AH18-AJ18-AK18-AL18-AD18*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH18-AJ18-AK18-AL18-AD18*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN18" s="56">
@@ -27718,7 +27152,7 @@
         <v/>
       </c>
       <c r="X19" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y19" s="56">
@@ -27730,7 +27164,7 @@
         <v/>
       </c>
       <c r="AA19" s="56">
-        <f>IF(F19=1,IFERROR(H19/J19,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F19=1,IFERROR(H19/J19,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB19" s="54">
@@ -27750,11 +27184,11 @@
         <v/>
       </c>
       <c r="AF19" s="18">
-        <f>IF(E19="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG19" s="18">
-        <f>IF(E19="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C19,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH19" s="24">
@@ -27778,7 +27212,7 @@
         <v/>
       </c>
       <c r="AM19" s="22">
-        <f>AH19-AJ19-AK19-AL19-AD19*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH19-AJ19-AK19-AL19-AD19*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN19" s="56">
@@ -27888,7 +27322,7 @@
         <v/>
       </c>
       <c r="X20" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y20" s="56">
@@ -27900,7 +27334,7 @@
         <v/>
       </c>
       <c r="AA20" s="56">
-        <f>IF(F20=1,IFERROR(H20/J20,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F20=1,IFERROR(H20/J20,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB20" s="54">
@@ -27920,11 +27354,11 @@
         <v/>
       </c>
       <c r="AF20" s="18">
-        <f>IF(E20="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG20" s="18">
-        <f>IF(E20="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C20,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH20" s="24">
@@ -27948,7 +27382,7 @@
         <v/>
       </c>
       <c r="AM20" s="22">
-        <f>AH20-AJ20-AK20-AL20-AD20*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH20-AJ20-AK20-AL20-AD20*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN20" s="56">
@@ -28058,7 +27492,7 @@
         <v/>
       </c>
       <c r="X21" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y21" s="56">
@@ -28070,7 +27504,7 @@
         <v/>
       </c>
       <c r="AA21" s="56">
-        <f>IF(F21=1,IFERROR(H21/J21,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F21=1,IFERROR(H21/J21,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB21" s="54">
@@ -28090,11 +27524,11 @@
         <v/>
       </c>
       <c r="AF21" s="18">
-        <f>IF(E21="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG21" s="18">
-        <f>IF(E21="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C21,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH21" s="24">
@@ -28118,7 +27552,7 @@
         <v/>
       </c>
       <c r="AM21" s="22">
-        <f>AH21-AJ21-AK21-AL21-AD21*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH21-AJ21-AK21-AL21-AD21*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN21" s="56">
@@ -28228,7 +27662,7 @@
         <v/>
       </c>
       <c r="X22" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y22" s="56">
@@ -28240,7 +27674,7 @@
         <v/>
       </c>
       <c r="AA22" s="56">
-        <f>IF(F22=1,IFERROR(H22/J22,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F22=1,IFERROR(H22/J22,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB22" s="54">
@@ -28260,11 +27694,11 @@
         <v/>
       </c>
       <c r="AF22" s="18">
-        <f>IF(E22="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG22" s="18">
-        <f>IF(E22="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C22,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH22" s="24">
@@ -28288,7 +27722,7 @@
         <v/>
       </c>
       <c r="AM22" s="22">
-        <f>AH22-AJ22-AK22-AL22-AD22*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH22-AJ22-AK22-AL22-AD22*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN22" s="56">
@@ -28398,7 +27832,7 @@
         <v/>
       </c>
       <c r="X23" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y23" s="56">
@@ -28410,7 +27844,7 @@
         <v/>
       </c>
       <c r="AA23" s="56">
-        <f>IF(F23=1,IFERROR(H23/J23,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F23=1,IFERROR(H23/J23,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB23" s="54">
@@ -28430,11 +27864,11 @@
         <v/>
       </c>
       <c r="AF23" s="18">
-        <f>IF(E23="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG23" s="18">
-        <f>IF(E23="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C23,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH23" s="24">
@@ -28458,7 +27892,7 @@
         <v/>
       </c>
       <c r="AM23" s="22">
-        <f>AH23-AJ23-AK23-AL23-AD23*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH23-AJ23-AK23-AL23-AD23*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN23" s="56">
@@ -28568,7 +28002,7 @@
         <v/>
       </c>
       <c r="X24" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y24" s="56">
@@ -28580,7 +28014,7 @@
         <v/>
       </c>
       <c r="AA24" s="56">
-        <f>IF(F24=1,IFERROR(H24/J24,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F24=1,IFERROR(H24/J24,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB24" s="54">
@@ -28600,11 +28034,11 @@
         <v/>
       </c>
       <c r="AF24" s="18">
-        <f>IF(E24="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG24" s="18">
-        <f>IF(E24="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C24,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH24" s="24">
@@ -28628,7 +28062,7 @@
         <v/>
       </c>
       <c r="AM24" s="22">
-        <f>AH24-AJ24-AK24-AL24-AD24*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH24-AJ24-AK24-AL24-AD24*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN24" s="56">
@@ -28738,7 +28172,7 @@
         <v/>
       </c>
       <c r="X25" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y25" s="56">
@@ -28750,7 +28184,7 @@
         <v/>
       </c>
       <c r="AA25" s="56">
-        <f>IF(F25=1,IFERROR(H25/J25,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F25=1,IFERROR(H25/J25,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB25" s="54">
@@ -28770,11 +28204,11 @@
         <v/>
       </c>
       <c r="AF25" s="18">
-        <f>IF(E25="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG25" s="18">
-        <f>IF(E25="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C25,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH25" s="24">
@@ -28798,7 +28232,7 @@
         <v/>
       </c>
       <c r="AM25" s="22">
-        <f>AH25-AJ25-AK25-AL25-AD25*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH25-AJ25-AK25-AL25-AD25*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN25" s="56">
@@ -28908,7 +28342,7 @@
         <v/>
       </c>
       <c r="X26" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y26" s="56">
@@ -28920,7 +28354,7 @@
         <v/>
       </c>
       <c r="AA26" s="56">
-        <f>IF(F26=1,IFERROR(H26/J26,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F26=1,IFERROR(H26/J26,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB26" s="54">
@@ -28940,11 +28374,11 @@
         <v/>
       </c>
       <c r="AF26" s="18">
-        <f>IF(E26="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG26" s="18">
-        <f>IF(E26="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C26,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH26" s="24">
@@ -28968,7 +28402,7 @@
         <v/>
       </c>
       <c r="AM26" s="22">
-        <f>AH26-AJ26-AK26-AL26-AD26*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH26-AJ26-AK26-AL26-AD26*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN26" s="56">
@@ -29078,7 +28512,7 @@
         <v/>
       </c>
       <c r="X27" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y27" s="56">
@@ -29090,7 +28524,7 @@
         <v/>
       </c>
       <c r="AA27" s="56">
-        <f>IF(F27=1,IFERROR(H27/J27,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F27=1,IFERROR(H27/J27,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB27" s="54">
@@ -29110,11 +28544,11 @@
         <v/>
       </c>
       <c r="AF27" s="18">
-        <f>IF(E27="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG27" s="18">
-        <f>IF(E27="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C27,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH27" s="24">
@@ -29138,7 +28572,7 @@
         <v/>
       </c>
       <c r="AM27" s="22">
-        <f>AH27-AJ27-AK27-AL27-AD27*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH27-AJ27-AK27-AL27-AD27*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN27" s="56">
@@ -29248,7 +28682,7 @@
         <v/>
       </c>
       <c r="X28" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y28" s="56">
@@ -29260,7 +28694,7 @@
         <v/>
       </c>
       <c r="AA28" s="56">
-        <f>IF(F28=1,IFERROR(H28/J28,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F28=1,IFERROR(H28/J28,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB28" s="54">
@@ -29280,11 +28714,11 @@
         <v/>
       </c>
       <c r="AF28" s="18">
-        <f>IF(E28="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG28" s="18">
-        <f>IF(E28="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C28,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH28" s="24">
@@ -29308,7 +28742,7 @@
         <v/>
       </c>
       <c r="AM28" s="22">
-        <f>AH28-AJ28-AK28-AL28-AD28*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH28-AJ28-AK28-AL28-AD28*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN28" s="56">
@@ -29418,7 +28852,7 @@
         <v/>
       </c>
       <c r="X29" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y29" s="56">
@@ -29430,7 +28864,7 @@
         <v/>
       </c>
       <c r="AA29" s="56">
-        <f>IF(F29=1,IFERROR(H29/J29,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F29=1,IFERROR(H29/J29,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB29" s="54">
@@ -29450,11 +28884,11 @@
         <v/>
       </c>
       <c r="AF29" s="18">
-        <f>IF(E29="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG29" s="18">
-        <f>IF(E29="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C29,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH29" s="24">
@@ -29478,7 +28912,7 @@
         <v/>
       </c>
       <c r="AM29" s="22">
-        <f>AH29-AJ29-AK29-AL29-AD29*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH29-AJ29-AK29-AL29-AD29*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN29" s="56">
@@ -29588,7 +29022,7 @@
         <v/>
       </c>
       <c r="X30" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y30" s="56">
@@ -29600,7 +29034,7 @@
         <v/>
       </c>
       <c r="AA30" s="56">
-        <f>IF(F30=1,IFERROR(H30/J30,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F30=1,IFERROR(H30/J30,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB30" s="54">
@@ -29620,11 +29054,11 @@
         <v/>
       </c>
       <c r="AF30" s="18">
-        <f>IF(E30="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG30" s="18">
-        <f>IF(E30="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C30,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH30" s="24">
@@ -29648,7 +29082,7 @@
         <v/>
       </c>
       <c r="AM30" s="22">
-        <f>AH30-AJ30-AK30-AL30-AD30*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH30-AJ30-AK30-AL30-AD30*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN30" s="56">
@@ -29758,7 +29192,7 @@
         <v/>
       </c>
       <c r="X31" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y31" s="56">
@@ -29770,7 +29204,7 @@
         <v/>
       </c>
       <c r="AA31" s="56">
-        <f>IF(F31=1,IFERROR(H31/J31,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F31=1,IFERROR(H31/J31,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB31" s="54">
@@ -29790,11 +29224,11 @@
         <v/>
       </c>
       <c r="AF31" s="18">
-        <f>IF(E31="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG31" s="18">
-        <f>IF(E31="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C31,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH31" s="24">
@@ -29818,7 +29252,7 @@
         <v/>
       </c>
       <c r="AM31" s="22">
-        <f>AH31-AJ31-AK31-AL31-AD31*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH31-AJ31-AK31-AL31-AD31*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN31" s="56">
@@ -29928,7 +29362,7 @@
         <v/>
       </c>
       <c r="X32" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y32" s="56">
@@ -29940,7 +29374,7 @@
         <v/>
       </c>
       <c r="AA32" s="56">
-        <f>IF(F32=1,IFERROR(H32/J32,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F32=1,IFERROR(H32/J32,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB32" s="54">
@@ -29960,11 +29394,11 @@
         <v/>
       </c>
       <c r="AF32" s="18">
-        <f>IF(E32="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG32" s="18">
-        <f>IF(E32="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C32,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH32" s="24">
@@ -29988,7 +29422,7 @@
         <v/>
       </c>
       <c r="AM32" s="22">
-        <f>AH32-AJ32-AK32-AL32-AD32*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH32-AJ32-AK32-AL32-AD32*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN32" s="56">
@@ -30098,7 +29532,7 @@
         <v/>
       </c>
       <c r="X33" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y33" s="56">
@@ -30110,7 +29544,7 @@
         <v/>
       </c>
       <c r="AA33" s="56">
-        <f>IF(F33=1,IFERROR(H33/J33,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F33=1,IFERROR(H33/J33,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB33" s="54">
@@ -30130,11 +29564,11 @@
         <v/>
       </c>
       <c r="AF33" s="18">
-        <f>IF(E33="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG33" s="18">
-        <f>IF(E33="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C33,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH33" s="24">
@@ -30158,7 +29592,7 @@
         <v/>
       </c>
       <c r="AM33" s="22">
-        <f>AH33-AJ33-AK33-AL33-AD33*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH33-AJ33-AK33-AL33-AD33*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN33" s="56">
@@ -30268,7 +29702,7 @@
         <v/>
       </c>
       <c r="X34" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y34" s="56">
@@ -30280,7 +29714,7 @@
         <v/>
       </c>
       <c r="AA34" s="56">
-        <f>IF(F34=1,IFERROR(H34/J34,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F34=1,IFERROR(H34/J34,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB34" s="54">
@@ -30300,11 +29734,11 @@
         <v/>
       </c>
       <c r="AF34" s="18">
-        <f>IF(E34="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG34" s="18">
-        <f>IF(E34="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C34,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH34" s="24">
@@ -30328,7 +29762,7 @@
         <v/>
       </c>
       <c r="AM34" s="22">
-        <f>AH34-AJ34-AK34-AL34-AD34*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH34-AJ34-AK34-AL34-AD34*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN34" s="56">
@@ -30438,7 +29872,7 @@
         <v/>
       </c>
       <c r="X35" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y35" s="56">
@@ -30450,7 +29884,7 @@
         <v/>
       </c>
       <c r="AA35" s="56">
-        <f>IF(F35=1,IFERROR(H35/J35,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F35=1,IFERROR(H35/J35,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB35" s="54">
@@ -30470,11 +29904,11 @@
         <v/>
       </c>
       <c r="AF35" s="18">
-        <f>IF(E35="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG35" s="18">
-        <f>IF(E35="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C35,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH35" s="24">
@@ -30498,7 +29932,7 @@
         <v/>
       </c>
       <c r="AM35" s="22">
-        <f>AH35-AJ35-AK35-AL35-AD35*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH35-AJ35-AK35-AL35-AD35*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN35" s="56">
@@ -30608,7 +30042,7 @@
         <v/>
       </c>
       <c r="X36" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y36" s="56">
@@ -30620,7 +30054,7 @@
         <v/>
       </c>
       <c r="AA36" s="56">
-        <f>IF(F36=1,IFERROR(H36/J36,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F36=1,IFERROR(H36/J36,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB36" s="54">
@@ -30640,11 +30074,11 @@
         <v/>
       </c>
       <c r="AF36" s="18">
-        <f>IF(E36="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG36" s="18">
-        <f>IF(E36="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C36,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH36" s="24">
@@ -30668,7 +30102,7 @@
         <v/>
       </c>
       <c r="AM36" s="22">
-        <f>AH36-AJ36-AK36-AL36-AD36*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH36-AJ36-AK36-AL36-AD36*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN36" s="56">
@@ -30778,7 +30212,7 @@
         <v/>
       </c>
       <c r="X37" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y37" s="56">
@@ -30790,7 +30224,7 @@
         <v/>
       </c>
       <c r="AA37" s="56">
-        <f>IF(F37=1,IFERROR(H37/J37,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F37=1,IFERROR(H37/J37,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB37" s="54">
@@ -30810,11 +30244,11 @@
         <v/>
       </c>
       <c r="AF37" s="18">
-        <f>IF(E37="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG37" s="18">
-        <f>IF(E37="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C37,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH37" s="24">
@@ -30838,7 +30272,7 @@
         <v/>
       </c>
       <c r="AM37" s="22">
-        <f>AH37-AJ37-AK37-AL37-AD37*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH37-AJ37-AK37-AL37-AD37*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN37" s="56">
@@ -30948,7 +30382,7 @@
         <v/>
       </c>
       <c r="X38" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y38" s="56">
@@ -30960,7 +30394,7 @@
         <v/>
       </c>
       <c r="AA38" s="56">
-        <f>IF(F38=1,IFERROR(H38/J38,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F38=1,IFERROR(H38/J38,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB38" s="54">
@@ -30980,11 +30414,11 @@
         <v/>
       </c>
       <c r="AF38" s="18">
-        <f>IF(E38="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG38" s="18">
-        <f>IF(E38="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C38,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH38" s="24">
@@ -31008,7 +30442,7 @@
         <v/>
       </c>
       <c r="AM38" s="22">
-        <f>AH38-AJ38-AK38-AL38-AD38*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH38-AJ38-AK38-AL38-AD38*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN38" s="56">
@@ -31118,7 +30552,7 @@
         <v/>
       </c>
       <c r="X39" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y39" s="56">
@@ -31130,7 +30564,7 @@
         <v/>
       </c>
       <c r="AA39" s="56">
-        <f>IF(F39=1,IFERROR(H39/J39,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F39=1,IFERROR(H39/J39,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB39" s="54">
@@ -31150,11 +30584,11 @@
         <v/>
       </c>
       <c r="AF39" s="18">
-        <f>IF(E39="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG39" s="18">
-        <f>IF(E39="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C39,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH39" s="24">
@@ -31178,7 +30612,7 @@
         <v/>
       </c>
       <c r="AM39" s="22">
-        <f>AH39-AJ39-AK39-AL39-AD39*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH39-AJ39-AK39-AL39-AD39*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN39" s="56">
@@ -31288,7 +30722,7 @@
         <v/>
       </c>
       <c r="X40" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y40" s="56">
@@ -31300,7 +30734,7 @@
         <v/>
       </c>
       <c r="AA40" s="56">
-        <f>IF(F40=1,IFERROR(H40/J40,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F40=1,IFERROR(H40/J40,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB40" s="54">
@@ -31320,11 +30754,11 @@
         <v/>
       </c>
       <c r="AF40" s="18">
-        <f>IF(E40="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG40" s="18">
-        <f>IF(E40="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C40,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH40" s="24">
@@ -31348,7 +30782,7 @@
         <v/>
       </c>
       <c r="AM40" s="22">
-        <f>AH40-AJ40-AK40-AL40-AD40*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH40-AJ40-AK40-AL40-AD40*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN40" s="56">
@@ -31458,7 +30892,7 @@
         <v/>
       </c>
       <c r="X41" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y41" s="56">
@@ -31470,7 +30904,7 @@
         <v/>
       </c>
       <c r="AA41" s="56">
-        <f>IF(F41=1,IFERROR(H41/J41,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F41=1,IFERROR(H41/J41,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB41" s="54">
@@ -31490,11 +30924,11 @@
         <v/>
       </c>
       <c r="AF41" s="18">
-        <f>IF(E41="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG41" s="18">
-        <f>IF(E41="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C41,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH41" s="24">
@@ -31518,7 +30952,7 @@
         <v/>
       </c>
       <c r="AM41" s="22">
-        <f>AH41-AJ41-AK41-AL41-AD41*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH41-AJ41-AK41-AL41-AD41*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN41" s="56">
@@ -31628,7 +31062,7 @@
         <v/>
       </c>
       <c r="X42" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y42" s="56">
@@ -31640,7 +31074,7 @@
         <v/>
       </c>
       <c r="AA42" s="56">
-        <f>IF(F42=1,IFERROR(H42/J42,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F42=1,IFERROR(H42/J42,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB42" s="54">
@@ -31660,11 +31094,11 @@
         <v/>
       </c>
       <c r="AF42" s="18">
-        <f>IF(E42="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG42" s="18">
-        <f>IF(E42="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C42,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH42" s="24">
@@ -31688,7 +31122,7 @@
         <v/>
       </c>
       <c r="AM42" s="22">
-        <f>AH42-AJ42-AK42-AL42-AD42*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH42-AJ42-AK42-AL42-AD42*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN42" s="56">
@@ -31798,7 +31232,7 @@
         <v/>
       </c>
       <c r="X43" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y43" s="56">
@@ -31810,7 +31244,7 @@
         <v/>
       </c>
       <c r="AA43" s="56">
-        <f>IF(F43=1,IFERROR(H43/J43,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F43=1,IFERROR(H43/J43,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB43" s="54">
@@ -31830,11 +31264,11 @@
         <v/>
       </c>
       <c r="AF43" s="18">
-        <f>IF(E43="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG43" s="18">
-        <f>IF(E43="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C43,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH43" s="24">
@@ -31858,7 +31292,7 @@
         <v/>
       </c>
       <c r="AM43" s="22">
-        <f>AH43-AJ43-AK43-AL43-AD43*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH43-AJ43-AK43-AL43-AD43*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN43" s="56">
@@ -31968,7 +31402,7 @@
         <v/>
       </c>
       <c r="X44" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y44" s="56">
@@ -31980,7 +31414,7 @@
         <v/>
       </c>
       <c r="AA44" s="56">
-        <f>IF(F44=1,IFERROR(H44/J44,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F44=1,IFERROR(H44/J44,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB44" s="54">
@@ -32000,11 +31434,11 @@
         <v/>
       </c>
       <c r="AF44" s="18">
-        <f>IF(E44="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG44" s="18">
-        <f>IF(E44="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C44,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH44" s="24">
@@ -32028,7 +31462,7 @@
         <v/>
       </c>
       <c r="AM44" s="22">
-        <f>AH44-AJ44-AK44-AL44-AD44*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH44-AJ44-AK44-AL44-AD44*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN44" s="56">
@@ -32138,7 +31572,7 @@
         <v/>
       </c>
       <c r="X45" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y45" s="56">
@@ -32150,7 +31584,7 @@
         <v/>
       </c>
       <c r="AA45" s="56">
-        <f>IF(F45=1,IFERROR(H45/J45,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F45=1,IFERROR(H45/J45,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB45" s="54">
@@ -32170,11 +31604,11 @@
         <v/>
       </c>
       <c r="AF45" s="18">
-        <f>IF(E45="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG45" s="18">
-        <f>IF(E45="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C45,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH45" s="24">
@@ -32198,7 +31632,7 @@
         <v/>
       </c>
       <c r="AM45" s="22">
-        <f>AH45-AJ45-AK45-AL45-AD45*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH45-AJ45-AK45-AL45-AD45*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN45" s="56">
@@ -32308,7 +31742,7 @@
         <v/>
       </c>
       <c r="X46" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y46" s="56">
@@ -32320,7 +31754,7 @@
         <v/>
       </c>
       <c r="AA46" s="56">
-        <f>IF(F46=1,IFERROR(H46/J46,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F46=1,IFERROR(H46/J46,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB46" s="54">
@@ -32340,11 +31774,11 @@
         <v/>
       </c>
       <c r="AF46" s="18">
-        <f>IF(E46="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG46" s="18">
-        <f>IF(E46="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C46,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH46" s="24">
@@ -32368,7 +31802,7 @@
         <v/>
       </c>
       <c r="AM46" s="22">
-        <f>AH46-AJ46-AK46-AL46-AD46*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH46-AJ46-AK46-AL46-AD46*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN46" s="56">
@@ -32478,7 +31912,7 @@
         <v/>
       </c>
       <c r="X47" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y47" s="56">
@@ -32490,7 +31924,7 @@
         <v/>
       </c>
       <c r="AA47" s="56">
-        <f>IF(F47=1,IFERROR(H47/J47,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F47=1,IFERROR(H47/J47,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB47" s="54">
@@ -32510,11 +31944,11 @@
         <v/>
       </c>
       <c r="AF47" s="18">
-        <f>IF(E47="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG47" s="18">
-        <f>IF(E47="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C47,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH47" s="24">
@@ -32538,7 +31972,7 @@
         <v/>
       </c>
       <c r="AM47" s="22">
-        <f>AH47-AJ47-AK47-AL47-AD47*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH47-AJ47-AK47-AL47-AD47*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN47" s="56">
@@ -32648,7 +32082,7 @@
         <v/>
       </c>
       <c r="X48" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y48" s="56">
@@ -32660,7 +32094,7 @@
         <v/>
       </c>
       <c r="AA48" s="56">
-        <f>IF(F48=1,IFERROR(H48/J48,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F48=1,IFERROR(H48/J48,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB48" s="54">
@@ -32680,11 +32114,11 @@
         <v/>
       </c>
       <c r="AF48" s="18">
-        <f>IF(E48="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG48" s="18">
-        <f>IF(E48="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C48,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH48" s="24">
@@ -32708,7 +32142,7 @@
         <v/>
       </c>
       <c r="AM48" s="22">
-        <f>AH48-AJ48-AK48-AL48-AD48*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH48-AJ48-AK48-AL48-AD48*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN48" s="56">
@@ -32818,7 +32252,7 @@
         <v/>
       </c>
       <c r="X49" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y49" s="56">
@@ -32830,7 +32264,7 @@
         <v/>
       </c>
       <c r="AA49" s="56">
-        <f>IF(F49=1,IFERROR(H49/J49,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F49=1,IFERROR(H49/J49,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB49" s="54">
@@ -32850,11 +32284,11 @@
         <v/>
       </c>
       <c r="AF49" s="18">
-        <f>IF(E49="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG49" s="18">
-        <f>IF(E49="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C49,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH49" s="24">
@@ -32878,7 +32312,7 @@
         <v/>
       </c>
       <c r="AM49" s="22">
-        <f>AH49-AJ49-AK49-AL49-AD49*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH49-AJ49-AK49-AL49-AD49*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN49" s="56">
@@ -32988,7 +32422,7 @@
         <v/>
       </c>
       <c r="X50" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y50" s="56">
@@ -33000,7 +32434,7 @@
         <v/>
       </c>
       <c r="AA50" s="56">
-        <f>IF(F50=1,IFERROR(H50/J50,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F50=1,IFERROR(H50/J50,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB50" s="54">
@@ -33020,11 +32454,11 @@
         <v/>
       </c>
       <c r="AF50" s="18">
-        <f>IF(E50="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG50" s="18">
-        <f>IF(E50="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C50,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH50" s="24">
@@ -33048,7 +32482,7 @@
         <v/>
       </c>
       <c r="AM50" s="22">
-        <f>AH50-AJ50-AK50-AL50-AD50*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH50-AJ50-AK50-AL50-AD50*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN50" s="56">
@@ -33158,7 +32592,7 @@
         <v/>
       </c>
       <c r="X51" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y51" s="56">
@@ -33170,7 +32604,7 @@
         <v/>
       </c>
       <c r="AA51" s="56">
-        <f>IF(F51=1,IFERROR(H51/J51,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F51=1,IFERROR(H51/J51,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB51" s="54">
@@ -33190,11 +32624,11 @@
         <v/>
       </c>
       <c r="AF51" s="18">
-        <f>IF(E51="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG51" s="18">
-        <f>IF(E51="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C51,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH51" s="24">
@@ -33218,7 +32652,7 @@
         <v/>
       </c>
       <c r="AM51" s="22">
-        <f>AH51-AJ51-AK51-AL51-AD51*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH51-AJ51-AK51-AL51-AD51*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN51" s="56">
@@ -33328,7 +32762,7 @@
         <v/>
       </c>
       <c r="X52" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y52" s="56">
@@ -33340,7 +32774,7 @@
         <v/>
       </c>
       <c r="AA52" s="56">
-        <f>IF(F52=1,IFERROR(H52/J52,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F52=1,IFERROR(H52/J52,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB52" s="54">
@@ -33360,11 +32794,11 @@
         <v/>
       </c>
       <c r="AF52" s="18">
-        <f>IF(E52="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG52" s="18">
-        <f>IF(E52="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C52,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH52" s="24">
@@ -33388,7 +32822,7 @@
         <v/>
       </c>
       <c r="AM52" s="22">
-        <f>AH52-AJ52-AK52-AL52-AD52*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH52-AJ52-AK52-AL52-AD52*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN52" s="56">
@@ -33498,7 +32932,7 @@
         <v/>
       </c>
       <c r="X53" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y53" s="56">
@@ -33510,7 +32944,7 @@
         <v/>
       </c>
       <c r="AA53" s="56">
-        <f>IF(F53=1,IFERROR(H53/J53,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F53=1,IFERROR(H53/J53,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB53" s="54">
@@ -33530,11 +32964,11 @@
         <v/>
       </c>
       <c r="AF53" s="18">
-        <f>IF(E53="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG53" s="18">
-        <f>IF(E53="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C53,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH53" s="24">
@@ -33558,7 +32992,7 @@
         <v/>
       </c>
       <c r="AM53" s="22">
-        <f>AH53-AJ53-AK53-AL53-AD53*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH53-AJ53-AK53-AL53-AD53*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN53" s="56">
@@ -33668,7 +33102,7 @@
         <v/>
       </c>
       <c r="X54" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y54" s="56">
@@ -33680,7 +33114,7 @@
         <v/>
       </c>
       <c r="AA54" s="56">
-        <f>IF(F54=1,IFERROR(H54/J54,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F54=1,IFERROR(H54/J54,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB54" s="54">
@@ -33700,11 +33134,11 @@
         <v/>
       </c>
       <c r="AF54" s="18">
-        <f>IF(E54="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG54" s="18">
-        <f>IF(E54="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C54,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH54" s="24">
@@ -33728,7 +33162,7 @@
         <v/>
       </c>
       <c r="AM54" s="22">
-        <f>AH54-AJ54-AK54-AL54-AD54*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH54-AJ54-AK54-AL54-AD54*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN54" s="56">
@@ -33838,7 +33272,7 @@
         <v/>
       </c>
       <c r="X55" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y55" s="56">
@@ -33850,7 +33284,7 @@
         <v/>
       </c>
       <c r="AA55" s="56">
-        <f>IF(F55=1,IFERROR(H55/J55,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F55=1,IFERROR(H55/J55,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB55" s="54">
@@ -33870,11 +33304,11 @@
         <v/>
       </c>
       <c r="AF55" s="18">
-        <f>IF(E55="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG55" s="18">
-        <f>IF(E55="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C55,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH55" s="24">
@@ -33898,7 +33332,7 @@
         <v/>
       </c>
       <c r="AM55" s="22">
-        <f>AH55-AJ55-AK55-AL55-AD55*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH55-AJ55-AK55-AL55-AD55*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN55" s="56">
@@ -34008,7 +33442,7 @@
         <v/>
       </c>
       <c r="X56" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y56" s="56">
@@ -34020,7 +33454,7 @@
         <v/>
       </c>
       <c r="AA56" s="56">
-        <f>IF(F56=1,IFERROR(H56/J56,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F56=1,IFERROR(H56/J56,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB56" s="54">
@@ -34040,11 +33474,11 @@
         <v/>
       </c>
       <c r="AF56" s="18">
-        <f>IF(E56="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG56" s="18">
-        <f>IF(E56="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C56,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH56" s="24">
@@ -34068,7 +33502,7 @@
         <v/>
       </c>
       <c r="AM56" s="22">
-        <f>AH56-AJ56-AK56-AL56-AD56*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH56-AJ56-AK56-AL56-AD56*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN56" s="56">
@@ -34178,7 +33612,7 @@
         <v/>
       </c>
       <c r="X57" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y57" s="56">
@@ -34190,7 +33624,7 @@
         <v/>
       </c>
       <c r="AA57" s="56">
-        <f>IF(F57=1,IFERROR(H57/J57,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F57=1,IFERROR(H57/J57,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB57" s="54">
@@ -34210,11 +33644,11 @@
         <v/>
       </c>
       <c r="AF57" s="18">
-        <f>IF(E57="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG57" s="18">
-        <f>IF(E57="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C57,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH57" s="24">
@@ -34238,7 +33672,7 @@
         <v/>
       </c>
       <c r="AM57" s="22">
-        <f>AH57-AJ57-AK57-AL57-AD57*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH57-AJ57-AK57-AL57-AD57*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN57" s="56">
@@ -34348,7 +33782,7 @@
         <v/>
       </c>
       <c r="X58" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y58" s="56">
@@ -34360,7 +33794,7 @@
         <v/>
       </c>
       <c r="AA58" s="56">
-        <f>IF(F58=1,IFERROR(H58/J58,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F58=1,IFERROR(H58/J58,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB58" s="54">
@@ -34380,11 +33814,11 @@
         <v/>
       </c>
       <c r="AF58" s="18">
-        <f>IF(E58="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG58" s="18">
-        <f>IF(E58="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C58,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH58" s="24">
@@ -34408,7 +33842,7 @@
         <v/>
       </c>
       <c r="AM58" s="22">
-        <f>AH58-AJ58-AK58-AL58-AD58*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH58-AJ58-AK58-AL58-AD58*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN58" s="56">
@@ -34518,7 +33952,7 @@
         <v/>
       </c>
       <c r="X59" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y59" s="56">
@@ -34530,7 +33964,7 @@
         <v/>
       </c>
       <c r="AA59" s="56">
-        <f>IF(F59=1,IFERROR(H59/J59,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F59=1,IFERROR(H59/J59,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB59" s="54">
@@ -34550,11 +33984,11 @@
         <v/>
       </c>
       <c r="AF59" s="18">
-        <f>IF(E59="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG59" s="18">
-        <f>IF(E59="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C59,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH59" s="24">
@@ -34578,7 +34012,7 @@
         <v/>
       </c>
       <c r="AM59" s="22">
-        <f>AH59-AJ59-AK59-AL59-AD59*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH59-AJ59-AK59-AL59-AD59*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN59" s="56">
@@ -34688,7 +34122,7 @@
         <v/>
       </c>
       <c r="X60" s="18">
-        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$29)</f>
+        <f>IFERROR(INDEX('06_Historique'!$F$66:$F$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$27)</f>
         <v/>
       </c>
       <c r="Y60" s="56">
@@ -34700,7 +34134,7 @@
         <v/>
       </c>
       <c r="AA60" s="56">
-        <f>IF(F60=1,IFERROR(H60/J60,'01_Cadrage'!$H$30)+'01_Cadrage'!$H$18,0)</f>
+        <f>IF(F60=1,IFERROR(H60/J60,'01_Cadrage'!$H$28)+'01_Cadrage'!$H$18,0)</f>
         <v/>
       </c>
       <c r="AB60" s="54">
@@ -34720,11 +34154,11 @@
         <v/>
       </c>
       <c r="AF60" s="18">
-        <f>IF(E60="ALT",'01_Cadrage'!$H$28+(1-'01_Cadrage'!$H$28)*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AG60" s="18">
-        <f>IF(E60="ALT",IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28)+(1-IFERROR(INDEX('06_Historique'!$G$66:$G$73,MATCH(C60,'06_Historique'!$A$66:$A$73,0)),'01_Cadrage'!$H$28))*'01_Cadrage'!$H$26,1)</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="AH60" s="24">
@@ -34748,7 +34182,7 @@
         <v/>
       </c>
       <c r="AM60" s="22">
-        <f>AH60-AJ60-AK60-AL60-AD60*'01_Cadrage'!$H$27*(1+'01_Cadrage'!$H$20)</f>
+        <f>AH60-AJ60-AK60-AL60-AD60*'01_Cadrage'!$H$26*(1+'01_Cadrage'!$H$20)</f>
         <v/>
       </c>
       <c r="AN60" s="56">
@@ -34921,7 +34355,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Tarif &amp; financement alternance : tarif budget, facteur sécurisation, CA budget</t>
+          <t>Tarif &amp; CA budget : tarif budget, CA budget</t>
         </is>
       </c>
     </row>
